--- a/Ekta_Schedule_With_Matchups.xlsx
+++ b/Ekta_Schedule_With_Matchups.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TT Women's Singles" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table Tennis Singles Men" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table Tennis Doubles" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Carrom Singles Men" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Carrom Singles Women" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Carrom Doubles" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pool" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chess" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Squash" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Overview" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="TT Women's Singles" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Table Tennis Singles Men" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Table Tennis Doubles" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Carrom Singles Men" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Carrom Singles Women" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Carrom Doubles" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Pool" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Chess" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Squash" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -26,7 +26,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -79,8 +79,12 @@
       <b val="1"/>
       <sz val="11"/>
     </font>
+    <font/>
+    <font>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="17">
+  <fills count="23">
     <fill>
       <patternFill/>
     </fill>
@@ -174,8 +178,38 @@
         <bgColor rgb="00F8CBAD"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00203864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00B4C7E7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00366092"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0070AD47"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -231,11 +265,12 @@
       <bottom style="thin"/>
       <diagonal/>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -303,6 +338,35 @@
     <xf numFmtId="0" fontId="10" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1391,7 +1455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F65"/>
+  <dimension ref="A1:G65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1404,1337 +1468,1426 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="29" t="inlineStr">
         <is>
           <t>SQUASH TOURNAMENT - PLAYER GROUPS</t>
         </is>
       </c>
+      <c r="B1" s="30" t="n"/>
+      <c r="C1" s="30" t="n"/>
+      <c r="D1" s="30" t="n"/>
+      <c r="E1" s="31" t="n"/>
+      <c r="F1" s="31" t="n"/>
+      <c r="G1" s="31" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="31" t="n"/>
+      <c r="B2" s="31" t="n"/>
+      <c r="C2" s="31" t="n"/>
+      <c r="D2" s="31" t="n"/>
+      <c r="E2" s="31" t="n"/>
+      <c r="F2" s="31" t="n"/>
+      <c r="G2" s="31" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="32" t="inlineStr">
         <is>
           <t>UNDER 15 (7 Players) - SINGLE ELIMINATION KNOCKOUT</t>
         </is>
       </c>
+      <c r="B3" s="33" t="n"/>
+      <c r="C3" s="33" t="n"/>
+      <c r="D3" s="33" t="n"/>
+      <c r="E3" s="31" t="n"/>
+      <c r="F3" s="31" t="n"/>
+      <c r="G3" s="31" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="34" t="inlineStr">
         <is>
           <t>S.No</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="34" t="inlineStr">
         <is>
           <t>Player Name</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="34" t="inlineStr">
         <is>
           <t>Age</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="34" t="inlineStr">
         <is>
           <t>Group/Seed</t>
         </is>
       </c>
+      <c r="E4" s="31" t="n"/>
+      <c r="F4" s="31" t="n"/>
+      <c r="G4" s="31" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="n">
+      <c r="A5" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="35" t="inlineStr">
         <is>
           <t>Shaurya Tripathi</t>
         </is>
       </c>
-      <c r="C5" s="8" t="n">
+      <c r="C5" s="35" t="n">
         <v>10</v>
       </c>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="D5" s="35" t="inlineStr">
         <is>
           <t>Round 1</t>
         </is>
       </c>
+      <c r="E5" s="31" t="n"/>
+      <c r="F5" s="31" t="n"/>
+      <c r="G5" s="31" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="n">
+      <c r="A6" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="35" t="inlineStr">
         <is>
           <t>Parth yadav</t>
         </is>
       </c>
-      <c r="C6" s="8" t="n">
+      <c r="C6" s="35" t="n">
         <v>10</v>
       </c>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="D6" s="35" t="inlineStr">
         <is>
           <t>Round 1</t>
         </is>
       </c>
+      <c r="E6" s="31" t="n"/>
+      <c r="F6" s="31" t="n"/>
+      <c r="G6" s="31" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="n">
+      <c r="A7" s="35" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="35" t="inlineStr">
         <is>
           <t>Peher Krunal Shah</t>
         </is>
       </c>
-      <c r="C7" s="8" t="n">
+      <c r="C7" s="35" t="n">
         <v>12</v>
       </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="D7" s="35" t="inlineStr">
         <is>
           <t>Round 1</t>
         </is>
       </c>
+      <c r="E7" s="31" t="n"/>
+      <c r="F7" s="31" t="n"/>
+      <c r="G7" s="31" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="n">
+      <c r="A8" s="35" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="35" t="inlineStr">
         <is>
           <t>Aadit Joshi</t>
         </is>
       </c>
-      <c r="C8" s="8" t="n">
+      <c r="C8" s="35" t="n">
         <v>12</v>
       </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="D8" s="35" t="inlineStr">
         <is>
           <t>Round 1</t>
         </is>
       </c>
+      <c r="E8" s="31" t="n"/>
+      <c r="F8" s="31" t="n"/>
+      <c r="G8" s="31" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="n">
+      <c r="A9" s="35" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="35" t="inlineStr">
         <is>
           <t>Viaan Neema</t>
         </is>
       </c>
-      <c r="C9" s="8" t="n">
+      <c r="C9" s="35" t="n">
         <v>12</v>
       </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="D9" s="35" t="inlineStr">
         <is>
           <t>Round 1</t>
         </is>
       </c>
+      <c r="E9" s="31" t="n"/>
+      <c r="F9" s="31" t="n"/>
+      <c r="G9" s="31" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="n">
+      <c r="A10" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="35" t="inlineStr">
         <is>
           <t>Yash agarwal</t>
         </is>
       </c>
-      <c r="C10" s="8" t="n">
+      <c r="C10" s="35" t="n">
         <v>13</v>
       </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="D10" s="35" t="inlineStr">
         <is>
           <t>Round 1</t>
         </is>
       </c>
+      <c r="E10" s="31" t="n"/>
+      <c r="F10" s="31" t="n"/>
+      <c r="G10" s="31" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="n">
+      <c r="A11" s="35" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="35" t="inlineStr">
         <is>
           <t>Hridh jhala</t>
         </is>
       </c>
-      <c r="C11" s="8" t="n">
+      <c r="C11" s="35" t="n">
         <v>13</v>
       </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="D11" s="35" t="inlineStr">
         <is>
           <t>BYE (Semifinal)</t>
         </is>
       </c>
+      <c r="E11" s="31" t="n"/>
+      <c r="F11" s="31" t="n"/>
+      <c r="G11" s="31" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="31" t="n"/>
+      <c r="B12" s="31" t="n"/>
+      <c r="C12" s="31" t="n"/>
+      <c r="D12" s="31" t="n"/>
+      <c r="E12" s="31" t="n"/>
+      <c r="F12" s="31" t="n"/>
+      <c r="G12" s="31" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>ABOVE 15 (9 Players) - TWO POOL GROUPS</t>
-        </is>
-      </c>
+      <c r="A13" s="32" t="inlineStr">
+        <is>
+          <t>UNDER 25 (3 Players) - ROUND ROBIN + FINAL</t>
+        </is>
+      </c>
+      <c r="B13" s="33" t="n"/>
+      <c r="C13" s="33" t="n"/>
+      <c r="D13" s="33" t="n"/>
+      <c r="E13" s="31" t="n"/>
+      <c r="F13" s="31" t="n"/>
+      <c r="G13" s="31" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>GROUP A (5 Players) - Round Robin Pool</t>
-        </is>
-      </c>
+      <c r="A14" s="34" t="inlineStr">
+        <is>
+          <t>S.No</t>
+        </is>
+      </c>
+      <c r="B14" s="34" t="inlineStr">
+        <is>
+          <t>Player Name</t>
+        </is>
+      </c>
+      <c r="C14" s="34" t="inlineStr">
+        <is>
+          <t>Age</t>
+        </is>
+      </c>
+      <c r="D14" s="34" t="inlineStr">
+        <is>
+          <t>Group/Seed</t>
+        </is>
+      </c>
+      <c r="E14" s="31" t="n"/>
+      <c r="F14" s="31" t="n"/>
+      <c r="G14" s="31" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="B15" s="35" t="inlineStr">
+        <is>
+          <t>Aaditya Kumar</t>
+        </is>
+      </c>
+      <c r="C15" s="35" t="n">
+        <v>17</v>
+      </c>
+      <c r="D15" s="35" t="inlineStr">
+        <is>
+          <t>Round Robin</t>
+        </is>
+      </c>
+      <c r="E15" s="31" t="n"/>
+      <c r="F15" s="31" t="n"/>
+      <c r="G15" s="31" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="B16" s="35" t="inlineStr">
+        <is>
+          <t>Hryday Goyal</t>
+        </is>
+      </c>
+      <c r="C16" s="35" t="n">
+        <v>20</v>
+      </c>
+      <c r="D16" s="35" t="inlineStr">
+        <is>
+          <t>Round Robin</t>
+        </is>
+      </c>
+      <c r="E16" s="31" t="n"/>
+      <c r="F16" s="31" t="n"/>
+      <c r="G16" s="31" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="B17" s="35" t="inlineStr">
+        <is>
+          <t>Shravan Gajera</t>
+        </is>
+      </c>
+      <c r="C17" s="35" t="n">
+        <v>23</v>
+      </c>
+      <c r="D17" s="35" t="inlineStr">
+        <is>
+          <t>Round Robin</t>
+        </is>
+      </c>
+      <c r="E17" s="31" t="n"/>
+      <c r="F17" s="31" t="n"/>
+      <c r="G17" s="31" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="31" t="n"/>
+      <c r="B18" s="31" t="n"/>
+      <c r="C18" s="31" t="n"/>
+      <c r="D18" s="31" t="n"/>
+      <c r="E18" s="31" t="n"/>
+      <c r="F18" s="31" t="n"/>
+      <c r="G18" s="31" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="32" t="inlineStr">
+        <is>
+          <t>ABOVE 25 (6 Players) - TWO POOL GROUPS</t>
+        </is>
+      </c>
+      <c r="B19" s="33" t="n"/>
+      <c r="C19" s="33" t="n"/>
+      <c r="D19" s="33" t="n"/>
+      <c r="E19" s="31" t="n"/>
+      <c r="F19" s="31" t="n"/>
+      <c r="G19" s="31" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="36" t="inlineStr">
+        <is>
+          <t>GROUP A (3 Players) - Round Robin Pool</t>
+        </is>
+      </c>
+      <c r="B20" s="37" t="n"/>
+      <c r="C20" s="37" t="n"/>
+      <c r="D20" s="37" t="n"/>
+      <c r="E20" s="31" t="n"/>
+      <c r="F20" s="31" t="n"/>
+      <c r="G20" s="31" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="34" t="inlineStr">
         <is>
           <t>S.No</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B21" s="34" t="inlineStr">
         <is>
           <t>Player Name</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C21" s="34" t="inlineStr">
         <is>
           <t>Age</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>Group</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="n">
+      <c r="D21" s="34" t="inlineStr">
+        <is>
+          <t>Group/Seed</t>
+        </is>
+      </c>
+      <c r="E21" s="31" t="n"/>
+      <c r="F21" s="31" t="n"/>
+      <c r="G21" s="31" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t>Shravan Gajera</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="n">
-        <v>23</v>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
+      <c r="B22" s="35" t="inlineStr">
+        <is>
+          <t>Ravi Modi</t>
+        </is>
+      </c>
+      <c r="C22" s="35" t="n">
+        <v>29</v>
+      </c>
+      <c r="D22" s="35" t="inlineStr">
         <is>
           <t>Group A</t>
         </is>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="8" t="n">
+      <c r="E22" s="31" t="n"/>
+      <c r="F22" s="31" t="n"/>
+      <c r="G22" s="31" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="B17" s="9" t="inlineStr">
-        <is>
-          <t>Hryday Goyal</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
+      <c r="B23" s="35" t="inlineStr">
+        <is>
+          <t>Mayank Aggarwal</t>
+        </is>
+      </c>
+      <c r="C23" s="35" t="n">
+        <v>40</v>
+      </c>
+      <c r="D23" s="35" t="inlineStr">
         <is>
           <t>Group A</t>
         </is>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="8" t="n">
+      <c r="E23" s="31" t="n"/>
+      <c r="F23" s="31" t="n"/>
+      <c r="G23" s="31" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="35" t="n">
         <v>3</v>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B24" s="35" t="inlineStr">
+        <is>
+          <t>Tejas doshi</t>
+        </is>
+      </c>
+      <c r="C24" s="35" t="n">
+        <v>40</v>
+      </c>
+      <c r="D24" s="35" t="inlineStr">
+        <is>
+          <t>Group A</t>
+        </is>
+      </c>
+      <c r="E24" s="31" t="n"/>
+      <c r="F24" s="31" t="n"/>
+      <c r="G24" s="31" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="31" t="n"/>
+      <c r="B25" s="31" t="n"/>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+      <c r="E25" s="31" t="n"/>
+      <c r="F25" s="31" t="n"/>
+      <c r="G25" s="31" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="36" t="inlineStr">
+        <is>
+          <t>GROUP B (3 Players) - Round Robin Pool</t>
+        </is>
+      </c>
+      <c r="B26" s="37" t="n"/>
+      <c r="C26" s="37" t="n"/>
+      <c r="D26" s="37" t="n"/>
+      <c r="E26" s="31" t="n"/>
+      <c r="F26" s="31" t="n"/>
+      <c r="G26" s="31" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="34" t="inlineStr">
+        <is>
+          <t>S.No</t>
+        </is>
+      </c>
+      <c r="B27" s="34" t="inlineStr">
+        <is>
+          <t>Player Name</t>
+        </is>
+      </c>
+      <c r="C27" s="34" t="inlineStr">
+        <is>
+          <t>Age</t>
+        </is>
+      </c>
+      <c r="D27" s="34" t="inlineStr">
+        <is>
+          <t>Group/Seed</t>
+        </is>
+      </c>
+      <c r="E27" s="31" t="n"/>
+      <c r="F27" s="31" t="n"/>
+      <c r="G27" s="31" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="B28" s="35" t="inlineStr">
         <is>
           <t>Dr Rahul Modi</t>
         </is>
       </c>
-      <c r="C18" s="8" t="n">
+      <c r="C28" s="35" t="n">
         <v>36</v>
       </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>Group A</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="B19" s="9" t="inlineStr">
+      <c r="D28" s="35" t="inlineStr">
+        <is>
+          <t>Group B</t>
+        </is>
+      </c>
+      <c r="E28" s="31" t="n"/>
+      <c r="F28" s="31" t="n"/>
+      <c r="G28" s="31" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="B29" s="35" t="inlineStr">
         <is>
           <t>Tanmay Sharma</t>
         </is>
       </c>
-      <c r="C19" s="8" t="n">
+      <c r="C29" s="35" t="n">
         <v>39</v>
       </c>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>Group A</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="B20" s="9" t="inlineStr">
-        <is>
-          <t>Mayank Aggarwal</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>Group A</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="10" t="inlineStr">
-        <is>
-          <t>GROUP B (4 Players) - Round Robin Pool</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>S.No</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>Player Name</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>Age</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>Group</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="B24" s="9" t="inlineStr">
-        <is>
-          <t>Aaditya Kumar</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="n">
-        <v>17</v>
-      </c>
-      <c r="D24" s="8" t="inlineStr">
+      <c r="D29" s="35" t="inlineStr">
         <is>
           <t>Group B</t>
         </is>
       </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="B25" s="9" t="inlineStr">
-        <is>
-          <t>Ravi Modi</t>
-        </is>
-      </c>
-      <c r="C25" s="8" t="n">
-        <v>29</v>
-      </c>
-      <c r="D25" s="8" t="inlineStr">
+      <c r="E29" s="31" t="n"/>
+      <c r="F29" s="31" t="n"/>
+      <c r="G29" s="31" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="B30" s="35" t="inlineStr">
+        <is>
+          <t>Vinit Padia</t>
+        </is>
+      </c>
+      <c r="C30" s="35" t="n">
+        <v>44</v>
+      </c>
+      <c r="D30" s="35" t="inlineStr">
         <is>
           <t>Group B</t>
         </is>
       </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="B26" s="9" t="inlineStr">
-        <is>
-          <t>Tejas doshi</t>
-        </is>
-      </c>
-      <c r="C26" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>Group B</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="B27" s="9" t="inlineStr">
-        <is>
-          <t>Vinit Padia</t>
-        </is>
-      </c>
-      <c r="C27" s="8" t="n">
-        <v>44</v>
-      </c>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t>Group B</t>
-        </is>
-      </c>
-    </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
+      <c r="E30" s="31" t="n"/>
+      <c r="F30" s="31" t="n"/>
+      <c r="G30" s="31" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="31" t="n"/>
+      <c r="B31" s="31" t="n"/>
+      <c r="C31" s="31" t="n"/>
+      <c r="D31" s="31" t="n"/>
+      <c r="E31" s="31" t="n"/>
+      <c r="F31" s="31" t="n"/>
+      <c r="G31" s="31" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="31" t="n"/>
+      <c r="B32" s="31" t="n"/>
+      <c r="C32" s="31" t="n"/>
+      <c r="D32" s="31" t="n"/>
+      <c r="E32" s="31" t="n"/>
+      <c r="F32" s="31" t="n"/>
+      <c r="G32" s="31" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="32" t="inlineStr">
         <is>
           <t>SQUASH TOURNAMENT SCHEDULE</t>
         </is>
       </c>
-    </row>
-    <row r="31"/>
-    <row r="32">
-      <c r="A32" s="11" t="inlineStr">
+      <c r="B33" s="33" t="n"/>
+      <c r="C33" s="33" t="n"/>
+      <c r="D33" s="33" t="n"/>
+      <c r="E33" s="33" t="n"/>
+      <c r="F33" s="33" t="n"/>
+      <c r="G33" s="31" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="31" t="n"/>
+      <c r="B34" s="31" t="n"/>
+      <c r="C34" s="31" t="n"/>
+      <c r="D34" s="31" t="n"/>
+      <c r="E34" s="31" t="n"/>
+      <c r="F34" s="31" t="n"/>
+      <c r="G34" s="31" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="38" t="inlineStr">
         <is>
           <t>AUGUST 15 - POOLS &amp; KNOCKOUTS</t>
         </is>
       </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="12" t="inlineStr">
+      <c r="B35" s="30" t="n"/>
+      <c r="C35" s="30" t="n"/>
+      <c r="D35" s="30" t="n"/>
+      <c r="E35" s="30" t="n"/>
+      <c r="F35" s="30" t="n"/>
+      <c r="G35" s="31" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="39" t="inlineStr">
         <is>
           <t>Time</t>
         </is>
       </c>
-      <c r="B33" s="12" t="inlineStr">
+      <c r="B36" s="39" t="inlineStr">
         <is>
           <t>Match</t>
         </is>
       </c>
-      <c r="C33" s="12" t="inlineStr">
+      <c r="C36" s="39" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D33" s="12" t="inlineStr">
+      <c r="D36" s="39" t="inlineStr">
         <is>
           <t>Player A</t>
         </is>
       </c>
-      <c r="E33" s="12" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="F33" s="12" t="inlineStr">
+      <c r="E36" s="39" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="F36" s="39" t="inlineStr">
         <is>
           <t>Player B</t>
         </is>
       </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="8" t="inlineStr">
+      <c r="G36" s="31" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="35" t="inlineStr">
         <is>
           <t>8:30 AM</t>
         </is>
       </c>
-      <c r="B34" s="8" t="inlineStr">
+      <c r="B37" s="35" t="inlineStr">
         <is>
           <t>U15-R1-M1</t>
         </is>
       </c>
-      <c r="C34" s="8" t="inlineStr">
+      <c r="C37" s="35" t="inlineStr">
         <is>
           <t>U15-R1</t>
         </is>
       </c>
-      <c r="D34" s="9" t="inlineStr">
+      <c r="D37" s="35" t="inlineStr">
         <is>
           <t>Shaurya Tripathi (10)</t>
         </is>
       </c>
-      <c r="E34" s="8" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="F34" s="9" t="inlineStr">
+      <c r="E37" s="35" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="F37" s="35" t="inlineStr">
         <is>
           <t>Parth yadav (10)</t>
         </is>
       </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="8" t="inlineStr">
+      <c r="G37" s="31" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="35" t="inlineStr">
         <is>
           <t>8:48 AM</t>
         </is>
       </c>
-      <c r="B35" s="8" t="inlineStr">
+      <c r="B38" s="35" t="inlineStr">
+        <is>
+          <t>U25-1</t>
+        </is>
+      </c>
+      <c r="C38" s="35" t="inlineStr">
+        <is>
+          <t>U25</t>
+        </is>
+      </c>
+      <c r="D38" s="35" t="inlineStr">
+        <is>
+          <t>Aaditya Kumar (17)</t>
+        </is>
+      </c>
+      <c r="E38" s="35" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="F38" s="35" t="inlineStr">
+        <is>
+          <t>Hryday Goyal (20)</t>
+        </is>
+      </c>
+      <c r="G38" s="31" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="35" t="inlineStr">
+        <is>
+          <t>9:06 AM</t>
+        </is>
+      </c>
+      <c r="B39" s="35" t="inlineStr">
+        <is>
+          <t>U15-R1-M2</t>
+        </is>
+      </c>
+      <c r="C39" s="35" t="inlineStr">
+        <is>
+          <t>U15-R1</t>
+        </is>
+      </c>
+      <c r="D39" s="35" t="inlineStr">
+        <is>
+          <t>Peher Krunal Shah (12)</t>
+        </is>
+      </c>
+      <c r="E39" s="35" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="F39" s="35" t="inlineStr">
+        <is>
+          <t>Aadit Joshi (12)</t>
+        </is>
+      </c>
+      <c r="G39" s="31" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="35" t="inlineStr">
+        <is>
+          <t>9:24 AM</t>
+        </is>
+      </c>
+      <c r="B40" s="35" t="inlineStr">
+        <is>
+          <t>U25-2</t>
+        </is>
+      </c>
+      <c r="C40" s="35" t="inlineStr">
+        <is>
+          <t>U25</t>
+        </is>
+      </c>
+      <c r="D40" s="35" t="inlineStr">
+        <is>
+          <t>Aaditya Kumar (17)</t>
+        </is>
+      </c>
+      <c r="E40" s="35" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="F40" s="35" t="inlineStr">
+        <is>
+          <t>Shravan Gajera (23)</t>
+        </is>
+      </c>
+      <c r="G40" s="31" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="35" t="inlineStr">
+        <is>
+          <t>9:42 AM</t>
+        </is>
+      </c>
+      <c r="B41" s="35" t="inlineStr">
         <is>
           <t>GA-1</t>
         </is>
       </c>
-      <c r="C35" s="8" t="inlineStr">
+      <c r="C41" s="35" t="inlineStr">
         <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="D35" s="9" t="inlineStr">
+      <c r="D41" s="35" t="inlineStr">
+        <is>
+          <t>Ravi Modi (29)</t>
+        </is>
+      </c>
+      <c r="E41" s="35" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="F41" s="35" t="inlineStr">
+        <is>
+          <t>Mayank Aggarwal (40)</t>
+        </is>
+      </c>
+      <c r="G41" s="31" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="35" t="inlineStr">
+        <is>
+          <t>11:00 AM</t>
+        </is>
+      </c>
+      <c r="B42" s="35" t="inlineStr">
+        <is>
+          <t>U15-R1-M3</t>
+        </is>
+      </c>
+      <c r="C42" s="35" t="inlineStr">
+        <is>
+          <t>U15-R1</t>
+        </is>
+      </c>
+      <c r="D42" s="35" t="inlineStr">
+        <is>
+          <t>Viaan Neema (12)</t>
+        </is>
+      </c>
+      <c r="E42" s="35" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="F42" s="35" t="inlineStr">
+        <is>
+          <t>Yash agarwal (13)</t>
+        </is>
+      </c>
+      <c r="G42" s="31" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="35" t="inlineStr">
+        <is>
+          <t>11:18 AM</t>
+        </is>
+      </c>
+      <c r="B43" s="35" t="inlineStr">
+        <is>
+          <t>U25-3</t>
+        </is>
+      </c>
+      <c r="C43" s="35" t="inlineStr">
+        <is>
+          <t>U25</t>
+        </is>
+      </c>
+      <c r="D43" s="35" t="inlineStr">
+        <is>
+          <t>Hryday Goyal (20)</t>
+        </is>
+      </c>
+      <c r="E43" s="35" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="F43" s="35" t="inlineStr">
         <is>
           <t>Shravan Gajera (23)</t>
         </is>
       </c>
-      <c r="E35" s="8" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="F35" s="9" t="inlineStr">
-        <is>
-          <t>Hryday Goyal (20)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="8" t="inlineStr">
-        <is>
-          <t>9:06 AM</t>
-        </is>
-      </c>
-      <c r="B36" s="8" t="inlineStr">
-        <is>
-          <t>U15-R1-M2</t>
-        </is>
-      </c>
-      <c r="C36" s="8" t="inlineStr">
-        <is>
-          <t>U15-R1</t>
-        </is>
-      </c>
-      <c r="D36" s="9" t="inlineStr">
-        <is>
-          <t>Peher Krunal Shah (12)</t>
-        </is>
-      </c>
-      <c r="E36" s="8" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="F36" s="9" t="inlineStr">
-        <is>
-          <t>Aadit Joshi (12)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="8" t="inlineStr">
-        <is>
-          <t>9:24 AM</t>
-        </is>
-      </c>
-      <c r="B37" s="8" t="inlineStr">
+      <c r="G43" s="31" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="35" t="inlineStr">
+        <is>
+          <t>11:36 AM</t>
+        </is>
+      </c>
+      <c r="B44" s="35" t="inlineStr">
+        <is>
+          <t>GB-1</t>
+        </is>
+      </c>
+      <c r="C44" s="35" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="D44" s="35" t="inlineStr">
+        <is>
+          <t>Dr Rahul Modi (36)</t>
+        </is>
+      </c>
+      <c r="E44" s="35" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="F44" s="35" t="inlineStr">
+        <is>
+          <t>Tanmay Sharma (39)</t>
+        </is>
+      </c>
+      <c r="G44" s="31" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="35" t="inlineStr">
+        <is>
+          <t>11:54 AM</t>
+        </is>
+      </c>
+      <c r="B45" s="35" t="inlineStr">
         <is>
           <t>GA-2</t>
         </is>
       </c>
-      <c r="C37" s="8" t="inlineStr">
+      <c r="C45" s="35" t="inlineStr">
         <is>
           <t>GA</t>
         </is>
       </c>
-      <c r="D37" s="9" t="inlineStr">
-        <is>
-          <t>Shravan Gajera (23)</t>
-        </is>
-      </c>
-      <c r="E37" s="8" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="F37" s="9" t="inlineStr">
+      <c r="D45" s="35" t="inlineStr">
+        <is>
+          <t>Ravi Modi (29)</t>
+        </is>
+      </c>
+      <c r="E45" s="35" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="F45" s="35" t="inlineStr">
+        <is>
+          <t>Tejas doshi (40)</t>
+        </is>
+      </c>
+      <c r="G45" s="31" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="35" t="inlineStr">
+        <is>
+          <t>3:00 PM</t>
+        </is>
+      </c>
+      <c r="B46" s="35" t="inlineStr">
+        <is>
+          <t>GB-2</t>
+        </is>
+      </c>
+      <c r="C46" s="35" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="D46" s="35" t="inlineStr">
         <is>
           <t>Dr Rahul Modi (36)</t>
         </is>
       </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="8" t="inlineStr">
-        <is>
-          <t>9:42 AM</t>
-        </is>
-      </c>
-      <c r="B38" s="8" t="inlineStr">
-        <is>
-          <t>GB-1</t>
-        </is>
-      </c>
-      <c r="C38" s="8" t="inlineStr">
+      <c r="E46" s="35" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="F46" s="35" t="inlineStr">
+        <is>
+          <t>Vinit Padia (44)</t>
+        </is>
+      </c>
+      <c r="G46" s="31" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="35" t="inlineStr">
+        <is>
+          <t>3:18 PM</t>
+        </is>
+      </c>
+      <c r="B47" s="35" t="inlineStr">
+        <is>
+          <t>GA-3</t>
+        </is>
+      </c>
+      <c r="C47" s="35" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="D47" s="35" t="inlineStr">
+        <is>
+          <t>Mayank Aggarwal (40)</t>
+        </is>
+      </c>
+      <c r="E47" s="35" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="F47" s="35" t="inlineStr">
+        <is>
+          <t>Tejas doshi (40)</t>
+        </is>
+      </c>
+      <c r="G47" s="31" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="35" t="inlineStr">
+        <is>
+          <t>3:36 PM</t>
+        </is>
+      </c>
+      <c r="B48" s="35" t="inlineStr">
+        <is>
+          <t>GB-3</t>
+        </is>
+      </c>
+      <c r="C48" s="35" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="D38" s="9" t="inlineStr">
-        <is>
-          <t>Aaditya Kumar (17)</t>
-        </is>
-      </c>
-      <c r="E38" s="8" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="F38" s="9" t="inlineStr">
-        <is>
-          <t>Ravi Modi (29)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="8" t="inlineStr">
-        <is>
-          <t>11:00 AM</t>
-        </is>
-      </c>
-      <c r="B39" s="8" t="inlineStr">
-        <is>
-          <t>U15-R1-M3</t>
-        </is>
-      </c>
-      <c r="C39" s="8" t="inlineStr">
-        <is>
-          <t>U15-R1</t>
-        </is>
-      </c>
-      <c r="D39" s="9" t="inlineStr">
-        <is>
-          <t>Viaan Neema (12)</t>
-        </is>
-      </c>
-      <c r="E39" s="8" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="F39" s="9" t="inlineStr">
-        <is>
-          <t>Yash agarwal (13)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="8" t="inlineStr">
-        <is>
-          <t>11:18 AM</t>
-        </is>
-      </c>
-      <c r="B40" s="8" t="inlineStr">
-        <is>
-          <t>GA-3</t>
-        </is>
-      </c>
-      <c r="C40" s="8" t="inlineStr">
-        <is>
-          <t>GA</t>
-        </is>
-      </c>
-      <c r="D40" s="9" t="inlineStr">
-        <is>
-          <t>Shravan Gajera (23)</t>
-        </is>
-      </c>
-      <c r="E40" s="8" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="F40" s="9" t="inlineStr">
+      <c r="D48" s="35" t="inlineStr">
         <is>
           <t>Tanmay Sharma (39)</t>
         </is>
       </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="8" t="inlineStr">
-        <is>
-          <t>11:36 AM</t>
-        </is>
-      </c>
-      <c r="B41" s="8" t="inlineStr">
-        <is>
-          <t>GB-2</t>
-        </is>
-      </c>
-      <c r="C41" s="8" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="D41" s="9" t="inlineStr">
-        <is>
-          <t>Aaditya Kumar (17)</t>
-        </is>
-      </c>
-      <c r="E41" s="8" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="F41" s="9" t="inlineStr">
-        <is>
-          <t>Tejas doshi (40)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="8" t="inlineStr">
-        <is>
-          <t>11:54 AM</t>
-        </is>
-      </c>
-      <c r="B42" s="8" t="inlineStr">
-        <is>
-          <t>GA-4</t>
-        </is>
-      </c>
-      <c r="C42" s="8" t="inlineStr">
-        <is>
-          <t>GA</t>
-        </is>
-      </c>
-      <c r="D42" s="9" t="inlineStr">
-        <is>
-          <t>Shravan Gajera (23)</t>
-        </is>
-      </c>
-      <c r="E42" s="8" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="F42" s="9" t="inlineStr">
-        <is>
-          <t>Mayank Aggarwal (40)</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="8" t="inlineStr">
-        <is>
-          <t>3:00 PM</t>
-        </is>
-      </c>
-      <c r="B43" s="8" t="inlineStr">
-        <is>
-          <t>GB-3</t>
-        </is>
-      </c>
-      <c r="C43" s="8" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="D43" s="9" t="inlineStr">
-        <is>
-          <t>Aaditya Kumar (17)</t>
-        </is>
-      </c>
-      <c r="E43" s="8" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="F43" s="9" t="inlineStr">
+      <c r="E48" s="35" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="F48" s="35" t="inlineStr">
         <is>
           <t>Vinit Padia (44)</t>
         </is>
       </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="8" t="inlineStr">
-        <is>
-          <t>3:18 PM</t>
-        </is>
-      </c>
-      <c r="B44" s="8" t="inlineStr">
-        <is>
-          <t>GA-5</t>
-        </is>
-      </c>
-      <c r="C44" s="8" t="inlineStr">
-        <is>
-          <t>GA</t>
-        </is>
-      </c>
-      <c r="D44" s="9" t="inlineStr">
-        <is>
-          <t>Hryday Goyal (20)</t>
-        </is>
-      </c>
-      <c r="E44" s="8" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="F44" s="9" t="inlineStr">
-        <is>
-          <t>Dr Rahul Modi (36)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="8" t="inlineStr">
-        <is>
-          <t>3:36 PM</t>
-        </is>
-      </c>
-      <c r="B45" s="8" t="inlineStr">
-        <is>
-          <t>GB-4</t>
-        </is>
-      </c>
-      <c r="C45" s="8" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="D45" s="9" t="inlineStr">
-        <is>
-          <t>Ravi Modi (29)</t>
-        </is>
-      </c>
-      <c r="E45" s="8" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="F45" s="9" t="inlineStr">
-        <is>
-          <t>Tejas doshi (40)</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="8" t="inlineStr">
+      <c r="G48" s="31" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="31" t="n"/>
+      <c r="B49" s="31" t="n"/>
+      <c r="C49" s="31" t="n"/>
+      <c r="D49" s="31" t="n"/>
+      <c r="E49" s="31" t="n"/>
+      <c r="F49" s="31" t="n"/>
+      <c r="G49" s="31" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="40" t="inlineStr">
+        <is>
+          <t>KNOCKOUTS - AUGUST 15</t>
+        </is>
+      </c>
+      <c r="B50" s="41" t="n"/>
+      <c r="C50" s="41" t="n"/>
+      <c r="D50" s="41" t="n"/>
+      <c r="E50" s="41" t="n"/>
+      <c r="F50" s="41" t="n"/>
+      <c r="G50" s="31" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="39" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="B51" s="39" t="inlineStr">
+        <is>
+          <t>Match</t>
+        </is>
+      </c>
+      <c r="C51" s="39" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D51" s="39" t="inlineStr">
+        <is>
+          <t>Player A</t>
+        </is>
+      </c>
+      <c r="E51" s="39" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="F51" s="39" t="inlineStr">
+        <is>
+          <t>Player B</t>
+        </is>
+      </c>
+      <c r="G51" s="31" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="35" t="inlineStr">
         <is>
           <t>3:54 PM</t>
         </is>
       </c>
-      <c r="B46" s="8" t="inlineStr">
-        <is>
-          <t>GA-6</t>
-        </is>
-      </c>
-      <c r="C46" s="8" t="inlineStr">
-        <is>
-          <t>GA</t>
-        </is>
-      </c>
-      <c r="D46" s="9" t="inlineStr">
-        <is>
-          <t>Hryday Goyal (20)</t>
-        </is>
-      </c>
-      <c r="E46" s="8" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="F46" s="9" t="inlineStr">
-        <is>
-          <t>Tanmay Sharma (39)</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="8" t="inlineStr">
+      <c r="B52" s="35" t="inlineStr">
+        <is>
+          <t>U15-SF-1</t>
+        </is>
+      </c>
+      <c r="C52" s="35" t="inlineStr">
+        <is>
+          <t>U15-SF</t>
+        </is>
+      </c>
+      <c r="D52" s="35" t="inlineStr">
+        <is>
+          <t>Winner U15-R1-M1</t>
+        </is>
+      </c>
+      <c r="E52" s="35" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="F52" s="35" t="inlineStr">
+        <is>
+          <t>Hridh jhala (BYE)</t>
+        </is>
+      </c>
+      <c r="G52" s="31" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="35" t="inlineStr">
         <is>
           <t>4:12 PM</t>
         </is>
       </c>
-      <c r="B47" s="8" t="inlineStr">
-        <is>
-          <t>GB-5</t>
-        </is>
-      </c>
-      <c r="C47" s="8" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="D47" s="9" t="inlineStr">
-        <is>
-          <t>Ravi Modi (29)</t>
-        </is>
-      </c>
-      <c r="E47" s="8" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="F47" s="9" t="inlineStr">
-        <is>
-          <t>Vinit Padia (44)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="8" t="inlineStr">
+      <c r="B53" s="35" t="inlineStr">
+        <is>
+          <t>U15-SF-2</t>
+        </is>
+      </c>
+      <c r="C53" s="35" t="inlineStr">
+        <is>
+          <t>U15-SF</t>
+        </is>
+      </c>
+      <c r="D53" s="35" t="inlineStr">
+        <is>
+          <t>Winner U15-R1-M2</t>
+        </is>
+      </c>
+      <c r="E53" s="35" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="F53" s="35" t="inlineStr">
+        <is>
+          <t>Winner U15-R1-M3</t>
+        </is>
+      </c>
+      <c r="G53" s="31" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="35" t="inlineStr">
         <is>
           <t>4:30 PM</t>
         </is>
       </c>
-      <c r="B48" s="8" t="inlineStr">
-        <is>
-          <t>GA-7</t>
-        </is>
-      </c>
-      <c r="C48" s="8" t="inlineStr">
-        <is>
-          <t>GA</t>
-        </is>
-      </c>
-      <c r="D48" s="9" t="inlineStr">
-        <is>
-          <t>Hryday Goyal (20)</t>
-        </is>
-      </c>
-      <c r="E48" s="8" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="F48" s="9" t="inlineStr">
-        <is>
-          <t>Mayank Aggarwal (40)</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="8" t="inlineStr">
+      <c r="B54" s="35" t="inlineStr">
+        <is>
+          <t>U25-FINAL</t>
+        </is>
+      </c>
+      <c r="C54" s="35" t="inlineStr">
+        <is>
+          <t>U25-F</t>
+        </is>
+      </c>
+      <c r="D54" s="35" t="inlineStr">
+        <is>
+          <t>U25 RR Winner</t>
+        </is>
+      </c>
+      <c r="E54" s="35" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="F54" s="35" t="inlineStr">
+        <is>
+          <t>U25 RR Runner-up</t>
+        </is>
+      </c>
+      <c r="G54" s="31" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="35" t="inlineStr">
         <is>
           <t>4:48 PM</t>
         </is>
       </c>
-      <c r="B49" s="8" t="inlineStr">
-        <is>
-          <t>GB-6</t>
-        </is>
-      </c>
-      <c r="C49" s="8" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="D49" s="9" t="inlineStr">
-        <is>
-          <t>Tejas doshi (40)</t>
-        </is>
-      </c>
-      <c r="E49" s="8" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="F49" s="9" t="inlineStr">
-        <is>
-          <t>Vinit Padia (44)</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="8" t="inlineStr">
+      <c r="B55" s="35" t="inlineStr">
+        <is>
+          <t>U15-FINAL</t>
+        </is>
+      </c>
+      <c r="C55" s="35" t="inlineStr">
+        <is>
+          <t>U15-F</t>
+        </is>
+      </c>
+      <c r="D55" s="35" t="inlineStr">
+        <is>
+          <t>Winner U15-SF-1</t>
+        </is>
+      </c>
+      <c r="E55" s="35" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="F55" s="35" t="inlineStr">
+        <is>
+          <t>Winner U15-SF-2</t>
+        </is>
+      </c>
+      <c r="G55" s="31" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="35" t="inlineStr">
         <is>
           <t>5:06 PM</t>
         </is>
       </c>
-      <c r="B50" s="8" t="inlineStr">
-        <is>
-          <t>GA-8</t>
-        </is>
-      </c>
-      <c r="C50" s="8" t="inlineStr">
-        <is>
-          <t>GA</t>
-        </is>
-      </c>
-      <c r="D50" s="9" t="inlineStr">
-        <is>
-          <t>Dr Rahul Modi (36)</t>
-        </is>
-      </c>
-      <c r="E50" s="8" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="F50" s="9" t="inlineStr">
-        <is>
-          <t>Tanmay Sharma (39)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="8" t="inlineStr">
+      <c r="B56" s="35" t="inlineStr">
+        <is>
+          <t>A25-SF-1</t>
+        </is>
+      </c>
+      <c r="C56" s="35" t="inlineStr">
+        <is>
+          <t>A25-SF</t>
+        </is>
+      </c>
+      <c r="D56" s="35" t="inlineStr">
+        <is>
+          <t>GA Pool Winner</t>
+        </is>
+      </c>
+      <c r="E56" s="35" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="F56" s="35" t="inlineStr">
+        <is>
+          <t>GB Pool 2nd</t>
+        </is>
+      </c>
+      <c r="G56" s="31" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="35" t="inlineStr">
         <is>
           <t>5:24 PM</t>
         </is>
       </c>
-      <c r="B51" s="8" t="inlineStr">
-        <is>
-          <t>GA-9</t>
-        </is>
-      </c>
-      <c r="C51" s="8" t="inlineStr">
-        <is>
-          <t>GA</t>
-        </is>
-      </c>
-      <c r="D51" s="9" t="inlineStr">
-        <is>
-          <t>Dr Rahul Modi (36)</t>
-        </is>
-      </c>
-      <c r="E51" s="8" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="F51" s="9" t="inlineStr">
-        <is>
-          <t>Mayank Aggarwal (40)</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="8" t="inlineStr">
-        <is>
-          <t>5:42 PM</t>
-        </is>
-      </c>
-      <c r="B52" s="8" t="inlineStr">
-        <is>
-          <t>GA-10</t>
-        </is>
-      </c>
-      <c r="C52" s="8" t="inlineStr">
-        <is>
-          <t>GA</t>
-        </is>
-      </c>
-      <c r="D52" s="9" t="inlineStr">
-        <is>
-          <t>Tanmay Sharma (39)</t>
-        </is>
-      </c>
-      <c r="E52" s="8" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="F52" s="9" t="inlineStr">
-        <is>
-          <t>Mayank Aggarwal (40)</t>
-        </is>
-      </c>
-    </row>
-    <row r="53"/>
-    <row r="54">
-      <c r="A54" s="13" t="inlineStr">
-        <is>
-          <t>KNOCKOUTS - AUGUST 15</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="12" t="inlineStr">
+      <c r="B57" s="35" t="inlineStr">
+        <is>
+          <t>A25-SF-2</t>
+        </is>
+      </c>
+      <c r="C57" s="35" t="inlineStr">
+        <is>
+          <t>A25-SF</t>
+        </is>
+      </c>
+      <c r="D57" s="35" t="inlineStr">
+        <is>
+          <t>GB Pool Winner</t>
+        </is>
+      </c>
+      <c r="E57" s="35" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="F57" s="35" t="inlineStr">
+        <is>
+          <t>GA Pool 2nd</t>
+        </is>
+      </c>
+      <c r="G57" s="31" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="31" t="n"/>
+      <c r="B58" s="31" t="n"/>
+      <c r="C58" s="31" t="n"/>
+      <c r="D58" s="31" t="n"/>
+      <c r="E58" s="31" t="n"/>
+      <c r="F58" s="31" t="n"/>
+      <c r="G58" s="31" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="38" t="inlineStr">
+        <is>
+          <t>AUGUST 16 - A25 FINAL</t>
+        </is>
+      </c>
+      <c r="B59" s="30" t="n"/>
+      <c r="C59" s="30" t="n"/>
+      <c r="D59" s="30" t="n"/>
+      <c r="E59" s="30" t="n"/>
+      <c r="F59" s="30" t="n"/>
+      <c r="G59" s="31" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="39" t="inlineStr">
         <is>
           <t>Time</t>
         </is>
       </c>
-      <c r="B55" s="12" t="inlineStr">
+      <c r="B60" s="39" t="inlineStr">
         <is>
           <t>Match</t>
         </is>
       </c>
-      <c r="C55" s="12" t="inlineStr">
+      <c r="C60" s="39" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D55" s="12" t="inlineStr">
+      <c r="D60" s="39" t="inlineStr">
         <is>
           <t>Player A</t>
         </is>
       </c>
-      <c r="E55" s="12" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="F55" s="12" t="inlineStr">
+      <c r="E60" s="39" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="F60" s="39" t="inlineStr">
         <is>
           <t>Player B</t>
         </is>
       </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="8" t="inlineStr">
-        <is>
-          <t>6:30 PM</t>
-        </is>
-      </c>
-      <c r="B56" s="8" t="inlineStr">
-        <is>
-          <t>U15-SF-1</t>
-        </is>
-      </c>
-      <c r="C56" s="8" t="inlineStr">
-        <is>
-          <t>U15-SF</t>
-        </is>
-      </c>
-      <c r="D56" s="9" t="inlineStr">
-        <is>
-          <t>Winner U15-R1-M1</t>
-        </is>
-      </c>
-      <c r="E56" s="8" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="F56" s="9" t="inlineStr">
-        <is>
-          <t>Hridh jhala (BYE)</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="8" t="inlineStr">
-        <is>
-          <t>6:48 PM</t>
-        </is>
-      </c>
-      <c r="B57" s="8" t="inlineStr">
-        <is>
-          <t>U15-SF-2</t>
-        </is>
-      </c>
-      <c r="C57" s="8" t="inlineStr">
-        <is>
-          <t>U15-SF</t>
-        </is>
-      </c>
-      <c r="D57" s="9" t="inlineStr">
-        <is>
-          <t>Winner U15-R1-M2</t>
-        </is>
-      </c>
-      <c r="E57" s="8" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="F57" s="9" t="inlineStr">
-        <is>
-          <t>Winner U15-R1-M3</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="8" t="inlineStr">
-        <is>
-          <t>7:06 PM</t>
-        </is>
-      </c>
-      <c r="B58" s="8" t="inlineStr">
-        <is>
-          <t>A15-SF-1</t>
-        </is>
-      </c>
-      <c r="C58" s="8" t="inlineStr">
-        <is>
-          <t>A15-SF</t>
-        </is>
-      </c>
-      <c r="D58" s="9" t="inlineStr">
-        <is>
-          <t>GA Pool Winner</t>
-        </is>
-      </c>
-      <c r="E58" s="8" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="F58" s="9" t="inlineStr">
-        <is>
-          <t>GB Pool Winner</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="8" t="inlineStr">
-        <is>
-          <t>7:24 PM</t>
-        </is>
-      </c>
-      <c r="B59" s="8" t="inlineStr">
-        <is>
-          <t>A15-SF-2</t>
-        </is>
-      </c>
-      <c r="C59" s="8" t="inlineStr">
-        <is>
-          <t>A15-SF</t>
-        </is>
-      </c>
-      <c r="D59" s="9" t="inlineStr">
-        <is>
-          <t>GA Pool 2nd</t>
-        </is>
-      </c>
-      <c r="E59" s="8" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="F59" s="9" t="inlineStr">
-        <is>
-          <t>GB Pool 2nd</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="8" t="inlineStr">
-        <is>
-          <t>7:42 PM</t>
-        </is>
-      </c>
-      <c r="B60" s="8" t="inlineStr">
-        <is>
-          <t>U15-FINAL</t>
-        </is>
-      </c>
-      <c r="C60" s="8" t="inlineStr">
-        <is>
-          <t>U15-F</t>
-        </is>
-      </c>
-      <c r="D60" s="9" t="inlineStr">
-        <is>
-          <t>Winner U15-SF-1</t>
-        </is>
-      </c>
-      <c r="E60" s="8" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="F60" s="9" t="inlineStr">
-        <is>
-          <t>Winner U15-SF-2</t>
-        </is>
-      </c>
-    </row>
-    <row r="62"/>
+      <c r="G60" s="31" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="35" t="inlineStr">
+        <is>
+          <t>5:00 PM</t>
+        </is>
+      </c>
+      <c r="B61" s="35" t="inlineStr">
+        <is>
+          <t>A25-FINAL</t>
+        </is>
+      </c>
+      <c r="C61" s="35" t="inlineStr">
+        <is>
+          <t>A25-F</t>
+        </is>
+      </c>
+      <c r="D61" s="35" t="inlineStr">
+        <is>
+          <t>Winner A25-SF-1</t>
+        </is>
+      </c>
+      <c r="E61" s="35" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="F61" s="35" t="inlineStr">
+        <is>
+          <t>Winner A25-SF-2</t>
+        </is>
+      </c>
+      <c r="G61" s="31" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="31" t="n"/>
+      <c r="B62" s="31" t="n"/>
+      <c r="C62" s="31" t="n"/>
+      <c r="D62" s="31" t="n"/>
+      <c r="E62" s="31" t="n"/>
+      <c r="F62" s="31" t="n"/>
+      <c r="G62" s="31" t="n"/>
+    </row>
     <row r="63">
-      <c r="A63" s="11" t="inlineStr">
-        <is>
-          <t>AUGUST 16 - A15 FINAL</t>
-        </is>
-      </c>
+      <c r="A63" s="31" t="n"/>
+      <c r="B63" s="31" t="n"/>
+      <c r="C63" s="31" t="n"/>
+      <c r="D63" s="31" t="n"/>
+      <c r="E63" s="31" t="n"/>
+      <c r="F63" s="31" t="n"/>
+      <c r="G63" s="31" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="12" t="inlineStr">
-        <is>
-          <t>Time</t>
-        </is>
-      </c>
-      <c r="B64" s="12" t="inlineStr">
-        <is>
-          <t>Match</t>
-        </is>
-      </c>
-      <c r="C64" s="12" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D64" s="12" t="inlineStr">
-        <is>
-          <t>Player A</t>
-        </is>
-      </c>
-      <c r="E64" s="12" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="F64" s="12" t="inlineStr">
-        <is>
-          <t>Player B</t>
-        </is>
-      </c>
+      <c r="A64" s="31" t="n"/>
+      <c r="B64" s="31" t="n"/>
+      <c r="C64" s="31" t="n"/>
+      <c r="D64" s="31" t="n"/>
+      <c r="E64" s="31" t="n"/>
+      <c r="F64" s="31" t="n"/>
+      <c r="G64" s="31" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="8" t="inlineStr">
-        <is>
-          <t>5:00 PM</t>
-        </is>
-      </c>
-      <c r="B65" s="8" t="inlineStr">
-        <is>
-          <t>A15-FINAL</t>
-        </is>
-      </c>
-      <c r="C65" s="8" t="inlineStr">
-        <is>
-          <t>A15-F</t>
-        </is>
-      </c>
-      <c r="D65" s="9" t="inlineStr">
-        <is>
-          <t>Winner A15-SF-1</t>
-        </is>
-      </c>
-      <c r="E65" s="8" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="F65" s="9" t="inlineStr">
-        <is>
-          <t>Winner A15-SF-2</t>
-        </is>
-      </c>
+      <c r="A65" s="31" t="n"/>
+      <c r="B65" s="31" t="n"/>
+      <c r="C65" s="31" t="n"/>
+      <c r="D65" s="31" t="n"/>
+      <c r="E65" s="31" t="n"/>
+      <c r="F65" s="31" t="n"/>
+      <c r="G65" s="31" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="10">
+    <mergeCell ref="A33:F33"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A63:F63"/>
-    <mergeCell ref="A54:F54"/>
-    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="A20:D20"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A32:F32"/>
-    <mergeCell ref="A29:D29"/>
-    <mergeCell ref="A62:F62"/>
-    <mergeCell ref="A30:F30"/>
-    <mergeCell ref="A53:F53"/>
-    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A50:F50"/>
+    <mergeCell ref="A59:F59"/>
     <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A14:D14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Ekta_Schedule_With_Matchups.xlsx
+++ b/Ekta_Schedule_With_Matchups.xlsx
@@ -705,21 +705,21 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="15" t="inlineStr">
         <is>
-          <t>Fully conflict-free: no player with matches in multiple events is ever double-booked. All 308</t>
+          <t>Fully conflict-free: no player is ever double-booked, and a 10-minute break is inserted whenever a</t>
         </is>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" s="15" t="inlineStr">
         <is>
-          <t>matches were scheduled together by a single match-by-match solver across all 9 events, not</t>
+          <t>player would otherwise play back-to-back in the same event, or continuously for 60+ minutes across</t>
         </is>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="15" t="inlineStr">
         <is>
-          <t>per-event in isolation.</t>
+          <t>different events. Semis and finals (and both Doubles events, in full) run only after every group/pool match, in every event, has finished.</t>
         </is>
       </c>
     </row>
@@ -757,12 +757,12 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>8:00 - 9:30 AM</t>
+          <t>8:00 AM - 9:00 PM</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>TT Mens Singles - Senior band (runs first)</t>
+          <t>Group / pool ("Americano") stage for all 7 non-doubles events, running concurrently on their own tables/boards/court</t>
         </is>
       </c>
       <c r="D8" s="4" t="n"/>
@@ -771,17 +771,17 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>9:30 - 10:30 AM</t>
+          <t>8:00 - 11:50 AM</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>BREAK</t>
+          <t>Remaining group-stage matches (Chess, TT Men's Singles, Pool) wrap up — held over from Aug 15 by the player rest-break rule</t>
         </is>
       </c>
       <c r="D9" s="10" t="n"/>
@@ -790,114 +790,58 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>10:30 AM - 12:30 PM</t>
+          <t>11:50 AM - 2:05 PM</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>TT Womens Singles (complete event)</t>
+          <t>Semis + Finals for every singles event, plus both Doubles events in full (TT Doubles, Carrom Doubles) — none of this starts until every group/pool match everywhere is done</t>
         </is>
       </c>
       <c r="D10" s="4" t="n"/>
       <c r="E10" s="4" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B11" s="10" t="inlineStr">
-        <is>
-          <t>12:30 - 3:00 PM</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="inlineStr">
-        <is>
-          <t>BREAK</t>
-        </is>
-      </c>
+      <c r="A11" s="10" t="n"/>
+      <c r="B11" s="10" t="n"/>
+      <c r="C11" s="10" t="n"/>
       <c r="D11" s="10" t="n"/>
       <c r="E11" s="10" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>3:00 - 10:00 PM</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>All remaining events continue (see per-sheet schedules)</t>
-        </is>
-      </c>
+          <t>No matches are scheduled between 10:00 PM and 8:00 AM — any match that would otherwise land in that window rolls to 8:00 AM the next day.</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n"/>
+      <c r="C12" s="4" t="n"/>
       <c r="D12" s="4" t="n"/>
       <c r="E12" s="4" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>Aug 16</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>8:00 AM - 12:00 PM</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>Remaining events continue</t>
-        </is>
-      </c>
+      <c r="A13" s="6" t="n"/>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="n"/>
       <c r="D13" s="6" t="n"/>
       <c r="E13" s="6" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>Aug 16</t>
-        </is>
-      </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>12:00 - 3:00 PM</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>BREAK</t>
-        </is>
-      </c>
+      <c r="A14" s="10" t="n"/>
+      <c r="B14" s="10" t="n"/>
+      <c r="C14" s="10" t="n"/>
       <c r="D14" s="10" t="n"/>
       <c r="E14" s="10" t="n"/>
     </row>
     <row r="15" ht="33" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>Aug 16</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>3:00 - 10:00 PM</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>Remaining events continue / wrap up</t>
-        </is>
-      </c>
+      <c r="A15" s="6" t="n"/>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
       <c r="D15" s="6" t="n"/>
       <c r="E15" s="6" t="n"/>
     </row>
@@ -963,7 +907,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>Aug15 12:30PM</t>
+          <t>Aug16 12:20PM</t>
         </is>
       </c>
     </row>
@@ -988,7 +932,7 @@
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>Aug16 9:20AM</t>
+          <t>Aug16 1:35PM</t>
         </is>
       </c>
     </row>
@@ -1008,12 +952,12 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Aug15 8:30PM</t>
+          <t>Aug16 12:35PM</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>Aug16 10:15AM</t>
+          <t>Aug16 2:05PM</t>
         </is>
       </c>
     </row>
@@ -1038,7 +982,7 @@
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>Aug16 10:50AM</t>
+          <t>Aug16 1:30PM</t>
         </is>
       </c>
     </row>
@@ -1063,7 +1007,7 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Aug16 9:15AM</t>
+          <t>Aug16 1:30PM</t>
         </is>
       </c>
     </row>
@@ -1088,7 +1032,7 @@
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>Aug16 11:30AM</t>
+          <t>Aug16 12:35PM</t>
         </is>
       </c>
     </row>
@@ -1113,7 +1057,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>Aug15 10:55AM</t>
+          <t>Aug16 12:05PM</t>
         </is>
       </c>
     </row>
@@ -1133,12 +1077,12 @@
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>Aug15 3:45PM</t>
+          <t>Aug16 11:50AM</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>Aug16 3:25PM</t>
+          <t>Aug16 1:20PM</t>
         </is>
       </c>
     </row>
@@ -1163,14 +1107,14 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>Aug15 9:30PM</t>
+          <t>Aug16 1:56PM</t>
         </is>
       </c>
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="19" t="inlineStr">
         <is>
-          <t>Overall tournament span: Aug 15, 8:00 AM start → Aug 16, 3:25 PM finish — comfortably inside the Aug 16, 10 PM cap.</t>
+          <t>Overall tournament span: Aug 15, 8:00 AM start → Aug 16, 2:05 PM finish — comfortably inside the Aug 16, 10 PM cap.</t>
         </is>
       </c>
     </row>
@@ -2045,12 +1989,12 @@
       </c>
       <c r="B38" s="28" t="inlineStr">
         <is>
-          <t>11:06AM</t>
+          <t>11:16AM</t>
         </is>
       </c>
       <c r="C38" s="28" t="inlineStr">
         <is>
-          <t>11:24AM</t>
+          <t>11:34AM</t>
         </is>
       </c>
       <c r="D38" s="28" t="inlineStr">
@@ -2095,17 +2039,17 @@
       </c>
       <c r="B39" s="27" t="inlineStr">
         <is>
-          <t>11:24AM</t>
+          <t>12:10PM</t>
         </is>
       </c>
       <c r="C39" s="27" t="inlineStr">
         <is>
-          <t>11:42AM</t>
+          <t>12:28PM</t>
         </is>
       </c>
       <c r="D39" s="27" t="inlineStr">
         <is>
-          <t>Under 15</t>
+          <t>15-25 Bracket</t>
         </is>
       </c>
       <c r="E39" s="27" t="n">
@@ -2113,7 +2057,7 @@
       </c>
       <c r="F39" s="27" t="inlineStr">
         <is>
-          <t>U15-SF1</t>
+          <t>GC-3</t>
         </is>
       </c>
       <c r="G39" s="27" t="inlineStr">
@@ -2123,7 +2067,7 @@
       </c>
       <c r="H39" s="27" t="inlineStr">
         <is>
-          <t>Winner U15-R1-M1</t>
+          <t>Hryday Goyal</t>
         </is>
       </c>
       <c r="I39" s="27" t="inlineStr">
@@ -2133,7 +2077,7 @@
       </c>
       <c r="J39" s="27" t="inlineStr">
         <is>
-          <t>Hridh jhala (BYE)</t>
+          <t>Shravan Gajera</t>
         </is>
       </c>
     </row>
@@ -2145,17 +2089,17 @@
       </c>
       <c r="B40" s="28" t="inlineStr">
         <is>
-          <t>11:50AM</t>
+          <t>3:15PM</t>
         </is>
       </c>
       <c r="C40" s="28" t="inlineStr">
         <is>
-          <t>12:08PM</t>
+          <t>3:33PM</t>
         </is>
       </c>
       <c r="D40" s="28" t="inlineStr">
         <is>
-          <t>15-25 Bracket</t>
+          <t>Above 25 Bracket</t>
         </is>
       </c>
       <c r="E40" s="28" t="n">
@@ -2163,7 +2107,7 @@
       </c>
       <c r="F40" s="28" t="inlineStr">
         <is>
-          <t>GC-3</t>
+          <t>GA-3</t>
         </is>
       </c>
       <c r="G40" s="28" t="inlineStr">
@@ -2173,7 +2117,7 @@
       </c>
       <c r="H40" s="28" t="inlineStr">
         <is>
-          <t>Hryday Goyal</t>
+          <t>Tanmay Sharma</t>
         </is>
       </c>
       <c r="I40" s="28" t="inlineStr">
@@ -2183,7 +2127,7 @@
       </c>
       <c r="J40" s="28" t="inlineStr">
         <is>
-          <t>Shravan Gajera</t>
+          <t>Mayank Aggarwal</t>
         </is>
       </c>
     </row>
@@ -2195,17 +2139,17 @@
       </c>
       <c r="B41" s="27" t="inlineStr">
         <is>
-          <t>12:08PM</t>
+          <t>3:40PM</t>
         </is>
       </c>
       <c r="C41" s="27" t="inlineStr">
         <is>
-          <t>12:26PM</t>
+          <t>3:58PM</t>
         </is>
       </c>
       <c r="D41" s="27" t="inlineStr">
         <is>
-          <t>Under 15</t>
+          <t>Above 25 Bracket</t>
         </is>
       </c>
       <c r="E41" s="27" t="n">
@@ -2213,7 +2157,7 @@
       </c>
       <c r="F41" s="27" t="inlineStr">
         <is>
-          <t>U15-SF2</t>
+          <t>GB-2</t>
         </is>
       </c>
       <c r="G41" s="27" t="inlineStr">
@@ -2223,7 +2167,7 @@
       </c>
       <c r="H41" s="27" t="inlineStr">
         <is>
-          <t>Winner U15-R1-M2</t>
+          <t>Ravi Modi</t>
         </is>
       </c>
       <c r="I41" s="27" t="inlineStr">
@@ -2233,7 +2177,7 @@
       </c>
       <c r="J41" s="27" t="inlineStr">
         <is>
-          <t>Winner U15-R1-M3</t>
+          <t>Vinit Padia</t>
         </is>
       </c>
     </row>
@@ -2245,12 +2189,12 @@
       </c>
       <c r="B42" s="28" t="inlineStr">
         <is>
-          <t>3:15PM</t>
+          <t>4:08PM</t>
         </is>
       </c>
       <c r="C42" s="28" t="inlineStr">
         <is>
-          <t>3:33PM</t>
+          <t>4:26PM</t>
         </is>
       </c>
       <c r="D42" s="28" t="inlineStr">
@@ -2263,7 +2207,7 @@
       </c>
       <c r="F42" s="28" t="inlineStr">
         <is>
-          <t>GA-3</t>
+          <t>GB-3</t>
         </is>
       </c>
       <c r="G42" s="28" t="inlineStr">
@@ -2273,7 +2217,7 @@
       </c>
       <c r="H42" s="28" t="inlineStr">
         <is>
-          <t>Tanmay Sharma</t>
+          <t>Tejas doshi</t>
         </is>
       </c>
       <c r="I42" s="28" t="inlineStr">
@@ -2283,29 +2227,29 @@
       </c>
       <c r="J42" s="28" t="inlineStr">
         <is>
-          <t>Mayank Aggarwal</t>
+          <t>Vinit Padia</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="27" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B43" s="27" t="inlineStr">
         <is>
-          <t>3:33PM</t>
+          <t>11:50AM</t>
         </is>
       </c>
       <c r="C43" s="27" t="inlineStr">
         <is>
-          <t>3:51PM</t>
+          <t>12:08PM</t>
         </is>
       </c>
       <c r="D43" s="27" t="inlineStr">
         <is>
-          <t>Above 25 Bracket</t>
+          <t>Under 15</t>
         </is>
       </c>
       <c r="E43" s="27" t="n">
@@ -2313,7 +2257,7 @@
       </c>
       <c r="F43" s="27" t="inlineStr">
         <is>
-          <t>GB-2</t>
+          <t>U15-SF1</t>
         </is>
       </c>
       <c r="G43" s="27" t="inlineStr">
@@ -2323,7 +2267,7 @@
       </c>
       <c r="H43" s="27" t="inlineStr">
         <is>
-          <t>Ravi Modi</t>
+          <t>Winner U15-R1-M1</t>
         </is>
       </c>
       <c r="I43" s="27" t="inlineStr">
@@ -2333,29 +2277,29 @@
       </c>
       <c r="J43" s="27" t="inlineStr">
         <is>
-          <t>Vinit Padia</t>
+          <t>Hridh jhala (BYE)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="28" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B44" s="28" t="inlineStr">
         <is>
-          <t>3:51PM</t>
+          <t>12:08PM</t>
         </is>
       </c>
       <c r="C44" s="28" t="inlineStr">
         <is>
-          <t>4:09PM</t>
+          <t>12:26PM</t>
         </is>
       </c>
       <c r="D44" s="28" t="inlineStr">
         <is>
-          <t>Above 25 Bracket</t>
+          <t>Under 15</t>
         </is>
       </c>
       <c r="E44" s="28" t="n">
@@ -2363,7 +2307,7 @@
       </c>
       <c r="F44" s="28" t="inlineStr">
         <is>
-          <t>GB-3</t>
+          <t>U15-SF2</t>
         </is>
       </c>
       <c r="G44" s="28" t="inlineStr">
@@ -2373,7 +2317,7 @@
       </c>
       <c r="H44" s="28" t="inlineStr">
         <is>
-          <t>Tejas doshi</t>
+          <t>Winner U15-R1-M2</t>
         </is>
       </c>
       <c r="I44" s="28" t="inlineStr">
@@ -2383,24 +2327,24 @@
       </c>
       <c r="J44" s="28" t="inlineStr">
         <is>
-          <t>Vinit Padia</t>
+          <t>Winner U15-R1-M3</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="27" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B45" s="27" t="inlineStr">
         <is>
-          <t>4:09PM</t>
+          <t>12:26PM</t>
         </is>
       </c>
       <c r="C45" s="27" t="inlineStr">
         <is>
-          <t>4:39PM</t>
+          <t>12:44PM</t>
         </is>
       </c>
       <c r="D45" s="27" t="inlineStr">
@@ -2440,17 +2384,17 @@
     <row r="46">
       <c r="A46" s="28" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B46" s="28" t="inlineStr">
         <is>
-          <t>4:39PM</t>
+          <t>12:44PM</t>
         </is>
       </c>
       <c r="C46" s="28" t="inlineStr">
         <is>
-          <t>5:09PM</t>
+          <t>1:02PM</t>
         </is>
       </c>
       <c r="D46" s="28" t="inlineStr">
@@ -2490,17 +2434,17 @@
     <row r="47">
       <c r="A47" s="27" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B47" s="27" t="inlineStr">
         <is>
-          <t>7:45PM</t>
+          <t>1:02PM</t>
         </is>
       </c>
       <c r="C47" s="27" t="inlineStr">
         <is>
-          <t>8:03PM</t>
+          <t>1:20PM</t>
         </is>
       </c>
       <c r="D47" s="27" t="inlineStr">
@@ -2540,17 +2484,17 @@
     <row r="48">
       <c r="A48" s="28" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B48" s="28" t="inlineStr">
         <is>
-          <t>8:03PM</t>
+          <t>1:20PM</t>
         </is>
       </c>
       <c r="C48" s="28" t="inlineStr">
         <is>
-          <t>8:21PM</t>
+          <t>1:38PM</t>
         </is>
       </c>
       <c r="D48" s="28" t="inlineStr">
@@ -2590,17 +2534,17 @@
     <row r="49">
       <c r="A49" s="27" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B49" s="27" t="inlineStr">
         <is>
-          <t>9:00PM</t>
+          <t>1:38PM</t>
         </is>
       </c>
       <c r="C49" s="27" t="inlineStr">
         <is>
-          <t>9:30PM</t>
+          <t>1:56PM</t>
         </is>
       </c>
       <c r="D49" s="27" t="inlineStr">
@@ -2954,12 +2898,12 @@
       </c>
       <c r="B18" s="27" t="inlineStr">
         <is>
-          <t>10:45AM</t>
+          <t>10:55AM</t>
         </is>
       </c>
       <c r="C18" s="27" t="inlineStr">
         <is>
-          <t>11:00AM</t>
+          <t>11:10AM</t>
         </is>
       </c>
       <c r="D18" s="27" t="inlineStr">
@@ -3004,12 +2948,12 @@
       </c>
       <c r="B19" s="28" t="inlineStr">
         <is>
-          <t>10:45AM</t>
+          <t>10:55AM</t>
         </is>
       </c>
       <c r="C19" s="28" t="inlineStr">
         <is>
-          <t>11:00AM</t>
+          <t>11:10AM</t>
         </is>
       </c>
       <c r="D19" s="28" t="inlineStr">
@@ -3054,12 +2998,12 @@
       </c>
       <c r="B20" s="27" t="inlineStr">
         <is>
-          <t>11:00AM</t>
+          <t>11:20AM</t>
         </is>
       </c>
       <c r="C20" s="27" t="inlineStr">
         <is>
-          <t>11:15AM</t>
+          <t>11:35AM</t>
         </is>
       </c>
       <c r="D20" s="27" t="inlineStr">
@@ -3104,12 +3048,12 @@
       </c>
       <c r="B21" s="28" t="inlineStr">
         <is>
-          <t>11:00AM</t>
+          <t>11:20AM</t>
         </is>
       </c>
       <c r="C21" s="28" t="inlineStr">
         <is>
-          <t>11:15AM</t>
+          <t>11:35AM</t>
         </is>
       </c>
       <c r="D21" s="28" t="inlineStr">
@@ -3154,12 +3098,12 @@
       </c>
       <c r="B22" s="27" t="inlineStr">
         <is>
-          <t>11:15AM</t>
+          <t>11:35AM</t>
         </is>
       </c>
       <c r="C22" s="27" t="inlineStr">
         <is>
-          <t>11:30AM</t>
+          <t>11:50AM</t>
         </is>
       </c>
       <c r="D22" s="27" t="inlineStr">
@@ -3204,12 +3148,12 @@
       </c>
       <c r="B23" s="28" t="inlineStr">
         <is>
-          <t>11:15AM</t>
+          <t>11:35AM</t>
         </is>
       </c>
       <c r="C23" s="28" t="inlineStr">
         <is>
-          <t>11:30AM</t>
+          <t>11:50AM</t>
         </is>
       </c>
       <c r="D23" s="28" t="inlineStr">
@@ -3254,12 +3198,12 @@
       </c>
       <c r="B24" s="27" t="inlineStr">
         <is>
-          <t>11:30AM</t>
+          <t>12:00PM</t>
         </is>
       </c>
       <c r="C24" s="27" t="inlineStr">
         <is>
-          <t>11:45AM</t>
+          <t>12:15PM</t>
         </is>
       </c>
       <c r="D24" s="27" t="inlineStr">
@@ -3304,12 +3248,12 @@
       </c>
       <c r="B25" s="28" t="inlineStr">
         <is>
-          <t>11:30AM</t>
+          <t>12:00PM</t>
         </is>
       </c>
       <c r="C25" s="28" t="inlineStr">
         <is>
-          <t>11:45AM</t>
+          <t>12:15PM</t>
         </is>
       </c>
       <c r="D25" s="28" t="inlineStr">
@@ -3354,12 +3298,12 @@
       </c>
       <c r="B26" s="27" t="inlineStr">
         <is>
-          <t>11:45AM</t>
+          <t>12:25PM</t>
         </is>
       </c>
       <c r="C26" s="27" t="inlineStr">
         <is>
-          <t>12:00PM</t>
+          <t>12:40PM</t>
         </is>
       </c>
       <c r="D26" s="27" t="inlineStr">
@@ -3404,12 +3348,12 @@
       </c>
       <c r="B27" s="28" t="inlineStr">
         <is>
-          <t>11:45AM</t>
+          <t>12:25PM</t>
         </is>
       </c>
       <c r="C27" s="28" t="inlineStr">
         <is>
-          <t>12:00PM</t>
+          <t>12:40PM</t>
         </is>
       </c>
       <c r="D27" s="28" t="inlineStr">
@@ -3449,17 +3393,17 @@
     <row r="28">
       <c r="A28" s="27" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B28" s="27" t="inlineStr">
         <is>
-          <t>12:00PM</t>
+          <t>11:50AM</t>
         </is>
       </c>
       <c r="C28" s="27" t="inlineStr">
         <is>
-          <t>12:15PM</t>
+          <t>12:05PM</t>
         </is>
       </c>
       <c r="D28" s="27" t="inlineStr">
@@ -3499,17 +3443,17 @@
     <row r="29">
       <c r="A29" s="28" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B29" s="28" t="inlineStr">
         <is>
-          <t>12:00PM</t>
+          <t>11:50AM</t>
         </is>
       </c>
       <c r="C29" s="28" t="inlineStr">
         <is>
-          <t>12:15PM</t>
+          <t>12:05PM</t>
         </is>
       </c>
       <c r="D29" s="28" t="inlineStr">
@@ -3549,17 +3493,17 @@
     <row r="30">
       <c r="A30" s="27" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B30" s="27" t="inlineStr">
         <is>
-          <t>12:15PM</t>
+          <t>12:05PM</t>
         </is>
       </c>
       <c r="C30" s="27" t="inlineStr">
         <is>
-          <t>12:30PM</t>
+          <t>12:20PM</t>
         </is>
       </c>
       <c r="D30" s="27" t="inlineStr">
@@ -4247,12 +4191,12 @@
       </c>
       <c r="B47" s="27" t="inlineStr">
         <is>
-          <t>8:15AM</t>
+          <t>8:25AM</t>
         </is>
       </c>
       <c r="C47" s="27" t="inlineStr">
         <is>
-          <t>8:30AM</t>
+          <t>8:40AM</t>
         </is>
       </c>
       <c r="D47" s="27" t="inlineStr">
@@ -4297,12 +4241,12 @@
       </c>
       <c r="B48" s="28" t="inlineStr">
         <is>
-          <t>8:15AM</t>
+          <t>8:25AM</t>
         </is>
       </c>
       <c r="C48" s="28" t="inlineStr">
         <is>
-          <t>8:30AM</t>
+          <t>8:40AM</t>
         </is>
       </c>
       <c r="D48" s="28" t="inlineStr">
@@ -4347,12 +4291,12 @@
       </c>
       <c r="B49" s="27" t="inlineStr">
         <is>
-          <t>8:30AM</t>
+          <t>8:50AM</t>
         </is>
       </c>
       <c r="C49" s="27" t="inlineStr">
         <is>
-          <t>8:45AM</t>
+          <t>9:05AM</t>
         </is>
       </c>
       <c r="D49" s="27" t="inlineStr">
@@ -4397,12 +4341,12 @@
       </c>
       <c r="B50" s="28" t="inlineStr">
         <is>
-          <t>8:30AM</t>
+          <t>8:50AM</t>
         </is>
       </c>
       <c r="C50" s="28" t="inlineStr">
         <is>
-          <t>8:45AM</t>
+          <t>9:05AM</t>
         </is>
       </c>
       <c r="D50" s="28" t="inlineStr">
@@ -4447,17 +4391,17 @@
       </c>
       <c r="B51" s="27" t="inlineStr">
         <is>
-          <t>8:45AM</t>
+          <t>12:30PM</t>
         </is>
       </c>
       <c r="C51" s="27" t="inlineStr">
         <is>
-          <t>9:00AM</t>
+          <t>12:45PM</t>
         </is>
       </c>
       <c r="D51" s="27" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Under 36</t>
         </is>
       </c>
       <c r="E51" s="27" t="n">
@@ -4465,7 +4409,7 @@
       </c>
       <c r="F51" s="27" t="inlineStr">
         <is>
-          <t>SR-SF1</t>
+          <t>U36-GA-2</t>
         </is>
       </c>
       <c r="G51" s="27" t="inlineStr">
@@ -4475,7 +4419,7 @@
       </c>
       <c r="H51" s="27" t="inlineStr">
         <is>
-          <t>Group A 1st</t>
+          <t>Tapabrata Dutta</t>
         </is>
       </c>
       <c r="I51" s="27" t="inlineStr">
@@ -4485,7 +4429,7 @@
       </c>
       <c r="J51" s="27" t="inlineStr">
         <is>
-          <t>Group B 2nd</t>
+          <t>Prakshal Shah</t>
         </is>
       </c>
     </row>
@@ -4497,17 +4441,17 @@
       </c>
       <c r="B52" s="28" t="inlineStr">
         <is>
-          <t>8:45AM</t>
+          <t>3:00PM</t>
         </is>
       </c>
       <c r="C52" s="28" t="inlineStr">
         <is>
-          <t>9:00AM</t>
+          <t>3:15PM</t>
         </is>
       </c>
       <c r="D52" s="28" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Under 36</t>
         </is>
       </c>
       <c r="E52" s="28" t="n">
@@ -4515,17 +4459,17 @@
       </c>
       <c r="F52" s="28" t="inlineStr">
         <is>
-          <t>SR-SF2</t>
+          <t>U36-GA-1</t>
         </is>
       </c>
       <c r="G52" s="28" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H52" s="28" t="inlineStr">
         <is>
-          <t>Group B 1st</t>
+          <t>Jashit Bajaj</t>
         </is>
       </c>
       <c r="I52" s="28" t="inlineStr">
@@ -4535,7 +4479,7 @@
       </c>
       <c r="J52" s="28" t="inlineStr">
         <is>
-          <t>Group A 2nd</t>
+          <t>Ravi Modi</t>
         </is>
       </c>
     </row>
@@ -4547,17 +4491,17 @@
       </c>
       <c r="B53" s="27" t="inlineStr">
         <is>
-          <t>9:00AM</t>
+          <t>3:00PM</t>
         </is>
       </c>
       <c r="C53" s="27" t="inlineStr">
         <is>
-          <t>9:25AM</t>
+          <t>3:15PM</t>
         </is>
       </c>
       <c r="D53" s="27" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Under 36</t>
         </is>
       </c>
       <c r="E53" s="27" t="n">
@@ -4565,17 +4509,17 @@
       </c>
       <c r="F53" s="27" t="inlineStr">
         <is>
-          <t>SR-FINAL</t>
+          <t>U36-GB-1</t>
         </is>
       </c>
       <c r="G53" s="27" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H53" s="27" t="inlineStr">
         <is>
-          <t>Winner SF1</t>
+          <t>Tej</t>
         </is>
       </c>
       <c r="I53" s="27" t="inlineStr">
@@ -4585,7 +4529,7 @@
       </c>
       <c r="J53" s="27" t="inlineStr">
         <is>
-          <t>Winner SF2</t>
+          <t>Dr Rahul Modi</t>
         </is>
       </c>
     </row>
@@ -4597,12 +4541,12 @@
       </c>
       <c r="B54" s="28" t="inlineStr">
         <is>
-          <t>12:15PM</t>
+          <t>3:15PM</t>
         </is>
       </c>
       <c r="C54" s="28" t="inlineStr">
         <is>
-          <t>12:30PM</t>
+          <t>3:30PM</t>
         </is>
       </c>
       <c r="D54" s="28" t="inlineStr">
@@ -4615,17 +4559,17 @@
       </c>
       <c r="F54" s="28" t="inlineStr">
         <is>
-          <t>U36-GA-2</t>
+          <t>U36-GB-2</t>
         </is>
       </c>
       <c r="G54" s="28" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H54" s="28" t="inlineStr">
         <is>
-          <t>Tapabrata Dutta</t>
+          <t>Ankur Mahante</t>
         </is>
       </c>
       <c r="I54" s="28" t="inlineStr">
@@ -4635,7 +4579,7 @@
       </c>
       <c r="J54" s="28" t="inlineStr">
         <is>
-          <t>Prakshal Shah</t>
+          <t>Sudip Parui</t>
         </is>
       </c>
     </row>
@@ -4647,12 +4591,12 @@
       </c>
       <c r="B55" s="27" t="inlineStr">
         <is>
-          <t>3:00PM</t>
+          <t>3:25PM</t>
         </is>
       </c>
       <c r="C55" s="27" t="inlineStr">
         <is>
-          <t>3:15PM</t>
+          <t>3:40PM</t>
         </is>
       </c>
       <c r="D55" s="27" t="inlineStr">
@@ -4665,7 +4609,7 @@
       </c>
       <c r="F55" s="27" t="inlineStr">
         <is>
-          <t>U36-GA-1</t>
+          <t>U36-GA-3</t>
         </is>
       </c>
       <c r="G55" s="27" t="inlineStr">
@@ -4675,7 +4619,7 @@
       </c>
       <c r="H55" s="27" t="inlineStr">
         <is>
-          <t>Jashit Bajaj</t>
+          <t>Ravi Modi</t>
         </is>
       </c>
       <c r="I55" s="27" t="inlineStr">
@@ -4685,7 +4629,7 @@
       </c>
       <c r="J55" s="27" t="inlineStr">
         <is>
-          <t>Ravi Modi</t>
+          <t>Amar Parulekar</t>
         </is>
       </c>
     </row>
@@ -4697,12 +4641,12 @@
       </c>
       <c r="B56" s="28" t="inlineStr">
         <is>
-          <t>3:00PM</t>
+          <t>3:40PM</t>
         </is>
       </c>
       <c r="C56" s="28" t="inlineStr">
         <is>
-          <t>3:15PM</t>
+          <t>3:55PM</t>
         </is>
       </c>
       <c r="D56" s="28" t="inlineStr">
@@ -4715,17 +4659,17 @@
       </c>
       <c r="F56" s="28" t="inlineStr">
         <is>
-          <t>U36-GB-1</t>
+          <t>U36-GA-4</t>
         </is>
       </c>
       <c r="G56" s="28" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H56" s="28" t="inlineStr">
         <is>
-          <t>Tej</t>
+          <t>Jashit Bajaj</t>
         </is>
       </c>
       <c r="I56" s="28" t="inlineStr">
@@ -4735,7 +4679,7 @@
       </c>
       <c r="J56" s="28" t="inlineStr">
         <is>
-          <t>Dr Rahul Modi</t>
+          <t>Tapabrata Dutta</t>
         </is>
       </c>
     </row>
@@ -4747,12 +4691,12 @@
       </c>
       <c r="B57" s="27" t="inlineStr">
         <is>
-          <t>3:15PM</t>
+          <t>3:50PM</t>
         </is>
       </c>
       <c r="C57" s="27" t="inlineStr">
         <is>
-          <t>3:30PM</t>
+          <t>4:05PM</t>
         </is>
       </c>
       <c r="D57" s="27" t="inlineStr">
@@ -4765,17 +4709,17 @@
       </c>
       <c r="F57" s="27" t="inlineStr">
         <is>
-          <t>U36-GA-3</t>
+          <t>U36-GA-5</t>
         </is>
       </c>
       <c r="G57" s="27" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H57" s="27" t="inlineStr">
         <is>
-          <t>Ravi Modi</t>
+          <t>Prakshal Shah</t>
         </is>
       </c>
       <c r="I57" s="27" t="inlineStr">
@@ -4797,12 +4741,12 @@
       </c>
       <c r="B58" s="28" t="inlineStr">
         <is>
-          <t>3:15PM</t>
+          <t>4:05PM</t>
         </is>
       </c>
       <c r="C58" s="28" t="inlineStr">
         <is>
-          <t>3:30PM</t>
+          <t>4:20PM</t>
         </is>
       </c>
       <c r="D58" s="28" t="inlineStr">
@@ -4815,7 +4759,7 @@
       </c>
       <c r="F58" s="28" t="inlineStr">
         <is>
-          <t>U36-GB-2</t>
+          <t>U36-GB-3</t>
         </is>
       </c>
       <c r="G58" s="28" t="inlineStr">
@@ -4825,7 +4769,7 @@
       </c>
       <c r="H58" s="28" t="inlineStr">
         <is>
-          <t>Ankur Mahante</t>
+          <t>Dr Rahul Modi</t>
         </is>
       </c>
       <c r="I58" s="28" t="inlineStr">
@@ -4835,7 +4779,7 @@
       </c>
       <c r="J58" s="28" t="inlineStr">
         <is>
-          <t>Sudip Parui</t>
+          <t>Tanmay Sharma</t>
         </is>
       </c>
     </row>
@@ -4847,12 +4791,12 @@
       </c>
       <c r="B59" s="27" t="inlineStr">
         <is>
-          <t>3:30PM</t>
+          <t>4:15PM</t>
         </is>
       </c>
       <c r="C59" s="27" t="inlineStr">
         <is>
-          <t>3:45PM</t>
+          <t>4:30PM</t>
         </is>
       </c>
       <c r="D59" s="27" t="inlineStr">
@@ -4865,7 +4809,7 @@
       </c>
       <c r="F59" s="27" t="inlineStr">
         <is>
-          <t>U36-GA-4</t>
+          <t>U36-GA-7</t>
         </is>
       </c>
       <c r="G59" s="27" t="inlineStr">
@@ -4885,7 +4829,7 @@
       </c>
       <c r="J59" s="27" t="inlineStr">
         <is>
-          <t>Tapabrata Dutta</t>
+          <t>Prakshal Shah</t>
         </is>
       </c>
     </row>
@@ -4897,12 +4841,12 @@
       </c>
       <c r="B60" s="28" t="inlineStr">
         <is>
-          <t>3:30PM</t>
+          <t>4:30PM</t>
         </is>
       </c>
       <c r="C60" s="28" t="inlineStr">
         <is>
-          <t>3:45PM</t>
+          <t>4:45PM</t>
         </is>
       </c>
       <c r="D60" s="28" t="inlineStr">
@@ -4915,17 +4859,17 @@
       </c>
       <c r="F60" s="28" t="inlineStr">
         <is>
-          <t>U36-GA-5</t>
+          <t>U36-GB-4</t>
         </is>
       </c>
       <c r="G60" s="28" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H60" s="28" t="inlineStr">
         <is>
-          <t>Prakshal Shah</t>
+          <t>Tej</t>
         </is>
       </c>
       <c r="I60" s="28" t="inlineStr">
@@ -4935,7 +4879,7 @@
       </c>
       <c r="J60" s="28" t="inlineStr">
         <is>
-          <t>Amar Parulekar</t>
+          <t>Ankur Mahante</t>
         </is>
       </c>
     </row>
@@ -4947,12 +4891,12 @@
       </c>
       <c r="B61" s="27" t="inlineStr">
         <is>
-          <t>3:45PM</t>
+          <t>4:30PM</t>
         </is>
       </c>
       <c r="C61" s="27" t="inlineStr">
         <is>
-          <t>4:00PM</t>
+          <t>4:45PM</t>
         </is>
       </c>
       <c r="D61" s="27" t="inlineStr">
@@ -4965,17 +4909,17 @@
       </c>
       <c r="F61" s="27" t="inlineStr">
         <is>
-          <t>U36-GA-7</t>
+          <t>U36-GB-5</t>
         </is>
       </c>
       <c r="G61" s="27" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H61" s="27" t="inlineStr">
         <is>
-          <t>Jashit Bajaj</t>
+          <t>Sudip Parui</t>
         </is>
       </c>
       <c r="I61" s="27" t="inlineStr">
@@ -4985,7 +4929,7 @@
       </c>
       <c r="J61" s="27" t="inlineStr">
         <is>
-          <t>Prakshal Shah</t>
+          <t>Tanmay Sharma</t>
         </is>
       </c>
     </row>
@@ -4997,12 +4941,12 @@
       </c>
       <c r="B62" s="28" t="inlineStr">
         <is>
-          <t>3:45PM</t>
+          <t>4:45PM</t>
         </is>
       </c>
       <c r="C62" s="28" t="inlineStr">
         <is>
-          <t>4:00PM</t>
+          <t>5:00PM</t>
         </is>
       </c>
       <c r="D62" s="28" t="inlineStr">
@@ -5015,17 +4959,17 @@
       </c>
       <c r="F62" s="28" t="inlineStr">
         <is>
-          <t>U36-GB-3</t>
+          <t>U36-GA-6</t>
         </is>
       </c>
       <c r="G62" s="28" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H62" s="28" t="inlineStr">
         <is>
-          <t>Dr Rahul Modi</t>
+          <t>Ravi Modi</t>
         </is>
       </c>
       <c r="I62" s="28" t="inlineStr">
@@ -5035,7 +4979,7 @@
       </c>
       <c r="J62" s="28" t="inlineStr">
         <is>
-          <t>Tanmay Sharma</t>
+          <t>Tapabrata Dutta</t>
         </is>
       </c>
     </row>
@@ -5047,12 +4991,12 @@
       </c>
       <c r="B63" s="27" t="inlineStr">
         <is>
-          <t>4:00PM</t>
+          <t>4:55PM</t>
         </is>
       </c>
       <c r="C63" s="27" t="inlineStr">
         <is>
-          <t>4:15PM</t>
+          <t>5:10PM</t>
         </is>
       </c>
       <c r="D63" s="27" t="inlineStr">
@@ -5065,17 +5009,17 @@
       </c>
       <c r="F63" s="27" t="inlineStr">
         <is>
-          <t>U36-GB-4</t>
+          <t>U36-GB-6</t>
         </is>
       </c>
       <c r="G63" s="27" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H63" s="27" t="inlineStr">
         <is>
-          <t>Tej</t>
+          <t>Dr Rahul Modi</t>
         </is>
       </c>
       <c r="I63" s="27" t="inlineStr">
@@ -5097,12 +5041,12 @@
       </c>
       <c r="B64" s="28" t="inlineStr">
         <is>
-          <t>4:00PM</t>
+          <t>5:10PM</t>
         </is>
       </c>
       <c r="C64" s="28" t="inlineStr">
         <is>
-          <t>4:15PM</t>
+          <t>5:25PM</t>
         </is>
       </c>
       <c r="D64" s="28" t="inlineStr">
@@ -5115,17 +5059,17 @@
       </c>
       <c r="F64" s="28" t="inlineStr">
         <is>
-          <t>U36-GB-5</t>
+          <t>U36-GA-8</t>
         </is>
       </c>
       <c r="G64" s="28" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H64" s="28" t="inlineStr">
         <is>
-          <t>Sudip Parui</t>
+          <t>Tapabrata Dutta</t>
         </is>
       </c>
       <c r="I64" s="28" t="inlineStr">
@@ -5135,7 +5079,7 @@
       </c>
       <c r="J64" s="28" t="inlineStr">
         <is>
-          <t>Tanmay Sharma</t>
+          <t>Amar Parulekar</t>
         </is>
       </c>
     </row>
@@ -5147,12 +5091,12 @@
       </c>
       <c r="B65" s="27" t="inlineStr">
         <is>
-          <t>4:15PM</t>
+          <t>5:20PM</t>
         </is>
       </c>
       <c r="C65" s="27" t="inlineStr">
         <is>
-          <t>4:30PM</t>
+          <t>5:35PM</t>
         </is>
       </c>
       <c r="D65" s="27" t="inlineStr">
@@ -5165,17 +5109,17 @@
       </c>
       <c r="F65" s="27" t="inlineStr">
         <is>
-          <t>U36-GA-6</t>
+          <t>U36-GB-8</t>
         </is>
       </c>
       <c r="G65" s="27" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H65" s="27" t="inlineStr">
         <is>
-          <t>Ravi Modi</t>
+          <t>Ankur Mahante</t>
         </is>
       </c>
       <c r="I65" s="27" t="inlineStr">
@@ -5185,7 +5129,7 @@
       </c>
       <c r="J65" s="27" t="inlineStr">
         <is>
-          <t>Tapabrata Dutta</t>
+          <t>Tanmay Sharma</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5141,12 @@
       </c>
       <c r="B66" s="28" t="inlineStr">
         <is>
-          <t>4:15PM</t>
+          <t>5:35PM</t>
         </is>
       </c>
       <c r="C66" s="28" t="inlineStr">
         <is>
-          <t>4:30PM</t>
+          <t>5:50PM</t>
         </is>
       </c>
       <c r="D66" s="28" t="inlineStr">
@@ -5215,17 +5159,17 @@
       </c>
       <c r="F66" s="28" t="inlineStr">
         <is>
-          <t>U36-GB-6</t>
+          <t>U36-GA-10</t>
         </is>
       </c>
       <c r="G66" s="28" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H66" s="28" t="inlineStr">
         <is>
-          <t>Dr Rahul Modi</t>
+          <t>Jashit Bajaj</t>
         </is>
       </c>
       <c r="I66" s="28" t="inlineStr">
@@ -5235,7 +5179,7 @@
       </c>
       <c r="J66" s="28" t="inlineStr">
         <is>
-          <t>Ankur Mahante</t>
+          <t>Amar Parulekar</t>
         </is>
       </c>
     </row>
@@ -5247,17 +5191,17 @@
       </c>
       <c r="B67" s="27" t="inlineStr">
         <is>
-          <t>4:30PM</t>
+          <t>5:35PM</t>
         </is>
       </c>
       <c r="C67" s="27" t="inlineStr">
         <is>
-          <t>4:45PM</t>
+          <t>5:50PM</t>
         </is>
       </c>
       <c r="D67" s="27" t="inlineStr">
         <is>
-          <t>Under 36</t>
+          <t>Under 46</t>
         </is>
       </c>
       <c r="E67" s="27" t="n">
@@ -5265,17 +5209,17 @@
       </c>
       <c r="F67" s="27" t="inlineStr">
         <is>
-          <t>U36-GA-8</t>
+          <t>U46-GB-4</t>
         </is>
       </c>
       <c r="G67" s="27" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H67" s="27" t="inlineStr">
         <is>
-          <t>Tapabrata Dutta</t>
+          <t>Mukul Joshi</t>
         </is>
       </c>
       <c r="I67" s="27" t="inlineStr">
@@ -5285,7 +5229,7 @@
       </c>
       <c r="J67" s="27" t="inlineStr">
         <is>
-          <t>Amar Parulekar</t>
+          <t>Vinod Agrawal</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5241,12 @@
       </c>
       <c r="B68" s="28" t="inlineStr">
         <is>
-          <t>4:30PM</t>
+          <t>5:50PM</t>
         </is>
       </c>
       <c r="C68" s="28" t="inlineStr">
         <is>
-          <t>4:45PM</t>
+          <t>6:05PM</t>
         </is>
       </c>
       <c r="D68" s="28" t="inlineStr">
@@ -5315,7 +5259,7 @@
       </c>
       <c r="F68" s="28" t="inlineStr">
         <is>
-          <t>U36-GB-8</t>
+          <t>U36-GB-7</t>
         </is>
       </c>
       <c r="G68" s="28" t="inlineStr">
@@ -5325,7 +5269,7 @@
       </c>
       <c r="H68" s="28" t="inlineStr">
         <is>
-          <t>Ankur Mahante</t>
+          <t>Tej</t>
         </is>
       </c>
       <c r="I68" s="28" t="inlineStr">
@@ -5335,7 +5279,7 @@
       </c>
       <c r="J68" s="28" t="inlineStr">
         <is>
-          <t>Tanmay Sharma</t>
+          <t>Sudip Parui</t>
         </is>
       </c>
     </row>
@@ -5347,17 +5291,17 @@
       </c>
       <c r="B69" s="27" t="inlineStr">
         <is>
-          <t>4:45PM</t>
+          <t>6:00PM</t>
         </is>
       </c>
       <c r="C69" s="27" t="inlineStr">
         <is>
-          <t>5:00PM</t>
+          <t>6:15PM</t>
         </is>
       </c>
       <c r="D69" s="27" t="inlineStr">
         <is>
-          <t>Under 36</t>
+          <t>Under 46</t>
         </is>
       </c>
       <c r="E69" s="27" t="n">
@@ -5365,7 +5309,7 @@
       </c>
       <c r="F69" s="27" t="inlineStr">
         <is>
-          <t>U36-GA-10</t>
+          <t>U46-GB-1</t>
         </is>
       </c>
       <c r="G69" s="27" t="inlineStr">
@@ -5375,7 +5319,7 @@
       </c>
       <c r="H69" s="27" t="inlineStr">
         <is>
-          <t>Jashit Bajaj</t>
+          <t>Amit Ranka</t>
         </is>
       </c>
       <c r="I69" s="27" t="inlineStr">
@@ -5385,7 +5329,7 @@
       </c>
       <c r="J69" s="27" t="inlineStr">
         <is>
-          <t>Amar Parulekar</t>
+          <t>Mukul Joshi</t>
         </is>
       </c>
     </row>
@@ -5397,12 +5341,12 @@
       </c>
       <c r="B70" s="28" t="inlineStr">
         <is>
-          <t>4:45PM</t>
+          <t>6:05PM</t>
         </is>
       </c>
       <c r="C70" s="28" t="inlineStr">
         <is>
-          <t>5:00PM</t>
+          <t>6:20PM</t>
         </is>
       </c>
       <c r="D70" s="28" t="inlineStr">
@@ -5415,7 +5359,7 @@
       </c>
       <c r="F70" s="28" t="inlineStr">
         <is>
-          <t>U46-GB-4</t>
+          <t>U46-GA-1</t>
         </is>
       </c>
       <c r="G70" s="28" t="inlineStr">
@@ -5425,7 +5369,7 @@
       </c>
       <c r="H70" s="28" t="inlineStr">
         <is>
-          <t>Mukul Joshi</t>
+          <t>Anuj Shah</t>
         </is>
       </c>
       <c r="I70" s="28" t="inlineStr">
@@ -5435,7 +5379,7 @@
       </c>
       <c r="J70" s="28" t="inlineStr">
         <is>
-          <t>Vinod Agrawal</t>
+          <t>Nikunj Jhala</t>
         </is>
       </c>
     </row>
@@ -5447,12 +5391,12 @@
       </c>
       <c r="B71" s="27" t="inlineStr">
         <is>
-          <t>5:00PM</t>
+          <t>6:15PM</t>
         </is>
       </c>
       <c r="C71" s="27" t="inlineStr">
         <is>
-          <t>5:15PM</t>
+          <t>6:30PM</t>
         </is>
       </c>
       <c r="D71" s="27" t="inlineStr">
@@ -5465,17 +5409,17 @@
       </c>
       <c r="F71" s="27" t="inlineStr">
         <is>
-          <t>U36-GB-7</t>
+          <t>U36-GA-9</t>
         </is>
       </c>
       <c r="G71" s="27" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H71" s="27" t="inlineStr">
         <is>
-          <t>Tej</t>
+          <t>Ravi Modi</t>
         </is>
       </c>
       <c r="I71" s="27" t="inlineStr">
@@ -5485,7 +5429,7 @@
       </c>
       <c r="J71" s="27" t="inlineStr">
         <is>
-          <t>Sudip Parui</t>
+          <t>Prakshal Shah</t>
         </is>
       </c>
     </row>
@@ -5497,12 +5441,12 @@
       </c>
       <c r="B72" s="28" t="inlineStr">
         <is>
-          <t>5:00PM</t>
+          <t>6:25PM</t>
         </is>
       </c>
       <c r="C72" s="28" t="inlineStr">
         <is>
-          <t>5:15PM</t>
+          <t>6:40PM</t>
         </is>
       </c>
       <c r="D72" s="28" t="inlineStr">
@@ -5515,12 +5459,12 @@
       </c>
       <c r="F72" s="28" t="inlineStr">
         <is>
-          <t>U46-GB-1</t>
+          <t>U46-GB-5</t>
         </is>
       </c>
       <c r="G72" s="28" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H72" s="28" t="inlineStr">
@@ -5535,7 +5479,7 @@
       </c>
       <c r="J72" s="28" t="inlineStr">
         <is>
-          <t>Mukul Joshi</t>
+          <t>Vinod Agrawal</t>
         </is>
       </c>
     </row>
@@ -5547,17 +5491,17 @@
       </c>
       <c r="B73" s="27" t="inlineStr">
         <is>
-          <t>5:15PM</t>
+          <t>6:30PM</t>
         </is>
       </c>
       <c r="C73" s="27" t="inlineStr">
         <is>
-          <t>5:30PM</t>
+          <t>6:45PM</t>
         </is>
       </c>
       <c r="D73" s="27" t="inlineStr">
         <is>
-          <t>Under 36</t>
+          <t>Under 46</t>
         </is>
       </c>
       <c r="E73" s="27" t="n">
@@ -5565,7 +5509,7 @@
       </c>
       <c r="F73" s="27" t="inlineStr">
         <is>
-          <t>U36-GA-9</t>
+          <t>U46-GA-3</t>
         </is>
       </c>
       <c r="G73" s="27" t="inlineStr">
@@ -5575,7 +5519,7 @@
       </c>
       <c r="H73" s="27" t="inlineStr">
         <is>
-          <t>Ravi Modi</t>
+          <t>Nikunj Jhala</t>
         </is>
       </c>
       <c r="I73" s="27" t="inlineStr">
@@ -5585,7 +5529,7 @@
       </c>
       <c r="J73" s="27" t="inlineStr">
         <is>
-          <t>Prakshal Shah</t>
+          <t>Nilesh Bagaria</t>
         </is>
       </c>
     </row>
@@ -5597,17 +5541,17 @@
       </c>
       <c r="B74" s="28" t="inlineStr">
         <is>
-          <t>5:15PM</t>
+          <t>6:40PM</t>
         </is>
       </c>
       <c r="C74" s="28" t="inlineStr">
         <is>
-          <t>5:30PM</t>
+          <t>6:55PM</t>
         </is>
       </c>
       <c r="D74" s="28" t="inlineStr">
         <is>
-          <t>Under 46</t>
+          <t>Under 36</t>
         </is>
       </c>
       <c r="E74" s="28" t="n">
@@ -5615,7 +5559,7 @@
       </c>
       <c r="F74" s="28" t="inlineStr">
         <is>
-          <t>U46-GA-1</t>
+          <t>U36-GB-9</t>
         </is>
       </c>
       <c r="G74" s="28" t="inlineStr">
@@ -5625,7 +5569,7 @@
       </c>
       <c r="H74" s="28" t="inlineStr">
         <is>
-          <t>Anuj Shah</t>
+          <t>Dr Rahul Modi</t>
         </is>
       </c>
       <c r="I74" s="28" t="inlineStr">
@@ -5635,7 +5579,7 @@
       </c>
       <c r="J74" s="28" t="inlineStr">
         <is>
-          <t>Nikunj Jhala</t>
+          <t>Sudip Parui</t>
         </is>
       </c>
     </row>
@@ -5647,17 +5591,17 @@
       </c>
       <c r="B75" s="27" t="inlineStr">
         <is>
-          <t>5:30PM</t>
+          <t>6:45PM</t>
         </is>
       </c>
       <c r="C75" s="27" t="inlineStr">
         <is>
-          <t>5:45PM</t>
+          <t>7:00PM</t>
         </is>
       </c>
       <c r="D75" s="27" t="inlineStr">
         <is>
-          <t>Under 46</t>
+          <t>Under 36</t>
         </is>
       </c>
       <c r="E75" s="27" t="n">
@@ -5665,7 +5609,7 @@
       </c>
       <c r="F75" s="27" t="inlineStr">
         <is>
-          <t>U46-GA-3</t>
+          <t>U36-GB-10</t>
         </is>
       </c>
       <c r="G75" s="27" t="inlineStr">
@@ -5675,7 +5619,7 @@
       </c>
       <c r="H75" s="27" t="inlineStr">
         <is>
-          <t>Nikunj Jhala</t>
+          <t>Tej</t>
         </is>
       </c>
       <c r="I75" s="27" t="inlineStr">
@@ -5685,7 +5629,7 @@
       </c>
       <c r="J75" s="27" t="inlineStr">
         <is>
-          <t>Nilesh Bagaria</t>
+          <t>Tanmay Sharma</t>
         </is>
       </c>
     </row>
@@ -5697,17 +5641,17 @@
       </c>
       <c r="B76" s="28" t="inlineStr">
         <is>
-          <t>5:30PM</t>
+          <t>6:55PM</t>
         </is>
       </c>
       <c r="C76" s="28" t="inlineStr">
         <is>
-          <t>5:45PM</t>
+          <t>7:10PM</t>
         </is>
       </c>
       <c r="D76" s="28" t="inlineStr">
         <is>
-          <t>Under 46</t>
+          <t>Under 15</t>
         </is>
       </c>
       <c r="E76" s="28" t="n">
@@ -5715,7 +5659,7 @@
       </c>
       <c r="F76" s="28" t="inlineStr">
         <is>
-          <t>U46-GB-5</t>
+          <t>U15-GA-1</t>
         </is>
       </c>
       <c r="G76" s="28" t="inlineStr">
@@ -5725,7 +5669,7 @@
       </c>
       <c r="H76" s="28" t="inlineStr">
         <is>
-          <t>Amit Ranka</t>
+          <t>Shaurya Tripathi</t>
         </is>
       </c>
       <c r="I76" s="28" t="inlineStr">
@@ -5735,7 +5679,7 @@
       </c>
       <c r="J76" s="28" t="inlineStr">
         <is>
-          <t>Vinod Agrawal</t>
+          <t>Parth yadav</t>
         </is>
       </c>
     </row>
@@ -5747,17 +5691,17 @@
       </c>
       <c r="B77" s="27" t="inlineStr">
         <is>
-          <t>5:45PM</t>
+          <t>7:00PM</t>
         </is>
       </c>
       <c r="C77" s="27" t="inlineStr">
         <is>
-          <t>6:00PM</t>
+          <t>7:15PM</t>
         </is>
       </c>
       <c r="D77" s="27" t="inlineStr">
         <is>
-          <t>Under 36</t>
+          <t>Under 46</t>
         </is>
       </c>
       <c r="E77" s="27" t="n">
@@ -5765,7 +5709,7 @@
       </c>
       <c r="F77" s="27" t="inlineStr">
         <is>
-          <t>U36-GB-10</t>
+          <t>U46-GA-5</t>
         </is>
       </c>
       <c r="G77" s="27" t="inlineStr">
@@ -5775,7 +5719,7 @@
       </c>
       <c r="H77" s="27" t="inlineStr">
         <is>
-          <t>Tej</t>
+          <t>Vinit Padia</t>
         </is>
       </c>
       <c r="I77" s="27" t="inlineStr">
@@ -5785,7 +5729,7 @@
       </c>
       <c r="J77" s="27" t="inlineStr">
         <is>
-          <t>Tanmay Sharma</t>
+          <t>Nilesh Bagaria</t>
         </is>
       </c>
     </row>
@@ -5797,17 +5741,17 @@
       </c>
       <c r="B78" s="28" t="inlineStr">
         <is>
-          <t>5:45PM</t>
+          <t>7:25PM</t>
         </is>
       </c>
       <c r="C78" s="28" t="inlineStr">
         <is>
-          <t>6:00PM</t>
+          <t>7:40PM</t>
         </is>
       </c>
       <c r="D78" s="28" t="inlineStr">
         <is>
-          <t>Under 36</t>
+          <t>Under 46</t>
         </is>
       </c>
       <c r="E78" s="28" t="n">
@@ -5815,7 +5759,7 @@
       </c>
       <c r="F78" s="28" t="inlineStr">
         <is>
-          <t>U36-GB-9</t>
+          <t>U46-GA-10</t>
         </is>
       </c>
       <c r="G78" s="28" t="inlineStr">
@@ -5825,7 +5769,7 @@
       </c>
       <c r="H78" s="28" t="inlineStr">
         <is>
-          <t>Dr Rahul Modi</t>
+          <t>Anuj Shah</t>
         </is>
       </c>
       <c r="I78" s="28" t="inlineStr">
@@ -5835,7 +5779,7 @@
       </c>
       <c r="J78" s="28" t="inlineStr">
         <is>
-          <t>Sudip Parui</t>
+          <t>Nilesh Bagaria</t>
         </is>
       </c>
     </row>
@@ -5847,17 +5791,17 @@
       </c>
       <c r="B79" s="27" t="inlineStr">
         <is>
-          <t>6:00PM</t>
+          <t>7:25PM</t>
         </is>
       </c>
       <c r="C79" s="27" t="inlineStr">
         <is>
-          <t>6:15PM</t>
+          <t>7:40PM</t>
         </is>
       </c>
       <c r="D79" s="27" t="inlineStr">
         <is>
-          <t>Under 15</t>
+          <t>Under 46</t>
         </is>
       </c>
       <c r="E79" s="27" t="n">
@@ -5865,17 +5809,17 @@
       </c>
       <c r="F79" s="27" t="inlineStr">
         <is>
-          <t>U15-GA-1</t>
+          <t>U46-GB-2</t>
         </is>
       </c>
       <c r="G79" s="27" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H79" s="27" t="inlineStr">
         <is>
-          <t>Shaurya Tripathi</t>
+          <t>Adil Khan</t>
         </is>
       </c>
       <c r="I79" s="27" t="inlineStr">
@@ -5885,7 +5829,7 @@
       </c>
       <c r="J79" s="27" t="inlineStr">
         <is>
-          <t>Parth yadav</t>
+          <t>Vinod Agrawal</t>
         </is>
       </c>
     </row>
@@ -5897,17 +5841,17 @@
       </c>
       <c r="B80" s="28" t="inlineStr">
         <is>
-          <t>6:00PM</t>
+          <t>7:40PM</t>
         </is>
       </c>
       <c r="C80" s="28" t="inlineStr">
         <is>
-          <t>6:15PM</t>
+          <t>7:55PM</t>
         </is>
       </c>
       <c r="D80" s="28" t="inlineStr">
         <is>
-          <t>Under 46</t>
+          <t>Under 15</t>
         </is>
       </c>
       <c r="E80" s="28" t="n">
@@ -5915,17 +5859,17 @@
       </c>
       <c r="F80" s="28" t="inlineStr">
         <is>
-          <t>U46-GA-5</t>
+          <t>U15-GB-1</t>
         </is>
       </c>
       <c r="G80" s="28" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H80" s="28" t="inlineStr">
         <is>
-          <t>Vinit Padia</t>
+          <t>Viaan Neema</t>
         </is>
       </c>
       <c r="I80" s="28" t="inlineStr">
@@ -5935,7 +5879,7 @@
       </c>
       <c r="J80" s="28" t="inlineStr">
         <is>
-          <t>Nilesh Bagaria</t>
+          <t>Yash agarwal</t>
         </is>
       </c>
     </row>
@@ -5947,12 +5891,12 @@
       </c>
       <c r="B81" s="27" t="inlineStr">
         <is>
-          <t>6:15PM</t>
+          <t>7:50PM</t>
         </is>
       </c>
       <c r="C81" s="27" t="inlineStr">
         <is>
-          <t>6:30PM</t>
+          <t>8:05PM</t>
         </is>
       </c>
       <c r="D81" s="27" t="inlineStr">
@@ -5965,17 +5909,17 @@
       </c>
       <c r="F81" s="27" t="inlineStr">
         <is>
-          <t>U46-GA-10</t>
+          <t>U46-GB-3</t>
         </is>
       </c>
       <c r="G81" s="27" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H81" s="27" t="inlineStr">
         <is>
-          <t>Anuj Shah</t>
+          <t>Amit Ranka</t>
         </is>
       </c>
       <c r="I81" s="27" t="inlineStr">
@@ -5985,7 +5929,7 @@
       </c>
       <c r="J81" s="27" t="inlineStr">
         <is>
-          <t>Nilesh Bagaria</t>
+          <t>Adil Khan</t>
         </is>
       </c>
     </row>
@@ -5997,17 +5941,17 @@
       </c>
       <c r="B82" s="28" t="inlineStr">
         <is>
-          <t>6:15PM</t>
+          <t>7:55PM</t>
         </is>
       </c>
       <c r="C82" s="28" t="inlineStr">
         <is>
-          <t>6:30PM</t>
+          <t>8:10PM</t>
         </is>
       </c>
       <c r="D82" s="28" t="inlineStr">
         <is>
-          <t>Under 46</t>
+          <t>Under 15</t>
         </is>
       </c>
       <c r="E82" s="28" t="n">
@@ -6015,17 +5959,17 @@
       </c>
       <c r="F82" s="28" t="inlineStr">
         <is>
-          <t>U46-GB-2</t>
+          <t>U15-GA-2</t>
         </is>
       </c>
       <c r="G82" s="28" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H82" s="28" t="inlineStr">
         <is>
-          <t>Adil Khan</t>
+          <t>Shaurya Tripathi</t>
         </is>
       </c>
       <c r="I82" s="28" t="inlineStr">
@@ -6035,7 +5979,7 @@
       </c>
       <c r="J82" s="28" t="inlineStr">
         <is>
-          <t>Vinod Agrawal</t>
+          <t>Aadit Joshi</t>
         </is>
       </c>
     </row>
@@ -6047,17 +5991,17 @@
       </c>
       <c r="B83" s="27" t="inlineStr">
         <is>
-          <t>6:30PM</t>
+          <t>8:15PM</t>
         </is>
       </c>
       <c r="C83" s="27" t="inlineStr">
         <is>
-          <t>6:45PM</t>
+          <t>8:30PM</t>
         </is>
       </c>
       <c r="D83" s="27" t="inlineStr">
         <is>
-          <t>Under 15</t>
+          <t>Under 46</t>
         </is>
       </c>
       <c r="E83" s="27" t="n">
@@ -6065,17 +6009,17 @@
       </c>
       <c r="F83" s="27" t="inlineStr">
         <is>
-          <t>U15-GB-1</t>
+          <t>U46-GB-6</t>
         </is>
       </c>
       <c r="G83" s="27" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H83" s="27" t="inlineStr">
         <is>
-          <t>Viaan Neema</t>
+          <t>Mukul Joshi</t>
         </is>
       </c>
       <c r="I83" s="27" t="inlineStr">
@@ -6085,7 +6029,7 @@
       </c>
       <c r="J83" s="27" t="inlineStr">
         <is>
-          <t>Yash agarwal</t>
+          <t>Adil Khan</t>
         </is>
       </c>
     </row>
@@ -6097,17 +6041,17 @@
       </c>
       <c r="B84" s="28" t="inlineStr">
         <is>
-          <t>6:30PM</t>
+          <t>8:20PM</t>
         </is>
       </c>
       <c r="C84" s="28" t="inlineStr">
         <is>
-          <t>6:45PM</t>
+          <t>8:35PM</t>
         </is>
       </c>
       <c r="D84" s="28" t="inlineStr">
         <is>
-          <t>Under 46</t>
+          <t>Under 15</t>
         </is>
       </c>
       <c r="E84" s="28" t="n">
@@ -6115,17 +6059,17 @@
       </c>
       <c r="F84" s="28" t="inlineStr">
         <is>
-          <t>U46-GB-3</t>
+          <t>U15-GA-3</t>
         </is>
       </c>
       <c r="G84" s="28" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H84" s="28" t="inlineStr">
         <is>
-          <t>Amit Ranka</t>
+          <t>Parth yadav</t>
         </is>
       </c>
       <c r="I84" s="28" t="inlineStr">
@@ -6135,7 +6079,7 @@
       </c>
       <c r="J84" s="28" t="inlineStr">
         <is>
-          <t>Adil Khan</t>
+          <t>Aadit Joshi</t>
         </is>
       </c>
     </row>
@@ -6147,17 +6091,17 @@
       </c>
       <c r="B85" s="27" t="inlineStr">
         <is>
-          <t>6:45PM</t>
+          <t>8:30PM</t>
         </is>
       </c>
       <c r="C85" s="27" t="inlineStr">
         <is>
-          <t>7:00PM</t>
+          <t>8:45PM</t>
         </is>
       </c>
       <c r="D85" s="27" t="inlineStr">
         <is>
-          <t>Under 15</t>
+          <t>Under 46</t>
         </is>
       </c>
       <c r="E85" s="27" t="n">
@@ -6165,17 +6109,17 @@
       </c>
       <c r="F85" s="27" t="inlineStr">
         <is>
-          <t>U15-GA-2</t>
+          <t>U46-GA-2</t>
         </is>
       </c>
       <c r="G85" s="27" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H85" s="27" t="inlineStr">
         <is>
-          <t>Shaurya Tripathi</t>
+          <t>Piyush Makharia</t>
         </is>
       </c>
       <c r="I85" s="27" t="inlineStr">
@@ -6185,7 +6129,7 @@
       </c>
       <c r="J85" s="27" t="inlineStr">
         <is>
-          <t>Aadit Joshi</t>
+          <t>Vinit Padia</t>
         </is>
       </c>
     </row>
@@ -6197,12 +6141,12 @@
       </c>
       <c r="B86" s="28" t="inlineStr">
         <is>
-          <t>6:45PM</t>
+          <t>8:55PM</t>
         </is>
       </c>
       <c r="C86" s="28" t="inlineStr">
         <is>
-          <t>7:00PM</t>
+          <t>9:10PM</t>
         </is>
       </c>
       <c r="D86" s="28" t="inlineStr">
@@ -6215,7 +6159,7 @@
       </c>
       <c r="F86" s="28" t="inlineStr">
         <is>
-          <t>U46-GB-6</t>
+          <t>U46-GA-4</t>
         </is>
       </c>
       <c r="G86" s="28" t="inlineStr">
@@ -6225,7 +6169,7 @@
       </c>
       <c r="H86" s="28" t="inlineStr">
         <is>
-          <t>Mukul Joshi</t>
+          <t>Anuj Shah</t>
         </is>
       </c>
       <c r="I86" s="28" t="inlineStr">
@@ -6235,7 +6179,7 @@
       </c>
       <c r="J86" s="28" t="inlineStr">
         <is>
-          <t>Adil Khan</t>
+          <t>Piyush Makharia</t>
         </is>
       </c>
     </row>
@@ -6247,17 +6191,17 @@
       </c>
       <c r="B87" s="27" t="inlineStr">
         <is>
-          <t>7:00PM</t>
+          <t>8:55PM</t>
         </is>
       </c>
       <c r="C87" s="27" t="inlineStr">
         <is>
-          <t>7:15PM</t>
+          <t>9:10PM</t>
         </is>
       </c>
       <c r="D87" s="27" t="inlineStr">
         <is>
-          <t>Under 15</t>
+          <t>Under 46</t>
         </is>
       </c>
       <c r="E87" s="27" t="n">
@@ -6265,7 +6209,7 @@
       </c>
       <c r="F87" s="27" t="inlineStr">
         <is>
-          <t>U15-GA-3</t>
+          <t>U46-GA-9</t>
         </is>
       </c>
       <c r="G87" s="27" t="inlineStr">
@@ -6275,7 +6219,7 @@
       </c>
       <c r="H87" s="27" t="inlineStr">
         <is>
-          <t>Parth yadav</t>
+          <t>Nikunj Jhala</t>
         </is>
       </c>
       <c r="I87" s="27" t="inlineStr">
@@ -6285,24 +6229,24 @@
       </c>
       <c r="J87" s="27" t="inlineStr">
         <is>
-          <t>Aadit Joshi</t>
+          <t>Vinit Padia</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="28" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B88" s="28" t="inlineStr">
         <is>
-          <t>7:00PM</t>
+          <t>8:00AM</t>
         </is>
       </c>
       <c r="C88" s="28" t="inlineStr">
         <is>
-          <t>7:15PM</t>
+          <t>8:15AM</t>
         </is>
       </c>
       <c r="D88" s="28" t="inlineStr">
@@ -6315,7 +6259,7 @@
       </c>
       <c r="F88" s="28" t="inlineStr">
         <is>
-          <t>U46-GA-2</t>
+          <t>U46-GA-6</t>
         </is>
       </c>
       <c r="G88" s="28" t="inlineStr">
@@ -6325,34 +6269,34 @@
       </c>
       <c r="H88" s="28" t="inlineStr">
         <is>
+          <t>Nikunj Jhala</t>
+        </is>
+      </c>
+      <c r="I88" s="28" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J88" s="28" t="inlineStr">
+        <is>
           <t>Piyush Makharia</t>
-        </is>
-      </c>
-      <c r="I88" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J88" s="28" t="inlineStr">
-        <is>
-          <t>Vinit Padia</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="27" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B89" s="27" t="inlineStr">
         <is>
-          <t>7:15PM</t>
+          <t>8:00AM</t>
         </is>
       </c>
       <c r="C89" s="27" t="inlineStr">
         <is>
-          <t>7:30PM</t>
+          <t>8:15AM</t>
         </is>
       </c>
       <c r="D89" s="27" t="inlineStr">
@@ -6365,12 +6309,12 @@
       </c>
       <c r="F89" s="27" t="inlineStr">
         <is>
-          <t>U46-GA-4</t>
+          <t>U46-GA-7</t>
         </is>
       </c>
       <c r="G89" s="27" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H89" s="27" t="inlineStr">
@@ -6385,29 +6329,29 @@
       </c>
       <c r="J89" s="27" t="inlineStr">
         <is>
-          <t>Piyush Makharia</t>
+          <t>Vinit Padia</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="28" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B90" s="28" t="inlineStr">
         <is>
-          <t>7:15PM</t>
+          <t>8:15AM</t>
         </is>
       </c>
       <c r="C90" s="28" t="inlineStr">
         <is>
-          <t>7:30PM</t>
+          <t>8:30AM</t>
         </is>
       </c>
       <c r="D90" s="28" t="inlineStr">
         <is>
-          <t>Under 46</t>
+          <t>Under 15</t>
         </is>
       </c>
       <c r="E90" s="28" t="n">
@@ -6415,7 +6359,7 @@
       </c>
       <c r="F90" s="28" t="inlineStr">
         <is>
-          <t>U46-GA-9</t>
+          <t>U15-GB-2</t>
         </is>
       </c>
       <c r="G90" s="28" t="inlineStr">
@@ -6425,7 +6369,7 @@
       </c>
       <c r="H90" s="28" t="inlineStr">
         <is>
-          <t>Nikunj Jhala</t>
+          <t>Viaan Neema</t>
         </is>
       </c>
       <c r="I90" s="28" t="inlineStr">
@@ -6435,24 +6379,24 @@
       </c>
       <c r="J90" s="28" t="inlineStr">
         <is>
-          <t>Vinit Padia</t>
+          <t>Hridh jhala</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="27" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B91" s="27" t="inlineStr">
         <is>
-          <t>7:30PM</t>
+          <t>8:25AM</t>
         </is>
       </c>
       <c r="C91" s="27" t="inlineStr">
         <is>
-          <t>7:45PM</t>
+          <t>8:40AM</t>
         </is>
       </c>
       <c r="D91" s="27" t="inlineStr">
@@ -6465,7 +6409,7 @@
       </c>
       <c r="F91" s="27" t="inlineStr">
         <is>
-          <t>U46-GA-6</t>
+          <t>U46-GA-8</t>
         </is>
       </c>
       <c r="G91" s="27" t="inlineStr">
@@ -6475,7 +6419,7 @@
       </c>
       <c r="H91" s="27" t="inlineStr">
         <is>
-          <t>Nikunj Jhala</t>
+          <t>Piyush Makharia</t>
         </is>
       </c>
       <c r="I91" s="27" t="inlineStr">
@@ -6485,29 +6429,29 @@
       </c>
       <c r="J91" s="27" t="inlineStr">
         <is>
-          <t>Piyush Makharia</t>
+          <t>Nilesh Bagaria</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="28" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B92" s="28" t="inlineStr">
         <is>
-          <t>7:30PM</t>
+          <t>8:30AM</t>
         </is>
       </c>
       <c r="C92" s="28" t="inlineStr">
         <is>
-          <t>7:45PM</t>
+          <t>8:45AM</t>
         </is>
       </c>
       <c r="D92" s="28" t="inlineStr">
         <is>
-          <t>Under 46</t>
+          <t>Under 32</t>
         </is>
       </c>
       <c r="E92" s="28" t="n">
@@ -6515,7 +6459,7 @@
       </c>
       <c r="F92" s="28" t="inlineStr">
         <is>
-          <t>U46-GA-7</t>
+          <t>U32-1</t>
         </is>
       </c>
       <c r="G92" s="28" t="inlineStr">
@@ -6525,7 +6469,7 @@
       </c>
       <c r="H92" s="28" t="inlineStr">
         <is>
-          <t>Anuj Shah</t>
+          <t>Yuvraj jain</t>
         </is>
       </c>
       <c r="I92" s="28" t="inlineStr">
@@ -6535,24 +6479,24 @@
       </c>
       <c r="J92" s="28" t="inlineStr">
         <is>
-          <t>Vinit Padia</t>
+          <t>Aaditya Kumar</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="27" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B93" s="27" t="inlineStr">
         <is>
-          <t>7:45PM</t>
+          <t>8:40AM</t>
         </is>
       </c>
       <c r="C93" s="27" t="inlineStr">
         <is>
-          <t>8:00PM</t>
+          <t>8:55AM</t>
         </is>
       </c>
       <c r="D93" s="27" t="inlineStr">
@@ -6565,17 +6509,17 @@
       </c>
       <c r="F93" s="27" t="inlineStr">
         <is>
-          <t>U15-GB-2</t>
+          <t>U15-GB-3</t>
         </is>
       </c>
       <c r="G93" s="27" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H93" s="27" t="inlineStr">
         <is>
-          <t>Viaan Neema</t>
+          <t>Yash agarwal</t>
         </is>
       </c>
       <c r="I93" s="27" t="inlineStr">
@@ -6592,22 +6536,22 @@
     <row r="94">
       <c r="A94" s="28" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B94" s="28" t="inlineStr">
         <is>
-          <t>7:45PM</t>
+          <t>8:55AM</t>
         </is>
       </c>
       <c r="C94" s="28" t="inlineStr">
         <is>
-          <t>8:00PM</t>
+          <t>9:10AM</t>
         </is>
       </c>
       <c r="D94" s="28" t="inlineStr">
         <is>
-          <t>Under 46</t>
+          <t>Under 32</t>
         </is>
       </c>
       <c r="E94" s="28" t="n">
@@ -6615,17 +6559,17 @@
       </c>
       <c r="F94" s="28" t="inlineStr">
         <is>
-          <t>U46-GA-8</t>
+          <t>U32-10</t>
         </is>
       </c>
       <c r="G94" s="28" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H94" s="28" t="inlineStr">
         <is>
-          <t>Piyush Makharia</t>
+          <t>Yuvraj jain</t>
         </is>
       </c>
       <c r="I94" s="28" t="inlineStr">
@@ -6635,29 +6579,29 @@
       </c>
       <c r="J94" s="28" t="inlineStr">
         <is>
-          <t>Nilesh Bagaria</t>
+          <t>Rahul Garg</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="27" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B95" s="27" t="inlineStr">
         <is>
-          <t>8:00PM</t>
+          <t>8:55AM</t>
         </is>
       </c>
       <c r="C95" s="27" t="inlineStr">
         <is>
-          <t>8:15PM</t>
+          <t>9:10AM</t>
         </is>
       </c>
       <c r="D95" s="27" t="inlineStr">
         <is>
-          <t>Under 15</t>
+          <t>Under 32</t>
         </is>
       </c>
       <c r="E95" s="27" t="n">
@@ -6665,7 +6609,7 @@
       </c>
       <c r="F95" s="27" t="inlineStr">
         <is>
-          <t>U15-GB-3</t>
+          <t>U32-2</t>
         </is>
       </c>
       <c r="G95" s="27" t="inlineStr">
@@ -6675,7 +6619,7 @@
       </c>
       <c r="H95" s="27" t="inlineStr">
         <is>
-          <t>Yash agarwal</t>
+          <t>Hryday Goyal</t>
         </is>
       </c>
       <c r="I95" s="27" t="inlineStr">
@@ -6685,24 +6629,24 @@
       </c>
       <c r="J95" s="27" t="inlineStr">
         <is>
-          <t>Hridh jhala</t>
+          <t>Pranit Shriyan</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="28" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B96" s="28" t="inlineStr">
         <is>
-          <t>8:00PM</t>
+          <t>9:20AM</t>
         </is>
       </c>
       <c r="C96" s="28" t="inlineStr">
         <is>
-          <t>8:15PM</t>
+          <t>9:35AM</t>
         </is>
       </c>
       <c r="D96" s="28" t="inlineStr">
@@ -6715,7 +6659,7 @@
       </c>
       <c r="F96" s="28" t="inlineStr">
         <is>
-          <t>U32-1</t>
+          <t>U32-4</t>
         </is>
       </c>
       <c r="G96" s="28" t="inlineStr">
@@ -6735,24 +6679,24 @@
       </c>
       <c r="J96" s="28" t="inlineStr">
         <is>
-          <t>Aaditya Kumar</t>
+          <t>Hryday Goyal</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="27" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B97" s="27" t="inlineStr">
         <is>
-          <t>8:15PM</t>
+          <t>9:35AM</t>
         </is>
       </c>
       <c r="C97" s="27" t="inlineStr">
         <is>
-          <t>8:30PM</t>
+          <t>9:50AM</t>
         </is>
       </c>
       <c r="D97" s="27" t="inlineStr">
@@ -6765,17 +6709,17 @@
       </c>
       <c r="F97" s="27" t="inlineStr">
         <is>
-          <t>U32-2</t>
+          <t>U32-9</t>
         </is>
       </c>
       <c r="G97" s="27" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H97" s="27" t="inlineStr">
         <is>
-          <t>Hryday Goyal</t>
+          <t>Aaditya Kumar</t>
         </is>
       </c>
       <c r="I97" s="27" t="inlineStr">
@@ -6792,17 +6736,17 @@
     <row r="98">
       <c r="A98" s="28" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B98" s="28" t="inlineStr">
         <is>
-          <t>8:20PM</t>
+          <t>9:45AM</t>
         </is>
       </c>
       <c r="C98" s="28" t="inlineStr">
         <is>
-          <t>8:35PM</t>
+          <t>10:00AM</t>
         </is>
       </c>
       <c r="D98" s="28" t="inlineStr">
@@ -6815,17 +6759,17 @@
       </c>
       <c r="F98" s="28" t="inlineStr">
         <is>
-          <t>U32-10</t>
+          <t>U32-8</t>
         </is>
       </c>
       <c r="G98" s="28" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H98" s="28" t="inlineStr">
         <is>
-          <t>Yuvraj jain</t>
+          <t>Hryday Goyal</t>
         </is>
       </c>
       <c r="I98" s="28" t="inlineStr">
@@ -6842,17 +6786,17 @@
     <row r="99">
       <c r="A99" s="27" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B99" s="27" t="inlineStr">
         <is>
-          <t>8:35PM</t>
+          <t>10:00AM</t>
         </is>
       </c>
       <c r="C99" s="27" t="inlineStr">
         <is>
-          <t>8:50PM</t>
+          <t>10:15AM</t>
         </is>
       </c>
       <c r="D99" s="27" t="inlineStr">
@@ -6865,7 +6809,7 @@
       </c>
       <c r="F99" s="27" t="inlineStr">
         <is>
-          <t>U32-4</t>
+          <t>U32-7</t>
         </is>
       </c>
       <c r="G99" s="27" t="inlineStr">
@@ -6885,24 +6829,24 @@
       </c>
       <c r="J99" s="27" t="inlineStr">
         <is>
-          <t>Hryday Goyal</t>
+          <t>Pranit Shriyan</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="28" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B100" s="28" t="inlineStr">
         <is>
-          <t>8:55PM</t>
+          <t>10:10AM</t>
         </is>
       </c>
       <c r="C100" s="28" t="inlineStr">
         <is>
-          <t>9:10PM</t>
+          <t>10:25AM</t>
         </is>
       </c>
       <c r="D100" s="28" t="inlineStr">
@@ -6915,12 +6859,12 @@
       </c>
       <c r="F100" s="28" t="inlineStr">
         <is>
-          <t>U32-9</t>
+          <t>U32-3</t>
         </is>
       </c>
       <c r="G100" s="28" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H100" s="28" t="inlineStr">
@@ -6935,24 +6879,24 @@
       </c>
       <c r="J100" s="28" t="inlineStr">
         <is>
-          <t>Pranit Shriyan</t>
+          <t>Rahul Garg</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="27" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B101" s="27" t="inlineStr">
         <is>
-          <t>9:00PM</t>
+          <t>10:35AM</t>
         </is>
       </c>
       <c r="C101" s="27" t="inlineStr">
         <is>
-          <t>9:15PM</t>
+          <t>10:50AM</t>
         </is>
       </c>
       <c r="D101" s="27" t="inlineStr">
@@ -6965,17 +6909,17 @@
       </c>
       <c r="F101" s="27" t="inlineStr">
         <is>
-          <t>U32-8</t>
+          <t>U32-5</t>
         </is>
       </c>
       <c r="G101" s="27" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H101" s="27" t="inlineStr">
         <is>
-          <t>Hryday Goyal</t>
+          <t>Pranit Shriyan</t>
         </is>
       </c>
       <c r="I101" s="27" t="inlineStr">
@@ -6992,17 +6936,17 @@
     <row r="102">
       <c r="A102" s="28" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B102" s="28" t="inlineStr">
         <is>
-          <t>9:10PM</t>
+          <t>10:35AM</t>
         </is>
       </c>
       <c r="C102" s="28" t="inlineStr">
         <is>
-          <t>9:25PM</t>
+          <t>10:50AM</t>
         </is>
       </c>
       <c r="D102" s="28" t="inlineStr">
@@ -7015,17 +6959,17 @@
       </c>
       <c r="F102" s="28" t="inlineStr">
         <is>
-          <t>U32-7</t>
+          <t>U32-6</t>
         </is>
       </c>
       <c r="G102" s="28" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H102" s="28" t="inlineStr">
         <is>
-          <t>Yuvraj jain</t>
+          <t>Aaditya Kumar</t>
         </is>
       </c>
       <c r="I102" s="28" t="inlineStr">
@@ -7035,29 +6979,29 @@
       </c>
       <c r="J102" s="28" t="inlineStr">
         <is>
-          <t>Pranit Shriyan</t>
+          <t>Hryday Goyal</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="27" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B103" s="27" t="inlineStr">
         <is>
-          <t>9:15PM</t>
+          <t>11:50AM</t>
         </is>
       </c>
       <c r="C103" s="27" t="inlineStr">
         <is>
-          <t>9:30PM</t>
+          <t>12:05PM</t>
         </is>
       </c>
       <c r="D103" s="27" t="inlineStr">
         <is>
-          <t>Under 32</t>
+          <t>Senior</t>
         </is>
       </c>
       <c r="E103" s="27" t="n">
@@ -7065,7 +7009,7 @@
       </c>
       <c r="F103" s="27" t="inlineStr">
         <is>
-          <t>U32-3</t>
+          <t>SR-SF1</t>
         </is>
       </c>
       <c r="G103" s="27" t="inlineStr">
@@ -7075,7 +7019,7 @@
       </c>
       <c r="H103" s="27" t="inlineStr">
         <is>
-          <t>Aaditya Kumar</t>
+          <t>Group A 1st</t>
         </is>
       </c>
       <c r="I103" s="27" t="inlineStr">
@@ -7085,29 +7029,29 @@
       </c>
       <c r="J103" s="27" t="inlineStr">
         <is>
-          <t>Rahul Garg</t>
+          <t>Group B 2nd</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="28" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B104" s="28" t="inlineStr">
         <is>
-          <t>9:30PM</t>
+          <t>11:50AM</t>
         </is>
       </c>
       <c r="C104" s="28" t="inlineStr">
         <is>
-          <t>9:45PM</t>
+          <t>12:05PM</t>
         </is>
       </c>
       <c r="D104" s="28" t="inlineStr">
         <is>
-          <t>Under 32</t>
+          <t>Senior</t>
         </is>
       </c>
       <c r="E104" s="28" t="n">
@@ -7115,7 +7059,7 @@
       </c>
       <c r="F104" s="28" t="inlineStr">
         <is>
-          <t>U32-5</t>
+          <t>SR-SF2</t>
         </is>
       </c>
       <c r="G104" s="28" t="inlineStr">
@@ -7125,7 +7069,7 @@
       </c>
       <c r="H104" s="28" t="inlineStr">
         <is>
-          <t>Pranit Shriyan</t>
+          <t>Group B 1st</t>
         </is>
       </c>
       <c r="I104" s="28" t="inlineStr">
@@ -7135,29 +7079,29 @@
       </c>
       <c r="J104" s="28" t="inlineStr">
         <is>
-          <t>Rahul Garg</t>
+          <t>Group A 2nd</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="27" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B105" s="27" t="inlineStr">
         <is>
-          <t>9:30PM</t>
+          <t>12:05PM</t>
         </is>
       </c>
       <c r="C105" s="27" t="inlineStr">
         <is>
-          <t>9:45PM</t>
+          <t>12:20PM</t>
         </is>
       </c>
       <c r="D105" s="27" t="inlineStr">
         <is>
-          <t>Under 32</t>
+          <t>Senior</t>
         </is>
       </c>
       <c r="E105" s="27" t="n">
@@ -7165,7 +7109,7 @@
       </c>
       <c r="F105" s="27" t="inlineStr">
         <is>
-          <t>U32-6</t>
+          <t>SR-FINAL</t>
         </is>
       </c>
       <c r="G105" s="27" t="inlineStr">
@@ -7175,7 +7119,7 @@
       </c>
       <c r="H105" s="27" t="inlineStr">
         <is>
-          <t>Aaditya Kumar</t>
+          <t>Winner SF1</t>
         </is>
       </c>
       <c r="I105" s="27" t="inlineStr">
@@ -7185,24 +7129,24 @@
       </c>
       <c r="J105" s="27" t="inlineStr">
         <is>
-          <t>Hryday Goyal</t>
+          <t>Winner SF2</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="28" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B106" s="28" t="inlineStr">
         <is>
-          <t>9:45PM</t>
+          <t>12:05PM</t>
         </is>
       </c>
       <c r="C106" s="28" t="inlineStr">
         <is>
-          <t>10:00PM</t>
+          <t>12:20PM</t>
         </is>
       </c>
       <c r="D106" s="28" t="inlineStr">
@@ -7215,17 +7159,17 @@
       </c>
       <c r="F106" s="28" t="inlineStr">
         <is>
-          <t>U46-SF1</t>
+          <t>U46-SF2</t>
         </is>
       </c>
       <c r="G106" s="28" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H106" s="28" t="inlineStr">
         <is>
-          <t>Group A 1st</t>
+          <t>Group B 1st</t>
         </is>
       </c>
       <c r="I106" s="28" t="inlineStr">
@@ -7235,29 +7179,29 @@
       </c>
       <c r="J106" s="28" t="inlineStr">
         <is>
-          <t>Group B 2nd</t>
+          <t>Group A 2nd</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="27" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B107" s="27" t="inlineStr">
         <is>
-          <t>9:45PM</t>
+          <t>12:20PM</t>
         </is>
       </c>
       <c r="C107" s="27" t="inlineStr">
         <is>
-          <t>10:00PM</t>
+          <t>12:35PM</t>
         </is>
       </c>
       <c r="D107" s="27" t="inlineStr">
         <is>
-          <t>Under 46</t>
+          <t>Under 36</t>
         </is>
       </c>
       <c r="E107" s="27" t="n">
@@ -7265,7 +7209,7 @@
       </c>
       <c r="F107" s="27" t="inlineStr">
         <is>
-          <t>U46-SF2</t>
+          <t>U36-SF2</t>
         </is>
       </c>
       <c r="G107" s="27" t="inlineStr">
@@ -7297,17 +7241,17 @@
       </c>
       <c r="B108" s="28" t="inlineStr">
         <is>
-          <t>8:00AM</t>
+          <t>12:20PM</t>
         </is>
       </c>
       <c r="C108" s="28" t="inlineStr">
         <is>
-          <t>8:15AM</t>
+          <t>12:35PM</t>
         </is>
       </c>
       <c r="D108" s="28" t="inlineStr">
         <is>
-          <t>Under 36</t>
+          <t>Under 46</t>
         </is>
       </c>
       <c r="E108" s="28" t="n">
@@ -7315,7 +7259,7 @@
       </c>
       <c r="F108" s="28" t="inlineStr">
         <is>
-          <t>U36-SF1</t>
+          <t>U46-SF1</t>
         </is>
       </c>
       <c r="G108" s="28" t="inlineStr">
@@ -7347,17 +7291,17 @@
       </c>
       <c r="B109" s="27" t="inlineStr">
         <is>
-          <t>8:00AM</t>
+          <t>12:35PM</t>
         </is>
       </c>
       <c r="C109" s="27" t="inlineStr">
         <is>
-          <t>8:15AM</t>
+          <t>12:50PM</t>
         </is>
       </c>
       <c r="D109" s="27" t="inlineStr">
         <is>
-          <t>Under 36</t>
+          <t>Under 32</t>
         </is>
       </c>
       <c r="E109" s="27" t="n">
@@ -7365,7 +7309,7 @@
       </c>
       <c r="F109" s="27" t="inlineStr">
         <is>
-          <t>U36-SF2</t>
+          <t>U32-FINAL</t>
         </is>
       </c>
       <c r="G109" s="27" t="inlineStr">
@@ -7375,7 +7319,7 @@
       </c>
       <c r="H109" s="27" t="inlineStr">
         <is>
-          <t>Group B 1st</t>
+          <t>Pool 1st</t>
         </is>
       </c>
       <c r="I109" s="27" t="inlineStr">
@@ -7385,7 +7329,7 @@
       </c>
       <c r="J109" s="27" t="inlineStr">
         <is>
-          <t>Group A 2nd</t>
+          <t>Pool 2nd</t>
         </is>
       </c>
     </row>
@@ -7397,17 +7341,17 @@
       </c>
       <c r="B110" s="28" t="inlineStr">
         <is>
-          <t>8:15AM</t>
+          <t>12:35PM</t>
         </is>
       </c>
       <c r="C110" s="28" t="inlineStr">
         <is>
-          <t>8:40AM</t>
+          <t>12:50PM</t>
         </is>
       </c>
       <c r="D110" s="28" t="inlineStr">
         <is>
-          <t>Under 32</t>
+          <t>Under 36</t>
         </is>
       </c>
       <c r="E110" s="28" t="n">
@@ -7415,17 +7359,17 @@
       </c>
       <c r="F110" s="28" t="inlineStr">
         <is>
-          <t>U32-FINAL</t>
+          <t>U36-SF1</t>
         </is>
       </c>
       <c r="G110" s="28" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H110" s="28" t="inlineStr">
         <is>
-          <t>Pool 1st</t>
+          <t>Group A 1st</t>
         </is>
       </c>
       <c r="I110" s="28" t="inlineStr">
@@ -7435,7 +7379,7 @@
       </c>
       <c r="J110" s="28" t="inlineStr">
         <is>
-          <t>Pool 2nd</t>
+          <t>Group B 2nd</t>
         </is>
       </c>
     </row>
@@ -7447,17 +7391,17 @@
       </c>
       <c r="B111" s="27" t="inlineStr">
         <is>
-          <t>8:15AM</t>
+          <t>12:50PM</t>
         </is>
       </c>
       <c r="C111" s="27" t="inlineStr">
         <is>
-          <t>8:40AM</t>
+          <t>1:05PM</t>
         </is>
       </c>
       <c r="D111" s="27" t="inlineStr">
         <is>
-          <t>Under 36</t>
+          <t>Under 15</t>
         </is>
       </c>
       <c r="E111" s="27" t="n">
@@ -7465,17 +7409,17 @@
       </c>
       <c r="F111" s="27" t="inlineStr">
         <is>
-          <t>U36-FINAL</t>
+          <t>U15-SF2</t>
         </is>
       </c>
       <c r="G111" s="27" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H111" s="27" t="inlineStr">
         <is>
-          <t>Winner SF1</t>
+          <t>Group B 1st</t>
         </is>
       </c>
       <c r="I111" s="27" t="inlineStr">
@@ -7485,7 +7429,7 @@
       </c>
       <c r="J111" s="27" t="inlineStr">
         <is>
-          <t>Winner SF2</t>
+          <t>Group A 2nd</t>
         </is>
       </c>
     </row>
@@ -7497,17 +7441,17 @@
       </c>
       <c r="B112" s="28" t="inlineStr">
         <is>
-          <t>8:40AM</t>
+          <t>12:50PM</t>
         </is>
       </c>
       <c r="C112" s="28" t="inlineStr">
         <is>
-          <t>8:55AM</t>
+          <t>1:05PM</t>
         </is>
       </c>
       <c r="D112" s="28" t="inlineStr">
         <is>
-          <t>Under 15</t>
+          <t>Under 36</t>
         </is>
       </c>
       <c r="E112" s="28" t="n">
@@ -7515,7 +7459,7 @@
       </c>
       <c r="F112" s="28" t="inlineStr">
         <is>
-          <t>U15-SF1</t>
+          <t>U36-FINAL</t>
         </is>
       </c>
       <c r="G112" s="28" t="inlineStr">
@@ -7525,7 +7469,7 @@
       </c>
       <c r="H112" s="28" t="inlineStr">
         <is>
-          <t>Group A 1st</t>
+          <t>Winner SF1</t>
         </is>
       </c>
       <c r="I112" s="28" t="inlineStr">
@@ -7535,7 +7479,7 @@
       </c>
       <c r="J112" s="28" t="inlineStr">
         <is>
-          <t>Group B 2nd</t>
+          <t>Winner SF2</t>
         </is>
       </c>
     </row>
@@ -7547,12 +7491,12 @@
       </c>
       <c r="B113" s="27" t="inlineStr">
         <is>
-          <t>8:40AM</t>
+          <t>1:05PM</t>
         </is>
       </c>
       <c r="C113" s="27" t="inlineStr">
         <is>
-          <t>8:55AM</t>
+          <t>1:20PM</t>
         </is>
       </c>
       <c r="D113" s="27" t="inlineStr">
@@ -7565,7 +7509,7 @@
       </c>
       <c r="F113" s="27" t="inlineStr">
         <is>
-          <t>U15-SF2</t>
+          <t>U15-FINAL</t>
         </is>
       </c>
       <c r="G113" s="27" t="inlineStr">
@@ -7575,7 +7519,7 @@
       </c>
       <c r="H113" s="27" t="inlineStr">
         <is>
-          <t>Group B 1st</t>
+          <t>Winner SF1</t>
         </is>
       </c>
       <c r="I113" s="27" t="inlineStr">
@@ -7585,7 +7529,7 @@
       </c>
       <c r="J113" s="27" t="inlineStr">
         <is>
-          <t>Group A 2nd</t>
+          <t>Winner SF2</t>
         </is>
       </c>
     </row>
@@ -7597,12 +7541,12 @@
       </c>
       <c r="B114" s="28" t="inlineStr">
         <is>
-          <t>8:55AM</t>
+          <t>1:05PM</t>
         </is>
       </c>
       <c r="C114" s="28" t="inlineStr">
         <is>
-          <t>9:20AM</t>
+          <t>1:20PM</t>
         </is>
       </c>
       <c r="D114" s="28" t="inlineStr">
@@ -7615,17 +7559,17 @@
       </c>
       <c r="F114" s="28" t="inlineStr">
         <is>
-          <t>U15-FINAL</t>
+          <t>U15-SF1</t>
         </is>
       </c>
       <c r="G114" s="28" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H114" s="28" t="inlineStr">
         <is>
-          <t>Winner SF1</t>
+          <t>Group A 1st</t>
         </is>
       </c>
       <c r="I114" s="28" t="inlineStr">
@@ -7635,7 +7579,7 @@
       </c>
       <c r="J114" s="28" t="inlineStr">
         <is>
-          <t>Winner SF2</t>
+          <t>Group B 2nd</t>
         </is>
       </c>
     </row>
@@ -7647,12 +7591,12 @@
       </c>
       <c r="B115" s="27" t="inlineStr">
         <is>
-          <t>8:55AM</t>
+          <t>1:20PM</t>
         </is>
       </c>
       <c r="C115" s="27" t="inlineStr">
         <is>
-          <t>9:20AM</t>
+          <t>1:35PM</t>
         </is>
       </c>
       <c r="D115" s="27" t="inlineStr">
@@ -7916,17 +7860,17 @@
     <row r="20">
       <c r="A20" s="27" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B20" s="27" t="inlineStr">
         <is>
-          <t>8:30PM</t>
+          <t>12:35PM</t>
         </is>
       </c>
       <c r="C20" s="27" t="inlineStr">
         <is>
-          <t>8:45PM</t>
+          <t>12:50PM</t>
         </is>
       </c>
       <c r="D20" s="27" t="inlineStr">
@@ -7939,17 +7883,17 @@
       </c>
       <c r="F20" s="27" t="inlineStr">
         <is>
-          <t>QF2</t>
+          <t>QF3</t>
         </is>
       </c>
       <c r="G20" s="27" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H20" s="27" t="inlineStr">
         <is>
-          <t>Tanmay Sharma &amp; Sankalp</t>
+          <t>Nilesh Bagaria &amp; Parthiv</t>
         </is>
       </c>
       <c r="I20" s="27" t="inlineStr">
@@ -7959,24 +7903,24 @@
       </c>
       <c r="J20" s="27" t="inlineStr">
         <is>
-          <t>Ravi Modi &amp; Dr Rahul Modi</t>
+          <t>Rahul Garg &amp; Nilesh Mahtre</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="28" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B21" s="28" t="inlineStr">
         <is>
-          <t>8:45PM</t>
+          <t>12:50PM</t>
         </is>
       </c>
       <c r="C21" s="28" t="inlineStr">
         <is>
-          <t>9:00PM</t>
+          <t>1:05PM</t>
         </is>
       </c>
       <c r="D21" s="28" t="inlineStr">
@@ -7989,7 +7933,7 @@
       </c>
       <c r="F21" s="28" t="inlineStr">
         <is>
-          <t>QF4</t>
+          <t>QF2</t>
         </is>
       </c>
       <c r="G21" s="28" t="inlineStr">
@@ -7999,7 +7943,7 @@
       </c>
       <c r="H21" s="28" t="inlineStr">
         <is>
-          <t>Mayank Aggarwal &amp; Sudip Parui</t>
+          <t>Tanmay Sharma &amp; Sankalp</t>
         </is>
       </c>
       <c r="I21" s="28" t="inlineStr">
@@ -8009,7 +7953,7 @@
       </c>
       <c r="J21" s="28" t="inlineStr">
         <is>
-          <t>Nidhi Sharma &amp; Tushar</t>
+          <t>Ravi Modi &amp; Dr Rahul Modi</t>
         </is>
       </c>
     </row>
@@ -8021,12 +7965,12 @@
       </c>
       <c r="B22" s="27" t="inlineStr">
         <is>
-          <t>9:20AM</t>
+          <t>12:50PM</t>
         </is>
       </c>
       <c r="C22" s="27" t="inlineStr">
         <is>
-          <t>9:35AM</t>
+          <t>1:05PM</t>
         </is>
       </c>
       <c r="D22" s="27" t="inlineStr">
@@ -8039,17 +7983,17 @@
       </c>
       <c r="F22" s="27" t="inlineStr">
         <is>
-          <t>QF1</t>
+          <t>SF2</t>
         </is>
       </c>
       <c r="G22" s="27" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H22" s="27" t="inlineStr">
         <is>
-          <t>Adil Khan &amp; Anuj Shah</t>
+          <t>Winner QF3</t>
         </is>
       </c>
       <c r="I22" s="27" t="inlineStr">
@@ -8059,7 +8003,7 @@
       </c>
       <c r="J22" s="27" t="inlineStr">
         <is>
-          <t>Vinit Padia &amp; Pratik Haldiya</t>
+          <t>Winner QF4</t>
         </is>
       </c>
     </row>
@@ -8071,12 +8015,12 @@
       </c>
       <c r="B23" s="28" t="inlineStr">
         <is>
-          <t>9:20AM</t>
+          <t>1:05PM</t>
         </is>
       </c>
       <c r="C23" s="28" t="inlineStr">
         <is>
-          <t>9:35AM</t>
+          <t>1:20PM</t>
         </is>
       </c>
       <c r="D23" s="28" t="inlineStr">
@@ -8089,17 +8033,17 @@
       </c>
       <c r="F23" s="28" t="inlineStr">
         <is>
-          <t>QF3</t>
+          <t>QF4</t>
         </is>
       </c>
       <c r="G23" s="28" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H23" s="28" t="inlineStr">
         <is>
-          <t>Nilesh Bagaria &amp; Parthiv</t>
+          <t>Mayank Aggarwal &amp; Sudip Parui</t>
         </is>
       </c>
       <c r="I23" s="28" t="inlineStr">
@@ -8109,7 +8053,7 @@
       </c>
       <c r="J23" s="28" t="inlineStr">
         <is>
-          <t>Rahul Garg &amp; Nilesh Mahtre</t>
+          <t>Nidhi Sharma &amp; Tushar</t>
         </is>
       </c>
     </row>
@@ -8121,12 +8065,12 @@
       </c>
       <c r="B24" s="27" t="inlineStr">
         <is>
-          <t>9:35AM</t>
+          <t>1:20PM</t>
         </is>
       </c>
       <c r="C24" s="27" t="inlineStr">
         <is>
-          <t>9:50AM</t>
+          <t>1:35PM</t>
         </is>
       </c>
       <c r="D24" s="27" t="inlineStr">
@@ -8139,7 +8083,7 @@
       </c>
       <c r="F24" s="27" t="inlineStr">
         <is>
-          <t>SF1</t>
+          <t>QF1</t>
         </is>
       </c>
       <c r="G24" s="27" t="inlineStr">
@@ -8149,7 +8093,7 @@
       </c>
       <c r="H24" s="27" t="inlineStr">
         <is>
-          <t>Winner QF1</t>
+          <t>Adil Khan &amp; Anuj Shah</t>
         </is>
       </c>
       <c r="I24" s="27" t="inlineStr">
@@ -8159,7 +8103,7 @@
       </c>
       <c r="J24" s="27" t="inlineStr">
         <is>
-          <t>Winner QF2</t>
+          <t>Vinit Padia &amp; Pratik Haldiya</t>
         </is>
       </c>
     </row>
@@ -8171,12 +8115,12 @@
       </c>
       <c r="B25" s="28" t="inlineStr">
         <is>
-          <t>9:35AM</t>
+          <t>1:35PM</t>
         </is>
       </c>
       <c r="C25" s="28" t="inlineStr">
         <is>
-          <t>9:50AM</t>
+          <t>1:50PM</t>
         </is>
       </c>
       <c r="D25" s="28" t="inlineStr">
@@ -8189,17 +8133,17 @@
       </c>
       <c r="F25" s="28" t="inlineStr">
         <is>
-          <t>SF2</t>
+          <t>SF1</t>
         </is>
       </c>
       <c r="G25" s="28" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H25" s="28" t="inlineStr">
         <is>
-          <t>Winner QF3</t>
+          <t>Winner QF1</t>
         </is>
       </c>
       <c r="I25" s="28" t="inlineStr">
@@ -8209,7 +8153,7 @@
       </c>
       <c r="J25" s="28" t="inlineStr">
         <is>
-          <t>Winner QF4</t>
+          <t>Winner QF2</t>
         </is>
       </c>
     </row>
@@ -8221,12 +8165,12 @@
       </c>
       <c r="B26" s="27" t="inlineStr">
         <is>
-          <t>9:50AM</t>
+          <t>1:50PM</t>
         </is>
       </c>
       <c r="C26" s="27" t="inlineStr">
         <is>
-          <t>10:15AM</t>
+          <t>2:05PM</t>
         </is>
       </c>
       <c r="D26" s="27" t="inlineStr">
@@ -8702,12 +8646,12 @@
       </c>
       <c r="B32" s="28" t="inlineStr">
         <is>
-          <t>8:15AM</t>
+          <t>8:25AM</t>
         </is>
       </c>
       <c r="C32" s="28" t="inlineStr">
         <is>
-          <t>8:30AM</t>
+          <t>8:40AM</t>
         </is>
       </c>
       <c r="D32" s="28" t="inlineStr">
@@ -8752,12 +8696,12 @@
       </c>
       <c r="B33" s="27" t="inlineStr">
         <is>
-          <t>8:30AM</t>
+          <t>8:40AM</t>
         </is>
       </c>
       <c r="C33" s="27" t="inlineStr">
         <is>
-          <t>8:45AM</t>
+          <t>8:55AM</t>
         </is>
       </c>
       <c r="D33" s="27" t="inlineStr">
@@ -8802,12 +8746,12 @@
       </c>
       <c r="B34" s="28" t="inlineStr">
         <is>
-          <t>8:45AM</t>
+          <t>9:05AM</t>
         </is>
       </c>
       <c r="C34" s="28" t="inlineStr">
         <is>
-          <t>9:00AM</t>
+          <t>9:20AM</t>
         </is>
       </c>
       <c r="D34" s="28" t="inlineStr">
@@ -8852,12 +8796,12 @@
       </c>
       <c r="B35" s="27" t="inlineStr">
         <is>
-          <t>9:00AM</t>
+          <t>9:15AM</t>
         </is>
       </c>
       <c r="C35" s="27" t="inlineStr">
         <is>
-          <t>9:15AM</t>
+          <t>9:30AM</t>
         </is>
       </c>
       <c r="D35" s="27" t="inlineStr">
@@ -8870,17 +8814,17 @@
       </c>
       <c r="F35" s="27" t="inlineStr">
         <is>
-          <t>CM-U46-GA-10</t>
+          <t>CM-U46-GB-1</t>
         </is>
       </c>
       <c r="G35" s="27" t="inlineStr">
         <is>
-          <t>Board 3</t>
+          <t>Board 2</t>
         </is>
       </c>
       <c r="H35" s="27" t="inlineStr">
         <is>
-          <t>Abhishek Dugar</t>
+          <t>Mayank Aggarwal</t>
         </is>
       </c>
       <c r="I35" s="27" t="inlineStr">
@@ -8890,7 +8834,7 @@
       </c>
       <c r="J35" s="27" t="inlineStr">
         <is>
-          <t>Anuj Shah</t>
+          <t>Amit Ranka</t>
         </is>
       </c>
     </row>
@@ -8902,12 +8846,12 @@
       </c>
       <c r="B36" s="28" t="inlineStr">
         <is>
-          <t>9:15AM</t>
+          <t>9:20AM</t>
         </is>
       </c>
       <c r="C36" s="28" t="inlineStr">
         <is>
-          <t>9:30AM</t>
+          <t>9:35AM</t>
         </is>
       </c>
       <c r="D36" s="28" t="inlineStr">
@@ -8920,17 +8864,17 @@
       </c>
       <c r="F36" s="28" t="inlineStr">
         <is>
-          <t>CM-U46-GA-6</t>
+          <t>CM-U46-GA-10</t>
         </is>
       </c>
       <c r="G36" s="28" t="inlineStr">
         <is>
-          <t>Board 1</t>
+          <t>Board 3</t>
         </is>
       </c>
       <c r="H36" s="28" t="inlineStr">
         <is>
-          <t>Ravi Modi</t>
+          <t>Abhishek Dugar</t>
         </is>
       </c>
       <c r="I36" s="28" t="inlineStr">
@@ -8940,7 +8884,7 @@
       </c>
       <c r="J36" s="28" t="inlineStr">
         <is>
-          <t>Abhishek Dugar</t>
+          <t>Anuj Shah</t>
         </is>
       </c>
     </row>
@@ -8952,12 +8896,12 @@
       </c>
       <c r="B37" s="27" t="inlineStr">
         <is>
-          <t>9:15AM</t>
+          <t>9:35AM</t>
         </is>
       </c>
       <c r="C37" s="27" t="inlineStr">
         <is>
-          <t>9:30AM</t>
+          <t>9:50AM</t>
         </is>
       </c>
       <c r="D37" s="27" t="inlineStr">
@@ -8970,17 +8914,17 @@
       </c>
       <c r="F37" s="27" t="inlineStr">
         <is>
-          <t>CM-U46-GB-1</t>
+          <t>CM-U46-GB-2</t>
         </is>
       </c>
       <c r="G37" s="27" t="inlineStr">
         <is>
-          <t>Board 2</t>
+          <t>Board 3</t>
         </is>
       </c>
       <c r="H37" s="27" t="inlineStr">
         <is>
-          <t>Mayank Aggarwal</t>
+          <t>Nikunj Jhala</t>
         </is>
       </c>
       <c r="I37" s="27" t="inlineStr">
@@ -8990,7 +8934,7 @@
       </c>
       <c r="J37" s="27" t="inlineStr">
         <is>
-          <t>Amit Ranka</t>
+          <t>Nilesh Bagaria</t>
         </is>
       </c>
     </row>
@@ -9002,12 +8946,12 @@
       </c>
       <c r="B38" s="28" t="inlineStr">
         <is>
-          <t>9:15AM</t>
+          <t>9:45AM</t>
         </is>
       </c>
       <c r="C38" s="28" t="inlineStr">
         <is>
-          <t>9:30AM</t>
+          <t>10:00AM</t>
         </is>
       </c>
       <c r="D38" s="28" t="inlineStr">
@@ -9020,17 +8964,17 @@
       </c>
       <c r="F38" s="28" t="inlineStr">
         <is>
-          <t>CM-U46-GB-2</t>
+          <t>CM-U46-GA-6</t>
         </is>
       </c>
       <c r="G38" s="28" t="inlineStr">
         <is>
-          <t>Board 3</t>
+          <t>Board 1</t>
         </is>
       </c>
       <c r="H38" s="28" t="inlineStr">
         <is>
-          <t>Nikunj Jhala</t>
+          <t>Ravi Modi</t>
         </is>
       </c>
       <c r="I38" s="28" t="inlineStr">
@@ -9040,7 +8984,7 @@
       </c>
       <c r="J38" s="28" t="inlineStr">
         <is>
-          <t>Nilesh Bagaria</t>
+          <t>Abhishek Dugar</t>
         </is>
       </c>
     </row>
@@ -9152,12 +9096,12 @@
       </c>
       <c r="B41" s="27" t="inlineStr">
         <is>
-          <t>10:45AM</t>
+          <t>10:55AM</t>
         </is>
       </c>
       <c r="C41" s="27" t="inlineStr">
         <is>
-          <t>11:00AM</t>
+          <t>11:10AM</t>
         </is>
       </c>
       <c r="D41" s="27" t="inlineStr">
@@ -9202,12 +9146,12 @@
       </c>
       <c r="B42" s="28" t="inlineStr">
         <is>
-          <t>10:45AM</t>
+          <t>10:55AM</t>
         </is>
       </c>
       <c r="C42" s="28" t="inlineStr">
         <is>
-          <t>11:00AM</t>
+          <t>11:10AM</t>
         </is>
       </c>
       <c r="D42" s="28" t="inlineStr">
@@ -9302,12 +9246,12 @@
       </c>
       <c r="B44" s="28" t="inlineStr">
         <is>
-          <t>11:00AM</t>
+          <t>11:10AM</t>
         </is>
       </c>
       <c r="C44" s="28" t="inlineStr">
         <is>
-          <t>11:15AM</t>
+          <t>11:25AM</t>
         </is>
       </c>
       <c r="D44" s="28" t="inlineStr">
@@ -9320,17 +9264,17 @@
       </c>
       <c r="F44" s="28" t="inlineStr">
         <is>
-          <t>CM-U46-GA-12</t>
+          <t>CM-U46-GB-4</t>
         </is>
       </c>
       <c r="G44" s="28" t="inlineStr">
         <is>
-          <t>Board 2</t>
+          <t>Board 1</t>
         </is>
       </c>
       <c r="H44" s="28" t="inlineStr">
         <is>
-          <t>Rahul Garg</t>
+          <t>Nilesh Bagaria</t>
         </is>
       </c>
       <c r="I44" s="28" t="inlineStr">
@@ -9340,7 +9284,7 @@
       </c>
       <c r="J44" s="28" t="inlineStr">
         <is>
-          <t>Ankur Mahante</t>
+          <t>Amit Ranka</t>
         </is>
       </c>
     </row>
@@ -9352,12 +9296,12 @@
       </c>
       <c r="B45" s="27" t="inlineStr">
         <is>
-          <t>11:00AM</t>
+          <t>11:20AM</t>
         </is>
       </c>
       <c r="C45" s="27" t="inlineStr">
         <is>
-          <t>11:15AM</t>
+          <t>11:35AM</t>
         </is>
       </c>
       <c r="D45" s="27" t="inlineStr">
@@ -9370,17 +9314,17 @@
       </c>
       <c r="F45" s="27" t="inlineStr">
         <is>
-          <t>CM-U46-GA-13</t>
+          <t>CM-U46-GA-12</t>
         </is>
       </c>
       <c r="G45" s="27" t="inlineStr">
         <is>
-          <t>Board 3</t>
+          <t>Board 2</t>
         </is>
       </c>
       <c r="H45" s="27" t="inlineStr">
         <is>
-          <t>Ravi Modi</t>
+          <t>Rahul Garg</t>
         </is>
       </c>
       <c r="I45" s="27" t="inlineStr">
@@ -9390,7 +9334,7 @@
       </c>
       <c r="J45" s="27" t="inlineStr">
         <is>
-          <t>Anuj Shah</t>
+          <t>Ankur Mahante</t>
         </is>
       </c>
     </row>
@@ -9402,12 +9346,12 @@
       </c>
       <c r="B46" s="28" t="inlineStr">
         <is>
-          <t>11:10AM</t>
+          <t>11:20AM</t>
         </is>
       </c>
       <c r="C46" s="28" t="inlineStr">
         <is>
-          <t>11:25AM</t>
+          <t>11:35AM</t>
         </is>
       </c>
       <c r="D46" s="28" t="inlineStr">
@@ -9420,17 +9364,17 @@
       </c>
       <c r="F46" s="28" t="inlineStr">
         <is>
-          <t>CM-U46-GB-4</t>
+          <t>CM-U46-GA-13</t>
         </is>
       </c>
       <c r="G46" s="28" t="inlineStr">
         <is>
-          <t>Board 1</t>
+          <t>Board 3</t>
         </is>
       </c>
       <c r="H46" s="28" t="inlineStr">
         <is>
-          <t>Nilesh Bagaria</t>
+          <t>Ravi Modi</t>
         </is>
       </c>
       <c r="I46" s="28" t="inlineStr">
@@ -9440,7 +9384,7 @@
       </c>
       <c r="J46" s="28" t="inlineStr">
         <is>
-          <t>Amit Ranka</t>
+          <t>Anuj Shah</t>
         </is>
       </c>
     </row>
@@ -9452,12 +9396,12 @@
       </c>
       <c r="B47" s="27" t="inlineStr">
         <is>
-          <t>11:15AM</t>
+          <t>11:35AM</t>
         </is>
       </c>
       <c r="C47" s="27" t="inlineStr">
         <is>
-          <t>11:30AM</t>
+          <t>11:50AM</t>
         </is>
       </c>
       <c r="D47" s="27" t="inlineStr">
@@ -9470,17 +9414,17 @@
       </c>
       <c r="F47" s="27" t="inlineStr">
         <is>
-          <t>CM-U46-GA-14</t>
+          <t>CM-U46-GB-5</t>
         </is>
       </c>
       <c r="G47" s="27" t="inlineStr">
         <is>
-          <t>Board 2</t>
+          <t>Board 3</t>
         </is>
       </c>
       <c r="H47" s="27" t="inlineStr">
         <is>
-          <t>Rahul Garg</t>
+          <t>Mayank Aggarwal</t>
         </is>
       </c>
       <c r="I47" s="27" t="inlineStr">
@@ -9490,7 +9434,7 @@
       </c>
       <c r="J47" s="27" t="inlineStr">
         <is>
-          <t>Abhishek Dugar</t>
+          <t>Vinit Padia</t>
         </is>
       </c>
     </row>
@@ -9502,12 +9446,12 @@
       </c>
       <c r="B48" s="28" t="inlineStr">
         <is>
-          <t>11:15AM</t>
+          <t>11:45AM</t>
         </is>
       </c>
       <c r="C48" s="28" t="inlineStr">
         <is>
-          <t>11:30AM</t>
+          <t>12:00PM</t>
         </is>
       </c>
       <c r="D48" s="28" t="inlineStr">
@@ -9520,17 +9464,17 @@
       </c>
       <c r="F48" s="28" t="inlineStr">
         <is>
-          <t>CM-U46-GB-5</t>
+          <t>CM-U46-GA-11</t>
         </is>
       </c>
       <c r="G48" s="28" t="inlineStr">
         <is>
-          <t>Board 3</t>
+          <t>Board 1</t>
         </is>
       </c>
       <c r="H48" s="28" t="inlineStr">
         <is>
-          <t>Mayank Aggarwal</t>
+          <t>Ravi Modi</t>
         </is>
       </c>
       <c r="I48" s="28" t="inlineStr">
@@ -9540,7 +9484,7 @@
       </c>
       <c r="J48" s="28" t="inlineStr">
         <is>
-          <t>Vinit Padia</t>
+          <t>Dr Rahul Modi</t>
         </is>
       </c>
     </row>
@@ -9552,12 +9496,12 @@
       </c>
       <c r="B49" s="27" t="inlineStr">
         <is>
-          <t>11:25AM</t>
+          <t>11:45AM</t>
         </is>
       </c>
       <c r="C49" s="27" t="inlineStr">
         <is>
-          <t>11:40AM</t>
+          <t>12:00PM</t>
         </is>
       </c>
       <c r="D49" s="27" t="inlineStr">
@@ -9570,17 +9514,17 @@
       </c>
       <c r="F49" s="27" t="inlineStr">
         <is>
-          <t>CM-U46-GA-11</t>
+          <t>CM-U46-GA-14</t>
         </is>
       </c>
       <c r="G49" s="27" t="inlineStr">
         <is>
-          <t>Board 1</t>
+          <t>Board 2</t>
         </is>
       </c>
       <c r="H49" s="27" t="inlineStr">
         <is>
-          <t>Ravi Modi</t>
+          <t>Rahul Garg</t>
         </is>
       </c>
       <c r="I49" s="27" t="inlineStr">
@@ -9590,7 +9534,7 @@
       </c>
       <c r="J49" s="27" t="inlineStr">
         <is>
-          <t>Dr Rahul Modi</t>
+          <t>Abhishek Dugar</t>
         </is>
       </c>
     </row>
@@ -9602,17 +9546,17 @@
       </c>
       <c r="B50" s="28" t="inlineStr">
         <is>
-          <t>11:30AM</t>
+          <t>12:00PM</t>
         </is>
       </c>
       <c r="C50" s="28" t="inlineStr">
         <is>
-          <t>11:45AM</t>
+          <t>12:15PM</t>
         </is>
       </c>
       <c r="D50" s="28" t="inlineStr">
         <is>
-          <t>Under 46</t>
+          <t>Under 15</t>
         </is>
       </c>
       <c r="E50" s="28" t="n">
@@ -9620,17 +9564,17 @@
       </c>
       <c r="F50" s="28" t="inlineStr">
         <is>
-          <t>CM-U46-GB-6</t>
+          <t>CM-U15-3</t>
         </is>
       </c>
       <c r="G50" s="28" t="inlineStr">
         <is>
-          <t>Board 2</t>
+          <t>Board 1</t>
         </is>
       </c>
       <c r="H50" s="28" t="inlineStr">
         <is>
-          <t>Nikunj Jhala</t>
+          <t>Aarav Pilankar</t>
         </is>
       </c>
       <c r="I50" s="28" t="inlineStr">
@@ -9640,7 +9584,7 @@
       </c>
       <c r="J50" s="28" t="inlineStr">
         <is>
-          <t>Amar Jain</t>
+          <t>Yash agarwal</t>
         </is>
       </c>
     </row>
@@ -9652,12 +9596,12 @@
       </c>
       <c r="B51" s="27" t="inlineStr">
         <is>
-          <t>11:30AM</t>
+          <t>12:00PM</t>
         </is>
       </c>
       <c r="C51" s="27" t="inlineStr">
         <is>
-          <t>11:45AM</t>
+          <t>12:15PM</t>
         </is>
       </c>
       <c r="D51" s="27" t="inlineStr">
@@ -9670,17 +9614,17 @@
       </c>
       <c r="F51" s="27" t="inlineStr">
         <is>
-          <t>CM-U46-GB-7</t>
+          <t>CM-U46-GB-6</t>
         </is>
       </c>
       <c r="G51" s="27" t="inlineStr">
         <is>
-          <t>Board 3</t>
+          <t>Board 2</t>
         </is>
       </c>
       <c r="H51" s="27" t="inlineStr">
         <is>
-          <t>Vinit Padia</t>
+          <t>Nikunj Jhala</t>
         </is>
       </c>
       <c r="I51" s="27" t="inlineStr">
@@ -9690,7 +9634,7 @@
       </c>
       <c r="J51" s="27" t="inlineStr">
         <is>
-          <t>Amit Ranka</t>
+          <t>Amar Jain</t>
         </is>
       </c>
     </row>
@@ -9702,17 +9646,17 @@
       </c>
       <c r="B52" s="28" t="inlineStr">
         <is>
-          <t>11:40AM</t>
+          <t>12:00PM</t>
         </is>
       </c>
       <c r="C52" s="28" t="inlineStr">
         <is>
-          <t>11:55AM</t>
+          <t>12:15PM</t>
         </is>
       </c>
       <c r="D52" s="28" t="inlineStr">
         <is>
-          <t>Under 15</t>
+          <t>Under 46</t>
         </is>
       </c>
       <c r="E52" s="28" t="n">
@@ -9720,17 +9664,17 @@
       </c>
       <c r="F52" s="28" t="inlineStr">
         <is>
-          <t>CM-U15-3</t>
+          <t>CM-U46-GB-7</t>
         </is>
       </c>
       <c r="G52" s="28" t="inlineStr">
         <is>
-          <t>Board 1</t>
+          <t>Board 3</t>
         </is>
       </c>
       <c r="H52" s="28" t="inlineStr">
         <is>
-          <t>Aarav Pilankar</t>
+          <t>Vinit Padia</t>
         </is>
       </c>
       <c r="I52" s="28" t="inlineStr">
@@ -9740,7 +9684,7 @@
       </c>
       <c r="J52" s="28" t="inlineStr">
         <is>
-          <t>Yash agarwal</t>
+          <t>Amit Ranka</t>
         </is>
       </c>
     </row>
@@ -9752,17 +9696,17 @@
       </c>
       <c r="B53" s="27" t="inlineStr">
         <is>
-          <t>11:45AM</t>
+          <t>12:25PM</t>
         </is>
       </c>
       <c r="C53" s="27" t="inlineStr">
         <is>
-          <t>12:00PM</t>
+          <t>12:40PM</t>
         </is>
       </c>
       <c r="D53" s="27" t="inlineStr">
         <is>
-          <t>Under 46</t>
+          <t>Under 15</t>
         </is>
       </c>
       <c r="E53" s="27" t="n">
@@ -9770,17 +9714,17 @@
       </c>
       <c r="F53" s="27" t="inlineStr">
         <is>
-          <t>CM-U46-GB-11</t>
+          <t>CM-U15-1</t>
         </is>
       </c>
       <c r="G53" s="27" t="inlineStr">
         <is>
-          <t>Board 2</t>
+          <t>Board 1</t>
         </is>
       </c>
       <c r="H53" s="27" t="inlineStr">
         <is>
-          <t>Nikunj Jhala</t>
+          <t>Shaurya Tripathi</t>
         </is>
       </c>
       <c r="I53" s="27" t="inlineStr">
@@ -9790,7 +9734,7 @@
       </c>
       <c r="J53" s="27" t="inlineStr">
         <is>
-          <t>Vinit Padia</t>
+          <t>Aarav Pilankar</t>
         </is>
       </c>
     </row>
@@ -9802,12 +9746,12 @@
       </c>
       <c r="B54" s="28" t="inlineStr">
         <is>
-          <t>11:45AM</t>
+          <t>12:25PM</t>
         </is>
       </c>
       <c r="C54" s="28" t="inlineStr">
         <is>
-          <t>12:00PM</t>
+          <t>12:40PM</t>
         </is>
       </c>
       <c r="D54" s="28" t="inlineStr">
@@ -9820,17 +9764,17 @@
       </c>
       <c r="F54" s="28" t="inlineStr">
         <is>
-          <t>CM-U46-GB-8</t>
+          <t>CM-U46-GB-11</t>
         </is>
       </c>
       <c r="G54" s="28" t="inlineStr">
         <is>
-          <t>Board 3</t>
+          <t>Board 2</t>
         </is>
       </c>
       <c r="H54" s="28" t="inlineStr">
         <is>
-          <t>Amar Jain</t>
+          <t>Nikunj Jhala</t>
         </is>
       </c>
       <c r="I54" s="28" t="inlineStr">
@@ -9840,7 +9784,7 @@
       </c>
       <c r="J54" s="28" t="inlineStr">
         <is>
-          <t>Nilesh Bagaria</t>
+          <t>Vinit Padia</t>
         </is>
       </c>
     </row>
@@ -9852,17 +9796,17 @@
       </c>
       <c r="B55" s="27" t="inlineStr">
         <is>
-          <t>11:55AM</t>
+          <t>12:25PM</t>
         </is>
       </c>
       <c r="C55" s="27" t="inlineStr">
         <is>
-          <t>12:10PM</t>
+          <t>12:40PM</t>
         </is>
       </c>
       <c r="D55" s="27" t="inlineStr">
         <is>
-          <t>Under 15</t>
+          <t>Under 46</t>
         </is>
       </c>
       <c r="E55" s="27" t="n">
@@ -9870,17 +9814,17 @@
       </c>
       <c r="F55" s="27" t="inlineStr">
         <is>
-          <t>CM-U15-1</t>
+          <t>CM-U46-GB-8</t>
         </is>
       </c>
       <c r="G55" s="27" t="inlineStr">
         <is>
-          <t>Board 1</t>
+          <t>Board 3</t>
         </is>
       </c>
       <c r="H55" s="27" t="inlineStr">
         <is>
-          <t>Shaurya Tripathi</t>
+          <t>Amar Jain</t>
         </is>
       </c>
       <c r="I55" s="27" t="inlineStr">
@@ -9890,7 +9834,7 @@
       </c>
       <c r="J55" s="27" t="inlineStr">
         <is>
-          <t>Aarav Pilankar</t>
+          <t>Nilesh Bagaria</t>
         </is>
       </c>
     </row>
@@ -9902,12 +9846,12 @@
       </c>
       <c r="B56" s="28" t="inlineStr">
         <is>
-          <t>12:00PM</t>
+          <t>12:50PM</t>
         </is>
       </c>
       <c r="C56" s="28" t="inlineStr">
         <is>
-          <t>12:15PM</t>
+          <t>1:05PM</t>
         </is>
       </c>
       <c r="D56" s="28" t="inlineStr">
@@ -9952,12 +9896,12 @@
       </c>
       <c r="B57" s="27" t="inlineStr">
         <is>
-          <t>12:00PM</t>
+          <t>12:50PM</t>
         </is>
       </c>
       <c r="C57" s="27" t="inlineStr">
         <is>
-          <t>12:15PM</t>
+          <t>1:05PM</t>
         </is>
       </c>
       <c r="D57" s="27" t="inlineStr">
@@ -9970,17 +9914,17 @@
       </c>
       <c r="F57" s="27" t="inlineStr">
         <is>
-          <t>CM-U46-GB-9</t>
+          <t>CM-U46-GB-15</t>
         </is>
       </c>
       <c r="G57" s="27" t="inlineStr">
         <is>
-          <t>Board 3</t>
+          <t>Board 1</t>
         </is>
       </c>
       <c r="H57" s="27" t="inlineStr">
         <is>
-          <t>Mayank Aggarwal</t>
+          <t>Vinit Padia</t>
         </is>
       </c>
       <c r="I57" s="27" t="inlineStr">
@@ -9990,7 +9934,7 @@
       </c>
       <c r="J57" s="27" t="inlineStr">
         <is>
-          <t>Nikunj Jhala</t>
+          <t>Nilesh Bagaria</t>
         </is>
       </c>
     </row>
@@ -10002,12 +9946,12 @@
       </c>
       <c r="B58" s="28" t="inlineStr">
         <is>
-          <t>12:10PM</t>
+          <t>12:50PM</t>
         </is>
       </c>
       <c r="C58" s="28" t="inlineStr">
         <is>
-          <t>12:25PM</t>
+          <t>1:05PM</t>
         </is>
       </c>
       <c r="D58" s="28" t="inlineStr">
@@ -10020,17 +9964,17 @@
       </c>
       <c r="F58" s="28" t="inlineStr">
         <is>
-          <t>CM-U46-GB-15</t>
+          <t>CM-U46-GB-9</t>
         </is>
       </c>
       <c r="G58" s="28" t="inlineStr">
         <is>
-          <t>Board 1</t>
+          <t>Board 3</t>
         </is>
       </c>
       <c r="H58" s="28" t="inlineStr">
         <is>
-          <t>Vinit Padia</t>
+          <t>Mayank Aggarwal</t>
         </is>
       </c>
       <c r="I58" s="28" t="inlineStr">
@@ -10040,7 +9984,7 @@
       </c>
       <c r="J58" s="28" t="inlineStr">
         <is>
-          <t>Nilesh Bagaria</t>
+          <t>Nikunj Jhala</t>
         </is>
       </c>
     </row>
@@ -10052,12 +9996,12 @@
       </c>
       <c r="B59" s="27" t="inlineStr">
         <is>
-          <t>12:15PM</t>
+          <t>1:15PM</t>
         </is>
       </c>
       <c r="C59" s="27" t="inlineStr">
         <is>
-          <t>12:30PM</t>
+          <t>1:30PM</t>
         </is>
       </c>
       <c r="D59" s="27" t="inlineStr">
@@ -10102,12 +10046,12 @@
       </c>
       <c r="B60" s="28" t="inlineStr">
         <is>
-          <t>12:15PM</t>
+          <t>1:15PM</t>
         </is>
       </c>
       <c r="C60" s="28" t="inlineStr">
         <is>
-          <t>12:30PM</t>
+          <t>1:30PM</t>
         </is>
       </c>
       <c r="D60" s="28" t="inlineStr">
@@ -10402,17 +10346,17 @@
       </c>
       <c r="B66" s="28" t="inlineStr">
         <is>
-          <t>3:15PM</t>
+          <t>3:30PM</t>
         </is>
       </c>
       <c r="C66" s="28" t="inlineStr">
         <is>
-          <t>3:40PM</t>
+          <t>3:45PM</t>
         </is>
       </c>
       <c r="D66" s="28" t="inlineStr">
         <is>
-          <t>Under 15</t>
+          <t>Under 46</t>
         </is>
       </c>
       <c r="E66" s="28" t="n">
@@ -10420,17 +10364,17 @@
       </c>
       <c r="F66" s="28" t="inlineStr">
         <is>
-          <t>U15-FINAL</t>
+          <t>CM-U46-GA-15</t>
         </is>
       </c>
       <c r="G66" s="28" t="inlineStr">
         <is>
-          <t>Board 3</t>
+          <t>Board 1</t>
         </is>
       </c>
       <c r="H66" s="28" t="inlineStr">
         <is>
-          <t>Pool 1st</t>
+          <t>Dr Rahul Modi</t>
         </is>
       </c>
       <c r="I66" s="28" t="inlineStr">
@@ -10440,7 +10384,7 @@
       </c>
       <c r="J66" s="28" t="inlineStr">
         <is>
-          <t>Pool 2nd</t>
+          <t>Ankur Mahante</t>
         </is>
       </c>
     </row>
@@ -10452,12 +10396,12 @@
       </c>
       <c r="B67" s="27" t="inlineStr">
         <is>
-          <t>3:30PM</t>
+          <t>3:40PM</t>
         </is>
       </c>
       <c r="C67" s="27" t="inlineStr">
         <is>
-          <t>3:45PM</t>
+          <t>3:55PM</t>
         </is>
       </c>
       <c r="D67" s="27" t="inlineStr">
@@ -10502,17 +10446,17 @@
       </c>
       <c r="B68" s="28" t="inlineStr">
         <is>
-          <t>3:30PM</t>
+          <t>3:50PM</t>
         </is>
       </c>
       <c r="C68" s="28" t="inlineStr">
         <is>
-          <t>3:45PM</t>
+          <t>4:05PM</t>
         </is>
       </c>
       <c r="D68" s="28" t="inlineStr">
         <is>
-          <t>Under 46</t>
+          <t>Above 46</t>
         </is>
       </c>
       <c r="E68" s="28" t="n">
@@ -10520,17 +10464,17 @@
       </c>
       <c r="F68" s="28" t="inlineStr">
         <is>
-          <t>CM-U46-GA-15</t>
+          <t>CM-A46-GA-1</t>
         </is>
       </c>
       <c r="G68" s="28" t="inlineStr">
         <is>
-          <t>Board 1</t>
+          <t>Board 3</t>
         </is>
       </c>
       <c r="H68" s="28" t="inlineStr">
         <is>
-          <t>Dr Rahul Modi</t>
+          <t>Vinay Sawant</t>
         </is>
       </c>
       <c r="I68" s="28" t="inlineStr">
@@ -10540,7 +10484,7 @@
       </c>
       <c r="J68" s="28" t="inlineStr">
         <is>
-          <t>Ankur Mahante</t>
+          <t>Mukul Joshi</t>
         </is>
       </c>
     </row>
@@ -10552,12 +10496,12 @@
       </c>
       <c r="B69" s="27" t="inlineStr">
         <is>
-          <t>3:40PM</t>
+          <t>4:05PM</t>
         </is>
       </c>
       <c r="C69" s="27" t="inlineStr">
         <is>
-          <t>3:55PM</t>
+          <t>4:20PM</t>
         </is>
       </c>
       <c r="D69" s="27" t="inlineStr">
@@ -10570,17 +10514,17 @@
       </c>
       <c r="F69" s="27" t="inlineStr">
         <is>
-          <t>CM-A46-GA-1</t>
+          <t>CM-A46-GB-5</t>
         </is>
       </c>
       <c r="G69" s="27" t="inlineStr">
         <is>
-          <t>Board 3</t>
+          <t>Board 1</t>
         </is>
       </c>
       <c r="H69" s="27" t="inlineStr">
         <is>
-          <t>Vinay Sawant</t>
+          <t>Vinod Agrawal</t>
         </is>
       </c>
       <c r="I69" s="27" t="inlineStr">
@@ -10590,7 +10534,7 @@
       </c>
       <c r="J69" s="27" t="inlineStr">
         <is>
-          <t>Mukul Joshi</t>
+          <t>Gopal Krishna</t>
         </is>
       </c>
     </row>
@@ -10602,12 +10546,12 @@
       </c>
       <c r="B70" s="28" t="inlineStr">
         <is>
-          <t>3:45PM</t>
+          <t>4:15PM</t>
         </is>
       </c>
       <c r="C70" s="28" t="inlineStr">
         <is>
-          <t>4:00PM</t>
+          <t>4:30PM</t>
         </is>
       </c>
       <c r="D70" s="28" t="inlineStr">
@@ -10620,17 +10564,17 @@
       </c>
       <c r="F70" s="28" t="inlineStr">
         <is>
-          <t>CM-A46-GB-5</t>
+          <t>CM-A46-GA-4</t>
         </is>
       </c>
       <c r="G70" s="28" t="inlineStr">
         <is>
-          <t>Board 1</t>
+          <t>Board 3</t>
         </is>
       </c>
       <c r="H70" s="28" t="inlineStr">
         <is>
-          <t>Vinod Agrawal</t>
+          <t>Mukul Joshi</t>
         </is>
       </c>
       <c r="I70" s="28" t="inlineStr">
@@ -10640,7 +10584,7 @@
       </c>
       <c r="J70" s="28" t="inlineStr">
         <is>
-          <t>Gopal Krishna</t>
+          <t>Mr. Hiral Khadepau</t>
         </is>
       </c>
     </row>
@@ -10652,12 +10596,12 @@
       </c>
       <c r="B71" s="27" t="inlineStr">
         <is>
-          <t>3:55PM</t>
+          <t>4:50PM</t>
         </is>
       </c>
       <c r="C71" s="27" t="inlineStr">
         <is>
-          <t>4:10PM</t>
+          <t>5:05PM</t>
         </is>
       </c>
       <c r="D71" s="27" t="inlineStr">
@@ -10670,17 +10614,17 @@
       </c>
       <c r="F71" s="27" t="inlineStr">
         <is>
-          <t>CM-A46-GA-4</t>
+          <t>CM-A46-GA-3</t>
         </is>
       </c>
       <c r="G71" s="27" t="inlineStr">
         <is>
-          <t>Board 3</t>
+          <t>Board 1</t>
         </is>
       </c>
       <c r="H71" s="27" t="inlineStr">
         <is>
-          <t>Mukul Joshi</t>
+          <t>Vinay Sawant</t>
         </is>
       </c>
       <c r="I71" s="27" t="inlineStr">
@@ -10690,7 +10634,7 @@
       </c>
       <c r="J71" s="27" t="inlineStr">
         <is>
-          <t>Mr. Hiral Khadepau</t>
+          <t>Adil Khan</t>
         </is>
       </c>
     </row>
@@ -10702,12 +10646,12 @@
       </c>
       <c r="B72" s="28" t="inlineStr">
         <is>
-          <t>4:20PM</t>
+          <t>4:50PM</t>
         </is>
       </c>
       <c r="C72" s="28" t="inlineStr">
         <is>
-          <t>4:35PM</t>
+          <t>5:05PM</t>
         </is>
       </c>
       <c r="D72" s="28" t="inlineStr">
@@ -10720,17 +10664,17 @@
       </c>
       <c r="F72" s="28" t="inlineStr">
         <is>
-          <t>CM-A46-GA-3</t>
+          <t>CM-A46-GB-4</t>
         </is>
       </c>
       <c r="G72" s="28" t="inlineStr">
         <is>
-          <t>Board 1</t>
+          <t>Board 2</t>
         </is>
       </c>
       <c r="H72" s="28" t="inlineStr">
         <is>
-          <t>Vinay Sawant</t>
+          <t>Prasad Akshintala</t>
         </is>
       </c>
       <c r="I72" s="28" t="inlineStr">
@@ -10740,7 +10684,7 @@
       </c>
       <c r="J72" s="28" t="inlineStr">
         <is>
-          <t>Adil Khan</t>
+          <t>Gopal Krishna</t>
         </is>
       </c>
     </row>
@@ -10752,12 +10696,12 @@
       </c>
       <c r="B73" s="27" t="inlineStr">
         <is>
-          <t>4:24PM</t>
+          <t>5:15PM</t>
         </is>
       </c>
       <c r="C73" s="27" t="inlineStr">
         <is>
-          <t>4:39PM</t>
+          <t>5:30PM</t>
         </is>
       </c>
       <c r="D73" s="27" t="inlineStr">
@@ -10770,17 +10714,17 @@
       </c>
       <c r="F73" s="27" t="inlineStr">
         <is>
-          <t>CM-A46-GB-4</t>
+          <t>CM-A46-GA-5</t>
         </is>
       </c>
       <c r="G73" s="27" t="inlineStr">
         <is>
-          <t>Board 2</t>
+          <t>Board 3</t>
         </is>
       </c>
       <c r="H73" s="27" t="inlineStr">
         <is>
-          <t>Prasad Akshintala</t>
+          <t>Vinay Sawant</t>
         </is>
       </c>
       <c r="I73" s="27" t="inlineStr">
@@ -10790,7 +10734,7 @@
       </c>
       <c r="J73" s="27" t="inlineStr">
         <is>
-          <t>Gopal Krishna</t>
+          <t>Mr. Hiral Khadepau</t>
         </is>
       </c>
     </row>
@@ -10802,12 +10746,12 @@
       </c>
       <c r="B74" s="28" t="inlineStr">
         <is>
-          <t>4:35PM</t>
+          <t>6:40PM</t>
         </is>
       </c>
       <c r="C74" s="28" t="inlineStr">
         <is>
-          <t>4:50PM</t>
+          <t>6:55PM</t>
         </is>
       </c>
       <c r="D74" s="28" t="inlineStr">
@@ -10820,7 +10764,7 @@
       </c>
       <c r="F74" s="28" t="inlineStr">
         <is>
-          <t>CM-A46-GA-5</t>
+          <t>CM-A46-GA-6</t>
         </is>
       </c>
       <c r="G74" s="28" t="inlineStr">
@@ -10830,7 +10774,7 @@
       </c>
       <c r="H74" s="28" t="inlineStr">
         <is>
-          <t>Vinay Sawant</t>
+          <t>Mukul Joshi</t>
         </is>
       </c>
       <c r="I74" s="28" t="inlineStr">
@@ -10840,7 +10784,7 @@
       </c>
       <c r="J74" s="28" t="inlineStr">
         <is>
-          <t>Mr. Hiral Khadepau</t>
+          <t>Adil Khan</t>
         </is>
       </c>
     </row>
@@ -10852,12 +10796,12 @@
       </c>
       <c r="B75" s="27" t="inlineStr">
         <is>
-          <t>5:40PM</t>
+          <t>7:20PM</t>
         </is>
       </c>
       <c r="C75" s="27" t="inlineStr">
         <is>
-          <t>5:55PM</t>
+          <t>7:35PM</t>
         </is>
       </c>
       <c r="D75" s="27" t="inlineStr">
@@ -10870,17 +10814,17 @@
       </c>
       <c r="F75" s="27" t="inlineStr">
         <is>
-          <t>CM-A46-GA-6</t>
+          <t>CM-A46-GB-6</t>
         </is>
       </c>
       <c r="G75" s="27" t="inlineStr">
         <is>
-          <t>Board 3</t>
+          <t>Board 2</t>
         </is>
       </c>
       <c r="H75" s="27" t="inlineStr">
         <is>
-          <t>Mukul Joshi</t>
+          <t>Prasad Akshintala</t>
         </is>
       </c>
       <c r="I75" s="27" t="inlineStr">
@@ -10890,24 +10834,24 @@
       </c>
       <c r="J75" s="27" t="inlineStr">
         <is>
-          <t>Adil Khan</t>
+          <t>Sanjay Kumar</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="28" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B76" s="28" t="inlineStr">
         <is>
-          <t>6:20PM</t>
+          <t>11:50AM</t>
         </is>
       </c>
       <c r="C76" s="28" t="inlineStr">
         <is>
-          <t>6:35PM</t>
+          <t>12:05PM</t>
         </is>
       </c>
       <c r="D76" s="28" t="inlineStr">
@@ -10920,7 +10864,7 @@
       </c>
       <c r="F76" s="28" t="inlineStr">
         <is>
-          <t>CM-A46-GB-6</t>
+          <t>A46-FINAL</t>
         </is>
       </c>
       <c r="G76" s="28" t="inlineStr">
@@ -10930,7 +10874,7 @@
       </c>
       <c r="H76" s="28" t="inlineStr">
         <is>
-          <t>Prasad Akshintala</t>
+          <t>Winner SF1</t>
         </is>
       </c>
       <c r="I76" s="28" t="inlineStr">
@@ -10940,24 +10884,24 @@
       </c>
       <c r="J76" s="28" t="inlineStr">
         <is>
-          <t>Sanjay Kumar</t>
+          <t>Winner SF2</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="27" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B77" s="27" t="inlineStr">
         <is>
-          <t>7:40PM</t>
+          <t>11:50AM</t>
         </is>
       </c>
       <c r="C77" s="27" t="inlineStr">
         <is>
-          <t>7:55PM</t>
+          <t>12:05PM</t>
         </is>
       </c>
       <c r="D77" s="27" t="inlineStr">
@@ -10997,22 +10941,22 @@
     <row r="78">
       <c r="A78" s="28" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B78" s="28" t="inlineStr">
         <is>
-          <t>7:40PM</t>
+          <t>11:50AM</t>
         </is>
       </c>
       <c r="C78" s="28" t="inlineStr">
         <is>
-          <t>7:55PM</t>
+          <t>12:05PM</t>
         </is>
       </c>
       <c r="D78" s="28" t="inlineStr">
         <is>
-          <t>Above 46</t>
+          <t>Under 15</t>
         </is>
       </c>
       <c r="E78" s="28" t="n">
@@ -11020,7 +10964,7 @@
       </c>
       <c r="F78" s="28" t="inlineStr">
         <is>
-          <t>A46-SF2</t>
+          <t>U15-FINAL</t>
         </is>
       </c>
       <c r="G78" s="28" t="inlineStr">
@@ -11030,7 +10974,7 @@
       </c>
       <c r="H78" s="28" t="inlineStr">
         <is>
-          <t>Group B 1st</t>
+          <t>Pool 1st</t>
         </is>
       </c>
       <c r="I78" s="28" t="inlineStr">
@@ -11040,24 +10984,24 @@
       </c>
       <c r="J78" s="28" t="inlineStr">
         <is>
-          <t>Group A 2nd</t>
+          <t>Pool 2nd</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="27" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B79" s="27" t="inlineStr">
         <is>
-          <t>7:55PM</t>
+          <t>12:05PM</t>
         </is>
       </c>
       <c r="C79" s="27" t="inlineStr">
         <is>
-          <t>8:20PM</t>
+          <t>12:20PM</t>
         </is>
       </c>
       <c r="D79" s="27" t="inlineStr">
@@ -11070,17 +11014,17 @@
       </c>
       <c r="F79" s="27" t="inlineStr">
         <is>
-          <t>A46-FINAL</t>
+          <t>A46-SF2</t>
         </is>
       </c>
       <c r="G79" s="27" t="inlineStr">
         <is>
-          <t>Board 2</t>
+          <t>Board 3</t>
         </is>
       </c>
       <c r="H79" s="27" t="inlineStr">
         <is>
-          <t>Winner SF1</t>
+          <t>Group B 1st</t>
         </is>
       </c>
       <c r="I79" s="27" t="inlineStr">
@@ -11090,7 +11034,7 @@
       </c>
       <c r="J79" s="27" t="inlineStr">
         <is>
-          <t>Winner SF2</t>
+          <t>Group A 2nd</t>
         </is>
       </c>
     </row>
@@ -11102,12 +11046,12 @@
       </c>
       <c r="B80" s="28" t="inlineStr">
         <is>
-          <t>10:50AM</t>
+          <t>12:05PM</t>
         </is>
       </c>
       <c r="C80" s="28" t="inlineStr">
         <is>
-          <t>11:05AM</t>
+          <t>12:20PM</t>
         </is>
       </c>
       <c r="D80" s="28" t="inlineStr">
@@ -11152,12 +11096,12 @@
       </c>
       <c r="B81" s="27" t="inlineStr">
         <is>
-          <t>10:50AM</t>
+          <t>12:05PM</t>
         </is>
       </c>
       <c r="C81" s="27" t="inlineStr">
         <is>
-          <t>11:05AM</t>
+          <t>12:20PM</t>
         </is>
       </c>
       <c r="D81" s="27" t="inlineStr">
@@ -11202,12 +11146,12 @@
       </c>
       <c r="B82" s="28" t="inlineStr">
         <is>
-          <t>11:05AM</t>
+          <t>12:20PM</t>
         </is>
       </c>
       <c r="C82" s="28" t="inlineStr">
         <is>
-          <t>11:30AM</t>
+          <t>12:35PM</t>
         </is>
       </c>
       <c r="D82" s="28" t="inlineStr">
@@ -11541,12 +11485,12 @@
       </c>
       <c r="B19" s="27" t="inlineStr">
         <is>
-          <t>8:15AM</t>
+          <t>8:25AM</t>
         </is>
       </c>
       <c r="C19" s="27" t="inlineStr">
         <is>
-          <t>8:30AM</t>
+          <t>8:40AM</t>
         </is>
       </c>
       <c r="D19" s="27" t="inlineStr">
@@ -11591,12 +11535,12 @@
       </c>
       <c r="B20" s="28" t="inlineStr">
         <is>
-          <t>8:15AM</t>
+          <t>8:25AM</t>
         </is>
       </c>
       <c r="C20" s="28" t="inlineStr">
         <is>
-          <t>8:30AM</t>
+          <t>8:40AM</t>
         </is>
       </c>
       <c r="D20" s="28" t="inlineStr">
@@ -11641,12 +11585,12 @@
       </c>
       <c r="B21" s="27" t="inlineStr">
         <is>
-          <t>8:30AM</t>
+          <t>8:50AM</t>
         </is>
       </c>
       <c r="C21" s="27" t="inlineStr">
         <is>
-          <t>8:45AM</t>
+          <t>9:05AM</t>
         </is>
       </c>
       <c r="D21" s="27" t="inlineStr">
@@ -11691,12 +11635,12 @@
       </c>
       <c r="B22" s="28" t="inlineStr">
         <is>
-          <t>8:30AM</t>
+          <t>8:50AM</t>
         </is>
       </c>
       <c r="C22" s="28" t="inlineStr">
         <is>
-          <t>8:45AM</t>
+          <t>9:05AM</t>
         </is>
       </c>
       <c r="D22" s="28" t="inlineStr">
@@ -11741,12 +11685,12 @@
       </c>
       <c r="B23" s="27" t="inlineStr">
         <is>
-          <t>8:45AM</t>
+          <t>9:15AM</t>
         </is>
       </c>
       <c r="C23" s="27" t="inlineStr">
         <is>
-          <t>9:00AM</t>
+          <t>9:30AM</t>
         </is>
       </c>
       <c r="D23" s="27" t="inlineStr">
@@ -11791,12 +11735,12 @@
       </c>
       <c r="B24" s="28" t="inlineStr">
         <is>
-          <t>8:45AM</t>
+          <t>9:15AM</t>
         </is>
       </c>
       <c r="C24" s="28" t="inlineStr">
         <is>
-          <t>9:00AM</t>
+          <t>9:30AM</t>
         </is>
       </c>
       <c r="D24" s="28" t="inlineStr">
@@ -11841,12 +11785,12 @@
       </c>
       <c r="B25" s="27" t="inlineStr">
         <is>
-          <t>9:00AM</t>
+          <t>9:40AM</t>
         </is>
       </c>
       <c r="C25" s="27" t="inlineStr">
         <is>
-          <t>9:15AM</t>
+          <t>9:55AM</t>
         </is>
       </c>
       <c r="D25" s="27" t="inlineStr">
@@ -11891,12 +11835,12 @@
       </c>
       <c r="B26" s="28" t="inlineStr">
         <is>
-          <t>9:00AM</t>
+          <t>9:40AM</t>
         </is>
       </c>
       <c r="C26" s="28" t="inlineStr">
         <is>
-          <t>9:15AM</t>
+          <t>9:55AM</t>
         </is>
       </c>
       <c r="D26" s="28" t="inlineStr">
@@ -11936,17 +11880,17 @@
     <row r="27">
       <c r="A27" s="27" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B27" s="27" t="inlineStr">
         <is>
-          <t>10:30AM</t>
+          <t>11:50AM</t>
         </is>
       </c>
       <c r="C27" s="27" t="inlineStr">
         <is>
-          <t>10:55AM</t>
+          <t>12:05PM</t>
         </is>
       </c>
       <c r="D27" s="27" t="inlineStr">
@@ -12275,17 +12219,17 @@
     <row r="28">
       <c r="A28" s="27" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B28" s="27" t="inlineStr">
         <is>
-          <t>3:45PM</t>
+          <t>11:50AM</t>
         </is>
       </c>
       <c r="C28" s="27" t="inlineStr">
         <is>
-          <t>4:00PM</t>
+          <t>12:05PM</t>
         </is>
       </c>
       <c r="D28" s="27" t="inlineStr">
@@ -12298,17 +12242,17 @@
       </c>
       <c r="F28" s="27" t="inlineStr">
         <is>
-          <t>M5</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="G28" s="27" t="inlineStr">
         <is>
-          <t>Board 2</t>
+          <t>Board 1</t>
         </is>
       </c>
       <c r="H28" s="27" t="inlineStr">
         <is>
-          <t>Poornima Shriyan &amp; Shreya Shriyan</t>
+          <t>Rahul Garg &amp; Parthiv Mody</t>
         </is>
       </c>
       <c r="I28" s="27" t="inlineStr">
@@ -12318,24 +12262,24 @@
       </c>
       <c r="J28" s="27" t="inlineStr">
         <is>
-          <t>Renuka Tripathi &amp; Swati Tripathi</t>
+          <t>Sankalp Bhatnagar &amp; Jitin Bhatnagar</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="28" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B29" s="28" t="inlineStr">
         <is>
-          <t>4:00PM</t>
+          <t>11:50AM</t>
         </is>
       </c>
       <c r="C29" s="28" t="inlineStr">
         <is>
-          <t>4:15PM</t>
+          <t>12:05PM</t>
         </is>
       </c>
       <c r="D29" s="28" t="inlineStr">
@@ -12348,17 +12292,17 @@
       </c>
       <c r="F29" s="28" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M5</t>
         </is>
       </c>
       <c r="G29" s="28" t="inlineStr">
         <is>
-          <t>Board 1</t>
+          <t>Board 2</t>
         </is>
       </c>
       <c r="H29" s="28" t="inlineStr">
         <is>
-          <t>Rahul Garg &amp; Parthiv Mody</t>
+          <t>Poornima Shriyan &amp; Shreya Shriyan</t>
         </is>
       </c>
       <c r="I29" s="28" t="inlineStr">
@@ -12368,24 +12312,24 @@
       </c>
       <c r="J29" s="28" t="inlineStr">
         <is>
-          <t>Sankalp Bhatnagar &amp; Jitin Bhatnagar</t>
+          <t>Renuka Tripathi &amp; Swati Tripathi</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="27" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B30" s="27" t="inlineStr">
         <is>
-          <t>4:09PM</t>
+          <t>11:50AM</t>
         </is>
       </c>
       <c r="C30" s="27" t="inlineStr">
         <is>
-          <t>4:24PM</t>
+          <t>12:05PM</t>
         </is>
       </c>
       <c r="D30" s="27" t="inlineStr">
@@ -12398,17 +12342,17 @@
       </c>
       <c r="F30" s="27" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M7</t>
         </is>
       </c>
       <c r="G30" s="27" t="inlineStr">
         <is>
-          <t>Board 2</t>
+          <t>Board 3</t>
         </is>
       </c>
       <c r="H30" s="27" t="inlineStr">
         <is>
-          <t>Shalu Agarwal &amp; Vrinda Agrawal</t>
+          <t>Tejas doshi &amp; Krutika</t>
         </is>
       </c>
       <c r="I30" s="27" t="inlineStr">
@@ -12418,24 +12362,24 @@
       </c>
       <c r="J30" s="27" t="inlineStr">
         <is>
-          <t>Vinit Padia &amp; Pratik Haldiya</t>
+          <t>Shraddha malgadnkar &amp; Sachin Malgadnkar</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="28" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B31" s="28" t="inlineStr">
         <is>
-          <t>4:10PM</t>
+          <t>12:05PM</t>
         </is>
       </c>
       <c r="C31" s="28" t="inlineStr">
         <is>
-          <t>4:25PM</t>
+          <t>12:20PM</t>
         </is>
       </c>
       <c r="D31" s="28" t="inlineStr">
@@ -12448,17 +12392,17 @@
       </c>
       <c r="F31" s="28" t="inlineStr">
         <is>
-          <t>M7</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="G31" s="28" t="inlineStr">
         <is>
-          <t>Board 3</t>
+          <t>Board 2</t>
         </is>
       </c>
       <c r="H31" s="28" t="inlineStr">
         <is>
-          <t>Tejas doshi &amp; Krutika</t>
+          <t>Shalu Agarwal &amp; Vrinda Agrawal</t>
         </is>
       </c>
       <c r="I31" s="28" t="inlineStr">
@@ -12468,24 +12412,24 @@
       </c>
       <c r="J31" s="28" t="inlineStr">
         <is>
-          <t>Shraddha malgadnkar &amp; Sachin Malgadnkar</t>
+          <t>Vinit Padia &amp; Pratik Haldiya</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="27" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B32" s="27" t="inlineStr">
         <is>
-          <t>4:35PM</t>
+          <t>12:05PM</t>
         </is>
       </c>
       <c r="C32" s="27" t="inlineStr">
         <is>
-          <t>4:50PM</t>
+          <t>12:20PM</t>
         </is>
       </c>
       <c r="D32" s="27" t="inlineStr">
@@ -12525,17 +12469,17 @@
     <row r="33">
       <c r="A33" s="28" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B33" s="28" t="inlineStr">
         <is>
-          <t>4:39PM</t>
+          <t>12:05PM</t>
         </is>
       </c>
       <c r="C33" s="28" t="inlineStr">
         <is>
-          <t>4:54PM</t>
+          <t>12:20PM</t>
         </is>
       </c>
       <c r="D33" s="28" t="inlineStr">
@@ -12548,17 +12492,17 @@
       </c>
       <c r="F33" s="28" t="inlineStr">
         <is>
-          <t>M4</t>
+          <t>QF3</t>
         </is>
       </c>
       <c r="G33" s="28" t="inlineStr">
         <is>
-          <t>Board 2</t>
+          <t>Board 3</t>
         </is>
       </c>
       <c r="H33" s="28" t="inlineStr">
         <is>
-          <t>Nilesh Bagaria &amp; Parthiv</t>
+          <t>Winner M5</t>
         </is>
       </c>
       <c r="I33" s="28" t="inlineStr">
@@ -12568,24 +12512,24 @@
       </c>
       <c r="J33" s="28" t="inlineStr">
         <is>
-          <t>Prasad Akshintala &amp; Suvarna Akshintala</t>
+          <t>Winner M6</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="27" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B34" s="27" t="inlineStr">
         <is>
-          <t>4:50PM</t>
+          <t>12:20PM</t>
         </is>
       </c>
       <c r="C34" s="27" t="inlineStr">
         <is>
-          <t>5:05PM</t>
+          <t>12:35PM</t>
         </is>
       </c>
       <c r="D34" s="27" t="inlineStr">
@@ -12598,17 +12542,17 @@
       </c>
       <c r="F34" s="27" t="inlineStr">
         <is>
-          <t>M6</t>
+          <t>M4</t>
         </is>
       </c>
       <c r="G34" s="27" t="inlineStr">
         <is>
-          <t>Board 1</t>
+          <t>Board 2</t>
         </is>
       </c>
       <c r="H34" s="27" t="inlineStr">
         <is>
-          <t>Mayank Aggarwal &amp; Naresh Aggarwal</t>
+          <t>Nilesh Bagaria &amp; Parthiv</t>
         </is>
       </c>
       <c r="I34" s="27" t="inlineStr">
@@ -12618,24 +12562,24 @@
       </c>
       <c r="J34" s="27" t="inlineStr">
         <is>
-          <t>Vinay Sawant &amp; Amar Jain</t>
+          <t>Prasad Akshintala &amp; Suvarna Akshintala</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="28" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B35" s="28" t="inlineStr">
         <is>
-          <t>5:05PM</t>
+          <t>12:20PM</t>
         </is>
       </c>
       <c r="C35" s="28" t="inlineStr">
         <is>
-          <t>5:20PM</t>
+          <t>12:35PM</t>
         </is>
       </c>
       <c r="D35" s="28" t="inlineStr">
@@ -12648,17 +12592,17 @@
       </c>
       <c r="F35" s="28" t="inlineStr">
         <is>
-          <t>QF3</t>
+          <t>M6</t>
         </is>
       </c>
       <c r="G35" s="28" t="inlineStr">
         <is>
-          <t>Board 3</t>
+          <t>Board 1</t>
         </is>
       </c>
       <c r="H35" s="28" t="inlineStr">
         <is>
-          <t>Winner M5</t>
+          <t>Mayank Aggarwal &amp; Naresh Aggarwal</t>
         </is>
       </c>
       <c r="I35" s="28" t="inlineStr">
@@ -12668,24 +12612,24 @@
       </c>
       <c r="J35" s="28" t="inlineStr">
         <is>
-          <t>Winner M6</t>
+          <t>Vinay Sawant &amp; Amar Jain</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="27" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B36" s="27" t="inlineStr">
         <is>
-          <t>5:09PM</t>
+          <t>12:20PM</t>
         </is>
       </c>
       <c r="C36" s="27" t="inlineStr">
         <is>
-          <t>5:24PM</t>
+          <t>12:35PM</t>
         </is>
       </c>
       <c r="D36" s="27" t="inlineStr">
@@ -12698,17 +12642,17 @@
       </c>
       <c r="F36" s="27" t="inlineStr">
         <is>
-          <t>QF1</t>
+          <t>SF2</t>
         </is>
       </c>
       <c r="G36" s="27" t="inlineStr">
         <is>
-          <t>Board 2</t>
+          <t>Board 3</t>
         </is>
       </c>
       <c r="H36" s="27" t="inlineStr">
         <is>
-          <t>Winner M1</t>
+          <t>Winner QF3</t>
         </is>
       </c>
       <c r="I36" s="27" t="inlineStr">
@@ -12718,24 +12662,24 @@
       </c>
       <c r="J36" s="27" t="inlineStr">
         <is>
-          <t>Winner M2</t>
+          <t>Winner QF4</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="28" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B37" s="28" t="inlineStr">
         <is>
-          <t>5:30PM</t>
+          <t>12:35PM</t>
         </is>
       </c>
       <c r="C37" s="28" t="inlineStr">
         <is>
-          <t>5:45PM</t>
+          <t>12:50PM</t>
         </is>
       </c>
       <c r="D37" s="28" t="inlineStr">
@@ -12748,17 +12692,17 @@
       </c>
       <c r="F37" s="28" t="inlineStr">
         <is>
-          <t>QF4</t>
+          <t>QF1</t>
         </is>
       </c>
       <c r="G37" s="28" t="inlineStr">
         <is>
-          <t>Board 1</t>
+          <t>Board 2</t>
         </is>
       </c>
       <c r="H37" s="28" t="inlineStr">
         <is>
-          <t>Winner M7</t>
+          <t>Winner M1</t>
         </is>
       </c>
       <c r="I37" s="28" t="inlineStr">
@@ -12768,24 +12712,24 @@
       </c>
       <c r="J37" s="28" t="inlineStr">
         <is>
-          <t>Ravi Modi &amp; Dr Rahul Modi (BYE)</t>
+          <t>Winner M2</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="27" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B38" s="27" t="inlineStr">
         <is>
-          <t>9:15PM</t>
+          <t>12:35PM</t>
         </is>
       </c>
       <c r="C38" s="27" t="inlineStr">
         <is>
-          <t>9:30PM</t>
+          <t>12:50PM</t>
         </is>
       </c>
       <c r="D38" s="27" t="inlineStr">
@@ -12798,7 +12742,7 @@
       </c>
       <c r="F38" s="27" t="inlineStr">
         <is>
-          <t>QF2</t>
+          <t>QF4</t>
         </is>
       </c>
       <c r="G38" s="27" t="inlineStr">
@@ -12808,7 +12752,7 @@
       </c>
       <c r="H38" s="27" t="inlineStr">
         <is>
-          <t>Winner M3</t>
+          <t>Winner M7</t>
         </is>
       </c>
       <c r="I38" s="27" t="inlineStr">
@@ -12818,7 +12762,7 @@
       </c>
       <c r="J38" s="27" t="inlineStr">
         <is>
-          <t>Winner M4</t>
+          <t>Ravi Modi &amp; Dr Rahul Modi (BYE)</t>
         </is>
       </c>
     </row>
@@ -12830,12 +12774,12 @@
       </c>
       <c r="B39" s="28" t="inlineStr">
         <is>
-          <t>8:55AM</t>
+          <t>12:50PM</t>
         </is>
       </c>
       <c r="C39" s="28" t="inlineStr">
         <is>
-          <t>9:10AM</t>
+          <t>1:05PM</t>
         </is>
       </c>
       <c r="D39" s="28" t="inlineStr">
@@ -12848,17 +12792,17 @@
       </c>
       <c r="F39" s="28" t="inlineStr">
         <is>
-          <t>SF2</t>
+          <t>FINAL</t>
         </is>
       </c>
       <c r="G39" s="28" t="inlineStr">
         <is>
-          <t>Board 3</t>
+          <t>Board 2</t>
         </is>
       </c>
       <c r="H39" s="28" t="inlineStr">
         <is>
-          <t>Winner QF3</t>
+          <t>Winner SF1</t>
         </is>
       </c>
       <c r="I39" s="28" t="inlineStr">
@@ -12868,7 +12812,7 @@
       </c>
       <c r="J39" s="28" t="inlineStr">
         <is>
-          <t>Winner QF4</t>
+          <t>Winner SF2</t>
         </is>
       </c>
     </row>
@@ -12880,12 +12824,12 @@
       </c>
       <c r="B40" s="27" t="inlineStr">
         <is>
-          <t>11:30AM</t>
+          <t>12:50PM</t>
         </is>
       </c>
       <c r="C40" s="27" t="inlineStr">
         <is>
-          <t>11:45AM</t>
+          <t>1:05PM</t>
         </is>
       </c>
       <c r="D40" s="27" t="inlineStr">
@@ -12898,7 +12842,7 @@
       </c>
       <c r="F40" s="27" t="inlineStr">
         <is>
-          <t>SF1</t>
+          <t>QF2</t>
         </is>
       </c>
       <c r="G40" s="27" t="inlineStr">
@@ -12908,7 +12852,7 @@
       </c>
       <c r="H40" s="27" t="inlineStr">
         <is>
-          <t>Winner QF1</t>
+          <t>Winner M3</t>
         </is>
       </c>
       <c r="I40" s="27" t="inlineStr">
@@ -12918,7 +12862,7 @@
       </c>
       <c r="J40" s="27" t="inlineStr">
         <is>
-          <t>Winner QF2</t>
+          <t>Winner M4</t>
         </is>
       </c>
     </row>
@@ -12930,12 +12874,12 @@
       </c>
       <c r="B41" s="28" t="inlineStr">
         <is>
-          <t>3:00PM</t>
+          <t>1:05PM</t>
         </is>
       </c>
       <c r="C41" s="28" t="inlineStr">
         <is>
-          <t>3:25PM</t>
+          <t>1:20PM</t>
         </is>
       </c>
       <c r="D41" s="28" t="inlineStr">
@@ -12948,17 +12892,17 @@
       </c>
       <c r="F41" s="28" t="inlineStr">
         <is>
-          <t>FINAL</t>
+          <t>SF1</t>
         </is>
       </c>
       <c r="G41" s="28" t="inlineStr">
         <is>
-          <t>Board 2</t>
+          <t>Board 1</t>
         </is>
       </c>
       <c r="H41" s="28" t="inlineStr">
         <is>
-          <t>Winner SF1</t>
+          <t>Winner QF1</t>
         </is>
       </c>
       <c r="I41" s="28" t="inlineStr">
@@ -12968,7 +12912,7 @@
       </c>
       <c r="J41" s="28" t="inlineStr">
         <is>
-          <t>Winner SF2</t>
+          <t>Winner QF2</t>
         </is>
       </c>
     </row>
@@ -13553,12 +13497,12 @@
       </c>
       <c r="B35" s="28" t="inlineStr">
         <is>
-          <t>8:20AM</t>
+          <t>8:30AM</t>
         </is>
       </c>
       <c r="C35" s="28" t="inlineStr">
         <is>
-          <t>8:40AM</t>
+          <t>8:50AM</t>
         </is>
       </c>
       <c r="D35" s="28" t="inlineStr">
@@ -13653,12 +13597,12 @@
       </c>
       <c r="B37" s="28" t="inlineStr">
         <is>
-          <t>8:40AM</t>
+          <t>8:50AM</t>
         </is>
       </c>
       <c r="C37" s="28" t="inlineStr">
         <is>
-          <t>9:00AM</t>
+          <t>9:10AM</t>
         </is>
       </c>
       <c r="D37" s="28" t="inlineStr">
@@ -13753,12 +13697,12 @@
       </c>
       <c r="B39" s="28" t="inlineStr">
         <is>
-          <t>9:00AM</t>
+          <t>9:20AM</t>
         </is>
       </c>
       <c r="C39" s="28" t="inlineStr">
         <is>
-          <t>9:20AM</t>
+          <t>9:40AM</t>
         </is>
       </c>
       <c r="D39" s="28" t="inlineStr">
@@ -13903,12 +13847,12 @@
       </c>
       <c r="B42" s="27" t="inlineStr">
         <is>
-          <t>10:50AM</t>
+          <t>11:00AM</t>
         </is>
       </c>
       <c r="C42" s="27" t="inlineStr">
         <is>
-          <t>11:10AM</t>
+          <t>11:20AM</t>
         </is>
       </c>
       <c r="D42" s="27" t="inlineStr">
@@ -13953,12 +13897,12 @@
       </c>
       <c r="B43" s="28" t="inlineStr">
         <is>
-          <t>10:50AM</t>
+          <t>11:00AM</t>
         </is>
       </c>
       <c r="C43" s="28" t="inlineStr">
         <is>
-          <t>11:10AM</t>
+          <t>11:20AM</t>
         </is>
       </c>
       <c r="D43" s="28" t="inlineStr">
@@ -14003,12 +13947,12 @@
       </c>
       <c r="B44" s="27" t="inlineStr">
         <is>
-          <t>11:10AM</t>
+          <t>11:20AM</t>
         </is>
       </c>
       <c r="C44" s="27" t="inlineStr">
         <is>
-          <t>11:30AM</t>
+          <t>11:40AM</t>
         </is>
       </c>
       <c r="D44" s="27" t="inlineStr">
@@ -14021,17 +13965,17 @@
       </c>
       <c r="F44" s="27" t="inlineStr">
         <is>
-          <t>2639-GA-10</t>
+          <t>2639-GB-9</t>
         </is>
       </c>
       <c r="G44" s="27" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H44" s="27" t="inlineStr">
         <is>
-          <t>Suraj Kakkar</t>
+          <t>Japan Parikh</t>
         </is>
       </c>
       <c r="I44" s="27" t="inlineStr">
@@ -14041,7 +13985,7 @@
       </c>
       <c r="J44" s="27" t="inlineStr">
         <is>
-          <t>Tushar</t>
+          <t>Sudip Parui</t>
         </is>
       </c>
     </row>
@@ -14053,12 +13997,12 @@
       </c>
       <c r="B45" s="28" t="inlineStr">
         <is>
-          <t>11:10AM</t>
+          <t>11:30AM</t>
         </is>
       </c>
       <c r="C45" s="28" t="inlineStr">
         <is>
-          <t>11:30AM</t>
+          <t>11:50AM</t>
         </is>
       </c>
       <c r="D45" s="28" t="inlineStr">
@@ -14071,17 +14015,17 @@
       </c>
       <c r="F45" s="28" t="inlineStr">
         <is>
-          <t>2639-GB-9</t>
+          <t>2639-GA-10</t>
         </is>
       </c>
       <c r="G45" s="28" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H45" s="28" t="inlineStr">
         <is>
-          <t>Japan Parikh</t>
+          <t>Suraj Kakkar</t>
         </is>
       </c>
       <c r="I45" s="28" t="inlineStr">
@@ -14091,7 +14035,7 @@
       </c>
       <c r="J45" s="28" t="inlineStr">
         <is>
-          <t>Sudip Parui</t>
+          <t>Tushar</t>
         </is>
       </c>
     </row>
@@ -14103,12 +14047,12 @@
       </c>
       <c r="B46" s="27" t="inlineStr">
         <is>
-          <t>11:30AM</t>
+          <t>11:50AM</t>
         </is>
       </c>
       <c r="C46" s="27" t="inlineStr">
         <is>
-          <t>11:50AM</t>
+          <t>12:10PM</t>
         </is>
       </c>
       <c r="D46" s="27" t="inlineStr">
@@ -14153,12 +14097,12 @@
       </c>
       <c r="B47" s="28" t="inlineStr">
         <is>
-          <t>11:30AM</t>
+          <t>11:50AM</t>
         </is>
       </c>
       <c r="C47" s="28" t="inlineStr">
         <is>
-          <t>11:50AM</t>
+          <t>12:10PM</t>
         </is>
       </c>
       <c r="D47" s="28" t="inlineStr">
@@ -14203,12 +14147,12 @@
       </c>
       <c r="B48" s="27" t="inlineStr">
         <is>
-          <t>11:50AM</t>
+          <t>12:10PM</t>
         </is>
       </c>
       <c r="C48" s="27" t="inlineStr">
         <is>
-          <t>12:10PM</t>
+          <t>12:30PM</t>
         </is>
       </c>
       <c r="D48" s="27" t="inlineStr">
@@ -14253,12 +14197,12 @@
       </c>
       <c r="B49" s="28" t="inlineStr">
         <is>
-          <t>11:50AM</t>
+          <t>12:10PM</t>
         </is>
       </c>
       <c r="C49" s="28" t="inlineStr">
         <is>
-          <t>12:10PM</t>
+          <t>12:30PM</t>
         </is>
       </c>
       <c r="D49" s="28" t="inlineStr">
@@ -14303,12 +14247,12 @@
       </c>
       <c r="B50" s="27" t="inlineStr">
         <is>
-          <t>12:10PM</t>
+          <t>12:30PM</t>
         </is>
       </c>
       <c r="C50" s="27" t="inlineStr">
         <is>
-          <t>12:30PM</t>
+          <t>12:50PM</t>
         </is>
       </c>
       <c r="D50" s="27" t="inlineStr">
@@ -14321,17 +14265,17 @@
       </c>
       <c r="F50" s="27" t="inlineStr">
         <is>
-          <t>2639-GA-9</t>
+          <t>2639-GB-8</t>
         </is>
       </c>
       <c r="G50" s="27" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H50" s="27" t="inlineStr">
         <is>
-          <t>Ravi Modi</t>
+          <t>Ankur Mahante</t>
         </is>
       </c>
       <c r="I50" s="27" t="inlineStr">
@@ -14341,7 +14285,7 @@
       </c>
       <c r="J50" s="27" t="inlineStr">
         <is>
-          <t>Tej</t>
+          <t>Tanmay Sharma</t>
         </is>
       </c>
     </row>
@@ -14353,12 +14297,12 @@
       </c>
       <c r="B51" s="28" t="inlineStr">
         <is>
-          <t>12:10PM</t>
+          <t>12:40PM</t>
         </is>
       </c>
       <c r="C51" s="28" t="inlineStr">
         <is>
-          <t>12:30PM</t>
+          <t>1:00PM</t>
         </is>
       </c>
       <c r="D51" s="28" t="inlineStr">
@@ -14371,17 +14315,17 @@
       </c>
       <c r="F51" s="28" t="inlineStr">
         <is>
-          <t>2639-GB-8</t>
+          <t>2639-GA-9</t>
         </is>
       </c>
       <c r="G51" s="28" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H51" s="28" t="inlineStr">
         <is>
-          <t>Ankur Mahante</t>
+          <t>Ravi Modi</t>
         </is>
       </c>
       <c r="I51" s="28" t="inlineStr">
@@ -14391,7 +14335,7 @@
       </c>
       <c r="J51" s="28" t="inlineStr">
         <is>
-          <t>Tanmay Sharma</t>
+          <t>Tej</t>
         </is>
       </c>
     </row>
@@ -14553,12 +14497,12 @@
       </c>
       <c r="B55" s="28" t="inlineStr">
         <is>
-          <t>3:20PM</t>
+          <t>3:30PM</t>
         </is>
       </c>
       <c r="C55" s="28" t="inlineStr">
         <is>
-          <t>3:40PM</t>
+          <t>3:50PM</t>
         </is>
       </c>
       <c r="D55" s="28" t="inlineStr">
@@ -14603,12 +14547,12 @@
       </c>
       <c r="B56" s="27" t="inlineStr">
         <is>
-          <t>3:40PM</t>
+          <t>3:50PM</t>
         </is>
       </c>
       <c r="C56" s="27" t="inlineStr">
         <is>
-          <t>4:00PM</t>
+          <t>4:10PM</t>
         </is>
       </c>
       <c r="D56" s="27" t="inlineStr">
@@ -14653,12 +14597,12 @@
       </c>
       <c r="B57" s="28" t="inlineStr">
         <is>
-          <t>3:40PM</t>
+          <t>4:00PM</t>
         </is>
       </c>
       <c r="C57" s="28" t="inlineStr">
         <is>
-          <t>4:00PM</t>
+          <t>4:20PM</t>
         </is>
       </c>
       <c r="D57" s="28" t="inlineStr">
@@ -14703,12 +14647,12 @@
       </c>
       <c r="B58" s="27" t="inlineStr">
         <is>
-          <t>4:00PM</t>
+          <t>4:30PM</t>
         </is>
       </c>
       <c r="C58" s="27" t="inlineStr">
         <is>
-          <t>4:20PM</t>
+          <t>4:50PM</t>
         </is>
       </c>
       <c r="D58" s="27" t="inlineStr">
@@ -14753,12 +14697,12 @@
       </c>
       <c r="B59" s="28" t="inlineStr">
         <is>
-          <t>4:00PM</t>
+          <t>4:30PM</t>
         </is>
       </c>
       <c r="C59" s="28" t="inlineStr">
         <is>
-          <t>4:20PM</t>
+          <t>4:50PM</t>
         </is>
       </c>
       <c r="D59" s="28" t="inlineStr">
@@ -14803,12 +14747,12 @@
       </c>
       <c r="B60" s="27" t="inlineStr">
         <is>
-          <t>4:20PM</t>
+          <t>4:50PM</t>
         </is>
       </c>
       <c r="C60" s="27" t="inlineStr">
         <is>
-          <t>4:40PM</t>
+          <t>5:10PM</t>
         </is>
       </c>
       <c r="D60" s="27" t="inlineStr">
@@ -14853,12 +14797,12 @@
       </c>
       <c r="B61" s="28" t="inlineStr">
         <is>
-          <t>4:20PM</t>
+          <t>5:00PM</t>
         </is>
       </c>
       <c r="C61" s="28" t="inlineStr">
         <is>
-          <t>4:40PM</t>
+          <t>5:20PM</t>
         </is>
       </c>
       <c r="D61" s="28" t="inlineStr">
@@ -14903,17 +14847,17 @@
       </c>
       <c r="B62" s="27" t="inlineStr">
         <is>
-          <t>4:40PM</t>
+          <t>5:10PM</t>
         </is>
       </c>
       <c r="C62" s="27" t="inlineStr">
         <is>
-          <t>5:00PM</t>
+          <t>5:30PM</t>
         </is>
       </c>
       <c r="D62" s="27" t="inlineStr">
         <is>
-          <t>40 and above</t>
+          <t>Under 26</t>
         </is>
       </c>
       <c r="E62" s="27" t="n">
@@ -14921,17 +14865,17 @@
       </c>
       <c r="F62" s="27" t="inlineStr">
         <is>
-          <t>40P-GA-9</t>
+          <t>U26-GA-2</t>
         </is>
       </c>
       <c r="G62" s="27" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H62" s="27" t="inlineStr">
         <is>
-          <t>Piyush Makharia</t>
+          <t>Sankalp Bhatnagar</t>
         </is>
       </c>
       <c r="I62" s="27" t="inlineStr">
@@ -14941,7 +14885,7 @@
       </c>
       <c r="J62" s="27" t="inlineStr">
         <is>
-          <t>Amit Ranka</t>
+          <t>Rutvij sawant</t>
         </is>
       </c>
     </row>
@@ -14953,17 +14897,17 @@
       </c>
       <c r="B63" s="28" t="inlineStr">
         <is>
-          <t>4:40PM</t>
+          <t>5:20PM</t>
         </is>
       </c>
       <c r="C63" s="28" t="inlineStr">
         <is>
-          <t>5:00PM</t>
+          <t>5:40PM</t>
         </is>
       </c>
       <c r="D63" s="28" t="inlineStr">
         <is>
-          <t>Under 26</t>
+          <t>40 and above</t>
         </is>
       </c>
       <c r="E63" s="28" t="n">
@@ -14971,17 +14915,17 @@
       </c>
       <c r="F63" s="28" t="inlineStr">
         <is>
-          <t>U26-GA-2</t>
+          <t>40P-GA-9</t>
         </is>
       </c>
       <c r="G63" s="28" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H63" s="28" t="inlineStr">
         <is>
-          <t>Sankalp Bhatnagar</t>
+          <t>Piyush Makharia</t>
         </is>
       </c>
       <c r="I63" s="28" t="inlineStr">
@@ -14991,7 +14935,7 @@
       </c>
       <c r="J63" s="28" t="inlineStr">
         <is>
-          <t>Rutvij sawant</t>
+          <t>Amit Ranka</t>
         </is>
       </c>
     </row>
@@ -15003,12 +14947,12 @@
       </c>
       <c r="B64" s="27" t="inlineStr">
         <is>
-          <t>5:00PM</t>
+          <t>5:40PM</t>
         </is>
       </c>
       <c r="C64" s="27" t="inlineStr">
         <is>
-          <t>5:20PM</t>
+          <t>6:00PM</t>
         </is>
       </c>
       <c r="D64" s="27" t="inlineStr">
@@ -15053,12 +14997,12 @@
       </c>
       <c r="B65" s="28" t="inlineStr">
         <is>
-          <t>5:00PM</t>
+          <t>5:50PM</t>
         </is>
       </c>
       <c r="C65" s="28" t="inlineStr">
         <is>
-          <t>5:20PM</t>
+          <t>6:10PM</t>
         </is>
       </c>
       <c r="D65" s="28" t="inlineStr">
@@ -15103,12 +15047,12 @@
       </c>
       <c r="B66" s="27" t="inlineStr">
         <is>
-          <t>5:20PM</t>
+          <t>6:10PM</t>
         </is>
       </c>
       <c r="C66" s="27" t="inlineStr">
         <is>
-          <t>5:40PM</t>
+          <t>6:30PM</t>
         </is>
       </c>
       <c r="D66" s="27" t="inlineStr">
@@ -15153,12 +15097,12 @@
       </c>
       <c r="B67" s="28" t="inlineStr">
         <is>
-          <t>5:20PM</t>
+          <t>6:20PM</t>
         </is>
       </c>
       <c r="C67" s="28" t="inlineStr">
         <is>
-          <t>5:40PM</t>
+          <t>6:40PM</t>
         </is>
       </c>
       <c r="D67" s="28" t="inlineStr">
@@ -15203,12 +15147,12 @@
       </c>
       <c r="B68" s="27" t="inlineStr">
         <is>
-          <t>5:40PM</t>
+          <t>6:40PM</t>
         </is>
       </c>
       <c r="C68" s="27" t="inlineStr">
         <is>
-          <t>6:00PM</t>
+          <t>7:00PM</t>
         </is>
       </c>
       <c r="D68" s="27" t="inlineStr">
@@ -15253,12 +15197,12 @@
       </c>
       <c r="B69" s="28" t="inlineStr">
         <is>
-          <t>5:40PM</t>
+          <t>6:40PM</t>
         </is>
       </c>
       <c r="C69" s="28" t="inlineStr">
         <is>
-          <t>6:00PM</t>
+          <t>7:00PM</t>
         </is>
       </c>
       <c r="D69" s="28" t="inlineStr">
@@ -15303,12 +15247,12 @@
       </c>
       <c r="B70" s="27" t="inlineStr">
         <is>
-          <t>6:00PM</t>
+          <t>7:00PM</t>
         </is>
       </c>
       <c r="C70" s="27" t="inlineStr">
         <is>
-          <t>6:20PM</t>
+          <t>7:20PM</t>
         </is>
       </c>
       <c r="D70" s="27" t="inlineStr">
@@ -15353,12 +15297,12 @@
       </c>
       <c r="B71" s="28" t="inlineStr">
         <is>
-          <t>6:00PM</t>
+          <t>7:00PM</t>
         </is>
       </c>
       <c r="C71" s="28" t="inlineStr">
         <is>
-          <t>6:20PM</t>
+          <t>7:20PM</t>
         </is>
       </c>
       <c r="D71" s="28" t="inlineStr">
@@ -15403,12 +15347,12 @@
       </c>
       <c r="B72" s="27" t="inlineStr">
         <is>
-          <t>6:20PM</t>
+          <t>7:20PM</t>
         </is>
       </c>
       <c r="C72" s="27" t="inlineStr">
         <is>
-          <t>6:40PM</t>
+          <t>7:40PM</t>
         </is>
       </c>
       <c r="D72" s="27" t="inlineStr">
@@ -15453,12 +15397,12 @@
       </c>
       <c r="B73" s="28" t="inlineStr">
         <is>
-          <t>6:20PM</t>
+          <t>7:20PM</t>
         </is>
       </c>
       <c r="C73" s="28" t="inlineStr">
         <is>
-          <t>6:40PM</t>
+          <t>7:40PM</t>
         </is>
       </c>
       <c r="D73" s="28" t="inlineStr">
@@ -15503,17 +15447,17 @@
       </c>
       <c r="B74" s="27" t="inlineStr">
         <is>
-          <t>6:40PM</t>
+          <t>7:40PM</t>
         </is>
       </c>
       <c r="C74" s="27" t="inlineStr">
         <is>
-          <t>7:00PM</t>
+          <t>8:00PM</t>
         </is>
       </c>
       <c r="D74" s="27" t="inlineStr">
         <is>
-          <t>40 and above</t>
+          <t>Under 26</t>
         </is>
       </c>
       <c r="E74" s="27" t="n">
@@ -15521,17 +15465,17 @@
       </c>
       <c r="F74" s="27" t="inlineStr">
         <is>
-          <t>40P-GA-6</t>
+          <t>U26-GB-3</t>
         </is>
       </c>
       <c r="G74" s="27" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H74" s="27" t="inlineStr">
         <is>
-          <t>Piyush Makharia</t>
+          <t>Shravan Gajera</t>
         </is>
       </c>
       <c r="I74" s="27" t="inlineStr">
@@ -15541,7 +15485,7 @@
       </c>
       <c r="J74" s="27" t="inlineStr">
         <is>
-          <t>Vinit Padia</t>
+          <t>Pranit Shriyan</t>
         </is>
       </c>
     </row>
@@ -15553,17 +15497,17 @@
       </c>
       <c r="B75" s="28" t="inlineStr">
         <is>
-          <t>6:40PM</t>
+          <t>7:50PM</t>
         </is>
       </c>
       <c r="C75" s="28" t="inlineStr">
         <is>
-          <t>7:00PM</t>
+          <t>8:10PM</t>
         </is>
       </c>
       <c r="D75" s="28" t="inlineStr">
         <is>
-          <t>Under 26</t>
+          <t>40 and above</t>
         </is>
       </c>
       <c r="E75" s="28" t="n">
@@ -15571,17 +15515,17 @@
       </c>
       <c r="F75" s="28" t="inlineStr">
         <is>
-          <t>U26-GB-3</t>
+          <t>40P-GA-6</t>
         </is>
       </c>
       <c r="G75" s="28" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H75" s="28" t="inlineStr">
         <is>
-          <t>Shravan Gajera</t>
+          <t>Piyush Makharia</t>
         </is>
       </c>
       <c r="I75" s="28" t="inlineStr">
@@ -15591,7 +15535,7 @@
       </c>
       <c r="J75" s="28" t="inlineStr">
         <is>
-          <t>Pranit Shriyan</t>
+          <t>Vinit Padia</t>
         </is>
       </c>
     </row>
@@ -15603,12 +15547,12 @@
       </c>
       <c r="B76" s="27" t="inlineStr">
         <is>
-          <t>7:00PM</t>
+          <t>8:10PM</t>
         </is>
       </c>
       <c r="C76" s="27" t="inlineStr">
         <is>
-          <t>7:20PM</t>
+          <t>8:30PM</t>
         </is>
       </c>
       <c r="D76" s="27" t="inlineStr">
@@ -15653,12 +15597,12 @@
       </c>
       <c r="B77" s="28" t="inlineStr">
         <is>
-          <t>7:00PM</t>
+          <t>8:10PM</t>
         </is>
       </c>
       <c r="C77" s="28" t="inlineStr">
         <is>
-          <t>7:20PM</t>
+          <t>8:30PM</t>
         </is>
       </c>
       <c r="D77" s="28" t="inlineStr">
@@ -15703,12 +15647,12 @@
       </c>
       <c r="B78" s="27" t="inlineStr">
         <is>
-          <t>7:20PM</t>
+          <t>8:35PM</t>
         </is>
       </c>
       <c r="C78" s="27" t="inlineStr">
         <is>
-          <t>7:40PM</t>
+          <t>8:55PM</t>
         </is>
       </c>
       <c r="D78" s="27" t="inlineStr">
@@ -15753,12 +15697,12 @@
       </c>
       <c r="B79" s="28" t="inlineStr">
         <is>
-          <t>7:20PM</t>
+          <t>8:40PM</t>
         </is>
       </c>
       <c r="C79" s="28" t="inlineStr">
         <is>
-          <t>7:40PM</t>
+          <t>9:00PM</t>
         </is>
       </c>
       <c r="D79" s="28" t="inlineStr">
@@ -15798,17 +15742,17 @@
     <row r="80">
       <c r="A80" s="27" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B80" s="27" t="inlineStr">
         <is>
-          <t>7:40PM</t>
+          <t>8:00AM</t>
         </is>
       </c>
       <c r="C80" s="27" t="inlineStr">
         <is>
-          <t>8:00PM</t>
+          <t>8:20AM</t>
         </is>
       </c>
       <c r="D80" s="27" t="inlineStr">
@@ -15848,17 +15792,17 @@
     <row r="81">
       <c r="A81" s="28" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B81" s="28" t="inlineStr">
         <is>
-          <t>7:40PM</t>
+          <t>8:00AM</t>
         </is>
       </c>
       <c r="C81" s="28" t="inlineStr">
         <is>
-          <t>8:00PM</t>
+          <t>8:20AM</t>
         </is>
       </c>
       <c r="D81" s="28" t="inlineStr">
@@ -15898,17 +15842,17 @@
     <row r="82">
       <c r="A82" s="27" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B82" s="27" t="inlineStr">
         <is>
-          <t>8:00PM</t>
+          <t>8:30AM</t>
         </is>
       </c>
       <c r="C82" s="27" t="inlineStr">
         <is>
-          <t>8:20PM</t>
+          <t>8:50AM</t>
         </is>
       </c>
       <c r="D82" s="27" t="inlineStr">
@@ -15948,17 +15892,17 @@
     <row r="83">
       <c r="A83" s="28" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B83" s="28" t="inlineStr">
         <is>
-          <t>8:15PM</t>
+          <t>8:45AM</t>
         </is>
       </c>
       <c r="C83" s="28" t="inlineStr">
         <is>
-          <t>8:35PM</t>
+          <t>9:05AM</t>
         </is>
       </c>
       <c r="D83" s="28" t="inlineStr">
@@ -15998,17 +15942,17 @@
     <row r="84">
       <c r="A84" s="27" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B84" s="27" t="inlineStr">
         <is>
-          <t>8:35PM</t>
+          <t>11:50AM</t>
         </is>
       </c>
       <c r="C84" s="27" t="inlineStr">
         <is>
-          <t>8:55PM</t>
+          <t>12:10PM</t>
         </is>
       </c>
       <c r="D84" s="27" t="inlineStr">
@@ -16048,17 +15992,17 @@
     <row r="85">
       <c r="A85" s="28" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B85" s="28" t="inlineStr">
         <is>
-          <t>8:35PM</t>
+          <t>11:50AM</t>
         </is>
       </c>
       <c r="C85" s="28" t="inlineStr">
         <is>
-          <t>8:55PM</t>
+          <t>12:10PM</t>
         </is>
       </c>
       <c r="D85" s="28" t="inlineStr">
@@ -16098,17 +16042,17 @@
     <row r="86">
       <c r="A86" s="27" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B86" s="27" t="inlineStr">
         <is>
-          <t>9:00PM</t>
+          <t>12:10PM</t>
         </is>
       </c>
       <c r="C86" s="27" t="inlineStr">
         <is>
-          <t>9:20PM</t>
+          <t>12:30PM</t>
         </is>
       </c>
       <c r="D86" s="27" t="inlineStr">
@@ -16148,17 +16092,17 @@
     <row r="87">
       <c r="A87" s="28" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B87" s="28" t="inlineStr">
         <is>
-          <t>9:00PM</t>
+          <t>12:10PM</t>
         </is>
       </c>
       <c r="C87" s="28" t="inlineStr">
         <is>
-          <t>9:20PM</t>
+          <t>12:30PM</t>
         </is>
       </c>
       <c r="D87" s="28" t="inlineStr">
@@ -16198,17 +16142,17 @@
     <row r="88">
       <c r="A88" s="27" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B88" s="27" t="inlineStr">
         <is>
-          <t>9:20PM</t>
+          <t>12:30PM</t>
         </is>
       </c>
       <c r="C88" s="27" t="inlineStr">
         <is>
-          <t>9:55PM</t>
+          <t>12:50PM</t>
         </is>
       </c>
       <c r="D88" s="27" t="inlineStr">
@@ -16253,12 +16197,12 @@
       </c>
       <c r="B89" s="28" t="inlineStr">
         <is>
-          <t>8:00AM</t>
+          <t>12:30PM</t>
         </is>
       </c>
       <c r="C89" s="28" t="inlineStr">
         <is>
-          <t>8:20AM</t>
+          <t>12:50PM</t>
         </is>
       </c>
       <c r="D89" s="28" t="inlineStr">
@@ -16271,17 +16215,17 @@
       </c>
       <c r="F89" s="28" t="inlineStr">
         <is>
-          <t>40P-SF1</t>
+          <t>40P-SF2</t>
         </is>
       </c>
       <c r="G89" s="28" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H89" s="28" t="inlineStr">
         <is>
-          <t>Group A 1st</t>
+          <t>Group B 1st</t>
         </is>
       </c>
       <c r="I89" s="28" t="inlineStr">
@@ -16291,7 +16235,7 @@
       </c>
       <c r="J89" s="28" t="inlineStr">
         <is>
-          <t>Group B 2nd</t>
+          <t>Group A 2nd</t>
         </is>
       </c>
     </row>
@@ -16303,12 +16247,12 @@
       </c>
       <c r="B90" s="27" t="inlineStr">
         <is>
-          <t>8:00AM</t>
+          <t>12:50PM</t>
         </is>
       </c>
       <c r="C90" s="27" t="inlineStr">
         <is>
-          <t>8:20AM</t>
+          <t>1:10PM</t>
         </is>
       </c>
       <c r="D90" s="27" t="inlineStr">
@@ -16321,17 +16265,17 @@
       </c>
       <c r="F90" s="27" t="inlineStr">
         <is>
-          <t>40P-SF2</t>
+          <t>40P-SF1</t>
         </is>
       </c>
       <c r="G90" s="27" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H90" s="27" t="inlineStr">
         <is>
-          <t>Group B 1st</t>
+          <t>Group A 1st</t>
         </is>
       </c>
       <c r="I90" s="27" t="inlineStr">
@@ -16341,7 +16285,7 @@
       </c>
       <c r="J90" s="27" t="inlineStr">
         <is>
-          <t>Group A 2nd</t>
+          <t>Group B 2nd</t>
         </is>
       </c>
     </row>
@@ -16353,17 +16297,17 @@
       </c>
       <c r="B91" s="28" t="inlineStr">
         <is>
-          <t>8:20AM</t>
+          <t>12:50PM</t>
         </is>
       </c>
       <c r="C91" s="28" t="inlineStr">
         <is>
-          <t>8:55AM</t>
+          <t>1:10PM</t>
         </is>
       </c>
       <c r="D91" s="28" t="inlineStr">
         <is>
-          <t>40 and above</t>
+          <t>Under 26</t>
         </is>
       </c>
       <c r="E91" s="28" t="n">
@@ -16371,12 +16315,12 @@
       </c>
       <c r="F91" s="28" t="inlineStr">
         <is>
-          <t>40P-FINAL</t>
+          <t>U26-FINAL</t>
         </is>
       </c>
       <c r="G91" s="28" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H91" s="28" t="inlineStr">
@@ -16403,17 +16347,17 @@
       </c>
       <c r="B92" s="27" t="inlineStr">
         <is>
-          <t>10:15AM</t>
+          <t>1:10PM</t>
         </is>
       </c>
       <c r="C92" s="27" t="inlineStr">
         <is>
-          <t>10:50AM</t>
+          <t>1:30PM</t>
         </is>
       </c>
       <c r="D92" s="27" t="inlineStr">
         <is>
-          <t>Under 26</t>
+          <t>40 and above</t>
         </is>
       </c>
       <c r="E92" s="27" t="n">
@@ -16421,12 +16365,12 @@
       </c>
       <c r="F92" s="27" t="inlineStr">
         <is>
-          <t>U26-FINAL</t>
+          <t>40P-FINAL</t>
         </is>
       </c>
       <c r="G92" s="27" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H92" s="27" t="inlineStr">
@@ -17229,12 +17173,12 @@
       </c>
       <c r="B45" s="27" t="inlineStr">
         <is>
-          <t>8:20AM</t>
+          <t>8:30AM</t>
         </is>
       </c>
       <c r="C45" s="27" t="inlineStr">
         <is>
-          <t>8:40AM</t>
+          <t>8:50AM</t>
         </is>
       </c>
       <c r="D45" s="27" t="inlineStr">
@@ -17279,12 +17223,12 @@
       </c>
       <c r="B46" s="28" t="inlineStr">
         <is>
-          <t>8:20AM</t>
+          <t>8:30AM</t>
         </is>
       </c>
       <c r="C46" s="28" t="inlineStr">
         <is>
-          <t>8:40AM</t>
+          <t>8:50AM</t>
         </is>
       </c>
       <c r="D46" s="28" t="inlineStr">
@@ -17329,12 +17273,12 @@
       </c>
       <c r="B47" s="27" t="inlineStr">
         <is>
-          <t>8:40AM</t>
+          <t>8:50AM</t>
         </is>
       </c>
       <c r="C47" s="27" t="inlineStr">
         <is>
-          <t>9:00AM</t>
+          <t>9:10AM</t>
         </is>
       </c>
       <c r="D47" s="27" t="inlineStr">
@@ -17379,12 +17323,12 @@
       </c>
       <c r="B48" s="28" t="inlineStr">
         <is>
-          <t>8:40AM</t>
+          <t>9:00AM</t>
         </is>
       </c>
       <c r="C48" s="28" t="inlineStr">
         <is>
-          <t>9:00AM</t>
+          <t>9:20AM</t>
         </is>
       </c>
       <c r="D48" s="28" t="inlineStr">
@@ -17429,12 +17373,12 @@
       </c>
       <c r="B49" s="27" t="inlineStr">
         <is>
-          <t>9:00AM</t>
+          <t>9:10AM</t>
         </is>
       </c>
       <c r="C49" s="27" t="inlineStr">
         <is>
-          <t>9:20AM</t>
+          <t>9:30AM</t>
         </is>
       </c>
       <c r="D49" s="27" t="inlineStr">
@@ -17479,12 +17423,12 @@
       </c>
       <c r="B50" s="28" t="inlineStr">
         <is>
-          <t>9:00AM</t>
+          <t>9:30AM</t>
         </is>
       </c>
       <c r="C50" s="28" t="inlineStr">
         <is>
-          <t>9:20AM</t>
+          <t>9:50AM</t>
         </is>
       </c>
       <c r="D50" s="28" t="inlineStr">
@@ -17679,12 +17623,12 @@
       </c>
       <c r="B54" s="28" t="inlineStr">
         <is>
-          <t>10:50AM</t>
+          <t>11:00AM</t>
         </is>
       </c>
       <c r="C54" s="28" t="inlineStr">
         <is>
-          <t>11:10AM</t>
+          <t>11:20AM</t>
         </is>
       </c>
       <c r="D54" s="28" t="inlineStr">
@@ -17729,12 +17673,12 @@
       </c>
       <c r="B55" s="27" t="inlineStr">
         <is>
-          <t>11:10AM</t>
+          <t>11:20AM</t>
         </is>
       </c>
       <c r="C55" s="27" t="inlineStr">
         <is>
-          <t>11:30AM</t>
+          <t>11:40AM</t>
         </is>
       </c>
       <c r="D55" s="27" t="inlineStr">
@@ -17779,12 +17723,12 @@
       </c>
       <c r="B56" s="28" t="inlineStr">
         <is>
-          <t>11:10AM</t>
+          <t>11:20AM</t>
         </is>
       </c>
       <c r="C56" s="28" t="inlineStr">
         <is>
-          <t>11:30AM</t>
+          <t>11:40AM</t>
         </is>
       </c>
       <c r="D56" s="28" t="inlineStr">
@@ -17829,12 +17773,12 @@
       </c>
       <c r="B57" s="27" t="inlineStr">
         <is>
-          <t>11:30AM</t>
+          <t>11:50AM</t>
         </is>
       </c>
       <c r="C57" s="27" t="inlineStr">
         <is>
-          <t>11:50AM</t>
+          <t>12:10PM</t>
         </is>
       </c>
       <c r="D57" s="27" t="inlineStr">
@@ -17879,12 +17823,12 @@
       </c>
       <c r="B58" s="28" t="inlineStr">
         <is>
-          <t>11:30AM</t>
+          <t>11:50AM</t>
         </is>
       </c>
       <c r="C58" s="28" t="inlineStr">
         <is>
-          <t>11:50AM</t>
+          <t>12:10PM</t>
         </is>
       </c>
       <c r="D58" s="28" t="inlineStr">
@@ -17929,12 +17873,12 @@
       </c>
       <c r="B59" s="27" t="inlineStr">
         <is>
-          <t>11:50AM</t>
+          <t>12:10PM</t>
         </is>
       </c>
       <c r="C59" s="27" t="inlineStr">
         <is>
-          <t>12:10PM</t>
+          <t>12:30PM</t>
         </is>
       </c>
       <c r="D59" s="27" t="inlineStr">
@@ -17979,12 +17923,12 @@
       </c>
       <c r="B60" s="28" t="inlineStr">
         <is>
-          <t>11:50AM</t>
+          <t>12:10PM</t>
         </is>
       </c>
       <c r="C60" s="28" t="inlineStr">
         <is>
-          <t>12:10PM</t>
+          <t>12:30PM</t>
         </is>
       </c>
       <c r="D60" s="28" t="inlineStr">
@@ -18029,12 +17973,12 @@
       </c>
       <c r="B61" s="27" t="inlineStr">
         <is>
-          <t>12:10PM</t>
+          <t>12:40PM</t>
         </is>
       </c>
       <c r="C61" s="27" t="inlineStr">
         <is>
-          <t>12:30PM</t>
+          <t>1:00PM</t>
         </is>
       </c>
       <c r="D61" s="27" t="inlineStr">
@@ -18079,12 +18023,12 @@
       </c>
       <c r="B62" s="28" t="inlineStr">
         <is>
-          <t>12:10PM</t>
+          <t>12:40PM</t>
         </is>
       </c>
       <c r="C62" s="28" t="inlineStr">
         <is>
-          <t>12:30PM</t>
+          <t>1:00PM</t>
         </is>
       </c>
       <c r="D62" s="28" t="inlineStr">
@@ -18247,17 +18191,17 @@
       </c>
       <c r="F65" s="27" t="inlineStr">
         <is>
-          <t>2140-2b</t>
+          <t>2140-3b</t>
         </is>
       </c>
       <c r="G65" s="27" t="inlineStr">
         <is>
-          <t>Board 1</t>
+          <t>Board 2</t>
         </is>
       </c>
       <c r="H65" s="27" t="inlineStr">
         <is>
-          <t>Tejas doshi</t>
+          <t>Tej</t>
         </is>
       </c>
       <c r="I65" s="27" t="inlineStr">
@@ -18267,7 +18211,7 @@
       </c>
       <c r="J65" s="27" t="inlineStr">
         <is>
-          <t>Nikunj Jhala</t>
+          <t>Swati Tripathi</t>
         </is>
       </c>
     </row>
@@ -18279,12 +18223,12 @@
       </c>
       <c r="B66" s="28" t="inlineStr">
         <is>
-          <t>3:20PM</t>
+          <t>3:30PM</t>
         </is>
       </c>
       <c r="C66" s="28" t="inlineStr">
         <is>
-          <t>3:40PM</t>
+          <t>3:50PM</t>
         </is>
       </c>
       <c r="D66" s="28" t="inlineStr">
@@ -18297,17 +18241,17 @@
       </c>
       <c r="F66" s="28" t="inlineStr">
         <is>
-          <t>2140-3b</t>
+          <t>2140-2b</t>
         </is>
       </c>
       <c r="G66" s="28" t="inlineStr">
         <is>
-          <t>Board 2</t>
+          <t>Board 1</t>
         </is>
       </c>
       <c r="H66" s="28" t="inlineStr">
         <is>
-          <t>Tej</t>
+          <t>Tejas doshi</t>
         </is>
       </c>
       <c r="I66" s="28" t="inlineStr">
@@ -18317,7 +18261,7 @@
       </c>
       <c r="J66" s="28" t="inlineStr">
         <is>
-          <t>Swati Tripathi</t>
+          <t>Nikunj Jhala</t>
         </is>
       </c>
     </row>
@@ -18329,12 +18273,12 @@
       </c>
       <c r="B67" s="27" t="inlineStr">
         <is>
-          <t>3:40PM</t>
+          <t>3:50PM</t>
         </is>
       </c>
       <c r="C67" s="27" t="inlineStr">
         <is>
-          <t>4:00PM</t>
+          <t>4:10PM</t>
         </is>
       </c>
       <c r="D67" s="27" t="inlineStr">
@@ -18347,17 +18291,17 @@
       </c>
       <c r="F67" s="27" t="inlineStr">
         <is>
-          <t>2140-4</t>
+          <t>2140-5</t>
         </is>
       </c>
       <c r="G67" s="27" t="inlineStr">
         <is>
-          <t>Board 1</t>
+          <t>Board 2</t>
         </is>
       </c>
       <c r="H67" s="27" t="inlineStr">
         <is>
-          <t>Amit Nawandhar</t>
+          <t>Rahul Garg</t>
         </is>
       </c>
       <c r="I67" s="27" t="inlineStr">
@@ -18367,7 +18311,7 @@
       </c>
       <c r="J67" s="27" t="inlineStr">
         <is>
-          <t>Nikunj Jhala</t>
+          <t>Tej</t>
         </is>
       </c>
     </row>
@@ -18379,12 +18323,12 @@
       </c>
       <c r="B68" s="28" t="inlineStr">
         <is>
-          <t>3:40PM</t>
+          <t>4:00PM</t>
         </is>
       </c>
       <c r="C68" s="28" t="inlineStr">
         <is>
-          <t>4:00PM</t>
+          <t>4:20PM</t>
         </is>
       </c>
       <c r="D68" s="28" t="inlineStr">
@@ -18397,17 +18341,17 @@
       </c>
       <c r="F68" s="28" t="inlineStr">
         <is>
-          <t>2140-5</t>
+          <t>2140-4</t>
         </is>
       </c>
       <c r="G68" s="28" t="inlineStr">
         <is>
-          <t>Board 2</t>
+          <t>Board 1</t>
         </is>
       </c>
       <c r="H68" s="28" t="inlineStr">
         <is>
-          <t>Rahul Garg</t>
+          <t>Amit Nawandhar</t>
         </is>
       </c>
       <c r="I68" s="28" t="inlineStr">
@@ -18417,7 +18361,7 @@
       </c>
       <c r="J68" s="28" t="inlineStr">
         <is>
-          <t>Tej</t>
+          <t>Nikunj Jhala</t>
         </is>
       </c>
     </row>
@@ -18429,17 +18373,17 @@
       </c>
       <c r="B69" s="27" t="inlineStr">
         <is>
-          <t>4:00PM</t>
+          <t>4:10PM</t>
         </is>
       </c>
       <c r="C69" s="27" t="inlineStr">
         <is>
-          <t>4:20PM</t>
+          <t>4:30PM</t>
         </is>
       </c>
       <c r="D69" s="27" t="inlineStr">
         <is>
-          <t>21 to 40</t>
+          <t>41 and above</t>
         </is>
       </c>
       <c r="E69" s="27" t="n">
@@ -18447,17 +18391,17 @@
       </c>
       <c r="F69" s="27" t="inlineStr">
         <is>
-          <t>2140-5b</t>
+          <t>41P-1</t>
         </is>
       </c>
       <c r="G69" s="27" t="inlineStr">
         <is>
-          <t>Board 1</t>
+          <t>Board 2</t>
         </is>
       </c>
       <c r="H69" s="27" t="inlineStr">
         <is>
-          <t>Swati Tripathi</t>
+          <t>Piyush Makharia</t>
         </is>
       </c>
       <c r="I69" s="27" t="inlineStr">
@@ -18467,7 +18411,7 @@
       </c>
       <c r="J69" s="27" t="inlineStr">
         <is>
-          <t>Nikunj Jhala</t>
+          <t>Ajit nair</t>
         </is>
       </c>
     </row>
@@ -18479,17 +18423,17 @@
       </c>
       <c r="B70" s="28" t="inlineStr">
         <is>
-          <t>4:00PM</t>
+          <t>4:30PM</t>
         </is>
       </c>
       <c r="C70" s="28" t="inlineStr">
         <is>
-          <t>4:20PM</t>
+          <t>4:50PM</t>
         </is>
       </c>
       <c r="D70" s="28" t="inlineStr">
         <is>
-          <t>41 and above</t>
+          <t>21 to 40</t>
         </is>
       </c>
       <c r="E70" s="28" t="n">
@@ -18497,17 +18441,17 @@
       </c>
       <c r="F70" s="28" t="inlineStr">
         <is>
-          <t>41P-1</t>
+          <t>2140-5b</t>
         </is>
       </c>
       <c r="G70" s="28" t="inlineStr">
         <is>
-          <t>Board 2</t>
+          <t>Board 1</t>
         </is>
       </c>
       <c r="H70" s="28" t="inlineStr">
         <is>
-          <t>Piyush Makharia</t>
+          <t>Swati Tripathi</t>
         </is>
       </c>
       <c r="I70" s="28" t="inlineStr">
@@ -18517,7 +18461,7 @@
       </c>
       <c r="J70" s="28" t="inlineStr">
         <is>
-          <t>Ajit nair</t>
+          <t>Nikunj Jhala</t>
         </is>
       </c>
     </row>
@@ -18529,12 +18473,12 @@
       </c>
       <c r="B71" s="27" t="inlineStr">
         <is>
-          <t>4:20PM</t>
+          <t>4:50PM</t>
         </is>
       </c>
       <c r="C71" s="27" t="inlineStr">
         <is>
-          <t>4:40PM</t>
+          <t>5:10PM</t>
         </is>
       </c>
       <c r="D71" s="27" t="inlineStr">
@@ -18579,12 +18523,12 @@
       </c>
       <c r="B72" s="28" t="inlineStr">
         <is>
-          <t>4:20PM</t>
+          <t>5:00PM</t>
         </is>
       </c>
       <c r="C72" s="28" t="inlineStr">
         <is>
-          <t>4:40PM</t>
+          <t>5:20PM</t>
         </is>
       </c>
       <c r="D72" s="28" t="inlineStr">
@@ -18629,12 +18573,12 @@
       </c>
       <c r="B73" s="27" t="inlineStr">
         <is>
-          <t>4:40PM</t>
+          <t>5:20PM</t>
         </is>
       </c>
       <c r="C73" s="27" t="inlineStr">
         <is>
-          <t>5:00PM</t>
+          <t>5:40PM</t>
         </is>
       </c>
       <c r="D73" s="27" t="inlineStr">
@@ -18679,12 +18623,12 @@
       </c>
       <c r="B74" s="28" t="inlineStr">
         <is>
-          <t>4:40PM</t>
+          <t>5:20PM</t>
         </is>
       </c>
       <c r="C74" s="28" t="inlineStr">
         <is>
-          <t>5:00PM</t>
+          <t>5:40PM</t>
         </is>
       </c>
       <c r="D74" s="28" t="inlineStr">
@@ -18729,12 +18673,12 @@
       </c>
       <c r="B75" s="27" t="inlineStr">
         <is>
-          <t>5:00PM</t>
+          <t>5:40PM</t>
         </is>
       </c>
       <c r="C75" s="27" t="inlineStr">
         <is>
-          <t>5:20PM</t>
+          <t>6:00PM</t>
         </is>
       </c>
       <c r="D75" s="27" t="inlineStr">
@@ -18779,17 +18723,17 @@
       </c>
       <c r="B76" s="28" t="inlineStr">
         <is>
-          <t>5:00PM</t>
+          <t>6:10PM</t>
         </is>
       </c>
       <c r="C76" s="28" t="inlineStr">
         <is>
-          <t>5:35PM</t>
+          <t>6:30PM</t>
         </is>
       </c>
       <c r="D76" s="28" t="inlineStr">
         <is>
-          <t>Under 11</t>
+          <t>41 and above</t>
         </is>
       </c>
       <c r="E76" s="28" t="n">
@@ -18797,17 +18741,17 @@
       </c>
       <c r="F76" s="28" t="inlineStr">
         <is>
-          <t>U11-FINAL</t>
+          <t>41P-4</t>
         </is>
       </c>
       <c r="G76" s="28" t="inlineStr">
         <is>
-          <t>Board 2</t>
+          <t>Board 1</t>
         </is>
       </c>
       <c r="H76" s="28" t="inlineStr">
         <is>
-          <t>Pool 1st</t>
+          <t>Piyush Makharia</t>
         </is>
       </c>
       <c r="I76" s="28" t="inlineStr">
@@ -18817,7 +18761,7 @@
       </c>
       <c r="J76" s="28" t="inlineStr">
         <is>
-          <t>Pool 2nd</t>
+          <t>Sanjay Kumar</t>
         </is>
       </c>
     </row>
@@ -18829,12 +18773,12 @@
       </c>
       <c r="B77" s="27" t="inlineStr">
         <is>
-          <t>5:20PM</t>
+          <t>6:10PM</t>
         </is>
       </c>
       <c r="C77" s="27" t="inlineStr">
         <is>
-          <t>5:40PM</t>
+          <t>6:30PM</t>
         </is>
       </c>
       <c r="D77" s="27" t="inlineStr">
@@ -18847,17 +18791,17 @@
       </c>
       <c r="F77" s="27" t="inlineStr">
         <is>
-          <t>41P-4</t>
+          <t>41P-5</t>
         </is>
       </c>
       <c r="G77" s="27" t="inlineStr">
         <is>
-          <t>Board 1</t>
+          <t>Board 2</t>
         </is>
       </c>
       <c r="H77" s="27" t="inlineStr">
         <is>
-          <t>Piyush Makharia</t>
+          <t>Prasad Akshintala</t>
         </is>
       </c>
       <c r="I77" s="27" t="inlineStr">
@@ -18867,7 +18811,7 @@
       </c>
       <c r="J77" s="27" t="inlineStr">
         <is>
-          <t>Sanjay Kumar</t>
+          <t>Ajit nair</t>
         </is>
       </c>
     </row>
@@ -18879,17 +18823,17 @@
       </c>
       <c r="B78" s="28" t="inlineStr">
         <is>
-          <t>5:35PM</t>
+          <t>6:30PM</t>
         </is>
       </c>
       <c r="C78" s="28" t="inlineStr">
         <is>
-          <t>5:55PM</t>
+          <t>6:50PM</t>
         </is>
       </c>
       <c r="D78" s="28" t="inlineStr">
         <is>
-          <t>41 and above</t>
+          <t>21 to 40</t>
         </is>
       </c>
       <c r="E78" s="28" t="n">
@@ -18897,17 +18841,17 @@
       </c>
       <c r="F78" s="28" t="inlineStr">
         <is>
-          <t>41P-5</t>
+          <t>2140-6b</t>
         </is>
       </c>
       <c r="G78" s="28" t="inlineStr">
         <is>
-          <t>Board 2</t>
+          <t>Board 1</t>
         </is>
       </c>
       <c r="H78" s="28" t="inlineStr">
         <is>
-          <t>Prasad Akshintala</t>
+          <t>Rahul Garg</t>
         </is>
       </c>
       <c r="I78" s="28" t="inlineStr">
@@ -18917,7 +18861,7 @@
       </c>
       <c r="J78" s="28" t="inlineStr">
         <is>
-          <t>Ajit nair</t>
+          <t>Tejas doshi</t>
         </is>
       </c>
     </row>
@@ -18929,17 +18873,17 @@
       </c>
       <c r="B79" s="27" t="inlineStr">
         <is>
-          <t>5:40PM</t>
+          <t>6:55PM</t>
         </is>
       </c>
       <c r="C79" s="27" t="inlineStr">
         <is>
-          <t>6:15PM</t>
+          <t>7:15PM</t>
         </is>
       </c>
       <c r="D79" s="27" t="inlineStr">
         <is>
-          <t>12 to 20</t>
+          <t>41 and above</t>
         </is>
       </c>
       <c r="E79" s="27" t="n">
@@ -18947,17 +18891,17 @@
       </c>
       <c r="F79" s="27" t="inlineStr">
         <is>
-          <t>1220-FINAL</t>
+          <t>41P-6</t>
         </is>
       </c>
       <c r="G79" s="27" t="inlineStr">
         <is>
-          <t>Board 1</t>
+          <t>Board 2</t>
         </is>
       </c>
       <c r="H79" s="27" t="inlineStr">
         <is>
-          <t>Pool 1st</t>
+          <t>Piyush Makharia</t>
         </is>
       </c>
       <c r="I79" s="27" t="inlineStr">
@@ -18967,7 +18911,7 @@
       </c>
       <c r="J79" s="27" t="inlineStr">
         <is>
-          <t>Pool 2nd</t>
+          <t>Adil Khan</t>
         </is>
       </c>
     </row>
@@ -18979,12 +18923,12 @@
       </c>
       <c r="B80" s="28" t="inlineStr">
         <is>
-          <t>5:55PM</t>
+          <t>7:25PM</t>
         </is>
       </c>
       <c r="C80" s="28" t="inlineStr">
         <is>
-          <t>6:15PM</t>
+          <t>7:45PM</t>
         </is>
       </c>
       <c r="D80" s="28" t="inlineStr">
@@ -18997,7 +18941,7 @@
       </c>
       <c r="F80" s="28" t="inlineStr">
         <is>
-          <t>41P-6</t>
+          <t>41P-7</t>
         </is>
       </c>
       <c r="G80" s="28" t="inlineStr">
@@ -19017,7 +18961,7 @@
       </c>
       <c r="J80" s="28" t="inlineStr">
         <is>
-          <t>Adil Khan</t>
+          <t>Sachin Malgadnkar</t>
         </is>
       </c>
     </row>
@@ -19029,17 +18973,17 @@
       </c>
       <c r="B81" s="27" t="inlineStr">
         <is>
-          <t>6:15PM</t>
+          <t>7:45PM</t>
         </is>
       </c>
       <c r="C81" s="27" t="inlineStr">
         <is>
-          <t>6:35PM</t>
+          <t>8:05PM</t>
         </is>
       </c>
       <c r="D81" s="27" t="inlineStr">
         <is>
-          <t>21 to 40</t>
+          <t>41 and above</t>
         </is>
       </c>
       <c r="E81" s="27" t="n">
@@ -19047,17 +18991,17 @@
       </c>
       <c r="F81" s="27" t="inlineStr">
         <is>
-          <t>2140-6b</t>
+          <t>41P-8</t>
         </is>
       </c>
       <c r="G81" s="27" t="inlineStr">
         <is>
-          <t>Board 1</t>
+          <t>Board 2</t>
         </is>
       </c>
       <c r="H81" s="27" t="inlineStr">
         <is>
-          <t>Rahul Garg</t>
+          <t>Prasad Akshintala</t>
         </is>
       </c>
       <c r="I81" s="27" t="inlineStr">
@@ -19067,7 +19011,7 @@
       </c>
       <c r="J81" s="27" t="inlineStr">
         <is>
-          <t>Tejas doshi</t>
+          <t>Sanjay Kumar</t>
         </is>
       </c>
     </row>
@@ -19079,12 +19023,12 @@
       </c>
       <c r="B82" s="28" t="inlineStr">
         <is>
-          <t>6:15PM</t>
+          <t>8:30PM</t>
         </is>
       </c>
       <c r="C82" s="28" t="inlineStr">
         <is>
-          <t>6:35PM</t>
+          <t>8:50PM</t>
         </is>
       </c>
       <c r="D82" s="28" t="inlineStr">
@@ -19097,7 +19041,7 @@
       </c>
       <c r="F82" s="28" t="inlineStr">
         <is>
-          <t>41P-7</t>
+          <t>41P-9</t>
         </is>
       </c>
       <c r="G82" s="28" t="inlineStr">
@@ -19107,7 +19051,7 @@
       </c>
       <c r="H82" s="28" t="inlineStr">
         <is>
-          <t>Piyush Makharia</t>
+          <t>Adil Khan</t>
         </is>
       </c>
       <c r="I82" s="28" t="inlineStr">
@@ -19117,29 +19061,29 @@
       </c>
       <c r="J82" s="28" t="inlineStr">
         <is>
-          <t>Sachin Malgadnkar</t>
+          <t>Sanjay Kumar</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="27" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B83" s="27" t="inlineStr">
         <is>
-          <t>6:35PM</t>
+          <t>8:00AM</t>
         </is>
       </c>
       <c r="C83" s="27" t="inlineStr">
         <is>
-          <t>7:10PM</t>
+          <t>8:20AM</t>
         </is>
       </c>
       <c r="D83" s="27" t="inlineStr">
         <is>
-          <t>21 to 40</t>
+          <t>41 and above</t>
         </is>
       </c>
       <c r="E83" s="27" t="n">
@@ -19147,7 +19091,7 @@
       </c>
       <c r="F83" s="27" t="inlineStr">
         <is>
-          <t>2140-FINAL</t>
+          <t>41P-10</t>
         </is>
       </c>
       <c r="G83" s="27" t="inlineStr">
@@ -19157,7 +19101,7 @@
       </c>
       <c r="H83" s="27" t="inlineStr">
         <is>
-          <t>Pool 1st</t>
+          <t>Adil Khan</t>
         </is>
       </c>
       <c r="I83" s="27" t="inlineStr">
@@ -19167,24 +19111,24 @@
       </c>
       <c r="J83" s="27" t="inlineStr">
         <is>
-          <t>Pool 2nd</t>
+          <t>Prasad Akshintala</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="28" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B84" s="28" t="inlineStr">
         <is>
-          <t>6:35PM</t>
+          <t>8:00AM</t>
         </is>
       </c>
       <c r="C84" s="28" t="inlineStr">
         <is>
-          <t>6:55PM</t>
+          <t>8:20AM</t>
         </is>
       </c>
       <c r="D84" s="28" t="inlineStr">
@@ -19197,7 +19141,7 @@
       </c>
       <c r="F84" s="28" t="inlineStr">
         <is>
-          <t>41P-8</t>
+          <t>41P-11</t>
         </is>
       </c>
       <c r="G84" s="28" t="inlineStr">
@@ -19207,7 +19151,7 @@
       </c>
       <c r="H84" s="28" t="inlineStr">
         <is>
-          <t>Prasad Akshintala</t>
+          <t>Sachin Malgadnkar</t>
         </is>
       </c>
       <c r="I84" s="28" t="inlineStr">
@@ -19224,17 +19168,17 @@
     <row r="85">
       <c r="A85" s="27" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B85" s="27" t="inlineStr">
         <is>
-          <t>7:00PM</t>
+          <t>8:30AM</t>
         </is>
       </c>
       <c r="C85" s="27" t="inlineStr">
         <is>
-          <t>7:20PM</t>
+          <t>8:50AM</t>
         </is>
       </c>
       <c r="D85" s="27" t="inlineStr">
@@ -19247,12 +19191,12 @@
       </c>
       <c r="F85" s="27" t="inlineStr">
         <is>
-          <t>41P-9</t>
+          <t>41P-12</t>
         </is>
       </c>
       <c r="G85" s="27" t="inlineStr">
         <is>
-          <t>Board 2</t>
+          <t>Board 1</t>
         </is>
       </c>
       <c r="H85" s="27" t="inlineStr">
@@ -19267,24 +19211,24 @@
       </c>
       <c r="J85" s="27" t="inlineStr">
         <is>
-          <t>Sanjay Kumar</t>
+          <t>Ajit nair</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="28" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B86" s="28" t="inlineStr">
         <is>
-          <t>7:20PM</t>
+          <t>8:30AM</t>
         </is>
       </c>
       <c r="C86" s="28" t="inlineStr">
         <is>
-          <t>7:40PM</t>
+          <t>8:50AM</t>
         </is>
       </c>
       <c r="D86" s="28" t="inlineStr">
@@ -19297,17 +19241,17 @@
       </c>
       <c r="F86" s="28" t="inlineStr">
         <is>
-          <t>41P-10</t>
+          <t>41P-13</t>
         </is>
       </c>
       <c r="G86" s="28" t="inlineStr">
         <is>
-          <t>Board 1</t>
+          <t>Board 2</t>
         </is>
       </c>
       <c r="H86" s="28" t="inlineStr">
         <is>
-          <t>Adil Khan</t>
+          <t>Sachin Malgadnkar</t>
         </is>
       </c>
       <c r="I86" s="28" t="inlineStr">
@@ -19324,17 +19268,17 @@
     <row r="87">
       <c r="A87" s="27" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B87" s="27" t="inlineStr">
         <is>
-          <t>7:20PM</t>
+          <t>8:50AM</t>
         </is>
       </c>
       <c r="C87" s="27" t="inlineStr">
         <is>
-          <t>7:40PM</t>
+          <t>9:10AM</t>
         </is>
       </c>
       <c r="D87" s="27" t="inlineStr">
@@ -19347,7 +19291,7 @@
       </c>
       <c r="F87" s="27" t="inlineStr">
         <is>
-          <t>41P-11</t>
+          <t>41P-15</t>
         </is>
       </c>
       <c r="G87" s="27" t="inlineStr">
@@ -19357,7 +19301,7 @@
       </c>
       <c r="H87" s="27" t="inlineStr">
         <is>
-          <t>Sachin Malgadnkar</t>
+          <t>Sanjay Kumar</t>
         </is>
       </c>
       <c r="I87" s="27" t="inlineStr">
@@ -19367,24 +19311,24 @@
       </c>
       <c r="J87" s="27" t="inlineStr">
         <is>
-          <t>Sanjay Kumar</t>
+          <t>Harkishin malkan</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="28" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B88" s="28" t="inlineStr">
         <is>
-          <t>7:40PM</t>
+          <t>9:00AM</t>
         </is>
       </c>
       <c r="C88" s="28" t="inlineStr">
         <is>
-          <t>8:00PM</t>
+          <t>9:20AM</t>
         </is>
       </c>
       <c r="D88" s="28" t="inlineStr">
@@ -19397,7 +19341,7 @@
       </c>
       <c r="F88" s="28" t="inlineStr">
         <is>
-          <t>41P-12</t>
+          <t>41P-14</t>
         </is>
       </c>
       <c r="G88" s="28" t="inlineStr">
@@ -19417,24 +19361,24 @@
       </c>
       <c r="J88" s="28" t="inlineStr">
         <is>
-          <t>Ajit nair</t>
+          <t>Sachin Malgadnkar</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="27" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B89" s="27" t="inlineStr">
         <is>
-          <t>7:40PM</t>
+          <t>9:30AM</t>
         </is>
       </c>
       <c r="C89" s="27" t="inlineStr">
         <is>
-          <t>8:00PM</t>
+          <t>9:50AM</t>
         </is>
       </c>
       <c r="D89" s="27" t="inlineStr">
@@ -19447,17 +19391,17 @@
       </c>
       <c r="F89" s="27" t="inlineStr">
         <is>
-          <t>41P-13</t>
+          <t>41P-16</t>
         </is>
       </c>
       <c r="G89" s="27" t="inlineStr">
         <is>
-          <t>Board 2</t>
+          <t>Board 1</t>
         </is>
       </c>
       <c r="H89" s="27" t="inlineStr">
         <is>
-          <t>Sachin Malgadnkar</t>
+          <t>Adil Khan</t>
         </is>
       </c>
       <c r="I89" s="27" t="inlineStr">
@@ -19467,24 +19411,24 @@
       </c>
       <c r="J89" s="27" t="inlineStr">
         <is>
-          <t>Prasad Akshintala</t>
+          <t>Harkishin malkan</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="28" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B90" s="28" t="inlineStr">
         <is>
-          <t>8:00PM</t>
+          <t>9:30AM</t>
         </is>
       </c>
       <c r="C90" s="28" t="inlineStr">
         <is>
-          <t>8:20PM</t>
+          <t>9:50AM</t>
         </is>
       </c>
       <c r="D90" s="28" t="inlineStr">
@@ -19497,17 +19441,17 @@
       </c>
       <c r="F90" s="28" t="inlineStr">
         <is>
-          <t>41P-14</t>
+          <t>41P-17</t>
         </is>
       </c>
       <c r="G90" s="28" t="inlineStr">
         <is>
-          <t>Board 1</t>
+          <t>Board 2</t>
         </is>
       </c>
       <c r="H90" s="28" t="inlineStr">
         <is>
-          <t>Adil Khan</t>
+          <t>Sachin Malgadnkar</t>
         </is>
       </c>
       <c r="I90" s="28" t="inlineStr">
@@ -19517,24 +19461,24 @@
       </c>
       <c r="J90" s="28" t="inlineStr">
         <is>
-          <t>Sachin Malgadnkar</t>
+          <t>Ajit nair</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="27" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B91" s="27" t="inlineStr">
         <is>
-          <t>8:00PM</t>
+          <t>10:00AM</t>
         </is>
       </c>
       <c r="C91" s="27" t="inlineStr">
         <is>
-          <t>8:20PM</t>
+          <t>10:20AM</t>
         </is>
       </c>
       <c r="D91" s="27" t="inlineStr">
@@ -19547,17 +19491,17 @@
       </c>
       <c r="F91" s="27" t="inlineStr">
         <is>
-          <t>41P-15</t>
+          <t>41P-18</t>
         </is>
       </c>
       <c r="G91" s="27" t="inlineStr">
         <is>
-          <t>Board 2</t>
+          <t>Board 1</t>
         </is>
       </c>
       <c r="H91" s="27" t="inlineStr">
         <is>
-          <t>Sanjay Kumar</t>
+          <t>Piyush Makharia</t>
         </is>
       </c>
       <c r="I91" s="27" t="inlineStr">
@@ -19574,17 +19518,17 @@
     <row r="92">
       <c r="A92" s="28" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B92" s="28" t="inlineStr">
         <is>
-          <t>8:20PM</t>
+          <t>10:30AM</t>
         </is>
       </c>
       <c r="C92" s="28" t="inlineStr">
         <is>
-          <t>8:40PM</t>
+          <t>10:50AM</t>
         </is>
       </c>
       <c r="D92" s="28" t="inlineStr">
@@ -19597,7 +19541,7 @@
       </c>
       <c r="F92" s="28" t="inlineStr">
         <is>
-          <t>41P-16</t>
+          <t>41P-19</t>
         </is>
       </c>
       <c r="G92" s="28" t="inlineStr">
@@ -19607,7 +19551,7 @@
       </c>
       <c r="H92" s="28" t="inlineStr">
         <is>
-          <t>Adil Khan</t>
+          <t>Prasad Akshintala</t>
         </is>
       </c>
       <c r="I92" s="28" t="inlineStr">
@@ -19624,17 +19568,17 @@
     <row r="93">
       <c r="A93" s="27" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B93" s="27" t="inlineStr">
         <is>
-          <t>8:20PM</t>
+          <t>11:00AM</t>
         </is>
       </c>
       <c r="C93" s="27" t="inlineStr">
         <is>
-          <t>8:40PM</t>
+          <t>11:20AM</t>
         </is>
       </c>
       <c r="D93" s="27" t="inlineStr">
@@ -19647,17 +19591,17 @@
       </c>
       <c r="F93" s="27" t="inlineStr">
         <is>
-          <t>41P-17</t>
+          <t>41P-20</t>
         </is>
       </c>
       <c r="G93" s="27" t="inlineStr">
         <is>
-          <t>Board 2</t>
+          <t>Board 1</t>
         </is>
       </c>
       <c r="H93" s="27" t="inlineStr">
         <is>
-          <t>Sachin Malgadnkar</t>
+          <t>Ajit nair</t>
         </is>
       </c>
       <c r="I93" s="27" t="inlineStr">
@@ -19667,24 +19611,24 @@
       </c>
       <c r="J93" s="27" t="inlineStr">
         <is>
-          <t>Ajit nair</t>
+          <t>Harkishin malkan</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="28" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B94" s="28" t="inlineStr">
         <is>
-          <t>8:40PM</t>
+          <t>11:30AM</t>
         </is>
       </c>
       <c r="C94" s="28" t="inlineStr">
         <is>
-          <t>9:00PM</t>
+          <t>11:50AM</t>
         </is>
       </c>
       <c r="D94" s="28" t="inlineStr">
@@ -19697,7 +19641,7 @@
       </c>
       <c r="F94" s="28" t="inlineStr">
         <is>
-          <t>41P-18</t>
+          <t>41P-21</t>
         </is>
       </c>
       <c r="G94" s="28" t="inlineStr">
@@ -19707,7 +19651,7 @@
       </c>
       <c r="H94" s="28" t="inlineStr">
         <is>
-          <t>Piyush Makharia</t>
+          <t>Sachin Malgadnkar</t>
         </is>
       </c>
       <c r="I94" s="28" t="inlineStr">
@@ -19724,22 +19668,22 @@
     <row r="95">
       <c r="A95" s="27" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B95" s="27" t="inlineStr">
         <is>
-          <t>9:00PM</t>
+          <t>11:50AM</t>
         </is>
       </c>
       <c r="C95" s="27" t="inlineStr">
         <is>
-          <t>9:20PM</t>
+          <t>12:10PM</t>
         </is>
       </c>
       <c r="D95" s="27" t="inlineStr">
         <is>
-          <t>41 and above</t>
+          <t>12 to 20</t>
         </is>
       </c>
       <c r="E95" s="27" t="n">
@@ -19747,7 +19691,7 @@
       </c>
       <c r="F95" s="27" t="inlineStr">
         <is>
-          <t>41P-19</t>
+          <t>1220-FINAL</t>
         </is>
       </c>
       <c r="G95" s="27" t="inlineStr">
@@ -19757,7 +19701,7 @@
       </c>
       <c r="H95" s="27" t="inlineStr">
         <is>
-          <t>Prasad Akshintala</t>
+          <t>Pool 1st</t>
         </is>
       </c>
       <c r="I95" s="27" t="inlineStr">
@@ -19767,29 +19711,29 @@
       </c>
       <c r="J95" s="27" t="inlineStr">
         <is>
-          <t>Harkishin malkan</t>
+          <t>Pool 2nd</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="28" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B96" s="28" t="inlineStr">
         <is>
-          <t>9:20PM</t>
+          <t>11:50AM</t>
         </is>
       </c>
       <c r="C96" s="28" t="inlineStr">
         <is>
-          <t>9:40PM</t>
+          <t>12:10PM</t>
         </is>
       </c>
       <c r="D96" s="28" t="inlineStr">
         <is>
-          <t>41 and above</t>
+          <t>Under 11</t>
         </is>
       </c>
       <c r="E96" s="28" t="n">
@@ -19797,17 +19741,17 @@
       </c>
       <c r="F96" s="28" t="inlineStr">
         <is>
-          <t>41P-20</t>
+          <t>U11-FINAL</t>
         </is>
       </c>
       <c r="G96" s="28" t="inlineStr">
         <is>
-          <t>Board 1</t>
+          <t>Board 2</t>
         </is>
       </c>
       <c r="H96" s="28" t="inlineStr">
         <is>
-          <t>Ajit nair</t>
+          <t>Pool 1st</t>
         </is>
       </c>
       <c r="I96" s="28" t="inlineStr">
@@ -19817,29 +19761,29 @@
       </c>
       <c r="J96" s="28" t="inlineStr">
         <is>
-          <t>Harkishin malkan</t>
+          <t>Pool 2nd</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="27" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B97" s="27" t="inlineStr">
         <is>
-          <t>9:40PM</t>
+          <t>12:10PM</t>
         </is>
       </c>
       <c r="C97" s="27" t="inlineStr">
         <is>
-          <t>10:00PM</t>
+          <t>12:30PM</t>
         </is>
       </c>
       <c r="D97" s="27" t="inlineStr">
         <is>
-          <t>41 and above</t>
+          <t>21 to 40</t>
         </is>
       </c>
       <c r="E97" s="27" t="n">
@@ -19847,7 +19791,7 @@
       </c>
       <c r="F97" s="27" t="inlineStr">
         <is>
-          <t>41P-21</t>
+          <t>2140-FINAL</t>
         </is>
       </c>
       <c r="G97" s="27" t="inlineStr">
@@ -19857,7 +19801,7 @@
       </c>
       <c r="H97" s="27" t="inlineStr">
         <is>
-          <t>Sachin Malgadnkar</t>
+          <t>Pool 1st</t>
         </is>
       </c>
       <c r="I97" s="27" t="inlineStr">
@@ -19867,7 +19811,7 @@
       </c>
       <c r="J97" s="27" t="inlineStr">
         <is>
-          <t>Harkishin malkan</t>
+          <t>Pool 2nd</t>
         </is>
       </c>
     </row>
@@ -19879,12 +19823,12 @@
       </c>
       <c r="B98" s="28" t="inlineStr">
         <is>
-          <t>8:00AM</t>
+          <t>12:30PM</t>
         </is>
       </c>
       <c r="C98" s="28" t="inlineStr">
         <is>
-          <t>8:20AM</t>
+          <t>12:50PM</t>
         </is>
       </c>
       <c r="D98" s="28" t="inlineStr">
@@ -19929,12 +19873,12 @@
       </c>
       <c r="B99" s="27" t="inlineStr">
         <is>
-          <t>8:20AM</t>
+          <t>12:50PM</t>
         </is>
       </c>
       <c r="C99" s="27" t="inlineStr">
         <is>
-          <t>8:40AM</t>
+          <t>1:10PM</t>
         </is>
       </c>
       <c r="D99" s="27" t="inlineStr">
@@ -19979,12 +19923,12 @@
       </c>
       <c r="B100" s="28" t="inlineStr">
         <is>
-          <t>8:40AM</t>
+          <t>1:10PM</t>
         </is>
       </c>
       <c r="C100" s="28" t="inlineStr">
         <is>
-          <t>9:15AM</t>
+          <t>1:30PM</t>
         </is>
       </c>
       <c r="D100" s="28" t="inlineStr">

--- a/Ekta_Schedule_With_Matchups.xlsx
+++ b/Ekta_Schedule_With_Matchups.xlsx
@@ -795,32 +795,52 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>11:50 AM - 2:05 PM</t>
+          <t>11:50 AM - 12:00 PM</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Semis + Finals for every singles event, plus both Doubles events in full (TT Doubles, Carrom Doubles) — none of this starts until every group/pool match everywhere is done</t>
+          <t>Semis + Finals begin, plus both Doubles events in full (TT Doubles, Carrom Doubles) — none of this starts until every group/pool match everywhere is done</t>
         </is>
       </c>
       <c r="D10" s="4" t="n"/>
       <c r="E10" s="4" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="n"/>
-      <c r="B11" s="10" t="n"/>
-      <c r="C11" s="10" t="n"/>
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>Aug 16</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>12:00 - 3:00 PM</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>BREAK</t>
+        </is>
+      </c>
       <c r="D11" s="10" t="n"/>
       <c r="E11" s="10" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>No matches are scheduled between 10:00 PM and 8:00 AM — any match that would otherwise land in that window rolls to 8:00 AM the next day.</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="n"/>
-      <c r="C12" s="4" t="n"/>
+          <t>Aug 16</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>3:00 - 5:00 PM</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Semis + Finals + Doubles resume and wrap up</t>
+        </is>
+      </c>
       <c r="D12" s="4" t="n"/>
       <c r="E12" s="4" t="n"/>
     </row>
@@ -832,7 +852,11 @@
       <c r="E13" s="6" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="n"/>
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>No matches are scheduled between 10:00 PM and 8:00 AM, or between 12:00 PM and 3:00 PM on Aug 16 — any match that would otherwise land in those windows rolls to the end of the window.</t>
+        </is>
+      </c>
       <c r="B14" s="10" t="n"/>
       <c r="C14" s="10" t="n"/>
       <c r="D14" s="10" t="n"/>
@@ -907,7 +931,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>Aug16 12:20PM</t>
+          <t>Aug16 3:15PM</t>
         </is>
       </c>
     </row>
@@ -932,7 +956,7 @@
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>Aug16 1:35PM</t>
+          <t>Aug16 4:30PM</t>
         </is>
       </c>
     </row>
@@ -952,12 +976,12 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Aug16 12:35PM</t>
+          <t>Aug16 3:30PM</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>Aug16 2:05PM</t>
+          <t>Aug16 5:00PM</t>
         </is>
       </c>
     </row>
@@ -982,7 +1006,7 @@
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>Aug16 1:30PM</t>
+          <t>Aug16 4:20PM</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1031,7 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Aug16 1:30PM</t>
+          <t>Aug16 4:20PM</t>
         </is>
       </c>
     </row>
@@ -1032,7 +1056,7 @@
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>Aug16 12:35PM</t>
+          <t>Aug16 3:30PM</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1106,7 @@
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>Aug16 1:20PM</t>
+          <t>Aug16 4:15PM</t>
         </is>
       </c>
     </row>
@@ -1107,14 +1131,14 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>Aug16 1:56PM</t>
+          <t>Aug16 4:48PM</t>
         </is>
       </c>
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="19" t="inlineStr">
         <is>
-          <t>Overall tournament span: Aug 15, 8:00 AM start → Aug 16, 2:05 PM finish — comfortably inside the Aug 16, 10 PM cap.</t>
+          <t>Overall tournament span: Aug 15, 8:00 AM start → Aug 16, 5:00 PM finish — comfortably inside the Aug 16, 10 PM cap.</t>
         </is>
       </c>
     </row>
@@ -2289,12 +2313,12 @@
       </c>
       <c r="B44" s="28" t="inlineStr">
         <is>
-          <t>12:08PM</t>
+          <t>3:00PM</t>
         </is>
       </c>
       <c r="C44" s="28" t="inlineStr">
         <is>
-          <t>12:26PM</t>
+          <t>3:18PM</t>
         </is>
       </c>
       <c r="D44" s="28" t="inlineStr">
@@ -2339,12 +2363,12 @@
       </c>
       <c r="B45" s="27" t="inlineStr">
         <is>
-          <t>12:26PM</t>
+          <t>3:18PM</t>
         </is>
       </c>
       <c r="C45" s="27" t="inlineStr">
         <is>
-          <t>12:44PM</t>
+          <t>3:36PM</t>
         </is>
       </c>
       <c r="D45" s="27" t="inlineStr">
@@ -2389,12 +2413,12 @@
       </c>
       <c r="B46" s="28" t="inlineStr">
         <is>
-          <t>12:44PM</t>
+          <t>3:36PM</t>
         </is>
       </c>
       <c r="C46" s="28" t="inlineStr">
         <is>
-          <t>1:02PM</t>
+          <t>3:54PM</t>
         </is>
       </c>
       <c r="D46" s="28" t="inlineStr">
@@ -2439,12 +2463,12 @@
       </c>
       <c r="B47" s="27" t="inlineStr">
         <is>
-          <t>1:02PM</t>
+          <t>3:54PM</t>
         </is>
       </c>
       <c r="C47" s="27" t="inlineStr">
         <is>
-          <t>1:20PM</t>
+          <t>4:12PM</t>
         </is>
       </c>
       <c r="D47" s="27" t="inlineStr">
@@ -2489,12 +2513,12 @@
       </c>
       <c r="B48" s="28" t="inlineStr">
         <is>
-          <t>1:20PM</t>
+          <t>4:12PM</t>
         </is>
       </c>
       <c r="C48" s="28" t="inlineStr">
         <is>
-          <t>1:38PM</t>
+          <t>4:30PM</t>
         </is>
       </c>
       <c r="D48" s="28" t="inlineStr">
@@ -2539,12 +2563,12 @@
       </c>
       <c r="B49" s="27" t="inlineStr">
         <is>
-          <t>1:38PM</t>
+          <t>4:30PM</t>
         </is>
       </c>
       <c r="C49" s="27" t="inlineStr">
         <is>
-          <t>1:56PM</t>
+          <t>4:48PM</t>
         </is>
       </c>
       <c r="D49" s="27" t="inlineStr">
@@ -3498,12 +3522,12 @@
       </c>
       <c r="B30" s="27" t="inlineStr">
         <is>
-          <t>12:05PM</t>
+          <t>3:00PM</t>
         </is>
       </c>
       <c r="C30" s="27" t="inlineStr">
         <is>
-          <t>12:20PM</t>
+          <t>3:15PM</t>
         </is>
       </c>
       <c r="D30" s="27" t="inlineStr">
@@ -7091,12 +7115,12 @@
       </c>
       <c r="B105" s="27" t="inlineStr">
         <is>
-          <t>12:05PM</t>
+          <t>3:00PM</t>
         </is>
       </c>
       <c r="C105" s="27" t="inlineStr">
         <is>
-          <t>12:20PM</t>
+          <t>3:15PM</t>
         </is>
       </c>
       <c r="D105" s="27" t="inlineStr">
@@ -7141,12 +7165,12 @@
       </c>
       <c r="B106" s="28" t="inlineStr">
         <is>
-          <t>12:05PM</t>
+          <t>3:00PM</t>
         </is>
       </c>
       <c r="C106" s="28" t="inlineStr">
         <is>
-          <t>12:20PM</t>
+          <t>3:15PM</t>
         </is>
       </c>
       <c r="D106" s="28" t="inlineStr">
@@ -7191,12 +7215,12 @@
       </c>
       <c r="B107" s="27" t="inlineStr">
         <is>
-          <t>12:20PM</t>
+          <t>3:15PM</t>
         </is>
       </c>
       <c r="C107" s="27" t="inlineStr">
         <is>
-          <t>12:35PM</t>
+          <t>3:30PM</t>
         </is>
       </c>
       <c r="D107" s="27" t="inlineStr">
@@ -7241,12 +7265,12 @@
       </c>
       <c r="B108" s="28" t="inlineStr">
         <is>
-          <t>12:20PM</t>
+          <t>3:15PM</t>
         </is>
       </c>
       <c r="C108" s="28" t="inlineStr">
         <is>
-          <t>12:35PM</t>
+          <t>3:30PM</t>
         </is>
       </c>
       <c r="D108" s="28" t="inlineStr">
@@ -7291,12 +7315,12 @@
       </c>
       <c r="B109" s="27" t="inlineStr">
         <is>
-          <t>12:35PM</t>
+          <t>3:30PM</t>
         </is>
       </c>
       <c r="C109" s="27" t="inlineStr">
         <is>
-          <t>12:50PM</t>
+          <t>3:45PM</t>
         </is>
       </c>
       <c r="D109" s="27" t="inlineStr">
@@ -7341,12 +7365,12 @@
       </c>
       <c r="B110" s="28" t="inlineStr">
         <is>
-          <t>12:35PM</t>
+          <t>3:30PM</t>
         </is>
       </c>
       <c r="C110" s="28" t="inlineStr">
         <is>
-          <t>12:50PM</t>
+          <t>3:45PM</t>
         </is>
       </c>
       <c r="D110" s="28" t="inlineStr">
@@ -7391,12 +7415,12 @@
       </c>
       <c r="B111" s="27" t="inlineStr">
         <is>
-          <t>12:50PM</t>
+          <t>3:45PM</t>
         </is>
       </c>
       <c r="C111" s="27" t="inlineStr">
         <is>
-          <t>1:05PM</t>
+          <t>4:00PM</t>
         </is>
       </c>
       <c r="D111" s="27" t="inlineStr">
@@ -7441,12 +7465,12 @@
       </c>
       <c r="B112" s="28" t="inlineStr">
         <is>
-          <t>12:50PM</t>
+          <t>3:45PM</t>
         </is>
       </c>
       <c r="C112" s="28" t="inlineStr">
         <is>
-          <t>1:05PM</t>
+          <t>4:00PM</t>
         </is>
       </c>
       <c r="D112" s="28" t="inlineStr">
@@ -7491,12 +7515,12 @@
       </c>
       <c r="B113" s="27" t="inlineStr">
         <is>
-          <t>1:05PM</t>
+          <t>4:00PM</t>
         </is>
       </c>
       <c r="C113" s="27" t="inlineStr">
         <is>
-          <t>1:20PM</t>
+          <t>4:15PM</t>
         </is>
       </c>
       <c r="D113" s="27" t="inlineStr">
@@ -7541,12 +7565,12 @@
       </c>
       <c r="B114" s="28" t="inlineStr">
         <is>
-          <t>1:05PM</t>
+          <t>4:00PM</t>
         </is>
       </c>
       <c r="C114" s="28" t="inlineStr">
         <is>
-          <t>1:20PM</t>
+          <t>4:15PM</t>
         </is>
       </c>
       <c r="D114" s="28" t="inlineStr">
@@ -7591,12 +7615,12 @@
       </c>
       <c r="B115" s="27" t="inlineStr">
         <is>
-          <t>1:20PM</t>
+          <t>4:15PM</t>
         </is>
       </c>
       <c r="C115" s="27" t="inlineStr">
         <is>
-          <t>1:35PM</t>
+          <t>4:30PM</t>
         </is>
       </c>
       <c r="D115" s="27" t="inlineStr">
@@ -7865,12 +7889,12 @@
       </c>
       <c r="B20" s="27" t="inlineStr">
         <is>
-          <t>12:35PM</t>
+          <t>3:30PM</t>
         </is>
       </c>
       <c r="C20" s="27" t="inlineStr">
         <is>
-          <t>12:50PM</t>
+          <t>3:45PM</t>
         </is>
       </c>
       <c r="D20" s="27" t="inlineStr">
@@ -7915,12 +7939,12 @@
       </c>
       <c r="B21" s="28" t="inlineStr">
         <is>
-          <t>12:50PM</t>
+          <t>3:45PM</t>
         </is>
       </c>
       <c r="C21" s="28" t="inlineStr">
         <is>
-          <t>1:05PM</t>
+          <t>4:00PM</t>
         </is>
       </c>
       <c r="D21" s="28" t="inlineStr">
@@ -7965,12 +7989,12 @@
       </c>
       <c r="B22" s="27" t="inlineStr">
         <is>
-          <t>12:50PM</t>
+          <t>3:45PM</t>
         </is>
       </c>
       <c r="C22" s="27" t="inlineStr">
         <is>
-          <t>1:05PM</t>
+          <t>4:00PM</t>
         </is>
       </c>
       <c r="D22" s="27" t="inlineStr">
@@ -8015,12 +8039,12 @@
       </c>
       <c r="B23" s="28" t="inlineStr">
         <is>
-          <t>1:05PM</t>
+          <t>4:00PM</t>
         </is>
       </c>
       <c r="C23" s="28" t="inlineStr">
         <is>
-          <t>1:20PM</t>
+          <t>4:15PM</t>
         </is>
       </c>
       <c r="D23" s="28" t="inlineStr">
@@ -8065,12 +8089,12 @@
       </c>
       <c r="B24" s="27" t="inlineStr">
         <is>
-          <t>1:20PM</t>
+          <t>4:15PM</t>
         </is>
       </c>
       <c r="C24" s="27" t="inlineStr">
         <is>
-          <t>1:35PM</t>
+          <t>4:30PM</t>
         </is>
       </c>
       <c r="D24" s="27" t="inlineStr">
@@ -8115,12 +8139,12 @@
       </c>
       <c r="B25" s="28" t="inlineStr">
         <is>
-          <t>1:35PM</t>
+          <t>4:30PM</t>
         </is>
       </c>
       <c r="C25" s="28" t="inlineStr">
         <is>
-          <t>1:50PM</t>
+          <t>4:45PM</t>
         </is>
       </c>
       <c r="D25" s="28" t="inlineStr">
@@ -8165,12 +8189,12 @@
       </c>
       <c r="B26" s="27" t="inlineStr">
         <is>
-          <t>1:50PM</t>
+          <t>4:45PM</t>
         </is>
       </c>
       <c r="C26" s="27" t="inlineStr">
         <is>
-          <t>2:05PM</t>
+          <t>5:00PM</t>
         </is>
       </c>
       <c r="D26" s="27" t="inlineStr">
@@ -10996,12 +11020,12 @@
       </c>
       <c r="B79" s="27" t="inlineStr">
         <is>
-          <t>12:05PM</t>
+          <t>3:00PM</t>
         </is>
       </c>
       <c r="C79" s="27" t="inlineStr">
         <is>
-          <t>12:20PM</t>
+          <t>3:15PM</t>
         </is>
       </c>
       <c r="D79" s="27" t="inlineStr">
@@ -11046,12 +11070,12 @@
       </c>
       <c r="B80" s="28" t="inlineStr">
         <is>
-          <t>12:05PM</t>
+          <t>3:00PM</t>
         </is>
       </c>
       <c r="C80" s="28" t="inlineStr">
         <is>
-          <t>12:20PM</t>
+          <t>3:15PM</t>
         </is>
       </c>
       <c r="D80" s="28" t="inlineStr">
@@ -11096,12 +11120,12 @@
       </c>
       <c r="B81" s="27" t="inlineStr">
         <is>
-          <t>12:05PM</t>
+          <t>3:00PM</t>
         </is>
       </c>
       <c r="C81" s="27" t="inlineStr">
         <is>
-          <t>12:20PM</t>
+          <t>3:15PM</t>
         </is>
       </c>
       <c r="D81" s="27" t="inlineStr">
@@ -11146,12 +11170,12 @@
       </c>
       <c r="B82" s="28" t="inlineStr">
         <is>
-          <t>12:20PM</t>
+          <t>3:15PM</t>
         </is>
       </c>
       <c r="C82" s="28" t="inlineStr">
         <is>
-          <t>12:35PM</t>
+          <t>3:30PM</t>
         </is>
       </c>
       <c r="D82" s="28" t="inlineStr">
@@ -12374,12 +12398,12 @@
       </c>
       <c r="B31" s="28" t="inlineStr">
         <is>
-          <t>12:05PM</t>
+          <t>3:00PM</t>
         </is>
       </c>
       <c r="C31" s="28" t="inlineStr">
         <is>
-          <t>12:20PM</t>
+          <t>3:15PM</t>
         </is>
       </c>
       <c r="D31" s="28" t="inlineStr">
@@ -12424,12 +12448,12 @@
       </c>
       <c r="B32" s="27" t="inlineStr">
         <is>
-          <t>12:05PM</t>
+          <t>3:00PM</t>
         </is>
       </c>
       <c r="C32" s="27" t="inlineStr">
         <is>
-          <t>12:20PM</t>
+          <t>3:15PM</t>
         </is>
       </c>
       <c r="D32" s="27" t="inlineStr">
@@ -12474,12 +12498,12 @@
       </c>
       <c r="B33" s="28" t="inlineStr">
         <is>
-          <t>12:05PM</t>
+          <t>3:00PM</t>
         </is>
       </c>
       <c r="C33" s="28" t="inlineStr">
         <is>
-          <t>12:20PM</t>
+          <t>3:15PM</t>
         </is>
       </c>
       <c r="D33" s="28" t="inlineStr">
@@ -12524,12 +12548,12 @@
       </c>
       <c r="B34" s="27" t="inlineStr">
         <is>
-          <t>12:20PM</t>
+          <t>3:15PM</t>
         </is>
       </c>
       <c r="C34" s="27" t="inlineStr">
         <is>
-          <t>12:35PM</t>
+          <t>3:30PM</t>
         </is>
       </c>
       <c r="D34" s="27" t="inlineStr">
@@ -12574,12 +12598,12 @@
       </c>
       <c r="B35" s="28" t="inlineStr">
         <is>
-          <t>12:20PM</t>
+          <t>3:15PM</t>
         </is>
       </c>
       <c r="C35" s="28" t="inlineStr">
         <is>
-          <t>12:35PM</t>
+          <t>3:30PM</t>
         </is>
       </c>
       <c r="D35" s="28" t="inlineStr">
@@ -12624,12 +12648,12 @@
       </c>
       <c r="B36" s="27" t="inlineStr">
         <is>
-          <t>12:20PM</t>
+          <t>3:15PM</t>
         </is>
       </c>
       <c r="C36" s="27" t="inlineStr">
         <is>
-          <t>12:35PM</t>
+          <t>3:30PM</t>
         </is>
       </c>
       <c r="D36" s="27" t="inlineStr">
@@ -12674,12 +12698,12 @@
       </c>
       <c r="B37" s="28" t="inlineStr">
         <is>
-          <t>12:35PM</t>
+          <t>3:30PM</t>
         </is>
       </c>
       <c r="C37" s="28" t="inlineStr">
         <is>
-          <t>12:50PM</t>
+          <t>3:45PM</t>
         </is>
       </c>
       <c r="D37" s="28" t="inlineStr">
@@ -12724,12 +12748,12 @@
       </c>
       <c r="B38" s="27" t="inlineStr">
         <is>
-          <t>12:35PM</t>
+          <t>3:30PM</t>
         </is>
       </c>
       <c r="C38" s="27" t="inlineStr">
         <is>
-          <t>12:50PM</t>
+          <t>3:45PM</t>
         </is>
       </c>
       <c r="D38" s="27" t="inlineStr">
@@ -12774,12 +12798,12 @@
       </c>
       <c r="B39" s="28" t="inlineStr">
         <is>
-          <t>12:50PM</t>
+          <t>3:45PM</t>
         </is>
       </c>
       <c r="C39" s="28" t="inlineStr">
         <is>
-          <t>1:05PM</t>
+          <t>4:00PM</t>
         </is>
       </c>
       <c r="D39" s="28" t="inlineStr">
@@ -12824,12 +12848,12 @@
       </c>
       <c r="B40" s="27" t="inlineStr">
         <is>
-          <t>12:50PM</t>
+          <t>3:45PM</t>
         </is>
       </c>
       <c r="C40" s="27" t="inlineStr">
         <is>
-          <t>1:05PM</t>
+          <t>4:00PM</t>
         </is>
       </c>
       <c r="D40" s="27" t="inlineStr">
@@ -12874,12 +12898,12 @@
       </c>
       <c r="B41" s="28" t="inlineStr">
         <is>
-          <t>1:05PM</t>
+          <t>4:00PM</t>
         </is>
       </c>
       <c r="C41" s="28" t="inlineStr">
         <is>
-          <t>1:20PM</t>
+          <t>4:15PM</t>
         </is>
       </c>
       <c r="D41" s="28" t="inlineStr">
@@ -16047,12 +16071,12 @@
       </c>
       <c r="B86" s="27" t="inlineStr">
         <is>
-          <t>12:10PM</t>
+          <t>3:00PM</t>
         </is>
       </c>
       <c r="C86" s="27" t="inlineStr">
         <is>
-          <t>12:30PM</t>
+          <t>3:20PM</t>
         </is>
       </c>
       <c r="D86" s="27" t="inlineStr">
@@ -16097,12 +16121,12 @@
       </c>
       <c r="B87" s="28" t="inlineStr">
         <is>
-          <t>12:10PM</t>
+          <t>3:00PM</t>
         </is>
       </c>
       <c r="C87" s="28" t="inlineStr">
         <is>
-          <t>12:30PM</t>
+          <t>3:20PM</t>
         </is>
       </c>
       <c r="D87" s="28" t="inlineStr">
@@ -16147,12 +16171,12 @@
       </c>
       <c r="B88" s="27" t="inlineStr">
         <is>
-          <t>12:30PM</t>
+          <t>3:20PM</t>
         </is>
       </c>
       <c r="C88" s="27" t="inlineStr">
         <is>
-          <t>12:50PM</t>
+          <t>3:40PM</t>
         </is>
       </c>
       <c r="D88" s="27" t="inlineStr">
@@ -16197,12 +16221,12 @@
       </c>
       <c r="B89" s="28" t="inlineStr">
         <is>
-          <t>12:30PM</t>
+          <t>3:20PM</t>
         </is>
       </c>
       <c r="C89" s="28" t="inlineStr">
         <is>
-          <t>12:50PM</t>
+          <t>3:40PM</t>
         </is>
       </c>
       <c r="D89" s="28" t="inlineStr">
@@ -16247,12 +16271,12 @@
       </c>
       <c r="B90" s="27" t="inlineStr">
         <is>
-          <t>12:50PM</t>
+          <t>3:40PM</t>
         </is>
       </c>
       <c r="C90" s="27" t="inlineStr">
         <is>
-          <t>1:10PM</t>
+          <t>4:00PM</t>
         </is>
       </c>
       <c r="D90" s="27" t="inlineStr">
@@ -16297,12 +16321,12 @@
       </c>
       <c r="B91" s="28" t="inlineStr">
         <is>
-          <t>12:50PM</t>
+          <t>3:40PM</t>
         </is>
       </c>
       <c r="C91" s="28" t="inlineStr">
         <is>
-          <t>1:10PM</t>
+          <t>4:00PM</t>
         </is>
       </c>
       <c r="D91" s="28" t="inlineStr">
@@ -16347,12 +16371,12 @@
       </c>
       <c r="B92" s="27" t="inlineStr">
         <is>
-          <t>1:10PM</t>
+          <t>4:00PM</t>
         </is>
       </c>
       <c r="C92" s="27" t="inlineStr">
         <is>
-          <t>1:30PM</t>
+          <t>4:20PM</t>
         </is>
       </c>
       <c r="D92" s="27" t="inlineStr">
@@ -19773,12 +19797,12 @@
       </c>
       <c r="B97" s="27" t="inlineStr">
         <is>
-          <t>12:10PM</t>
+          <t>3:00PM</t>
         </is>
       </c>
       <c r="C97" s="27" t="inlineStr">
         <is>
-          <t>12:30PM</t>
+          <t>3:20PM</t>
         </is>
       </c>
       <c r="D97" s="27" t="inlineStr">
@@ -19823,12 +19847,12 @@
       </c>
       <c r="B98" s="28" t="inlineStr">
         <is>
-          <t>12:30PM</t>
+          <t>3:20PM</t>
         </is>
       </c>
       <c r="C98" s="28" t="inlineStr">
         <is>
-          <t>12:50PM</t>
+          <t>3:40PM</t>
         </is>
       </c>
       <c r="D98" s="28" t="inlineStr">
@@ -19873,12 +19897,12 @@
       </c>
       <c r="B99" s="27" t="inlineStr">
         <is>
-          <t>12:50PM</t>
+          <t>3:40PM</t>
         </is>
       </c>
       <c r="C99" s="27" t="inlineStr">
         <is>
-          <t>1:10PM</t>
+          <t>4:00PM</t>
         </is>
       </c>
       <c r="D99" s="27" t="inlineStr">
@@ -19923,12 +19947,12 @@
       </c>
       <c r="B100" s="28" t="inlineStr">
         <is>
-          <t>1:10PM</t>
+          <t>4:00PM</t>
         </is>
       </c>
       <c r="C100" s="28" t="inlineStr">
         <is>
-          <t>1:30PM</t>
+          <t>4:20PM</t>
         </is>
       </c>
       <c r="D100" s="28" t="inlineStr">

--- a/Ekta_Schedule_With_Matchups.xlsx
+++ b/Ekta_Schedule_With_Matchups.xlsx
@@ -25,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -116,6 +116,11 @@
       <color rgb="FFCBD5E1"/>
       <sz val="9"/>
     </font>
+    <font>
+      <i val="1"/>
+      <color rgb="FF64748B"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -165,7 +170,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -203,11 +208,55 @@
         <color rgb="FFCBD5E1"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFCBD5E1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFCBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCBD5E1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFCBD5E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCBD5E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFCBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCBD5E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCBD5E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -314,6 +363,23 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -680,7 +746,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" style="21" min="1" max="1"/>
@@ -746,103 +812,115 @@
           <t>Activity</t>
         </is>
       </c>
-      <c r="D7" s="17" t="n"/>
-      <c r="E7" s="17" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="D7" s="37" t="n"/>
+      <c r="E7" s="37" t="n"/>
+      <c r="F7" s="37" t="n"/>
+      <c r="G7" s="38" t="n"/>
+    </row>
+    <row r="8" ht="45" customHeight="1">
+      <c r="A8" s="39" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B8" s="39" t="inlineStr">
         <is>
           <t>8:00 AM - 9:00 PM</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="40" t="inlineStr">
         <is>
           <t>Group / pool ("Americano") stage for all 7 non-doubles events, running concurrently on their own tables/boards/court</t>
         </is>
       </c>
-      <c r="D8" s="4" t="n"/>
-      <c r="E8" s="4" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="D8" s="37" t="n"/>
+      <c r="E8" s="37" t="n"/>
+      <c r="F8" s="37" t="n"/>
+      <c r="G8" s="38" t="n"/>
+    </row>
+    <row r="9" ht="45" customHeight="1">
+      <c r="A9" s="41" t="inlineStr">
         <is>
           <t>Aug 16</t>
         </is>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="41" t="inlineStr">
         <is>
           <t>8:00 - 11:50 AM</t>
         </is>
       </c>
-      <c r="C9" s="10" t="inlineStr">
+      <c r="C9" s="42" t="inlineStr">
         <is>
           <t>Remaining group-stage matches (Chess, TT Men's Singles, Pool) wrap up — held over from Aug 15 by the player rest-break rule</t>
         </is>
       </c>
-      <c r="D9" s="10" t="n"/>
-      <c r="E9" s="10" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="D9" s="37" t="n"/>
+      <c r="E9" s="37" t="n"/>
+      <c r="F9" s="37" t="n"/>
+      <c r="G9" s="38" t="n"/>
+    </row>
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" s="39" t="inlineStr">
         <is>
           <t>Aug 16</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="39" t="inlineStr">
         <is>
           <t>11:50 AM - 12:00 PM</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="40" t="inlineStr">
         <is>
           <t>Semis + Finals begin, plus both Doubles events in full (TT Doubles, Carrom Doubles) — none of this starts until every group/pool match everywhere is done</t>
         </is>
       </c>
-      <c r="D10" s="4" t="n"/>
-      <c r="E10" s="4" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="D10" s="37" t="n"/>
+      <c r="E10" s="37" t="n"/>
+      <c r="F10" s="37" t="n"/>
+      <c r="G10" s="38" t="n"/>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" s="41" t="inlineStr">
         <is>
           <t>Aug 16</t>
         </is>
       </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B11" s="41" t="inlineStr">
         <is>
           <t>12:00 - 3:00 PM</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C11" s="42" t="inlineStr">
         <is>
           <t>BREAK</t>
         </is>
       </c>
-      <c r="D11" s="10" t="n"/>
-      <c r="E11" s="10" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="D11" s="37" t="n"/>
+      <c r="E11" s="37" t="n"/>
+      <c r="F11" s="37" t="n"/>
+      <c r="G11" s="38" t="n"/>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="39" t="inlineStr">
         <is>
           <t>Aug 16</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="39" t="inlineStr">
         <is>
           <t>3:00 - 5:00 PM</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="40" t="inlineStr">
         <is>
           <t>Semis + Finals + Doubles resume and wrap up</t>
         </is>
       </c>
-      <c r="D12" s="4" t="n"/>
-      <c r="E12" s="4" t="n"/>
+      <c r="D12" s="37" t="n"/>
+      <c r="E12" s="37" t="n"/>
+      <c r="F12" s="37" t="n"/>
+      <c r="G12" s="38" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n"/>
@@ -851,16 +929,18 @@
       <c r="D13" s="6" t="n"/>
       <c r="E13" s="6" t="n"/>
     </row>
-    <row r="14">
-      <c r="A14" s="10" t="inlineStr">
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="43" t="inlineStr">
         <is>
           <t>No matches are scheduled between 10:00 PM and 8:00 AM, or between 12:00 PM and 3:00 PM on Aug 16 — any match that would otherwise land in those windows rolls to the end of the window.</t>
         </is>
       </c>
-      <c r="B14" s="10" t="n"/>
-      <c r="C14" s="10" t="n"/>
-      <c r="D14" s="10" t="n"/>
-      <c r="E14" s="10" t="n"/>
+      <c r="B14" s="37" t="n"/>
+      <c r="C14" s="37" t="n"/>
+      <c r="D14" s="37" t="n"/>
+      <c r="E14" s="37" t="n"/>
+      <c r="F14" s="37" t="n"/>
+      <c r="G14" s="38" t="n"/>
     </row>
     <row r="15" ht="33" customHeight="1">
       <c r="A15" s="6" t="n"/>
@@ -1157,15 +1237,22 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="17">
+    <mergeCell ref="C9:G9"/>
     <mergeCell ref="A34:E34"/>
+    <mergeCell ref="C7:G7"/>
     <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="C12:G12"/>
     <mergeCell ref="A2:E2"/>
+    <mergeCell ref="C10:G10"/>
     <mergeCell ref="A33:E33"/>
     <mergeCell ref="A19:E19"/>
+    <mergeCell ref="C11:G11"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A31:E31"/>
     <mergeCell ref="A6:E6"/>
+    <mergeCell ref="C8:G8"/>
     <mergeCell ref="A17:E17"/>
     <mergeCell ref="A3:E3"/>
   </mergeCells>

--- a/Ekta_Schedule_With_Matchups.xlsx
+++ b/Ekta_Schedule_With_Matchups.xlsx
@@ -25,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="17">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -120,6 +120,15 @@
       <i val="1"/>
       <color rgb="FF64748B"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="000F172A"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="10">
@@ -256,7 +265,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -379,6 +388,36 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -797,17 +836,17 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="44" t="inlineStr">
         <is>
           <t>Day</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="44" t="inlineStr">
         <is>
           <t>Time</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="44" t="inlineStr">
         <is>
           <t>Activity</t>
         </is>
@@ -817,20 +856,20 @@
       <c r="F7" s="37" t="n"/>
       <c r="G7" s="38" t="n"/>
     </row>
-    <row r="8" ht="45" customHeight="1">
-      <c r="A8" s="39" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B8" s="39" t="inlineStr">
-        <is>
-          <t>8:00 AM - 9:00 PM</t>
-        </is>
-      </c>
-      <c r="C8" s="40" t="inlineStr">
-        <is>
-          <t>Group / pool ("Americano") stage for all 7 non-doubles events, running concurrently on their own tables/boards/court</t>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="45" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B8" s="45" t="inlineStr">
+        <is>
+          <t>8:00 - 9:30 AM</t>
+        </is>
+      </c>
+      <c r="C8" s="46" t="inlineStr">
+        <is>
+          <t>Events begin — group/pool ("Americano") stage for all 7 non-doubles events</t>
         </is>
       </c>
       <c r="D8" s="37" t="n"/>
@@ -838,20 +877,20 @@
       <c r="F8" s="37" t="n"/>
       <c r="G8" s="38" t="n"/>
     </row>
-    <row r="9" ht="45" customHeight="1">
-      <c r="A9" s="41" t="inlineStr">
-        <is>
-          <t>Aug 16</t>
-        </is>
-      </c>
-      <c r="B9" s="41" t="inlineStr">
-        <is>
-          <t>8:00 - 11:50 AM</t>
-        </is>
-      </c>
-      <c r="C9" s="42" t="inlineStr">
-        <is>
-          <t>Remaining group-stage matches (Chess, TT Men's Singles, Pool) wrap up — held over from Aug 15 by the player rest-break rule</t>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="47" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B9" s="47" t="inlineStr">
+        <is>
+          <t>9:30 - 10:30 AM</t>
+        </is>
+      </c>
+      <c r="C9" s="48" t="inlineStr">
+        <is>
+          <t>FLAG HOISTING — Independence Day ceremony, no matches</t>
         </is>
       </c>
       <c r="D9" s="37" t="n"/>
@@ -859,20 +898,20 @@
       <c r="F9" s="37" t="n"/>
       <c r="G9" s="38" t="n"/>
     </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" s="39" t="inlineStr">
-        <is>
-          <t>Aug 16</t>
-        </is>
-      </c>
-      <c r="B10" s="39" t="inlineStr">
-        <is>
-          <t>11:50 AM - 12:00 PM</t>
-        </is>
-      </c>
-      <c r="C10" s="40" t="inlineStr">
-        <is>
-          <t>Semis + Finals begin, plus both Doubles events in full (TT Doubles, Carrom Doubles) — none of this starts until every group/pool match everywhere is done</t>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" s="45" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B10" s="45" t="inlineStr">
+        <is>
+          <t>10:30 AM - 12:00 PM</t>
+        </is>
+      </c>
+      <c r="C10" s="46" t="inlineStr">
+        <is>
+          <t>Group/pool stage resumes</t>
         </is>
       </c>
       <c r="D10" s="37" t="n"/>
@@ -881,17 +920,17 @@
       <c r="G10" s="38" t="n"/>
     </row>
     <row r="11" ht="15" customHeight="1">
-      <c r="A11" s="41" t="inlineStr">
-        <is>
-          <t>Aug 16</t>
-        </is>
-      </c>
-      <c r="B11" s="41" t="inlineStr">
+      <c r="A11" s="47" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B11" s="47" t="inlineStr">
         <is>
           <t>12:00 - 3:00 PM</t>
         </is>
       </c>
-      <c r="C11" s="42" t="inlineStr">
+      <c r="C11" s="48" t="inlineStr">
         <is>
           <t>BREAK</t>
         </is>
@@ -901,20 +940,20 @@
       <c r="F11" s="37" t="n"/>
       <c r="G11" s="38" t="n"/>
     </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="39" t="inlineStr">
-        <is>
-          <t>Aug 16</t>
-        </is>
-      </c>
-      <c r="B12" s="39" t="inlineStr">
-        <is>
-          <t>3:00 - 5:00 PM</t>
-        </is>
-      </c>
-      <c r="C12" s="40" t="inlineStr">
-        <is>
-          <t>Semis + Finals + Doubles resume and wrap up</t>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" s="45" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B12" s="45" t="inlineStr">
+        <is>
+          <t>3:00 - 10:00 PM</t>
+        </is>
+      </c>
+      <c r="C12" s="46" t="inlineStr">
+        <is>
+          <t>Group/pool stage continues</t>
         </is>
       </c>
       <c r="D12" s="37" t="n"/>
@@ -922,32 +961,81 @@
       <c r="F12" s="37" t="n"/>
       <c r="G12" s="38" t="n"/>
     </row>
-    <row r="13">
-      <c r="A13" s="6" t="n"/>
-      <c r="B13" s="6" t="n"/>
-      <c r="C13" s="6" t="n"/>
-      <c r="D13" s="6" t="n"/>
-      <c r="E13" s="6" t="n"/>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="43" t="inlineStr">
-        <is>
-          <t>No matches are scheduled between 10:00 PM and 8:00 AM, or between 12:00 PM and 3:00 PM on Aug 16 — any match that would otherwise land in those windows rolls to the end of the window.</t>
-        </is>
-      </c>
-      <c r="B14" s="37" t="n"/>
-      <c r="C14" s="37" t="n"/>
-      <c r="D14" s="37" t="n"/>
-      <c r="E14" s="37" t="n"/>
-      <c r="F14" s="37" t="n"/>
-      <c r="G14" s="38" t="n"/>
-    </row>
-    <row r="15" ht="33" customHeight="1">
-      <c r="A15" s="6" t="n"/>
-      <c r="B15" s="6" t="n"/>
-      <c r="C15" s="6" t="n"/>
-      <c r="D15" s="6" t="n"/>
-      <c r="E15" s="6" t="n"/>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="49" t="inlineStr">
+        <is>
+          <t>Aug 16</t>
+        </is>
+      </c>
+      <c r="B13" s="49" t="inlineStr">
+        <is>
+          <t>8:00 AM - 12:00 PM</t>
+        </is>
+      </c>
+      <c r="C13" s="50" t="inlineStr">
+        <is>
+          <t>Remaining group-stage matches (Chess, TT Men's Singles, Pool) continue</t>
+        </is>
+      </c>
+      <c r="D13" s="37" t="n"/>
+      <c r="E13" s="37" t="n"/>
+      <c r="F13" s="37" t="n"/>
+      <c r="G13" s="38" t="n"/>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" s="47" t="inlineStr">
+        <is>
+          <t>Aug 16</t>
+        </is>
+      </c>
+      <c r="B14" s="51" t="inlineStr">
+        <is>
+          <t>12:00 - 3:00 PM</t>
+        </is>
+      </c>
+      <c r="C14" s="52" t="inlineStr">
+        <is>
+          <t>BREAK</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="49" t="inlineStr">
+        <is>
+          <t>Aug 16</t>
+        </is>
+      </c>
+      <c r="B15" s="49" t="inlineStr">
+        <is>
+          <t>3:00 - 3:20 PM</t>
+        </is>
+      </c>
+      <c r="C15" s="50" t="inlineStr">
+        <is>
+          <t>Remaining group-stage matches finish</t>
+        </is>
+      </c>
+      <c r="D15" s="37" t="n"/>
+      <c r="E15" s="37" t="n"/>
+      <c r="F15" s="37" t="n"/>
+      <c r="G15" s="38" t="n"/>
+    </row>
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" s="51" t="inlineStr">
+        <is>
+          <t>Aug 16</t>
+        </is>
+      </c>
+      <c r="B16" s="51" t="inlineStr">
+        <is>
+          <t>3:20 - 5:35 PM</t>
+        </is>
+      </c>
+      <c r="C16" s="52" t="inlineStr">
+        <is>
+          <t>Semis + Finals for every singles event, plus both Doubles events in full (TT Doubles, Carrom Doubles) — none of this starts until every group/pool match everywhere is done</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="27.95" customHeight="1">
       <c r="A17" s="18" t="inlineStr">
@@ -956,6 +1044,13 @@
         </is>
       </c>
     </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="53" t="inlineStr">
+        <is>
+          <t>No matches are scheduled before 8:00 AM, between 9:30-10:30 AM (Aug 15 flag hoisting), between 12:00-3:00 PM on either day, or after 10:00 PM — any match that would otherwise land in those windows rolls to the end of the window.</t>
+        </is>
+      </c>
+    </row>
     <row r="19" ht="20.1" customHeight="1">
       <c r="A19" s="16" t="inlineStr">
         <is>
@@ -1011,7 +1106,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>Aug16 3:15PM</t>
+          <t>Aug16 3:50PM</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1131,7 @@
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>Aug16 4:30PM</t>
+          <t>Aug16 5:05PM</t>
         </is>
       </c>
     </row>
@@ -1056,12 +1151,12 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Aug16 3:30PM</t>
+          <t>Aug16 4:05PM</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>Aug16 5:00PM</t>
+          <t>Aug16 5:35PM</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1181,7 @@
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>Aug16 4:20PM</t>
+          <t>Aug16 5:00PM</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1206,7 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Aug16 4:20PM</t>
+          <t>Aug16 5:00PM</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1231,7 @@
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>Aug16 3:30PM</t>
+          <t>Aug16 4:05PM</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1256,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>Aug16 12:05PM</t>
+          <t>Aug16 3:35PM</t>
         </is>
       </c>
     </row>
@@ -1181,12 +1276,12 @@
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>Aug16 11:50AM</t>
+          <t>Aug16 3:20PM</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>Aug16 4:15PM</t>
+          <t>Aug16 4:50PM</t>
         </is>
       </c>
     </row>
@@ -1211,14 +1306,14 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>Aug16 4:48PM</t>
+          <t>Aug16 5:26PM</t>
         </is>
       </c>
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="19" t="inlineStr">
         <is>
-          <t>Overall tournament span: Aug 15, 8:00 AM start → Aug 16, 5:00 PM finish — comfortably inside the Aug 16, 10 PM cap.</t>
+          <t>Overall tournament span: Aug 15, 8:00 AM start → Aug 16, 5:35 PM finish — comfortably inside the Aug 16, 10 PM cap.</t>
         </is>
       </c>
     </row>
@@ -1237,24 +1332,28 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="21">
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="C14:G14"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C16:G16"/>
     <mergeCell ref="C9:G9"/>
-    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="A17:E17"/>
     <mergeCell ref="C7:G7"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A14:G14"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A18:G18"/>
     <mergeCell ref="A19:E19"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="A1:E1"/>
     <mergeCell ref="A31:E31"/>
-    <mergeCell ref="A6:E6"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="C13:G13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2050,12 +2149,12 @@
       </c>
       <c r="B37" s="27" t="inlineStr">
         <is>
-          <t>10:48AM</t>
+          <t>11:00AM</t>
         </is>
       </c>
       <c r="C37" s="27" t="inlineStr">
         <is>
-          <t>11:06AM</t>
+          <t>11:18AM</t>
         </is>
       </c>
       <c r="D37" s="27" t="inlineStr">
@@ -2100,12 +2199,12 @@
       </c>
       <c r="B38" s="28" t="inlineStr">
         <is>
-          <t>11:16AM</t>
+          <t>11:28AM</t>
         </is>
       </c>
       <c r="C38" s="28" t="inlineStr">
         <is>
-          <t>11:34AM</t>
+          <t>11:46AM</t>
         </is>
       </c>
       <c r="D38" s="28" t="inlineStr">
@@ -2150,12 +2249,12 @@
       </c>
       <c r="B39" s="27" t="inlineStr">
         <is>
-          <t>12:10PM</t>
+          <t>3:20PM</t>
         </is>
       </c>
       <c r="C39" s="27" t="inlineStr">
         <is>
-          <t>12:28PM</t>
+          <t>3:38PM</t>
         </is>
       </c>
       <c r="D39" s="27" t="inlineStr">
@@ -2200,12 +2299,12 @@
       </c>
       <c r="B40" s="28" t="inlineStr">
         <is>
-          <t>3:15PM</t>
+          <t>5:20PM</t>
         </is>
       </c>
       <c r="C40" s="28" t="inlineStr">
         <is>
-          <t>3:33PM</t>
+          <t>5:38PM</t>
         </is>
       </c>
       <c r="D40" s="28" t="inlineStr">
@@ -2250,12 +2349,12 @@
       </c>
       <c r="B41" s="27" t="inlineStr">
         <is>
-          <t>3:40PM</t>
+          <t>5:38PM</t>
         </is>
       </c>
       <c r="C41" s="27" t="inlineStr">
         <is>
-          <t>3:58PM</t>
+          <t>5:56PM</t>
         </is>
       </c>
       <c r="D41" s="27" t="inlineStr">
@@ -2300,12 +2399,12 @@
       </c>
       <c r="B42" s="28" t="inlineStr">
         <is>
-          <t>4:08PM</t>
+          <t>6:06PM</t>
         </is>
       </c>
       <c r="C42" s="28" t="inlineStr">
         <is>
-          <t>4:26PM</t>
+          <t>6:24PM</t>
         </is>
       </c>
       <c r="D42" s="28" t="inlineStr">
@@ -2350,12 +2449,12 @@
       </c>
       <c r="B43" s="27" t="inlineStr">
         <is>
-          <t>11:50AM</t>
+          <t>3:20PM</t>
         </is>
       </c>
       <c r="C43" s="27" t="inlineStr">
         <is>
-          <t>12:08PM</t>
+          <t>3:38PM</t>
         </is>
       </c>
       <c r="D43" s="27" t="inlineStr">
@@ -2400,12 +2499,12 @@
       </c>
       <c r="B44" s="28" t="inlineStr">
         <is>
-          <t>3:00PM</t>
+          <t>3:38PM</t>
         </is>
       </c>
       <c r="C44" s="28" t="inlineStr">
         <is>
-          <t>3:18PM</t>
+          <t>3:56PM</t>
         </is>
       </c>
       <c r="D44" s="28" t="inlineStr">
@@ -2450,12 +2549,12 @@
       </c>
       <c r="B45" s="27" t="inlineStr">
         <is>
-          <t>3:18PM</t>
+          <t>3:56PM</t>
         </is>
       </c>
       <c r="C45" s="27" t="inlineStr">
         <is>
-          <t>3:36PM</t>
+          <t>4:14PM</t>
         </is>
       </c>
       <c r="D45" s="27" t="inlineStr">
@@ -2500,12 +2599,12 @@
       </c>
       <c r="B46" s="28" t="inlineStr">
         <is>
-          <t>3:36PM</t>
+          <t>4:14PM</t>
         </is>
       </c>
       <c r="C46" s="28" t="inlineStr">
         <is>
-          <t>3:54PM</t>
+          <t>4:32PM</t>
         </is>
       </c>
       <c r="D46" s="28" t="inlineStr">
@@ -2550,12 +2649,12 @@
       </c>
       <c r="B47" s="27" t="inlineStr">
         <is>
-          <t>3:54PM</t>
+          <t>4:32PM</t>
         </is>
       </c>
       <c r="C47" s="27" t="inlineStr">
         <is>
-          <t>4:12PM</t>
+          <t>4:50PM</t>
         </is>
       </c>
       <c r="D47" s="27" t="inlineStr">
@@ -2600,12 +2699,12 @@
       </c>
       <c r="B48" s="28" t="inlineStr">
         <is>
-          <t>4:12PM</t>
+          <t>4:50PM</t>
         </is>
       </c>
       <c r="C48" s="28" t="inlineStr">
         <is>
-          <t>4:30PM</t>
+          <t>5:08PM</t>
         </is>
       </c>
       <c r="D48" s="28" t="inlineStr">
@@ -2650,12 +2749,12 @@
       </c>
       <c r="B49" s="27" t="inlineStr">
         <is>
-          <t>4:30PM</t>
+          <t>5:08PM</t>
         </is>
       </c>
       <c r="C49" s="27" t="inlineStr">
         <is>
-          <t>4:48PM</t>
+          <t>5:26PM</t>
         </is>
       </c>
       <c r="D49" s="27" t="inlineStr">
@@ -3309,12 +3408,12 @@
       </c>
       <c r="B24" s="27" t="inlineStr">
         <is>
-          <t>12:00PM</t>
+          <t>3:00PM</t>
         </is>
       </c>
       <c r="C24" s="27" t="inlineStr">
         <is>
-          <t>12:15PM</t>
+          <t>3:15PM</t>
         </is>
       </c>
       <c r="D24" s="27" t="inlineStr">
@@ -3359,12 +3458,12 @@
       </c>
       <c r="B25" s="28" t="inlineStr">
         <is>
-          <t>12:00PM</t>
+          <t>3:00PM</t>
         </is>
       </c>
       <c r="C25" s="28" t="inlineStr">
         <is>
-          <t>12:15PM</t>
+          <t>3:15PM</t>
         </is>
       </c>
       <c r="D25" s="28" t="inlineStr">
@@ -3409,12 +3508,12 @@
       </c>
       <c r="B26" s="27" t="inlineStr">
         <is>
-          <t>12:25PM</t>
+          <t>3:25PM</t>
         </is>
       </c>
       <c r="C26" s="27" t="inlineStr">
         <is>
-          <t>12:40PM</t>
+          <t>3:40PM</t>
         </is>
       </c>
       <c r="D26" s="27" t="inlineStr">
@@ -3459,12 +3558,12 @@
       </c>
       <c r="B27" s="28" t="inlineStr">
         <is>
-          <t>12:25PM</t>
+          <t>3:25PM</t>
         </is>
       </c>
       <c r="C27" s="28" t="inlineStr">
         <is>
-          <t>12:40PM</t>
+          <t>3:40PM</t>
         </is>
       </c>
       <c r="D27" s="28" t="inlineStr">
@@ -3509,12 +3608,12 @@
       </c>
       <c r="B28" s="27" t="inlineStr">
         <is>
-          <t>11:50AM</t>
+          <t>3:20PM</t>
         </is>
       </c>
       <c r="C28" s="27" t="inlineStr">
         <is>
-          <t>12:05PM</t>
+          <t>3:35PM</t>
         </is>
       </c>
       <c r="D28" s="27" t="inlineStr">
@@ -3559,12 +3658,12 @@
       </c>
       <c r="B29" s="28" t="inlineStr">
         <is>
-          <t>11:50AM</t>
+          <t>3:20PM</t>
         </is>
       </c>
       <c r="C29" s="28" t="inlineStr">
         <is>
-          <t>12:05PM</t>
+          <t>3:35PM</t>
         </is>
       </c>
       <c r="D29" s="28" t="inlineStr">
@@ -3609,12 +3708,12 @@
       </c>
       <c r="B30" s="27" t="inlineStr">
         <is>
-          <t>3:00PM</t>
+          <t>3:35PM</t>
         </is>
       </c>
       <c r="C30" s="27" t="inlineStr">
         <is>
-          <t>3:15PM</t>
+          <t>3:50PM</t>
         </is>
       </c>
       <c r="D30" s="27" t="inlineStr">
@@ -4502,12 +4601,12 @@
       </c>
       <c r="B51" s="27" t="inlineStr">
         <is>
-          <t>12:30PM</t>
+          <t>3:40PM</t>
         </is>
       </c>
       <c r="C51" s="27" t="inlineStr">
         <is>
-          <t>12:45PM</t>
+          <t>3:55PM</t>
         </is>
       </c>
       <c r="D51" s="27" t="inlineStr">
@@ -4552,12 +4651,12 @@
       </c>
       <c r="B52" s="28" t="inlineStr">
         <is>
-          <t>3:00PM</t>
+          <t>4:10PM</t>
         </is>
       </c>
       <c r="C52" s="28" t="inlineStr">
         <is>
-          <t>3:15PM</t>
+          <t>4:25PM</t>
         </is>
       </c>
       <c r="D52" s="28" t="inlineStr">
@@ -4602,12 +4701,12 @@
       </c>
       <c r="B53" s="27" t="inlineStr">
         <is>
-          <t>3:00PM</t>
+          <t>4:10PM</t>
         </is>
       </c>
       <c r="C53" s="27" t="inlineStr">
         <is>
-          <t>3:15PM</t>
+          <t>4:25PM</t>
         </is>
       </c>
       <c r="D53" s="27" t="inlineStr">
@@ -4652,12 +4751,12 @@
       </c>
       <c r="B54" s="28" t="inlineStr">
         <is>
-          <t>3:15PM</t>
+          <t>4:25PM</t>
         </is>
       </c>
       <c r="C54" s="28" t="inlineStr">
         <is>
-          <t>3:30PM</t>
+          <t>4:40PM</t>
         </is>
       </c>
       <c r="D54" s="28" t="inlineStr">
@@ -4702,12 +4801,12 @@
       </c>
       <c r="B55" s="27" t="inlineStr">
         <is>
-          <t>3:25PM</t>
+          <t>4:35PM</t>
         </is>
       </c>
       <c r="C55" s="27" t="inlineStr">
         <is>
-          <t>3:40PM</t>
+          <t>4:50PM</t>
         </is>
       </c>
       <c r="D55" s="27" t="inlineStr">
@@ -4752,12 +4851,12 @@
       </c>
       <c r="B56" s="28" t="inlineStr">
         <is>
-          <t>3:40PM</t>
+          <t>4:50PM</t>
         </is>
       </c>
       <c r="C56" s="28" t="inlineStr">
         <is>
-          <t>3:55PM</t>
+          <t>5:05PM</t>
         </is>
       </c>
       <c r="D56" s="28" t="inlineStr">
@@ -4802,12 +4901,12 @@
       </c>
       <c r="B57" s="27" t="inlineStr">
         <is>
-          <t>3:50PM</t>
+          <t>5:00PM</t>
         </is>
       </c>
       <c r="C57" s="27" t="inlineStr">
         <is>
-          <t>4:05PM</t>
+          <t>5:15PM</t>
         </is>
       </c>
       <c r="D57" s="27" t="inlineStr">
@@ -4852,12 +4951,12 @@
       </c>
       <c r="B58" s="28" t="inlineStr">
         <is>
-          <t>4:05PM</t>
+          <t>5:25PM</t>
         </is>
       </c>
       <c r="C58" s="28" t="inlineStr">
         <is>
-          <t>4:20PM</t>
+          <t>5:40PM</t>
         </is>
       </c>
       <c r="D58" s="28" t="inlineStr">
@@ -4870,17 +4969,17 @@
       </c>
       <c r="F58" s="28" t="inlineStr">
         <is>
-          <t>U36-GB-3</t>
+          <t>U36-GA-7</t>
         </is>
       </c>
       <c r="G58" s="28" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H58" s="28" t="inlineStr">
         <is>
-          <t>Dr Rahul Modi</t>
+          <t>Jashit Bajaj</t>
         </is>
       </c>
       <c r="I58" s="28" t="inlineStr">
@@ -4890,7 +4989,7 @@
       </c>
       <c r="J58" s="28" t="inlineStr">
         <is>
-          <t>Tanmay Sharma</t>
+          <t>Prakshal Shah</t>
         </is>
       </c>
     </row>
@@ -4902,12 +5001,12 @@
       </c>
       <c r="B59" s="27" t="inlineStr">
         <is>
-          <t>4:15PM</t>
+          <t>5:38PM</t>
         </is>
       </c>
       <c r="C59" s="27" t="inlineStr">
         <is>
-          <t>4:30PM</t>
+          <t>5:53PM</t>
         </is>
       </c>
       <c r="D59" s="27" t="inlineStr">
@@ -4920,17 +5019,17 @@
       </c>
       <c r="F59" s="27" t="inlineStr">
         <is>
-          <t>U36-GA-7</t>
+          <t>U36-GB-3</t>
         </is>
       </c>
       <c r="G59" s="27" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H59" s="27" t="inlineStr">
         <is>
-          <t>Jashit Bajaj</t>
+          <t>Dr Rahul Modi</t>
         </is>
       </c>
       <c r="I59" s="27" t="inlineStr">
@@ -4940,7 +5039,7 @@
       </c>
       <c r="J59" s="27" t="inlineStr">
         <is>
-          <t>Prakshal Shah</t>
+          <t>Tanmay Sharma</t>
         </is>
       </c>
     </row>
@@ -4952,12 +5051,12 @@
       </c>
       <c r="B60" s="28" t="inlineStr">
         <is>
-          <t>4:30PM</t>
+          <t>5:45PM</t>
         </is>
       </c>
       <c r="C60" s="28" t="inlineStr">
         <is>
-          <t>4:45PM</t>
+          <t>6:00PM</t>
         </is>
       </c>
       <c r="D60" s="28" t="inlineStr">
@@ -5002,12 +5101,12 @@
       </c>
       <c r="B61" s="27" t="inlineStr">
         <is>
-          <t>4:30PM</t>
+          <t>6:00PM</t>
         </is>
       </c>
       <c r="C61" s="27" t="inlineStr">
         <is>
-          <t>4:45PM</t>
+          <t>6:15PM</t>
         </is>
       </c>
       <c r="D61" s="27" t="inlineStr">
@@ -5020,17 +5119,17 @@
       </c>
       <c r="F61" s="27" t="inlineStr">
         <is>
-          <t>U36-GB-5</t>
+          <t>U36-GA-6</t>
         </is>
       </c>
       <c r="G61" s="27" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H61" s="27" t="inlineStr">
         <is>
-          <t>Sudip Parui</t>
+          <t>Ravi Modi</t>
         </is>
       </c>
       <c r="I61" s="27" t="inlineStr">
@@ -5040,7 +5139,7 @@
       </c>
       <c r="J61" s="27" t="inlineStr">
         <is>
-          <t>Tanmay Sharma</t>
+          <t>Tapabrata Dutta</t>
         </is>
       </c>
     </row>
@@ -5052,12 +5151,12 @@
       </c>
       <c r="B62" s="28" t="inlineStr">
         <is>
-          <t>4:45PM</t>
+          <t>6:03PM</t>
         </is>
       </c>
       <c r="C62" s="28" t="inlineStr">
         <is>
-          <t>5:00PM</t>
+          <t>6:18PM</t>
         </is>
       </c>
       <c r="D62" s="28" t="inlineStr">
@@ -5070,17 +5169,17 @@
       </c>
       <c r="F62" s="28" t="inlineStr">
         <is>
-          <t>U36-GA-6</t>
+          <t>U36-GB-5</t>
         </is>
       </c>
       <c r="G62" s="28" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H62" s="28" t="inlineStr">
         <is>
-          <t>Ravi Modi</t>
+          <t>Sudip Parui</t>
         </is>
       </c>
       <c r="I62" s="28" t="inlineStr">
@@ -5090,7 +5189,7 @@
       </c>
       <c r="J62" s="28" t="inlineStr">
         <is>
-          <t>Tapabrata Dutta</t>
+          <t>Tanmay Sharma</t>
         </is>
       </c>
     </row>
@@ -5102,12 +5201,12 @@
       </c>
       <c r="B63" s="27" t="inlineStr">
         <is>
-          <t>4:55PM</t>
+          <t>6:18PM</t>
         </is>
       </c>
       <c r="C63" s="27" t="inlineStr">
         <is>
-          <t>5:10PM</t>
+          <t>6:33PM</t>
         </is>
       </c>
       <c r="D63" s="27" t="inlineStr">
@@ -5152,12 +5251,12 @@
       </c>
       <c r="B64" s="28" t="inlineStr">
         <is>
-          <t>5:10PM</t>
+          <t>6:25PM</t>
         </is>
       </c>
       <c r="C64" s="28" t="inlineStr">
         <is>
-          <t>5:25PM</t>
+          <t>6:40PM</t>
         </is>
       </c>
       <c r="D64" s="28" t="inlineStr">
@@ -5202,12 +5301,12 @@
       </c>
       <c r="B65" s="27" t="inlineStr">
         <is>
-          <t>5:20PM</t>
+          <t>6:43PM</t>
         </is>
       </c>
       <c r="C65" s="27" t="inlineStr">
         <is>
-          <t>5:35PM</t>
+          <t>6:58PM</t>
         </is>
       </c>
       <c r="D65" s="27" t="inlineStr">
@@ -5252,12 +5351,12 @@
       </c>
       <c r="B66" s="28" t="inlineStr">
         <is>
-          <t>5:35PM</t>
+          <t>6:50PM</t>
         </is>
       </c>
       <c r="C66" s="28" t="inlineStr">
         <is>
-          <t>5:50PM</t>
+          <t>7:05PM</t>
         </is>
       </c>
       <c r="D66" s="28" t="inlineStr">
@@ -5302,12 +5401,12 @@
       </c>
       <c r="B67" s="27" t="inlineStr">
         <is>
-          <t>5:35PM</t>
+          <t>7:00PM</t>
         </is>
       </c>
       <c r="C67" s="27" t="inlineStr">
         <is>
-          <t>5:50PM</t>
+          <t>7:15PM</t>
         </is>
       </c>
       <c r="D67" s="27" t="inlineStr">
@@ -5352,17 +5451,17 @@
       </c>
       <c r="B68" s="28" t="inlineStr">
         <is>
-          <t>5:50PM</t>
+          <t>7:25PM</t>
         </is>
       </c>
       <c r="C68" s="28" t="inlineStr">
         <is>
-          <t>6:05PM</t>
+          <t>7:40PM</t>
         </is>
       </c>
       <c r="D68" s="28" t="inlineStr">
         <is>
-          <t>Under 36</t>
+          <t>Under 46</t>
         </is>
       </c>
       <c r="E68" s="28" t="n">
@@ -5370,17 +5469,17 @@
       </c>
       <c r="F68" s="28" t="inlineStr">
         <is>
-          <t>U36-GB-7</t>
+          <t>U46-GB-1</t>
         </is>
       </c>
       <c r="G68" s="28" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H68" s="28" t="inlineStr">
         <is>
-          <t>Tej</t>
+          <t>Amit Ranka</t>
         </is>
       </c>
       <c r="I68" s="28" t="inlineStr">
@@ -5390,7 +5489,7 @@
       </c>
       <c r="J68" s="28" t="inlineStr">
         <is>
-          <t>Sudip Parui</t>
+          <t>Mukul Joshi</t>
         </is>
       </c>
     </row>
@@ -5402,17 +5501,17 @@
       </c>
       <c r="B69" s="27" t="inlineStr">
         <is>
-          <t>6:00PM</t>
+          <t>7:35PM</t>
         </is>
       </c>
       <c r="C69" s="27" t="inlineStr">
         <is>
-          <t>6:15PM</t>
+          <t>7:50PM</t>
         </is>
       </c>
       <c r="D69" s="27" t="inlineStr">
         <is>
-          <t>Under 46</t>
+          <t>Under 36</t>
         </is>
       </c>
       <c r="E69" s="27" t="n">
@@ -5420,17 +5519,17 @@
       </c>
       <c r="F69" s="27" t="inlineStr">
         <is>
-          <t>U46-GB-1</t>
+          <t>U36-GB-7</t>
         </is>
       </c>
       <c r="G69" s="27" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H69" s="27" t="inlineStr">
         <is>
-          <t>Amit Ranka</t>
+          <t>Tej</t>
         </is>
       </c>
       <c r="I69" s="27" t="inlineStr">
@@ -5440,7 +5539,7 @@
       </c>
       <c r="J69" s="27" t="inlineStr">
         <is>
-          <t>Mukul Joshi</t>
+          <t>Sudip Parui</t>
         </is>
       </c>
     </row>
@@ -5452,17 +5551,17 @@
       </c>
       <c r="B70" s="28" t="inlineStr">
         <is>
-          <t>6:05PM</t>
+          <t>7:40PM</t>
         </is>
       </c>
       <c r="C70" s="28" t="inlineStr">
         <is>
-          <t>6:20PM</t>
+          <t>7:55PM</t>
         </is>
       </c>
       <c r="D70" s="28" t="inlineStr">
         <is>
-          <t>Under 46</t>
+          <t>Under 36</t>
         </is>
       </c>
       <c r="E70" s="28" t="n">
@@ -5470,17 +5569,17 @@
       </c>
       <c r="F70" s="28" t="inlineStr">
         <is>
-          <t>U46-GA-1</t>
+          <t>U36-GA-9</t>
         </is>
       </c>
       <c r="G70" s="28" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H70" s="28" t="inlineStr">
         <is>
-          <t>Anuj Shah</t>
+          <t>Ravi Modi</t>
         </is>
       </c>
       <c r="I70" s="28" t="inlineStr">
@@ -5490,7 +5589,7 @@
       </c>
       <c r="J70" s="28" t="inlineStr">
         <is>
-          <t>Nikunj Jhala</t>
+          <t>Prakshal Shah</t>
         </is>
       </c>
     </row>
@@ -5502,17 +5601,17 @@
       </c>
       <c r="B71" s="27" t="inlineStr">
         <is>
-          <t>6:15PM</t>
+          <t>7:50PM</t>
         </is>
       </c>
       <c r="C71" s="27" t="inlineStr">
         <is>
-          <t>6:30PM</t>
+          <t>8:05PM</t>
         </is>
       </c>
       <c r="D71" s="27" t="inlineStr">
         <is>
-          <t>Under 36</t>
+          <t>Under 46</t>
         </is>
       </c>
       <c r="E71" s="27" t="n">
@@ -5520,17 +5619,17 @@
       </c>
       <c r="F71" s="27" t="inlineStr">
         <is>
-          <t>U36-GA-9</t>
+          <t>U46-GA-1</t>
         </is>
       </c>
       <c r="G71" s="27" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H71" s="27" t="inlineStr">
         <is>
-          <t>Ravi Modi</t>
+          <t>Anuj Shah</t>
         </is>
       </c>
       <c r="I71" s="27" t="inlineStr">
@@ -5540,7 +5639,7 @@
       </c>
       <c r="J71" s="27" t="inlineStr">
         <is>
-          <t>Prakshal Shah</t>
+          <t>Nikunj Jhala</t>
         </is>
       </c>
     </row>
@@ -5552,12 +5651,12 @@
       </c>
       <c r="B72" s="28" t="inlineStr">
         <is>
-          <t>6:25PM</t>
+          <t>8:05PM</t>
         </is>
       </c>
       <c r="C72" s="28" t="inlineStr">
         <is>
-          <t>6:40PM</t>
+          <t>8:20PM</t>
         </is>
       </c>
       <c r="D72" s="28" t="inlineStr">
@@ -5602,12 +5701,12 @@
       </c>
       <c r="B73" s="27" t="inlineStr">
         <is>
-          <t>6:30PM</t>
+          <t>8:15PM</t>
         </is>
       </c>
       <c r="C73" s="27" t="inlineStr">
         <is>
-          <t>6:45PM</t>
+          <t>8:30PM</t>
         </is>
       </c>
       <c r="D73" s="27" t="inlineStr">
@@ -5652,12 +5751,12 @@
       </c>
       <c r="B74" s="28" t="inlineStr">
         <is>
-          <t>6:40PM</t>
+          <t>8:20PM</t>
         </is>
       </c>
       <c r="C74" s="28" t="inlineStr">
         <is>
-          <t>6:55PM</t>
+          <t>8:35PM</t>
         </is>
       </c>
       <c r="D74" s="28" t="inlineStr">
@@ -5702,12 +5801,12 @@
       </c>
       <c r="B75" s="27" t="inlineStr">
         <is>
-          <t>6:45PM</t>
+          <t>8:30PM</t>
         </is>
       </c>
       <c r="C75" s="27" t="inlineStr">
         <is>
-          <t>7:00PM</t>
+          <t>8:45PM</t>
         </is>
       </c>
       <c r="D75" s="27" t="inlineStr">
@@ -5752,12 +5851,12 @@
       </c>
       <c r="B76" s="28" t="inlineStr">
         <is>
-          <t>6:55PM</t>
+          <t>8:35PM</t>
         </is>
       </c>
       <c r="C76" s="28" t="inlineStr">
         <is>
-          <t>7:10PM</t>
+          <t>8:50PM</t>
         </is>
       </c>
       <c r="D76" s="28" t="inlineStr">
@@ -5802,12 +5901,12 @@
       </c>
       <c r="B77" s="27" t="inlineStr">
         <is>
-          <t>7:00PM</t>
+          <t>8:45PM</t>
         </is>
       </c>
       <c r="C77" s="27" t="inlineStr">
         <is>
-          <t>7:15PM</t>
+          <t>9:00PM</t>
         </is>
       </c>
       <c r="D77" s="27" t="inlineStr">
@@ -5852,12 +5951,12 @@
       </c>
       <c r="B78" s="28" t="inlineStr">
         <is>
-          <t>7:25PM</t>
+          <t>9:10PM</t>
         </is>
       </c>
       <c r="C78" s="28" t="inlineStr">
         <is>
-          <t>7:40PM</t>
+          <t>9:25PM</t>
         </is>
       </c>
       <c r="D78" s="28" t="inlineStr">
@@ -5902,12 +6001,12 @@
       </c>
       <c r="B79" s="27" t="inlineStr">
         <is>
-          <t>7:25PM</t>
+          <t>9:10PM</t>
         </is>
       </c>
       <c r="C79" s="27" t="inlineStr">
         <is>
-          <t>7:40PM</t>
+          <t>9:25PM</t>
         </is>
       </c>
       <c r="D79" s="27" t="inlineStr">
@@ -5952,12 +6051,12 @@
       </c>
       <c r="B80" s="28" t="inlineStr">
         <is>
-          <t>7:40PM</t>
+          <t>9:25PM</t>
         </is>
       </c>
       <c r="C80" s="28" t="inlineStr">
         <is>
-          <t>7:55PM</t>
+          <t>9:40PM</t>
         </is>
       </c>
       <c r="D80" s="28" t="inlineStr">
@@ -6002,12 +6101,12 @@
       </c>
       <c r="B81" s="27" t="inlineStr">
         <is>
-          <t>7:50PM</t>
+          <t>9:35PM</t>
         </is>
       </c>
       <c r="C81" s="27" t="inlineStr">
         <is>
-          <t>8:05PM</t>
+          <t>9:50PM</t>
         </is>
       </c>
       <c r="D81" s="27" t="inlineStr">
@@ -6052,12 +6151,12 @@
       </c>
       <c r="B82" s="28" t="inlineStr">
         <is>
-          <t>7:55PM</t>
+          <t>9:40PM</t>
         </is>
       </c>
       <c r="C82" s="28" t="inlineStr">
         <is>
-          <t>8:10PM</t>
+          <t>9:55PM</t>
         </is>
       </c>
       <c r="D82" s="28" t="inlineStr">
@@ -6097,22 +6196,22 @@
     <row r="83">
       <c r="A83" s="27" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B83" s="27" t="inlineStr">
         <is>
-          <t>8:15PM</t>
+          <t>8:00AM</t>
         </is>
       </c>
       <c r="C83" s="27" t="inlineStr">
         <is>
-          <t>8:30PM</t>
+          <t>8:15AM</t>
         </is>
       </c>
       <c r="D83" s="27" t="inlineStr">
         <is>
-          <t>Under 46</t>
+          <t>Under 15</t>
         </is>
       </c>
       <c r="E83" s="27" t="n">
@@ -6120,17 +6219,17 @@
       </c>
       <c r="F83" s="27" t="inlineStr">
         <is>
-          <t>U46-GB-6</t>
+          <t>U15-GA-3</t>
         </is>
       </c>
       <c r="G83" s="27" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H83" s="27" t="inlineStr">
         <is>
-          <t>Mukul Joshi</t>
+          <t>Parth yadav</t>
         </is>
       </c>
       <c r="I83" s="27" t="inlineStr">
@@ -6140,29 +6239,29 @@
       </c>
       <c r="J83" s="27" t="inlineStr">
         <is>
-          <t>Adil Khan</t>
+          <t>Aadit Joshi</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="28" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B84" s="28" t="inlineStr">
         <is>
-          <t>8:20PM</t>
+          <t>8:00AM</t>
         </is>
       </c>
       <c r="C84" s="28" t="inlineStr">
         <is>
-          <t>8:35PM</t>
+          <t>8:15AM</t>
         </is>
       </c>
       <c r="D84" s="28" t="inlineStr">
         <is>
-          <t>Under 15</t>
+          <t>Under 46</t>
         </is>
       </c>
       <c r="E84" s="28" t="n">
@@ -6170,17 +6269,17 @@
       </c>
       <c r="F84" s="28" t="inlineStr">
         <is>
-          <t>U15-GA-3</t>
+          <t>U46-GB-6</t>
         </is>
       </c>
       <c r="G84" s="28" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H84" s="28" t="inlineStr">
         <is>
-          <t>Parth yadav</t>
+          <t>Mukul Joshi</t>
         </is>
       </c>
       <c r="I84" s="28" t="inlineStr">
@@ -6190,24 +6289,24 @@
       </c>
       <c r="J84" s="28" t="inlineStr">
         <is>
-          <t>Aadit Joshi</t>
+          <t>Adil Khan</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="27" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B85" s="27" t="inlineStr">
         <is>
-          <t>8:30PM</t>
+          <t>8:15AM</t>
         </is>
       </c>
       <c r="C85" s="27" t="inlineStr">
         <is>
-          <t>8:45PM</t>
+          <t>8:30AM</t>
         </is>
       </c>
       <c r="D85" s="27" t="inlineStr">
@@ -6247,17 +6346,17 @@
     <row r="86">
       <c r="A86" s="28" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B86" s="28" t="inlineStr">
         <is>
-          <t>8:55PM</t>
+          <t>8:40AM</t>
         </is>
       </c>
       <c r="C86" s="28" t="inlineStr">
         <is>
-          <t>9:10PM</t>
+          <t>8:55AM</t>
         </is>
       </c>
       <c r="D86" s="28" t="inlineStr">
@@ -6297,17 +6396,17 @@
     <row r="87">
       <c r="A87" s="27" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B87" s="27" t="inlineStr">
         <is>
-          <t>8:55PM</t>
+          <t>8:40AM</t>
         </is>
       </c>
       <c r="C87" s="27" t="inlineStr">
         <is>
-          <t>9:10PM</t>
+          <t>8:55AM</t>
         </is>
       </c>
       <c r="D87" s="27" t="inlineStr">
@@ -6352,12 +6451,12 @@
       </c>
       <c r="B88" s="28" t="inlineStr">
         <is>
-          <t>8:00AM</t>
+          <t>9:05AM</t>
         </is>
       </c>
       <c r="C88" s="28" t="inlineStr">
         <is>
-          <t>8:15AM</t>
+          <t>9:20AM</t>
         </is>
       </c>
       <c r="D88" s="28" t="inlineStr">
@@ -6402,12 +6501,12 @@
       </c>
       <c r="B89" s="27" t="inlineStr">
         <is>
-          <t>8:00AM</t>
+          <t>9:05AM</t>
         </is>
       </c>
       <c r="C89" s="27" t="inlineStr">
         <is>
-          <t>8:15AM</t>
+          <t>9:20AM</t>
         </is>
       </c>
       <c r="D89" s="27" t="inlineStr">
@@ -6452,12 +6551,12 @@
       </c>
       <c r="B90" s="28" t="inlineStr">
         <is>
-          <t>8:15AM</t>
+          <t>9:20AM</t>
         </is>
       </c>
       <c r="C90" s="28" t="inlineStr">
         <is>
-          <t>8:30AM</t>
+          <t>9:35AM</t>
         </is>
       </c>
       <c r="D90" s="28" t="inlineStr">
@@ -6502,12 +6601,12 @@
       </c>
       <c r="B91" s="27" t="inlineStr">
         <is>
-          <t>8:25AM</t>
+          <t>9:30AM</t>
         </is>
       </c>
       <c r="C91" s="27" t="inlineStr">
         <is>
-          <t>8:40AM</t>
+          <t>9:45AM</t>
         </is>
       </c>
       <c r="D91" s="27" t="inlineStr">
@@ -6552,12 +6651,12 @@
       </c>
       <c r="B92" s="28" t="inlineStr">
         <is>
-          <t>8:30AM</t>
+          <t>9:35AM</t>
         </is>
       </c>
       <c r="C92" s="28" t="inlineStr">
         <is>
-          <t>8:45AM</t>
+          <t>9:50AM</t>
         </is>
       </c>
       <c r="D92" s="28" t="inlineStr">
@@ -6602,12 +6701,12 @@
       </c>
       <c r="B93" s="27" t="inlineStr">
         <is>
-          <t>8:40AM</t>
+          <t>9:45AM</t>
         </is>
       </c>
       <c r="C93" s="27" t="inlineStr">
         <is>
-          <t>8:55AM</t>
+          <t>10:00AM</t>
         </is>
       </c>
       <c r="D93" s="27" t="inlineStr">
@@ -6652,12 +6751,12 @@
       </c>
       <c r="B94" s="28" t="inlineStr">
         <is>
-          <t>8:55AM</t>
+          <t>10:00AM</t>
         </is>
       </c>
       <c r="C94" s="28" t="inlineStr">
         <is>
-          <t>9:10AM</t>
+          <t>10:15AM</t>
         </is>
       </c>
       <c r="D94" s="28" t="inlineStr">
@@ -6702,12 +6801,12 @@
       </c>
       <c r="B95" s="27" t="inlineStr">
         <is>
-          <t>8:55AM</t>
+          <t>10:00AM</t>
         </is>
       </c>
       <c r="C95" s="27" t="inlineStr">
         <is>
-          <t>9:10AM</t>
+          <t>10:15AM</t>
         </is>
       </c>
       <c r="D95" s="27" t="inlineStr">
@@ -6752,12 +6851,12 @@
       </c>
       <c r="B96" s="28" t="inlineStr">
         <is>
-          <t>9:20AM</t>
+          <t>10:25AM</t>
         </is>
       </c>
       <c r="C96" s="28" t="inlineStr">
         <is>
-          <t>9:35AM</t>
+          <t>10:40AM</t>
         </is>
       </c>
       <c r="D96" s="28" t="inlineStr">
@@ -6802,12 +6901,12 @@
       </c>
       <c r="B97" s="27" t="inlineStr">
         <is>
-          <t>9:35AM</t>
+          <t>10:40AM</t>
         </is>
       </c>
       <c r="C97" s="27" t="inlineStr">
         <is>
-          <t>9:50AM</t>
+          <t>10:55AM</t>
         </is>
       </c>
       <c r="D97" s="27" t="inlineStr">
@@ -6852,12 +6951,12 @@
       </c>
       <c r="B98" s="28" t="inlineStr">
         <is>
-          <t>9:45AM</t>
+          <t>10:50AM</t>
         </is>
       </c>
       <c r="C98" s="28" t="inlineStr">
         <is>
-          <t>10:00AM</t>
+          <t>11:05AM</t>
         </is>
       </c>
       <c r="D98" s="28" t="inlineStr">
@@ -6902,12 +7001,12 @@
       </c>
       <c r="B99" s="27" t="inlineStr">
         <is>
-          <t>10:00AM</t>
+          <t>11:05AM</t>
         </is>
       </c>
       <c r="C99" s="27" t="inlineStr">
         <is>
-          <t>10:15AM</t>
+          <t>11:20AM</t>
         </is>
       </c>
       <c r="D99" s="27" t="inlineStr">
@@ -6952,12 +7051,12 @@
       </c>
       <c r="B100" s="28" t="inlineStr">
         <is>
-          <t>10:10AM</t>
+          <t>11:15AM</t>
         </is>
       </c>
       <c r="C100" s="28" t="inlineStr">
         <is>
-          <t>10:25AM</t>
+          <t>11:30AM</t>
         </is>
       </c>
       <c r="D100" s="28" t="inlineStr">
@@ -7002,12 +7101,12 @@
       </c>
       <c r="B101" s="27" t="inlineStr">
         <is>
-          <t>10:35AM</t>
+          <t>11:40AM</t>
         </is>
       </c>
       <c r="C101" s="27" t="inlineStr">
         <is>
-          <t>10:50AM</t>
+          <t>11:55AM</t>
         </is>
       </c>
       <c r="D101" s="27" t="inlineStr">
@@ -7052,12 +7151,12 @@
       </c>
       <c r="B102" s="28" t="inlineStr">
         <is>
-          <t>10:35AM</t>
+          <t>11:40AM</t>
         </is>
       </c>
       <c r="C102" s="28" t="inlineStr">
         <is>
-          <t>10:50AM</t>
+          <t>11:55AM</t>
         </is>
       </c>
       <c r="D102" s="28" t="inlineStr">
@@ -7102,12 +7201,12 @@
       </c>
       <c r="B103" s="27" t="inlineStr">
         <is>
-          <t>11:50AM</t>
+          <t>3:20PM</t>
         </is>
       </c>
       <c r="C103" s="27" t="inlineStr">
         <is>
-          <t>12:05PM</t>
+          <t>3:35PM</t>
         </is>
       </c>
       <c r="D103" s="27" t="inlineStr">
@@ -7152,12 +7251,12 @@
       </c>
       <c r="B104" s="28" t="inlineStr">
         <is>
-          <t>11:50AM</t>
+          <t>3:20PM</t>
         </is>
       </c>
       <c r="C104" s="28" t="inlineStr">
         <is>
-          <t>12:05PM</t>
+          <t>3:35PM</t>
         </is>
       </c>
       <c r="D104" s="28" t="inlineStr">
@@ -7202,12 +7301,12 @@
       </c>
       <c r="B105" s="27" t="inlineStr">
         <is>
-          <t>3:00PM</t>
+          <t>3:35PM</t>
         </is>
       </c>
       <c r="C105" s="27" t="inlineStr">
         <is>
-          <t>3:15PM</t>
+          <t>3:50PM</t>
         </is>
       </c>
       <c r="D105" s="27" t="inlineStr">
@@ -7252,12 +7351,12 @@
       </c>
       <c r="B106" s="28" t="inlineStr">
         <is>
-          <t>3:00PM</t>
+          <t>3:35PM</t>
         </is>
       </c>
       <c r="C106" s="28" t="inlineStr">
         <is>
-          <t>3:15PM</t>
+          <t>3:50PM</t>
         </is>
       </c>
       <c r="D106" s="28" t="inlineStr">
@@ -7302,12 +7401,12 @@
       </c>
       <c r="B107" s="27" t="inlineStr">
         <is>
-          <t>3:15PM</t>
+          <t>3:50PM</t>
         </is>
       </c>
       <c r="C107" s="27" t="inlineStr">
         <is>
-          <t>3:30PM</t>
+          <t>4:05PM</t>
         </is>
       </c>
       <c r="D107" s="27" t="inlineStr">
@@ -7352,12 +7451,12 @@
       </c>
       <c r="B108" s="28" t="inlineStr">
         <is>
-          <t>3:15PM</t>
+          <t>3:50PM</t>
         </is>
       </c>
       <c r="C108" s="28" t="inlineStr">
         <is>
-          <t>3:30PM</t>
+          <t>4:05PM</t>
         </is>
       </c>
       <c r="D108" s="28" t="inlineStr">
@@ -7402,12 +7501,12 @@
       </c>
       <c r="B109" s="27" t="inlineStr">
         <is>
-          <t>3:30PM</t>
+          <t>4:05PM</t>
         </is>
       </c>
       <c r="C109" s="27" t="inlineStr">
         <is>
-          <t>3:45PM</t>
+          <t>4:20PM</t>
         </is>
       </c>
       <c r="D109" s="27" t="inlineStr">
@@ -7452,12 +7551,12 @@
       </c>
       <c r="B110" s="28" t="inlineStr">
         <is>
-          <t>3:30PM</t>
+          <t>4:05PM</t>
         </is>
       </c>
       <c r="C110" s="28" t="inlineStr">
         <is>
-          <t>3:45PM</t>
+          <t>4:20PM</t>
         </is>
       </c>
       <c r="D110" s="28" t="inlineStr">
@@ -7502,12 +7601,12 @@
       </c>
       <c r="B111" s="27" t="inlineStr">
         <is>
-          <t>3:45PM</t>
+          <t>4:20PM</t>
         </is>
       </c>
       <c r="C111" s="27" t="inlineStr">
         <is>
-          <t>4:00PM</t>
+          <t>4:35PM</t>
         </is>
       </c>
       <c r="D111" s="27" t="inlineStr">
@@ -7552,12 +7651,12 @@
       </c>
       <c r="B112" s="28" t="inlineStr">
         <is>
-          <t>3:45PM</t>
+          <t>4:20PM</t>
         </is>
       </c>
       <c r="C112" s="28" t="inlineStr">
         <is>
-          <t>4:00PM</t>
+          <t>4:35PM</t>
         </is>
       </c>
       <c r="D112" s="28" t="inlineStr">
@@ -7602,12 +7701,12 @@
       </c>
       <c r="B113" s="27" t="inlineStr">
         <is>
-          <t>4:00PM</t>
+          <t>4:35PM</t>
         </is>
       </c>
       <c r="C113" s="27" t="inlineStr">
         <is>
-          <t>4:15PM</t>
+          <t>4:50PM</t>
         </is>
       </c>
       <c r="D113" s="27" t="inlineStr">
@@ -7652,12 +7751,12 @@
       </c>
       <c r="B114" s="28" t="inlineStr">
         <is>
-          <t>4:00PM</t>
+          <t>4:35PM</t>
         </is>
       </c>
       <c r="C114" s="28" t="inlineStr">
         <is>
-          <t>4:15PM</t>
+          <t>4:50PM</t>
         </is>
       </c>
       <c r="D114" s="28" t="inlineStr">
@@ -7702,12 +7801,12 @@
       </c>
       <c r="B115" s="27" t="inlineStr">
         <is>
-          <t>4:15PM</t>
+          <t>4:50PM</t>
         </is>
       </c>
       <c r="C115" s="27" t="inlineStr">
         <is>
-          <t>4:30PM</t>
+          <t>5:05PM</t>
         </is>
       </c>
       <c r="D115" s="27" t="inlineStr">
@@ -7976,12 +8075,12 @@
       </c>
       <c r="B20" s="27" t="inlineStr">
         <is>
-          <t>3:30PM</t>
+          <t>4:05PM</t>
         </is>
       </c>
       <c r="C20" s="27" t="inlineStr">
         <is>
-          <t>3:45PM</t>
+          <t>4:20PM</t>
         </is>
       </c>
       <c r="D20" s="27" t="inlineStr">
@@ -8026,12 +8125,12 @@
       </c>
       <c r="B21" s="28" t="inlineStr">
         <is>
-          <t>3:45PM</t>
+          <t>4:20PM</t>
         </is>
       </c>
       <c r="C21" s="28" t="inlineStr">
         <is>
-          <t>4:00PM</t>
+          <t>4:35PM</t>
         </is>
       </c>
       <c r="D21" s="28" t="inlineStr">
@@ -8076,12 +8175,12 @@
       </c>
       <c r="B22" s="27" t="inlineStr">
         <is>
-          <t>3:45PM</t>
+          <t>4:20PM</t>
         </is>
       </c>
       <c r="C22" s="27" t="inlineStr">
         <is>
-          <t>4:00PM</t>
+          <t>4:35PM</t>
         </is>
       </c>
       <c r="D22" s="27" t="inlineStr">
@@ -8126,12 +8225,12 @@
       </c>
       <c r="B23" s="28" t="inlineStr">
         <is>
-          <t>4:00PM</t>
+          <t>4:35PM</t>
         </is>
       </c>
       <c r="C23" s="28" t="inlineStr">
         <is>
-          <t>4:15PM</t>
+          <t>4:50PM</t>
         </is>
       </c>
       <c r="D23" s="28" t="inlineStr">
@@ -8176,12 +8275,12 @@
       </c>
       <c r="B24" s="27" t="inlineStr">
         <is>
-          <t>4:15PM</t>
+          <t>4:50PM</t>
         </is>
       </c>
       <c r="C24" s="27" t="inlineStr">
         <is>
-          <t>4:30PM</t>
+          <t>5:05PM</t>
         </is>
       </c>
       <c r="D24" s="27" t="inlineStr">
@@ -8226,12 +8325,12 @@
       </c>
       <c r="B25" s="28" t="inlineStr">
         <is>
-          <t>4:30PM</t>
+          <t>5:05PM</t>
         </is>
       </c>
       <c r="C25" s="28" t="inlineStr">
         <is>
-          <t>4:45PM</t>
+          <t>5:20PM</t>
         </is>
       </c>
       <c r="D25" s="28" t="inlineStr">
@@ -8276,12 +8375,12 @@
       </c>
       <c r="B26" s="27" t="inlineStr">
         <is>
-          <t>4:45PM</t>
+          <t>5:20PM</t>
         </is>
       </c>
       <c r="C26" s="27" t="inlineStr">
         <is>
-          <t>5:00PM</t>
+          <t>5:35PM</t>
         </is>
       </c>
       <c r="D26" s="27" t="inlineStr">
@@ -9007,12 +9106,12 @@
       </c>
       <c r="B37" s="27" t="inlineStr">
         <is>
-          <t>9:35AM</t>
+          <t>10:30AM</t>
         </is>
       </c>
       <c r="C37" s="27" t="inlineStr">
         <is>
-          <t>9:50AM</t>
+          <t>10:45AM</t>
         </is>
       </c>
       <c r="D37" s="27" t="inlineStr">
@@ -9025,17 +9124,17 @@
       </c>
       <c r="F37" s="27" t="inlineStr">
         <is>
-          <t>CM-U46-GB-2</t>
+          <t>CM-U46-GA-6</t>
         </is>
       </c>
       <c r="G37" s="27" t="inlineStr">
         <is>
-          <t>Board 3</t>
+          <t>Board 1</t>
         </is>
       </c>
       <c r="H37" s="27" t="inlineStr">
         <is>
-          <t>Nikunj Jhala</t>
+          <t>Ravi Modi</t>
         </is>
       </c>
       <c r="I37" s="27" t="inlineStr">
@@ -9045,7 +9144,7 @@
       </c>
       <c r="J37" s="27" t="inlineStr">
         <is>
-          <t>Nilesh Bagaria</t>
+          <t>Abhishek Dugar</t>
         </is>
       </c>
     </row>
@@ -9057,12 +9156,12 @@
       </c>
       <c r="B38" s="28" t="inlineStr">
         <is>
-          <t>9:45AM</t>
+          <t>10:30AM</t>
         </is>
       </c>
       <c r="C38" s="28" t="inlineStr">
         <is>
-          <t>10:00AM</t>
+          <t>10:45AM</t>
         </is>
       </c>
       <c r="D38" s="28" t="inlineStr">
@@ -9075,17 +9174,17 @@
       </c>
       <c r="F38" s="28" t="inlineStr">
         <is>
-          <t>CM-U46-GA-6</t>
+          <t>CM-U46-GB-2</t>
         </is>
       </c>
       <c r="G38" s="28" t="inlineStr">
         <is>
-          <t>Board 1</t>
+          <t>Board 3</t>
         </is>
       </c>
       <c r="H38" s="28" t="inlineStr">
         <is>
-          <t>Ravi Modi</t>
+          <t>Nikunj Jhala</t>
         </is>
       </c>
       <c r="I38" s="28" t="inlineStr">
@@ -9095,7 +9194,7 @@
       </c>
       <c r="J38" s="28" t="inlineStr">
         <is>
-          <t>Abhishek Dugar</t>
+          <t>Nilesh Bagaria</t>
         </is>
       </c>
     </row>
@@ -9107,12 +9206,12 @@
       </c>
       <c r="B39" s="27" t="inlineStr">
         <is>
-          <t>10:30AM</t>
+          <t>10:45AM</t>
         </is>
       </c>
       <c r="C39" s="27" t="inlineStr">
         <is>
-          <t>10:45AM</t>
+          <t>11:00AM</t>
         </is>
       </c>
       <c r="D39" s="27" t="inlineStr">
@@ -9125,17 +9224,17 @@
       </c>
       <c r="F39" s="27" t="inlineStr">
         <is>
-          <t>CM-U46-GA-2</t>
+          <t>CM-U46-GA-7</t>
         </is>
       </c>
       <c r="G39" s="27" t="inlineStr">
         <is>
-          <t>Board 2</t>
+          <t>Board 3</t>
         </is>
       </c>
       <c r="H39" s="27" t="inlineStr">
         <is>
-          <t>Ravi Modi</t>
+          <t>Dr Rahul Modi</t>
         </is>
       </c>
       <c r="I39" s="27" t="inlineStr">
@@ -9145,7 +9244,7 @@
       </c>
       <c r="J39" s="27" t="inlineStr">
         <is>
-          <t>Ankur Mahante</t>
+          <t>Anuj Shah</t>
         </is>
       </c>
     </row>
@@ -9157,12 +9256,12 @@
       </c>
       <c r="B40" s="28" t="inlineStr">
         <is>
-          <t>10:30AM</t>
+          <t>10:55AM</t>
         </is>
       </c>
       <c r="C40" s="28" t="inlineStr">
         <is>
-          <t>10:45AM</t>
+          <t>11:10AM</t>
         </is>
       </c>
       <c r="D40" s="28" t="inlineStr">
@@ -9175,17 +9274,17 @@
       </c>
       <c r="F40" s="28" t="inlineStr">
         <is>
-          <t>CM-U46-GA-7</t>
+          <t>CM-U46-GA-2</t>
         </is>
       </c>
       <c r="G40" s="28" t="inlineStr">
         <is>
-          <t>Board 3</t>
+          <t>Board 2</t>
         </is>
       </c>
       <c r="H40" s="28" t="inlineStr">
         <is>
-          <t>Dr Rahul Modi</t>
+          <t>Ravi Modi</t>
         </is>
       </c>
       <c r="I40" s="28" t="inlineStr">
@@ -9195,7 +9294,7 @@
       </c>
       <c r="J40" s="28" t="inlineStr">
         <is>
-          <t>Anuj Shah</t>
+          <t>Ankur Mahante</t>
         </is>
       </c>
     </row>
@@ -9225,17 +9324,17 @@
       </c>
       <c r="F41" s="27" t="inlineStr">
         <is>
-          <t>CM-U46-GA-8</t>
+          <t>CM-U46-GB-3</t>
         </is>
       </c>
       <c r="G41" s="27" t="inlineStr">
         <is>
-          <t>Board 2</t>
+          <t>Board 1</t>
         </is>
       </c>
       <c r="H41" s="27" t="inlineStr">
         <is>
-          <t>Abhishek Dugar</t>
+          <t>Amar Jain</t>
         </is>
       </c>
       <c r="I41" s="27" t="inlineStr">
@@ -9245,7 +9344,7 @@
       </c>
       <c r="J41" s="27" t="inlineStr">
         <is>
-          <t>Ankur Mahante</t>
+          <t>Vinit Padia</t>
         </is>
       </c>
     </row>
@@ -9257,12 +9356,12 @@
       </c>
       <c r="B42" s="28" t="inlineStr">
         <is>
-          <t>10:55AM</t>
+          <t>11:10AM</t>
         </is>
       </c>
       <c r="C42" s="28" t="inlineStr">
         <is>
-          <t>11:10AM</t>
+          <t>11:25AM</t>
         </is>
       </c>
       <c r="D42" s="28" t="inlineStr">
@@ -9275,17 +9374,17 @@
       </c>
       <c r="F42" s="28" t="inlineStr">
         <is>
-          <t>CM-U46-GA-9</t>
+          <t>CM-U46-GB-4</t>
         </is>
       </c>
       <c r="G42" s="28" t="inlineStr">
         <is>
-          <t>Board 3</t>
+          <t>Board 1</t>
         </is>
       </c>
       <c r="H42" s="28" t="inlineStr">
         <is>
-          <t>Rahul Garg</t>
+          <t>Nilesh Bagaria</t>
         </is>
       </c>
       <c r="I42" s="28" t="inlineStr">
@@ -9295,7 +9394,7 @@
       </c>
       <c r="J42" s="28" t="inlineStr">
         <is>
-          <t>Ravi Modi</t>
+          <t>Amit Ranka</t>
         </is>
       </c>
     </row>
@@ -9307,12 +9406,12 @@
       </c>
       <c r="B43" s="27" t="inlineStr">
         <is>
-          <t>10:55AM</t>
+          <t>11:20AM</t>
         </is>
       </c>
       <c r="C43" s="27" t="inlineStr">
         <is>
-          <t>11:10AM</t>
+          <t>11:35AM</t>
         </is>
       </c>
       <c r="D43" s="27" t="inlineStr">
@@ -9325,17 +9424,17 @@
       </c>
       <c r="F43" s="27" t="inlineStr">
         <is>
-          <t>CM-U46-GB-3</t>
+          <t>CM-U46-GA-8</t>
         </is>
       </c>
       <c r="G43" s="27" t="inlineStr">
         <is>
-          <t>Board 1</t>
+          <t>Board 2</t>
         </is>
       </c>
       <c r="H43" s="27" t="inlineStr">
         <is>
-          <t>Amar Jain</t>
+          <t>Abhishek Dugar</t>
         </is>
       </c>
       <c r="I43" s="27" t="inlineStr">
@@ -9345,7 +9444,7 @@
       </c>
       <c r="J43" s="27" t="inlineStr">
         <is>
-          <t>Vinit Padia</t>
+          <t>Ankur Mahante</t>
         </is>
       </c>
     </row>
@@ -9357,12 +9456,12 @@
       </c>
       <c r="B44" s="28" t="inlineStr">
         <is>
-          <t>11:10AM</t>
+          <t>11:20AM</t>
         </is>
       </c>
       <c r="C44" s="28" t="inlineStr">
         <is>
-          <t>11:25AM</t>
+          <t>11:35AM</t>
         </is>
       </c>
       <c r="D44" s="28" t="inlineStr">
@@ -9375,17 +9474,17 @@
       </c>
       <c r="F44" s="28" t="inlineStr">
         <is>
-          <t>CM-U46-GB-4</t>
+          <t>CM-U46-GA-9</t>
         </is>
       </c>
       <c r="G44" s="28" t="inlineStr">
         <is>
-          <t>Board 1</t>
+          <t>Board 3</t>
         </is>
       </c>
       <c r="H44" s="28" t="inlineStr">
         <is>
-          <t>Nilesh Bagaria</t>
+          <t>Rahul Garg</t>
         </is>
       </c>
       <c r="I44" s="28" t="inlineStr">
@@ -9395,7 +9494,7 @@
       </c>
       <c r="J44" s="28" t="inlineStr">
         <is>
-          <t>Amit Ranka</t>
+          <t>Ravi Modi</t>
         </is>
       </c>
     </row>
@@ -9407,12 +9506,12 @@
       </c>
       <c r="B45" s="27" t="inlineStr">
         <is>
-          <t>11:20AM</t>
+          <t>11:45AM</t>
         </is>
       </c>
       <c r="C45" s="27" t="inlineStr">
         <is>
-          <t>11:35AM</t>
+          <t>12:00PM</t>
         </is>
       </c>
       <c r="D45" s="27" t="inlineStr">
@@ -9457,12 +9556,12 @@
       </c>
       <c r="B46" s="28" t="inlineStr">
         <is>
-          <t>11:20AM</t>
+          <t>11:45AM</t>
         </is>
       </c>
       <c r="C46" s="28" t="inlineStr">
         <is>
-          <t>11:35AM</t>
+          <t>12:00PM</t>
         </is>
       </c>
       <c r="D46" s="28" t="inlineStr">
@@ -9507,12 +9606,12 @@
       </c>
       <c r="B47" s="27" t="inlineStr">
         <is>
-          <t>11:35AM</t>
+          <t>3:00PM</t>
         </is>
       </c>
       <c r="C47" s="27" t="inlineStr">
         <is>
-          <t>11:50AM</t>
+          <t>3:15PM</t>
         </is>
       </c>
       <c r="D47" s="27" t="inlineStr">
@@ -9525,17 +9624,17 @@
       </c>
       <c r="F47" s="27" t="inlineStr">
         <is>
-          <t>CM-U46-GB-5</t>
+          <t>CM-U46-GA-11</t>
         </is>
       </c>
       <c r="G47" s="27" t="inlineStr">
         <is>
-          <t>Board 3</t>
+          <t>Board 1</t>
         </is>
       </c>
       <c r="H47" s="27" t="inlineStr">
         <is>
-          <t>Mayank Aggarwal</t>
+          <t>Ravi Modi</t>
         </is>
       </c>
       <c r="I47" s="27" t="inlineStr">
@@ -9545,7 +9644,7 @@
       </c>
       <c r="J47" s="27" t="inlineStr">
         <is>
-          <t>Vinit Padia</t>
+          <t>Dr Rahul Modi</t>
         </is>
       </c>
     </row>
@@ -9557,12 +9656,12 @@
       </c>
       <c r="B48" s="28" t="inlineStr">
         <is>
-          <t>11:45AM</t>
+          <t>3:00PM</t>
         </is>
       </c>
       <c r="C48" s="28" t="inlineStr">
         <is>
-          <t>12:00PM</t>
+          <t>3:15PM</t>
         </is>
       </c>
       <c r="D48" s="28" t="inlineStr">
@@ -9575,17 +9674,17 @@
       </c>
       <c r="F48" s="28" t="inlineStr">
         <is>
-          <t>CM-U46-GA-11</t>
+          <t>CM-U46-GA-14</t>
         </is>
       </c>
       <c r="G48" s="28" t="inlineStr">
         <is>
-          <t>Board 1</t>
+          <t>Board 2</t>
         </is>
       </c>
       <c r="H48" s="28" t="inlineStr">
         <is>
-          <t>Ravi Modi</t>
+          <t>Rahul Garg</t>
         </is>
       </c>
       <c r="I48" s="28" t="inlineStr">
@@ -9595,7 +9694,7 @@
       </c>
       <c r="J48" s="28" t="inlineStr">
         <is>
-          <t>Dr Rahul Modi</t>
+          <t>Abhishek Dugar</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9706,12 @@
       </c>
       <c r="B49" s="27" t="inlineStr">
         <is>
-          <t>11:45AM</t>
+          <t>3:00PM</t>
         </is>
       </c>
       <c r="C49" s="27" t="inlineStr">
         <is>
-          <t>12:00PM</t>
+          <t>3:15PM</t>
         </is>
       </c>
       <c r="D49" s="27" t="inlineStr">
@@ -9625,17 +9724,17 @@
       </c>
       <c r="F49" s="27" t="inlineStr">
         <is>
-          <t>CM-U46-GA-14</t>
+          <t>CM-U46-GB-5</t>
         </is>
       </c>
       <c r="G49" s="27" t="inlineStr">
         <is>
-          <t>Board 2</t>
+          <t>Board 3</t>
         </is>
       </c>
       <c r="H49" s="27" t="inlineStr">
         <is>
-          <t>Rahul Garg</t>
+          <t>Mayank Aggarwal</t>
         </is>
       </c>
       <c r="I49" s="27" t="inlineStr">
@@ -9645,7 +9744,7 @@
       </c>
       <c r="J49" s="27" t="inlineStr">
         <is>
-          <t>Abhishek Dugar</t>
+          <t>Vinit Padia</t>
         </is>
       </c>
     </row>
@@ -9657,12 +9756,12 @@
       </c>
       <c r="B50" s="28" t="inlineStr">
         <is>
-          <t>12:00PM</t>
+          <t>3:15PM</t>
         </is>
       </c>
       <c r="C50" s="28" t="inlineStr">
         <is>
-          <t>12:15PM</t>
+          <t>3:30PM</t>
         </is>
       </c>
       <c r="D50" s="28" t="inlineStr">
@@ -9707,12 +9806,12 @@
       </c>
       <c r="B51" s="27" t="inlineStr">
         <is>
-          <t>12:00PM</t>
+          <t>3:15PM</t>
         </is>
       </c>
       <c r="C51" s="27" t="inlineStr">
         <is>
-          <t>12:15PM</t>
+          <t>3:30PM</t>
         </is>
       </c>
       <c r="D51" s="27" t="inlineStr">
@@ -9757,12 +9856,12 @@
       </c>
       <c r="B52" s="28" t="inlineStr">
         <is>
-          <t>12:00PM</t>
+          <t>3:25PM</t>
         </is>
       </c>
       <c r="C52" s="28" t="inlineStr">
         <is>
-          <t>12:15PM</t>
+          <t>3:40PM</t>
         </is>
       </c>
       <c r="D52" s="28" t="inlineStr">
@@ -9807,12 +9906,12 @@
       </c>
       <c r="B53" s="27" t="inlineStr">
         <is>
-          <t>12:25PM</t>
+          <t>3:40PM</t>
         </is>
       </c>
       <c r="C53" s="27" t="inlineStr">
         <is>
-          <t>12:40PM</t>
+          <t>3:55PM</t>
         </is>
       </c>
       <c r="D53" s="27" t="inlineStr">
@@ -9857,12 +9956,12 @@
       </c>
       <c r="B54" s="28" t="inlineStr">
         <is>
-          <t>12:25PM</t>
+          <t>3:40PM</t>
         </is>
       </c>
       <c r="C54" s="28" t="inlineStr">
         <is>
-          <t>12:40PM</t>
+          <t>3:55PM</t>
         </is>
       </c>
       <c r="D54" s="28" t="inlineStr">
@@ -9875,17 +9974,17 @@
       </c>
       <c r="F54" s="28" t="inlineStr">
         <is>
-          <t>CM-U46-GB-11</t>
+          <t>CM-U46-GB-8</t>
         </is>
       </c>
       <c r="G54" s="28" t="inlineStr">
         <is>
-          <t>Board 2</t>
+          <t>Board 3</t>
         </is>
       </c>
       <c r="H54" s="28" t="inlineStr">
         <is>
-          <t>Nikunj Jhala</t>
+          <t>Amar Jain</t>
         </is>
       </c>
       <c r="I54" s="28" t="inlineStr">
@@ -9895,7 +9994,7 @@
       </c>
       <c r="J54" s="28" t="inlineStr">
         <is>
-          <t>Vinit Padia</t>
+          <t>Nilesh Bagaria</t>
         </is>
       </c>
     </row>
@@ -9907,12 +10006,12 @@
       </c>
       <c r="B55" s="27" t="inlineStr">
         <is>
-          <t>12:25PM</t>
+          <t>3:50PM</t>
         </is>
       </c>
       <c r="C55" s="27" t="inlineStr">
         <is>
-          <t>12:40PM</t>
+          <t>4:05PM</t>
         </is>
       </c>
       <c r="D55" s="27" t="inlineStr">
@@ -9925,17 +10024,17 @@
       </c>
       <c r="F55" s="27" t="inlineStr">
         <is>
-          <t>CM-U46-GB-8</t>
+          <t>CM-U46-GB-11</t>
         </is>
       </c>
       <c r="G55" s="27" t="inlineStr">
         <is>
-          <t>Board 3</t>
+          <t>Board 2</t>
         </is>
       </c>
       <c r="H55" s="27" t="inlineStr">
         <is>
-          <t>Amar Jain</t>
+          <t>Nikunj Jhala</t>
         </is>
       </c>
       <c r="I55" s="27" t="inlineStr">
@@ -9945,7 +10044,7 @@
       </c>
       <c r="J55" s="27" t="inlineStr">
         <is>
-          <t>Nilesh Bagaria</t>
+          <t>Vinit Padia</t>
         </is>
       </c>
     </row>
@@ -9957,12 +10056,12 @@
       </c>
       <c r="B56" s="28" t="inlineStr">
         <is>
-          <t>12:50PM</t>
+          <t>4:05PM</t>
         </is>
       </c>
       <c r="C56" s="28" t="inlineStr">
         <is>
-          <t>1:05PM</t>
+          <t>4:20PM</t>
         </is>
       </c>
       <c r="D56" s="28" t="inlineStr">
@@ -10007,12 +10106,12 @@
       </c>
       <c r="B57" s="27" t="inlineStr">
         <is>
-          <t>12:50PM</t>
+          <t>4:15PM</t>
         </is>
       </c>
       <c r="C57" s="27" t="inlineStr">
         <is>
-          <t>1:05PM</t>
+          <t>4:30PM</t>
         </is>
       </c>
       <c r="D57" s="27" t="inlineStr">
@@ -10057,12 +10156,12 @@
       </c>
       <c r="B58" s="28" t="inlineStr">
         <is>
-          <t>12:50PM</t>
+          <t>4:15PM</t>
         </is>
       </c>
       <c r="C58" s="28" t="inlineStr">
         <is>
-          <t>1:05PM</t>
+          <t>4:30PM</t>
         </is>
       </c>
       <c r="D58" s="28" t="inlineStr">
@@ -10107,17 +10206,17 @@
       </c>
       <c r="B59" s="27" t="inlineStr">
         <is>
-          <t>1:15PM</t>
+          <t>4:30PM</t>
         </is>
       </c>
       <c r="C59" s="27" t="inlineStr">
         <is>
-          <t>1:30PM</t>
+          <t>4:45PM</t>
         </is>
       </c>
       <c r="D59" s="27" t="inlineStr">
         <is>
-          <t>Under 46</t>
+          <t>Under 15</t>
         </is>
       </c>
       <c r="E59" s="27" t="n">
@@ -10125,17 +10224,17 @@
       </c>
       <c r="F59" s="27" t="inlineStr">
         <is>
-          <t>CM-U46-GB-13</t>
+          <t>CM-U15-2</t>
         </is>
       </c>
       <c r="G59" s="27" t="inlineStr">
         <is>
-          <t>Board 2</t>
+          <t>Board 1</t>
         </is>
       </c>
       <c r="H59" s="27" t="inlineStr">
         <is>
-          <t>Nikunj Jhala</t>
+          <t>Shaurya Tripathi</t>
         </is>
       </c>
       <c r="I59" s="27" t="inlineStr">
@@ -10145,7 +10244,7 @@
       </c>
       <c r="J59" s="27" t="inlineStr">
         <is>
-          <t>Amit Ranka</t>
+          <t>Yash agarwal</t>
         </is>
       </c>
     </row>
@@ -10157,12 +10256,12 @@
       </c>
       <c r="B60" s="28" t="inlineStr">
         <is>
-          <t>1:15PM</t>
+          <t>4:40PM</t>
         </is>
       </c>
       <c r="C60" s="28" t="inlineStr">
         <is>
-          <t>1:30PM</t>
+          <t>4:55PM</t>
         </is>
       </c>
       <c r="D60" s="28" t="inlineStr">
@@ -10175,17 +10274,17 @@
       </c>
       <c r="F60" s="28" t="inlineStr">
         <is>
-          <t>CM-U46-GB-14</t>
+          <t>CM-U46-GB-13</t>
         </is>
       </c>
       <c r="G60" s="28" t="inlineStr">
         <is>
-          <t>Board 3</t>
+          <t>Board 2</t>
         </is>
       </c>
       <c r="H60" s="28" t="inlineStr">
         <is>
-          <t>Mayank Aggarwal</t>
+          <t>Nikunj Jhala</t>
         </is>
       </c>
       <c r="I60" s="28" t="inlineStr">
@@ -10195,7 +10294,7 @@
       </c>
       <c r="J60" s="28" t="inlineStr">
         <is>
-          <t>Amar Jain</t>
+          <t>Amit Ranka</t>
         </is>
       </c>
     </row>
@@ -10207,17 +10306,17 @@
       </c>
       <c r="B61" s="27" t="inlineStr">
         <is>
-          <t>3:00PM</t>
+          <t>4:40PM</t>
         </is>
       </c>
       <c r="C61" s="27" t="inlineStr">
         <is>
-          <t>3:15PM</t>
+          <t>4:55PM</t>
         </is>
       </c>
       <c r="D61" s="27" t="inlineStr">
         <is>
-          <t>Above 46</t>
+          <t>Under 46</t>
         </is>
       </c>
       <c r="E61" s="27" t="n">
@@ -10225,7 +10324,7 @@
       </c>
       <c r="F61" s="27" t="inlineStr">
         <is>
-          <t>CM-A46-GB-1</t>
+          <t>CM-U46-GB-14</t>
         </is>
       </c>
       <c r="G61" s="27" t="inlineStr">
@@ -10235,7 +10334,7 @@
       </c>
       <c r="H61" s="27" t="inlineStr">
         <is>
-          <t>Vinod Agrawal</t>
+          <t>Mayank Aggarwal</t>
         </is>
       </c>
       <c r="I61" s="27" t="inlineStr">
@@ -10245,7 +10344,7 @@
       </c>
       <c r="J61" s="27" t="inlineStr">
         <is>
-          <t>Prasad Akshintala</t>
+          <t>Amar Jain</t>
         </is>
       </c>
     </row>
@@ -10257,17 +10356,17 @@
       </c>
       <c r="B62" s="28" t="inlineStr">
         <is>
-          <t>3:00PM</t>
+          <t>4:45PM</t>
         </is>
       </c>
       <c r="C62" s="28" t="inlineStr">
         <is>
-          <t>3:15PM</t>
+          <t>5:00PM</t>
         </is>
       </c>
       <c r="D62" s="28" t="inlineStr">
         <is>
-          <t>Under 15</t>
+          <t>Above 46</t>
         </is>
       </c>
       <c r="E62" s="28" t="n">
@@ -10275,7 +10374,7 @@
       </c>
       <c r="F62" s="28" t="inlineStr">
         <is>
-          <t>CM-U15-2</t>
+          <t>CM-A46-GA-2</t>
         </is>
       </c>
       <c r="G62" s="28" t="inlineStr">
@@ -10285,7 +10384,7 @@
       </c>
       <c r="H62" s="28" t="inlineStr">
         <is>
-          <t>Shaurya Tripathi</t>
+          <t>Adil Khan</t>
         </is>
       </c>
       <c r="I62" s="28" t="inlineStr">
@@ -10295,7 +10394,7 @@
       </c>
       <c r="J62" s="28" t="inlineStr">
         <is>
-          <t>Yash agarwal</t>
+          <t>Mr. Hiral Khadepau</t>
         </is>
       </c>
     </row>
@@ -10307,17 +10406,17 @@
       </c>
       <c r="B63" s="27" t="inlineStr">
         <is>
-          <t>3:00PM</t>
+          <t>4:55PM</t>
         </is>
       </c>
       <c r="C63" s="27" t="inlineStr">
         <is>
-          <t>3:15PM</t>
+          <t>5:10PM</t>
         </is>
       </c>
       <c r="D63" s="27" t="inlineStr">
         <is>
-          <t>Under 46</t>
+          <t>Above 46</t>
         </is>
       </c>
       <c r="E63" s="27" t="n">
@@ -10325,17 +10424,17 @@
       </c>
       <c r="F63" s="27" t="inlineStr">
         <is>
-          <t>CM-U46-GB-12</t>
+          <t>CM-A46-GB-1</t>
         </is>
       </c>
       <c r="G63" s="27" t="inlineStr">
         <is>
-          <t>Board 2</t>
+          <t>Board 3</t>
         </is>
       </c>
       <c r="H63" s="27" t="inlineStr">
         <is>
-          <t>Mayank Aggarwal</t>
+          <t>Vinod Agrawal</t>
         </is>
       </c>
       <c r="I63" s="27" t="inlineStr">
@@ -10345,7 +10444,7 @@
       </c>
       <c r="J63" s="27" t="inlineStr">
         <is>
-          <t>Nilesh Bagaria</t>
+          <t>Prasad Akshintala</t>
         </is>
       </c>
     </row>
@@ -10357,17 +10456,17 @@
       </c>
       <c r="B64" s="28" t="inlineStr">
         <is>
-          <t>3:15PM</t>
+          <t>5:00PM</t>
         </is>
       </c>
       <c r="C64" s="28" t="inlineStr">
         <is>
-          <t>3:30PM</t>
+          <t>5:15PM</t>
         </is>
       </c>
       <c r="D64" s="28" t="inlineStr">
         <is>
-          <t>Above 46</t>
+          <t>Under 46</t>
         </is>
       </c>
       <c r="E64" s="28" t="n">
@@ -10375,7 +10474,7 @@
       </c>
       <c r="F64" s="28" t="inlineStr">
         <is>
-          <t>CM-A46-GA-2</t>
+          <t>CM-U46-GA-15</t>
         </is>
       </c>
       <c r="G64" s="28" t="inlineStr">
@@ -10385,7 +10484,7 @@
       </c>
       <c r="H64" s="28" t="inlineStr">
         <is>
-          <t>Adil Khan</t>
+          <t>Dr Rahul Modi</t>
         </is>
       </c>
       <c r="I64" s="28" t="inlineStr">
@@ -10395,7 +10494,7 @@
       </c>
       <c r="J64" s="28" t="inlineStr">
         <is>
-          <t>Mr. Hiral Khadepau</t>
+          <t>Ankur Mahante</t>
         </is>
       </c>
     </row>
@@ -10407,17 +10506,17 @@
       </c>
       <c r="B65" s="27" t="inlineStr">
         <is>
-          <t>3:15PM</t>
+          <t>5:05PM</t>
         </is>
       </c>
       <c r="C65" s="27" t="inlineStr">
         <is>
-          <t>3:30PM</t>
+          <t>5:20PM</t>
         </is>
       </c>
       <c r="D65" s="27" t="inlineStr">
         <is>
-          <t>Above 46</t>
+          <t>Under 46</t>
         </is>
       </c>
       <c r="E65" s="27" t="n">
@@ -10425,7 +10524,7 @@
       </c>
       <c r="F65" s="27" t="inlineStr">
         <is>
-          <t>CM-A46-GB-2</t>
+          <t>CM-U46-GB-12</t>
         </is>
       </c>
       <c r="G65" s="27" t="inlineStr">
@@ -10435,7 +10534,7 @@
       </c>
       <c r="H65" s="27" t="inlineStr">
         <is>
-          <t>Sanjay Kumar</t>
+          <t>Mayank Aggarwal</t>
         </is>
       </c>
       <c r="I65" s="27" t="inlineStr">
@@ -10445,7 +10544,7 @@
       </c>
       <c r="J65" s="27" t="inlineStr">
         <is>
-          <t>Gopal Krishna</t>
+          <t>Nilesh Bagaria</t>
         </is>
       </c>
     </row>
@@ -10457,17 +10556,17 @@
       </c>
       <c r="B66" s="28" t="inlineStr">
         <is>
-          <t>3:30PM</t>
+          <t>5:20PM</t>
         </is>
       </c>
       <c r="C66" s="28" t="inlineStr">
         <is>
-          <t>3:45PM</t>
+          <t>5:35PM</t>
         </is>
       </c>
       <c r="D66" s="28" t="inlineStr">
         <is>
-          <t>Under 46</t>
+          <t>Above 46</t>
         </is>
       </c>
       <c r="E66" s="28" t="n">
@@ -10475,17 +10574,17 @@
       </c>
       <c r="F66" s="28" t="inlineStr">
         <is>
-          <t>CM-U46-GA-15</t>
+          <t>CM-A46-GB-2</t>
         </is>
       </c>
       <c r="G66" s="28" t="inlineStr">
         <is>
-          <t>Board 1</t>
+          <t>Board 2</t>
         </is>
       </c>
       <c r="H66" s="28" t="inlineStr">
         <is>
-          <t>Dr Rahul Modi</t>
+          <t>Sanjay Kumar</t>
         </is>
       </c>
       <c r="I66" s="28" t="inlineStr">
@@ -10495,7 +10594,7 @@
       </c>
       <c r="J66" s="28" t="inlineStr">
         <is>
-          <t>Ankur Mahante</t>
+          <t>Gopal Krishna</t>
         </is>
       </c>
     </row>
@@ -10507,12 +10606,12 @@
       </c>
       <c r="B67" s="27" t="inlineStr">
         <is>
-          <t>3:40PM</t>
+          <t>5:30PM</t>
         </is>
       </c>
       <c r="C67" s="27" t="inlineStr">
         <is>
-          <t>3:55PM</t>
+          <t>5:45PM</t>
         </is>
       </c>
       <c r="D67" s="27" t="inlineStr">
@@ -10525,17 +10624,17 @@
       </c>
       <c r="F67" s="27" t="inlineStr">
         <is>
-          <t>CM-A46-GB-3</t>
+          <t>CM-A46-GA-1</t>
         </is>
       </c>
       <c r="G67" s="27" t="inlineStr">
         <is>
-          <t>Board 2</t>
+          <t>Board 3</t>
         </is>
       </c>
       <c r="H67" s="27" t="inlineStr">
         <is>
-          <t>Vinod Agrawal</t>
+          <t>Vinay Sawant</t>
         </is>
       </c>
       <c r="I67" s="27" t="inlineStr">
@@ -10545,7 +10644,7 @@
       </c>
       <c r="J67" s="27" t="inlineStr">
         <is>
-          <t>Sanjay Kumar</t>
+          <t>Mukul Joshi</t>
         </is>
       </c>
     </row>
@@ -10557,12 +10656,12 @@
       </c>
       <c r="B68" s="28" t="inlineStr">
         <is>
-          <t>3:50PM</t>
+          <t>5:45PM</t>
         </is>
       </c>
       <c r="C68" s="28" t="inlineStr">
         <is>
-          <t>4:05PM</t>
+          <t>6:00PM</t>
         </is>
       </c>
       <c r="D68" s="28" t="inlineStr">
@@ -10575,17 +10674,17 @@
       </c>
       <c r="F68" s="28" t="inlineStr">
         <is>
-          <t>CM-A46-GA-1</t>
+          <t>CM-A46-GB-3</t>
         </is>
       </c>
       <c r="G68" s="28" t="inlineStr">
         <is>
-          <t>Board 3</t>
+          <t>Board 2</t>
         </is>
       </c>
       <c r="H68" s="28" t="inlineStr">
         <is>
-          <t>Vinay Sawant</t>
+          <t>Vinod Agrawal</t>
         </is>
       </c>
       <c r="I68" s="28" t="inlineStr">
@@ -10595,7 +10694,7 @@
       </c>
       <c r="J68" s="28" t="inlineStr">
         <is>
-          <t>Mukul Joshi</t>
+          <t>Sanjay Kumar</t>
         </is>
       </c>
     </row>
@@ -10607,12 +10706,12 @@
       </c>
       <c r="B69" s="27" t="inlineStr">
         <is>
-          <t>4:05PM</t>
+          <t>5:55PM</t>
         </is>
       </c>
       <c r="C69" s="27" t="inlineStr">
         <is>
-          <t>4:20PM</t>
+          <t>6:10PM</t>
         </is>
       </c>
       <c r="D69" s="27" t="inlineStr">
@@ -10625,17 +10724,17 @@
       </c>
       <c r="F69" s="27" t="inlineStr">
         <is>
-          <t>CM-A46-GB-5</t>
+          <t>CM-A46-GA-4</t>
         </is>
       </c>
       <c r="G69" s="27" t="inlineStr">
         <is>
-          <t>Board 1</t>
+          <t>Board 3</t>
         </is>
       </c>
       <c r="H69" s="27" t="inlineStr">
         <is>
-          <t>Vinod Agrawal</t>
+          <t>Mukul Joshi</t>
         </is>
       </c>
       <c r="I69" s="27" t="inlineStr">
@@ -10645,7 +10744,7 @@
       </c>
       <c r="J69" s="27" t="inlineStr">
         <is>
-          <t>Gopal Krishna</t>
+          <t>Mr. Hiral Khadepau</t>
         </is>
       </c>
     </row>
@@ -10657,12 +10756,12 @@
       </c>
       <c r="B70" s="28" t="inlineStr">
         <is>
-          <t>4:15PM</t>
+          <t>6:10PM</t>
         </is>
       </c>
       <c r="C70" s="28" t="inlineStr">
         <is>
-          <t>4:30PM</t>
+          <t>6:25PM</t>
         </is>
       </c>
       <c r="D70" s="28" t="inlineStr">
@@ -10675,17 +10774,17 @@
       </c>
       <c r="F70" s="28" t="inlineStr">
         <is>
-          <t>CM-A46-GA-4</t>
+          <t>CM-A46-GB-5</t>
         </is>
       </c>
       <c r="G70" s="28" t="inlineStr">
         <is>
-          <t>Board 3</t>
+          <t>Board 1</t>
         </is>
       </c>
       <c r="H70" s="28" t="inlineStr">
         <is>
-          <t>Mukul Joshi</t>
+          <t>Vinod Agrawal</t>
         </is>
       </c>
       <c r="I70" s="28" t="inlineStr">
@@ -10695,7 +10794,7 @@
       </c>
       <c r="J70" s="28" t="inlineStr">
         <is>
-          <t>Mr. Hiral Khadepau</t>
+          <t>Gopal Krishna</t>
         </is>
       </c>
     </row>
@@ -10707,12 +10806,12 @@
       </c>
       <c r="B71" s="27" t="inlineStr">
         <is>
-          <t>4:50PM</t>
+          <t>6:30PM</t>
         </is>
       </c>
       <c r="C71" s="27" t="inlineStr">
         <is>
-          <t>5:05PM</t>
+          <t>6:45PM</t>
         </is>
       </c>
       <c r="D71" s="27" t="inlineStr">
@@ -10757,12 +10856,12 @@
       </c>
       <c r="B72" s="28" t="inlineStr">
         <is>
-          <t>4:50PM</t>
+          <t>6:35PM</t>
         </is>
       </c>
       <c r="C72" s="28" t="inlineStr">
         <is>
-          <t>5:05PM</t>
+          <t>6:50PM</t>
         </is>
       </c>
       <c r="D72" s="28" t="inlineStr">
@@ -10807,12 +10906,12 @@
       </c>
       <c r="B73" s="27" t="inlineStr">
         <is>
-          <t>5:15PM</t>
+          <t>6:55PM</t>
         </is>
       </c>
       <c r="C73" s="27" t="inlineStr">
         <is>
-          <t>5:30PM</t>
+          <t>7:10PM</t>
         </is>
       </c>
       <c r="D73" s="27" t="inlineStr">
@@ -10857,12 +10956,12 @@
       </c>
       <c r="B74" s="28" t="inlineStr">
         <is>
-          <t>6:40PM</t>
+          <t>8:25PM</t>
         </is>
       </c>
       <c r="C74" s="28" t="inlineStr">
         <is>
-          <t>6:55PM</t>
+          <t>8:40PM</t>
         </is>
       </c>
       <c r="D74" s="28" t="inlineStr">
@@ -10907,12 +11006,12 @@
       </c>
       <c r="B75" s="27" t="inlineStr">
         <is>
-          <t>7:20PM</t>
+          <t>9:05PM</t>
         </is>
       </c>
       <c r="C75" s="27" t="inlineStr">
         <is>
-          <t>7:35PM</t>
+          <t>9:20PM</t>
         </is>
       </c>
       <c r="D75" s="27" t="inlineStr">
@@ -10957,12 +11056,12 @@
       </c>
       <c r="B76" s="28" t="inlineStr">
         <is>
-          <t>11:50AM</t>
+          <t>3:20PM</t>
         </is>
       </c>
       <c r="C76" s="28" t="inlineStr">
         <is>
-          <t>12:05PM</t>
+          <t>3:35PM</t>
         </is>
       </c>
       <c r="D76" s="28" t="inlineStr">
@@ -11007,12 +11106,12 @@
       </c>
       <c r="B77" s="27" t="inlineStr">
         <is>
-          <t>11:50AM</t>
+          <t>3:20PM</t>
         </is>
       </c>
       <c r="C77" s="27" t="inlineStr">
         <is>
-          <t>12:05PM</t>
+          <t>3:35PM</t>
         </is>
       </c>
       <c r="D77" s="27" t="inlineStr">
@@ -11057,12 +11156,12 @@
       </c>
       <c r="B78" s="28" t="inlineStr">
         <is>
-          <t>11:50AM</t>
+          <t>3:20PM</t>
         </is>
       </c>
       <c r="C78" s="28" t="inlineStr">
         <is>
-          <t>12:05PM</t>
+          <t>3:35PM</t>
         </is>
       </c>
       <c r="D78" s="28" t="inlineStr">
@@ -11107,12 +11206,12 @@
       </c>
       <c r="B79" s="27" t="inlineStr">
         <is>
-          <t>3:00PM</t>
+          <t>3:35PM</t>
         </is>
       </c>
       <c r="C79" s="27" t="inlineStr">
         <is>
-          <t>3:15PM</t>
+          <t>3:50PM</t>
         </is>
       </c>
       <c r="D79" s="27" t="inlineStr">
@@ -11157,12 +11256,12 @@
       </c>
       <c r="B80" s="28" t="inlineStr">
         <is>
-          <t>3:00PM</t>
+          <t>3:35PM</t>
         </is>
       </c>
       <c r="C80" s="28" t="inlineStr">
         <is>
-          <t>3:15PM</t>
+          <t>3:50PM</t>
         </is>
       </c>
       <c r="D80" s="28" t="inlineStr">
@@ -11207,12 +11306,12 @@
       </c>
       <c r="B81" s="27" t="inlineStr">
         <is>
-          <t>3:00PM</t>
+          <t>3:35PM</t>
         </is>
       </c>
       <c r="C81" s="27" t="inlineStr">
         <is>
-          <t>3:15PM</t>
+          <t>3:50PM</t>
         </is>
       </c>
       <c r="D81" s="27" t="inlineStr">
@@ -11257,12 +11356,12 @@
       </c>
       <c r="B82" s="28" t="inlineStr">
         <is>
-          <t>3:15PM</t>
+          <t>3:50PM</t>
         </is>
       </c>
       <c r="C82" s="28" t="inlineStr">
         <is>
-          <t>3:30PM</t>
+          <t>4:05PM</t>
         </is>
       </c>
       <c r="D82" s="28" t="inlineStr">
@@ -11896,12 +11995,12 @@
       </c>
       <c r="B25" s="27" t="inlineStr">
         <is>
-          <t>9:40AM</t>
+          <t>10:30AM</t>
         </is>
       </c>
       <c r="C25" s="27" t="inlineStr">
         <is>
-          <t>9:55AM</t>
+          <t>10:45AM</t>
         </is>
       </c>
       <c r="D25" s="27" t="inlineStr">
@@ -11946,12 +12045,12 @@
       </c>
       <c r="B26" s="28" t="inlineStr">
         <is>
-          <t>9:40AM</t>
+          <t>10:30AM</t>
         </is>
       </c>
       <c r="C26" s="28" t="inlineStr">
         <is>
-          <t>9:55AM</t>
+          <t>10:45AM</t>
         </is>
       </c>
       <c r="D26" s="28" t="inlineStr">
@@ -11996,12 +12095,12 @@
       </c>
       <c r="B27" s="27" t="inlineStr">
         <is>
-          <t>11:50AM</t>
+          <t>3:20PM</t>
         </is>
       </c>
       <c r="C27" s="27" t="inlineStr">
         <is>
-          <t>12:05PM</t>
+          <t>3:35PM</t>
         </is>
       </c>
       <c r="D27" s="27" t="inlineStr">
@@ -12335,12 +12434,12 @@
       </c>
       <c r="B28" s="27" t="inlineStr">
         <is>
-          <t>11:50AM</t>
+          <t>3:20PM</t>
         </is>
       </c>
       <c r="C28" s="27" t="inlineStr">
         <is>
-          <t>12:05PM</t>
+          <t>3:35PM</t>
         </is>
       </c>
       <c r="D28" s="27" t="inlineStr">
@@ -12385,12 +12484,12 @@
       </c>
       <c r="B29" s="28" t="inlineStr">
         <is>
-          <t>11:50AM</t>
+          <t>3:20PM</t>
         </is>
       </c>
       <c r="C29" s="28" t="inlineStr">
         <is>
-          <t>12:05PM</t>
+          <t>3:35PM</t>
         </is>
       </c>
       <c r="D29" s="28" t="inlineStr">
@@ -12435,12 +12534,12 @@
       </c>
       <c r="B30" s="27" t="inlineStr">
         <is>
-          <t>11:50AM</t>
+          <t>3:20PM</t>
         </is>
       </c>
       <c r="C30" s="27" t="inlineStr">
         <is>
-          <t>12:05PM</t>
+          <t>3:35PM</t>
         </is>
       </c>
       <c r="D30" s="27" t="inlineStr">
@@ -12485,12 +12584,12 @@
       </c>
       <c r="B31" s="28" t="inlineStr">
         <is>
-          <t>3:00PM</t>
+          <t>3:35PM</t>
         </is>
       </c>
       <c r="C31" s="28" t="inlineStr">
         <is>
-          <t>3:15PM</t>
+          <t>3:50PM</t>
         </is>
       </c>
       <c r="D31" s="28" t="inlineStr">
@@ -12535,12 +12634,12 @@
       </c>
       <c r="B32" s="27" t="inlineStr">
         <is>
-          <t>3:00PM</t>
+          <t>3:35PM</t>
         </is>
       </c>
       <c r="C32" s="27" t="inlineStr">
         <is>
-          <t>3:15PM</t>
+          <t>3:50PM</t>
         </is>
       </c>
       <c r="D32" s="27" t="inlineStr">
@@ -12585,12 +12684,12 @@
       </c>
       <c r="B33" s="28" t="inlineStr">
         <is>
-          <t>3:00PM</t>
+          <t>3:35PM</t>
         </is>
       </c>
       <c r="C33" s="28" t="inlineStr">
         <is>
-          <t>3:15PM</t>
+          <t>3:50PM</t>
         </is>
       </c>
       <c r="D33" s="28" t="inlineStr">
@@ -12635,12 +12734,12 @@
       </c>
       <c r="B34" s="27" t="inlineStr">
         <is>
-          <t>3:15PM</t>
+          <t>3:50PM</t>
         </is>
       </c>
       <c r="C34" s="27" t="inlineStr">
         <is>
-          <t>3:30PM</t>
+          <t>4:05PM</t>
         </is>
       </c>
       <c r="D34" s="27" t="inlineStr">
@@ -12685,12 +12784,12 @@
       </c>
       <c r="B35" s="28" t="inlineStr">
         <is>
-          <t>3:15PM</t>
+          <t>3:50PM</t>
         </is>
       </c>
       <c r="C35" s="28" t="inlineStr">
         <is>
-          <t>3:30PM</t>
+          <t>4:05PM</t>
         </is>
       </c>
       <c r="D35" s="28" t="inlineStr">
@@ -12735,12 +12834,12 @@
       </c>
       <c r="B36" s="27" t="inlineStr">
         <is>
-          <t>3:15PM</t>
+          <t>3:50PM</t>
         </is>
       </c>
       <c r="C36" s="27" t="inlineStr">
         <is>
-          <t>3:30PM</t>
+          <t>4:05PM</t>
         </is>
       </c>
       <c r="D36" s="27" t="inlineStr">
@@ -12785,12 +12884,12 @@
       </c>
       <c r="B37" s="28" t="inlineStr">
         <is>
-          <t>3:30PM</t>
+          <t>4:05PM</t>
         </is>
       </c>
       <c r="C37" s="28" t="inlineStr">
         <is>
-          <t>3:45PM</t>
+          <t>4:20PM</t>
         </is>
       </c>
       <c r="D37" s="28" t="inlineStr">
@@ -12835,12 +12934,12 @@
       </c>
       <c r="B38" s="27" t="inlineStr">
         <is>
-          <t>3:30PM</t>
+          <t>4:05PM</t>
         </is>
       </c>
       <c r="C38" s="27" t="inlineStr">
         <is>
-          <t>3:45PM</t>
+          <t>4:20PM</t>
         </is>
       </c>
       <c r="D38" s="27" t="inlineStr">
@@ -12885,12 +12984,12 @@
       </c>
       <c r="B39" s="28" t="inlineStr">
         <is>
-          <t>3:45PM</t>
+          <t>4:20PM</t>
         </is>
       </c>
       <c r="C39" s="28" t="inlineStr">
         <is>
-          <t>4:00PM</t>
+          <t>4:35PM</t>
         </is>
       </c>
       <c r="D39" s="28" t="inlineStr">
@@ -12935,12 +13034,12 @@
       </c>
       <c r="B40" s="27" t="inlineStr">
         <is>
-          <t>3:45PM</t>
+          <t>4:20PM</t>
         </is>
       </c>
       <c r="C40" s="27" t="inlineStr">
         <is>
-          <t>4:00PM</t>
+          <t>4:35PM</t>
         </is>
       </c>
       <c r="D40" s="27" t="inlineStr">
@@ -12985,12 +13084,12 @@
       </c>
       <c r="B41" s="28" t="inlineStr">
         <is>
-          <t>4:00PM</t>
+          <t>4:35PM</t>
         </is>
       </c>
       <c r="C41" s="28" t="inlineStr">
         <is>
-          <t>4:15PM</t>
+          <t>4:50PM</t>
         </is>
       </c>
       <c r="D41" s="28" t="inlineStr">
@@ -14158,12 +14257,12 @@
       </c>
       <c r="B46" s="27" t="inlineStr">
         <is>
-          <t>11:50AM</t>
+          <t>3:00PM</t>
         </is>
       </c>
       <c r="C46" s="27" t="inlineStr">
         <is>
-          <t>12:10PM</t>
+          <t>3:20PM</t>
         </is>
       </c>
       <c r="D46" s="27" t="inlineStr">
@@ -14208,12 +14307,12 @@
       </c>
       <c r="B47" s="28" t="inlineStr">
         <is>
-          <t>11:50AM</t>
+          <t>3:15PM</t>
         </is>
       </c>
       <c r="C47" s="28" t="inlineStr">
         <is>
-          <t>12:10PM</t>
+          <t>3:35PM</t>
         </is>
       </c>
       <c r="D47" s="28" t="inlineStr">
@@ -14258,12 +14357,12 @@
       </c>
       <c r="B48" s="27" t="inlineStr">
         <is>
-          <t>12:10PM</t>
+          <t>3:20PM</t>
         </is>
       </c>
       <c r="C48" s="27" t="inlineStr">
         <is>
-          <t>12:30PM</t>
+          <t>3:40PM</t>
         </is>
       </c>
       <c r="D48" s="27" t="inlineStr">
@@ -14308,12 +14407,12 @@
       </c>
       <c r="B49" s="28" t="inlineStr">
         <is>
-          <t>12:10PM</t>
+          <t>3:35PM</t>
         </is>
       </c>
       <c r="C49" s="28" t="inlineStr">
         <is>
-          <t>12:30PM</t>
+          <t>3:55PM</t>
         </is>
       </c>
       <c r="D49" s="28" t="inlineStr">
@@ -14358,12 +14457,12 @@
       </c>
       <c r="B50" s="27" t="inlineStr">
         <is>
-          <t>12:30PM</t>
+          <t>3:50PM</t>
         </is>
       </c>
       <c r="C50" s="27" t="inlineStr">
         <is>
-          <t>12:50PM</t>
+          <t>4:10PM</t>
         </is>
       </c>
       <c r="D50" s="27" t="inlineStr">
@@ -14376,17 +14475,17 @@
       </c>
       <c r="F50" s="27" t="inlineStr">
         <is>
-          <t>2639-GB-8</t>
+          <t>2639-GA-9</t>
         </is>
       </c>
       <c r="G50" s="27" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H50" s="27" t="inlineStr">
         <is>
-          <t>Ankur Mahante</t>
+          <t>Ravi Modi</t>
         </is>
       </c>
       <c r="I50" s="27" t="inlineStr">
@@ -14396,7 +14495,7 @@
       </c>
       <c r="J50" s="27" t="inlineStr">
         <is>
-          <t>Tanmay Sharma</t>
+          <t>Tej</t>
         </is>
       </c>
     </row>
@@ -14408,12 +14507,12 @@
       </c>
       <c r="B51" s="28" t="inlineStr">
         <is>
-          <t>12:40PM</t>
+          <t>3:55PM</t>
         </is>
       </c>
       <c r="C51" s="28" t="inlineStr">
         <is>
-          <t>1:00PM</t>
+          <t>4:15PM</t>
         </is>
       </c>
       <c r="D51" s="28" t="inlineStr">
@@ -14426,17 +14525,17 @@
       </c>
       <c r="F51" s="28" t="inlineStr">
         <is>
-          <t>2639-GA-9</t>
+          <t>2639-GB-8</t>
         </is>
       </c>
       <c r="G51" s="28" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H51" s="28" t="inlineStr">
         <is>
-          <t>Ravi Modi</t>
+          <t>Ankur Mahante</t>
         </is>
       </c>
       <c r="I51" s="28" t="inlineStr">
@@ -14446,7 +14545,7 @@
       </c>
       <c r="J51" s="28" t="inlineStr">
         <is>
-          <t>Tej</t>
+          <t>Tanmay Sharma</t>
         </is>
       </c>
     </row>
@@ -14458,12 +14557,12 @@
       </c>
       <c r="B52" s="27" t="inlineStr">
         <is>
-          <t>3:00PM</t>
+          <t>4:15PM</t>
         </is>
       </c>
       <c r="C52" s="27" t="inlineStr">
         <is>
-          <t>3:20PM</t>
+          <t>4:35PM</t>
         </is>
       </c>
       <c r="D52" s="27" t="inlineStr">
@@ -14476,17 +14575,17 @@
       </c>
       <c r="F52" s="27" t="inlineStr">
         <is>
-          <t>40P-GA-2</t>
+          <t>40P-GB-1</t>
         </is>
       </c>
       <c r="G52" s="27" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H52" s="27" t="inlineStr">
         <is>
-          <t>Vinit Padia</t>
+          <t>Vinay Sawant</t>
         </is>
       </c>
       <c r="I52" s="27" t="inlineStr">
@@ -14496,7 +14595,7 @@
       </c>
       <c r="J52" s="27" t="inlineStr">
         <is>
-          <t>Amit Ranka</t>
+          <t>Mukul Joshi</t>
         </is>
       </c>
     </row>
@@ -14508,12 +14607,12 @@
       </c>
       <c r="B53" s="28" t="inlineStr">
         <is>
-          <t>3:00PM</t>
+          <t>4:55PM</t>
         </is>
       </c>
       <c r="C53" s="28" t="inlineStr">
         <is>
-          <t>3:20PM</t>
+          <t>5:15PM</t>
         </is>
       </c>
       <c r="D53" s="28" t="inlineStr">
@@ -14526,17 +14625,17 @@
       </c>
       <c r="F53" s="28" t="inlineStr">
         <is>
-          <t>40P-GB-1</t>
+          <t>40P-GA-2</t>
         </is>
       </c>
       <c r="G53" s="28" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H53" s="28" t="inlineStr">
         <is>
-          <t>Vinay Sawant</t>
+          <t>Vinit Padia</t>
         </is>
       </c>
       <c r="I53" s="28" t="inlineStr">
@@ -14546,7 +14645,7 @@
       </c>
       <c r="J53" s="28" t="inlineStr">
         <is>
-          <t>Mukul Joshi</t>
+          <t>Amit Ranka</t>
         </is>
       </c>
     </row>
@@ -14558,12 +14657,12 @@
       </c>
       <c r="B54" s="27" t="inlineStr">
         <is>
-          <t>3:20PM</t>
+          <t>5:10PM</t>
         </is>
       </c>
       <c r="C54" s="27" t="inlineStr">
         <is>
-          <t>3:40PM</t>
+          <t>5:30PM</t>
         </is>
       </c>
       <c r="D54" s="27" t="inlineStr">
@@ -14576,17 +14675,17 @@
       </c>
       <c r="F54" s="27" t="inlineStr">
         <is>
-          <t>40P-GA-3</t>
+          <t>40P-GB-7</t>
         </is>
       </c>
       <c r="G54" s="27" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H54" s="27" t="inlineStr">
         <is>
-          <t>Piyush Makharia</t>
+          <t>Vinay Sawant</t>
         </is>
       </c>
       <c r="I54" s="27" t="inlineStr">
@@ -14596,7 +14695,7 @@
       </c>
       <c r="J54" s="27" t="inlineStr">
         <is>
-          <t>Oscar Dsa</t>
+          <t>Prasad Akshintala</t>
         </is>
       </c>
     </row>
@@ -14608,12 +14707,12 @@
       </c>
       <c r="B55" s="28" t="inlineStr">
         <is>
-          <t>3:30PM</t>
+          <t>5:15PM</t>
         </is>
       </c>
       <c r="C55" s="28" t="inlineStr">
         <is>
-          <t>3:50PM</t>
+          <t>5:35PM</t>
         </is>
       </c>
       <c r="D55" s="28" t="inlineStr">
@@ -14626,17 +14725,17 @@
       </c>
       <c r="F55" s="28" t="inlineStr">
         <is>
-          <t>40P-GB-7</t>
+          <t>40P-GA-3</t>
         </is>
       </c>
       <c r="G55" s="28" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H55" s="28" t="inlineStr">
         <is>
-          <t>Vinay Sawant</t>
+          <t>Piyush Makharia</t>
         </is>
       </c>
       <c r="I55" s="28" t="inlineStr">
@@ -14646,7 +14745,7 @@
       </c>
       <c r="J55" s="28" t="inlineStr">
         <is>
-          <t>Prasad Akshintala</t>
+          <t>Oscar Dsa</t>
         </is>
       </c>
     </row>
@@ -14658,12 +14757,12 @@
       </c>
       <c r="B56" s="27" t="inlineStr">
         <is>
-          <t>3:50PM</t>
+          <t>5:40PM</t>
         </is>
       </c>
       <c r="C56" s="27" t="inlineStr">
         <is>
-          <t>4:10PM</t>
+          <t>6:00PM</t>
         </is>
       </c>
       <c r="D56" s="27" t="inlineStr">
@@ -14676,17 +14775,17 @@
       </c>
       <c r="F56" s="27" t="inlineStr">
         <is>
-          <t>40P-GA-5</t>
+          <t>40P-GB-2</t>
         </is>
       </c>
       <c r="G56" s="27" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H56" s="27" t="inlineStr">
         <is>
-          <t>Amit Ranka</t>
+          <t>Adil Khan</t>
         </is>
       </c>
       <c r="I56" s="27" t="inlineStr">
@@ -14696,7 +14795,7 @@
       </c>
       <c r="J56" s="27" t="inlineStr">
         <is>
-          <t>Oscar Dsa</t>
+          <t>Prasad Akshintala</t>
         </is>
       </c>
     </row>
@@ -14708,12 +14807,12 @@
       </c>
       <c r="B57" s="28" t="inlineStr">
         <is>
-          <t>4:00PM</t>
+          <t>5:45PM</t>
         </is>
       </c>
       <c r="C57" s="28" t="inlineStr">
         <is>
-          <t>4:20PM</t>
+          <t>6:05PM</t>
         </is>
       </c>
       <c r="D57" s="28" t="inlineStr">
@@ -14726,17 +14825,17 @@
       </c>
       <c r="F57" s="28" t="inlineStr">
         <is>
-          <t>40P-GB-2</t>
+          <t>40P-GA-5</t>
         </is>
       </c>
       <c r="G57" s="28" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H57" s="28" t="inlineStr">
         <is>
-          <t>Adil Khan</t>
+          <t>Amit Ranka</t>
         </is>
       </c>
       <c r="I57" s="28" t="inlineStr">
@@ -14746,7 +14845,7 @@
       </c>
       <c r="J57" s="28" t="inlineStr">
         <is>
-          <t>Prasad Akshintala</t>
+          <t>Oscar Dsa</t>
         </is>
       </c>
     </row>
@@ -14758,12 +14857,12 @@
       </c>
       <c r="B58" s="27" t="inlineStr">
         <is>
-          <t>4:30PM</t>
+          <t>6:10PM</t>
         </is>
       </c>
       <c r="C58" s="27" t="inlineStr">
         <is>
-          <t>4:50PM</t>
+          <t>6:30PM</t>
         </is>
       </c>
       <c r="D58" s="27" t="inlineStr">
@@ -14808,12 +14907,12 @@
       </c>
       <c r="B59" s="28" t="inlineStr">
         <is>
-          <t>4:30PM</t>
+          <t>6:10PM</t>
         </is>
       </c>
       <c r="C59" s="28" t="inlineStr">
         <is>
-          <t>4:50PM</t>
+          <t>6:30PM</t>
         </is>
       </c>
       <c r="D59" s="28" t="inlineStr">
@@ -14858,12 +14957,12 @@
       </c>
       <c r="B60" s="27" t="inlineStr">
         <is>
-          <t>4:50PM</t>
+          <t>6:30PM</t>
         </is>
       </c>
       <c r="C60" s="27" t="inlineStr">
         <is>
-          <t>5:10PM</t>
+          <t>6:50PM</t>
         </is>
       </c>
       <c r="D60" s="27" t="inlineStr">
@@ -14908,12 +15007,12 @@
       </c>
       <c r="B61" s="28" t="inlineStr">
         <is>
-          <t>5:00PM</t>
+          <t>6:40PM</t>
         </is>
       </c>
       <c r="C61" s="28" t="inlineStr">
         <is>
-          <t>5:20PM</t>
+          <t>7:00PM</t>
         </is>
       </c>
       <c r="D61" s="28" t="inlineStr">
@@ -14958,12 +15057,12 @@
       </c>
       <c r="B62" s="27" t="inlineStr">
         <is>
-          <t>5:10PM</t>
+          <t>6:50PM</t>
         </is>
       </c>
       <c r="C62" s="27" t="inlineStr">
         <is>
-          <t>5:30PM</t>
+          <t>7:10PM</t>
         </is>
       </c>
       <c r="D62" s="27" t="inlineStr">
@@ -15008,12 +15107,12 @@
       </c>
       <c r="B63" s="28" t="inlineStr">
         <is>
-          <t>5:20PM</t>
+          <t>7:00PM</t>
         </is>
       </c>
       <c r="C63" s="28" t="inlineStr">
         <is>
-          <t>5:40PM</t>
+          <t>7:20PM</t>
         </is>
       </c>
       <c r="D63" s="28" t="inlineStr">
@@ -15058,12 +15157,12 @@
       </c>
       <c r="B64" s="27" t="inlineStr">
         <is>
-          <t>5:40PM</t>
+          <t>7:20PM</t>
         </is>
       </c>
       <c r="C64" s="27" t="inlineStr">
         <is>
-          <t>6:00PM</t>
+          <t>7:40PM</t>
         </is>
       </c>
       <c r="D64" s="27" t="inlineStr">
@@ -15108,12 +15207,12 @@
       </c>
       <c r="B65" s="28" t="inlineStr">
         <is>
-          <t>5:50PM</t>
+          <t>7:35PM</t>
         </is>
       </c>
       <c r="C65" s="28" t="inlineStr">
         <is>
-          <t>6:10PM</t>
+          <t>7:55PM</t>
         </is>
       </c>
       <c r="D65" s="28" t="inlineStr">
@@ -15158,12 +15257,12 @@
       </c>
       <c r="B66" s="27" t="inlineStr">
         <is>
-          <t>6:10PM</t>
+          <t>7:55PM</t>
         </is>
       </c>
       <c r="C66" s="27" t="inlineStr">
         <is>
-          <t>6:30PM</t>
+          <t>8:15PM</t>
         </is>
       </c>
       <c r="D66" s="27" t="inlineStr">
@@ -15208,12 +15307,12 @@
       </c>
       <c r="B67" s="28" t="inlineStr">
         <is>
-          <t>6:20PM</t>
+          <t>8:05PM</t>
         </is>
       </c>
       <c r="C67" s="28" t="inlineStr">
         <is>
-          <t>6:40PM</t>
+          <t>8:25PM</t>
         </is>
       </c>
       <c r="D67" s="28" t="inlineStr">
@@ -15258,12 +15357,12 @@
       </c>
       <c r="B68" s="27" t="inlineStr">
         <is>
-          <t>6:40PM</t>
+          <t>8:25PM</t>
         </is>
       </c>
       <c r="C68" s="27" t="inlineStr">
         <is>
-          <t>7:00PM</t>
+          <t>8:45PM</t>
         </is>
       </c>
       <c r="D68" s="27" t="inlineStr">
@@ -15308,12 +15407,12 @@
       </c>
       <c r="B69" s="28" t="inlineStr">
         <is>
-          <t>6:40PM</t>
+          <t>8:25PM</t>
         </is>
       </c>
       <c r="C69" s="28" t="inlineStr">
         <is>
-          <t>7:00PM</t>
+          <t>8:45PM</t>
         </is>
       </c>
       <c r="D69" s="28" t="inlineStr">
@@ -15358,12 +15457,12 @@
       </c>
       <c r="B70" s="27" t="inlineStr">
         <is>
-          <t>7:00PM</t>
+          <t>8:45PM</t>
         </is>
       </c>
       <c r="C70" s="27" t="inlineStr">
         <is>
-          <t>7:20PM</t>
+          <t>9:05PM</t>
         </is>
       </c>
       <c r="D70" s="27" t="inlineStr">
@@ -15408,12 +15507,12 @@
       </c>
       <c r="B71" s="28" t="inlineStr">
         <is>
-          <t>7:00PM</t>
+          <t>8:45PM</t>
         </is>
       </c>
       <c r="C71" s="28" t="inlineStr">
         <is>
-          <t>7:20PM</t>
+          <t>9:05PM</t>
         </is>
       </c>
       <c r="D71" s="28" t="inlineStr">
@@ -15458,12 +15557,12 @@
       </c>
       <c r="B72" s="27" t="inlineStr">
         <is>
-          <t>7:20PM</t>
+          <t>9:05PM</t>
         </is>
       </c>
       <c r="C72" s="27" t="inlineStr">
         <is>
-          <t>7:40PM</t>
+          <t>9:25PM</t>
         </is>
       </c>
       <c r="D72" s="27" t="inlineStr">
@@ -15508,12 +15607,12 @@
       </c>
       <c r="B73" s="28" t="inlineStr">
         <is>
-          <t>7:20PM</t>
+          <t>9:05PM</t>
         </is>
       </c>
       <c r="C73" s="28" t="inlineStr">
         <is>
-          <t>7:40PM</t>
+          <t>9:25PM</t>
         </is>
       </c>
       <c r="D73" s="28" t="inlineStr">
@@ -15558,12 +15657,12 @@
       </c>
       <c r="B74" s="27" t="inlineStr">
         <is>
-          <t>7:40PM</t>
+          <t>9:25PM</t>
         </is>
       </c>
       <c r="C74" s="27" t="inlineStr">
         <is>
-          <t>8:00PM</t>
+          <t>9:45PM</t>
         </is>
       </c>
       <c r="D74" s="27" t="inlineStr">
@@ -15608,12 +15707,12 @@
       </c>
       <c r="B75" s="28" t="inlineStr">
         <is>
-          <t>7:50PM</t>
+          <t>9:35PM</t>
         </is>
       </c>
       <c r="C75" s="28" t="inlineStr">
         <is>
-          <t>8:10PM</t>
+          <t>9:55PM</t>
         </is>
       </c>
       <c r="D75" s="28" t="inlineStr">
@@ -15658,12 +15757,12 @@
       </c>
       <c r="B76" s="27" t="inlineStr">
         <is>
-          <t>8:10PM</t>
+          <t>9:55PM</t>
         </is>
       </c>
       <c r="C76" s="27" t="inlineStr">
         <is>
-          <t>8:30PM</t>
+          <t>10:15PM</t>
         </is>
       </c>
       <c r="D76" s="27" t="inlineStr">
@@ -15708,12 +15807,12 @@
       </c>
       <c r="B77" s="28" t="inlineStr">
         <is>
-          <t>8:10PM</t>
+          <t>9:55PM</t>
         </is>
       </c>
       <c r="C77" s="28" t="inlineStr">
         <is>
-          <t>8:30PM</t>
+          <t>10:15PM</t>
         </is>
       </c>
       <c r="D77" s="28" t="inlineStr">
@@ -15753,17 +15852,17 @@
     <row r="78">
       <c r="A78" s="27" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B78" s="27" t="inlineStr">
         <is>
-          <t>8:35PM</t>
+          <t>8:00AM</t>
         </is>
       </c>
       <c r="C78" s="27" t="inlineStr">
         <is>
-          <t>8:55PM</t>
+          <t>8:20AM</t>
         </is>
       </c>
       <c r="D78" s="27" t="inlineStr">
@@ -15776,17 +15875,17 @@
       </c>
       <c r="F78" s="27" t="inlineStr">
         <is>
-          <t>U26-GA-3</t>
+          <t>U26-GB-2</t>
         </is>
       </c>
       <c r="G78" s="27" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H78" s="27" t="inlineStr">
         <is>
-          <t>Aadit Joshi</t>
+          <t>Pranit Shriyan</t>
         </is>
       </c>
       <c r="I78" s="27" t="inlineStr">
@@ -15796,24 +15895,24 @@
       </c>
       <c r="J78" s="27" t="inlineStr">
         <is>
-          <t>Sankalp Bhatnagar</t>
+          <t>Rahul Garg</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="28" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B79" s="28" t="inlineStr">
         <is>
-          <t>8:40PM</t>
+          <t>8:15AM</t>
         </is>
       </c>
       <c r="C79" s="28" t="inlineStr">
         <is>
-          <t>9:00PM</t>
+          <t>8:35AM</t>
         </is>
       </c>
       <c r="D79" s="28" t="inlineStr">
@@ -15826,17 +15925,17 @@
       </c>
       <c r="F79" s="28" t="inlineStr">
         <is>
-          <t>U26-GB-2</t>
+          <t>U26-GA-3</t>
         </is>
       </c>
       <c r="G79" s="28" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H79" s="28" t="inlineStr">
         <is>
-          <t>Pranit Shriyan</t>
+          <t>Aadit Joshi</t>
         </is>
       </c>
       <c r="I79" s="28" t="inlineStr">
@@ -15846,7 +15945,7 @@
       </c>
       <c r="J79" s="28" t="inlineStr">
         <is>
-          <t>Rahul Garg</t>
+          <t>Sankalp Bhatnagar</t>
         </is>
       </c>
     </row>
@@ -15858,12 +15957,12 @@
       </c>
       <c r="B80" s="27" t="inlineStr">
         <is>
-          <t>8:00AM</t>
+          <t>8:35AM</t>
         </is>
       </c>
       <c r="C80" s="27" t="inlineStr">
         <is>
-          <t>8:20AM</t>
+          <t>8:55AM</t>
         </is>
       </c>
       <c r="D80" s="27" t="inlineStr">
@@ -15876,17 +15975,17 @@
       </c>
       <c r="F80" s="27" t="inlineStr">
         <is>
-          <t>U26-GA-5</t>
+          <t>U26-GB-4</t>
         </is>
       </c>
       <c r="G80" s="27" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H80" s="27" t="inlineStr">
         <is>
-          <t>Aadit Joshi</t>
+          <t>Ishaan Merchant</t>
         </is>
       </c>
       <c r="I80" s="27" t="inlineStr">
@@ -15896,7 +15995,7 @@
       </c>
       <c r="J80" s="27" t="inlineStr">
         <is>
-          <t>Rutvij sawant</t>
+          <t>Rahul Garg</t>
         </is>
       </c>
     </row>
@@ -15908,12 +16007,12 @@
       </c>
       <c r="B81" s="28" t="inlineStr">
         <is>
-          <t>8:00AM</t>
+          <t>8:45AM</t>
         </is>
       </c>
       <c r="C81" s="28" t="inlineStr">
         <is>
-          <t>8:20AM</t>
+          <t>9:05AM</t>
         </is>
       </c>
       <c r="D81" s="28" t="inlineStr">
@@ -15926,17 +16025,17 @@
       </c>
       <c r="F81" s="28" t="inlineStr">
         <is>
-          <t>U26-GB-4</t>
+          <t>U26-GA-5</t>
         </is>
       </c>
       <c r="G81" s="28" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H81" s="28" t="inlineStr">
         <is>
-          <t>Ishaan Merchant</t>
+          <t>Aadit Joshi</t>
         </is>
       </c>
       <c r="I81" s="28" t="inlineStr">
@@ -15946,7 +16045,7 @@
       </c>
       <c r="J81" s="28" t="inlineStr">
         <is>
-          <t>Rahul Garg</t>
+          <t>Rutvij sawant</t>
         </is>
       </c>
     </row>
@@ -15958,12 +16057,12 @@
       </c>
       <c r="B82" s="27" t="inlineStr">
         <is>
-          <t>8:30AM</t>
+          <t>9:05AM</t>
         </is>
       </c>
       <c r="C82" s="27" t="inlineStr">
         <is>
-          <t>8:50AM</t>
+          <t>9:25AM</t>
         </is>
       </c>
       <c r="D82" s="27" t="inlineStr">
@@ -16008,12 +16107,12 @@
       </c>
       <c r="B83" s="28" t="inlineStr">
         <is>
-          <t>8:45AM</t>
+          <t>9:50AM</t>
         </is>
       </c>
       <c r="C83" s="28" t="inlineStr">
         <is>
-          <t>9:05AM</t>
+          <t>10:10AM</t>
         </is>
       </c>
       <c r="D83" s="28" t="inlineStr">
@@ -16058,12 +16157,12 @@
       </c>
       <c r="B84" s="27" t="inlineStr">
         <is>
-          <t>11:50AM</t>
+          <t>3:20PM</t>
         </is>
       </c>
       <c r="C84" s="27" t="inlineStr">
         <is>
-          <t>12:10PM</t>
+          <t>3:40PM</t>
         </is>
       </c>
       <c r="D84" s="27" t="inlineStr">
@@ -16108,12 +16207,12 @@
       </c>
       <c r="B85" s="28" t="inlineStr">
         <is>
-          <t>11:50AM</t>
+          <t>3:20PM</t>
         </is>
       </c>
       <c r="C85" s="28" t="inlineStr">
         <is>
-          <t>12:10PM</t>
+          <t>3:40PM</t>
         </is>
       </c>
       <c r="D85" s="28" t="inlineStr">
@@ -16158,12 +16257,12 @@
       </c>
       <c r="B86" s="27" t="inlineStr">
         <is>
-          <t>3:00PM</t>
+          <t>3:40PM</t>
         </is>
       </c>
       <c r="C86" s="27" t="inlineStr">
         <is>
-          <t>3:20PM</t>
+          <t>4:00PM</t>
         </is>
       </c>
       <c r="D86" s="27" t="inlineStr">
@@ -16208,12 +16307,12 @@
       </c>
       <c r="B87" s="28" t="inlineStr">
         <is>
-          <t>3:00PM</t>
+          <t>3:40PM</t>
         </is>
       </c>
       <c r="C87" s="28" t="inlineStr">
         <is>
-          <t>3:20PM</t>
+          <t>4:00PM</t>
         </is>
       </c>
       <c r="D87" s="28" t="inlineStr">
@@ -16258,12 +16357,12 @@
       </c>
       <c r="B88" s="27" t="inlineStr">
         <is>
-          <t>3:20PM</t>
+          <t>4:00PM</t>
         </is>
       </c>
       <c r="C88" s="27" t="inlineStr">
         <is>
-          <t>3:40PM</t>
+          <t>4:20PM</t>
         </is>
       </c>
       <c r="D88" s="27" t="inlineStr">
@@ -16308,12 +16407,12 @@
       </c>
       <c r="B89" s="28" t="inlineStr">
         <is>
-          <t>3:20PM</t>
+          <t>4:00PM</t>
         </is>
       </c>
       <c r="C89" s="28" t="inlineStr">
         <is>
-          <t>3:40PM</t>
+          <t>4:20PM</t>
         </is>
       </c>
       <c r="D89" s="28" t="inlineStr">
@@ -16358,12 +16457,12 @@
       </c>
       <c r="B90" s="27" t="inlineStr">
         <is>
-          <t>3:40PM</t>
+          <t>4:20PM</t>
         </is>
       </c>
       <c r="C90" s="27" t="inlineStr">
         <is>
-          <t>4:00PM</t>
+          <t>4:40PM</t>
         </is>
       </c>
       <c r="D90" s="27" t="inlineStr">
@@ -16408,12 +16507,12 @@
       </c>
       <c r="B91" s="28" t="inlineStr">
         <is>
-          <t>3:40PM</t>
+          <t>4:20PM</t>
         </is>
       </c>
       <c r="C91" s="28" t="inlineStr">
         <is>
-          <t>4:00PM</t>
+          <t>4:40PM</t>
         </is>
       </c>
       <c r="D91" s="28" t="inlineStr">
@@ -16458,12 +16557,12 @@
       </c>
       <c r="B92" s="27" t="inlineStr">
         <is>
-          <t>4:00PM</t>
+          <t>4:40PM</t>
         </is>
       </c>
       <c r="C92" s="27" t="inlineStr">
         <is>
-          <t>4:20PM</t>
+          <t>5:00PM</t>
         </is>
       </c>
       <c r="D92" s="27" t="inlineStr">
@@ -17534,12 +17633,12 @@
       </c>
       <c r="B50" s="28" t="inlineStr">
         <is>
-          <t>9:30AM</t>
+          <t>10:30AM</t>
         </is>
       </c>
       <c r="C50" s="28" t="inlineStr">
         <is>
-          <t>9:50AM</t>
+          <t>10:50AM</t>
         </is>
       </c>
       <c r="D50" s="28" t="inlineStr">
@@ -17552,17 +17651,17 @@
       </c>
       <c r="F50" s="28" t="inlineStr">
         <is>
-          <t>U11-5</t>
+          <t>U11-4</t>
         </is>
       </c>
       <c r="G50" s="28" t="inlineStr">
         <is>
-          <t>Board 2</t>
+          <t>Board 1</t>
         </is>
       </c>
       <c r="H50" s="28" t="inlineStr">
         <is>
-          <t>Neev Chauhan</t>
+          <t>Rushabh</t>
         </is>
       </c>
       <c r="I50" s="28" t="inlineStr">
@@ -17572,7 +17671,7 @@
       </c>
       <c r="J50" s="28" t="inlineStr">
         <is>
-          <t>Kartik Relan</t>
+          <t>Jimit Relan</t>
         </is>
       </c>
     </row>
@@ -17602,17 +17701,17 @@
       </c>
       <c r="F51" s="27" t="inlineStr">
         <is>
-          <t>U11-4</t>
+          <t>U11-5</t>
         </is>
       </c>
       <c r="G51" s="27" t="inlineStr">
         <is>
-          <t>Board 1</t>
+          <t>Board 2</t>
         </is>
       </c>
       <c r="H51" s="27" t="inlineStr">
         <is>
-          <t>Rushabh</t>
+          <t>Neev Chauhan</t>
         </is>
       </c>
       <c r="I51" s="27" t="inlineStr">
@@ -17622,7 +17721,7 @@
       </c>
       <c r="J51" s="27" t="inlineStr">
         <is>
-          <t>Jimit Relan</t>
+          <t>Kartik Relan</t>
         </is>
       </c>
     </row>
@@ -17634,17 +17733,17 @@
       </c>
       <c r="B52" s="28" t="inlineStr">
         <is>
-          <t>10:30AM</t>
+          <t>10:50AM</t>
         </is>
       </c>
       <c r="C52" s="28" t="inlineStr">
         <is>
-          <t>10:50AM</t>
+          <t>11:10AM</t>
         </is>
       </c>
       <c r="D52" s="28" t="inlineStr">
         <is>
-          <t>Under 11</t>
+          <t>12 to 20</t>
         </is>
       </c>
       <c r="E52" s="28" t="n">
@@ -17652,17 +17751,17 @@
       </c>
       <c r="F52" s="28" t="inlineStr">
         <is>
-          <t>U11-4b</t>
+          <t>1220-1b</t>
         </is>
       </c>
       <c r="G52" s="28" t="inlineStr">
         <is>
-          <t>Board 2</t>
+          <t>Board 1</t>
         </is>
       </c>
       <c r="H52" s="28" t="inlineStr">
         <is>
-          <t>Neev Chauhan</t>
+          <t>Aaditya Kumar</t>
         </is>
       </c>
       <c r="I52" s="28" t="inlineStr">
@@ -17672,7 +17771,7 @@
       </c>
       <c r="J52" s="28" t="inlineStr">
         <is>
-          <t>Parth yadav</t>
+          <t>Hryday Goyal</t>
         </is>
       </c>
     </row>
@@ -17684,17 +17783,17 @@
       </c>
       <c r="B53" s="27" t="inlineStr">
         <is>
-          <t>10:50AM</t>
+          <t>11:00AM</t>
         </is>
       </c>
       <c r="C53" s="27" t="inlineStr">
         <is>
-          <t>11:10AM</t>
+          <t>11:20AM</t>
         </is>
       </c>
       <c r="D53" s="27" t="inlineStr">
         <is>
-          <t>12 to 20</t>
+          <t>Under 11</t>
         </is>
       </c>
       <c r="E53" s="27" t="n">
@@ -17702,17 +17801,17 @@
       </c>
       <c r="F53" s="27" t="inlineStr">
         <is>
-          <t>1220-1b</t>
+          <t>U11-4b</t>
         </is>
       </c>
       <c r="G53" s="27" t="inlineStr">
         <is>
-          <t>Board 1</t>
+          <t>Board 2</t>
         </is>
       </c>
       <c r="H53" s="27" t="inlineStr">
         <is>
-          <t>Aaditya Kumar</t>
+          <t>Neev Chauhan</t>
         </is>
       </c>
       <c r="I53" s="27" t="inlineStr">
@@ -17722,7 +17821,7 @@
       </c>
       <c r="J53" s="27" t="inlineStr">
         <is>
-          <t>Hryday Goyal</t>
+          <t>Parth yadav</t>
         </is>
       </c>
     </row>
@@ -17734,17 +17833,17 @@
       </c>
       <c r="B54" s="28" t="inlineStr">
         <is>
-          <t>11:00AM</t>
+          <t>11:20AM</t>
         </is>
       </c>
       <c r="C54" s="28" t="inlineStr">
         <is>
-          <t>11:20AM</t>
+          <t>11:40AM</t>
         </is>
       </c>
       <c r="D54" s="28" t="inlineStr">
         <is>
-          <t>Under 11</t>
+          <t>12 to 20</t>
         </is>
       </c>
       <c r="E54" s="28" t="n">
@@ -17752,17 +17851,17 @@
       </c>
       <c r="F54" s="28" t="inlineStr">
         <is>
-          <t>U11-5b</t>
+          <t>1220-2</t>
         </is>
       </c>
       <c r="G54" s="28" t="inlineStr">
         <is>
-          <t>Board 2</t>
+          <t>Board 1</t>
         </is>
       </c>
       <c r="H54" s="28" t="inlineStr">
         <is>
-          <t>Parth yadav</t>
+          <t>Aadit Joshi</t>
         </is>
       </c>
       <c r="I54" s="28" t="inlineStr">
@@ -17772,7 +17871,7 @@
       </c>
       <c r="J54" s="28" t="inlineStr">
         <is>
-          <t>Jimit Relan</t>
+          <t>Aaditya Kumar</t>
         </is>
       </c>
     </row>
@@ -17784,17 +17883,17 @@
       </c>
       <c r="B55" s="27" t="inlineStr">
         <is>
-          <t>11:20AM</t>
+          <t>11:30AM</t>
         </is>
       </c>
       <c r="C55" s="27" t="inlineStr">
         <is>
-          <t>11:40AM</t>
+          <t>11:50AM</t>
         </is>
       </c>
       <c r="D55" s="27" t="inlineStr">
         <is>
-          <t>12 to 20</t>
+          <t>Under 11</t>
         </is>
       </c>
       <c r="E55" s="27" t="n">
@@ -17802,17 +17901,17 @@
       </c>
       <c r="F55" s="27" t="inlineStr">
         <is>
-          <t>1220-2</t>
+          <t>U11-5b</t>
         </is>
       </c>
       <c r="G55" s="27" t="inlineStr">
         <is>
-          <t>Board 1</t>
+          <t>Board 2</t>
         </is>
       </c>
       <c r="H55" s="27" t="inlineStr">
         <is>
-          <t>Aadit Joshi</t>
+          <t>Parth yadav</t>
         </is>
       </c>
       <c r="I55" s="27" t="inlineStr">
@@ -17822,7 +17921,7 @@
       </c>
       <c r="J55" s="27" t="inlineStr">
         <is>
-          <t>Aaditya Kumar</t>
+          <t>Jimit Relan</t>
         </is>
       </c>
     </row>
@@ -17834,12 +17933,12 @@
       </c>
       <c r="B56" s="28" t="inlineStr">
         <is>
-          <t>11:20AM</t>
+          <t>11:50AM</t>
         </is>
       </c>
       <c r="C56" s="28" t="inlineStr">
         <is>
-          <t>11:40AM</t>
+          <t>12:10PM</t>
         </is>
       </c>
       <c r="D56" s="28" t="inlineStr">
@@ -17884,12 +17983,12 @@
       </c>
       <c r="B57" s="27" t="inlineStr">
         <is>
-          <t>11:50AM</t>
+          <t>3:00PM</t>
         </is>
       </c>
       <c r="C57" s="27" t="inlineStr">
         <is>
-          <t>12:10PM</t>
+          <t>3:20PM</t>
         </is>
       </c>
       <c r="D57" s="27" t="inlineStr">
@@ -17934,12 +18033,12 @@
       </c>
       <c r="B58" s="28" t="inlineStr">
         <is>
-          <t>11:50AM</t>
+          <t>3:00PM</t>
         </is>
       </c>
       <c r="C58" s="28" t="inlineStr">
         <is>
-          <t>12:10PM</t>
+          <t>3:20PM</t>
         </is>
       </c>
       <c r="D58" s="28" t="inlineStr">
@@ -17984,12 +18083,12 @@
       </c>
       <c r="B59" s="27" t="inlineStr">
         <is>
-          <t>12:10PM</t>
+          <t>3:20PM</t>
         </is>
       </c>
       <c r="C59" s="27" t="inlineStr">
         <is>
-          <t>12:30PM</t>
+          <t>3:40PM</t>
         </is>
       </c>
       <c r="D59" s="27" t="inlineStr">
@@ -18034,12 +18133,12 @@
       </c>
       <c r="B60" s="28" t="inlineStr">
         <is>
-          <t>12:10PM</t>
+          <t>3:20PM</t>
         </is>
       </c>
       <c r="C60" s="28" t="inlineStr">
         <is>
-          <t>12:30PM</t>
+          <t>3:40PM</t>
         </is>
       </c>
       <c r="D60" s="28" t="inlineStr">
@@ -18084,12 +18183,12 @@
       </c>
       <c r="B61" s="27" t="inlineStr">
         <is>
-          <t>12:40PM</t>
+          <t>3:50PM</t>
         </is>
       </c>
       <c r="C61" s="27" t="inlineStr">
         <is>
-          <t>1:00PM</t>
+          <t>4:10PM</t>
         </is>
       </c>
       <c r="D61" s="27" t="inlineStr">
@@ -18134,12 +18233,12 @@
       </c>
       <c r="B62" s="28" t="inlineStr">
         <is>
-          <t>12:40PM</t>
+          <t>3:50PM</t>
         </is>
       </c>
       <c r="C62" s="28" t="inlineStr">
         <is>
-          <t>1:00PM</t>
+          <t>4:10PM</t>
         </is>
       </c>
       <c r="D62" s="28" t="inlineStr">
@@ -18184,12 +18283,12 @@
       </c>
       <c r="B63" s="27" t="inlineStr">
         <is>
-          <t>3:00PM</t>
+          <t>4:20PM</t>
         </is>
       </c>
       <c r="C63" s="27" t="inlineStr">
         <is>
-          <t>3:20PM</t>
+          <t>4:40PM</t>
         </is>
       </c>
       <c r="D63" s="27" t="inlineStr">
@@ -18202,17 +18301,17 @@
       </c>
       <c r="F63" s="27" t="inlineStr">
         <is>
-          <t>2140-1</t>
+          <t>2140-8</t>
         </is>
       </c>
       <c r="G63" s="27" t="inlineStr">
         <is>
-          <t>Board 1</t>
+          <t>Board 2</t>
         </is>
       </c>
       <c r="H63" s="27" t="inlineStr">
         <is>
-          <t>Rahul Garg</t>
+          <t>Amit Nawandhar</t>
         </is>
       </c>
       <c r="I63" s="27" t="inlineStr">
@@ -18222,7 +18321,7 @@
       </c>
       <c r="J63" s="27" t="inlineStr">
         <is>
-          <t>Nikunj Jhala</t>
+          <t>Tejas doshi</t>
         </is>
       </c>
     </row>
@@ -18234,12 +18333,12 @@
       </c>
       <c r="B64" s="28" t="inlineStr">
         <is>
-          <t>3:00PM</t>
+          <t>4:40PM</t>
         </is>
       </c>
       <c r="C64" s="28" t="inlineStr">
         <is>
-          <t>3:20PM</t>
+          <t>5:00PM</t>
         </is>
       </c>
       <c r="D64" s="28" t="inlineStr">
@@ -18252,7 +18351,7 @@
       </c>
       <c r="F64" s="28" t="inlineStr">
         <is>
-          <t>2140-8</t>
+          <t>2140-3b</t>
         </is>
       </c>
       <c r="G64" s="28" t="inlineStr">
@@ -18262,7 +18361,7 @@
       </c>
       <c r="H64" s="28" t="inlineStr">
         <is>
-          <t>Amit Nawandhar</t>
+          <t>Tej</t>
         </is>
       </c>
       <c r="I64" s="28" t="inlineStr">
@@ -18272,7 +18371,7 @@
       </c>
       <c r="J64" s="28" t="inlineStr">
         <is>
-          <t>Tejas doshi</t>
+          <t>Swati Tripathi</t>
         </is>
       </c>
     </row>
@@ -18284,12 +18383,12 @@
       </c>
       <c r="B65" s="27" t="inlineStr">
         <is>
-          <t>3:20PM</t>
+          <t>4:55PM</t>
         </is>
       </c>
       <c r="C65" s="27" t="inlineStr">
         <is>
-          <t>3:40PM</t>
+          <t>5:15PM</t>
         </is>
       </c>
       <c r="D65" s="27" t="inlineStr">
@@ -18302,17 +18401,17 @@
       </c>
       <c r="F65" s="27" t="inlineStr">
         <is>
-          <t>2140-3b</t>
+          <t>2140-1</t>
         </is>
       </c>
       <c r="G65" s="27" t="inlineStr">
         <is>
-          <t>Board 2</t>
+          <t>Board 1</t>
         </is>
       </c>
       <c r="H65" s="27" t="inlineStr">
         <is>
-          <t>Tej</t>
+          <t>Rahul Garg</t>
         </is>
       </c>
       <c r="I65" s="27" t="inlineStr">
@@ -18322,7 +18421,7 @@
       </c>
       <c r="J65" s="27" t="inlineStr">
         <is>
-          <t>Swati Tripathi</t>
+          <t>Nikunj Jhala</t>
         </is>
       </c>
     </row>
@@ -18334,12 +18433,12 @@
       </c>
       <c r="B66" s="28" t="inlineStr">
         <is>
-          <t>3:30PM</t>
+          <t>5:25PM</t>
         </is>
       </c>
       <c r="C66" s="28" t="inlineStr">
         <is>
-          <t>3:50PM</t>
+          <t>5:45PM</t>
         </is>
       </c>
       <c r="D66" s="28" t="inlineStr">
@@ -18384,12 +18483,12 @@
       </c>
       <c r="B67" s="27" t="inlineStr">
         <is>
-          <t>3:50PM</t>
+          <t>5:25PM</t>
         </is>
       </c>
       <c r="C67" s="27" t="inlineStr">
         <is>
-          <t>4:10PM</t>
+          <t>5:45PM</t>
         </is>
       </c>
       <c r="D67" s="27" t="inlineStr">
@@ -18434,17 +18533,17 @@
       </c>
       <c r="B68" s="28" t="inlineStr">
         <is>
-          <t>4:00PM</t>
+          <t>5:45PM</t>
         </is>
       </c>
       <c r="C68" s="28" t="inlineStr">
         <is>
-          <t>4:20PM</t>
+          <t>6:05PM</t>
         </is>
       </c>
       <c r="D68" s="28" t="inlineStr">
         <is>
-          <t>21 to 40</t>
+          <t>41 and above</t>
         </is>
       </c>
       <c r="E68" s="28" t="n">
@@ -18452,17 +18551,17 @@
       </c>
       <c r="F68" s="28" t="inlineStr">
         <is>
-          <t>2140-4</t>
+          <t>41P-1</t>
         </is>
       </c>
       <c r="G68" s="28" t="inlineStr">
         <is>
-          <t>Board 1</t>
+          <t>Board 2</t>
         </is>
       </c>
       <c r="H68" s="28" t="inlineStr">
         <is>
-          <t>Amit Nawandhar</t>
+          <t>Piyush Makharia</t>
         </is>
       </c>
       <c r="I68" s="28" t="inlineStr">
@@ -18472,7 +18571,7 @@
       </c>
       <c r="J68" s="28" t="inlineStr">
         <is>
-          <t>Nikunj Jhala</t>
+          <t>Ajit nair</t>
         </is>
       </c>
     </row>
@@ -18484,17 +18583,17 @@
       </c>
       <c r="B69" s="27" t="inlineStr">
         <is>
-          <t>4:10PM</t>
+          <t>5:55PM</t>
         </is>
       </c>
       <c r="C69" s="27" t="inlineStr">
         <is>
-          <t>4:30PM</t>
+          <t>6:15PM</t>
         </is>
       </c>
       <c r="D69" s="27" t="inlineStr">
         <is>
-          <t>41 and above</t>
+          <t>21 to 40</t>
         </is>
       </c>
       <c r="E69" s="27" t="n">
@@ -18502,17 +18601,17 @@
       </c>
       <c r="F69" s="27" t="inlineStr">
         <is>
-          <t>41P-1</t>
+          <t>2140-4</t>
         </is>
       </c>
       <c r="G69" s="27" t="inlineStr">
         <is>
-          <t>Board 2</t>
+          <t>Board 1</t>
         </is>
       </c>
       <c r="H69" s="27" t="inlineStr">
         <is>
-          <t>Piyush Makharia</t>
+          <t>Amit Nawandhar</t>
         </is>
       </c>
       <c r="I69" s="27" t="inlineStr">
@@ -18522,7 +18621,7 @@
       </c>
       <c r="J69" s="27" t="inlineStr">
         <is>
-          <t>Ajit nair</t>
+          <t>Nikunj Jhala</t>
         </is>
       </c>
     </row>
@@ -18534,12 +18633,12 @@
       </c>
       <c r="B70" s="28" t="inlineStr">
         <is>
-          <t>4:30PM</t>
+          <t>6:25PM</t>
         </is>
       </c>
       <c r="C70" s="28" t="inlineStr">
         <is>
-          <t>4:50PM</t>
+          <t>6:45PM</t>
         </is>
       </c>
       <c r="D70" s="28" t="inlineStr">
@@ -18584,12 +18683,12 @@
       </c>
       <c r="B71" s="27" t="inlineStr">
         <is>
-          <t>4:50PM</t>
+          <t>6:45PM</t>
         </is>
       </c>
       <c r="C71" s="27" t="inlineStr">
         <is>
-          <t>5:10PM</t>
+          <t>7:05PM</t>
         </is>
       </c>
       <c r="D71" s="27" t="inlineStr">
@@ -18634,12 +18733,12 @@
       </c>
       <c r="B72" s="28" t="inlineStr">
         <is>
-          <t>5:00PM</t>
+          <t>6:55PM</t>
         </is>
       </c>
       <c r="C72" s="28" t="inlineStr">
         <is>
-          <t>5:20PM</t>
+          <t>7:15PM</t>
         </is>
       </c>
       <c r="D72" s="28" t="inlineStr">
@@ -18684,12 +18783,12 @@
       </c>
       <c r="B73" s="27" t="inlineStr">
         <is>
-          <t>5:20PM</t>
+          <t>7:15PM</t>
         </is>
       </c>
       <c r="C73" s="27" t="inlineStr">
         <is>
-          <t>5:40PM</t>
+          <t>7:35PM</t>
         </is>
       </c>
       <c r="D73" s="27" t="inlineStr">
@@ -18734,12 +18833,12 @@
       </c>
       <c r="B74" s="28" t="inlineStr">
         <is>
-          <t>5:20PM</t>
+          <t>7:15PM</t>
         </is>
       </c>
       <c r="C74" s="28" t="inlineStr">
         <is>
-          <t>5:40PM</t>
+          <t>7:35PM</t>
         </is>
       </c>
       <c r="D74" s="28" t="inlineStr">
@@ -18784,12 +18883,12 @@
       </c>
       <c r="B75" s="27" t="inlineStr">
         <is>
-          <t>5:40PM</t>
+          <t>7:35PM</t>
         </is>
       </c>
       <c r="C75" s="27" t="inlineStr">
         <is>
-          <t>6:00PM</t>
+          <t>7:55PM</t>
         </is>
       </c>
       <c r="D75" s="27" t="inlineStr">
@@ -18834,12 +18933,12 @@
       </c>
       <c r="B76" s="28" t="inlineStr">
         <is>
-          <t>6:10PM</t>
+          <t>8:05PM</t>
         </is>
       </c>
       <c r="C76" s="28" t="inlineStr">
         <is>
-          <t>6:30PM</t>
+          <t>8:25PM</t>
         </is>
       </c>
       <c r="D76" s="28" t="inlineStr">
@@ -18884,12 +18983,12 @@
       </c>
       <c r="B77" s="27" t="inlineStr">
         <is>
-          <t>6:10PM</t>
+          <t>8:05PM</t>
         </is>
       </c>
       <c r="C77" s="27" t="inlineStr">
         <is>
-          <t>6:30PM</t>
+          <t>8:25PM</t>
         </is>
       </c>
       <c r="D77" s="27" t="inlineStr">
@@ -18934,12 +19033,12 @@
       </c>
       <c r="B78" s="28" t="inlineStr">
         <is>
-          <t>6:30PM</t>
+          <t>8:25PM</t>
         </is>
       </c>
       <c r="C78" s="28" t="inlineStr">
         <is>
-          <t>6:50PM</t>
+          <t>8:45PM</t>
         </is>
       </c>
       <c r="D78" s="28" t="inlineStr">
@@ -18984,12 +19083,12 @@
       </c>
       <c r="B79" s="27" t="inlineStr">
         <is>
-          <t>6:55PM</t>
+          <t>8:40PM</t>
         </is>
       </c>
       <c r="C79" s="27" t="inlineStr">
         <is>
-          <t>7:15PM</t>
+          <t>9:00PM</t>
         </is>
       </c>
       <c r="D79" s="27" t="inlineStr">
@@ -19034,12 +19133,12 @@
       </c>
       <c r="B80" s="28" t="inlineStr">
         <is>
-          <t>7:25PM</t>
+          <t>9:10PM</t>
         </is>
       </c>
       <c r="C80" s="28" t="inlineStr">
         <is>
-          <t>7:45PM</t>
+          <t>9:30PM</t>
         </is>
       </c>
       <c r="D80" s="28" t="inlineStr">
@@ -19084,12 +19183,12 @@
       </c>
       <c r="B81" s="27" t="inlineStr">
         <is>
-          <t>7:45PM</t>
+          <t>9:30PM</t>
         </is>
       </c>
       <c r="C81" s="27" t="inlineStr">
         <is>
-          <t>8:05PM</t>
+          <t>9:50PM</t>
         </is>
       </c>
       <c r="D81" s="27" t="inlineStr">
@@ -19129,17 +19228,17 @@
     <row r="82">
       <c r="A82" s="28" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B82" s="28" t="inlineStr">
         <is>
-          <t>8:30PM</t>
+          <t>8:15AM</t>
         </is>
       </c>
       <c r="C82" s="28" t="inlineStr">
         <is>
-          <t>8:50PM</t>
+          <t>8:35AM</t>
         </is>
       </c>
       <c r="D82" s="28" t="inlineStr">
@@ -19184,12 +19283,12 @@
       </c>
       <c r="B83" s="27" t="inlineStr">
         <is>
-          <t>8:00AM</t>
+          <t>8:45AM</t>
         </is>
       </c>
       <c r="C83" s="27" t="inlineStr">
         <is>
-          <t>8:20AM</t>
+          <t>9:05AM</t>
         </is>
       </c>
       <c r="D83" s="27" t="inlineStr">
@@ -19234,12 +19333,12 @@
       </c>
       <c r="B84" s="28" t="inlineStr">
         <is>
-          <t>8:00AM</t>
+          <t>8:45AM</t>
         </is>
       </c>
       <c r="C84" s="28" t="inlineStr">
         <is>
-          <t>8:20AM</t>
+          <t>9:05AM</t>
         </is>
       </c>
       <c r="D84" s="28" t="inlineStr">
@@ -19284,12 +19383,12 @@
       </c>
       <c r="B85" s="27" t="inlineStr">
         <is>
-          <t>8:30AM</t>
+          <t>9:15AM</t>
         </is>
       </c>
       <c r="C85" s="27" t="inlineStr">
         <is>
-          <t>8:50AM</t>
+          <t>9:35AM</t>
         </is>
       </c>
       <c r="D85" s="27" t="inlineStr">
@@ -19334,12 +19433,12 @@
       </c>
       <c r="B86" s="28" t="inlineStr">
         <is>
-          <t>8:30AM</t>
+          <t>9:15AM</t>
         </is>
       </c>
       <c r="C86" s="28" t="inlineStr">
         <is>
-          <t>8:50AM</t>
+          <t>9:35AM</t>
         </is>
       </c>
       <c r="D86" s="28" t="inlineStr">
@@ -19384,12 +19483,12 @@
       </c>
       <c r="B87" s="27" t="inlineStr">
         <is>
-          <t>8:50AM</t>
+          <t>9:35AM</t>
         </is>
       </c>
       <c r="C87" s="27" t="inlineStr">
         <is>
-          <t>9:10AM</t>
+          <t>9:55AM</t>
         </is>
       </c>
       <c r="D87" s="27" t="inlineStr">
@@ -19434,12 +19533,12 @@
       </c>
       <c r="B88" s="28" t="inlineStr">
         <is>
-          <t>9:00AM</t>
+          <t>9:45AM</t>
         </is>
       </c>
       <c r="C88" s="28" t="inlineStr">
         <is>
-          <t>9:20AM</t>
+          <t>10:05AM</t>
         </is>
       </c>
       <c r="D88" s="28" t="inlineStr">
@@ -19484,12 +19583,12 @@
       </c>
       <c r="B89" s="27" t="inlineStr">
         <is>
-          <t>9:30AM</t>
+          <t>10:15AM</t>
         </is>
       </c>
       <c r="C89" s="27" t="inlineStr">
         <is>
-          <t>9:50AM</t>
+          <t>10:35AM</t>
         </is>
       </c>
       <c r="D89" s="27" t="inlineStr">
@@ -19534,12 +19633,12 @@
       </c>
       <c r="B90" s="28" t="inlineStr">
         <is>
-          <t>9:30AM</t>
+          <t>10:15AM</t>
         </is>
       </c>
       <c r="C90" s="28" t="inlineStr">
         <is>
-          <t>9:50AM</t>
+          <t>10:35AM</t>
         </is>
       </c>
       <c r="D90" s="28" t="inlineStr">
@@ -19584,12 +19683,12 @@
       </c>
       <c r="B91" s="27" t="inlineStr">
         <is>
-          <t>10:00AM</t>
+          <t>10:45AM</t>
         </is>
       </c>
       <c r="C91" s="27" t="inlineStr">
         <is>
-          <t>10:20AM</t>
+          <t>11:05AM</t>
         </is>
       </c>
       <c r="D91" s="27" t="inlineStr">
@@ -19634,12 +19733,12 @@
       </c>
       <c r="B92" s="28" t="inlineStr">
         <is>
-          <t>10:30AM</t>
+          <t>11:15AM</t>
         </is>
       </c>
       <c r="C92" s="28" t="inlineStr">
         <is>
-          <t>10:50AM</t>
+          <t>11:35AM</t>
         </is>
       </c>
       <c r="D92" s="28" t="inlineStr">
@@ -19684,12 +19783,12 @@
       </c>
       <c r="B93" s="27" t="inlineStr">
         <is>
-          <t>11:00AM</t>
+          <t>11:45AM</t>
         </is>
       </c>
       <c r="C93" s="27" t="inlineStr">
         <is>
-          <t>11:20AM</t>
+          <t>12:05PM</t>
         </is>
       </c>
       <c r="D93" s="27" t="inlineStr">
@@ -19734,12 +19833,12 @@
       </c>
       <c r="B94" s="28" t="inlineStr">
         <is>
-          <t>11:30AM</t>
+          <t>3:00PM</t>
         </is>
       </c>
       <c r="C94" s="28" t="inlineStr">
         <is>
-          <t>11:50AM</t>
+          <t>3:20PM</t>
         </is>
       </c>
       <c r="D94" s="28" t="inlineStr">
@@ -19784,12 +19883,12 @@
       </c>
       <c r="B95" s="27" t="inlineStr">
         <is>
-          <t>11:50AM</t>
+          <t>3:20PM</t>
         </is>
       </c>
       <c r="C95" s="27" t="inlineStr">
         <is>
-          <t>12:10PM</t>
+          <t>3:40PM</t>
         </is>
       </c>
       <c r="D95" s="27" t="inlineStr">
@@ -19834,12 +19933,12 @@
       </c>
       <c r="B96" s="28" t="inlineStr">
         <is>
-          <t>11:50AM</t>
+          <t>3:20PM</t>
         </is>
       </c>
       <c r="C96" s="28" t="inlineStr">
         <is>
-          <t>12:10PM</t>
+          <t>3:40PM</t>
         </is>
       </c>
       <c r="D96" s="28" t="inlineStr">
@@ -19884,12 +19983,12 @@
       </c>
       <c r="B97" s="27" t="inlineStr">
         <is>
-          <t>3:00PM</t>
+          <t>3:40PM</t>
         </is>
       </c>
       <c r="C97" s="27" t="inlineStr">
         <is>
-          <t>3:20PM</t>
+          <t>4:00PM</t>
         </is>
       </c>
       <c r="D97" s="27" t="inlineStr">
@@ -19934,12 +20033,12 @@
       </c>
       <c r="B98" s="28" t="inlineStr">
         <is>
-          <t>3:20PM</t>
+          <t>4:00PM</t>
         </is>
       </c>
       <c r="C98" s="28" t="inlineStr">
         <is>
-          <t>3:40PM</t>
+          <t>4:20PM</t>
         </is>
       </c>
       <c r="D98" s="28" t="inlineStr">
@@ -19984,12 +20083,12 @@
       </c>
       <c r="B99" s="27" t="inlineStr">
         <is>
-          <t>3:40PM</t>
+          <t>4:20PM</t>
         </is>
       </c>
       <c r="C99" s="27" t="inlineStr">
         <is>
-          <t>4:00PM</t>
+          <t>4:40PM</t>
         </is>
       </c>
       <c r="D99" s="27" t="inlineStr">
@@ -20034,12 +20133,12 @@
       </c>
       <c r="B100" s="28" t="inlineStr">
         <is>
-          <t>4:00PM</t>
+          <t>4:40PM</t>
         </is>
       </c>
       <c r="C100" s="28" t="inlineStr">
         <is>
-          <t>4:20PM</t>
+          <t>5:00PM</t>
         </is>
       </c>
       <c r="D100" s="28" t="inlineStr">

--- a/Ekta_Schedule_With_Matchups.xlsx
+++ b/Ekta_Schedule_With_Matchups.xlsx
@@ -25,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -130,8 +130,13 @@
       <color rgb="000F172A"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -176,6 +181,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFEF3C7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000E7490"/>
       </patternFill>
     </fill>
   </fills>
@@ -265,7 +275,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -420,6 +430,13 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -785,7 +802,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" style="21" min="1" max="1"/>
@@ -824,7 +841,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="15" t="inlineStr">
         <is>
-          <t>different events. Semis and finals (and both Doubles events, in full) run only after every group/pool match, in every event, has finished.</t>
+          <t>different events. Doubles events run once their own players are free (from 9:00 AM Aug 16); Semis and Finals for singles events wait until every group/pool match everywhere is finished.</t>
         </is>
       </c>
     </row>
@@ -982,7 +999,7 @@
       <c r="F13" s="37" t="n"/>
       <c r="G13" s="38" t="n"/>
     </row>
-    <row r="14" ht="15" customHeight="1">
+    <row r="14" ht="45" customHeight="1">
       <c r="A14" s="47" t="inlineStr">
         <is>
           <t>Aug 16</t>
@@ -990,29 +1007,29 @@
       </c>
       <c r="B14" s="51" t="inlineStr">
         <is>
+          <t>9:00 - 11:15 AM</t>
+        </is>
+      </c>
+      <c r="C14" s="52" t="inlineStr">
+        <is>
+          <t>Both Doubles events (TT Doubles, Carrom Doubles) run in full — only need their own players free, don't wait for other events' groups</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" s="49" t="inlineStr">
+        <is>
+          <t>Aug 16</t>
+        </is>
+      </c>
+      <c r="B15" s="49" t="inlineStr">
+        <is>
           <t>12:00 - 3:00 PM</t>
         </is>
       </c>
-      <c r="C14" s="52" t="inlineStr">
+      <c r="C15" s="50" t="inlineStr">
         <is>
           <t>BREAK</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="49" t="inlineStr">
-        <is>
-          <t>Aug 16</t>
-        </is>
-      </c>
-      <c r="B15" s="49" t="inlineStr">
-        <is>
-          <t>3:00 - 3:20 PM</t>
-        </is>
-      </c>
-      <c r="C15" s="50" t="inlineStr">
-        <is>
-          <t>Remaining group-stage matches finish</t>
         </is>
       </c>
       <c r="D15" s="37" t="n"/>
@@ -1020,7 +1037,7 @@
       <c r="F15" s="37" t="n"/>
       <c r="G15" s="38" t="n"/>
     </row>
-    <row r="16" ht="60" customHeight="1">
+    <row r="16" ht="30" customHeight="1">
       <c r="A16" s="51" t="inlineStr">
         <is>
           <t>Aug 16</t>
@@ -1028,121 +1045,85 @@
       </c>
       <c r="B16" s="51" t="inlineStr">
         <is>
-          <t>3:20 - 5:35 PM</t>
+          <t>3:00 - 3:20 PM</t>
         </is>
       </c>
       <c r="C16" s="52" t="inlineStr">
         <is>
-          <t>Semis + Finals for every singles event, plus both Doubles events in full (TT Doubles, Carrom Doubles) — none of this starts until every group/pool match everywhere is done</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="27.95" customHeight="1">
-      <c r="A17" s="18" t="inlineStr">
-        <is>
-          <t>Sports run concurrently on their own tables/boards/court and heavily share players, so each event's matches are spread across the day interleaved with other sports rather than run as one uninterrupted block. See each sport's own sheet for the exact chronological match list.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1">
+          <t>Remaining group-stage matches finish</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="45" customHeight="1">
+      <c r="A17" s="51" t="inlineStr">
+        <is>
+          <t>Aug 16</t>
+        </is>
+      </c>
+      <c r="B17" s="51" t="inlineStr">
+        <is>
+          <t>3:20 - 5:26 PM</t>
+        </is>
+      </c>
+      <c r="C17" s="52" t="inlineStr">
+        <is>
+          <t>Semis + Finals for every singles event — starts only once every group/pool match everywhere is done</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="40" customHeight="1">
       <c r="A18" s="53" t="inlineStr">
         <is>
-          <t>No matches are scheduled before 8:00 AM, between 9:30-10:30 AM (Aug 15 flag hoisting), between 12:00-3:00 PM on either day, or after 10:00 PM — any match that would otherwise land in those windows rolls to the end of the window.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="20.1" customHeight="1">
-      <c r="A19" s="16" t="inlineStr">
+          <t>No matches are scheduled before 8:00 AM, between 9:30-10:30 AM (Aug 15 flag hoisting), between 12:00-3:00 PM on either day, or after 10:00 PM — any match that would otherwise land in those windows rolls to the end of the window. Doubles events only need to wait for 9:00 AM Aug 16, not for other events' group stages.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="40" customHeight="1"/>
+    <row r="20">
+      <c r="A20" s="55" t="inlineStr">
         <is>
           <t>EVENTS</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="9" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="54" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>Event</t>
         </is>
       </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="B22" s="9" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C22" s="9" t="inlineStr">
         <is>
           <t>Equipment</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
+      <c r="D22" s="9" t="inlineStr">
         <is>
           <t>Starts</t>
         </is>
       </c>
-      <c r="E20" s="9" t="inlineStr">
+      <c r="E22" s="9" t="inlineStr">
         <is>
           <t>Finishes</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>TT Women's Singles</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>2 tables</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>Aug15 10:30AM</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>Aug16 3:50PM</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>Table Tennis Singles Men</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="n">
-        <v>71</v>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>2 tables</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>Aug15 8:00AM</t>
-        </is>
-      </c>
-      <c r="E22" s="6" t="inlineStr">
-        <is>
-          <t>Aug16 5:05PM</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Table Tennis Doubles</t>
+          <t>TT Women's Singles</t>
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
@@ -1151,23 +1132,23 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Aug16 4:05PM</t>
+          <t>Aug15 10:30AM</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>Aug16 5:35PM</t>
+          <t>Aug16 3:50PM</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Pool</t>
+          <t>Table Tennis Singles Men</t>
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
@@ -1181,47 +1162,47 @@
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>Aug16 5:00PM</t>
+          <t>Aug16 5:05PM</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Chess</t>
+          <t>Table Tennis Doubles</t>
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>58</v>
+        <v>7</v>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>2 boards</t>
+          <t>2 tables</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>Aug15 8:00AM</t>
+          <t>Aug16 9:45AM</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Aug16 5:00PM</t>
+          <t>Aug16 11:15AM</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Carrom Singles Men</t>
+          <t>Pool</t>
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>3 boards</t>
+          <t>2 tables</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -1231,22 +1212,22 @@
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>Aug16 4:05PM</t>
+          <t>Aug16 5:00PM</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Carrom Singles Women</t>
+          <t>Chess</t>
         </is>
       </c>
       <c r="B27" s="4" t="n">
-        <v>11</v>
+        <v>58</v>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>3 boards (1 used)</t>
+          <t>2 boards</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -1256,18 +1237,18 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>Aug16 3:35PM</t>
+          <t>Aug16 5:00PM</t>
         </is>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>Carrom Doubles</t>
+          <t>Carrom Singles Men</t>
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
@@ -1276,68 +1257,120 @@
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>Aug16 3:20PM</t>
+          <t>Aug15 8:00AM</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>Aug16 4:50PM</t>
+          <t>Aug16 4:05PM</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
+          <t>Carrom Singles Women</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>3 boards (1 used)</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>Aug15 8:00AM</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>Aug16 3:35PM</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Carrom Doubles</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>3 boards</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>Aug16 9:00AM</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>Aug16 10:30AM</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
           <t>Squash</t>
         </is>
       </c>
-      <c r="B29" s="4" t="n">
+      <c r="B31" t="n">
         <v>19</v>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>1 court</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>Aug15 8:00AM</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>Aug16 5:26PM</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="30" customHeight="1">
-      <c r="A31" s="19" t="inlineStr">
-        <is>
-          <t>Overall tournament span: Aug 15, 8:00 AM start → Aug 16, 5:35 PM finish — comfortably inside the Aug 16, 10 PM cap.</t>
-        </is>
-      </c>
-    </row>
     <row r="33" ht="20.1" customHeight="1">
-      <c r="A33" s="16" t="inlineStr">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>Overall tournament span: Aug 15, 8:00 AM start → Aug 16, 5:26 PM finish — comfortably inside the Aug 16, 10 PM cap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="15" customHeight="1"/>
+    <row r="35">
+      <c r="A35" s="16" t="inlineStr">
         <is>
           <t>NOTES</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="15" customHeight="1">
-      <c r="A34" s="20" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="20" t="inlineStr">
         <is>
           <t>Full match-by-match detail (exact times, table/board assignment, player groups) lives in each sport's own sheet — this tab is a summary only.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="21">
-    <mergeCell ref="A34:E34"/>
+  <mergeCells count="22">
     <mergeCell ref="C15:G15"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="C14:G14"/>
+    <mergeCell ref="A36:E36"/>
     <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A19:G19"/>
     <mergeCell ref="C10:G10"/>
     <mergeCell ref="C16:G16"/>
     <mergeCell ref="C9:G9"/>
@@ -1347,12 +1380,12 @@
     <mergeCell ref="A33:E33"/>
     <mergeCell ref="C11:G11"/>
     <mergeCell ref="C8:G8"/>
-    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="C17:G17"/>
     <mergeCell ref="C7:G7"/>
     <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A20:E20"/>
     <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A31:E31"/>
     <mergeCell ref="C13:G13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8075,12 +8108,12 @@
       </c>
       <c r="B20" s="27" t="inlineStr">
         <is>
-          <t>4:05PM</t>
+          <t>9:45AM</t>
         </is>
       </c>
       <c r="C20" s="27" t="inlineStr">
         <is>
-          <t>4:20PM</t>
+          <t>10:00AM</t>
         </is>
       </c>
       <c r="D20" s="27" t="inlineStr">
@@ -8125,12 +8158,12 @@
       </c>
       <c r="B21" s="28" t="inlineStr">
         <is>
-          <t>4:20PM</t>
+          <t>10:00AM</t>
         </is>
       </c>
       <c r="C21" s="28" t="inlineStr">
         <is>
-          <t>4:35PM</t>
+          <t>10:15AM</t>
         </is>
       </c>
       <c r="D21" s="28" t="inlineStr">
@@ -8175,12 +8208,12 @@
       </c>
       <c r="B22" s="27" t="inlineStr">
         <is>
-          <t>4:20PM</t>
+          <t>10:00AM</t>
         </is>
       </c>
       <c r="C22" s="27" t="inlineStr">
         <is>
-          <t>4:35PM</t>
+          <t>10:15AM</t>
         </is>
       </c>
       <c r="D22" s="27" t="inlineStr">
@@ -8225,12 +8258,12 @@
       </c>
       <c r="B23" s="28" t="inlineStr">
         <is>
-          <t>4:35PM</t>
+          <t>10:15AM</t>
         </is>
       </c>
       <c r="C23" s="28" t="inlineStr">
         <is>
-          <t>4:50PM</t>
+          <t>10:30AM</t>
         </is>
       </c>
       <c r="D23" s="28" t="inlineStr">
@@ -8275,12 +8308,12 @@
       </c>
       <c r="B24" s="27" t="inlineStr">
         <is>
-          <t>4:50PM</t>
+          <t>10:30AM</t>
         </is>
       </c>
       <c r="C24" s="27" t="inlineStr">
         <is>
-          <t>5:05PM</t>
+          <t>10:45AM</t>
         </is>
       </c>
       <c r="D24" s="27" t="inlineStr">
@@ -8325,12 +8358,12 @@
       </c>
       <c r="B25" s="28" t="inlineStr">
         <is>
-          <t>5:05PM</t>
+          <t>10:45AM</t>
         </is>
       </c>
       <c r="C25" s="28" t="inlineStr">
         <is>
-          <t>5:20PM</t>
+          <t>11:00AM</t>
         </is>
       </c>
       <c r="D25" s="28" t="inlineStr">
@@ -8375,12 +8408,12 @@
       </c>
       <c r="B26" s="27" t="inlineStr">
         <is>
-          <t>5:20PM</t>
+          <t>11:00AM</t>
         </is>
       </c>
       <c r="C26" s="27" t="inlineStr">
         <is>
-          <t>5:35PM</t>
+          <t>11:15AM</t>
         </is>
       </c>
       <c r="D26" s="27" t="inlineStr">
@@ -12434,12 +12467,12 @@
       </c>
       <c r="B28" s="27" t="inlineStr">
         <is>
-          <t>3:20PM</t>
+          <t>9:00AM</t>
         </is>
       </c>
       <c r="C28" s="27" t="inlineStr">
         <is>
-          <t>3:35PM</t>
+          <t>9:15AM</t>
         </is>
       </c>
       <c r="D28" s="27" t="inlineStr">
@@ -12484,12 +12517,12 @@
       </c>
       <c r="B29" s="28" t="inlineStr">
         <is>
-          <t>3:20PM</t>
+          <t>9:00AM</t>
         </is>
       </c>
       <c r="C29" s="28" t="inlineStr">
         <is>
-          <t>3:35PM</t>
+          <t>9:15AM</t>
         </is>
       </c>
       <c r="D29" s="28" t="inlineStr">
@@ -12534,12 +12567,12 @@
       </c>
       <c r="B30" s="27" t="inlineStr">
         <is>
-          <t>3:20PM</t>
+          <t>9:00AM</t>
         </is>
       </c>
       <c r="C30" s="27" t="inlineStr">
         <is>
-          <t>3:35PM</t>
+          <t>9:15AM</t>
         </is>
       </c>
       <c r="D30" s="27" t="inlineStr">
@@ -12584,12 +12617,12 @@
       </c>
       <c r="B31" s="28" t="inlineStr">
         <is>
-          <t>3:35PM</t>
+          <t>9:15AM</t>
         </is>
       </c>
       <c r="C31" s="28" t="inlineStr">
         <is>
-          <t>3:50PM</t>
+          <t>9:30AM</t>
         </is>
       </c>
       <c r="D31" s="28" t="inlineStr">
@@ -12634,12 +12667,12 @@
       </c>
       <c r="B32" s="27" t="inlineStr">
         <is>
-          <t>3:35PM</t>
+          <t>9:15AM</t>
         </is>
       </c>
       <c r="C32" s="27" t="inlineStr">
         <is>
-          <t>3:50PM</t>
+          <t>9:30AM</t>
         </is>
       </c>
       <c r="D32" s="27" t="inlineStr">
@@ -12684,12 +12717,12 @@
       </c>
       <c r="B33" s="28" t="inlineStr">
         <is>
-          <t>3:35PM</t>
+          <t>9:15AM</t>
         </is>
       </c>
       <c r="C33" s="28" t="inlineStr">
         <is>
-          <t>3:50PM</t>
+          <t>9:30AM</t>
         </is>
       </c>
       <c r="D33" s="28" t="inlineStr">
@@ -12734,12 +12767,12 @@
       </c>
       <c r="B34" s="27" t="inlineStr">
         <is>
-          <t>3:50PM</t>
+          <t>9:30AM</t>
         </is>
       </c>
       <c r="C34" s="27" t="inlineStr">
         <is>
-          <t>4:05PM</t>
+          <t>9:45AM</t>
         </is>
       </c>
       <c r="D34" s="27" t="inlineStr">
@@ -12784,12 +12817,12 @@
       </c>
       <c r="B35" s="28" t="inlineStr">
         <is>
-          <t>3:50PM</t>
+          <t>9:30AM</t>
         </is>
       </c>
       <c r="C35" s="28" t="inlineStr">
         <is>
-          <t>4:05PM</t>
+          <t>9:45AM</t>
         </is>
       </c>
       <c r="D35" s="28" t="inlineStr">
@@ -12834,12 +12867,12 @@
       </c>
       <c r="B36" s="27" t="inlineStr">
         <is>
-          <t>3:50PM</t>
+          <t>9:30AM</t>
         </is>
       </c>
       <c r="C36" s="27" t="inlineStr">
         <is>
-          <t>4:05PM</t>
+          <t>9:45AM</t>
         </is>
       </c>
       <c r="D36" s="27" t="inlineStr">
@@ -12884,12 +12917,12 @@
       </c>
       <c r="B37" s="28" t="inlineStr">
         <is>
-          <t>4:05PM</t>
+          <t>9:45AM</t>
         </is>
       </c>
       <c r="C37" s="28" t="inlineStr">
         <is>
-          <t>4:20PM</t>
+          <t>10:00AM</t>
         </is>
       </c>
       <c r="D37" s="28" t="inlineStr">
@@ -12934,12 +12967,12 @@
       </c>
       <c r="B38" s="27" t="inlineStr">
         <is>
-          <t>4:05PM</t>
+          <t>9:45AM</t>
         </is>
       </c>
       <c r="C38" s="27" t="inlineStr">
         <is>
-          <t>4:20PM</t>
+          <t>10:00AM</t>
         </is>
       </c>
       <c r="D38" s="27" t="inlineStr">
@@ -12984,12 +13017,12 @@
       </c>
       <c r="B39" s="28" t="inlineStr">
         <is>
-          <t>4:20PM</t>
+          <t>10:00AM</t>
         </is>
       </c>
       <c r="C39" s="28" t="inlineStr">
         <is>
-          <t>4:35PM</t>
+          <t>10:15AM</t>
         </is>
       </c>
       <c r="D39" s="28" t="inlineStr">
@@ -13034,12 +13067,12 @@
       </c>
       <c r="B40" s="27" t="inlineStr">
         <is>
-          <t>4:20PM</t>
+          <t>10:00AM</t>
         </is>
       </c>
       <c r="C40" s="27" t="inlineStr">
         <is>
-          <t>4:35PM</t>
+          <t>10:15AM</t>
         </is>
       </c>
       <c r="D40" s="27" t="inlineStr">
@@ -13084,12 +13117,12 @@
       </c>
       <c r="B41" s="28" t="inlineStr">
         <is>
-          <t>4:35PM</t>
+          <t>10:15AM</t>
         </is>
       </c>
       <c r="C41" s="28" t="inlineStr">
         <is>
-          <t>4:50PM</t>
+          <t>10:30AM</t>
         </is>
       </c>
       <c r="D41" s="28" t="inlineStr">

--- a/Ekta_Schedule_With_Matchups.xlsx
+++ b/Ekta_Schedule_With_Matchups.xlsx
@@ -25,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="20">
+  <fonts count="24">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -135,8 +135,28 @@
       <color rgb="00FFFFFF"/>
       <sz val="12"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00CBD5E1"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="0064748B"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -186,6 +206,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="000E7490"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000F172A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00334155"/>
       </patternFill>
     </fill>
   </fills>
@@ -275,7 +305,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -437,6 +467,35 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -802,7 +861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:J60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" style="21" min="1" max="1"/>
@@ -817,576 +876,1055 @@
     <col width="9.140625" customWidth="1" style="14" min="10" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="57" t="inlineStr">
         <is>
           <t>EKTA GAMES 2026 — SCHEDULE OVERVIEW</t>
         </is>
       </c>
-    </row>
-    <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="15" t="inlineStr">
-        <is>
-          <t>Fully conflict-free: no player is ever double-booked, and a 10-minute break is inserted whenever a</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="15" t="inlineStr">
-        <is>
-          <t>player would otherwise play back-to-back in the same event, or continuously for 60+ minutes across</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="15" t="inlineStr">
-        <is>
-          <t>different events. Doubles events run once their own players are free (from 9:00 AM Aug 16); Semis and Finals for singles events wait until every group/pool match everywhere is finished.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="20.1" customHeight="1">
-      <c r="A6" s="16" t="inlineStr">
+      <c r="B1" s="58" t="n"/>
+      <c r="C1" s="58" t="n"/>
+      <c r="D1" s="58" t="n"/>
+      <c r="E1" s="58" t="n"/>
+      <c r="F1" s="31" t="n"/>
+      <c r="G1" s="31" t="n"/>
+      <c r="H1" s="31" t="n"/>
+      <c r="I1" s="31" t="n"/>
+      <c r="J1" s="31" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="59" t="inlineStr">
+        <is>
+          <t>Fully conflict-free: no player is ever double-booked, TT tables are shared across TT Women's/Men's/Doubles</t>
+        </is>
+      </c>
+      <c r="B2" s="58" t="n"/>
+      <c r="C2" s="58" t="n"/>
+      <c r="D2" s="58" t="n"/>
+      <c r="E2" s="58" t="n"/>
+      <c r="F2" s="31" t="n"/>
+      <c r="G2" s="31" t="n"/>
+      <c r="H2" s="31" t="n"/>
+      <c r="I2" s="31" t="n"/>
+      <c r="J2" s="31" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="59" t="inlineStr">
+        <is>
+          <t>and Carrom boards across Carrom Men's/Women's/Doubles, and a 10-minute break is inserted whenever a player</t>
+        </is>
+      </c>
+      <c r="B3" s="58" t="n"/>
+      <c r="C3" s="58" t="n"/>
+      <c r="D3" s="58" t="n"/>
+      <c r="E3" s="58" t="n"/>
+      <c r="F3" s="31" t="n"/>
+      <c r="G3" s="31" t="n"/>
+      <c r="H3" s="31" t="n"/>
+      <c r="I3" s="31" t="n"/>
+      <c r="J3" s="31" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="59" t="inlineStr">
+        <is>
+          <t>would otherwise play back-to-back in the same event or continuously for 60+ minutes across different events.</t>
+        </is>
+      </c>
+      <c r="B4" s="58" t="n"/>
+      <c r="C4" s="58" t="n"/>
+      <c r="D4" s="58" t="n"/>
+      <c r="E4" s="58" t="n"/>
+      <c r="F4" s="31" t="n"/>
+      <c r="G4" s="31" t="n"/>
+      <c r="H4" s="31" t="n"/>
+      <c r="I4" s="31" t="n"/>
+      <c r="J4" s="31" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="59" t="inlineStr">
+        <is>
+          <t>Carrom Women's Singles, TT Women's Singles, Pool, and Squash's Under 15 + 15-25 Bracket knockouts each follow</t>
+        </is>
+      </c>
+      <c r="B5" s="58" t="n"/>
+      <c r="C5" s="58" t="n"/>
+      <c r="D5" s="58" t="n"/>
+      <c r="E5" s="58" t="n"/>
+      <c r="F5" s="31" t="n"/>
+      <c r="G5" s="31" t="n"/>
+      <c r="H5" s="31" t="n"/>
+      <c r="I5" s="31" t="n"/>
+      <c r="J5" s="31" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="59" t="inlineStr">
+        <is>
+          <t>immediately once that event's own league stage is done. Carrom Men's, TT Men's, Chess, and Squash's Above 25</t>
+        </is>
+      </c>
+      <c r="B6" s="58" t="n"/>
+      <c r="C6" s="58" t="n"/>
+      <c r="D6" s="58" t="n"/>
+      <c r="E6" s="58" t="n"/>
+      <c r="F6" s="31" t="n"/>
+      <c r="G6" s="31" t="n"/>
+      <c r="H6" s="31" t="n"/>
+      <c r="I6" s="31" t="n"/>
+      <c r="J6" s="31" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="59" t="inlineStr">
+        <is>
+          <t>Bracket knockouts, plus both entire Doubles events (from 9:00 AM Aug 16), wait for their own gating rule.</t>
+        </is>
+      </c>
+      <c r="B7" s="58" t="n"/>
+      <c r="C7" s="58" t="n"/>
+      <c r="D7" s="58" t="n"/>
+      <c r="E7" s="58" t="n"/>
+      <c r="F7" s="31" t="n"/>
+      <c r="G7" s="31" t="n"/>
+      <c r="H7" s="31" t="n"/>
+      <c r="I7" s="31" t="n"/>
+      <c r="J7" s="31" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="31" t="n"/>
+      <c r="B8" s="31" t="n"/>
+      <c r="C8" s="31" t="n"/>
+      <c r="D8" s="31" t="n"/>
+      <c r="E8" s="31" t="n"/>
+      <c r="F8" s="31" t="n"/>
+      <c r="G8" s="31" t="n"/>
+      <c r="H8" s="31" t="n"/>
+      <c r="I8" s="31" t="n"/>
+      <c r="J8" s="31" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="60" t="inlineStr">
         <is>
           <t>DAY STRUCTURE</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="44" t="inlineStr">
+      <c r="B9" s="56" t="n"/>
+      <c r="C9" s="56" t="n"/>
+      <c r="D9" s="56" t="n"/>
+      <c r="E9" s="56" t="n"/>
+      <c r="F9" s="31" t="n"/>
+      <c r="G9" s="31" t="n"/>
+      <c r="H9" s="31" t="n"/>
+      <c r="I9" s="31" t="n"/>
+      <c r="J9" s="31" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="61" t="inlineStr">
         <is>
           <t>Day</t>
         </is>
       </c>
-      <c r="B7" s="44" t="inlineStr">
+      <c r="B10" s="61" t="inlineStr">
         <is>
           <t>Time</t>
         </is>
       </c>
-      <c r="C7" s="44" t="inlineStr">
+      <c r="C10" s="61" t="inlineStr">
         <is>
           <t>Activity</t>
         </is>
       </c>
-      <c r="D7" s="37" t="n"/>
-      <c r="E7" s="37" t="n"/>
-      <c r="F7" s="37" t="n"/>
-      <c r="G7" s="38" t="n"/>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="45" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B8" s="45" t="inlineStr">
+      <c r="D10" s="62" t="n"/>
+      <c r="E10" s="62" t="n"/>
+      <c r="F10" s="62" t="n"/>
+      <c r="G10" s="62" t="n"/>
+      <c r="H10" s="31" t="n"/>
+      <c r="I10" s="31" t="n"/>
+      <c r="J10" s="31" t="n"/>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="63" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B11" s="63" t="inlineStr">
         <is>
           <t>8:00 - 9:30 AM</t>
         </is>
       </c>
-      <c r="C8" s="46" t="inlineStr">
-        <is>
-          <t>Events begin — group/pool ("Americano") stage for all 7 non-doubles events</t>
-        </is>
-      </c>
-      <c r="D8" s="37" t="n"/>
-      <c r="E8" s="37" t="n"/>
-      <c r="F8" s="37" t="n"/>
-      <c r="G8" s="38" t="n"/>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="47" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B9" s="47" t="inlineStr">
+      <c r="C11" s="64" t="inlineStr">
+        <is>
+          <t>Events begin — league ("Americano") stage for all 7 non-doubles events</t>
+        </is>
+      </c>
+      <c r="H11" s="31" t="n"/>
+      <c r="I11" s="31" t="n"/>
+      <c r="J11" s="31" t="n"/>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" s="63" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B12" s="63" t="inlineStr">
         <is>
           <t>9:30 - 10:30 AM</t>
         </is>
       </c>
-      <c r="C9" s="48" t="inlineStr">
+      <c r="C12" s="64" t="inlineStr">
         <is>
           <t>FLAG HOISTING — Independence Day ceremony, no matches</t>
         </is>
       </c>
-      <c r="D9" s="37" t="n"/>
-      <c r="E9" s="37" t="n"/>
-      <c r="F9" s="37" t="n"/>
-      <c r="G9" s="38" t="n"/>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" s="45" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B10" s="45" t="inlineStr">
+      <c r="H12" s="31" t="n"/>
+      <c r="I12" s="31" t="n"/>
+      <c r="J12" s="31" t="n"/>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" s="63" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B13" s="63" t="inlineStr">
         <is>
           <t>10:30 AM - 12:00 PM</t>
         </is>
       </c>
-      <c r="C10" s="46" t="inlineStr">
-        <is>
-          <t>Group/pool stage resumes</t>
-        </is>
-      </c>
-      <c r="D10" s="37" t="n"/>
-      <c r="E10" s="37" t="n"/>
-      <c r="F10" s="37" t="n"/>
-      <c r="G10" s="38" t="n"/>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" s="47" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B11" s="47" t="inlineStr">
+      <c r="C13" s="64" t="inlineStr">
+        <is>
+          <t>League stage resumes</t>
+        </is>
+      </c>
+      <c r="H13" s="31" t="n"/>
+      <c r="I13" s="31" t="n"/>
+      <c r="J13" s="31" t="n"/>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" s="63" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B14" s="63" t="inlineStr">
         <is>
           <t>12:00 - 3:00 PM</t>
         </is>
       </c>
-      <c r="C11" s="48" t="inlineStr">
+      <c r="C14" s="64" t="inlineStr">
         <is>
           <t>BREAK</t>
         </is>
       </c>
-      <c r="D11" s="37" t="n"/>
-      <c r="E11" s="37" t="n"/>
-      <c r="F11" s="37" t="n"/>
-      <c r="G11" s="38" t="n"/>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" s="45" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B12" s="45" t="inlineStr">
+      <c r="H14" s="31" t="n"/>
+      <c r="I14" s="31" t="n"/>
+      <c r="J14" s="31" t="n"/>
+    </row>
+    <row r="15" ht="45" customHeight="1">
+      <c r="A15" s="63" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B15" s="63" t="inlineStr">
         <is>
           <t>3:00 - 10:00 PM</t>
         </is>
       </c>
-      <c r="C12" s="46" t="inlineStr">
-        <is>
-          <t>Group/pool stage continues</t>
-        </is>
-      </c>
-      <c r="D12" s="37" t="n"/>
-      <c r="E12" s="37" t="n"/>
-      <c r="F12" s="37" t="n"/>
-      <c r="G12" s="38" t="n"/>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="49" t="inlineStr">
+      <c r="C15" s="64" t="inlineStr">
+        <is>
+          <t>League stage continues. Carrom Women's Singles (done ~11:00 AM) and TT Women's Singles (done ~4:10 PM) each finish in full today — their knockouts run right after their own league stage ends, no waiting for other events.</t>
+        </is>
+      </c>
+      <c r="H15" s="31" t="n"/>
+      <c r="I15" s="31" t="n"/>
+      <c r="J15" s="31" t="n"/>
+    </row>
+    <row r="16" ht="45" customHeight="1">
+      <c r="A16" s="63" t="inlineStr">
         <is>
           <t>Aug 16</t>
         </is>
       </c>
-      <c r="B13" s="49" t="inlineStr">
-        <is>
-          <t>8:00 AM - 12:00 PM</t>
-        </is>
-      </c>
-      <c r="C13" s="50" t="inlineStr">
-        <is>
-          <t>Remaining group-stage matches (Chess, TT Men's Singles, Pool) continue</t>
-        </is>
-      </c>
-      <c r="D13" s="37" t="n"/>
-      <c r="E13" s="37" t="n"/>
-      <c r="F13" s="37" t="n"/>
-      <c r="G13" s="38" t="n"/>
-    </row>
-    <row r="14" ht="45" customHeight="1">
-      <c r="A14" s="47" t="inlineStr">
+      <c r="B16" s="63" t="inlineStr">
+        <is>
+          <t>8:00 AM onward</t>
+        </is>
+      </c>
+      <c r="C16" s="64" t="inlineStr">
+        <is>
+          <t>Remaining league matches continue (TT Men's, Carrom Men's, Pool, Chess). Pool's knockouts follow immediately once Pool's own league stage ends (~10:10 AM); Squash's Under 15 + 15-25 Bracket knockouts likewise follow right after Squash's own league stage (~6:39 PM Aug 15).</t>
+        </is>
+      </c>
+      <c r="H16" s="31" t="n"/>
+      <c r="I16" s="31" t="n"/>
+      <c r="J16" s="31" t="n"/>
+    </row>
+    <row r="17" ht="45" customHeight="1">
+      <c r="A17" s="63" t="inlineStr">
         <is>
           <t>Aug 16</t>
         </is>
       </c>
-      <c r="B14" s="51" t="inlineStr">
-        <is>
-          <t>9:00 - 11:15 AM</t>
-        </is>
-      </c>
-      <c r="C14" s="52" t="inlineStr">
-        <is>
-          <t>Both Doubles events (TT Doubles, Carrom Doubles) run in full — only need their own players free, don't wait for other events' groups</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" s="49" t="inlineStr">
+      <c r="B17" s="63" t="inlineStr">
+        <is>
+          <t>9:00 AM onward</t>
+        </is>
+      </c>
+      <c r="C17" s="64" t="inlineStr">
+        <is>
+          <t>Both Doubles events run once their own players are free — Carrom Doubles 9:00-10:30 AM; TT Doubles now starts 11:55 AM (TT tables are shared with TT Men's Singles, whose league stage runs until then).</t>
+        </is>
+      </c>
+      <c r="H17" s="31" t="n"/>
+      <c r="I17" s="31" t="n"/>
+      <c r="J17" s="31" t="n"/>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" s="63" t="inlineStr">
         <is>
           <t>Aug 16</t>
         </is>
       </c>
-      <c r="B15" s="49" t="inlineStr">
+      <c r="B18" s="63" t="inlineStr">
         <is>
           <t>12:00 - 3:00 PM</t>
         </is>
       </c>
-      <c r="C15" s="50" t="inlineStr">
+      <c r="C18" s="64" t="inlineStr">
         <is>
           <t>BREAK</t>
         </is>
       </c>
-      <c r="D15" s="37" t="n"/>
-      <c r="E15" s="37" t="n"/>
-      <c r="F15" s="37" t="n"/>
-      <c r="G15" s="38" t="n"/>
-    </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="51" t="inlineStr">
+      <c r="H18" s="31" t="n"/>
+      <c r="I18" s="31" t="n"/>
+      <c r="J18" s="31" t="n"/>
+    </row>
+    <row r="19" ht="45" customHeight="1">
+      <c r="A19" s="63" t="inlineStr">
         <is>
           <t>Aug 16</t>
         </is>
       </c>
-      <c r="B16" s="51" t="inlineStr">
-        <is>
-          <t>3:00 - 3:20 PM</t>
-        </is>
-      </c>
-      <c r="C16" s="52" t="inlineStr">
-        <is>
-          <t>Remaining group-stage matches finish</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="45" customHeight="1">
-      <c r="A17" s="51" t="inlineStr">
-        <is>
-          <t>Aug 16</t>
-        </is>
-      </c>
-      <c r="B17" s="51" t="inlineStr">
-        <is>
-          <t>3:20 - 5:26 PM</t>
-        </is>
-      </c>
-      <c r="C17" s="52" t="inlineStr">
-        <is>
-          <t>Semis + Finals for every singles event — starts only once every group/pool match everywhere is done</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="40" customHeight="1">
-      <c r="A18" s="53" t="inlineStr">
-        <is>
-          <t>No matches are scheduled before 8:00 AM, between 9:30-10:30 AM (Aug 15 flag hoisting), between 12:00-3:00 PM on either day, or after 10:00 PM — any match that would otherwise land in those windows rolls to the end of the window. Doubles events only need to wait for 9:00 AM Aug 16, not for other events' group stages.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="40" customHeight="1"/>
-    <row r="20">
-      <c r="A20" s="55" t="inlineStr">
+      <c r="B19" s="63" t="inlineStr">
+        <is>
+          <t>~3:20 PM</t>
+        </is>
+      </c>
+      <c r="C19" s="64" t="inlineStr">
+        <is>
+          <t>Once every event's league stage is finished, the remaining Semis/Finals begin: Carrom Men's Singles, TT Men's Singles, Chess, and Squash's Above 25 Bracket.</t>
+        </is>
+      </c>
+      <c r="H19" s="31" t="n"/>
+      <c r="I19" s="31" t="n"/>
+      <c r="J19" s="31" t="n"/>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="65" t="inlineStr">
+        <is>
+          <t>No matches are scheduled before 8:00 AM, between 9:30-10:30 AM (Aug 15 flag hoisting), between 12:00-3:00 PM on either day, or after 10:00 PM — any match that would otherwise land in those windows rolls to the end of the window.</t>
+        </is>
+      </c>
+      <c r="H20" s="31" t="n"/>
+      <c r="I20" s="31" t="n"/>
+      <c r="J20" s="31" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="31" t="n"/>
+      <c r="B21" s="31" t="n"/>
+      <c r="C21" s="31" t="n"/>
+      <c r="D21" s="31" t="n"/>
+      <c r="E21" s="31" t="n"/>
+      <c r="F21" s="31" t="n"/>
+      <c r="G21" s="31" t="n"/>
+      <c r="H21" s="31" t="n"/>
+      <c r="I21" s="31" t="n"/>
+      <c r="J21" s="31" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="60" t="inlineStr">
         <is>
           <t>EVENTS</t>
         </is>
       </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="54" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="9" t="inlineStr">
+      <c r="B22" s="56" t="n"/>
+      <c r="C22" s="56" t="n"/>
+      <c r="D22" s="56" t="n"/>
+      <c r="E22" s="56" t="n"/>
+      <c r="F22" s="31" t="n"/>
+      <c r="G22" s="31" t="n"/>
+      <c r="H22" s="31" t="n"/>
+      <c r="I22" s="31" t="n"/>
+      <c r="J22" s="31" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="61" t="inlineStr">
         <is>
           <t>Event</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B23" s="61" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr">
+      <c r="C23" s="61" t="inlineStr">
         <is>
           <t>Equipment</t>
         </is>
       </c>
-      <c r="D22" s="9" t="inlineStr">
+      <c r="D23" s="61" t="inlineStr">
         <is>
           <t>Starts</t>
         </is>
       </c>
-      <c r="E22" s="9" t="inlineStr">
+      <c r="E23" s="61" t="inlineStr">
         <is>
           <t>Finishes</t>
         </is>
       </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="F23" s="31" t="n"/>
+      <c r="G23" s="31" t="n"/>
+      <c r="H23" s="31" t="n"/>
+      <c r="I23" s="31" t="n"/>
+      <c r="J23" s="31" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="66" t="inlineStr">
         <is>
           <t>TT Women's Singles</t>
         </is>
       </c>
-      <c r="B23" s="4" t="n">
+      <c r="B24" s="63" t="n">
         <v>15</v>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C24" s="63" t="inlineStr">
         <is>
           <t>2 tables</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D24" s="63" t="inlineStr">
         <is>
           <t>Aug15 10:30AM</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>Aug16 3:50PM</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
+      <c r="E24" s="63" t="inlineStr">
+        <is>
+          <t>Aug15 4:10PM</t>
+        </is>
+      </c>
+      <c r="F24" s="31" t="n"/>
+      <c r="G24" s="31" t="n"/>
+      <c r="H24" s="31" t="n"/>
+      <c r="I24" s="31" t="n"/>
+      <c r="J24" s="31" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="66" t="inlineStr">
         <is>
           <t>Table Tennis Singles Men</t>
         </is>
       </c>
-      <c r="B24" s="6" t="n">
+      <c r="B25" s="63" t="n">
         <v>71</v>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C25" s="63" t="inlineStr">
         <is>
           <t>2 tables</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="D25" s="63" t="inlineStr">
         <is>
           <t>Aug15 8:00AM</t>
         </is>
       </c>
-      <c r="E24" s="6" t="inlineStr">
-        <is>
-          <t>Aug16 5:05PM</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="E25" s="63" t="inlineStr">
+        <is>
+          <t>Aug16 5:45PM</t>
+        </is>
+      </c>
+      <c r="F25" s="31" t="n"/>
+      <c r="G25" s="31" t="n"/>
+      <c r="H25" s="31" t="n"/>
+      <c r="I25" s="31" t="n"/>
+      <c r="J25" s="31" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="66" t="inlineStr">
         <is>
           <t>Table Tennis Doubles</t>
         </is>
       </c>
-      <c r="B25" s="4" t="n">
+      <c r="B26" s="63" t="n">
         <v>7</v>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C26" s="63" t="inlineStr">
         <is>
           <t>2 tables</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>Aug16 9:45AM</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>Aug16 11:15AM</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
+      <c r="D26" s="63" t="inlineStr">
+        <is>
+          <t>Aug16 11:55AM</t>
+        </is>
+      </c>
+      <c r="E26" s="63" t="inlineStr">
+        <is>
+          <t>Aug16 4:00PM</t>
+        </is>
+      </c>
+      <c r="F26" s="31" t="n"/>
+      <c r="G26" s="31" t="n"/>
+      <c r="H26" s="31" t="n"/>
+      <c r="I26" s="31" t="n"/>
+      <c r="J26" s="31" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="66" t="inlineStr">
         <is>
           <t>Pool</t>
         </is>
       </c>
-      <c r="B26" s="6" t="n">
+      <c r="B27" s="63" t="n">
         <v>61</v>
       </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="C27" s="63" t="inlineStr">
         <is>
           <t>2 tables</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="D27" s="63" t="inlineStr">
         <is>
           <t>Aug15 8:00AM</t>
         </is>
       </c>
-      <c r="E26" s="6" t="inlineStr">
+      <c r="E27" s="63" t="inlineStr">
+        <is>
+          <t>Aug16 11:50AM</t>
+        </is>
+      </c>
+      <c r="F27" s="31" t="n"/>
+      <c r="G27" s="31" t="n"/>
+      <c r="H27" s="31" t="n"/>
+      <c r="I27" s="31" t="n"/>
+      <c r="J27" s="31" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="66" t="inlineStr">
+        <is>
+          <t>Chess</t>
+        </is>
+      </c>
+      <c r="B28" s="63" t="n">
+        <v>58</v>
+      </c>
+      <c r="C28" s="63" t="inlineStr">
+        <is>
+          <t>2 boards</t>
+        </is>
+      </c>
+      <c r="D28" s="63" t="inlineStr">
+        <is>
+          <t>Aug15 8:00AM</t>
+        </is>
+      </c>
+      <c r="E28" s="63" t="inlineStr">
         <is>
           <t>Aug16 5:00PM</t>
         </is>
       </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>Chess</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="n">
-        <v>58</v>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>2 boards</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="F28" s="31" t="n"/>
+      <c r="G28" s="31" t="n"/>
+      <c r="H28" s="31" t="n"/>
+      <c r="I28" s="31" t="n"/>
+      <c r="J28" s="31" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="66" t="inlineStr">
+        <is>
+          <t>Carrom Singles Men</t>
+        </is>
+      </c>
+      <c r="B29" s="63" t="n">
+        <v>52</v>
+      </c>
+      <c r="C29" s="63" t="inlineStr">
+        <is>
+          <t>3 boards</t>
+        </is>
+      </c>
+      <c r="D29" s="63" t="inlineStr">
         <is>
           <t>Aug15 8:00AM</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>Aug16 5:00PM</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>Carrom Singles Men</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="n">
-        <v>52</v>
-      </c>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="E29" s="63" t="inlineStr">
+        <is>
+          <t>Aug16 4:05PM</t>
+        </is>
+      </c>
+      <c r="F29" s="31" t="n"/>
+      <c r="G29" s="31" t="n"/>
+      <c r="H29" s="31" t="n"/>
+      <c r="I29" s="31" t="n"/>
+      <c r="J29" s="31" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="66" t="inlineStr">
+        <is>
+          <t>Carrom Singles Women</t>
+        </is>
+      </c>
+      <c r="B30" s="63" t="n">
+        <v>11</v>
+      </c>
+      <c r="C30" s="63" t="inlineStr">
+        <is>
+          <t>3 boards (1 used)</t>
+        </is>
+      </c>
+      <c r="D30" s="63" t="inlineStr">
+        <is>
+          <t>Aug15 8:00AM</t>
+        </is>
+      </c>
+      <c r="E30" s="63" t="inlineStr">
+        <is>
+          <t>Aug15 11:00AM</t>
+        </is>
+      </c>
+      <c r="F30" s="31" t="n"/>
+      <c r="G30" s="31" t="n"/>
+      <c r="H30" s="31" t="n"/>
+      <c r="I30" s="31" t="n"/>
+      <c r="J30" s="31" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="66" t="inlineStr">
+        <is>
+          <t>Carrom Doubles</t>
+        </is>
+      </c>
+      <c r="B31" s="63" t="n">
+        <v>14</v>
+      </c>
+      <c r="C31" s="63" t="inlineStr">
         <is>
           <t>3 boards</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr">
+      <c r="D31" s="63" t="inlineStr">
+        <is>
+          <t>Aug16 9:00AM</t>
+        </is>
+      </c>
+      <c r="E31" s="63" t="inlineStr">
+        <is>
+          <t>Aug16 10:30AM</t>
+        </is>
+      </c>
+      <c r="F31" s="31" t="n"/>
+      <c r="G31" s="31" t="n"/>
+      <c r="H31" s="31" t="n"/>
+      <c r="I31" s="31" t="n"/>
+      <c r="J31" s="31" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="66" t="inlineStr">
+        <is>
+          <t>Squash</t>
+        </is>
+      </c>
+      <c r="B32" s="63" t="n">
+        <v>19</v>
+      </c>
+      <c r="C32" s="63" t="inlineStr">
+        <is>
+          <t>1 court</t>
+        </is>
+      </c>
+      <c r="D32" s="63" t="inlineStr">
         <is>
           <t>Aug15 8:00AM</t>
         </is>
       </c>
-      <c r="E28" s="6" t="inlineStr">
-        <is>
-          <t>Aug16 4:05PM</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>Carrom Singles Women</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>3 boards (1 used)</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>Aug15 8:00AM</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>Aug16 3:35PM</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>Carrom Doubles</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="C30" s="6" t="inlineStr">
-        <is>
-          <t>3 boards</t>
-        </is>
-      </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>Aug16 9:00AM</t>
-        </is>
-      </c>
-      <c r="E30" s="6" t="inlineStr">
-        <is>
-          <t>Aug16 10:30AM</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="30" customHeight="1">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>Squash</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>19</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>1 court</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Aug15 8:00AM</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Aug16 5:26PM</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="20.1" customHeight="1">
-      <c r="A33" s="19" t="inlineStr">
-        <is>
-          <t>Overall tournament span: Aug 15, 8:00 AM start → Aug 16, 5:26 PM finish — comfortably inside the Aug 16, 10 PM cap.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="15" customHeight="1"/>
+      <c r="E32" s="63" t="inlineStr">
+        <is>
+          <t>Aug16 4:14PM</t>
+        </is>
+      </c>
+      <c r="F32" s="31" t="n"/>
+      <c r="G32" s="31" t="n"/>
+      <c r="H32" s="31" t="n"/>
+      <c r="I32" s="31" t="n"/>
+      <c r="J32" s="31" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="31" t="n"/>
+      <c r="B33" s="31" t="n"/>
+      <c r="C33" s="31" t="n"/>
+      <c r="D33" s="31" t="n"/>
+      <c r="E33" s="31" t="n"/>
+      <c r="F33" s="31" t="n"/>
+      <c r="G33" s="31" t="n"/>
+      <c r="H33" s="31" t="n"/>
+      <c r="I33" s="31" t="n"/>
+      <c r="J33" s="31" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="67" t="inlineStr">
+        <is>
+          <t>Overall tournament span: Aug 15, 8:00 AM start → Aug 16, 5:45 PM finish — comfortably inside the Aug 16, 10 PM cap.</t>
+        </is>
+      </c>
+      <c r="F34" s="31" t="n"/>
+      <c r="G34" s="31" t="n"/>
+      <c r="H34" s="31" t="n"/>
+      <c r="I34" s="31" t="n"/>
+      <c r="J34" s="31" t="n"/>
+    </row>
     <row r="35">
-      <c r="A35" s="16" t="inlineStr">
+      <c r="A35" s="31" t="n"/>
+      <c r="B35" s="31" t="n"/>
+      <c r="C35" s="31" t="n"/>
+      <c r="D35" s="31" t="n"/>
+      <c r="E35" s="31" t="n"/>
+      <c r="F35" s="31" t="n"/>
+      <c r="G35" s="31" t="n"/>
+      <c r="H35" s="31" t="n"/>
+      <c r="I35" s="31" t="n"/>
+      <c r="J35" s="31" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="60" t="inlineStr">
         <is>
           <t>NOTES</t>
         </is>
       </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="20" t="inlineStr">
+      <c r="B36" s="56" t="n"/>
+      <c r="C36" s="56" t="n"/>
+      <c r="D36" s="56" t="n"/>
+      <c r="E36" s="56" t="n"/>
+      <c r="F36" s="31" t="n"/>
+      <c r="G36" s="31" t="n"/>
+      <c r="H36" s="31" t="n"/>
+      <c r="I36" s="31" t="n"/>
+      <c r="J36" s="31" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="65" t="inlineStr">
         <is>
           <t>Full match-by-match detail (exact times, table/board assignment, player groups) lives in each sport's own sheet — this tab is a summary only.</t>
         </is>
       </c>
+      <c r="F37" s="31" t="n"/>
+      <c r="G37" s="31" t="n"/>
+      <c r="H37" s="31" t="n"/>
+      <c r="I37" s="31" t="n"/>
+      <c r="J37" s="31" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="31" t="n"/>
+      <c r="B38" s="31" t="n"/>
+      <c r="C38" s="31" t="n"/>
+      <c r="D38" s="31" t="n"/>
+      <c r="E38" s="31" t="n"/>
+      <c r="F38" s="31" t="n"/>
+      <c r="G38" s="31" t="n"/>
+      <c r="H38" s="31" t="n"/>
+      <c r="I38" s="31" t="n"/>
+      <c r="J38" s="31" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="31" t="n"/>
+      <c r="B39" s="31" t="n"/>
+      <c r="C39" s="31" t="n"/>
+      <c r="D39" s="31" t="n"/>
+      <c r="E39" s="31" t="n"/>
+      <c r="F39" s="31" t="n"/>
+      <c r="G39" s="31" t="n"/>
+      <c r="H39" s="31" t="n"/>
+      <c r="I39" s="31" t="n"/>
+      <c r="J39" s="31" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="31" t="n"/>
+      <c r="B40" s="31" t="n"/>
+      <c r="C40" s="31" t="n"/>
+      <c r="D40" s="31" t="n"/>
+      <c r="E40" s="31" t="n"/>
+      <c r="F40" s="31" t="n"/>
+      <c r="G40" s="31" t="n"/>
+      <c r="H40" s="31" t="n"/>
+      <c r="I40" s="31" t="n"/>
+      <c r="J40" s="31" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="31" t="n"/>
+      <c r="B41" s="31" t="n"/>
+      <c r="C41" s="31" t="n"/>
+      <c r="D41" s="31" t="n"/>
+      <c r="E41" s="31" t="n"/>
+      <c r="F41" s="31" t="n"/>
+      <c r="G41" s="31" t="n"/>
+      <c r="H41" s="31" t="n"/>
+      <c r="I41" s="31" t="n"/>
+      <c r="J41" s="31" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="31" t="n"/>
+      <c r="B42" s="31" t="n"/>
+      <c r="C42" s="31" t="n"/>
+      <c r="D42" s="31" t="n"/>
+      <c r="E42" s="31" t="n"/>
+      <c r="F42" s="31" t="n"/>
+      <c r="G42" s="31" t="n"/>
+      <c r="H42" s="31" t="n"/>
+      <c r="I42" s="31" t="n"/>
+      <c r="J42" s="31" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="31" t="n"/>
+      <c r="B43" s="31" t="n"/>
+      <c r="C43" s="31" t="n"/>
+      <c r="D43" s="31" t="n"/>
+      <c r="E43" s="31" t="n"/>
+      <c r="F43" s="31" t="n"/>
+      <c r="G43" s="31" t="n"/>
+      <c r="H43" s="31" t="n"/>
+      <c r="I43" s="31" t="n"/>
+      <c r="J43" s="31" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="31" t="n"/>
+      <c r="B44" s="31" t="n"/>
+      <c r="C44" s="31" t="n"/>
+      <c r="D44" s="31" t="n"/>
+      <c r="E44" s="31" t="n"/>
+      <c r="F44" s="31" t="n"/>
+      <c r="G44" s="31" t="n"/>
+      <c r="H44" s="31" t="n"/>
+      <c r="I44" s="31" t="n"/>
+      <c r="J44" s="31" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="31" t="n"/>
+      <c r="B45" s="31" t="n"/>
+      <c r="C45" s="31" t="n"/>
+      <c r="D45" s="31" t="n"/>
+      <c r="E45" s="31" t="n"/>
+      <c r="F45" s="31" t="n"/>
+      <c r="G45" s="31" t="n"/>
+      <c r="H45" s="31" t="n"/>
+      <c r="I45" s="31" t="n"/>
+      <c r="J45" s="31" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="31" t="n"/>
+      <c r="B46" s="31" t="n"/>
+      <c r="C46" s="31" t="n"/>
+      <c r="D46" s="31" t="n"/>
+      <c r="E46" s="31" t="n"/>
+      <c r="F46" s="31" t="n"/>
+      <c r="G46" s="31" t="n"/>
+      <c r="H46" s="31" t="n"/>
+      <c r="I46" s="31" t="n"/>
+      <c r="J46" s="31" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="31" t="n"/>
+      <c r="B47" s="31" t="n"/>
+      <c r="C47" s="31" t="n"/>
+      <c r="D47" s="31" t="n"/>
+      <c r="E47" s="31" t="n"/>
+      <c r="F47" s="31" t="n"/>
+      <c r="G47" s="31" t="n"/>
+      <c r="H47" s="31" t="n"/>
+      <c r="I47" s="31" t="n"/>
+      <c r="J47" s="31" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="31" t="n"/>
+      <c r="B48" s="31" t="n"/>
+      <c r="C48" s="31" t="n"/>
+      <c r="D48" s="31" t="n"/>
+      <c r="E48" s="31" t="n"/>
+      <c r="F48" s="31" t="n"/>
+      <c r="G48" s="31" t="n"/>
+      <c r="H48" s="31" t="n"/>
+      <c r="I48" s="31" t="n"/>
+      <c r="J48" s="31" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="31" t="n"/>
+      <c r="B49" s="31" t="n"/>
+      <c r="C49" s="31" t="n"/>
+      <c r="D49" s="31" t="n"/>
+      <c r="E49" s="31" t="n"/>
+      <c r="F49" s="31" t="n"/>
+      <c r="G49" s="31" t="n"/>
+      <c r="H49" s="31" t="n"/>
+      <c r="I49" s="31" t="n"/>
+      <c r="J49" s="31" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="31" t="n"/>
+      <c r="B50" s="31" t="n"/>
+      <c r="C50" s="31" t="n"/>
+      <c r="D50" s="31" t="n"/>
+      <c r="E50" s="31" t="n"/>
+      <c r="F50" s="31" t="n"/>
+      <c r="G50" s="31" t="n"/>
+      <c r="H50" s="31" t="n"/>
+      <c r="I50" s="31" t="n"/>
+      <c r="J50" s="31" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="31" t="n"/>
+      <c r="B51" s="31" t="n"/>
+      <c r="C51" s="31" t="n"/>
+      <c r="D51" s="31" t="n"/>
+      <c r="E51" s="31" t="n"/>
+      <c r="F51" s="31" t="n"/>
+      <c r="G51" s="31" t="n"/>
+      <c r="H51" s="31" t="n"/>
+      <c r="I51" s="31" t="n"/>
+      <c r="J51" s="31" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="31" t="n"/>
+      <c r="B52" s="31" t="n"/>
+      <c r="C52" s="31" t="n"/>
+      <c r="D52" s="31" t="n"/>
+      <c r="E52" s="31" t="n"/>
+      <c r="F52" s="31" t="n"/>
+      <c r="G52" s="31" t="n"/>
+      <c r="H52" s="31" t="n"/>
+      <c r="I52" s="31" t="n"/>
+      <c r="J52" s="31" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="31" t="n"/>
+      <c r="B53" s="31" t="n"/>
+      <c r="C53" s="31" t="n"/>
+      <c r="D53" s="31" t="n"/>
+      <c r="E53" s="31" t="n"/>
+      <c r="F53" s="31" t="n"/>
+      <c r="G53" s="31" t="n"/>
+      <c r="H53" s="31" t="n"/>
+      <c r="I53" s="31" t="n"/>
+      <c r="J53" s="31" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="31" t="n"/>
+      <c r="B54" s="31" t="n"/>
+      <c r="C54" s="31" t="n"/>
+      <c r="D54" s="31" t="n"/>
+      <c r="E54" s="31" t="n"/>
+      <c r="F54" s="31" t="n"/>
+      <c r="G54" s="31" t="n"/>
+      <c r="H54" s="31" t="n"/>
+      <c r="I54" s="31" t="n"/>
+      <c r="J54" s="31" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="31" t="n"/>
+      <c r="B55" s="31" t="n"/>
+      <c r="C55" s="31" t="n"/>
+      <c r="D55" s="31" t="n"/>
+      <c r="E55" s="31" t="n"/>
+      <c r="F55" s="31" t="n"/>
+      <c r="G55" s="31" t="n"/>
+      <c r="H55" s="31" t="n"/>
+      <c r="I55" s="31" t="n"/>
+      <c r="J55" s="31" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="31" t="n"/>
+      <c r="B56" s="31" t="n"/>
+      <c r="C56" s="31" t="n"/>
+      <c r="D56" s="31" t="n"/>
+      <c r="E56" s="31" t="n"/>
+      <c r="F56" s="31" t="n"/>
+      <c r="G56" s="31" t="n"/>
+      <c r="H56" s="31" t="n"/>
+      <c r="I56" s="31" t="n"/>
+      <c r="J56" s="31" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="31" t="n"/>
+      <c r="B57" s="31" t="n"/>
+      <c r="C57" s="31" t="n"/>
+      <c r="D57" s="31" t="n"/>
+      <c r="E57" s="31" t="n"/>
+      <c r="F57" s="31" t="n"/>
+      <c r="G57" s="31" t="n"/>
+      <c r="H57" s="31" t="n"/>
+      <c r="I57" s="31" t="n"/>
+      <c r="J57" s="31" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="31" t="n"/>
+      <c r="B58" s="31" t="n"/>
+      <c r="C58" s="31" t="n"/>
+      <c r="D58" s="31" t="n"/>
+      <c r="E58" s="31" t="n"/>
+      <c r="F58" s="31" t="n"/>
+      <c r="G58" s="31" t="n"/>
+      <c r="H58" s="31" t="n"/>
+      <c r="I58" s="31" t="n"/>
+      <c r="J58" s="31" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="31" t="n"/>
+      <c r="B59" s="31" t="n"/>
+      <c r="C59" s="31" t="n"/>
+      <c r="D59" s="31" t="n"/>
+      <c r="E59" s="31" t="n"/>
+      <c r="F59" s="31" t="n"/>
+      <c r="G59" s="31" t="n"/>
+      <c r="H59" s="31" t="n"/>
+      <c r="I59" s="31" t="n"/>
+      <c r="J59" s="31" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="31" t="n"/>
+      <c r="B60" s="31" t="n"/>
+      <c r="C60" s="31" t="n"/>
+      <c r="D60" s="31" t="n"/>
+      <c r="E60" s="31" t="n"/>
+      <c r="F60" s="31" t="n"/>
+      <c r="G60" s="31" t="n"/>
+      <c r="H60" s="31" t="n"/>
+      <c r="I60" s="31" t="n"/>
+      <c r="J60" s="31" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="23">
+    <mergeCell ref="A34:E34"/>
     <mergeCell ref="C15:G15"/>
+    <mergeCell ref="A20:G20"/>
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A36:E36"/>
     <mergeCell ref="C14:G14"/>
-    <mergeCell ref="A36:E36"/>
     <mergeCell ref="A6:E6"/>
-    <mergeCell ref="A19:G19"/>
     <mergeCell ref="C10:G10"/>
+    <mergeCell ref="A7:E7"/>
     <mergeCell ref="C16:G16"/>
-    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="A37:E37"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="C12:G12"/>
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A33:E33"/>
     <mergeCell ref="C11:G11"/>
-    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A22:E22"/>
     <mergeCell ref="C17:G17"/>
-    <mergeCell ref="C7:G7"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A35:E35"/>
-    <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="C19:G19"/>
     <mergeCell ref="C13:G13"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="A9:E9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2332,12 +2870,12 @@
       </c>
       <c r="B40" s="28" t="inlineStr">
         <is>
-          <t>5:20PM</t>
+          <t>5:35PM</t>
         </is>
       </c>
       <c r="C40" s="28" t="inlineStr">
         <is>
-          <t>5:38PM</t>
+          <t>5:53PM</t>
         </is>
       </c>
       <c r="D40" s="28" t="inlineStr">
@@ -2382,12 +2920,12 @@
       </c>
       <c r="B41" s="27" t="inlineStr">
         <is>
-          <t>5:38PM</t>
+          <t>5:53PM</t>
         </is>
       </c>
       <c r="C41" s="27" t="inlineStr">
         <is>
-          <t>5:56PM</t>
+          <t>6:11PM</t>
         </is>
       </c>
       <c r="D41" s="27" t="inlineStr">
@@ -2432,12 +2970,12 @@
       </c>
       <c r="B42" s="28" t="inlineStr">
         <is>
-          <t>6:06PM</t>
+          <t>6:21PM</t>
         </is>
       </c>
       <c r="C42" s="28" t="inlineStr">
         <is>
-          <t>6:24PM</t>
+          <t>6:39PM</t>
         </is>
       </c>
       <c r="D42" s="28" t="inlineStr">
@@ -2477,17 +3015,17 @@
     <row r="43">
       <c r="A43" s="27" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="B43" s="27" t="inlineStr">
         <is>
-          <t>3:20PM</t>
+          <t>6:39PM</t>
         </is>
       </c>
       <c r="C43" s="27" t="inlineStr">
         <is>
-          <t>3:38PM</t>
+          <t>6:57PM</t>
         </is>
       </c>
       <c r="D43" s="27" t="inlineStr">
@@ -2527,17 +3065,17 @@
     <row r="44">
       <c r="A44" s="28" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="B44" s="28" t="inlineStr">
         <is>
-          <t>3:38PM</t>
+          <t>6:57PM</t>
         </is>
       </c>
       <c r="C44" s="28" t="inlineStr">
         <is>
-          <t>3:56PM</t>
+          <t>7:15PM</t>
         </is>
       </c>
       <c r="D44" s="28" t="inlineStr">
@@ -2577,17 +3115,17 @@
     <row r="45">
       <c r="A45" s="27" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="B45" s="27" t="inlineStr">
         <is>
-          <t>3:56PM</t>
+          <t>7:15PM</t>
         </is>
       </c>
       <c r="C45" s="27" t="inlineStr">
         <is>
-          <t>4:14PM</t>
+          <t>7:33PM</t>
         </is>
       </c>
       <c r="D45" s="27" t="inlineStr">
@@ -2627,17 +3165,17 @@
     <row r="46">
       <c r="A46" s="28" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="B46" s="28" t="inlineStr">
         <is>
-          <t>4:14PM</t>
+          <t>7:33PM</t>
         </is>
       </c>
       <c r="C46" s="28" t="inlineStr">
         <is>
-          <t>4:32PM</t>
+          <t>7:51PM</t>
         </is>
       </c>
       <c r="D46" s="28" t="inlineStr">
@@ -2682,12 +3220,12 @@
       </c>
       <c r="B47" s="27" t="inlineStr">
         <is>
-          <t>4:32PM</t>
+          <t>3:20PM</t>
         </is>
       </c>
       <c r="C47" s="27" t="inlineStr">
         <is>
-          <t>4:50PM</t>
+          <t>3:38PM</t>
         </is>
       </c>
       <c r="D47" s="27" t="inlineStr">
@@ -2732,12 +3270,12 @@
       </c>
       <c r="B48" s="28" t="inlineStr">
         <is>
-          <t>4:50PM</t>
+          <t>3:38PM</t>
         </is>
       </c>
       <c r="C48" s="28" t="inlineStr">
         <is>
-          <t>5:08PM</t>
+          <t>3:56PM</t>
         </is>
       </c>
       <c r="D48" s="28" t="inlineStr">
@@ -2782,12 +3320,12 @@
       </c>
       <c r="B49" s="27" t="inlineStr">
         <is>
-          <t>5:08PM</t>
+          <t>3:56PM</t>
         </is>
       </c>
       <c r="C49" s="27" t="inlineStr">
         <is>
-          <t>5:26PM</t>
+          <t>4:14PM</t>
         </is>
       </c>
       <c r="D49" s="27" t="inlineStr">
@@ -3636,17 +4174,17 @@
     <row r="28">
       <c r="A28" s="27" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="B28" s="27" t="inlineStr">
         <is>
-          <t>3:20PM</t>
+          <t>3:40PM</t>
         </is>
       </c>
       <c r="C28" s="27" t="inlineStr">
         <is>
-          <t>3:35PM</t>
+          <t>3:55PM</t>
         </is>
       </c>
       <c r="D28" s="27" t="inlineStr">
@@ -3686,17 +4224,17 @@
     <row r="29">
       <c r="A29" s="28" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="B29" s="28" t="inlineStr">
         <is>
-          <t>3:20PM</t>
+          <t>3:40PM</t>
         </is>
       </c>
       <c r="C29" s="28" t="inlineStr">
         <is>
-          <t>3:35PM</t>
+          <t>3:55PM</t>
         </is>
       </c>
       <c r="D29" s="28" t="inlineStr">
@@ -3736,17 +4274,17 @@
     <row r="30">
       <c r="A30" s="27" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="B30" s="27" t="inlineStr">
         <is>
-          <t>3:35PM</t>
+          <t>3:55PM</t>
         </is>
       </c>
       <c r="C30" s="27" t="inlineStr">
         <is>
-          <t>3:50PM</t>
+          <t>4:10PM</t>
         </is>
       </c>
       <c r="D30" s="27" t="inlineStr">
@@ -4634,12 +5172,12 @@
       </c>
       <c r="B51" s="27" t="inlineStr">
         <is>
-          <t>3:40PM</t>
+          <t>4:00PM</t>
         </is>
       </c>
       <c r="C51" s="27" t="inlineStr">
         <is>
-          <t>3:55PM</t>
+          <t>4:15PM</t>
         </is>
       </c>
       <c r="D51" s="27" t="inlineStr">
@@ -4684,12 +5222,12 @@
       </c>
       <c r="B52" s="28" t="inlineStr">
         <is>
-          <t>4:10PM</t>
+          <t>4:30PM</t>
         </is>
       </c>
       <c r="C52" s="28" t="inlineStr">
         <is>
-          <t>4:25PM</t>
+          <t>4:45PM</t>
         </is>
       </c>
       <c r="D52" s="28" t="inlineStr">
@@ -4734,12 +5272,12 @@
       </c>
       <c r="B53" s="27" t="inlineStr">
         <is>
-          <t>4:10PM</t>
+          <t>4:30PM</t>
         </is>
       </c>
       <c r="C53" s="27" t="inlineStr">
         <is>
-          <t>4:25PM</t>
+          <t>4:45PM</t>
         </is>
       </c>
       <c r="D53" s="27" t="inlineStr">
@@ -4784,12 +5322,12 @@
       </c>
       <c r="B54" s="28" t="inlineStr">
         <is>
-          <t>4:25PM</t>
+          <t>4:45PM</t>
         </is>
       </c>
       <c r="C54" s="28" t="inlineStr">
         <is>
-          <t>4:40PM</t>
+          <t>5:00PM</t>
         </is>
       </c>
       <c r="D54" s="28" t="inlineStr">
@@ -4834,12 +5372,12 @@
       </c>
       <c r="B55" s="27" t="inlineStr">
         <is>
-          <t>4:35PM</t>
+          <t>4:55PM</t>
         </is>
       </c>
       <c r="C55" s="27" t="inlineStr">
         <is>
-          <t>4:50PM</t>
+          <t>5:10PM</t>
         </is>
       </c>
       <c r="D55" s="27" t="inlineStr">
@@ -4884,12 +5422,12 @@
       </c>
       <c r="B56" s="28" t="inlineStr">
         <is>
-          <t>4:50PM</t>
+          <t>5:10PM</t>
         </is>
       </c>
       <c r="C56" s="28" t="inlineStr">
         <is>
-          <t>5:05PM</t>
+          <t>5:25PM</t>
         </is>
       </c>
       <c r="D56" s="28" t="inlineStr">
@@ -4934,12 +5472,12 @@
       </c>
       <c r="B57" s="27" t="inlineStr">
         <is>
-          <t>5:00PM</t>
+          <t>5:20PM</t>
         </is>
       </c>
       <c r="C57" s="27" t="inlineStr">
         <is>
-          <t>5:15PM</t>
+          <t>5:35PM</t>
         </is>
       </c>
       <c r="D57" s="27" t="inlineStr">
@@ -4984,12 +5522,12 @@
       </c>
       <c r="B58" s="28" t="inlineStr">
         <is>
-          <t>5:25PM</t>
+          <t>5:45PM</t>
         </is>
       </c>
       <c r="C58" s="28" t="inlineStr">
         <is>
-          <t>5:40PM</t>
+          <t>6:00PM</t>
         </is>
       </c>
       <c r="D58" s="28" t="inlineStr">
@@ -5034,12 +5572,12 @@
       </c>
       <c r="B59" s="27" t="inlineStr">
         <is>
-          <t>5:38PM</t>
+          <t>5:53PM</t>
         </is>
       </c>
       <c r="C59" s="27" t="inlineStr">
         <is>
-          <t>5:53PM</t>
+          <t>6:08PM</t>
         </is>
       </c>
       <c r="D59" s="27" t="inlineStr">
@@ -5084,12 +5622,12 @@
       </c>
       <c r="B60" s="28" t="inlineStr">
         <is>
-          <t>5:45PM</t>
+          <t>6:00PM</t>
         </is>
       </c>
       <c r="C60" s="28" t="inlineStr">
         <is>
-          <t>6:00PM</t>
+          <t>6:15PM</t>
         </is>
       </c>
       <c r="D60" s="28" t="inlineStr">
@@ -5134,12 +5672,12 @@
       </c>
       <c r="B61" s="27" t="inlineStr">
         <is>
-          <t>6:00PM</t>
+          <t>6:15PM</t>
         </is>
       </c>
       <c r="C61" s="27" t="inlineStr">
         <is>
-          <t>6:15PM</t>
+          <t>6:30PM</t>
         </is>
       </c>
       <c r="D61" s="27" t="inlineStr">
@@ -5184,12 +5722,12 @@
       </c>
       <c r="B62" s="28" t="inlineStr">
         <is>
-          <t>6:03PM</t>
+          <t>6:18PM</t>
         </is>
       </c>
       <c r="C62" s="28" t="inlineStr">
         <is>
-          <t>6:18PM</t>
+          <t>6:33PM</t>
         </is>
       </c>
       <c r="D62" s="28" t="inlineStr">
@@ -5234,12 +5772,12 @@
       </c>
       <c r="B63" s="27" t="inlineStr">
         <is>
-          <t>6:18PM</t>
+          <t>6:33PM</t>
         </is>
       </c>
       <c r="C63" s="27" t="inlineStr">
         <is>
-          <t>6:33PM</t>
+          <t>6:48PM</t>
         </is>
       </c>
       <c r="D63" s="27" t="inlineStr">
@@ -5284,12 +5822,12 @@
       </c>
       <c r="B64" s="28" t="inlineStr">
         <is>
-          <t>6:25PM</t>
+          <t>6:40PM</t>
         </is>
       </c>
       <c r="C64" s="28" t="inlineStr">
         <is>
-          <t>6:40PM</t>
+          <t>6:55PM</t>
         </is>
       </c>
       <c r="D64" s="28" t="inlineStr">
@@ -5334,12 +5872,12 @@
       </c>
       <c r="B65" s="27" t="inlineStr">
         <is>
-          <t>6:43PM</t>
+          <t>6:58PM</t>
         </is>
       </c>
       <c r="C65" s="27" t="inlineStr">
         <is>
-          <t>6:58PM</t>
+          <t>7:13PM</t>
         </is>
       </c>
       <c r="D65" s="27" t="inlineStr">
@@ -5384,12 +5922,12 @@
       </c>
       <c r="B66" s="28" t="inlineStr">
         <is>
-          <t>6:50PM</t>
+          <t>7:05PM</t>
         </is>
       </c>
       <c r="C66" s="28" t="inlineStr">
         <is>
-          <t>7:05PM</t>
+          <t>7:20PM</t>
         </is>
       </c>
       <c r="D66" s="28" t="inlineStr">
@@ -5434,12 +5972,12 @@
       </c>
       <c r="B67" s="27" t="inlineStr">
         <is>
-          <t>7:00PM</t>
+          <t>7:15PM</t>
         </is>
       </c>
       <c r="C67" s="27" t="inlineStr">
         <is>
-          <t>7:15PM</t>
+          <t>7:30PM</t>
         </is>
       </c>
       <c r="D67" s="27" t="inlineStr">
@@ -5484,12 +6022,12 @@
       </c>
       <c r="B68" s="28" t="inlineStr">
         <is>
-          <t>7:25PM</t>
+          <t>7:40PM</t>
         </is>
       </c>
       <c r="C68" s="28" t="inlineStr">
         <is>
-          <t>7:40PM</t>
+          <t>7:55PM</t>
         </is>
       </c>
       <c r="D68" s="28" t="inlineStr">
@@ -5534,12 +6072,12 @@
       </c>
       <c r="B69" s="27" t="inlineStr">
         <is>
-          <t>7:35PM</t>
+          <t>7:50PM</t>
         </is>
       </c>
       <c r="C69" s="27" t="inlineStr">
         <is>
-          <t>7:50PM</t>
+          <t>8:05PM</t>
         </is>
       </c>
       <c r="D69" s="27" t="inlineStr">
@@ -5584,12 +6122,12 @@
       </c>
       <c r="B70" s="28" t="inlineStr">
         <is>
-          <t>7:40PM</t>
+          <t>7:55PM</t>
         </is>
       </c>
       <c r="C70" s="28" t="inlineStr">
         <is>
-          <t>7:55PM</t>
+          <t>8:10PM</t>
         </is>
       </c>
       <c r="D70" s="28" t="inlineStr">
@@ -5634,12 +6172,12 @@
       </c>
       <c r="B71" s="27" t="inlineStr">
         <is>
-          <t>7:50PM</t>
+          <t>8:05PM</t>
         </is>
       </c>
       <c r="C71" s="27" t="inlineStr">
         <is>
-          <t>8:05PM</t>
+          <t>8:20PM</t>
         </is>
       </c>
       <c r="D71" s="27" t="inlineStr">
@@ -5684,12 +6222,12 @@
       </c>
       <c r="B72" s="28" t="inlineStr">
         <is>
-          <t>8:05PM</t>
+          <t>8:20PM</t>
         </is>
       </c>
       <c r="C72" s="28" t="inlineStr">
         <is>
-          <t>8:20PM</t>
+          <t>8:35PM</t>
         </is>
       </c>
       <c r="D72" s="28" t="inlineStr">
@@ -5734,12 +6272,12 @@
       </c>
       <c r="B73" s="27" t="inlineStr">
         <is>
-          <t>8:15PM</t>
+          <t>8:30PM</t>
         </is>
       </c>
       <c r="C73" s="27" t="inlineStr">
         <is>
-          <t>8:30PM</t>
+          <t>8:45PM</t>
         </is>
       </c>
       <c r="D73" s="27" t="inlineStr">
@@ -5784,12 +6322,12 @@
       </c>
       <c r="B74" s="28" t="inlineStr">
         <is>
-          <t>8:20PM</t>
+          <t>8:35PM</t>
         </is>
       </c>
       <c r="C74" s="28" t="inlineStr">
         <is>
-          <t>8:35PM</t>
+          <t>8:50PM</t>
         </is>
       </c>
       <c r="D74" s="28" t="inlineStr">
@@ -5834,12 +6372,12 @@
       </c>
       <c r="B75" s="27" t="inlineStr">
         <is>
-          <t>8:30PM</t>
+          <t>8:45PM</t>
         </is>
       </c>
       <c r="C75" s="27" t="inlineStr">
         <is>
-          <t>8:45PM</t>
+          <t>9:00PM</t>
         </is>
       </c>
       <c r="D75" s="27" t="inlineStr">
@@ -5884,12 +6422,12 @@
       </c>
       <c r="B76" s="28" t="inlineStr">
         <is>
-          <t>8:35PM</t>
+          <t>8:50PM</t>
         </is>
       </c>
       <c r="C76" s="28" t="inlineStr">
         <is>
-          <t>8:50PM</t>
+          <t>9:05PM</t>
         </is>
       </c>
       <c r="D76" s="28" t="inlineStr">
@@ -5934,12 +6472,12 @@
       </c>
       <c r="B77" s="27" t="inlineStr">
         <is>
-          <t>8:45PM</t>
+          <t>9:00PM</t>
         </is>
       </c>
       <c r="C77" s="27" t="inlineStr">
         <is>
-          <t>9:00PM</t>
+          <t>9:15PM</t>
         </is>
       </c>
       <c r="D77" s="27" t="inlineStr">
@@ -5984,12 +6522,12 @@
       </c>
       <c r="B78" s="28" t="inlineStr">
         <is>
-          <t>9:10PM</t>
+          <t>9:25PM</t>
         </is>
       </c>
       <c r="C78" s="28" t="inlineStr">
         <is>
-          <t>9:25PM</t>
+          <t>9:40PM</t>
         </is>
       </c>
       <c r="D78" s="28" t="inlineStr">
@@ -6034,12 +6572,12 @@
       </c>
       <c r="B79" s="27" t="inlineStr">
         <is>
-          <t>9:10PM</t>
+          <t>9:25PM</t>
         </is>
       </c>
       <c r="C79" s="27" t="inlineStr">
         <is>
-          <t>9:25PM</t>
+          <t>9:40PM</t>
         </is>
       </c>
       <c r="D79" s="27" t="inlineStr">
@@ -6084,12 +6622,12 @@
       </c>
       <c r="B80" s="28" t="inlineStr">
         <is>
-          <t>9:25PM</t>
+          <t>9:40PM</t>
         </is>
       </c>
       <c r="C80" s="28" t="inlineStr">
         <is>
-          <t>9:40PM</t>
+          <t>9:55PM</t>
         </is>
       </c>
       <c r="D80" s="28" t="inlineStr">
@@ -6134,12 +6672,12 @@
       </c>
       <c r="B81" s="27" t="inlineStr">
         <is>
-          <t>9:35PM</t>
+          <t>9:50PM</t>
         </is>
       </c>
       <c r="C81" s="27" t="inlineStr">
         <is>
-          <t>9:50PM</t>
+          <t>10:05PM</t>
         </is>
       </c>
       <c r="D81" s="27" t="inlineStr">
@@ -6184,12 +6722,12 @@
       </c>
       <c r="B82" s="28" t="inlineStr">
         <is>
-          <t>9:40PM</t>
+          <t>9:55PM</t>
         </is>
       </c>
       <c r="C82" s="28" t="inlineStr">
         <is>
-          <t>9:55PM</t>
+          <t>10:10PM</t>
         </is>
       </c>
       <c r="D82" s="28" t="inlineStr">
@@ -7252,17 +7790,17 @@
       </c>
       <c r="F103" s="27" t="inlineStr">
         <is>
-          <t>SR-SF1</t>
+          <t>SR-SF2</t>
         </is>
       </c>
       <c r="G103" s="27" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H103" s="27" t="inlineStr">
         <is>
-          <t>Group A 1st</t>
+          <t>Group B 1st</t>
         </is>
       </c>
       <c r="I103" s="27" t="inlineStr">
@@ -7272,7 +7810,7 @@
       </c>
       <c r="J103" s="27" t="inlineStr">
         <is>
-          <t>Group B 2nd</t>
+          <t>Group A 2nd</t>
         </is>
       </c>
     </row>
@@ -7284,17 +7822,17 @@
       </c>
       <c r="B104" s="28" t="inlineStr">
         <is>
-          <t>3:20PM</t>
+          <t>3:35PM</t>
         </is>
       </c>
       <c r="C104" s="28" t="inlineStr">
         <is>
-          <t>3:35PM</t>
+          <t>3:50PM</t>
         </is>
       </c>
       <c r="D104" s="28" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Under 46</t>
         </is>
       </c>
       <c r="E104" s="28" t="n">
@@ -7302,7 +7840,7 @@
       </c>
       <c r="F104" s="28" t="inlineStr">
         <is>
-          <t>SR-SF2</t>
+          <t>U46-SF2</t>
         </is>
       </c>
       <c r="G104" s="28" t="inlineStr">
@@ -7334,17 +7872,17 @@
       </c>
       <c r="B105" s="27" t="inlineStr">
         <is>
-          <t>3:35PM</t>
+          <t>3:50PM</t>
         </is>
       </c>
       <c r="C105" s="27" t="inlineStr">
         <is>
-          <t>3:50PM</t>
+          <t>4:05PM</t>
         </is>
       </c>
       <c r="D105" s="27" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Under 36</t>
         </is>
       </c>
       <c r="E105" s="27" t="n">
@@ -7352,17 +7890,17 @@
       </c>
       <c r="F105" s="27" t="inlineStr">
         <is>
-          <t>SR-FINAL</t>
+          <t>U36-SF2</t>
         </is>
       </c>
       <c r="G105" s="27" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H105" s="27" t="inlineStr">
         <is>
-          <t>Winner SF1</t>
+          <t>Group B 1st</t>
         </is>
       </c>
       <c r="I105" s="27" t="inlineStr">
@@ -7372,7 +7910,7 @@
       </c>
       <c r="J105" s="27" t="inlineStr">
         <is>
-          <t>Winner SF2</t>
+          <t>Group A 2nd</t>
         </is>
       </c>
     </row>
@@ -7384,17 +7922,17 @@
       </c>
       <c r="B106" s="28" t="inlineStr">
         <is>
-          <t>3:35PM</t>
+          <t>4:00PM</t>
         </is>
       </c>
       <c r="C106" s="28" t="inlineStr">
         <is>
-          <t>3:50PM</t>
+          <t>4:15PM</t>
         </is>
       </c>
       <c r="D106" s="28" t="inlineStr">
         <is>
-          <t>Under 46</t>
+          <t>Senior</t>
         </is>
       </c>
       <c r="E106" s="28" t="n">
@@ -7402,17 +7940,17 @@
       </c>
       <c r="F106" s="28" t="inlineStr">
         <is>
-          <t>U46-SF2</t>
+          <t>SR-SF1</t>
         </is>
       </c>
       <c r="G106" s="28" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H106" s="28" t="inlineStr">
         <is>
-          <t>Group B 1st</t>
+          <t>Group A 1st</t>
         </is>
       </c>
       <c r="I106" s="28" t="inlineStr">
@@ -7422,7 +7960,7 @@
       </c>
       <c r="J106" s="28" t="inlineStr">
         <is>
-          <t>Group A 2nd</t>
+          <t>Group B 2nd</t>
         </is>
       </c>
     </row>
@@ -7434,17 +7972,17 @@
       </c>
       <c r="B107" s="27" t="inlineStr">
         <is>
-          <t>3:50PM</t>
+          <t>4:05PM</t>
         </is>
       </c>
       <c r="C107" s="27" t="inlineStr">
         <is>
-          <t>4:05PM</t>
+          <t>4:20PM</t>
         </is>
       </c>
       <c r="D107" s="27" t="inlineStr">
         <is>
-          <t>Under 36</t>
+          <t>Under 32</t>
         </is>
       </c>
       <c r="E107" s="27" t="n">
@@ -7452,7 +7990,7 @@
       </c>
       <c r="F107" s="27" t="inlineStr">
         <is>
-          <t>U36-SF2</t>
+          <t>U32-FINAL</t>
         </is>
       </c>
       <c r="G107" s="27" t="inlineStr">
@@ -7462,7 +8000,7 @@
       </c>
       <c r="H107" s="27" t="inlineStr">
         <is>
-          <t>Group B 1st</t>
+          <t>Pool 1st</t>
         </is>
       </c>
       <c r="I107" s="27" t="inlineStr">
@@ -7472,7 +8010,7 @@
       </c>
       <c r="J107" s="27" t="inlineStr">
         <is>
-          <t>Group A 2nd</t>
+          <t>Pool 2nd</t>
         </is>
       </c>
     </row>
@@ -7484,17 +8022,17 @@
       </c>
       <c r="B108" s="28" t="inlineStr">
         <is>
-          <t>3:50PM</t>
+          <t>4:15PM</t>
         </is>
       </c>
       <c r="C108" s="28" t="inlineStr">
         <is>
-          <t>4:05PM</t>
+          <t>4:30PM</t>
         </is>
       </c>
       <c r="D108" s="28" t="inlineStr">
         <is>
-          <t>Under 46</t>
+          <t>Senior</t>
         </is>
       </c>
       <c r="E108" s="28" t="n">
@@ -7502,7 +8040,7 @@
       </c>
       <c r="F108" s="28" t="inlineStr">
         <is>
-          <t>U46-SF1</t>
+          <t>SR-FINAL</t>
         </is>
       </c>
       <c r="G108" s="28" t="inlineStr">
@@ -7512,7 +8050,7 @@
       </c>
       <c r="H108" s="28" t="inlineStr">
         <is>
-          <t>Group A 1st</t>
+          <t>Winner SF1</t>
         </is>
       </c>
       <c r="I108" s="28" t="inlineStr">
@@ -7522,7 +8060,7 @@
       </c>
       <c r="J108" s="28" t="inlineStr">
         <is>
-          <t>Group B 2nd</t>
+          <t>Winner SF2</t>
         </is>
       </c>
     </row>
@@ -7534,17 +8072,17 @@
       </c>
       <c r="B109" s="27" t="inlineStr">
         <is>
-          <t>4:05PM</t>
+          <t>4:20PM</t>
         </is>
       </c>
       <c r="C109" s="27" t="inlineStr">
         <is>
-          <t>4:20PM</t>
+          <t>4:35PM</t>
         </is>
       </c>
       <c r="D109" s="27" t="inlineStr">
         <is>
-          <t>Under 32</t>
+          <t>Under 15</t>
         </is>
       </c>
       <c r="E109" s="27" t="n">
@@ -7552,7 +8090,7 @@
       </c>
       <c r="F109" s="27" t="inlineStr">
         <is>
-          <t>U32-FINAL</t>
+          <t>U15-SF2</t>
         </is>
       </c>
       <c r="G109" s="27" t="inlineStr">
@@ -7562,7 +8100,7 @@
       </c>
       <c r="H109" s="27" t="inlineStr">
         <is>
-          <t>Pool 1st</t>
+          <t>Group B 1st</t>
         </is>
       </c>
       <c r="I109" s="27" t="inlineStr">
@@ -7572,7 +8110,7 @@
       </c>
       <c r="J109" s="27" t="inlineStr">
         <is>
-          <t>Pool 2nd</t>
+          <t>Group A 2nd</t>
         </is>
       </c>
     </row>
@@ -7584,17 +8122,17 @@
       </c>
       <c r="B110" s="28" t="inlineStr">
         <is>
-          <t>4:05PM</t>
+          <t>4:30PM</t>
         </is>
       </c>
       <c r="C110" s="28" t="inlineStr">
         <is>
-          <t>4:20PM</t>
+          <t>4:45PM</t>
         </is>
       </c>
       <c r="D110" s="28" t="inlineStr">
         <is>
-          <t>Under 36</t>
+          <t>Under 46</t>
         </is>
       </c>
       <c r="E110" s="28" t="n">
@@ -7602,7 +8140,7 @@
       </c>
       <c r="F110" s="28" t="inlineStr">
         <is>
-          <t>U36-SF1</t>
+          <t>U46-SF1</t>
         </is>
       </c>
       <c r="G110" s="28" t="inlineStr">
@@ -7634,12 +8172,12 @@
       </c>
       <c r="B111" s="27" t="inlineStr">
         <is>
-          <t>4:20PM</t>
+          <t>4:35PM</t>
         </is>
       </c>
       <c r="C111" s="27" t="inlineStr">
         <is>
-          <t>4:35PM</t>
+          <t>4:50PM</t>
         </is>
       </c>
       <c r="D111" s="27" t="inlineStr">
@@ -7652,7 +8190,7 @@
       </c>
       <c r="F111" s="27" t="inlineStr">
         <is>
-          <t>U15-SF2</t>
+          <t>U15-FINAL</t>
         </is>
       </c>
       <c r="G111" s="27" t="inlineStr">
@@ -7662,7 +8200,7 @@
       </c>
       <c r="H111" s="27" t="inlineStr">
         <is>
-          <t>Group B 1st</t>
+          <t>Winner SF1</t>
         </is>
       </c>
       <c r="I111" s="27" t="inlineStr">
@@ -7672,7 +8210,7 @@
       </c>
       <c r="J111" s="27" t="inlineStr">
         <is>
-          <t>Group A 2nd</t>
+          <t>Winner SF2</t>
         </is>
       </c>
     </row>
@@ -7684,12 +8222,12 @@
       </c>
       <c r="B112" s="28" t="inlineStr">
         <is>
-          <t>4:20PM</t>
+          <t>4:45PM</t>
         </is>
       </c>
       <c r="C112" s="28" t="inlineStr">
         <is>
-          <t>4:35PM</t>
+          <t>5:00PM</t>
         </is>
       </c>
       <c r="D112" s="28" t="inlineStr">
@@ -7702,7 +8240,7 @@
       </c>
       <c r="F112" s="28" t="inlineStr">
         <is>
-          <t>U36-FINAL</t>
+          <t>U36-SF1</t>
         </is>
       </c>
       <c r="G112" s="28" t="inlineStr">
@@ -7712,7 +8250,7 @@
       </c>
       <c r="H112" s="28" t="inlineStr">
         <is>
-          <t>Winner SF1</t>
+          <t>Group A 1st</t>
         </is>
       </c>
       <c r="I112" s="28" t="inlineStr">
@@ -7722,7 +8260,7 @@
       </c>
       <c r="J112" s="28" t="inlineStr">
         <is>
-          <t>Winner SF2</t>
+          <t>Group B 2nd</t>
         </is>
       </c>
     </row>
@@ -7734,17 +8272,17 @@
       </c>
       <c r="B113" s="27" t="inlineStr">
         <is>
-          <t>4:35PM</t>
+          <t>5:00PM</t>
         </is>
       </c>
       <c r="C113" s="27" t="inlineStr">
         <is>
-          <t>4:50PM</t>
+          <t>5:15PM</t>
         </is>
       </c>
       <c r="D113" s="27" t="inlineStr">
         <is>
-          <t>Under 15</t>
+          <t>Under 36</t>
         </is>
       </c>
       <c r="E113" s="27" t="n">
@@ -7752,12 +8290,12 @@
       </c>
       <c r="F113" s="27" t="inlineStr">
         <is>
-          <t>U15-FINAL</t>
+          <t>U36-FINAL</t>
         </is>
       </c>
       <c r="G113" s="27" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H113" s="27" t="inlineStr">
@@ -7784,12 +8322,12 @@
       </c>
       <c r="B114" s="28" t="inlineStr">
         <is>
-          <t>4:35PM</t>
+          <t>5:15PM</t>
         </is>
       </c>
       <c r="C114" s="28" t="inlineStr">
         <is>
-          <t>4:50PM</t>
+          <t>5:30PM</t>
         </is>
       </c>
       <c r="D114" s="28" t="inlineStr">
@@ -7834,12 +8372,12 @@
       </c>
       <c r="B115" s="27" t="inlineStr">
         <is>
-          <t>4:50PM</t>
+          <t>5:30PM</t>
         </is>
       </c>
       <c r="C115" s="27" t="inlineStr">
         <is>
-          <t>5:05PM</t>
+          <t>5:45PM</t>
         </is>
       </c>
       <c r="D115" s="27" t="inlineStr">
@@ -8108,12 +8646,12 @@
       </c>
       <c r="B20" s="27" t="inlineStr">
         <is>
-          <t>9:45AM</t>
+          <t>11:55AM</t>
         </is>
       </c>
       <c r="C20" s="27" t="inlineStr">
         <is>
-          <t>10:00AM</t>
+          <t>12:10PM</t>
         </is>
       </c>
       <c r="D20" s="27" t="inlineStr">
@@ -8126,17 +8664,17 @@
       </c>
       <c r="F20" s="27" t="inlineStr">
         <is>
-          <t>QF3</t>
+          <t>QF2</t>
         </is>
       </c>
       <c r="G20" s="27" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H20" s="27" t="inlineStr">
         <is>
-          <t>Nilesh Bagaria &amp; Parthiv</t>
+          <t>Tanmay Sharma &amp; Sankalp</t>
         </is>
       </c>
       <c r="I20" s="27" t="inlineStr">
@@ -8146,7 +8684,7 @@
       </c>
       <c r="J20" s="27" t="inlineStr">
         <is>
-          <t>Rahul Garg &amp; Nilesh Mahtre</t>
+          <t>Ravi Modi &amp; Dr Rahul Modi</t>
         </is>
       </c>
     </row>
@@ -8158,12 +8696,12 @@
       </c>
       <c r="B21" s="28" t="inlineStr">
         <is>
-          <t>10:00AM</t>
+          <t>11:55AM</t>
         </is>
       </c>
       <c r="C21" s="28" t="inlineStr">
         <is>
-          <t>10:15AM</t>
+          <t>12:10PM</t>
         </is>
       </c>
       <c r="D21" s="28" t="inlineStr">
@@ -8176,17 +8714,17 @@
       </c>
       <c r="F21" s="28" t="inlineStr">
         <is>
-          <t>QF2</t>
+          <t>QF3</t>
         </is>
       </c>
       <c r="G21" s="28" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H21" s="28" t="inlineStr">
         <is>
-          <t>Tanmay Sharma &amp; Sankalp</t>
+          <t>Nilesh Bagaria &amp; Parthiv</t>
         </is>
       </c>
       <c r="I21" s="28" t="inlineStr">
@@ -8196,7 +8734,7 @@
       </c>
       <c r="J21" s="28" t="inlineStr">
         <is>
-          <t>Ravi Modi &amp; Dr Rahul Modi</t>
+          <t>Rahul Garg &amp; Nilesh Mahtre</t>
         </is>
       </c>
     </row>
@@ -8208,12 +8746,12 @@
       </c>
       <c r="B22" s="27" t="inlineStr">
         <is>
-          <t>10:00AM</t>
+          <t>3:00PM</t>
         </is>
       </c>
       <c r="C22" s="27" t="inlineStr">
         <is>
-          <t>10:15AM</t>
+          <t>3:15PM</t>
         </is>
       </c>
       <c r="D22" s="27" t="inlineStr">
@@ -8226,17 +8764,17 @@
       </c>
       <c r="F22" s="27" t="inlineStr">
         <is>
-          <t>SF2</t>
+          <t>QF4</t>
         </is>
       </c>
       <c r="G22" s="27" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H22" s="27" t="inlineStr">
         <is>
-          <t>Winner QF3</t>
+          <t>Mayank Aggarwal &amp; Sudip Parui</t>
         </is>
       </c>
       <c r="I22" s="27" t="inlineStr">
@@ -8246,7 +8784,7 @@
       </c>
       <c r="J22" s="27" t="inlineStr">
         <is>
-          <t>Winner QF4</t>
+          <t>Nidhi Sharma &amp; Tushar</t>
         </is>
       </c>
     </row>
@@ -8258,12 +8796,12 @@
       </c>
       <c r="B23" s="28" t="inlineStr">
         <is>
-          <t>10:15AM</t>
+          <t>3:00PM</t>
         </is>
       </c>
       <c r="C23" s="28" t="inlineStr">
         <is>
-          <t>10:30AM</t>
+          <t>3:15PM</t>
         </is>
       </c>
       <c r="D23" s="28" t="inlineStr">
@@ -8276,17 +8814,17 @@
       </c>
       <c r="F23" s="28" t="inlineStr">
         <is>
-          <t>QF4</t>
+          <t>SF2</t>
         </is>
       </c>
       <c r="G23" s="28" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H23" s="28" t="inlineStr">
         <is>
-          <t>Mayank Aggarwal &amp; Sudip Parui</t>
+          <t>Winner QF3</t>
         </is>
       </c>
       <c r="I23" s="28" t="inlineStr">
@@ -8296,7 +8834,7 @@
       </c>
       <c r="J23" s="28" t="inlineStr">
         <is>
-          <t>Nidhi Sharma &amp; Tushar</t>
+          <t>Winner QF4</t>
         </is>
       </c>
     </row>
@@ -8308,12 +8846,12 @@
       </c>
       <c r="B24" s="27" t="inlineStr">
         <is>
-          <t>10:30AM</t>
+          <t>3:15PM</t>
         </is>
       </c>
       <c r="C24" s="27" t="inlineStr">
         <is>
-          <t>10:45AM</t>
+          <t>3:30PM</t>
         </is>
       </c>
       <c r="D24" s="27" t="inlineStr">
@@ -8358,12 +8896,12 @@
       </c>
       <c r="B25" s="28" t="inlineStr">
         <is>
-          <t>10:45AM</t>
+          <t>3:30PM</t>
         </is>
       </c>
       <c r="C25" s="28" t="inlineStr">
         <is>
-          <t>11:00AM</t>
+          <t>3:45PM</t>
         </is>
       </c>
       <c r="D25" s="28" t="inlineStr">
@@ -8408,12 +8946,12 @@
       </c>
       <c r="B26" s="27" t="inlineStr">
         <is>
-          <t>11:00AM</t>
+          <t>3:45PM</t>
         </is>
       </c>
       <c r="C26" s="27" t="inlineStr">
         <is>
-          <t>11:15AM</t>
+          <t>4:00PM</t>
         </is>
       </c>
       <c r="D26" s="27" t="inlineStr">
@@ -9039,12 +9577,12 @@
       </c>
       <c r="B35" s="27" t="inlineStr">
         <is>
-          <t>9:15AM</t>
+          <t>9:20AM</t>
         </is>
       </c>
       <c r="C35" s="27" t="inlineStr">
         <is>
-          <t>9:30AM</t>
+          <t>9:35AM</t>
         </is>
       </c>
       <c r="D35" s="27" t="inlineStr">
@@ -9057,17 +9595,17 @@
       </c>
       <c r="F35" s="27" t="inlineStr">
         <is>
-          <t>CM-U46-GB-1</t>
+          <t>CM-U46-GA-10</t>
         </is>
       </c>
       <c r="G35" s="27" t="inlineStr">
         <is>
-          <t>Board 2</t>
+          <t>Board 3</t>
         </is>
       </c>
       <c r="H35" s="27" t="inlineStr">
         <is>
-          <t>Mayank Aggarwal</t>
+          <t>Abhishek Dugar</t>
         </is>
       </c>
       <c r="I35" s="27" t="inlineStr">
@@ -9077,7 +9615,7 @@
       </c>
       <c r="J35" s="27" t="inlineStr">
         <is>
-          <t>Amit Ranka</t>
+          <t>Anuj Shah</t>
         </is>
       </c>
     </row>
@@ -9089,12 +9627,12 @@
       </c>
       <c r="B36" s="28" t="inlineStr">
         <is>
-          <t>9:20AM</t>
+          <t>10:30AM</t>
         </is>
       </c>
       <c r="C36" s="28" t="inlineStr">
         <is>
-          <t>9:35AM</t>
+          <t>10:45AM</t>
         </is>
       </c>
       <c r="D36" s="28" t="inlineStr">
@@ -9107,7 +9645,7 @@
       </c>
       <c r="F36" s="28" t="inlineStr">
         <is>
-          <t>CM-U46-GA-10</t>
+          <t>CM-U46-GB-2</t>
         </is>
       </c>
       <c r="G36" s="28" t="inlineStr">
@@ -9117,7 +9655,7 @@
       </c>
       <c r="H36" s="28" t="inlineStr">
         <is>
-          <t>Abhishek Dugar</t>
+          <t>Nikunj Jhala</t>
         </is>
       </c>
       <c r="I36" s="28" t="inlineStr">
@@ -9127,7 +9665,7 @@
       </c>
       <c r="J36" s="28" t="inlineStr">
         <is>
-          <t>Anuj Shah</t>
+          <t>Nilesh Bagaria</t>
         </is>
       </c>
     </row>
@@ -9139,12 +9677,12 @@
       </c>
       <c r="B37" s="27" t="inlineStr">
         <is>
-          <t>10:30AM</t>
+          <t>10:45AM</t>
         </is>
       </c>
       <c r="C37" s="27" t="inlineStr">
         <is>
-          <t>10:45AM</t>
+          <t>11:00AM</t>
         </is>
       </c>
       <c r="D37" s="27" t="inlineStr">
@@ -9157,17 +9695,17 @@
       </c>
       <c r="F37" s="27" t="inlineStr">
         <is>
-          <t>CM-U46-GA-6</t>
+          <t>CM-U46-GA-7</t>
         </is>
       </c>
       <c r="G37" s="27" t="inlineStr">
         <is>
-          <t>Board 1</t>
+          <t>Board 3</t>
         </is>
       </c>
       <c r="H37" s="27" t="inlineStr">
         <is>
-          <t>Ravi Modi</t>
+          <t>Dr Rahul Modi</t>
         </is>
       </c>
       <c r="I37" s="27" t="inlineStr">
@@ -9177,7 +9715,7 @@
       </c>
       <c r="J37" s="27" t="inlineStr">
         <is>
-          <t>Abhishek Dugar</t>
+          <t>Anuj Shah</t>
         </is>
       </c>
     </row>
@@ -9189,12 +9727,12 @@
       </c>
       <c r="B38" s="28" t="inlineStr">
         <is>
-          <t>10:30AM</t>
+          <t>10:45AM</t>
         </is>
       </c>
       <c r="C38" s="28" t="inlineStr">
         <is>
-          <t>10:45AM</t>
+          <t>11:00AM</t>
         </is>
       </c>
       <c r="D38" s="28" t="inlineStr">
@@ -9207,17 +9745,17 @@
       </c>
       <c r="F38" s="28" t="inlineStr">
         <is>
-          <t>CM-U46-GB-2</t>
+          <t>CM-U46-GB-1</t>
         </is>
       </c>
       <c r="G38" s="28" t="inlineStr">
         <is>
-          <t>Board 3</t>
+          <t>Board 2</t>
         </is>
       </c>
       <c r="H38" s="28" t="inlineStr">
         <is>
-          <t>Nikunj Jhala</t>
+          <t>Mayank Aggarwal</t>
         </is>
       </c>
       <c r="I38" s="28" t="inlineStr">
@@ -9227,7 +9765,7 @@
       </c>
       <c r="J38" s="28" t="inlineStr">
         <is>
-          <t>Nilesh Bagaria</t>
+          <t>Amit Ranka</t>
         </is>
       </c>
     </row>
@@ -9239,12 +9777,12 @@
       </c>
       <c r="B39" s="27" t="inlineStr">
         <is>
-          <t>10:45AM</t>
+          <t>11:00AM</t>
         </is>
       </c>
       <c r="C39" s="27" t="inlineStr">
         <is>
-          <t>11:00AM</t>
+          <t>11:15AM</t>
         </is>
       </c>
       <c r="D39" s="27" t="inlineStr">
@@ -9257,17 +9795,17 @@
       </c>
       <c r="F39" s="27" t="inlineStr">
         <is>
-          <t>CM-U46-GA-7</t>
+          <t>CM-U46-GA-6</t>
         </is>
       </c>
       <c r="G39" s="27" t="inlineStr">
         <is>
-          <t>Board 3</t>
+          <t>Board 1</t>
         </is>
       </c>
       <c r="H39" s="27" t="inlineStr">
         <is>
-          <t>Dr Rahul Modi</t>
+          <t>Ravi Modi</t>
         </is>
       </c>
       <c r="I39" s="27" t="inlineStr">
@@ -9277,7 +9815,7 @@
       </c>
       <c r="J39" s="27" t="inlineStr">
         <is>
-          <t>Anuj Shah</t>
+          <t>Abhishek Dugar</t>
         </is>
       </c>
     </row>
@@ -9289,12 +9827,12 @@
       </c>
       <c r="B40" s="28" t="inlineStr">
         <is>
-          <t>10:55AM</t>
+          <t>11:15AM</t>
         </is>
       </c>
       <c r="C40" s="28" t="inlineStr">
         <is>
-          <t>11:10AM</t>
+          <t>11:30AM</t>
         </is>
       </c>
       <c r="D40" s="28" t="inlineStr">
@@ -9307,17 +9845,17 @@
       </c>
       <c r="F40" s="28" t="inlineStr">
         <is>
-          <t>CM-U46-GA-2</t>
+          <t>CM-U46-GB-3</t>
         </is>
       </c>
       <c r="G40" s="28" t="inlineStr">
         <is>
-          <t>Board 2</t>
+          <t>Board 1</t>
         </is>
       </c>
       <c r="H40" s="28" t="inlineStr">
         <is>
-          <t>Ravi Modi</t>
+          <t>Amar Jain</t>
         </is>
       </c>
       <c r="I40" s="28" t="inlineStr">
@@ -9327,7 +9865,7 @@
       </c>
       <c r="J40" s="28" t="inlineStr">
         <is>
-          <t>Ankur Mahante</t>
+          <t>Vinit Padia</t>
         </is>
       </c>
     </row>
@@ -9339,12 +9877,12 @@
       </c>
       <c r="B41" s="27" t="inlineStr">
         <is>
-          <t>10:55AM</t>
+          <t>11:25AM</t>
         </is>
       </c>
       <c r="C41" s="27" t="inlineStr">
         <is>
-          <t>11:10AM</t>
+          <t>11:40AM</t>
         </is>
       </c>
       <c r="D41" s="27" t="inlineStr">
@@ -9357,17 +9895,17 @@
       </c>
       <c r="F41" s="27" t="inlineStr">
         <is>
-          <t>CM-U46-GB-3</t>
+          <t>CM-U46-GA-2</t>
         </is>
       </c>
       <c r="G41" s="27" t="inlineStr">
         <is>
-          <t>Board 1</t>
+          <t>Board 2</t>
         </is>
       </c>
       <c r="H41" s="27" t="inlineStr">
         <is>
-          <t>Amar Jain</t>
+          <t>Ravi Modi</t>
         </is>
       </c>
       <c r="I41" s="27" t="inlineStr">
@@ -9377,7 +9915,7 @@
       </c>
       <c r="J41" s="27" t="inlineStr">
         <is>
-          <t>Vinit Padia</t>
+          <t>Ankur Mahante</t>
         </is>
       </c>
     </row>
@@ -9389,12 +9927,12 @@
       </c>
       <c r="B42" s="28" t="inlineStr">
         <is>
-          <t>11:10AM</t>
+          <t>11:30AM</t>
         </is>
       </c>
       <c r="C42" s="28" t="inlineStr">
         <is>
-          <t>11:25AM</t>
+          <t>11:45AM</t>
         </is>
       </c>
       <c r="D42" s="28" t="inlineStr">
@@ -9439,12 +9977,12 @@
       </c>
       <c r="B43" s="27" t="inlineStr">
         <is>
-          <t>11:20AM</t>
+          <t>11:50AM</t>
         </is>
       </c>
       <c r="C43" s="27" t="inlineStr">
         <is>
-          <t>11:35AM</t>
+          <t>12:05PM</t>
         </is>
       </c>
       <c r="D43" s="27" t="inlineStr">
@@ -9489,12 +10027,12 @@
       </c>
       <c r="B44" s="28" t="inlineStr">
         <is>
-          <t>11:20AM</t>
+          <t>11:50AM</t>
         </is>
       </c>
       <c r="C44" s="28" t="inlineStr">
         <is>
-          <t>11:35AM</t>
+          <t>12:05PM</t>
         </is>
       </c>
       <c r="D44" s="28" t="inlineStr">
@@ -9539,12 +10077,12 @@
       </c>
       <c r="B45" s="27" t="inlineStr">
         <is>
-          <t>11:45AM</t>
+          <t>3:00PM</t>
         </is>
       </c>
       <c r="C45" s="27" t="inlineStr">
         <is>
-          <t>12:00PM</t>
+          <t>3:15PM</t>
         </is>
       </c>
       <c r="D45" s="27" t="inlineStr">
@@ -9589,12 +10127,12 @@
       </c>
       <c r="B46" s="28" t="inlineStr">
         <is>
-          <t>11:45AM</t>
+          <t>3:00PM</t>
         </is>
       </c>
       <c r="C46" s="28" t="inlineStr">
         <is>
-          <t>12:00PM</t>
+          <t>3:15PM</t>
         </is>
       </c>
       <c r="D46" s="28" t="inlineStr">
@@ -9639,12 +10177,12 @@
       </c>
       <c r="B47" s="27" t="inlineStr">
         <is>
-          <t>3:00PM</t>
+          <t>3:15PM</t>
         </is>
       </c>
       <c r="C47" s="27" t="inlineStr">
         <is>
-          <t>3:15PM</t>
+          <t>3:30PM</t>
         </is>
       </c>
       <c r="D47" s="27" t="inlineStr">
@@ -9657,17 +10195,17 @@
       </c>
       <c r="F47" s="27" t="inlineStr">
         <is>
-          <t>CM-U46-GA-11</t>
+          <t>CM-U46-GB-5</t>
         </is>
       </c>
       <c r="G47" s="27" t="inlineStr">
         <is>
-          <t>Board 1</t>
+          <t>Board 3</t>
         </is>
       </c>
       <c r="H47" s="27" t="inlineStr">
         <is>
-          <t>Ravi Modi</t>
+          <t>Mayank Aggarwal</t>
         </is>
       </c>
       <c r="I47" s="27" t="inlineStr">
@@ -9677,7 +10215,7 @@
       </c>
       <c r="J47" s="27" t="inlineStr">
         <is>
-          <t>Dr Rahul Modi</t>
+          <t>Vinit Padia</t>
         </is>
       </c>
     </row>
@@ -9689,12 +10227,12 @@
       </c>
       <c r="B48" s="28" t="inlineStr">
         <is>
-          <t>3:00PM</t>
+          <t>3:25PM</t>
         </is>
       </c>
       <c r="C48" s="28" t="inlineStr">
         <is>
-          <t>3:15PM</t>
+          <t>3:40PM</t>
         </is>
       </c>
       <c r="D48" s="28" t="inlineStr">
@@ -9707,17 +10245,17 @@
       </c>
       <c r="F48" s="28" t="inlineStr">
         <is>
-          <t>CM-U46-GA-14</t>
+          <t>CM-U46-GA-11</t>
         </is>
       </c>
       <c r="G48" s="28" t="inlineStr">
         <is>
-          <t>Board 2</t>
+          <t>Board 1</t>
         </is>
       </c>
       <c r="H48" s="28" t="inlineStr">
         <is>
-          <t>Rahul Garg</t>
+          <t>Ravi Modi</t>
         </is>
       </c>
       <c r="I48" s="28" t="inlineStr">
@@ -9727,7 +10265,7 @@
       </c>
       <c r="J48" s="28" t="inlineStr">
         <is>
-          <t>Abhishek Dugar</t>
+          <t>Dr Rahul Modi</t>
         </is>
       </c>
     </row>
@@ -9739,12 +10277,12 @@
       </c>
       <c r="B49" s="27" t="inlineStr">
         <is>
-          <t>3:00PM</t>
+          <t>3:25PM</t>
         </is>
       </c>
       <c r="C49" s="27" t="inlineStr">
         <is>
-          <t>3:15PM</t>
+          <t>3:40PM</t>
         </is>
       </c>
       <c r="D49" s="27" t="inlineStr">
@@ -9757,17 +10295,17 @@
       </c>
       <c r="F49" s="27" t="inlineStr">
         <is>
-          <t>CM-U46-GB-5</t>
+          <t>CM-U46-GA-14</t>
         </is>
       </c>
       <c r="G49" s="27" t="inlineStr">
         <is>
-          <t>Board 3</t>
+          <t>Board 2</t>
         </is>
       </c>
       <c r="H49" s="27" t="inlineStr">
         <is>
-          <t>Mayank Aggarwal</t>
+          <t>Rahul Garg</t>
         </is>
       </c>
       <c r="I49" s="27" t="inlineStr">
@@ -9777,7 +10315,7 @@
       </c>
       <c r="J49" s="27" t="inlineStr">
         <is>
-          <t>Vinit Padia</t>
+          <t>Abhishek Dugar</t>
         </is>
       </c>
     </row>
@@ -9789,12 +10327,12 @@
       </c>
       <c r="B50" s="28" t="inlineStr">
         <is>
-          <t>3:15PM</t>
+          <t>3:40PM</t>
         </is>
       </c>
       <c r="C50" s="28" t="inlineStr">
         <is>
-          <t>3:30PM</t>
+          <t>3:55PM</t>
         </is>
       </c>
       <c r="D50" s="28" t="inlineStr">
@@ -9839,12 +10377,12 @@
       </c>
       <c r="B51" s="27" t="inlineStr">
         <is>
-          <t>3:15PM</t>
+          <t>3:40PM</t>
         </is>
       </c>
       <c r="C51" s="27" t="inlineStr">
         <is>
-          <t>3:30PM</t>
+          <t>3:55PM</t>
         </is>
       </c>
       <c r="D51" s="27" t="inlineStr">
@@ -9889,12 +10427,12 @@
       </c>
       <c r="B52" s="28" t="inlineStr">
         <is>
-          <t>3:25PM</t>
+          <t>3:40PM</t>
         </is>
       </c>
       <c r="C52" s="28" t="inlineStr">
         <is>
-          <t>3:40PM</t>
+          <t>3:55PM</t>
         </is>
       </c>
       <c r="D52" s="28" t="inlineStr">
@@ -9939,12 +10477,12 @@
       </c>
       <c r="B53" s="27" t="inlineStr">
         <is>
-          <t>3:40PM</t>
+          <t>4:05PM</t>
         </is>
       </c>
       <c r="C53" s="27" t="inlineStr">
         <is>
-          <t>3:55PM</t>
+          <t>4:20PM</t>
         </is>
       </c>
       <c r="D53" s="27" t="inlineStr">
@@ -9989,12 +10527,12 @@
       </c>
       <c r="B54" s="28" t="inlineStr">
         <is>
-          <t>3:40PM</t>
+          <t>4:05PM</t>
         </is>
       </c>
       <c r="C54" s="28" t="inlineStr">
         <is>
-          <t>3:55PM</t>
+          <t>4:20PM</t>
         </is>
       </c>
       <c r="D54" s="28" t="inlineStr">
@@ -10007,17 +10545,17 @@
       </c>
       <c r="F54" s="28" t="inlineStr">
         <is>
-          <t>CM-U46-GB-8</t>
+          <t>CM-U46-GB-11</t>
         </is>
       </c>
       <c r="G54" s="28" t="inlineStr">
         <is>
-          <t>Board 3</t>
+          <t>Board 2</t>
         </is>
       </c>
       <c r="H54" s="28" t="inlineStr">
         <is>
-          <t>Amar Jain</t>
+          <t>Nikunj Jhala</t>
         </is>
       </c>
       <c r="I54" s="28" t="inlineStr">
@@ -10027,7 +10565,7 @@
       </c>
       <c r="J54" s="28" t="inlineStr">
         <is>
-          <t>Nilesh Bagaria</t>
+          <t>Vinit Padia</t>
         </is>
       </c>
     </row>
@@ -10039,12 +10577,12 @@
       </c>
       <c r="B55" s="27" t="inlineStr">
         <is>
-          <t>3:50PM</t>
+          <t>4:05PM</t>
         </is>
       </c>
       <c r="C55" s="27" t="inlineStr">
         <is>
-          <t>4:05PM</t>
+          <t>4:20PM</t>
         </is>
       </c>
       <c r="D55" s="27" t="inlineStr">
@@ -10057,17 +10595,17 @@
       </c>
       <c r="F55" s="27" t="inlineStr">
         <is>
-          <t>CM-U46-GB-11</t>
+          <t>CM-U46-GB-8</t>
         </is>
       </c>
       <c r="G55" s="27" t="inlineStr">
         <is>
-          <t>Board 2</t>
+          <t>Board 3</t>
         </is>
       </c>
       <c r="H55" s="27" t="inlineStr">
         <is>
-          <t>Nikunj Jhala</t>
+          <t>Amar Jain</t>
         </is>
       </c>
       <c r="I55" s="27" t="inlineStr">
@@ -10077,7 +10615,7 @@
       </c>
       <c r="J55" s="27" t="inlineStr">
         <is>
-          <t>Vinit Padia</t>
+          <t>Nilesh Bagaria</t>
         </is>
       </c>
     </row>
@@ -10089,12 +10627,12 @@
       </c>
       <c r="B56" s="28" t="inlineStr">
         <is>
-          <t>4:05PM</t>
+          <t>4:30PM</t>
         </is>
       </c>
       <c r="C56" s="28" t="inlineStr">
         <is>
-          <t>4:20PM</t>
+          <t>4:45PM</t>
         </is>
       </c>
       <c r="D56" s="28" t="inlineStr">
@@ -10139,12 +10677,12 @@
       </c>
       <c r="B57" s="27" t="inlineStr">
         <is>
-          <t>4:15PM</t>
+          <t>4:30PM</t>
         </is>
       </c>
       <c r="C57" s="27" t="inlineStr">
         <is>
-          <t>4:30PM</t>
+          <t>4:45PM</t>
         </is>
       </c>
       <c r="D57" s="27" t="inlineStr">
@@ -10189,12 +10727,12 @@
       </c>
       <c r="B58" s="28" t="inlineStr">
         <is>
-          <t>4:15PM</t>
+          <t>4:30PM</t>
         </is>
       </c>
       <c r="C58" s="28" t="inlineStr">
         <is>
-          <t>4:30PM</t>
+          <t>4:45PM</t>
         </is>
       </c>
       <c r="D58" s="28" t="inlineStr">
@@ -10239,12 +10777,12 @@
       </c>
       <c r="B59" s="27" t="inlineStr">
         <is>
-          <t>4:30PM</t>
+          <t>4:45PM</t>
         </is>
       </c>
       <c r="C59" s="27" t="inlineStr">
         <is>
-          <t>4:45PM</t>
+          <t>5:00PM</t>
         </is>
       </c>
       <c r="D59" s="27" t="inlineStr">
@@ -10289,12 +10827,12 @@
       </c>
       <c r="B60" s="28" t="inlineStr">
         <is>
-          <t>4:40PM</t>
+          <t>4:55PM</t>
         </is>
       </c>
       <c r="C60" s="28" t="inlineStr">
         <is>
-          <t>4:55PM</t>
+          <t>5:10PM</t>
         </is>
       </c>
       <c r="D60" s="28" t="inlineStr">
@@ -10339,12 +10877,12 @@
       </c>
       <c r="B61" s="27" t="inlineStr">
         <is>
-          <t>4:40PM</t>
+          <t>4:55PM</t>
         </is>
       </c>
       <c r="C61" s="27" t="inlineStr">
         <is>
-          <t>4:55PM</t>
+          <t>5:10PM</t>
         </is>
       </c>
       <c r="D61" s="27" t="inlineStr">
@@ -10389,12 +10927,12 @@
       </c>
       <c r="B62" s="28" t="inlineStr">
         <is>
-          <t>4:45PM</t>
+          <t>5:00PM</t>
         </is>
       </c>
       <c r="C62" s="28" t="inlineStr">
         <is>
-          <t>5:00PM</t>
+          <t>5:15PM</t>
         </is>
       </c>
       <c r="D62" s="28" t="inlineStr">
@@ -10439,12 +10977,12 @@
       </c>
       <c r="B63" s="27" t="inlineStr">
         <is>
-          <t>4:55PM</t>
+          <t>5:10PM</t>
         </is>
       </c>
       <c r="C63" s="27" t="inlineStr">
         <is>
-          <t>5:10PM</t>
+          <t>5:25PM</t>
         </is>
       </c>
       <c r="D63" s="27" t="inlineStr">
@@ -10489,12 +11027,12 @@
       </c>
       <c r="B64" s="28" t="inlineStr">
         <is>
-          <t>5:00PM</t>
+          <t>5:15PM</t>
         </is>
       </c>
       <c r="C64" s="28" t="inlineStr">
         <is>
-          <t>5:15PM</t>
+          <t>5:30PM</t>
         </is>
       </c>
       <c r="D64" s="28" t="inlineStr">
@@ -10539,12 +11077,12 @@
       </c>
       <c r="B65" s="27" t="inlineStr">
         <is>
-          <t>5:05PM</t>
+          <t>5:20PM</t>
         </is>
       </c>
       <c r="C65" s="27" t="inlineStr">
         <is>
-          <t>5:20PM</t>
+          <t>5:35PM</t>
         </is>
       </c>
       <c r="D65" s="27" t="inlineStr">
@@ -10589,12 +11127,12 @@
       </c>
       <c r="B66" s="28" t="inlineStr">
         <is>
-          <t>5:20PM</t>
+          <t>5:35PM</t>
         </is>
       </c>
       <c r="C66" s="28" t="inlineStr">
         <is>
-          <t>5:35PM</t>
+          <t>5:50PM</t>
         </is>
       </c>
       <c r="D66" s="28" t="inlineStr">
@@ -10639,12 +11177,12 @@
       </c>
       <c r="B67" s="27" t="inlineStr">
         <is>
-          <t>5:30PM</t>
+          <t>5:45PM</t>
         </is>
       </c>
       <c r="C67" s="27" t="inlineStr">
         <is>
-          <t>5:45PM</t>
+          <t>6:00PM</t>
         </is>
       </c>
       <c r="D67" s="27" t="inlineStr">
@@ -10689,12 +11227,12 @@
       </c>
       <c r="B68" s="28" t="inlineStr">
         <is>
-          <t>5:45PM</t>
+          <t>6:00PM</t>
         </is>
       </c>
       <c r="C68" s="28" t="inlineStr">
         <is>
-          <t>6:00PM</t>
+          <t>6:15PM</t>
         </is>
       </c>
       <c r="D68" s="28" t="inlineStr">
@@ -10739,12 +11277,12 @@
       </c>
       <c r="B69" s="27" t="inlineStr">
         <is>
-          <t>5:55PM</t>
+          <t>6:10PM</t>
         </is>
       </c>
       <c r="C69" s="27" t="inlineStr">
         <is>
-          <t>6:10PM</t>
+          <t>6:25PM</t>
         </is>
       </c>
       <c r="D69" s="27" t="inlineStr">
@@ -10789,12 +11327,12 @@
       </c>
       <c r="B70" s="28" t="inlineStr">
         <is>
-          <t>6:10PM</t>
+          <t>6:25PM</t>
         </is>
       </c>
       <c r="C70" s="28" t="inlineStr">
         <is>
-          <t>6:25PM</t>
+          <t>6:40PM</t>
         </is>
       </c>
       <c r="D70" s="28" t="inlineStr">
@@ -10839,12 +11377,12 @@
       </c>
       <c r="B71" s="27" t="inlineStr">
         <is>
-          <t>6:30PM</t>
+          <t>6:45PM</t>
         </is>
       </c>
       <c r="C71" s="27" t="inlineStr">
         <is>
-          <t>6:45PM</t>
+          <t>7:00PM</t>
         </is>
       </c>
       <c r="D71" s="27" t="inlineStr">
@@ -10889,12 +11427,12 @@
       </c>
       <c r="B72" s="28" t="inlineStr">
         <is>
-          <t>6:35PM</t>
+          <t>6:50PM</t>
         </is>
       </c>
       <c r="C72" s="28" t="inlineStr">
         <is>
-          <t>6:50PM</t>
+          <t>7:05PM</t>
         </is>
       </c>
       <c r="D72" s="28" t="inlineStr">
@@ -10939,12 +11477,12 @@
       </c>
       <c r="B73" s="27" t="inlineStr">
         <is>
-          <t>6:55PM</t>
+          <t>7:10PM</t>
         </is>
       </c>
       <c r="C73" s="27" t="inlineStr">
         <is>
-          <t>7:10PM</t>
+          <t>7:25PM</t>
         </is>
       </c>
       <c r="D73" s="27" t="inlineStr">
@@ -10989,12 +11527,12 @@
       </c>
       <c r="B74" s="28" t="inlineStr">
         <is>
-          <t>8:25PM</t>
+          <t>8:40PM</t>
         </is>
       </c>
       <c r="C74" s="28" t="inlineStr">
         <is>
-          <t>8:40PM</t>
+          <t>8:55PM</t>
         </is>
       </c>
       <c r="D74" s="28" t="inlineStr">
@@ -11039,12 +11577,12 @@
       </c>
       <c r="B75" s="27" t="inlineStr">
         <is>
-          <t>9:05PM</t>
+          <t>9:20PM</t>
         </is>
       </c>
       <c r="C75" s="27" t="inlineStr">
         <is>
-          <t>9:20PM</t>
+          <t>9:35PM</t>
         </is>
       </c>
       <c r="D75" s="27" t="inlineStr">
@@ -12123,17 +12661,17 @@
     <row r="27">
       <c r="A27" s="27" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="B27" s="27" t="inlineStr">
         <is>
-          <t>3:20PM</t>
+          <t>10:45AM</t>
         </is>
       </c>
       <c r="C27" s="27" t="inlineStr">
         <is>
-          <t>3:35PM</t>
+          <t>11:00AM</t>
         </is>
       </c>
       <c r="D27" s="27" t="inlineStr">
@@ -14290,12 +14828,12 @@
       </c>
       <c r="B46" s="27" t="inlineStr">
         <is>
-          <t>3:00PM</t>
+          <t>3:15PM</t>
         </is>
       </c>
       <c r="C46" s="27" t="inlineStr">
         <is>
-          <t>3:20PM</t>
+          <t>3:35PM</t>
         </is>
       </c>
       <c r="D46" s="27" t="inlineStr">
@@ -14340,12 +14878,12 @@
       </c>
       <c r="B47" s="28" t="inlineStr">
         <is>
-          <t>3:15PM</t>
+          <t>3:30PM</t>
         </is>
       </c>
       <c r="C47" s="28" t="inlineStr">
         <is>
-          <t>3:35PM</t>
+          <t>3:50PM</t>
         </is>
       </c>
       <c r="D47" s="28" t="inlineStr">
@@ -14390,12 +14928,12 @@
       </c>
       <c r="B48" s="27" t="inlineStr">
         <is>
-          <t>3:20PM</t>
+          <t>3:40PM</t>
         </is>
       </c>
       <c r="C48" s="27" t="inlineStr">
         <is>
-          <t>3:40PM</t>
+          <t>4:00PM</t>
         </is>
       </c>
       <c r="D48" s="27" t="inlineStr">
@@ -14440,12 +14978,12 @@
       </c>
       <c r="B49" s="28" t="inlineStr">
         <is>
-          <t>3:35PM</t>
+          <t>3:50PM</t>
         </is>
       </c>
       <c r="C49" s="28" t="inlineStr">
         <is>
-          <t>3:55PM</t>
+          <t>4:10PM</t>
         </is>
       </c>
       <c r="D49" s="28" t="inlineStr">
@@ -14490,12 +15028,12 @@
       </c>
       <c r="B50" s="27" t="inlineStr">
         <is>
-          <t>3:50PM</t>
+          <t>4:10PM</t>
         </is>
       </c>
       <c r="C50" s="27" t="inlineStr">
         <is>
-          <t>4:10PM</t>
+          <t>4:30PM</t>
         </is>
       </c>
       <c r="D50" s="27" t="inlineStr">
@@ -14540,12 +15078,12 @@
       </c>
       <c r="B51" s="28" t="inlineStr">
         <is>
-          <t>3:55PM</t>
+          <t>4:10PM</t>
         </is>
       </c>
       <c r="C51" s="28" t="inlineStr">
         <is>
-          <t>4:15PM</t>
+          <t>4:30PM</t>
         </is>
       </c>
       <c r="D51" s="28" t="inlineStr">
@@ -14590,12 +15128,12 @@
       </c>
       <c r="B52" s="27" t="inlineStr">
         <is>
-          <t>4:15PM</t>
+          <t>4:30PM</t>
         </is>
       </c>
       <c r="C52" s="27" t="inlineStr">
         <is>
-          <t>4:35PM</t>
+          <t>4:50PM</t>
         </is>
       </c>
       <c r="D52" s="27" t="inlineStr">
@@ -14640,12 +15178,12 @@
       </c>
       <c r="B53" s="28" t="inlineStr">
         <is>
-          <t>4:55PM</t>
+          <t>5:10PM</t>
         </is>
       </c>
       <c r="C53" s="28" t="inlineStr">
         <is>
-          <t>5:15PM</t>
+          <t>5:30PM</t>
         </is>
       </c>
       <c r="D53" s="28" t="inlineStr">
@@ -14690,12 +15228,12 @@
       </c>
       <c r="B54" s="27" t="inlineStr">
         <is>
-          <t>5:10PM</t>
+          <t>5:25PM</t>
         </is>
       </c>
       <c r="C54" s="27" t="inlineStr">
         <is>
-          <t>5:30PM</t>
+          <t>5:45PM</t>
         </is>
       </c>
       <c r="D54" s="27" t="inlineStr">
@@ -14740,12 +15278,12 @@
       </c>
       <c r="B55" s="28" t="inlineStr">
         <is>
-          <t>5:15PM</t>
+          <t>5:30PM</t>
         </is>
       </c>
       <c r="C55" s="28" t="inlineStr">
         <is>
-          <t>5:35PM</t>
+          <t>5:50PM</t>
         </is>
       </c>
       <c r="D55" s="28" t="inlineStr">
@@ -14790,12 +15328,12 @@
       </c>
       <c r="B56" s="27" t="inlineStr">
         <is>
-          <t>5:40PM</t>
+          <t>5:55PM</t>
         </is>
       </c>
       <c r="C56" s="27" t="inlineStr">
         <is>
-          <t>6:00PM</t>
+          <t>6:15PM</t>
         </is>
       </c>
       <c r="D56" s="27" t="inlineStr">
@@ -14840,12 +15378,12 @@
       </c>
       <c r="B57" s="28" t="inlineStr">
         <is>
-          <t>5:45PM</t>
+          <t>6:00PM</t>
         </is>
       </c>
       <c r="C57" s="28" t="inlineStr">
         <is>
-          <t>6:05PM</t>
+          <t>6:20PM</t>
         </is>
       </c>
       <c r="D57" s="28" t="inlineStr">
@@ -14890,12 +15428,12 @@
       </c>
       <c r="B58" s="27" t="inlineStr">
         <is>
-          <t>6:10PM</t>
+          <t>6:25PM</t>
         </is>
       </c>
       <c r="C58" s="27" t="inlineStr">
         <is>
-          <t>6:30PM</t>
+          <t>6:45PM</t>
         </is>
       </c>
       <c r="D58" s="27" t="inlineStr">
@@ -14940,12 +15478,12 @@
       </c>
       <c r="B59" s="28" t="inlineStr">
         <is>
-          <t>6:10PM</t>
+          <t>6:25PM</t>
         </is>
       </c>
       <c r="C59" s="28" t="inlineStr">
         <is>
-          <t>6:30PM</t>
+          <t>6:45PM</t>
         </is>
       </c>
       <c r="D59" s="28" t="inlineStr">
@@ -14990,12 +15528,12 @@
       </c>
       <c r="B60" s="27" t="inlineStr">
         <is>
-          <t>6:30PM</t>
+          <t>6:45PM</t>
         </is>
       </c>
       <c r="C60" s="27" t="inlineStr">
         <is>
-          <t>6:50PM</t>
+          <t>7:05PM</t>
         </is>
       </c>
       <c r="D60" s="27" t="inlineStr">
@@ -15040,12 +15578,12 @@
       </c>
       <c r="B61" s="28" t="inlineStr">
         <is>
-          <t>6:40PM</t>
+          <t>6:55PM</t>
         </is>
       </c>
       <c r="C61" s="28" t="inlineStr">
         <is>
-          <t>7:00PM</t>
+          <t>7:15PM</t>
         </is>
       </c>
       <c r="D61" s="28" t="inlineStr">
@@ -15090,12 +15628,12 @@
       </c>
       <c r="B62" s="27" t="inlineStr">
         <is>
-          <t>6:50PM</t>
+          <t>7:05PM</t>
         </is>
       </c>
       <c r="C62" s="27" t="inlineStr">
         <is>
-          <t>7:10PM</t>
+          <t>7:25PM</t>
         </is>
       </c>
       <c r="D62" s="27" t="inlineStr">
@@ -15140,12 +15678,12 @@
       </c>
       <c r="B63" s="28" t="inlineStr">
         <is>
-          <t>7:00PM</t>
+          <t>7:15PM</t>
         </is>
       </c>
       <c r="C63" s="28" t="inlineStr">
         <is>
-          <t>7:20PM</t>
+          <t>7:35PM</t>
         </is>
       </c>
       <c r="D63" s="28" t="inlineStr">
@@ -15190,12 +15728,12 @@
       </c>
       <c r="B64" s="27" t="inlineStr">
         <is>
-          <t>7:20PM</t>
+          <t>7:35PM</t>
         </is>
       </c>
       <c r="C64" s="27" t="inlineStr">
         <is>
-          <t>7:40PM</t>
+          <t>7:55PM</t>
         </is>
       </c>
       <c r="D64" s="27" t="inlineStr">
@@ -15240,12 +15778,12 @@
       </c>
       <c r="B65" s="28" t="inlineStr">
         <is>
-          <t>7:35PM</t>
+          <t>7:50PM</t>
         </is>
       </c>
       <c r="C65" s="28" t="inlineStr">
         <is>
-          <t>7:55PM</t>
+          <t>8:10PM</t>
         </is>
       </c>
       <c r="D65" s="28" t="inlineStr">
@@ -15290,12 +15828,12 @@
       </c>
       <c r="B66" s="27" t="inlineStr">
         <is>
-          <t>7:55PM</t>
+          <t>8:10PM</t>
         </is>
       </c>
       <c r="C66" s="27" t="inlineStr">
         <is>
-          <t>8:15PM</t>
+          <t>8:30PM</t>
         </is>
       </c>
       <c r="D66" s="27" t="inlineStr">
@@ -15340,12 +15878,12 @@
       </c>
       <c r="B67" s="28" t="inlineStr">
         <is>
-          <t>8:05PM</t>
+          <t>8:20PM</t>
         </is>
       </c>
       <c r="C67" s="28" t="inlineStr">
         <is>
-          <t>8:25PM</t>
+          <t>8:40PM</t>
         </is>
       </c>
       <c r="D67" s="28" t="inlineStr">
@@ -15390,12 +15928,12 @@
       </c>
       <c r="B68" s="27" t="inlineStr">
         <is>
-          <t>8:25PM</t>
+          <t>8:40PM</t>
         </is>
       </c>
       <c r="C68" s="27" t="inlineStr">
         <is>
-          <t>8:45PM</t>
+          <t>9:00PM</t>
         </is>
       </c>
       <c r="D68" s="27" t="inlineStr">
@@ -15440,12 +15978,12 @@
       </c>
       <c r="B69" s="28" t="inlineStr">
         <is>
-          <t>8:25PM</t>
+          <t>8:40PM</t>
         </is>
       </c>
       <c r="C69" s="28" t="inlineStr">
         <is>
-          <t>8:45PM</t>
+          <t>9:00PM</t>
         </is>
       </c>
       <c r="D69" s="28" t="inlineStr">
@@ -15490,12 +16028,12 @@
       </c>
       <c r="B70" s="27" t="inlineStr">
         <is>
-          <t>8:45PM</t>
+          <t>9:00PM</t>
         </is>
       </c>
       <c r="C70" s="27" t="inlineStr">
         <is>
-          <t>9:05PM</t>
+          <t>9:20PM</t>
         </is>
       </c>
       <c r="D70" s="27" t="inlineStr">
@@ -15540,12 +16078,12 @@
       </c>
       <c r="B71" s="28" t="inlineStr">
         <is>
-          <t>8:45PM</t>
+          <t>9:00PM</t>
         </is>
       </c>
       <c r="C71" s="28" t="inlineStr">
         <is>
-          <t>9:05PM</t>
+          <t>9:20PM</t>
         </is>
       </c>
       <c r="D71" s="28" t="inlineStr">
@@ -15590,12 +16128,12 @@
       </c>
       <c r="B72" s="27" t="inlineStr">
         <is>
-          <t>9:05PM</t>
+          <t>9:20PM</t>
         </is>
       </c>
       <c r="C72" s="27" t="inlineStr">
         <is>
-          <t>9:25PM</t>
+          <t>9:40PM</t>
         </is>
       </c>
       <c r="D72" s="27" t="inlineStr">
@@ -15640,12 +16178,12 @@
       </c>
       <c r="B73" s="28" t="inlineStr">
         <is>
-          <t>9:05PM</t>
+          <t>9:20PM</t>
         </is>
       </c>
       <c r="C73" s="28" t="inlineStr">
         <is>
-          <t>9:25PM</t>
+          <t>9:40PM</t>
         </is>
       </c>
       <c r="D73" s="28" t="inlineStr">
@@ -15690,12 +16228,12 @@
       </c>
       <c r="B74" s="27" t="inlineStr">
         <is>
-          <t>9:25PM</t>
+          <t>9:40PM</t>
         </is>
       </c>
       <c r="C74" s="27" t="inlineStr">
         <is>
-          <t>9:45PM</t>
+          <t>10:00PM</t>
         </is>
       </c>
       <c r="D74" s="27" t="inlineStr">
@@ -15740,12 +16278,12 @@
       </c>
       <c r="B75" s="28" t="inlineStr">
         <is>
-          <t>9:35PM</t>
+          <t>9:50PM</t>
         </is>
       </c>
       <c r="C75" s="28" t="inlineStr">
         <is>
-          <t>9:55PM</t>
+          <t>10:10PM</t>
         </is>
       </c>
       <c r="D75" s="28" t="inlineStr">
@@ -15785,17 +16323,17 @@
     <row r="76">
       <c r="A76" s="27" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B76" s="27" t="inlineStr">
         <is>
-          <t>9:55PM</t>
+          <t>8:00AM</t>
         </is>
       </c>
       <c r="C76" s="27" t="inlineStr">
         <is>
-          <t>10:15PM</t>
+          <t>8:20AM</t>
         </is>
       </c>
       <c r="D76" s="27" t="inlineStr">
@@ -15835,17 +16373,17 @@
     <row r="77">
       <c r="A77" s="28" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B77" s="28" t="inlineStr">
         <is>
-          <t>9:55PM</t>
+          <t>8:00AM</t>
         </is>
       </c>
       <c r="C77" s="28" t="inlineStr">
         <is>
-          <t>10:15PM</t>
+          <t>8:20AM</t>
         </is>
       </c>
       <c r="D77" s="28" t="inlineStr">
@@ -15890,12 +16428,12 @@
       </c>
       <c r="B78" s="27" t="inlineStr">
         <is>
-          <t>8:00AM</t>
+          <t>8:20AM</t>
         </is>
       </c>
       <c r="C78" s="27" t="inlineStr">
         <is>
-          <t>8:20AM</t>
+          <t>8:40AM</t>
         </is>
       </c>
       <c r="D78" s="27" t="inlineStr">
@@ -15908,17 +16446,17 @@
       </c>
       <c r="F78" s="27" t="inlineStr">
         <is>
-          <t>U26-GB-2</t>
+          <t>U26-GA-3</t>
         </is>
       </c>
       <c r="G78" s="27" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H78" s="27" t="inlineStr">
         <is>
-          <t>Pranit Shriyan</t>
+          <t>Aadit Joshi</t>
         </is>
       </c>
       <c r="I78" s="27" t="inlineStr">
@@ -15928,7 +16466,7 @@
       </c>
       <c r="J78" s="27" t="inlineStr">
         <is>
-          <t>Rahul Garg</t>
+          <t>Sankalp Bhatnagar</t>
         </is>
       </c>
     </row>
@@ -15940,12 +16478,12 @@
       </c>
       <c r="B79" s="28" t="inlineStr">
         <is>
-          <t>8:15AM</t>
+          <t>8:30AM</t>
         </is>
       </c>
       <c r="C79" s="28" t="inlineStr">
         <is>
-          <t>8:35AM</t>
+          <t>8:50AM</t>
         </is>
       </c>
       <c r="D79" s="28" t="inlineStr">
@@ -15958,17 +16496,17 @@
       </c>
       <c r="F79" s="28" t="inlineStr">
         <is>
-          <t>U26-GA-3</t>
+          <t>U26-GB-2</t>
         </is>
       </c>
       <c r="G79" s="28" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H79" s="28" t="inlineStr">
         <is>
-          <t>Aadit Joshi</t>
+          <t>Pranit Shriyan</t>
         </is>
       </c>
       <c r="I79" s="28" t="inlineStr">
@@ -15978,7 +16516,7 @@
       </c>
       <c r="J79" s="28" t="inlineStr">
         <is>
-          <t>Sankalp Bhatnagar</t>
+          <t>Rahul Garg</t>
         </is>
       </c>
     </row>
@@ -15990,12 +16528,12 @@
       </c>
       <c r="B80" s="27" t="inlineStr">
         <is>
-          <t>8:35AM</t>
+          <t>8:50AM</t>
         </is>
       </c>
       <c r="C80" s="27" t="inlineStr">
         <is>
-          <t>8:55AM</t>
+          <t>9:10AM</t>
         </is>
       </c>
       <c r="D80" s="27" t="inlineStr">
@@ -16008,17 +16546,17 @@
       </c>
       <c r="F80" s="27" t="inlineStr">
         <is>
-          <t>U26-GB-4</t>
+          <t>U26-GA-5</t>
         </is>
       </c>
       <c r="G80" s="27" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H80" s="27" t="inlineStr">
         <is>
-          <t>Ishaan Merchant</t>
+          <t>Aadit Joshi</t>
         </is>
       </c>
       <c r="I80" s="27" t="inlineStr">
@@ -16028,7 +16566,7 @@
       </c>
       <c r="J80" s="27" t="inlineStr">
         <is>
-          <t>Rahul Garg</t>
+          <t>Rutvij sawant</t>
         </is>
       </c>
     </row>
@@ -16040,12 +16578,12 @@
       </c>
       <c r="B81" s="28" t="inlineStr">
         <is>
-          <t>8:45AM</t>
+          <t>9:00AM</t>
         </is>
       </c>
       <c r="C81" s="28" t="inlineStr">
         <is>
-          <t>9:05AM</t>
+          <t>9:20AM</t>
         </is>
       </c>
       <c r="D81" s="28" t="inlineStr">
@@ -16058,17 +16596,17 @@
       </c>
       <c r="F81" s="28" t="inlineStr">
         <is>
-          <t>U26-GA-5</t>
+          <t>U26-GB-4</t>
         </is>
       </c>
       <c r="G81" s="28" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H81" s="28" t="inlineStr">
         <is>
-          <t>Aadit Joshi</t>
+          <t>Ishaan Merchant</t>
         </is>
       </c>
       <c r="I81" s="28" t="inlineStr">
@@ -16078,7 +16616,7 @@
       </c>
       <c r="J81" s="28" t="inlineStr">
         <is>
-          <t>Rutvij sawant</t>
+          <t>Rahul Garg</t>
         </is>
       </c>
     </row>
@@ -16090,12 +16628,12 @@
       </c>
       <c r="B82" s="27" t="inlineStr">
         <is>
-          <t>9:05AM</t>
+          <t>9:30AM</t>
         </is>
       </c>
       <c r="C82" s="27" t="inlineStr">
         <is>
-          <t>9:25AM</t>
+          <t>9:50AM</t>
         </is>
       </c>
       <c r="D82" s="27" t="inlineStr">
@@ -16190,12 +16728,12 @@
       </c>
       <c r="B84" s="27" t="inlineStr">
         <is>
-          <t>3:20PM</t>
+          <t>10:10AM</t>
         </is>
       </c>
       <c r="C84" s="27" t="inlineStr">
         <is>
-          <t>3:40PM</t>
+          <t>10:30AM</t>
         </is>
       </c>
       <c r="D84" s="27" t="inlineStr">
@@ -16240,12 +16778,12 @@
       </c>
       <c r="B85" s="28" t="inlineStr">
         <is>
-          <t>3:20PM</t>
+          <t>10:10AM</t>
         </is>
       </c>
       <c r="C85" s="28" t="inlineStr">
         <is>
-          <t>3:40PM</t>
+          <t>10:30AM</t>
         </is>
       </c>
       <c r="D85" s="28" t="inlineStr">
@@ -16290,12 +16828,12 @@
       </c>
       <c r="B86" s="27" t="inlineStr">
         <is>
-          <t>3:40PM</t>
+          <t>10:30AM</t>
         </is>
       </c>
       <c r="C86" s="27" t="inlineStr">
         <is>
-          <t>4:00PM</t>
+          <t>10:50AM</t>
         </is>
       </c>
       <c r="D86" s="27" t="inlineStr">
@@ -16340,12 +16878,12 @@
       </c>
       <c r="B87" s="28" t="inlineStr">
         <is>
-          <t>3:40PM</t>
+          <t>10:30AM</t>
         </is>
       </c>
       <c r="C87" s="28" t="inlineStr">
         <is>
-          <t>4:00PM</t>
+          <t>10:50AM</t>
         </is>
       </c>
       <c r="D87" s="28" t="inlineStr">
@@ -16390,12 +16928,12 @@
       </c>
       <c r="B88" s="27" t="inlineStr">
         <is>
-          <t>4:00PM</t>
+          <t>10:50AM</t>
         </is>
       </c>
       <c r="C88" s="27" t="inlineStr">
         <is>
-          <t>4:20PM</t>
+          <t>11:10AM</t>
         </is>
       </c>
       <c r="D88" s="27" t="inlineStr">
@@ -16440,12 +16978,12 @@
       </c>
       <c r="B89" s="28" t="inlineStr">
         <is>
-          <t>4:00PM</t>
+          <t>10:50AM</t>
         </is>
       </c>
       <c r="C89" s="28" t="inlineStr">
         <is>
-          <t>4:20PM</t>
+          <t>11:10AM</t>
         </is>
       </c>
       <c r="D89" s="28" t="inlineStr">
@@ -16490,12 +17028,12 @@
       </c>
       <c r="B90" s="27" t="inlineStr">
         <is>
-          <t>4:20PM</t>
+          <t>11:10AM</t>
         </is>
       </c>
       <c r="C90" s="27" t="inlineStr">
         <is>
-          <t>4:40PM</t>
+          <t>11:30AM</t>
         </is>
       </c>
       <c r="D90" s="27" t="inlineStr">
@@ -16540,12 +17078,12 @@
       </c>
       <c r="B91" s="28" t="inlineStr">
         <is>
-          <t>4:20PM</t>
+          <t>11:10AM</t>
         </is>
       </c>
       <c r="C91" s="28" t="inlineStr">
         <is>
-          <t>4:40PM</t>
+          <t>11:30AM</t>
         </is>
       </c>
       <c r="D91" s="28" t="inlineStr">
@@ -16590,12 +17128,12 @@
       </c>
       <c r="B92" s="27" t="inlineStr">
         <is>
-          <t>4:40PM</t>
+          <t>11:30AM</t>
         </is>
       </c>
       <c r="C92" s="27" t="inlineStr">
         <is>
-          <t>5:00PM</t>
+          <t>11:50AM</t>
         </is>
       </c>
       <c r="D92" s="27" t="inlineStr">
@@ -18366,12 +18904,12 @@
       </c>
       <c r="B64" s="28" t="inlineStr">
         <is>
-          <t>4:40PM</t>
+          <t>4:45PM</t>
         </is>
       </c>
       <c r="C64" s="28" t="inlineStr">
         <is>
-          <t>5:00PM</t>
+          <t>5:05PM</t>
         </is>
       </c>
       <c r="D64" s="28" t="inlineStr">
@@ -18416,12 +18954,12 @@
       </c>
       <c r="B65" s="27" t="inlineStr">
         <is>
-          <t>4:55PM</t>
+          <t>5:10PM</t>
         </is>
       </c>
       <c r="C65" s="27" t="inlineStr">
         <is>
-          <t>5:15PM</t>
+          <t>5:30PM</t>
         </is>
       </c>
       <c r="D65" s="27" t="inlineStr">
@@ -18466,12 +19004,12 @@
       </c>
       <c r="B66" s="28" t="inlineStr">
         <is>
-          <t>5:25PM</t>
+          <t>5:40PM</t>
         </is>
       </c>
       <c r="C66" s="28" t="inlineStr">
         <is>
-          <t>5:45PM</t>
+          <t>6:00PM</t>
         </is>
       </c>
       <c r="D66" s="28" t="inlineStr">
@@ -18516,12 +19054,12 @@
       </c>
       <c r="B67" s="27" t="inlineStr">
         <is>
-          <t>5:25PM</t>
+          <t>5:40PM</t>
         </is>
       </c>
       <c r="C67" s="27" t="inlineStr">
         <is>
-          <t>5:45PM</t>
+          <t>6:00PM</t>
         </is>
       </c>
       <c r="D67" s="27" t="inlineStr">
@@ -18566,12 +19104,12 @@
       </c>
       <c r="B68" s="28" t="inlineStr">
         <is>
-          <t>5:45PM</t>
+          <t>6:00PM</t>
         </is>
       </c>
       <c r="C68" s="28" t="inlineStr">
         <is>
-          <t>6:05PM</t>
+          <t>6:20PM</t>
         </is>
       </c>
       <c r="D68" s="28" t="inlineStr">
@@ -18616,12 +19154,12 @@
       </c>
       <c r="B69" s="27" t="inlineStr">
         <is>
-          <t>5:55PM</t>
+          <t>6:10PM</t>
         </is>
       </c>
       <c r="C69" s="27" t="inlineStr">
         <is>
-          <t>6:15PM</t>
+          <t>6:30PM</t>
         </is>
       </c>
       <c r="D69" s="27" t="inlineStr">
@@ -18666,12 +19204,12 @@
       </c>
       <c r="B70" s="28" t="inlineStr">
         <is>
-          <t>6:25PM</t>
+          <t>6:40PM</t>
         </is>
       </c>
       <c r="C70" s="28" t="inlineStr">
         <is>
-          <t>6:45PM</t>
+          <t>7:00PM</t>
         </is>
       </c>
       <c r="D70" s="28" t="inlineStr">
@@ -18716,12 +19254,12 @@
       </c>
       <c r="B71" s="27" t="inlineStr">
         <is>
-          <t>6:45PM</t>
+          <t>7:00PM</t>
         </is>
       </c>
       <c r="C71" s="27" t="inlineStr">
         <is>
-          <t>7:05PM</t>
+          <t>7:20PM</t>
         </is>
       </c>
       <c r="D71" s="27" t="inlineStr">
@@ -18766,12 +19304,12 @@
       </c>
       <c r="B72" s="28" t="inlineStr">
         <is>
-          <t>6:55PM</t>
+          <t>7:10PM</t>
         </is>
       </c>
       <c r="C72" s="28" t="inlineStr">
         <is>
-          <t>7:15PM</t>
+          <t>7:30PM</t>
         </is>
       </c>
       <c r="D72" s="28" t="inlineStr">
@@ -18816,12 +19354,12 @@
       </c>
       <c r="B73" s="27" t="inlineStr">
         <is>
-          <t>7:15PM</t>
+          <t>7:30PM</t>
         </is>
       </c>
       <c r="C73" s="27" t="inlineStr">
         <is>
-          <t>7:35PM</t>
+          <t>7:50PM</t>
         </is>
       </c>
       <c r="D73" s="27" t="inlineStr">
@@ -18866,12 +19404,12 @@
       </c>
       <c r="B74" s="28" t="inlineStr">
         <is>
-          <t>7:15PM</t>
+          <t>7:30PM</t>
         </is>
       </c>
       <c r="C74" s="28" t="inlineStr">
         <is>
-          <t>7:35PM</t>
+          <t>7:50PM</t>
         </is>
       </c>
       <c r="D74" s="28" t="inlineStr">
@@ -18916,12 +19454,12 @@
       </c>
       <c r="B75" s="27" t="inlineStr">
         <is>
-          <t>7:35PM</t>
+          <t>7:50PM</t>
         </is>
       </c>
       <c r="C75" s="27" t="inlineStr">
         <is>
-          <t>7:55PM</t>
+          <t>8:10PM</t>
         </is>
       </c>
       <c r="D75" s="27" t="inlineStr">
@@ -18966,12 +19504,12 @@
       </c>
       <c r="B76" s="28" t="inlineStr">
         <is>
-          <t>8:05PM</t>
+          <t>8:20PM</t>
         </is>
       </c>
       <c r="C76" s="28" t="inlineStr">
         <is>
-          <t>8:25PM</t>
+          <t>8:40PM</t>
         </is>
       </c>
       <c r="D76" s="28" t="inlineStr">
@@ -19016,12 +19554,12 @@
       </c>
       <c r="B77" s="27" t="inlineStr">
         <is>
-          <t>8:05PM</t>
+          <t>8:20PM</t>
         </is>
       </c>
       <c r="C77" s="27" t="inlineStr">
         <is>
-          <t>8:25PM</t>
+          <t>8:40PM</t>
         </is>
       </c>
       <c r="D77" s="27" t="inlineStr">
@@ -19066,12 +19604,12 @@
       </c>
       <c r="B78" s="28" t="inlineStr">
         <is>
-          <t>8:25PM</t>
+          <t>8:40PM</t>
         </is>
       </c>
       <c r="C78" s="28" t="inlineStr">
         <is>
-          <t>8:45PM</t>
+          <t>9:00PM</t>
         </is>
       </c>
       <c r="D78" s="28" t="inlineStr">
@@ -19116,12 +19654,12 @@
       </c>
       <c r="B79" s="27" t="inlineStr">
         <is>
-          <t>8:40PM</t>
+          <t>8:55PM</t>
         </is>
       </c>
       <c r="C79" s="27" t="inlineStr">
         <is>
-          <t>9:00PM</t>
+          <t>9:15PM</t>
         </is>
       </c>
       <c r="D79" s="27" t="inlineStr">
@@ -19166,12 +19704,12 @@
       </c>
       <c r="B80" s="28" t="inlineStr">
         <is>
-          <t>9:10PM</t>
+          <t>9:25PM</t>
         </is>
       </c>
       <c r="C80" s="28" t="inlineStr">
         <is>
-          <t>9:30PM</t>
+          <t>9:45PM</t>
         </is>
       </c>
       <c r="D80" s="28" t="inlineStr">
@@ -19216,12 +19754,12 @@
       </c>
       <c r="B81" s="27" t="inlineStr">
         <is>
-          <t>9:30PM</t>
+          <t>9:45PM</t>
         </is>
       </c>
       <c r="C81" s="27" t="inlineStr">
         <is>
-          <t>9:50PM</t>
+          <t>10:05PM</t>
         </is>
       </c>
       <c r="D81" s="27" t="inlineStr">

--- a/Ekta_Schedule_With_Matchups.xlsx
+++ b/Ekta_Schedule_With_Matchups.xlsx
@@ -16,6 +16,7 @@
     <sheet name="Pool" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Chess" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Squash" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Trophies &amp; Medals" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -25,7 +26,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -155,6 +156,11 @@
       <color rgb="000F172A"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="13">
     <fill>
@@ -219,7 +225,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -301,11 +307,49 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <right/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -495,6 +539,52 @@
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -877,15 +967,11 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="57" t="inlineStr">
+      <c r="A1" s="68" t="inlineStr">
         <is>
           <t>EKTA GAMES 2026 — SCHEDULE OVERVIEW</t>
         </is>
       </c>
-      <c r="B1" s="58" t="n"/>
-      <c r="C1" s="58" t="n"/>
-      <c r="D1" s="58" t="n"/>
-      <c r="E1" s="58" t="n"/>
       <c r="F1" s="31" t="n"/>
       <c r="G1" s="31" t="n"/>
       <c r="H1" s="31" t="n"/>
@@ -893,15 +979,11 @@
       <c r="J1" s="31" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="59" t="inlineStr">
+      <c r="A2" s="69" t="inlineStr">
         <is>
           <t>Fully conflict-free: no player is ever double-booked, TT tables are shared across TT Women's/Men's/Doubles</t>
         </is>
       </c>
-      <c r="B2" s="58" t="n"/>
-      <c r="C2" s="58" t="n"/>
-      <c r="D2" s="58" t="n"/>
-      <c r="E2" s="58" t="n"/>
       <c r="F2" s="31" t="n"/>
       <c r="G2" s="31" t="n"/>
       <c r="H2" s="31" t="n"/>
@@ -909,15 +991,11 @@
       <c r="J2" s="31" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="59" t="inlineStr">
+      <c r="A3" s="69" t="inlineStr">
         <is>
           <t>and Carrom boards across Carrom Men's/Women's/Doubles, and a 10-minute break is inserted whenever a player</t>
         </is>
       </c>
-      <c r="B3" s="58" t="n"/>
-      <c r="C3" s="58" t="n"/>
-      <c r="D3" s="58" t="n"/>
-      <c r="E3" s="58" t="n"/>
       <c r="F3" s="31" t="n"/>
       <c r="G3" s="31" t="n"/>
       <c r="H3" s="31" t="n"/>
@@ -925,15 +1003,11 @@
       <c r="J3" s="31" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="59" t="inlineStr">
+      <c r="A4" s="69" t="inlineStr">
         <is>
           <t>would otherwise play back-to-back in the same event or continuously for 60+ minutes across different events.</t>
         </is>
       </c>
-      <c r="B4" s="58" t="n"/>
-      <c r="C4" s="58" t="n"/>
-      <c r="D4" s="58" t="n"/>
-      <c r="E4" s="58" t="n"/>
       <c r="F4" s="31" t="n"/>
       <c r="G4" s="31" t="n"/>
       <c r="H4" s="31" t="n"/>
@@ -941,15 +1015,11 @@
       <c r="J4" s="31" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="59" t="inlineStr">
+      <c r="A5" s="69" t="inlineStr">
         <is>
           <t>Carrom Women's Singles, TT Women's Singles, Pool, and Squash's Under 15 + 15-25 Bracket knockouts each follow</t>
         </is>
       </c>
-      <c r="B5" s="58" t="n"/>
-      <c r="C5" s="58" t="n"/>
-      <c r="D5" s="58" t="n"/>
-      <c r="E5" s="58" t="n"/>
       <c r="F5" s="31" t="n"/>
       <c r="G5" s="31" t="n"/>
       <c r="H5" s="31" t="n"/>
@@ -957,15 +1027,11 @@
       <c r="J5" s="31" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="59" t="inlineStr">
+      <c r="A6" s="69" t="inlineStr">
         <is>
           <t>immediately once that event's own league stage is done. Carrom Men's, TT Men's, Chess, and Squash's Above 25</t>
         </is>
       </c>
-      <c r="B6" s="58" t="n"/>
-      <c r="C6" s="58" t="n"/>
-      <c r="D6" s="58" t="n"/>
-      <c r="E6" s="58" t="n"/>
       <c r="F6" s="31" t="n"/>
       <c r="G6" s="31" t="n"/>
       <c r="H6" s="31" t="n"/>
@@ -973,15 +1039,11 @@
       <c r="J6" s="31" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="59" t="inlineStr">
+      <c r="A7" s="69" t="inlineStr">
         <is>
           <t>Bracket knockouts, plus both entire Doubles events (from 9:00 AM Aug 16), wait for their own gating rule.</t>
         </is>
       </c>
-      <c r="B7" s="58" t="n"/>
-      <c r="C7" s="58" t="n"/>
-      <c r="D7" s="58" t="n"/>
-      <c r="E7" s="58" t="n"/>
       <c r="F7" s="31" t="n"/>
       <c r="G7" s="31" t="n"/>
       <c r="H7" s="31" t="n"/>
@@ -1001,15 +1063,11 @@
       <c r="J8" s="31" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="60" t="inlineStr">
+      <c r="A9" s="70" t="inlineStr">
         <is>
           <t>DAY STRUCTURE</t>
         </is>
       </c>
-      <c r="B9" s="56" t="n"/>
-      <c r="C9" s="56" t="n"/>
-      <c r="D9" s="56" t="n"/>
-      <c r="E9" s="56" t="n"/>
       <c r="F9" s="31" t="n"/>
       <c r="G9" s="31" t="n"/>
       <c r="H9" s="31" t="n"/>
@@ -1027,15 +1085,11 @@
           <t>Time</t>
         </is>
       </c>
-      <c r="C10" s="61" t="inlineStr">
+      <c r="C10" s="71" t="inlineStr">
         <is>
           <t>Activity</t>
         </is>
       </c>
-      <c r="D10" s="62" t="n"/>
-      <c r="E10" s="62" t="n"/>
-      <c r="F10" s="62" t="n"/>
-      <c r="G10" s="62" t="n"/>
       <c r="H10" s="31" t="n"/>
       <c r="I10" s="31" t="n"/>
       <c r="J10" s="31" t="n"/>
@@ -1243,15 +1297,11 @@
       <c r="J21" s="31" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="60" t="inlineStr">
+      <c r="A22" s="70" t="inlineStr">
         <is>
           <t>EVENTS</t>
         </is>
       </c>
-      <c r="B22" s="56" t="n"/>
-      <c r="C22" s="56" t="n"/>
-      <c r="D22" s="56" t="n"/>
-      <c r="E22" s="56" t="n"/>
       <c r="F22" s="31" t="n"/>
       <c r="G22" s="31" t="n"/>
       <c r="H22" s="31" t="n"/>
@@ -1597,15 +1647,11 @@
       <c r="J35" s="31" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="60" t="inlineStr">
+      <c r="A36" s="70" t="inlineStr">
         <is>
           <t>NOTES</t>
         </is>
       </c>
-      <c r="B36" s="56" t="n"/>
-      <c r="C36" s="56" t="n"/>
-      <c r="D36" s="56" t="n"/>
-      <c r="E36" s="56" t="n"/>
       <c r="F36" s="31" t="n"/>
       <c r="G36" s="31" t="n"/>
       <c r="H36" s="31" t="n"/>
@@ -3378,6 +3424,1251 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G71"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="72" t="inlineStr">
+        <is>
+          <t>TROPHIES &amp; MEDALS</t>
+        </is>
+      </c>
+      <c r="B1" s="58" t="n"/>
+      <c r="C1" s="58" t="n"/>
+      <c r="D1" s="58" t="n"/>
+      <c r="E1" s="58" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="73" t="inlineStr">
+        <is>
+          <t>Every final's winner gets a big trophy, runner-up gets a small trophy. Under-16 players who don't reach any final they're entered in get a medal.</t>
+        </is>
+      </c>
+      <c r="B2" s="58" t="n"/>
+      <c r="C2" s="58" t="n"/>
+      <c r="D2" s="58" t="n"/>
+      <c r="E2" s="58" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="55" t="inlineStr">
+        <is>
+          <t>TROPHY COUNT</t>
+        </is>
+      </c>
+      <c r="B4" s="56" t="n"/>
+      <c r="C4" s="56" t="n"/>
+      <c r="D4" s="56" t="n"/>
+      <c r="E4" s="56" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="74" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B5" s="74" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C5" s="74" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="D5" s="74" t="inlineStr">
+        <is>
+          <t>Big Trophy (Winner)</t>
+        </is>
+      </c>
+      <c r="E5" s="74" t="inlineStr">
+        <is>
+          <t>Small Trophy (Runner-up)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="75" t="inlineStr">
+        <is>
+          <t>TT — Women's Singles</t>
+        </is>
+      </c>
+      <c r="B6" s="75" t="inlineStr">
+        <is>
+          <t>(single category)</t>
+        </is>
+      </c>
+      <c r="C6" s="75" t="inlineStr">
+        <is>
+          <t>FINAL</t>
+        </is>
+      </c>
+      <c r="D6" s="75" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="75" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="75" t="inlineStr">
+        <is>
+          <t>TT — Men's Singles</t>
+        </is>
+      </c>
+      <c r="B7" s="75" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="C7" s="75" t="inlineStr">
+        <is>
+          <t>SR-FINAL</t>
+        </is>
+      </c>
+      <c r="D7" s="75" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="75" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="75" t="inlineStr">
+        <is>
+          <t>TT — Men's Singles</t>
+        </is>
+      </c>
+      <c r="B8" s="75" t="inlineStr">
+        <is>
+          <t>Under 15</t>
+        </is>
+      </c>
+      <c r="C8" s="75" t="inlineStr">
+        <is>
+          <t>U15-FINAL</t>
+        </is>
+      </c>
+      <c r="D8" s="75" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="75" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="75" t="inlineStr">
+        <is>
+          <t>TT — Men's Singles</t>
+        </is>
+      </c>
+      <c r="B9" s="75" t="inlineStr">
+        <is>
+          <t>Under 32</t>
+        </is>
+      </c>
+      <c r="C9" s="75" t="inlineStr">
+        <is>
+          <t>U32-FINAL</t>
+        </is>
+      </c>
+      <c r="D9" s="75" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="75" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="75" t="inlineStr">
+        <is>
+          <t>TT — Men's Singles</t>
+        </is>
+      </c>
+      <c r="B10" s="75" t="inlineStr">
+        <is>
+          <t>Under 36</t>
+        </is>
+      </c>
+      <c r="C10" s="75" t="inlineStr">
+        <is>
+          <t>U36-FINAL</t>
+        </is>
+      </c>
+      <c r="D10" s="75" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="75" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="75" t="inlineStr">
+        <is>
+          <t>TT — Men's Singles</t>
+        </is>
+      </c>
+      <c r="B11" s="75" t="inlineStr">
+        <is>
+          <t>Under 46</t>
+        </is>
+      </c>
+      <c r="C11" s="75" t="inlineStr">
+        <is>
+          <t>U46-FINAL</t>
+        </is>
+      </c>
+      <c r="D11" s="75" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="75" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="75" t="inlineStr">
+        <is>
+          <t>TT — Doubles</t>
+        </is>
+      </c>
+      <c r="B12" s="75" t="inlineStr">
+        <is>
+          <t>(single category)</t>
+        </is>
+      </c>
+      <c r="C12" s="75" t="inlineStr">
+        <is>
+          <t>FINAL</t>
+        </is>
+      </c>
+      <c r="D12" s="75" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="75" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="75" t="inlineStr">
+        <is>
+          <t>Carrom — Women's Singles</t>
+        </is>
+      </c>
+      <c r="B13" s="75" t="inlineStr">
+        <is>
+          <t>(single category)</t>
+        </is>
+      </c>
+      <c r="C13" s="75" t="inlineStr">
+        <is>
+          <t>CW-FINAL</t>
+        </is>
+      </c>
+      <c r="D13" s="75" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="75" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="75" t="inlineStr">
+        <is>
+          <t>Carrom — Men's Singles</t>
+        </is>
+      </c>
+      <c r="B14" s="75" t="inlineStr">
+        <is>
+          <t>Above 46</t>
+        </is>
+      </c>
+      <c r="C14" s="75" t="inlineStr">
+        <is>
+          <t>A46-FINAL</t>
+        </is>
+      </c>
+      <c r="D14" s="75" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="75" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="75" t="inlineStr">
+        <is>
+          <t>Carrom — Men's Singles</t>
+        </is>
+      </c>
+      <c r="B15" s="75" t="inlineStr">
+        <is>
+          <t>Under 15</t>
+        </is>
+      </c>
+      <c r="C15" s="75" t="inlineStr">
+        <is>
+          <t>U15-FINAL</t>
+        </is>
+      </c>
+      <c r="D15" s="75" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="75" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="75" t="inlineStr">
+        <is>
+          <t>Carrom — Men's Singles</t>
+        </is>
+      </c>
+      <c r="B16" s="75" t="inlineStr">
+        <is>
+          <t>Under 46</t>
+        </is>
+      </c>
+      <c r="C16" s="75" t="inlineStr">
+        <is>
+          <t>U46-FINAL</t>
+        </is>
+      </c>
+      <c r="D16" s="75" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="75" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="75" t="inlineStr">
+        <is>
+          <t>Carrom — Doubles</t>
+        </is>
+      </c>
+      <c r="B17" s="75" t="inlineStr">
+        <is>
+          <t>(single category)</t>
+        </is>
+      </c>
+      <c r="C17" s="75" t="inlineStr">
+        <is>
+          <t>FINAL</t>
+        </is>
+      </c>
+      <c r="D17" s="75" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="75" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="75" t="inlineStr">
+        <is>
+          <t>Pool</t>
+        </is>
+      </c>
+      <c r="B18" s="75" t="inlineStr">
+        <is>
+          <t>26 to 39</t>
+        </is>
+      </c>
+      <c r="C18" s="75" t="inlineStr">
+        <is>
+          <t>2639-FINAL</t>
+        </is>
+      </c>
+      <c r="D18" s="75" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="75" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="75" t="inlineStr">
+        <is>
+          <t>Pool</t>
+        </is>
+      </c>
+      <c r="B19" s="75" t="inlineStr">
+        <is>
+          <t>40 and above</t>
+        </is>
+      </c>
+      <c r="C19" s="75" t="inlineStr">
+        <is>
+          <t>40P-FINAL</t>
+        </is>
+      </c>
+      <c r="D19" s="75" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="75" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="75" t="inlineStr">
+        <is>
+          <t>Pool</t>
+        </is>
+      </c>
+      <c r="B20" s="75" t="inlineStr">
+        <is>
+          <t>Under 26</t>
+        </is>
+      </c>
+      <c r="C20" s="75" t="inlineStr">
+        <is>
+          <t>U26-FINAL</t>
+        </is>
+      </c>
+      <c r="D20" s="75" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="75" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="75" t="inlineStr">
+        <is>
+          <t>Chess</t>
+        </is>
+      </c>
+      <c r="B21" s="75" t="inlineStr">
+        <is>
+          <t>12 to 20</t>
+        </is>
+      </c>
+      <c r="C21" s="75" t="inlineStr">
+        <is>
+          <t>1220-FINAL</t>
+        </is>
+      </c>
+      <c r="D21" s="75" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="75" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="75" t="inlineStr">
+        <is>
+          <t>Chess</t>
+        </is>
+      </c>
+      <c r="B22" s="75" t="inlineStr">
+        <is>
+          <t>21 to 40</t>
+        </is>
+      </c>
+      <c r="C22" s="75" t="inlineStr">
+        <is>
+          <t>2140-FINAL</t>
+        </is>
+      </c>
+      <c r="D22" s="75" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="75" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="75" t="inlineStr">
+        <is>
+          <t>Chess</t>
+        </is>
+      </c>
+      <c r="B23" s="75" t="inlineStr">
+        <is>
+          <t>41 and above</t>
+        </is>
+      </c>
+      <c r="C23" s="75" t="inlineStr">
+        <is>
+          <t>41P-FINAL</t>
+        </is>
+      </c>
+      <c r="D23" s="75" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" s="75" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="75" t="inlineStr">
+        <is>
+          <t>Chess</t>
+        </is>
+      </c>
+      <c r="B24" s="75" t="inlineStr">
+        <is>
+          <t>Under 11</t>
+        </is>
+      </c>
+      <c r="C24" s="75" t="inlineStr">
+        <is>
+          <t>U11-FINAL</t>
+        </is>
+      </c>
+      <c r="D24" s="75" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" s="75" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="75" t="inlineStr">
+        <is>
+          <t>Squash</t>
+        </is>
+      </c>
+      <c r="B25" s="75" t="inlineStr">
+        <is>
+          <t>15-25 Bracket</t>
+        </is>
+      </c>
+      <c r="C25" s="75" t="inlineStr">
+        <is>
+          <t>GC-FINAL</t>
+        </is>
+      </c>
+      <c r="D25" s="75" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="75" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="75" t="inlineStr">
+        <is>
+          <t>Squash</t>
+        </is>
+      </c>
+      <c r="B26" s="75" t="inlineStr">
+        <is>
+          <t>Above 25 Bracket</t>
+        </is>
+      </c>
+      <c r="C26" s="75" t="inlineStr">
+        <is>
+          <t>A25-FINAL</t>
+        </is>
+      </c>
+      <c r="D26" s="75" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="75" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="75" t="inlineStr">
+        <is>
+          <t>Squash</t>
+        </is>
+      </c>
+      <c r="B27" s="75" t="inlineStr">
+        <is>
+          <t>Under 15</t>
+        </is>
+      </c>
+      <c r="C27" s="75" t="inlineStr">
+        <is>
+          <t>U15-FINAL</t>
+        </is>
+      </c>
+      <c r="D27" s="75" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" s="75" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="76" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B28" s="77" t="n"/>
+      <c r="C28" s="76" t="inlineStr">
+        <is>
+          <t>22 finals</t>
+        </is>
+      </c>
+      <c r="D28" s="76" t="n">
+        <v>22</v>
+      </c>
+      <c r="E28" s="76" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="78" t="inlineStr">
+        <is>
+          <t>Per-event summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="74" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B31" s="74" t="inlineStr">
+        <is>
+          <t>Categories (finals)</t>
+        </is>
+      </c>
+      <c r="C31" s="74" t="inlineStr">
+        <is>
+          <t>Big Trophies</t>
+        </is>
+      </c>
+      <c r="D31" s="74" t="inlineStr">
+        <is>
+          <t>Small Trophies</t>
+        </is>
+      </c>
+      <c r="E31" s="74" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="75" t="inlineStr">
+        <is>
+          <t>TT — Men's Singles</t>
+        </is>
+      </c>
+      <c r="B32" s="75" t="n">
+        <v>5</v>
+      </c>
+      <c r="C32" s="75" t="n">
+        <v>5</v>
+      </c>
+      <c r="D32" s="75" t="n">
+        <v>5</v>
+      </c>
+      <c r="E32" s="77" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="75" t="inlineStr">
+        <is>
+          <t>Chess</t>
+        </is>
+      </c>
+      <c r="B33" s="75" t="n">
+        <v>4</v>
+      </c>
+      <c r="C33" s="75" t="n">
+        <v>4</v>
+      </c>
+      <c r="D33" s="75" t="n">
+        <v>4</v>
+      </c>
+      <c r="E33" s="77" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="75" t="inlineStr">
+        <is>
+          <t>Carrom — Men's Singles</t>
+        </is>
+      </c>
+      <c r="B34" s="75" t="n">
+        <v>3</v>
+      </c>
+      <c r="C34" s="75" t="n">
+        <v>3</v>
+      </c>
+      <c r="D34" s="75" t="n">
+        <v>3</v>
+      </c>
+      <c r="E34" s="77" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="75" t="inlineStr">
+        <is>
+          <t>Pool</t>
+        </is>
+      </c>
+      <c r="B35" s="75" t="n">
+        <v>3</v>
+      </c>
+      <c r="C35" s="75" t="n">
+        <v>3</v>
+      </c>
+      <c r="D35" s="75" t="n">
+        <v>3</v>
+      </c>
+      <c r="E35" s="77" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="75" t="inlineStr">
+        <is>
+          <t>Squash</t>
+        </is>
+      </c>
+      <c r="B36" s="75" t="n">
+        <v>3</v>
+      </c>
+      <c r="C36" s="75" t="n">
+        <v>3</v>
+      </c>
+      <c r="D36" s="75" t="n">
+        <v>3</v>
+      </c>
+      <c r="E36" s="77" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="75" t="inlineStr">
+        <is>
+          <t>TT — Women's Singles</t>
+        </is>
+      </c>
+      <c r="B37" s="75" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" s="75" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" s="75" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" s="77" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="75" t="inlineStr">
+        <is>
+          <t>TT — Doubles</t>
+        </is>
+      </c>
+      <c r="B38" s="75" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" s="75" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" s="75" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" s="77" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="75" t="inlineStr">
+        <is>
+          <t>Carrom — Women's Singles</t>
+        </is>
+      </c>
+      <c r="B39" s="75" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" s="75" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" s="75" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" s="77" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="75" t="inlineStr">
+        <is>
+          <t>Carrom — Doubles</t>
+        </is>
+      </c>
+      <c r="B40" s="75" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" s="75" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" s="75" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" s="77" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="55" t="inlineStr">
+        <is>
+          <t>MEDALS — UNDER 16 PARTICIPATION</t>
+        </is>
+      </c>
+      <c r="B42" s="56" t="n"/>
+      <c r="C42" s="56" t="n"/>
+      <c r="D42" s="56" t="n"/>
+      <c r="E42" s="56" t="n"/>
+    </row>
+    <row r="43" ht="30" customHeight="1">
+      <c r="A43" s="79" t="inlineStr">
+        <is>
+          <t>14 unique players across all events are under 16. A medal goes to any of them who doesn't reach a final in ANY event/category they're entered in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="74" t="inlineStr">
+        <is>
+          <t>Player</t>
+        </is>
+      </c>
+      <c r="B45" s="74" t="inlineStr">
+        <is>
+          <t>Age</t>
+        </is>
+      </c>
+      <c r="C45" s="74" t="inlineStr">
+        <is>
+          <t>Categories entered</t>
+        </is>
+      </c>
+      <c r="D45" s="80" t="n"/>
+      <c r="E45" s="80" t="n"/>
+      <c r="F45" s="80" t="n"/>
+      <c r="G45" s="81" t="n"/>
+    </row>
+    <row r="46" ht="15" customHeight="1">
+      <c r="A46" s="75" t="inlineStr">
+        <is>
+          <t>Rushabh</t>
+        </is>
+      </c>
+      <c r="B46" s="75" t="n">
+        <v>8</v>
+      </c>
+      <c r="C46" s="82" t="inlineStr">
+        <is>
+          <t>Chess (Under 11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="15" customHeight="1">
+      <c r="A47" s="75" t="inlineStr">
+        <is>
+          <t>Neev Chauhan</t>
+        </is>
+      </c>
+      <c r="B47" s="75" t="n">
+        <v>8</v>
+      </c>
+      <c r="C47" s="82" t="inlineStr">
+        <is>
+          <t>Chess (Under 11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="15" customHeight="1">
+      <c r="A48" s="75" t="inlineStr">
+        <is>
+          <t>Kaira</t>
+        </is>
+      </c>
+      <c r="B48" s="75" t="n">
+        <v>8</v>
+      </c>
+      <c r="C48" s="82" t="inlineStr">
+        <is>
+          <t>Carrom — Women's Singles (single category)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="15" customHeight="1">
+      <c r="A49" s="75" t="inlineStr">
+        <is>
+          <t>Kartik Relan</t>
+        </is>
+      </c>
+      <c r="B49" s="75" t="n">
+        <v>9</v>
+      </c>
+      <c r="C49" s="82" t="inlineStr">
+        <is>
+          <t>Chess (Under 11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="30" customHeight="1">
+      <c r="A50" s="75" t="inlineStr">
+        <is>
+          <t>Shaurya Tripathi</t>
+        </is>
+      </c>
+      <c r="B50" s="75" t="n">
+        <v>10</v>
+      </c>
+      <c r="C50" s="82" t="inlineStr">
+        <is>
+          <t>Carrom — Men's Singles (Under 15); Squash (Under 15); TT — Men's Singles (Under 15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="30" customHeight="1">
+      <c r="A51" s="75" t="inlineStr">
+        <is>
+          <t>Parth yadav</t>
+        </is>
+      </c>
+      <c r="B51" s="75" t="n">
+        <v>10</v>
+      </c>
+      <c r="C51" s="82" t="inlineStr">
+        <is>
+          <t>Chess (Under 11); Squash (Under 15); TT — Men's Singles (Under 15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="15" customHeight="1">
+      <c r="A52" s="75" t="inlineStr">
+        <is>
+          <t>Jimit Relan</t>
+        </is>
+      </c>
+      <c r="B52" s="75" t="n">
+        <v>11</v>
+      </c>
+      <c r="C52" s="82" t="inlineStr">
+        <is>
+          <t>Chess (Under 11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="15" customHeight="1">
+      <c r="A53" s="75" t="inlineStr">
+        <is>
+          <t>Aarav Pilankar</t>
+        </is>
+      </c>
+      <c r="B53" s="75" t="n">
+        <v>11</v>
+      </c>
+      <c r="C53" s="82" t="inlineStr">
+        <is>
+          <t>Carrom — Men's Singles (Under 15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="30" customHeight="1">
+      <c r="A54" s="75" t="inlineStr">
+        <is>
+          <t>Aadit Joshi</t>
+        </is>
+      </c>
+      <c r="B54" s="75" t="n">
+        <v>12</v>
+      </c>
+      <c r="C54" s="82" t="inlineStr">
+        <is>
+          <t>Chess (12 to 20); Pool (Under 26); Squash (Under 15); TT — Men's Singles (Under 15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="15" customHeight="1">
+      <c r="A55" s="75" t="inlineStr">
+        <is>
+          <t>Peher Krunal Shah</t>
+        </is>
+      </c>
+      <c r="B55" s="75" t="n">
+        <v>12</v>
+      </c>
+      <c r="C55" s="82" t="inlineStr">
+        <is>
+          <t>Squash (Under 15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="15" customHeight="1">
+      <c r="A56" s="75" t="inlineStr">
+        <is>
+          <t>Viaan Neema</t>
+        </is>
+      </c>
+      <c r="B56" s="75" t="n">
+        <v>12</v>
+      </c>
+      <c r="C56" s="82" t="inlineStr">
+        <is>
+          <t>Squash (Under 15); TT — Men's Singles (Under 15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="15" customHeight="1">
+      <c r="A57" s="75" t="inlineStr">
+        <is>
+          <t>Hridh jhala</t>
+        </is>
+      </c>
+      <c r="B57" s="75" t="n">
+        <v>13</v>
+      </c>
+      <c r="C57" s="82" t="inlineStr">
+        <is>
+          <t>Squash (Under 15); TT — Men's Singles (Under 15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="30" customHeight="1">
+      <c r="A58" s="75" t="inlineStr">
+        <is>
+          <t>Yash agarwal</t>
+        </is>
+      </c>
+      <c r="B58" s="75" t="n">
+        <v>13</v>
+      </c>
+      <c r="C58" s="82" t="inlineStr">
+        <is>
+          <t>Carrom — Men's Singles (Under 15); Squash (Under 15); TT — Men's Singles (Under 15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="15" customHeight="1">
+      <c r="A59" s="75" t="inlineStr">
+        <is>
+          <t>Maitreya Manvik</t>
+        </is>
+      </c>
+      <c r="B59" s="75" t="n">
+        <v>14</v>
+      </c>
+      <c r="C59" s="82" t="inlineStr">
+        <is>
+          <t>Chess (12 to 20)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="30" customHeight="1">
+      <c r="A61" s="83" t="inlineStr">
+        <is>
+          <t>Categories entirely or mostly made up of Under-16 players (tightest medal bottlenecks — only 2 final slots each)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="74" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B62" s="74" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C62" s="74" t="inlineStr">
+        <is>
+          <t>Under-16 players in it</t>
+        </is>
+      </c>
+      <c r="D62" s="84" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="75" t="inlineStr">
+        <is>
+          <t>Squash</t>
+        </is>
+      </c>
+      <c r="B63" s="75" t="inlineStr">
+        <is>
+          <t>Under 15</t>
+        </is>
+      </c>
+      <c r="C63" s="82" t="inlineStr">
+        <is>
+          <t>7: Aadit Joshi, Hridh jhala, Parth yadav, Peher Krunal Shah, Shaurya Tripathi, Viaan Neema, Yash agarwal</t>
+        </is>
+      </c>
+      <c r="E63" s="75" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="75" t="inlineStr">
+        <is>
+          <t>TT — Men's Singles</t>
+        </is>
+      </c>
+      <c r="B64" s="75" t="inlineStr">
+        <is>
+          <t>Under 15</t>
+        </is>
+      </c>
+      <c r="C64" s="82" t="inlineStr">
+        <is>
+          <t>6: Aadit Joshi, Hridh jhala, Parth yadav, Shaurya Tripathi, Viaan Neema, Yash agarwal</t>
+        </is>
+      </c>
+      <c r="E64" s="75" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="75" t="inlineStr">
+        <is>
+          <t>Chess</t>
+        </is>
+      </c>
+      <c r="B65" s="75" t="inlineStr">
+        <is>
+          <t>Under 11</t>
+        </is>
+      </c>
+      <c r="C65" s="82" t="inlineStr">
+        <is>
+          <t>5: Jimit Relan, Kartik Relan, Neev Chauhan, Parth yadav, Rushabh</t>
+        </is>
+      </c>
+      <c r="E65" s="75" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="75" t="inlineStr">
+        <is>
+          <t>Carrom — Men's Singles</t>
+        </is>
+      </c>
+      <c r="B66" s="75" t="inlineStr">
+        <is>
+          <t>Under 15</t>
+        </is>
+      </c>
+      <c r="C66" s="82" t="inlineStr">
+        <is>
+          <t>3: Aarav Pilankar, Shaurya Tripathi, Yash agarwal</t>
+        </is>
+      </c>
+      <c r="E66" s="75" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="75" t="inlineStr">
+        <is>
+          <t>Chess</t>
+        </is>
+      </c>
+      <c r="B67" s="75" t="inlineStr">
+        <is>
+          <t>12 to 20</t>
+        </is>
+      </c>
+      <c r="C67" s="82" t="inlineStr">
+        <is>
+          <t>2: Aadit Joshi, Maitreya Manvik</t>
+        </is>
+      </c>
+      <c r="E67" s="75" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="75" t="inlineStr">
+        <is>
+          <t>Pool</t>
+        </is>
+      </c>
+      <c r="B68" s="75" t="inlineStr">
+        <is>
+          <t>Under 26</t>
+        </is>
+      </c>
+      <c r="C68" s="82" t="inlineStr">
+        <is>
+          <t>1: Aadit Joshi</t>
+        </is>
+      </c>
+      <c r="E68" s="75" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="75" t="inlineStr">
+        <is>
+          <t>Carrom — Women's Singles</t>
+        </is>
+      </c>
+      <c r="B69" s="75" t="inlineStr">
+        <is>
+          <t>(single category)</t>
+        </is>
+      </c>
+      <c r="C69" s="82" t="inlineStr">
+        <is>
+          <t>1: Kaira</t>
+        </is>
+      </c>
+      <c r="E69" s="75" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71" ht="30" customHeight="1">
+      <c r="A71" s="85" t="inlineStr">
+        <is>
+          <t>Estimated medal count: minimum 3 (best case — every multi-category player escapes via a different event), maximum 14 (worst case — none of them reach any final). Actual count depends on match results.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="31">
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="C62:D62"/>
+    <mergeCell ref="C68:D68"/>
+    <mergeCell ref="C58:G58"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="A61:E61"/>
+    <mergeCell ref="C64:D64"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="C54:G54"/>
+    <mergeCell ref="C63:D63"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="C55:G55"/>
+    <mergeCell ref="C56:G56"/>
+    <mergeCell ref="C59:G59"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="A71:E71"/>
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A43:E43"/>
+    <mergeCell ref="C67:D67"/>
+    <mergeCell ref="C57:G57"/>
+    <mergeCell ref="C66:D66"/>
+    <mergeCell ref="C53:G53"/>
+    <mergeCell ref="C69:D69"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/Ekta_Schedule_With_Matchups.xlsx
+++ b/Ekta_Schedule_With_Matchups.xlsx
@@ -349,7 +349,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -586,6 +586,13 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -955,7 +962,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" style="21" min="1" max="1"/>
-    <col width="16" bestFit="1" customWidth="1" style="14" min="2" max="2"/>
+    <col width="20" bestFit="1" customWidth="1" style="14" min="2" max="2"/>
     <col width="20" bestFit="1" customWidth="1" style="14" min="3" max="3"/>
     <col width="16" bestFit="1" customWidth="1" style="14" min="4" max="4"/>
     <col width="16" customWidth="1" style="14" min="5" max="5"/>
@@ -1194,7 +1201,7 @@
       <c r="I15" s="31" t="n"/>
       <c r="J15" s="31" t="n"/>
     </row>
-    <row r="16" ht="45" customHeight="1">
+    <row r="16" ht="68" customHeight="1">
       <c r="A16" s="63" t="inlineStr">
         <is>
           <t>Aug 16</t>
@@ -1622,8 +1629,8 @@
       <c r="I33" s="31" t="n"/>
       <c r="J33" s="31" t="n"/>
     </row>
-    <row r="34">
-      <c r="A34" s="67" t="inlineStr">
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="86" t="inlineStr">
         <is>
           <t>Overall tournament span: Aug 15, 8:00 AM start → Aug 16, 5:45 PM finish — comfortably inside the Aug 16, 10 PM cap.</t>
         </is>
@@ -1658,7 +1665,7 @@
       <c r="I36" s="31" t="n"/>
       <c r="J36" s="31" t="n"/>
     </row>
-    <row r="37">
+    <row r="37" ht="30" customHeight="1">
       <c r="A37" s="65" t="inlineStr">
         <is>
           <t>Full match-by-match detail (exact times, table/board assignment, player groups) lives in each sport's own sheet — this tab is a summary only.</t>
@@ -1985,7 +1992,7 @@
   <dimension ref="A1:J49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" bestFit="1" customWidth="1" style="14" min="1" max="1"/>
+    <col width="20" bestFit="1" customWidth="1" style="14" min="1" max="1"/>
     <col width="10" customWidth="1" style="14" min="2" max="3"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" style="14" min="4" max="4"/>
@@ -3434,10 +3441,10 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
   </cols>
@@ -3448,21 +3455,13 @@
           <t>TROPHIES &amp; MEDALS</t>
         </is>
       </c>
-      <c r="B1" s="58" t="n"/>
-      <c r="C1" s="58" t="n"/>
-      <c r="D1" s="58" t="n"/>
-      <c r="E1" s="58" t="n"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="73" t="inlineStr">
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="87" t="inlineStr">
         <is>
           <t>Every final's winner gets a big trophy, runner-up gets a small trophy. Under-16 players who don't reach any final they're entered in get a medal.</t>
         </is>
       </c>
-      <c r="B2" s="58" t="n"/>
-      <c r="C2" s="58" t="n"/>
-      <c r="D2" s="58" t="n"/>
-      <c r="E2" s="58" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="55" t="inlineStr">
@@ -3470,10 +3469,6 @@
           <t>TROPHY COUNT</t>
         </is>
       </c>
-      <c r="B4" s="56" t="n"/>
-      <c r="C4" s="56" t="n"/>
-      <c r="D4" s="56" t="n"/>
-      <c r="E4" s="56" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="74" t="inlineStr">
@@ -4216,10 +4211,6 @@
           <t>MEDALS — UNDER 16 PARTICIPATION</t>
         </is>
       </c>
-      <c r="B42" s="56" t="n"/>
-      <c r="C42" s="56" t="n"/>
-      <c r="D42" s="56" t="n"/>
-      <c r="E42" s="56" t="n"/>
     </row>
     <row r="43" ht="30" customHeight="1">
       <c r="A43" s="79" t="inlineStr">
@@ -4244,10 +4235,10 @@
           <t>Categories entered</t>
         </is>
       </c>
-      <c r="D45" s="80" t="n"/>
-      <c r="E45" s="80" t="n"/>
-      <c r="F45" s="80" t="n"/>
-      <c r="G45" s="81" t="n"/>
+      <c r="D45" s="88" t="n"/>
+      <c r="E45" s="88" t="n"/>
+      <c r="F45" s="88" t="n"/>
+      <c r="G45" s="84" t="n"/>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" s="75" t="inlineStr">
@@ -4263,6 +4254,10 @@
           <t>Chess (Under 11)</t>
         </is>
       </c>
+      <c r="D46" s="88" t="n"/>
+      <c r="E46" s="88" t="n"/>
+      <c r="F46" s="88" t="n"/>
+      <c r="G46" s="84" t="n"/>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" s="75" t="inlineStr">
@@ -4278,6 +4273,10 @@
           <t>Chess (Under 11)</t>
         </is>
       </c>
+      <c r="D47" s="88" t="n"/>
+      <c r="E47" s="88" t="n"/>
+      <c r="F47" s="88" t="n"/>
+      <c r="G47" s="84" t="n"/>
     </row>
     <row r="48" ht="15" customHeight="1">
       <c r="A48" s="75" t="inlineStr">
@@ -4293,6 +4292,10 @@
           <t>Carrom — Women's Singles (single category)</t>
         </is>
       </c>
+      <c r="D48" s="88" t="n"/>
+      <c r="E48" s="88" t="n"/>
+      <c r="F48" s="88" t="n"/>
+      <c r="G48" s="84" t="n"/>
     </row>
     <row r="49" ht="15" customHeight="1">
       <c r="A49" s="75" t="inlineStr">
@@ -4308,6 +4311,10 @@
           <t>Chess (Under 11)</t>
         </is>
       </c>
+      <c r="D49" s="88" t="n"/>
+      <c r="E49" s="88" t="n"/>
+      <c r="F49" s="88" t="n"/>
+      <c r="G49" s="84" t="n"/>
     </row>
     <row r="50" ht="30" customHeight="1">
       <c r="A50" s="75" t="inlineStr">
@@ -4323,6 +4330,10 @@
           <t>Carrom — Men's Singles (Under 15); Squash (Under 15); TT — Men's Singles (Under 15)</t>
         </is>
       </c>
+      <c r="D50" s="88" t="n"/>
+      <c r="E50" s="88" t="n"/>
+      <c r="F50" s="88" t="n"/>
+      <c r="G50" s="84" t="n"/>
     </row>
     <row r="51" ht="30" customHeight="1">
       <c r="A51" s="75" t="inlineStr">
@@ -4338,6 +4349,10 @@
           <t>Chess (Under 11); Squash (Under 15); TT — Men's Singles (Under 15)</t>
         </is>
       </c>
+      <c r="D51" s="88" t="n"/>
+      <c r="E51" s="88" t="n"/>
+      <c r="F51" s="88" t="n"/>
+      <c r="G51" s="84" t="n"/>
     </row>
     <row r="52" ht="15" customHeight="1">
       <c r="A52" s="75" t="inlineStr">
@@ -4353,6 +4368,10 @@
           <t>Chess (Under 11)</t>
         </is>
       </c>
+      <c r="D52" s="88" t="n"/>
+      <c r="E52" s="88" t="n"/>
+      <c r="F52" s="88" t="n"/>
+      <c r="G52" s="84" t="n"/>
     </row>
     <row r="53" ht="15" customHeight="1">
       <c r="A53" s="75" t="inlineStr">
@@ -4368,6 +4387,10 @@
           <t>Carrom — Men's Singles (Under 15)</t>
         </is>
       </c>
+      <c r="D53" s="88" t="n"/>
+      <c r="E53" s="88" t="n"/>
+      <c r="F53" s="88" t="n"/>
+      <c r="G53" s="84" t="n"/>
     </row>
     <row r="54" ht="30" customHeight="1">
       <c r="A54" s="75" t="inlineStr">
@@ -4383,6 +4406,10 @@
           <t>Chess (12 to 20); Pool (Under 26); Squash (Under 15); TT — Men's Singles (Under 15)</t>
         </is>
       </c>
+      <c r="D54" s="88" t="n"/>
+      <c r="E54" s="88" t="n"/>
+      <c r="F54" s="88" t="n"/>
+      <c r="G54" s="84" t="n"/>
     </row>
     <row r="55" ht="15" customHeight="1">
       <c r="A55" s="75" t="inlineStr">
@@ -4398,6 +4425,10 @@
           <t>Squash (Under 15)</t>
         </is>
       </c>
+      <c r="D55" s="88" t="n"/>
+      <c r="E55" s="88" t="n"/>
+      <c r="F55" s="88" t="n"/>
+      <c r="G55" s="84" t="n"/>
     </row>
     <row r="56" ht="15" customHeight="1">
       <c r="A56" s="75" t="inlineStr">
@@ -4413,6 +4444,10 @@
           <t>Squash (Under 15); TT — Men's Singles (Under 15)</t>
         </is>
       </c>
+      <c r="D56" s="88" t="n"/>
+      <c r="E56" s="88" t="n"/>
+      <c r="F56" s="88" t="n"/>
+      <c r="G56" s="84" t="n"/>
     </row>
     <row r="57" ht="15" customHeight="1">
       <c r="A57" s="75" t="inlineStr">
@@ -4428,6 +4463,10 @@
           <t>Squash (Under 15); TT — Men's Singles (Under 15)</t>
         </is>
       </c>
+      <c r="D57" s="88" t="n"/>
+      <c r="E57" s="88" t="n"/>
+      <c r="F57" s="88" t="n"/>
+      <c r="G57" s="84" t="n"/>
     </row>
     <row r="58" ht="30" customHeight="1">
       <c r="A58" s="75" t="inlineStr">
@@ -4443,6 +4482,10 @@
           <t>Carrom — Men's Singles (Under 15); Squash (Under 15); TT — Men's Singles (Under 15)</t>
         </is>
       </c>
+      <c r="D58" s="88" t="n"/>
+      <c r="E58" s="88" t="n"/>
+      <c r="F58" s="88" t="n"/>
+      <c r="G58" s="84" t="n"/>
     </row>
     <row r="59" ht="15" customHeight="1">
       <c r="A59" s="75" t="inlineStr">
@@ -4458,6 +4501,10 @@
           <t>Chess (12 to 20)</t>
         </is>
       </c>
+      <c r="D59" s="88" t="n"/>
+      <c r="E59" s="88" t="n"/>
+      <c r="F59" s="88" t="n"/>
+      <c r="G59" s="84" t="n"/>
     </row>
     <row r="61" ht="30" customHeight="1">
       <c r="A61" s="83" t="inlineStr">
@@ -4484,7 +4531,7 @@
       </c>
       <c r="D62" s="84" t="n"/>
     </row>
-    <row r="63">
+    <row r="63" ht="50" customHeight="1">
       <c r="A63" s="75" t="inlineStr">
         <is>
           <t>Squash</t>
@@ -4500,11 +4547,12 @@
           <t>7: Aadit Joshi, Hridh jhala, Parth yadav, Peher Krunal Shah, Shaurya Tripathi, Viaan Neema, Yash agarwal</t>
         </is>
       </c>
+      <c r="D63" s="84" t="n"/>
       <c r="E63" s="75" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" ht="50" customHeight="1">
       <c r="A64" s="75" t="inlineStr">
         <is>
           <t>TT — Men's Singles</t>
@@ -4520,11 +4568,12 @@
           <t>6: Aadit Joshi, Hridh jhala, Parth yadav, Shaurya Tripathi, Viaan Neema, Yash agarwal</t>
         </is>
       </c>
+      <c r="D64" s="84" t="n"/>
       <c r="E64" s="75" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" ht="35" customHeight="1">
       <c r="A65" s="75" t="inlineStr">
         <is>
           <t>Chess</t>
@@ -4540,11 +4589,12 @@
           <t>5: Jimit Relan, Kartik Relan, Neev Chauhan, Parth yadav, Rushabh</t>
         </is>
       </c>
+      <c r="D65" s="84" t="n"/>
       <c r="E65" s="75" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" ht="35" customHeight="1">
       <c r="A66" s="75" t="inlineStr">
         <is>
           <t>Carrom — Men's Singles</t>
@@ -4560,11 +4610,12 @@
           <t>3: Aarav Pilankar, Shaurya Tripathi, Yash agarwal</t>
         </is>
       </c>
+      <c r="D66" s="84" t="n"/>
       <c r="E66" s="75" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" ht="20" customHeight="1">
       <c r="A67" s="75" t="inlineStr">
         <is>
           <t>Chess</t>
@@ -4580,11 +4631,12 @@
           <t>2: Aadit Joshi, Maitreya Manvik</t>
         </is>
       </c>
+      <c r="D67" s="84" t="n"/>
       <c r="E67" s="75" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" ht="20" customHeight="1">
       <c r="A68" s="75" t="inlineStr">
         <is>
           <t>Pool</t>
@@ -4600,11 +4652,12 @@
           <t>1: Aadit Joshi</t>
         </is>
       </c>
+      <c r="D68" s="84" t="n"/>
       <c r="E68" s="75" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" ht="20" customHeight="1">
       <c r="A69" s="75" t="inlineStr">
         <is>
           <t>Carrom — Women's Singles</t>
@@ -4620,6 +4673,7 @@
           <t>1: Kaira</t>
         </is>
       </c>
+      <c r="D69" s="84" t="n"/>
       <c r="E69" s="75" t="n">
         <v>2</v>
       </c>
@@ -4678,7 +4732,7 @@
   <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" bestFit="1" customWidth="1" style="14" min="1" max="1"/>
+    <col width="18" bestFit="1" customWidth="1" style="14" min="1" max="1"/>
     <col width="10" bestFit="1" customWidth="1" style="14" min="2" max="3"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="20" bestFit="1" customWidth="1" style="14" min="4" max="4"/>
@@ -5635,10 +5689,10 @@
   <dimension ref="A1:J115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" bestFit="1" customWidth="1" style="14" min="1" max="1"/>
+    <col width="19" bestFit="1" customWidth="1" style="14" min="1" max="1"/>
     <col width="10" bestFit="1" customWidth="1" style="14" min="2" max="3"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="20" bestFit="1" customWidth="1" style="14" min="4" max="4"/>
+    <col width="23" bestFit="1" customWidth="1" style="14" min="4" max="4"/>
     <col width="10" bestFit="1" customWidth="1" style="14" min="5" max="5"/>
     <col width="12" bestFit="1" customWidth="1" style="14" min="6" max="6"/>
     <col width="11" bestFit="1" customWidth="1" style="14" min="7" max="7"/>
@@ -9738,16 +9792,16 @@
   <dimension ref="A1:J26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" bestFit="1" customWidth="1" style="14" min="1" max="1"/>
+    <col width="32" bestFit="1" customWidth="1" style="14" min="1" max="1"/>
     <col width="10" bestFit="1" customWidth="1" style="14" min="2" max="2"/>
     <col width="10" bestFit="1" customWidth="1" style="14" min="3" max="3"/>
     <col width="20" bestFit="1" customWidth="1" style="14" min="4" max="4"/>
     <col width="10" bestFit="1" customWidth="1" style="14" min="5" max="5"/>
     <col width="12" bestFit="1" customWidth="1" style="14" min="6" max="6"/>
     <col width="11" bestFit="1" customWidth="1" style="14" min="7" max="7"/>
-    <col width="27" bestFit="1" customWidth="1" style="14" min="8" max="8"/>
+    <col width="32" bestFit="1" customWidth="1" style="14" min="8" max="8"/>
     <col width="4" bestFit="1" customWidth="1" style="14" min="9" max="9"/>
-    <col width="27" customWidth="1" style="14" min="10" max="16384"/>
+    <col width="32" customWidth="1" style="14" min="10" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.95" customHeight="1">
@@ -10300,7 +10354,7 @@
   <dimension ref="A1:J82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" bestFit="1" customWidth="1" style="14" min="1" max="1"/>
+    <col width="21" bestFit="1" customWidth="1" style="14" min="1" max="1"/>
     <col width="10" customWidth="1" style="14" min="2" max="3"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" style="14" min="4" max="4"/>
@@ -13287,7 +13341,7 @@
   <dimension ref="A1:J27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" bestFit="1" customWidth="1" style="14" min="1" max="1"/>
+    <col width="22" bestFit="1" customWidth="1" style="14" min="1" max="1"/>
     <col width="10" bestFit="1" customWidth="1" style="14" min="2" max="3"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="20" bestFit="1" customWidth="1" style="14" min="4" max="4"/>
@@ -14020,16 +14074,16 @@
   <dimension ref="A1:J41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" bestFit="1" customWidth="1" style="14" min="1" max="1"/>
+    <col width="42" bestFit="1" customWidth="1" style="14" min="1" max="1"/>
     <col width="10" bestFit="1" customWidth="1" style="14" min="2" max="3"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="20" bestFit="1" customWidth="1" style="14" min="4" max="4"/>
     <col width="10" bestFit="1" customWidth="1" style="14" min="5" max="5"/>
     <col width="12" bestFit="1" customWidth="1" style="14" min="6" max="6"/>
     <col width="11" bestFit="1" customWidth="1" style="14" min="7" max="7"/>
-    <col width="27" bestFit="1" customWidth="1" style="14" min="8" max="8"/>
+    <col width="42" bestFit="1" customWidth="1" style="14" min="8" max="8"/>
     <col width="4" bestFit="1" customWidth="1" style="14" min="9" max="9"/>
-    <col width="27" customWidth="1" style="14" min="10" max="16384"/>
+    <col width="42" customWidth="1" style="14" min="10" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.95" customHeight="1">
@@ -15010,7 +15064,7 @@
   <dimension ref="A1:J92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" bestFit="1" customWidth="1" style="14" min="1" max="1"/>
+    <col width="20" bestFit="1" customWidth="1" style="14" min="1" max="1"/>
     <col width="10" customWidth="1" style="14" min="2" max="3"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" style="14" min="4" max="4"/>
@@ -18490,7 +18544,7 @@
   <dimension ref="A1:J100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" bestFit="1" customWidth="1" style="14" min="1" max="1"/>
+    <col width="20" bestFit="1" customWidth="1" style="14" min="1" max="1"/>
     <col width="10" customWidth="1" style="14" min="2" max="3"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" style="14" min="4" max="4"/>

--- a/Ekta_Schedule_With_Matchups.xlsx
+++ b/Ekta_Schedule_With_Matchups.xlsx
@@ -965,7 +965,7 @@
     <col width="20" bestFit="1" customWidth="1" style="14" min="2" max="2"/>
     <col width="20" bestFit="1" customWidth="1" style="14" min="3" max="3"/>
     <col width="16" bestFit="1" customWidth="1" style="14" min="4" max="4"/>
-    <col width="16" customWidth="1" style="14" min="5" max="5"/>
+    <col width="17" customWidth="1" style="14" min="5" max="5"/>
     <col width="9" customWidth="1" style="14" min="6" max="6"/>
     <col width="11" customWidth="1" style="14" min="7" max="7"/>
     <col width="10" customWidth="1" style="14" min="8" max="8"/>
@@ -1992,7 +1992,7 @@
   <dimension ref="A1:J49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" bestFit="1" customWidth="1" style="14" min="1" max="1"/>
+    <col width="24.9" bestFit="1" customWidth="1" style="14" min="1" max="1"/>
     <col width="10" customWidth="1" style="14" min="2" max="3"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" style="14" min="4" max="4"/>
@@ -4732,10 +4732,10 @@
   <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" bestFit="1" customWidth="1" style="14" min="1" max="1"/>
+    <col width="21.9" bestFit="1" customWidth="1" style="14" min="1" max="1"/>
     <col width="10" bestFit="1" customWidth="1" style="14" min="2" max="3"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="20" bestFit="1" customWidth="1" style="14" min="4" max="4"/>
+    <col width="23.1" bestFit="1" customWidth="1" style="14" min="4" max="4"/>
     <col width="10" bestFit="1" customWidth="1" style="14" min="5" max="5"/>
     <col width="12" bestFit="1" customWidth="1" style="14" min="6" max="6"/>
     <col width="11" bestFit="1" customWidth="1" style="14" min="7" max="7"/>
@@ -5689,16 +5689,16 @@
   <dimension ref="A1:J115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" bestFit="1" customWidth="1" style="14" min="1" max="1"/>
+    <col width="24.5" bestFit="1" customWidth="1" style="14" min="1" max="1"/>
     <col width="10" bestFit="1" customWidth="1" style="14" min="2" max="3"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="23" bestFit="1" customWidth="1" style="14" min="4" max="4"/>
+    <col width="36.9" bestFit="1" customWidth="1" style="14" min="4" max="4"/>
     <col width="10" bestFit="1" customWidth="1" style="14" min="5" max="5"/>
     <col width="12" bestFit="1" customWidth="1" style="14" min="6" max="6"/>
     <col width="11" bestFit="1" customWidth="1" style="14" min="7" max="7"/>
-    <col width="27" bestFit="1" customWidth="1" style="14" min="8" max="8"/>
+    <col width="36.9" bestFit="1" customWidth="1" style="14" min="8" max="8"/>
     <col width="4" bestFit="1" customWidth="1" style="14" min="9" max="9"/>
-    <col width="27" customWidth="1" style="14" min="10" max="16384"/>
+    <col width="36.9" customWidth="1" style="14" min="10" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.95" customHeight="1">
@@ -9792,16 +9792,16 @@
   <dimension ref="A1:J26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" bestFit="1" customWidth="1" style="14" min="1" max="1"/>
+    <col width="40.1" bestFit="1" customWidth="1" style="14" min="1" max="1"/>
     <col width="10" bestFit="1" customWidth="1" style="14" min="2" max="2"/>
     <col width="10" bestFit="1" customWidth="1" style="14" min="3" max="3"/>
     <col width="20" bestFit="1" customWidth="1" style="14" min="4" max="4"/>
     <col width="10" bestFit="1" customWidth="1" style="14" min="5" max="5"/>
     <col width="12" bestFit="1" customWidth="1" style="14" min="6" max="6"/>
     <col width="11" bestFit="1" customWidth="1" style="14" min="7" max="7"/>
-    <col width="32" bestFit="1" customWidth="1" style="14" min="8" max="8"/>
+    <col width="40.1" bestFit="1" customWidth="1" style="14" min="8" max="8"/>
     <col width="4" bestFit="1" customWidth="1" style="14" min="9" max="9"/>
-    <col width="32" customWidth="1" style="14" min="10" max="16384"/>
+    <col width="35.5" customWidth="1" style="14" min="10" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.95" customHeight="1">
@@ -10354,12 +10354,12 @@
   <dimension ref="A1:J82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21" bestFit="1" customWidth="1" style="14" min="1" max="1"/>
+    <col width="25.1" bestFit="1" customWidth="1" style="14" min="1" max="1"/>
     <col width="10" customWidth="1" style="14" min="2" max="3"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" style="14" min="4" max="4"/>
+    <col width="23.9" customWidth="1" style="14" min="4" max="4"/>
     <col width="10" customWidth="1" style="14" min="5" max="5"/>
-    <col width="12" bestFit="1" customWidth="1" style="14" min="6" max="6"/>
+    <col width="15" bestFit="1" customWidth="1" style="14" min="6" max="6"/>
     <col width="11" customWidth="1" style="14" min="7" max="7"/>
     <col width="27" customWidth="1" style="14" min="8" max="8"/>
     <col width="4" customWidth="1" style="14" min="9" max="9"/>
@@ -13341,16 +13341,16 @@
   <dimension ref="A1:J27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" bestFit="1" customWidth="1" style="14" min="1" max="1"/>
+    <col width="28.7" bestFit="1" customWidth="1" style="14" min="1" max="1"/>
     <col width="10" bestFit="1" customWidth="1" style="14" min="2" max="3"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="20" bestFit="1" customWidth="1" style="14" min="4" max="4"/>
+    <col width="24" bestFit="1" customWidth="1" style="14" min="4" max="4"/>
     <col width="10" bestFit="1" customWidth="1" style="14" min="5" max="5"/>
     <col width="12" bestFit="1" customWidth="1" style="14" min="6" max="6"/>
     <col width="11" bestFit="1" customWidth="1" style="14" min="7" max="7"/>
-    <col width="27" bestFit="1" customWidth="1" style="14" min="8" max="8"/>
+    <col width="28.7" bestFit="1" customWidth="1" style="14" min="8" max="8"/>
     <col width="4" bestFit="1" customWidth="1" style="14" min="9" max="9"/>
-    <col width="27" customWidth="1" style="14" min="10" max="16384"/>
+    <col width="28.7" customWidth="1" style="14" min="10" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.95" customHeight="1">
@@ -14074,16 +14074,16 @@
   <dimension ref="A1:J41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" bestFit="1" customWidth="1" style="14" min="1" max="1"/>
+    <col width="54.1" bestFit="1" customWidth="1" style="14" min="1" max="1"/>
     <col width="10" bestFit="1" customWidth="1" style="14" min="2" max="3"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="20" bestFit="1" customWidth="1" style="14" min="4" max="4"/>
     <col width="10" bestFit="1" customWidth="1" style="14" min="5" max="5"/>
     <col width="12" bestFit="1" customWidth="1" style="14" min="6" max="6"/>
     <col width="11" bestFit="1" customWidth="1" style="14" min="7" max="7"/>
-    <col width="42" bestFit="1" customWidth="1" style="14" min="8" max="8"/>
+    <col width="46.5" bestFit="1" customWidth="1" style="14" min="8" max="8"/>
     <col width="4" bestFit="1" customWidth="1" style="14" min="9" max="9"/>
-    <col width="42" customWidth="1" style="14" min="10" max="16384"/>
+    <col width="54.1" customWidth="1" style="14" min="10" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.95" customHeight="1">
@@ -15064,10 +15064,10 @@
   <dimension ref="A1:J92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" bestFit="1" customWidth="1" style="14" min="1" max="1"/>
+    <col width="25.1" bestFit="1" customWidth="1" style="14" min="1" max="1"/>
     <col width="10" customWidth="1" style="14" min="2" max="3"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" style="14" min="4" max="4"/>
+    <col width="23.9" customWidth="1" style="14" min="4" max="4"/>
     <col width="10" customWidth="1" style="14" min="5" max="5"/>
     <col width="12" customWidth="1" style="14" min="6" max="6"/>
     <col width="11" customWidth="1" style="14" min="7" max="7"/>
@@ -18544,7 +18544,7 @@
   <dimension ref="A1:J100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" bestFit="1" customWidth="1" style="14" min="1" max="1"/>
+    <col width="25.3" bestFit="1" customWidth="1" style="14" min="1" max="1"/>
     <col width="10" customWidth="1" style="14" min="2" max="3"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" style="14" min="4" max="4"/>

--- a/Ekta_Schedule_With_Matchups.xlsx
+++ b/Ekta_Schedule_With_Matchups.xlsx
@@ -14169,7 +14169,7 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Shalu Agarwal &amp; Vrinda Agrawal</t>
+          <t>Vinod Agrawal &amp; Vrinda Agrawal</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
@@ -14528,7 +14528,7 @@
       </c>
       <c r="H31" s="28" t="inlineStr">
         <is>
-          <t>Shalu Agarwal &amp; Vrinda Agrawal</t>
+          <t>Vinod Agrawal &amp; Vrinda Agrawal</t>
         </is>
       </c>
       <c r="I31" s="28" t="inlineStr">

--- a/Ekta_Schedule_With_Matchups.xlsx
+++ b/Ekta_Schedule_With_Matchups.xlsx
@@ -1234,7 +1234,7 @@
       </c>
       <c r="C17" s="64" t="inlineStr">
         <is>
-          <t>Both Doubles events run once their own players are free — Carrom Doubles 9:00-10:30 AM; TT Doubles now starts 11:55 AM (TT tables are shared with TT Men's Singles, whose league stage runs until then).</t>
+          <t>Both Doubles events run once their own players are free — Carrom Doubles 9:30-11:50 AM; TT Doubles now starts 11:55 AM (TT tables are shared with TT Men's Singles, whose league stage runs until then).</t>
         </is>
       </c>
       <c r="H17" s="31" t="n"/>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="F32" s="28" t="inlineStr">
         <is>
-          <t>U15-R1-M2</t>
+          <t>U15-R1-M1</t>
         </is>
       </c>
       <c r="G32" s="28" t="inlineStr">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="F33" s="27" t="inlineStr">
         <is>
-          <t>U15-R1-M1</t>
+          <t>U15-R1-M2</t>
         </is>
       </c>
       <c r="G33" s="27" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="F37" s="27" t="inlineStr">
         <is>
-          <t>GA-2</t>
+          <t>GA-1</t>
         </is>
       </c>
       <c r="G37" s="27" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="F38" s="28" t="inlineStr">
         <is>
-          <t>GA-1</t>
+          <t>GA-2</t>
         </is>
       </c>
       <c r="G38" s="28" t="inlineStr">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="H43" s="27" t="inlineStr">
         <is>
-          <t>Winner U15-R1-M1</t>
+          <t>Winner U15-R1-M2</t>
         </is>
       </c>
       <c r="I43" s="27" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="H44" s="28" t="inlineStr">
         <is>
-          <t>Winner U15-R1-M2</t>
+          <t>Winner U15-R1-M1</t>
         </is>
       </c>
       <c r="I44" s="28" t="inlineStr">
@@ -4766,6 +4766,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6" ht="17.1" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
         <is>
@@ -4857,6 +4858,8 @@
         <v>58</v>
       </c>
     </row>
+    <row r="12"/>
+    <row r="13"/>
     <row r="14" ht="20.1" customHeight="1">
       <c r="A14" s="16" t="inlineStr">
         <is>
@@ -4947,12 +4950,12 @@
       </c>
       <c r="G16" s="27" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H16" s="27" t="inlineStr">
         <is>
-          <t>Nidhi Sharma</t>
+          <t>Nitika Aggarwal</t>
         </is>
       </c>
       <c r="I16" s="27" t="inlineStr">
@@ -4962,7 +4965,7 @@
       </c>
       <c r="J16" s="27" t="inlineStr">
         <is>
-          <t>Dr Divya patel</t>
+          <t>Deepali Acharya</t>
         </is>
       </c>
     </row>
@@ -4992,17 +4995,17 @@
       </c>
       <c r="F17" s="28" t="inlineStr">
         <is>
-          <t>GA-M6</t>
+          <t>GA-M2</t>
         </is>
       </c>
       <c r="G17" s="28" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H17" s="28" t="inlineStr">
         <is>
-          <t>Nitika Aggarwal</t>
+          <t>Nidhi Sharma</t>
         </is>
       </c>
       <c r="I17" s="28" t="inlineStr">
@@ -5012,7 +5015,7 @@
       </c>
       <c r="J17" s="28" t="inlineStr">
         <is>
-          <t>Deepali Acharya</t>
+          <t>Dr Divya patel</t>
         </is>
       </c>
     </row>
@@ -5042,7 +5045,7 @@
       </c>
       <c r="F18" s="27" t="inlineStr">
         <is>
-          <t>GA-M2</t>
+          <t>GA-M3</t>
         </is>
       </c>
       <c r="G18" s="27" t="inlineStr">
@@ -5092,7 +5095,7 @@
       </c>
       <c r="F19" s="28" t="inlineStr">
         <is>
-          <t>GA-M5</t>
+          <t>GA-M4</t>
         </is>
       </c>
       <c r="G19" s="28" t="inlineStr">
@@ -5142,7 +5145,7 @@
       </c>
       <c r="F20" s="27" t="inlineStr">
         <is>
-          <t>GA-M3</t>
+          <t>GA-M5</t>
         </is>
       </c>
       <c r="G20" s="27" t="inlineStr">
@@ -5192,7 +5195,7 @@
       </c>
       <c r="F21" s="28" t="inlineStr">
         <is>
-          <t>GA-M4</t>
+          <t>GA-M6</t>
         </is>
       </c>
       <c r="G21" s="28" t="inlineStr">
@@ -5292,7 +5295,7 @@
       </c>
       <c r="F23" s="28" t="inlineStr">
         <is>
-          <t>GB-M6</t>
+          <t>GB-M2</t>
         </is>
       </c>
       <c r="G23" s="28" t="inlineStr">
@@ -5342,7 +5345,7 @@
       </c>
       <c r="F24" s="27" t="inlineStr">
         <is>
-          <t>GB-M2</t>
+          <t>GB-M3</t>
         </is>
       </c>
       <c r="G24" s="27" t="inlineStr">
@@ -5392,7 +5395,7 @@
       </c>
       <c r="F25" s="28" t="inlineStr">
         <is>
-          <t>GB-M5</t>
+          <t>GB-M4</t>
         </is>
       </c>
       <c r="G25" s="28" t="inlineStr">
@@ -5442,7 +5445,7 @@
       </c>
       <c r="F26" s="27" t="inlineStr">
         <is>
-          <t>GB-M3</t>
+          <t>GB-M5</t>
         </is>
       </c>
       <c r="G26" s="27" t="inlineStr">
@@ -5492,7 +5495,7 @@
       </c>
       <c r="F27" s="28" t="inlineStr">
         <is>
-          <t>GB-M4</t>
+          <t>GB-M6</t>
         </is>
       </c>
       <c r="G27" s="28" t="inlineStr">
@@ -5723,6 +5726,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6" ht="17.1" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
         <is>
@@ -5796,6 +5800,7 @@
         <v>13</v>
       </c>
     </row>
+    <row r="11"/>
     <row r="12" ht="17.1" customHeight="1">
       <c r="A12" s="24" t="inlineStr">
         <is>
@@ -5865,6 +5870,7 @@
         <v>25</v>
       </c>
     </row>
+    <row r="19"/>
     <row r="20" ht="17.1" customHeight="1">
       <c r="A20" s="24" t="inlineStr">
         <is>
@@ -5974,6 +5980,7 @@
         <v>39</v>
       </c>
     </row>
+    <row r="27"/>
     <row r="28" ht="17.1" customHeight="1">
       <c r="A28" s="24" t="inlineStr">
         <is>
@@ -6077,6 +6084,7 @@
       <c r="D34" s="4" t="n"/>
       <c r="E34" s="1" t="n"/>
     </row>
+    <row r="35"/>
     <row r="36" ht="17.1" customHeight="1">
       <c r="A36" s="24" t="inlineStr">
         <is>
@@ -6150,6 +6158,8 @@
         <v>70</v>
       </c>
     </row>
+    <row r="41"/>
+    <row r="42"/>
     <row r="43" ht="20.1" customHeight="1">
       <c r="A43" s="16" t="inlineStr">
         <is>
@@ -6535,7 +6545,7 @@
       </c>
       <c r="F51" s="27" t="inlineStr">
         <is>
-          <t>U36-GA-2</t>
+          <t>U36-GA-1</t>
         </is>
       </c>
       <c r="G51" s="27" t="inlineStr">
@@ -6585,7 +6595,7 @@
       </c>
       <c r="F52" s="28" t="inlineStr">
         <is>
-          <t>U36-GA-1</t>
+          <t>U36-GA-2</t>
         </is>
       </c>
       <c r="G52" s="28" t="inlineStr">
@@ -6885,7 +6895,7 @@
       </c>
       <c r="F58" s="28" t="inlineStr">
         <is>
-          <t>U36-GA-7</t>
+          <t>U36-GA-6</t>
         </is>
       </c>
       <c r="G58" s="28" t="inlineStr">
@@ -7035,7 +7045,7 @@
       </c>
       <c r="F61" s="27" t="inlineStr">
         <is>
-          <t>U36-GA-6</t>
+          <t>U36-GA-7</t>
         </is>
       </c>
       <c r="G61" s="27" t="inlineStr">
@@ -7235,7 +7245,7 @@
       </c>
       <c r="F65" s="27" t="inlineStr">
         <is>
-          <t>U36-GB-8</t>
+          <t>U36-GB-7</t>
         </is>
       </c>
       <c r="G65" s="27" t="inlineStr">
@@ -7285,7 +7295,7 @@
       </c>
       <c r="F66" s="28" t="inlineStr">
         <is>
-          <t>U36-GA-10</t>
+          <t>U36-GA-9</t>
         </is>
       </c>
       <c r="G66" s="28" t="inlineStr">
@@ -7335,7 +7345,7 @@
       </c>
       <c r="F67" s="27" t="inlineStr">
         <is>
-          <t>U46-GB-4</t>
+          <t>U46-GB-1</t>
         </is>
       </c>
       <c r="G67" s="27" t="inlineStr">
@@ -7385,7 +7395,7 @@
       </c>
       <c r="F68" s="28" t="inlineStr">
         <is>
-          <t>U46-GB-1</t>
+          <t>U46-GB-2</t>
         </is>
       </c>
       <c r="G68" s="28" t="inlineStr">
@@ -7435,7 +7445,7 @@
       </c>
       <c r="F69" s="27" t="inlineStr">
         <is>
-          <t>U36-GB-7</t>
+          <t>U36-GB-8</t>
         </is>
       </c>
       <c r="G69" s="27" t="inlineStr">
@@ -7485,7 +7495,7 @@
       </c>
       <c r="F70" s="28" t="inlineStr">
         <is>
-          <t>U36-GA-9</t>
+          <t>U36-GA-10</t>
         </is>
       </c>
       <c r="G70" s="28" t="inlineStr">
@@ -7585,7 +7595,7 @@
       </c>
       <c r="F72" s="28" t="inlineStr">
         <is>
-          <t>U46-GB-5</t>
+          <t>U46-GB-3</t>
         </is>
       </c>
       <c r="G72" s="28" t="inlineStr">
@@ -7635,7 +7645,7 @@
       </c>
       <c r="F73" s="27" t="inlineStr">
         <is>
-          <t>U46-GA-3</t>
+          <t>U46-GA-2</t>
         </is>
       </c>
       <c r="G73" s="27" t="inlineStr">
@@ -7835,7 +7845,7 @@
       </c>
       <c r="F77" s="27" t="inlineStr">
         <is>
-          <t>U46-GA-5</t>
+          <t>U46-GA-3</t>
         </is>
       </c>
       <c r="G77" s="27" t="inlineStr">
@@ -7885,17 +7895,17 @@
       </c>
       <c r="F78" s="28" t="inlineStr">
         <is>
-          <t>U46-GA-10</t>
+          <t>U46-GB-4</t>
         </is>
       </c>
       <c r="G78" s="28" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H78" s="28" t="inlineStr">
         <is>
-          <t>Anuj Shah</t>
+          <t>Adil Khan</t>
         </is>
       </c>
       <c r="I78" s="28" t="inlineStr">
@@ -7905,7 +7915,7 @@
       </c>
       <c r="J78" s="28" t="inlineStr">
         <is>
-          <t>Nilesh Bagaria</t>
+          <t>Vinod Agrawal</t>
         </is>
       </c>
     </row>
@@ -7935,17 +7945,17 @@
       </c>
       <c r="F79" s="27" t="inlineStr">
         <is>
-          <t>U46-GB-2</t>
+          <t>U46-GA-4</t>
         </is>
       </c>
       <c r="G79" s="27" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H79" s="27" t="inlineStr">
         <is>
-          <t>Adil Khan</t>
+          <t>Anuj Shah</t>
         </is>
       </c>
       <c r="I79" s="27" t="inlineStr">
@@ -7955,7 +7965,7 @@
       </c>
       <c r="J79" s="27" t="inlineStr">
         <is>
-          <t>Vinod Agrawal</t>
+          <t>Nilesh Bagaria</t>
         </is>
       </c>
     </row>
@@ -8035,7 +8045,7 @@
       </c>
       <c r="F81" s="27" t="inlineStr">
         <is>
-          <t>U46-GB-3</t>
+          <t>U46-GB-5</t>
         </is>
       </c>
       <c r="G81" s="27" t="inlineStr">
@@ -8127,7 +8137,7 @@
       </c>
       <c r="D83" s="27" t="inlineStr">
         <is>
-          <t>Under 15</t>
+          <t>Under 46</t>
         </is>
       </c>
       <c r="E83" s="27" t="n">
@@ -8135,17 +8145,17 @@
       </c>
       <c r="F83" s="27" t="inlineStr">
         <is>
-          <t>U15-GA-3</t>
+          <t>U46-GB-6</t>
         </is>
       </c>
       <c r="G83" s="27" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H83" s="27" t="inlineStr">
         <is>
-          <t>Parth yadav</t>
+          <t>Mukul Joshi</t>
         </is>
       </c>
       <c r="I83" s="27" t="inlineStr">
@@ -8155,7 +8165,7 @@
       </c>
       <c r="J83" s="27" t="inlineStr">
         <is>
-          <t>Aadit Joshi</t>
+          <t>Adil Khan</t>
         </is>
       </c>
     </row>
@@ -8177,7 +8187,7 @@
       </c>
       <c r="D84" s="28" t="inlineStr">
         <is>
-          <t>Under 46</t>
+          <t>Under 15</t>
         </is>
       </c>
       <c r="E84" s="28" t="n">
@@ -8185,17 +8195,17 @@
       </c>
       <c r="F84" s="28" t="inlineStr">
         <is>
-          <t>U46-GB-6</t>
+          <t>U15-GA-3</t>
         </is>
       </c>
       <c r="G84" s="28" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H84" s="28" t="inlineStr">
         <is>
-          <t>Mukul Joshi</t>
+          <t>Parth yadav</t>
         </is>
       </c>
       <c r="I84" s="28" t="inlineStr">
@@ -8205,7 +8215,7 @@
       </c>
       <c r="J84" s="28" t="inlineStr">
         <is>
-          <t>Adil Khan</t>
+          <t>Aadit Joshi</t>
         </is>
       </c>
     </row>
@@ -8235,7 +8245,7 @@
       </c>
       <c r="F85" s="27" t="inlineStr">
         <is>
-          <t>U46-GA-2</t>
+          <t>U46-GA-5</t>
         </is>
       </c>
       <c r="G85" s="27" t="inlineStr">
@@ -8285,7 +8295,7 @@
       </c>
       <c r="F86" s="28" t="inlineStr">
         <is>
-          <t>U46-GA-4</t>
+          <t>U46-GA-6</t>
         </is>
       </c>
       <c r="G86" s="28" t="inlineStr">
@@ -8335,7 +8345,7 @@
       </c>
       <c r="F87" s="27" t="inlineStr">
         <is>
-          <t>U46-GA-9</t>
+          <t>U46-GA-7</t>
         </is>
       </c>
       <c r="G87" s="27" t="inlineStr">
@@ -8385,7 +8395,7 @@
       </c>
       <c r="F88" s="28" t="inlineStr">
         <is>
-          <t>U46-GA-6</t>
+          <t>U46-GA-8</t>
         </is>
       </c>
       <c r="G88" s="28" t="inlineStr">
@@ -8435,7 +8445,7 @@
       </c>
       <c r="F89" s="27" t="inlineStr">
         <is>
-          <t>U46-GA-7</t>
+          <t>U46-GA-9</t>
         </is>
       </c>
       <c r="G89" s="27" t="inlineStr">
@@ -8535,7 +8545,7 @@
       </c>
       <c r="F91" s="27" t="inlineStr">
         <is>
-          <t>U46-GA-8</t>
+          <t>U46-GA-10</t>
         </is>
       </c>
       <c r="G91" s="27" t="inlineStr">
@@ -8685,17 +8695,17 @@
       </c>
       <c r="F94" s="28" t="inlineStr">
         <is>
-          <t>U32-10</t>
+          <t>U32-3</t>
         </is>
       </c>
       <c r="G94" s="28" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H94" s="28" t="inlineStr">
         <is>
-          <t>Yuvraj jain</t>
+          <t>Hryday Goyal</t>
         </is>
       </c>
       <c r="I94" s="28" t="inlineStr">
@@ -8705,7 +8715,7 @@
       </c>
       <c r="J94" s="28" t="inlineStr">
         <is>
-          <t>Rahul Garg</t>
+          <t>Pranit Shriyan</t>
         </is>
       </c>
     </row>
@@ -8740,12 +8750,12 @@
       </c>
       <c r="G95" s="27" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H95" s="27" t="inlineStr">
         <is>
-          <t>Hryday Goyal</t>
+          <t>Yuvraj jain</t>
         </is>
       </c>
       <c r="I95" s="27" t="inlineStr">
@@ -8755,7 +8765,7 @@
       </c>
       <c r="J95" s="27" t="inlineStr">
         <is>
-          <t>Pranit Shriyan</t>
+          <t>Rahul Garg</t>
         </is>
       </c>
     </row>
@@ -8835,7 +8845,7 @@
       </c>
       <c r="F97" s="27" t="inlineStr">
         <is>
-          <t>U32-9</t>
+          <t>U32-5</t>
         </is>
       </c>
       <c r="G97" s="27" t="inlineStr">
@@ -8885,7 +8895,7 @@
       </c>
       <c r="F98" s="28" t="inlineStr">
         <is>
-          <t>U32-8</t>
+          <t>U32-6</t>
         </is>
       </c>
       <c r="G98" s="28" t="inlineStr">
@@ -8985,7 +8995,7 @@
       </c>
       <c r="F100" s="28" t="inlineStr">
         <is>
-          <t>U32-3</t>
+          <t>U32-8</t>
         </is>
       </c>
       <c r="G100" s="28" t="inlineStr">
@@ -9035,17 +9045,17 @@
       </c>
       <c r="F101" s="27" t="inlineStr">
         <is>
-          <t>U32-5</t>
+          <t>U32-10</t>
         </is>
       </c>
       <c r="G101" s="27" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H101" s="27" t="inlineStr">
         <is>
-          <t>Pranit Shriyan</t>
+          <t>Aaditya Kumar</t>
         </is>
       </c>
       <c r="I101" s="27" t="inlineStr">
@@ -9055,7 +9065,7 @@
       </c>
       <c r="J101" s="27" t="inlineStr">
         <is>
-          <t>Rahul Garg</t>
+          <t>Hryday Goyal</t>
         </is>
       </c>
     </row>
@@ -9085,17 +9095,17 @@
       </c>
       <c r="F102" s="28" t="inlineStr">
         <is>
-          <t>U32-6</t>
+          <t>U32-9</t>
         </is>
       </c>
       <c r="G102" s="28" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H102" s="28" t="inlineStr">
         <is>
-          <t>Aaditya Kumar</t>
+          <t>Pranit Shriyan</t>
         </is>
       </c>
       <c r="I102" s="28" t="inlineStr">
@@ -9105,7 +9115,7 @@
       </c>
       <c r="J102" s="28" t="inlineStr">
         <is>
-          <t>Hryday Goyal</t>
+          <t>Rahul Garg</t>
         </is>
       </c>
     </row>
@@ -9135,7 +9145,7 @@
       </c>
       <c r="F103" s="27" t="inlineStr">
         <is>
-          <t>SR-SF2</t>
+          <t>SR-SF1</t>
         </is>
       </c>
       <c r="G103" s="27" t="inlineStr">
@@ -9185,7 +9195,7 @@
       </c>
       <c r="F104" s="28" t="inlineStr">
         <is>
-          <t>U46-SF2</t>
+          <t>U46-SF1</t>
         </is>
       </c>
       <c r="G104" s="28" t="inlineStr">
@@ -9235,7 +9245,7 @@
       </c>
       <c r="F105" s="27" t="inlineStr">
         <is>
-          <t>U36-SF2</t>
+          <t>U36-SF1</t>
         </is>
       </c>
       <c r="G105" s="27" t="inlineStr">
@@ -9285,7 +9295,7 @@
       </c>
       <c r="F106" s="28" t="inlineStr">
         <is>
-          <t>SR-SF1</t>
+          <t>SR-SF2</t>
         </is>
       </c>
       <c r="G106" s="28" t="inlineStr">
@@ -9435,7 +9445,7 @@
       </c>
       <c r="F109" s="27" t="inlineStr">
         <is>
-          <t>U15-SF2</t>
+          <t>U15-SF1</t>
         </is>
       </c>
       <c r="G109" s="27" t="inlineStr">
@@ -9485,7 +9495,7 @@
       </c>
       <c r="F110" s="28" t="inlineStr">
         <is>
-          <t>U46-SF1</t>
+          <t>U46-SF2</t>
         </is>
       </c>
       <c r="G110" s="28" t="inlineStr">
@@ -9517,17 +9527,17 @@
       </c>
       <c r="B111" s="27" t="inlineStr">
         <is>
-          <t>4:35PM</t>
+          <t>4:45PM</t>
         </is>
       </c>
       <c r="C111" s="27" t="inlineStr">
         <is>
-          <t>4:50PM</t>
+          <t>5:00PM</t>
         </is>
       </c>
       <c r="D111" s="27" t="inlineStr">
         <is>
-          <t>Under 15</t>
+          <t>Under 36</t>
         </is>
       </c>
       <c r="E111" s="27" t="n">
@@ -9535,17 +9545,17 @@
       </c>
       <c r="F111" s="27" t="inlineStr">
         <is>
-          <t>U15-FINAL</t>
+          <t>U36-SF2</t>
         </is>
       </c>
       <c r="G111" s="27" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H111" s="27" t="inlineStr">
         <is>
-          <t>Winner SF1</t>
+          <t>Group A 1st</t>
         </is>
       </c>
       <c r="I111" s="27" t="inlineStr">
@@ -9555,7 +9565,7 @@
       </c>
       <c r="J111" s="27" t="inlineStr">
         <is>
-          <t>Winner SF2</t>
+          <t>Group B 2nd</t>
         </is>
       </c>
     </row>
@@ -9567,12 +9577,12 @@
       </c>
       <c r="B112" s="28" t="inlineStr">
         <is>
-          <t>4:45PM</t>
+          <t>5:00PM</t>
         </is>
       </c>
       <c r="C112" s="28" t="inlineStr">
         <is>
-          <t>5:00PM</t>
+          <t>5:15PM</t>
         </is>
       </c>
       <c r="D112" s="28" t="inlineStr">
@@ -9585,7 +9595,7 @@
       </c>
       <c r="F112" s="28" t="inlineStr">
         <is>
-          <t>U36-SF1</t>
+          <t>U36-FINAL</t>
         </is>
       </c>
       <c r="G112" s="28" t="inlineStr">
@@ -9595,7 +9605,7 @@
       </c>
       <c r="H112" s="28" t="inlineStr">
         <is>
-          <t>Group A 1st</t>
+          <t>Winner SF1</t>
         </is>
       </c>
       <c r="I112" s="28" t="inlineStr">
@@ -9605,7 +9615,7 @@
       </c>
       <c r="J112" s="28" t="inlineStr">
         <is>
-          <t>Group B 2nd</t>
+          <t>Winner SF2</t>
         </is>
       </c>
     </row>
@@ -9617,17 +9627,17 @@
       </c>
       <c r="B113" s="27" t="inlineStr">
         <is>
-          <t>5:00PM</t>
+          <t>5:15PM</t>
         </is>
       </c>
       <c r="C113" s="27" t="inlineStr">
         <is>
-          <t>5:15PM</t>
+          <t>5:30PM</t>
         </is>
       </c>
       <c r="D113" s="27" t="inlineStr">
         <is>
-          <t>Under 36</t>
+          <t>Under 15</t>
         </is>
       </c>
       <c r="E113" s="27" t="n">
@@ -9635,7 +9645,7 @@
       </c>
       <c r="F113" s="27" t="inlineStr">
         <is>
-          <t>U36-FINAL</t>
+          <t>U15-SF2</t>
         </is>
       </c>
       <c r="G113" s="27" t="inlineStr">
@@ -9645,7 +9655,7 @@
       </c>
       <c r="H113" s="27" t="inlineStr">
         <is>
-          <t>Winner SF1</t>
+          <t>Group A 1st</t>
         </is>
       </c>
       <c r="I113" s="27" t="inlineStr">
@@ -9655,7 +9665,7 @@
       </c>
       <c r="J113" s="27" t="inlineStr">
         <is>
-          <t>Winner SF2</t>
+          <t>Group B 2nd</t>
         </is>
       </c>
     </row>
@@ -9667,17 +9677,17 @@
       </c>
       <c r="B114" s="28" t="inlineStr">
         <is>
-          <t>5:15PM</t>
+          <t>5:30PM</t>
         </is>
       </c>
       <c r="C114" s="28" t="inlineStr">
         <is>
-          <t>5:30PM</t>
+          <t>5:45PM</t>
         </is>
       </c>
       <c r="D114" s="28" t="inlineStr">
         <is>
-          <t>Under 15</t>
+          <t>Under 46</t>
         </is>
       </c>
       <c r="E114" s="28" t="n">
@@ -9685,7 +9695,7 @@
       </c>
       <c r="F114" s="28" t="inlineStr">
         <is>
-          <t>U15-SF1</t>
+          <t>U46-FINAL</t>
         </is>
       </c>
       <c r="G114" s="28" t="inlineStr">
@@ -9695,7 +9705,7 @@
       </c>
       <c r="H114" s="28" t="inlineStr">
         <is>
-          <t>Group A 1st</t>
+          <t>Winner SF1</t>
         </is>
       </c>
       <c r="I114" s="28" t="inlineStr">
@@ -9705,7 +9715,7 @@
       </c>
       <c r="J114" s="28" t="inlineStr">
         <is>
-          <t>Group B 2nd</t>
+          <t>Winner SF2</t>
         </is>
       </c>
     </row>
@@ -9727,7 +9737,7 @@
       </c>
       <c r="D115" s="27" t="inlineStr">
         <is>
-          <t>Under 46</t>
+          <t>Under 15</t>
         </is>
       </c>
       <c r="E115" s="27" t="n">
@@ -9735,12 +9745,12 @@
       </c>
       <c r="F115" s="27" t="inlineStr">
         <is>
-          <t>U46-FINAL</t>
+          <t>U15-FINAL</t>
         </is>
       </c>
       <c r="G115" s="27" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H115" s="27" t="inlineStr">
@@ -10009,7 +10019,7 @@
       </c>
       <c r="F20" s="27" t="inlineStr">
         <is>
-          <t>QF2</t>
+          <t>QF1</t>
         </is>
       </c>
       <c r="G20" s="27" t="inlineStr">
@@ -10059,7 +10069,7 @@
       </c>
       <c r="F21" s="28" t="inlineStr">
         <is>
-          <t>QF3</t>
+          <t>QF2</t>
         </is>
       </c>
       <c r="G21" s="28" t="inlineStr">
@@ -10109,7 +10119,7 @@
       </c>
       <c r="F22" s="27" t="inlineStr">
         <is>
-          <t>QF4</t>
+          <t>QF3</t>
         </is>
       </c>
       <c r="G22" s="27" t="inlineStr">
@@ -10141,12 +10151,12 @@
       </c>
       <c r="B23" s="28" t="inlineStr">
         <is>
-          <t>3:00PM</t>
+          <t>3:15PM</t>
         </is>
       </c>
       <c r="C23" s="28" t="inlineStr">
         <is>
-          <t>3:15PM</t>
+          <t>3:30PM</t>
         </is>
       </c>
       <c r="D23" s="28" t="inlineStr">
@@ -10159,17 +10169,17 @@
       </c>
       <c r="F23" s="28" t="inlineStr">
         <is>
-          <t>SF2</t>
+          <t>QF4</t>
         </is>
       </c>
       <c r="G23" s="28" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H23" s="28" t="inlineStr">
         <is>
-          <t>Winner QF3</t>
+          <t>Adil Khan &amp; Anuj Shah</t>
         </is>
       </c>
       <c r="I23" s="28" t="inlineStr">
@@ -10179,7 +10189,7 @@
       </c>
       <c r="J23" s="28" t="inlineStr">
         <is>
-          <t>Winner QF4</t>
+          <t>Vinit Padia &amp; Pratik Haldiya</t>
         </is>
       </c>
     </row>
@@ -10209,17 +10219,17 @@
       </c>
       <c r="F24" s="27" t="inlineStr">
         <is>
-          <t>QF1</t>
+          <t>SF1</t>
         </is>
       </c>
       <c r="G24" s="27" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H24" s="27" t="inlineStr">
         <is>
-          <t>Adil Khan &amp; Anuj Shah</t>
+          <t>Winner QF2</t>
         </is>
       </c>
       <c r="I24" s="27" t="inlineStr">
@@ -10229,7 +10239,7 @@
       </c>
       <c r="J24" s="27" t="inlineStr">
         <is>
-          <t>Vinit Padia &amp; Pratik Haldiya</t>
+          <t>Winner QF3</t>
         </is>
       </c>
     </row>
@@ -10259,7 +10269,7 @@
       </c>
       <c r="F25" s="28" t="inlineStr">
         <is>
-          <t>SF1</t>
+          <t>SF2</t>
         </is>
       </c>
       <c r="G25" s="28" t="inlineStr">
@@ -10269,17 +10279,17 @@
       </c>
       <c r="H25" s="28" t="inlineStr">
         <is>
+          <t>Winner QF4</t>
+        </is>
+      </c>
+      <c r="I25" s="28" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J25" s="28" t="inlineStr">
+        <is>
           <t>Winner QF1</t>
-        </is>
-      </c>
-      <c r="I25" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J25" s="28" t="inlineStr">
-        <is>
-          <t>Winner QF2</t>
         </is>
       </c>
     </row>
@@ -10388,6 +10398,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6" ht="17.1" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
         <is>
@@ -10437,6 +10448,7 @@
         <v>13</v>
       </c>
     </row>
+    <row r="11"/>
     <row r="12" ht="17.1" customHeight="1">
       <c r="A12" s="24" t="inlineStr">
         <is>
@@ -10564,6 +10576,7 @@
         <v>45</v>
       </c>
     </row>
+    <row r="20"/>
     <row r="21" ht="17.1" customHeight="1">
       <c r="A21" s="24" t="inlineStr">
         <is>
@@ -10655,6 +10668,8 @@
         <v>65</v>
       </c>
     </row>
+    <row r="27"/>
+    <row r="28"/>
     <row r="29" ht="20.1" customHeight="1">
       <c r="A29" s="16" t="inlineStr">
         <is>
@@ -10790,7 +10805,7 @@
       </c>
       <c r="F32" s="28" t="inlineStr">
         <is>
-          <t>CM-U46-GA-4</t>
+          <t>CM-U46-GA-2</t>
         </is>
       </c>
       <c r="G32" s="28" t="inlineStr">
@@ -10890,7 +10905,7 @@
       </c>
       <c r="F34" s="28" t="inlineStr">
         <is>
-          <t>CM-U46-GA-5</t>
+          <t>CM-U46-GA-4</t>
         </is>
       </c>
       <c r="G34" s="28" t="inlineStr">
@@ -10940,7 +10955,7 @@
       </c>
       <c r="F35" s="27" t="inlineStr">
         <is>
-          <t>CM-U46-GA-10</t>
+          <t>CM-U46-GA-5</t>
         </is>
       </c>
       <c r="G35" s="27" t="inlineStr">
@@ -10990,7 +11005,7 @@
       </c>
       <c r="F36" s="28" t="inlineStr">
         <is>
-          <t>CM-U46-GB-2</t>
+          <t>CM-U46-GB-1</t>
         </is>
       </c>
       <c r="G36" s="28" t="inlineStr">
@@ -11040,17 +11055,17 @@
       </c>
       <c r="F37" s="27" t="inlineStr">
         <is>
-          <t>CM-U46-GA-7</t>
+          <t>CM-U46-GB-2</t>
         </is>
       </c>
       <c r="G37" s="27" t="inlineStr">
         <is>
-          <t>Board 3</t>
+          <t>Board 2</t>
         </is>
       </c>
       <c r="H37" s="27" t="inlineStr">
         <is>
-          <t>Dr Rahul Modi</t>
+          <t>Mayank Aggarwal</t>
         </is>
       </c>
       <c r="I37" s="27" t="inlineStr">
@@ -11060,7 +11075,7 @@
       </c>
       <c r="J37" s="27" t="inlineStr">
         <is>
-          <t>Anuj Shah</t>
+          <t>Amit Ranka</t>
         </is>
       </c>
     </row>
@@ -11090,17 +11105,17 @@
       </c>
       <c r="F38" s="28" t="inlineStr">
         <is>
-          <t>CM-U46-GB-1</t>
+          <t>CM-U46-GA-6</t>
         </is>
       </c>
       <c r="G38" s="28" t="inlineStr">
         <is>
-          <t>Board 2</t>
+          <t>Board 3</t>
         </is>
       </c>
       <c r="H38" s="28" t="inlineStr">
         <is>
-          <t>Mayank Aggarwal</t>
+          <t>Dr Rahul Modi</t>
         </is>
       </c>
       <c r="I38" s="28" t="inlineStr">
@@ -11110,7 +11125,7 @@
       </c>
       <c r="J38" s="28" t="inlineStr">
         <is>
-          <t>Amit Ranka</t>
+          <t>Anuj Shah</t>
         </is>
       </c>
     </row>
@@ -11140,7 +11155,7 @@
       </c>
       <c r="F39" s="27" t="inlineStr">
         <is>
-          <t>CM-U46-GA-6</t>
+          <t>CM-U46-GA-7</t>
         </is>
       </c>
       <c r="G39" s="27" t="inlineStr">
@@ -11240,7 +11255,7 @@
       </c>
       <c r="F41" s="27" t="inlineStr">
         <is>
-          <t>CM-U46-GA-2</t>
+          <t>CM-U46-GA-8</t>
         </is>
       </c>
       <c r="G41" s="27" t="inlineStr">
@@ -11340,7 +11355,7 @@
       </c>
       <c r="F43" s="27" t="inlineStr">
         <is>
-          <t>CM-U46-GA-8</t>
+          <t>CM-U46-GA-9</t>
         </is>
       </c>
       <c r="G43" s="27" t="inlineStr">
@@ -11390,7 +11405,7 @@
       </c>
       <c r="F44" s="28" t="inlineStr">
         <is>
-          <t>CM-U46-GA-9</t>
+          <t>CM-U46-GA-10</t>
         </is>
       </c>
       <c r="G44" s="28" t="inlineStr">
@@ -11440,7 +11455,7 @@
       </c>
       <c r="F45" s="27" t="inlineStr">
         <is>
-          <t>CM-U46-GA-12</t>
+          <t>CM-U46-GA-11</t>
         </is>
       </c>
       <c r="G45" s="27" t="inlineStr">
@@ -11490,7 +11505,7 @@
       </c>
       <c r="F46" s="28" t="inlineStr">
         <is>
-          <t>CM-U46-GA-13</t>
+          <t>CM-U46-GA-12</t>
         </is>
       </c>
       <c r="G46" s="28" t="inlineStr">
@@ -11590,7 +11605,7 @@
       </c>
       <c r="F48" s="28" t="inlineStr">
         <is>
-          <t>CM-U46-GA-11</t>
+          <t>CM-U46-GA-13</t>
         </is>
       </c>
       <c r="G48" s="28" t="inlineStr">
@@ -11690,7 +11705,7 @@
       </c>
       <c r="F50" s="28" t="inlineStr">
         <is>
-          <t>CM-U15-3</t>
+          <t>CM-U15-1</t>
         </is>
       </c>
       <c r="G50" s="28" t="inlineStr">
@@ -11840,7 +11855,7 @@
       </c>
       <c r="F53" s="27" t="inlineStr">
         <is>
-          <t>CM-U15-1</t>
+          <t>CM-U15-2</t>
         </is>
       </c>
       <c r="G53" s="27" t="inlineStr">
@@ -11890,7 +11905,7 @@
       </c>
       <c r="F54" s="28" t="inlineStr">
         <is>
-          <t>CM-U46-GB-11</t>
+          <t>CM-U46-GB-8</t>
         </is>
       </c>
       <c r="G54" s="28" t="inlineStr">
@@ -11940,7 +11955,7 @@
       </c>
       <c r="F55" s="27" t="inlineStr">
         <is>
-          <t>CM-U46-GB-8</t>
+          <t>CM-U46-GB-9</t>
         </is>
       </c>
       <c r="G55" s="27" t="inlineStr">
@@ -11995,12 +12010,12 @@
       </c>
       <c r="G56" s="28" t="inlineStr">
         <is>
-          <t>Board 2</t>
+          <t>Board 1</t>
         </is>
       </c>
       <c r="H56" s="28" t="inlineStr">
         <is>
-          <t>Amar Jain</t>
+          <t>Vinit Padia</t>
         </is>
       </c>
       <c r="I56" s="28" t="inlineStr">
@@ -12010,7 +12025,7 @@
       </c>
       <c r="J56" s="28" t="inlineStr">
         <is>
-          <t>Amit Ranka</t>
+          <t>Nilesh Bagaria</t>
         </is>
       </c>
     </row>
@@ -12040,17 +12055,17 @@
       </c>
       <c r="F57" s="27" t="inlineStr">
         <is>
-          <t>CM-U46-GB-15</t>
+          <t>CM-U46-GB-11</t>
         </is>
       </c>
       <c r="G57" s="27" t="inlineStr">
         <is>
-          <t>Board 1</t>
+          <t>Board 2</t>
         </is>
       </c>
       <c r="H57" s="27" t="inlineStr">
         <is>
-          <t>Vinit Padia</t>
+          <t>Amar Jain</t>
         </is>
       </c>
       <c r="I57" s="27" t="inlineStr">
@@ -12060,7 +12075,7 @@
       </c>
       <c r="J57" s="27" t="inlineStr">
         <is>
-          <t>Nilesh Bagaria</t>
+          <t>Amit Ranka</t>
         </is>
       </c>
     </row>
@@ -12090,7 +12105,7 @@
       </c>
       <c r="F58" s="28" t="inlineStr">
         <is>
-          <t>CM-U46-GB-9</t>
+          <t>CM-U46-GB-12</t>
         </is>
       </c>
       <c r="G58" s="28" t="inlineStr">
@@ -12140,7 +12155,7 @@
       </c>
       <c r="F59" s="27" t="inlineStr">
         <is>
-          <t>CM-U15-2</t>
+          <t>CM-U15-3</t>
         </is>
       </c>
       <c r="G59" s="27" t="inlineStr">
@@ -12290,7 +12305,7 @@
       </c>
       <c r="F62" s="28" t="inlineStr">
         <is>
-          <t>CM-A46-GA-2</t>
+          <t>CM-A46-GA-1</t>
         </is>
       </c>
       <c r="G62" s="28" t="inlineStr">
@@ -12440,7 +12455,7 @@
       </c>
       <c r="F65" s="27" t="inlineStr">
         <is>
-          <t>CM-U46-GB-12</t>
+          <t>CM-U46-GB-15</t>
         </is>
       </c>
       <c r="G65" s="27" t="inlineStr">
@@ -12540,7 +12555,7 @@
       </c>
       <c r="F67" s="27" t="inlineStr">
         <is>
-          <t>CM-A46-GA-1</t>
+          <t>CM-A46-GA-2</t>
         </is>
       </c>
       <c r="G67" s="27" t="inlineStr">
@@ -12640,7 +12655,7 @@
       </c>
       <c r="F69" s="27" t="inlineStr">
         <is>
-          <t>CM-A46-GA-4</t>
+          <t>CM-A46-GA-3</t>
         </is>
       </c>
       <c r="G69" s="27" t="inlineStr">
@@ -12690,7 +12705,7 @@
       </c>
       <c r="F70" s="28" t="inlineStr">
         <is>
-          <t>CM-A46-GB-5</t>
+          <t>CM-A46-GB-4</t>
         </is>
       </c>
       <c r="G70" s="28" t="inlineStr">
@@ -12740,7 +12755,7 @@
       </c>
       <c r="F71" s="27" t="inlineStr">
         <is>
-          <t>CM-A46-GA-3</t>
+          <t>CM-A46-GA-4</t>
         </is>
       </c>
       <c r="G71" s="27" t="inlineStr">
@@ -12790,7 +12805,7 @@
       </c>
       <c r="F72" s="28" t="inlineStr">
         <is>
-          <t>CM-A46-GB-4</t>
+          <t>CM-A46-GB-5</t>
         </is>
       </c>
       <c r="G72" s="28" t="inlineStr">
@@ -12990,17 +13005,17 @@
       </c>
       <c r="F76" s="28" t="inlineStr">
         <is>
-          <t>A46-FINAL</t>
+          <t>A46-SF1</t>
         </is>
       </c>
       <c r="G76" s="28" t="inlineStr">
         <is>
-          <t>Board 2</t>
+          <t>Board 1</t>
         </is>
       </c>
       <c r="H76" s="28" t="inlineStr">
         <is>
-          <t>Winner SF1</t>
+          <t>Group A 1st</t>
         </is>
       </c>
       <c r="I76" s="28" t="inlineStr">
@@ -13010,7 +13025,7 @@
       </c>
       <c r="J76" s="28" t="inlineStr">
         <is>
-          <t>Winner SF2</t>
+          <t>Group B 2nd</t>
         </is>
       </c>
     </row>
@@ -13032,7 +13047,7 @@
       </c>
       <c r="D77" s="27" t="inlineStr">
         <is>
-          <t>Above 46</t>
+          <t>Under 15</t>
         </is>
       </c>
       <c r="E77" s="27" t="n">
@@ -13040,17 +13055,17 @@
       </c>
       <c r="F77" s="27" t="inlineStr">
         <is>
-          <t>A46-SF1</t>
+          <t>U15-FINAL</t>
         </is>
       </c>
       <c r="G77" s="27" t="inlineStr">
         <is>
-          <t>Board 1</t>
+          <t>Board 3</t>
         </is>
       </c>
       <c r="H77" s="27" t="inlineStr">
         <is>
-          <t>Group A 1st</t>
+          <t>Pool 1st</t>
         </is>
       </c>
       <c r="I77" s="27" t="inlineStr">
@@ -13060,7 +13075,7 @@
       </c>
       <c r="J77" s="27" t="inlineStr">
         <is>
-          <t>Group B 2nd</t>
+          <t>Pool 2nd</t>
         </is>
       </c>
     </row>
@@ -13072,17 +13087,17 @@
       </c>
       <c r="B78" s="28" t="inlineStr">
         <is>
-          <t>3:20PM</t>
+          <t>3:35PM</t>
         </is>
       </c>
       <c r="C78" s="28" t="inlineStr">
         <is>
-          <t>3:35PM</t>
+          <t>3:50PM</t>
         </is>
       </c>
       <c r="D78" s="28" t="inlineStr">
         <is>
-          <t>Under 15</t>
+          <t>Under 46</t>
         </is>
       </c>
       <c r="E78" s="28" t="n">
@@ -13090,17 +13105,17 @@
       </c>
       <c r="F78" s="28" t="inlineStr">
         <is>
-          <t>U15-FINAL</t>
+          <t>U46-SF1</t>
         </is>
       </c>
       <c r="G78" s="28" t="inlineStr">
         <is>
-          <t>Board 3</t>
+          <t>Board 1</t>
         </is>
       </c>
       <c r="H78" s="28" t="inlineStr">
         <is>
-          <t>Pool 1st</t>
+          <t>Group A 1st</t>
         </is>
       </c>
       <c r="I78" s="28" t="inlineStr">
@@ -13110,7 +13125,7 @@
       </c>
       <c r="J78" s="28" t="inlineStr">
         <is>
-          <t>Pool 2nd</t>
+          <t>Group B 2nd</t>
         </is>
       </c>
     </row>
@@ -13132,7 +13147,7 @@
       </c>
       <c r="D79" s="27" t="inlineStr">
         <is>
-          <t>Above 46</t>
+          <t>Under 46</t>
         </is>
       </c>
       <c r="E79" s="27" t="n">
@@ -13140,12 +13155,12 @@
       </c>
       <c r="F79" s="27" t="inlineStr">
         <is>
-          <t>A46-SF2</t>
+          <t>U46-SF2</t>
         </is>
       </c>
       <c r="G79" s="27" t="inlineStr">
         <is>
-          <t>Board 3</t>
+          <t>Board 2</t>
         </is>
       </c>
       <c r="H79" s="27" t="inlineStr">
@@ -13182,7 +13197,7 @@
       </c>
       <c r="D80" s="28" t="inlineStr">
         <is>
-          <t>Under 46</t>
+          <t>Above 46</t>
         </is>
       </c>
       <c r="E80" s="28" t="n">
@@ -13190,17 +13205,17 @@
       </c>
       <c r="F80" s="28" t="inlineStr">
         <is>
-          <t>U46-SF1</t>
+          <t>A46-SF2</t>
         </is>
       </c>
       <c r="G80" s="28" t="inlineStr">
         <is>
-          <t>Board 1</t>
+          <t>Board 3</t>
         </is>
       </c>
       <c r="H80" s="28" t="inlineStr">
         <is>
-          <t>Group A 1st</t>
+          <t>Group B 1st</t>
         </is>
       </c>
       <c r="I80" s="28" t="inlineStr">
@@ -13210,7 +13225,7 @@
       </c>
       <c r="J80" s="28" t="inlineStr">
         <is>
-          <t>Group B 2nd</t>
+          <t>Group A 2nd</t>
         </is>
       </c>
     </row>
@@ -13222,17 +13237,17 @@
       </c>
       <c r="B81" s="27" t="inlineStr">
         <is>
-          <t>3:35PM</t>
+          <t>3:50PM</t>
         </is>
       </c>
       <c r="C81" s="27" t="inlineStr">
         <is>
-          <t>3:50PM</t>
+          <t>4:05PM</t>
         </is>
       </c>
       <c r="D81" s="27" t="inlineStr">
         <is>
-          <t>Under 46</t>
+          <t>Above 46</t>
         </is>
       </c>
       <c r="E81" s="27" t="n">
@@ -13240,17 +13255,17 @@
       </c>
       <c r="F81" s="27" t="inlineStr">
         <is>
-          <t>U46-SF2</t>
+          <t>A46-FINAL</t>
         </is>
       </c>
       <c r="G81" s="27" t="inlineStr">
         <is>
-          <t>Board 2</t>
+          <t>Board 1</t>
         </is>
       </c>
       <c r="H81" s="27" t="inlineStr">
         <is>
-          <t>Group B 1st</t>
+          <t>Winner SF1</t>
         </is>
       </c>
       <c r="I81" s="27" t="inlineStr">
@@ -13260,7 +13275,7 @@
       </c>
       <c r="J81" s="27" t="inlineStr">
         <is>
-          <t>Group A 2nd</t>
+          <t>Winner SF2</t>
         </is>
       </c>
     </row>
@@ -13929,7 +13944,7 @@
       </c>
       <c r="F25" s="27" t="inlineStr">
         <is>
-          <t>CW-10</t>
+          <t>CW-9</t>
         </is>
       </c>
       <c r="G25" s="27" t="inlineStr">
@@ -13979,7 +13994,7 @@
       </c>
       <c r="F26" s="28" t="inlineStr">
         <is>
-          <t>CW-9</t>
+          <t>CW-10</t>
         </is>
       </c>
       <c r="G26" s="28" t="inlineStr">
@@ -14350,12 +14365,12 @@
       </c>
       <c r="B28" s="27" t="inlineStr">
         <is>
-          <t>9:00AM</t>
+          <t>9:30AM</t>
         </is>
       </c>
       <c r="C28" s="27" t="inlineStr">
         <is>
-          <t>9:15AM</t>
+          <t>9:45AM</t>
         </is>
       </c>
       <c r="D28" s="27" t="inlineStr">
@@ -14378,7 +14393,7 @@
       </c>
       <c r="H28" s="27" t="inlineStr">
         <is>
-          <t>Rahul Garg &amp; Parthiv Mody</t>
+          <t>Vinod Agrawal &amp; Vrinda Agrawal</t>
         </is>
       </c>
       <c r="I28" s="27" t="inlineStr">
@@ -14388,7 +14403,7 @@
       </c>
       <c r="J28" s="27" t="inlineStr">
         <is>
-          <t>Sankalp Bhatnagar &amp; Jitin Bhatnagar</t>
+          <t>Vinit Padia &amp; Pratik Haldiya</t>
         </is>
       </c>
     </row>
@@ -14400,12 +14415,12 @@
       </c>
       <c r="B29" s="28" t="inlineStr">
         <is>
-          <t>9:00AM</t>
+          <t>9:30AM</t>
         </is>
       </c>
       <c r="C29" s="28" t="inlineStr">
         <is>
-          <t>9:15AM</t>
+          <t>9:45AM</t>
         </is>
       </c>
       <c r="D29" s="28" t="inlineStr">
@@ -14418,7 +14433,7 @@
       </c>
       <c r="F29" s="28" t="inlineStr">
         <is>
-          <t>M5</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="G29" s="28" t="inlineStr">
@@ -14450,12 +14465,12 @@
       </c>
       <c r="B30" s="27" t="inlineStr">
         <is>
-          <t>9:00AM</t>
+          <t>9:30AM</t>
         </is>
       </c>
       <c r="C30" s="27" t="inlineStr">
         <is>
-          <t>9:15AM</t>
+          <t>9:45AM</t>
         </is>
       </c>
       <c r="D30" s="27" t="inlineStr">
@@ -14468,7 +14483,7 @@
       </c>
       <c r="F30" s="27" t="inlineStr">
         <is>
-          <t>M7</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="G30" s="27" t="inlineStr">
@@ -14478,7 +14493,7 @@
       </c>
       <c r="H30" s="27" t="inlineStr">
         <is>
-          <t>Tejas doshi &amp; Krutika</t>
+          <t>Mayank Aggarwal &amp; Naresh Aggarwal</t>
         </is>
       </c>
       <c r="I30" s="27" t="inlineStr">
@@ -14488,7 +14503,7 @@
       </c>
       <c r="J30" s="27" t="inlineStr">
         <is>
-          <t>Shraddha malgadnkar &amp; Sachin Malgadnkar</t>
+          <t>Vinay Sawant &amp; Amar Jain</t>
         </is>
       </c>
     </row>
@@ -14500,12 +14515,12 @@
       </c>
       <c r="B31" s="28" t="inlineStr">
         <is>
-          <t>9:15AM</t>
+          <t>9:55AM</t>
         </is>
       </c>
       <c r="C31" s="28" t="inlineStr">
         <is>
-          <t>9:30AM</t>
+          <t>10:10AM</t>
         </is>
       </c>
       <c r="D31" s="28" t="inlineStr">
@@ -14518,17 +14533,17 @@
       </c>
       <c r="F31" s="28" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M4</t>
         </is>
       </c>
       <c r="G31" s="28" t="inlineStr">
         <is>
-          <t>Board 2</t>
+          <t>Board 1</t>
         </is>
       </c>
       <c r="H31" s="28" t="inlineStr">
         <is>
-          <t>Vinod Agrawal &amp; Vrinda Agrawal</t>
+          <t>Nilesh Bagaria &amp; Parthiv</t>
         </is>
       </c>
       <c r="I31" s="28" t="inlineStr">
@@ -14538,7 +14553,7 @@
       </c>
       <c r="J31" s="28" t="inlineStr">
         <is>
-          <t>Vinit Padia &amp; Pratik Haldiya</t>
+          <t>Prasad Akshintala &amp; Suvarna Akshintala</t>
         </is>
       </c>
     </row>
@@ -14550,12 +14565,12 @@
       </c>
       <c r="B32" s="27" t="inlineStr">
         <is>
-          <t>9:15AM</t>
+          <t>10:25AM</t>
         </is>
       </c>
       <c r="C32" s="27" t="inlineStr">
         <is>
-          <t>9:30AM</t>
+          <t>10:40AM</t>
         </is>
       </c>
       <c r="D32" s="27" t="inlineStr">
@@ -14568,7 +14583,7 @@
       </c>
       <c r="F32" s="27" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M5</t>
         </is>
       </c>
       <c r="G32" s="27" t="inlineStr">
@@ -14578,7 +14593,7 @@
       </c>
       <c r="H32" s="27" t="inlineStr">
         <is>
-          <t>Radhika &amp; Prashant</t>
+          <t>Rahul Garg &amp; Parthiv Mody</t>
         </is>
       </c>
       <c r="I32" s="27" t="inlineStr">
@@ -14588,7 +14603,7 @@
       </c>
       <c r="J32" s="27" t="inlineStr">
         <is>
-          <t>Adil Khan &amp; Anuj Shah</t>
+          <t>Sankalp Bhatnagar &amp; Jitin Bhatnagar</t>
         </is>
       </c>
     </row>
@@ -14600,12 +14615,12 @@
       </c>
       <c r="B33" s="28" t="inlineStr">
         <is>
-          <t>9:15AM</t>
+          <t>10:35AM</t>
         </is>
       </c>
       <c r="C33" s="28" t="inlineStr">
         <is>
-          <t>9:30AM</t>
+          <t>10:50AM</t>
         </is>
       </c>
       <c r="D33" s="28" t="inlineStr">
@@ -14618,17 +14633,17 @@
       </c>
       <c r="F33" s="28" t="inlineStr">
         <is>
-          <t>QF3</t>
+          <t>M6</t>
         </is>
       </c>
       <c r="G33" s="28" t="inlineStr">
         <is>
-          <t>Board 3</t>
+          <t>Board 2</t>
         </is>
       </c>
       <c r="H33" s="28" t="inlineStr">
         <is>
-          <t>Winner M5</t>
+          <t>Radhika &amp; Prashant</t>
         </is>
       </c>
       <c r="I33" s="28" t="inlineStr">
@@ -14638,7 +14653,7 @@
       </c>
       <c r="J33" s="28" t="inlineStr">
         <is>
-          <t>Winner M6</t>
+          <t>Adil Khan &amp; Anuj Shah</t>
         </is>
       </c>
     </row>
@@ -14650,12 +14665,12 @@
       </c>
       <c r="B34" s="27" t="inlineStr">
         <is>
-          <t>9:30AM</t>
+          <t>10:35AM</t>
         </is>
       </c>
       <c r="C34" s="27" t="inlineStr">
         <is>
-          <t>9:45AM</t>
+          <t>10:50AM</t>
         </is>
       </c>
       <c r="D34" s="27" t="inlineStr">
@@ -14668,17 +14683,17 @@
       </c>
       <c r="F34" s="27" t="inlineStr">
         <is>
-          <t>M4</t>
+          <t>M7</t>
         </is>
       </c>
       <c r="G34" s="27" t="inlineStr">
         <is>
-          <t>Board 2</t>
+          <t>Board 3</t>
         </is>
       </c>
       <c r="H34" s="27" t="inlineStr">
         <is>
-          <t>Nilesh Bagaria &amp; Parthiv</t>
+          <t>Tejas doshi &amp; Krutika</t>
         </is>
       </c>
       <c r="I34" s="27" t="inlineStr">
@@ -14688,7 +14703,7 @@
       </c>
       <c r="J34" s="27" t="inlineStr">
         <is>
-          <t>Prasad Akshintala &amp; Suvarna Akshintala</t>
+          <t>Shraddha malgadnkar &amp; Sachin Malgadnkar</t>
         </is>
       </c>
     </row>
@@ -14700,12 +14715,12 @@
       </c>
       <c r="B35" s="28" t="inlineStr">
         <is>
-          <t>9:30AM</t>
+          <t>10:50AM</t>
         </is>
       </c>
       <c r="C35" s="28" t="inlineStr">
         <is>
-          <t>9:45AM</t>
+          <t>11:05AM</t>
         </is>
       </c>
       <c r="D35" s="28" t="inlineStr">
@@ -14718,7 +14733,7 @@
       </c>
       <c r="F35" s="28" t="inlineStr">
         <is>
-          <t>M6</t>
+          <t>QF1</t>
         </is>
       </c>
       <c r="G35" s="28" t="inlineStr">
@@ -14728,7 +14743,7 @@
       </c>
       <c r="H35" s="28" t="inlineStr">
         <is>
-          <t>Mayank Aggarwal &amp; Naresh Aggarwal</t>
+          <t>Winner M5</t>
         </is>
       </c>
       <c r="I35" s="28" t="inlineStr">
@@ -14738,7 +14753,7 @@
       </c>
       <c r="J35" s="28" t="inlineStr">
         <is>
-          <t>Vinay Sawant &amp; Amar Jain</t>
+          <t>Winner M1</t>
         </is>
       </c>
     </row>
@@ -14750,12 +14765,12 @@
       </c>
       <c r="B36" s="27" t="inlineStr">
         <is>
-          <t>9:30AM</t>
+          <t>10:50AM</t>
         </is>
       </c>
       <c r="C36" s="27" t="inlineStr">
         <is>
-          <t>9:45AM</t>
+          <t>11:05AM</t>
         </is>
       </c>
       <c r="D36" s="27" t="inlineStr">
@@ -14768,17 +14783,17 @@
       </c>
       <c r="F36" s="27" t="inlineStr">
         <is>
-          <t>SF2</t>
+          <t>QF2</t>
         </is>
       </c>
       <c r="G36" s="27" t="inlineStr">
         <is>
-          <t>Board 3</t>
+          <t>Board 2</t>
         </is>
       </c>
       <c r="H36" s="27" t="inlineStr">
         <is>
-          <t>Winner QF3</t>
+          <t>Winner M6</t>
         </is>
       </c>
       <c r="I36" s="27" t="inlineStr">
@@ -14788,7 +14803,7 @@
       </c>
       <c r="J36" s="27" t="inlineStr">
         <is>
-          <t>Winner QF4</t>
+          <t>Winner M4</t>
         </is>
       </c>
     </row>
@@ -14800,12 +14815,12 @@
       </c>
       <c r="B37" s="28" t="inlineStr">
         <is>
-          <t>9:45AM</t>
+          <t>10:50AM</t>
         </is>
       </c>
       <c r="C37" s="28" t="inlineStr">
         <is>
-          <t>10:00AM</t>
+          <t>11:05AM</t>
         </is>
       </c>
       <c r="D37" s="28" t="inlineStr">
@@ -14818,17 +14833,17 @@
       </c>
       <c r="F37" s="28" t="inlineStr">
         <is>
-          <t>QF1</t>
+          <t>QF3</t>
         </is>
       </c>
       <c r="G37" s="28" t="inlineStr">
         <is>
-          <t>Board 2</t>
+          <t>Board 3</t>
         </is>
       </c>
       <c r="H37" s="28" t="inlineStr">
         <is>
-          <t>Winner M1</t>
+          <t>Winner M2</t>
         </is>
       </c>
       <c r="I37" s="28" t="inlineStr">
@@ -14838,7 +14853,7 @@
       </c>
       <c r="J37" s="28" t="inlineStr">
         <is>
-          <t>Winner M2</t>
+          <t>Winner M3</t>
         </is>
       </c>
     </row>
@@ -14850,12 +14865,12 @@
       </c>
       <c r="B38" s="27" t="inlineStr">
         <is>
-          <t>9:45AM</t>
+          <t>11:05AM</t>
         </is>
       </c>
       <c r="C38" s="27" t="inlineStr">
         <is>
-          <t>10:00AM</t>
+          <t>11:20AM</t>
         </is>
       </c>
       <c r="D38" s="27" t="inlineStr">
@@ -14900,12 +14915,12 @@
       </c>
       <c r="B39" s="28" t="inlineStr">
         <is>
-          <t>10:00AM</t>
+          <t>11:05AM</t>
         </is>
       </c>
       <c r="C39" s="28" t="inlineStr">
         <is>
-          <t>10:15AM</t>
+          <t>11:20AM</t>
         </is>
       </c>
       <c r="D39" s="28" t="inlineStr">
@@ -14918,7 +14933,7 @@
       </c>
       <c r="F39" s="28" t="inlineStr">
         <is>
-          <t>FINAL</t>
+          <t>SF1</t>
         </is>
       </c>
       <c r="G39" s="28" t="inlineStr">
@@ -14928,7 +14943,7 @@
       </c>
       <c r="H39" s="28" t="inlineStr">
         <is>
-          <t>Winner SF1</t>
+          <t>Winner QF1</t>
         </is>
       </c>
       <c r="I39" s="28" t="inlineStr">
@@ -14938,7 +14953,7 @@
       </c>
       <c r="J39" s="28" t="inlineStr">
         <is>
-          <t>Winner SF2</t>
+          <t>Winner QF2</t>
         </is>
       </c>
     </row>
@@ -14950,12 +14965,12 @@
       </c>
       <c r="B40" s="27" t="inlineStr">
         <is>
-          <t>10:00AM</t>
+          <t>11:20AM</t>
         </is>
       </c>
       <c r="C40" s="27" t="inlineStr">
         <is>
-          <t>10:15AM</t>
+          <t>11:35AM</t>
         </is>
       </c>
       <c r="D40" s="27" t="inlineStr">
@@ -14968,7 +14983,7 @@
       </c>
       <c r="F40" s="27" t="inlineStr">
         <is>
-          <t>QF2</t>
+          <t>SF2</t>
         </is>
       </c>
       <c r="G40" s="27" t="inlineStr">
@@ -14978,7 +14993,7 @@
       </c>
       <c r="H40" s="27" t="inlineStr">
         <is>
-          <t>Winner M3</t>
+          <t>Winner QF3</t>
         </is>
       </c>
       <c r="I40" s="27" t="inlineStr">
@@ -14988,7 +15003,7 @@
       </c>
       <c r="J40" s="27" t="inlineStr">
         <is>
-          <t>Winner M4</t>
+          <t>Winner QF4</t>
         </is>
       </c>
     </row>
@@ -15000,12 +15015,12 @@
       </c>
       <c r="B41" s="28" t="inlineStr">
         <is>
-          <t>10:15AM</t>
+          <t>11:35AM</t>
         </is>
       </c>
       <c r="C41" s="28" t="inlineStr">
         <is>
-          <t>10:30AM</t>
+          <t>11:50AM</t>
         </is>
       </c>
       <c r="D41" s="28" t="inlineStr">
@@ -15018,7 +15033,7 @@
       </c>
       <c r="F41" s="28" t="inlineStr">
         <is>
-          <t>SF1</t>
+          <t>FINAL</t>
         </is>
       </c>
       <c r="G41" s="28" t="inlineStr">
@@ -15028,7 +15043,7 @@
       </c>
       <c r="H41" s="28" t="inlineStr">
         <is>
-          <t>Winner QF1</t>
+          <t>Winner SF1</t>
         </is>
       </c>
       <c r="I41" s="28" t="inlineStr">
@@ -15038,7 +15053,7 @@
       </c>
       <c r="J41" s="28" t="inlineStr">
         <is>
-          <t>Winner QF2</t>
+          <t>Winner SF2</t>
         </is>
       </c>
     </row>
@@ -15090,6 +15105,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="20.1" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
@@ -15097,6 +15113,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6" ht="17.1" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
         <is>
@@ -15206,6 +15223,7 @@
         <v>39</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14" ht="17.1" customHeight="1">
       <c r="A14" s="24" t="inlineStr">
         <is>
@@ -15315,6 +15333,7 @@
         <v>61</v>
       </c>
     </row>
+    <row r="21"/>
     <row r="22" ht="17.1" customHeight="1">
       <c r="A22" s="24" t="inlineStr">
         <is>
@@ -15406,6 +15425,8 @@
         <v>25</v>
       </c>
     </row>
+    <row r="28"/>
+    <row r="29"/>
     <row r="30" ht="20.1" customHeight="1">
       <c r="A30" s="16" t="inlineStr">
         <is>
@@ -15991,7 +16012,7 @@
       </c>
       <c r="F42" s="27" t="inlineStr">
         <is>
-          <t>2639-GA-7</t>
+          <t>2639-GA-6</t>
         </is>
       </c>
       <c r="G42" s="27" t="inlineStr">
@@ -16041,7 +16062,7 @@
       </c>
       <c r="F43" s="28" t="inlineStr">
         <is>
-          <t>2639-GA-8</t>
+          <t>2639-GA-7</t>
         </is>
       </c>
       <c r="G43" s="28" t="inlineStr">
@@ -16091,7 +16112,7 @@
       </c>
       <c r="F44" s="27" t="inlineStr">
         <is>
-          <t>2639-GB-9</t>
+          <t>2639-GB-6</t>
         </is>
       </c>
       <c r="G44" s="27" t="inlineStr">
@@ -16141,7 +16162,7 @@
       </c>
       <c r="F45" s="28" t="inlineStr">
         <is>
-          <t>2639-GA-10</t>
+          <t>2639-GA-8</t>
         </is>
       </c>
       <c r="G45" s="28" t="inlineStr">
@@ -16191,7 +16212,7 @@
       </c>
       <c r="F46" s="27" t="inlineStr">
         <is>
-          <t>2639-GB-6</t>
+          <t>2639-GB-7</t>
         </is>
       </c>
       <c r="G46" s="27" t="inlineStr">
@@ -16291,7 +16312,7 @@
       </c>
       <c r="F48" s="27" t="inlineStr">
         <is>
-          <t>2639-GA-6</t>
+          <t>2639-GA-9</t>
         </is>
       </c>
       <c r="G48" s="27" t="inlineStr">
@@ -16341,7 +16362,7 @@
       </c>
       <c r="F49" s="28" t="inlineStr">
         <is>
-          <t>2639-GB-7</t>
+          <t>2639-GB-8</t>
         </is>
       </c>
       <c r="G49" s="28" t="inlineStr">
@@ -16391,7 +16412,7 @@
       </c>
       <c r="F50" s="27" t="inlineStr">
         <is>
-          <t>2639-GA-9</t>
+          <t>2639-GA-10</t>
         </is>
       </c>
       <c r="G50" s="27" t="inlineStr">
@@ -16441,7 +16462,7 @@
       </c>
       <c r="F51" s="28" t="inlineStr">
         <is>
-          <t>2639-GB-8</t>
+          <t>2639-GB-9</t>
         </is>
       </c>
       <c r="G51" s="28" t="inlineStr">
@@ -16591,7 +16612,7 @@
       </c>
       <c r="F54" s="27" t="inlineStr">
         <is>
-          <t>40P-GB-7</t>
+          <t>40P-GB-2</t>
         </is>
       </c>
       <c r="G54" s="27" t="inlineStr">
@@ -16691,7 +16712,7 @@
       </c>
       <c r="F56" s="27" t="inlineStr">
         <is>
-          <t>40P-GB-2</t>
+          <t>40P-GB-3</t>
         </is>
       </c>
       <c r="G56" s="27" t="inlineStr">
@@ -16741,7 +16762,7 @@
       </c>
       <c r="F57" s="28" t="inlineStr">
         <is>
-          <t>40P-GA-5</t>
+          <t>40P-GA-4</t>
         </is>
       </c>
       <c r="G57" s="28" t="inlineStr">
@@ -16891,7 +16912,7 @@
       </c>
       <c r="F60" s="27" t="inlineStr">
         <is>
-          <t>40P-GA-7</t>
+          <t>40P-GA-5</t>
         </is>
       </c>
       <c r="G60" s="27" t="inlineStr">
@@ -16941,7 +16962,7 @@
       </c>
       <c r="F61" s="28" t="inlineStr">
         <is>
-          <t>40P-GB-3</t>
+          <t>40P-GB-6</t>
         </is>
       </c>
       <c r="G61" s="28" t="inlineStr">
@@ -16991,7 +17012,7 @@
       </c>
       <c r="F62" s="27" t="inlineStr">
         <is>
-          <t>U26-GA-2</t>
+          <t>U26-GA-1</t>
         </is>
       </c>
       <c r="G62" s="27" t="inlineStr">
@@ -17041,7 +17062,7 @@
       </c>
       <c r="F63" s="28" t="inlineStr">
         <is>
-          <t>40P-GA-9</t>
+          <t>40P-GA-6</t>
         </is>
       </c>
       <c r="G63" s="28" t="inlineStr">
@@ -17141,7 +17162,7 @@
       </c>
       <c r="F65" s="28" t="inlineStr">
         <is>
-          <t>40P-GB-8</t>
+          <t>40P-GB-7</t>
         </is>
       </c>
       <c r="G65" s="28" t="inlineStr">
@@ -17191,7 +17212,7 @@
       </c>
       <c r="F66" s="27" t="inlineStr">
         <is>
-          <t>40P-GA-10</t>
+          <t>40P-GA-7</t>
         </is>
       </c>
       <c r="G66" s="27" t="inlineStr">
@@ -17241,7 +17262,7 @@
       </c>
       <c r="F67" s="28" t="inlineStr">
         <is>
-          <t>40P-GB-6</t>
+          <t>40P-GB-8</t>
         </is>
       </c>
       <c r="G67" s="28" t="inlineStr">
@@ -17291,7 +17312,7 @@
       </c>
       <c r="F68" s="27" t="inlineStr">
         <is>
-          <t>40P-GA-4</t>
+          <t>40P-GA-8</t>
         </is>
       </c>
       <c r="G68" s="27" t="inlineStr">
@@ -17341,7 +17362,7 @@
       </c>
       <c r="F69" s="28" t="inlineStr">
         <is>
-          <t>40P-GB-10</t>
+          <t>40P-GB-9</t>
         </is>
       </c>
       <c r="G69" s="28" t="inlineStr">
@@ -17391,7 +17412,7 @@
       </c>
       <c r="F70" s="27" t="inlineStr">
         <is>
-          <t>40P-GB-9</t>
+          <t>40P-GB-10</t>
         </is>
       </c>
       <c r="G70" s="27" t="inlineStr">
@@ -17491,7 +17512,7 @@
       </c>
       <c r="F72" s="27" t="inlineStr">
         <is>
-          <t>40P-GA-8</t>
+          <t>40P-GA-9</t>
         </is>
       </c>
       <c r="G72" s="27" t="inlineStr">
@@ -17541,7 +17562,7 @@
       </c>
       <c r="F73" s="28" t="inlineStr">
         <is>
-          <t>U26-GA-1</t>
+          <t>U26-GA-2</t>
         </is>
       </c>
       <c r="G73" s="28" t="inlineStr">
@@ -17591,7 +17612,7 @@
       </c>
       <c r="F74" s="27" t="inlineStr">
         <is>
-          <t>U26-GB-3</t>
+          <t>U26-GB-2</t>
         </is>
       </c>
       <c r="G74" s="27" t="inlineStr">
@@ -17641,7 +17662,7 @@
       </c>
       <c r="F75" s="28" t="inlineStr">
         <is>
-          <t>40P-GA-6</t>
+          <t>40P-GA-10</t>
         </is>
       </c>
       <c r="G75" s="28" t="inlineStr">
@@ -17691,7 +17712,7 @@
       </c>
       <c r="F76" s="27" t="inlineStr">
         <is>
-          <t>U26-GA-4</t>
+          <t>U26-GA-3</t>
         </is>
       </c>
       <c r="G76" s="27" t="inlineStr">
@@ -17741,7 +17762,7 @@
       </c>
       <c r="F77" s="28" t="inlineStr">
         <is>
-          <t>U26-GB-6</t>
+          <t>U26-GB-3</t>
         </is>
       </c>
       <c r="G77" s="28" t="inlineStr">
@@ -17791,7 +17812,7 @@
       </c>
       <c r="F78" s="27" t="inlineStr">
         <is>
-          <t>U26-GA-3</t>
+          <t>U26-GA-4</t>
         </is>
       </c>
       <c r="G78" s="27" t="inlineStr">
@@ -17841,7 +17862,7 @@
       </c>
       <c r="F79" s="28" t="inlineStr">
         <is>
-          <t>U26-GB-2</t>
+          <t>U26-GB-4</t>
         </is>
       </c>
       <c r="G79" s="28" t="inlineStr">
@@ -17941,7 +17962,7 @@
       </c>
       <c r="F81" s="28" t="inlineStr">
         <is>
-          <t>U26-GB-4</t>
+          <t>U26-GB-5</t>
         </is>
       </c>
       <c r="G81" s="28" t="inlineStr">
@@ -17991,7 +18012,7 @@
       </c>
       <c r="F82" s="27" t="inlineStr">
         <is>
-          <t>U26-GB-5</t>
+          <t>U26-GB-6</t>
         </is>
       </c>
       <c r="G82" s="27" t="inlineStr">
@@ -18341,7 +18362,7 @@
       </c>
       <c r="F89" s="28" t="inlineStr">
         <is>
-          <t>40P-SF2</t>
+          <t>40P-SF1</t>
         </is>
       </c>
       <c r="G89" s="28" t="inlineStr">
@@ -18391,7 +18412,7 @@
       </c>
       <c r="F90" s="27" t="inlineStr">
         <is>
-          <t>40P-SF1</t>
+          <t>40P-SF2</t>
         </is>
       </c>
       <c r="G90" s="27" t="inlineStr">
@@ -19267,7 +19288,7 @@
       </c>
       <c r="F44" s="28" t="inlineStr">
         <is>
-          <t>U11-1b</t>
+          <t>U11-2</t>
         </is>
       </c>
       <c r="G44" s="28" t="inlineStr">
@@ -19317,7 +19338,7 @@
       </c>
       <c r="F45" s="27" t="inlineStr">
         <is>
-          <t>U11-2</t>
+          <t>U11-3</t>
         </is>
       </c>
       <c r="G45" s="27" t="inlineStr">
@@ -19367,7 +19388,7 @@
       </c>
       <c r="F46" s="28" t="inlineStr">
         <is>
-          <t>U11-2b</t>
+          <t>U11-4</t>
         </is>
       </c>
       <c r="G46" s="28" t="inlineStr">
@@ -19467,7 +19488,7 @@
       </c>
       <c r="F48" s="28" t="inlineStr">
         <is>
-          <t>U11-3b</t>
+          <t>U11-5</t>
         </is>
       </c>
       <c r="G48" s="28" t="inlineStr">
@@ -19517,7 +19538,7 @@
       </c>
       <c r="F49" s="27" t="inlineStr">
         <is>
-          <t>U11-3</t>
+          <t>U11-6</t>
         </is>
       </c>
       <c r="G49" s="27" t="inlineStr">
@@ -19567,7 +19588,7 @@
       </c>
       <c r="F50" s="28" t="inlineStr">
         <is>
-          <t>U11-4</t>
+          <t>U11-7</t>
         </is>
       </c>
       <c r="G50" s="28" t="inlineStr">
@@ -19617,7 +19638,7 @@
       </c>
       <c r="F51" s="27" t="inlineStr">
         <is>
-          <t>U11-5</t>
+          <t>U11-8</t>
         </is>
       </c>
       <c r="G51" s="27" t="inlineStr">
@@ -19667,7 +19688,7 @@
       </c>
       <c r="F52" s="28" t="inlineStr">
         <is>
-          <t>1220-1b</t>
+          <t>1220-2</t>
         </is>
       </c>
       <c r="G52" s="28" t="inlineStr">
@@ -19717,7 +19738,7 @@
       </c>
       <c r="F53" s="27" t="inlineStr">
         <is>
-          <t>U11-4b</t>
+          <t>U11-9</t>
         </is>
       </c>
       <c r="G53" s="27" t="inlineStr">
@@ -19767,7 +19788,7 @@
       </c>
       <c r="F54" s="28" t="inlineStr">
         <is>
-          <t>1220-2</t>
+          <t>1220-3</t>
         </is>
       </c>
       <c r="G54" s="28" t="inlineStr">
@@ -19817,7 +19838,7 @@
       </c>
       <c r="F55" s="27" t="inlineStr">
         <is>
-          <t>U11-5b</t>
+          <t>U11-10</t>
         </is>
       </c>
       <c r="G55" s="27" t="inlineStr">
@@ -19867,7 +19888,7 @@
       </c>
       <c r="F56" s="28" t="inlineStr">
         <is>
-          <t>1220-2b</t>
+          <t>1220-4</t>
         </is>
       </c>
       <c r="G56" s="28" t="inlineStr">
@@ -19917,7 +19938,7 @@
       </c>
       <c r="F57" s="27" t="inlineStr">
         <is>
-          <t>1220-3</t>
+          <t>1220-5</t>
         </is>
       </c>
       <c r="G57" s="27" t="inlineStr">
@@ -19967,7 +19988,7 @@
       </c>
       <c r="F58" s="28" t="inlineStr">
         <is>
-          <t>1220-3b</t>
+          <t>1220-6</t>
         </is>
       </c>
       <c r="G58" s="28" t="inlineStr">
@@ -20017,7 +20038,7 @@
       </c>
       <c r="F59" s="27" t="inlineStr">
         <is>
-          <t>2140-1b</t>
+          <t>2140-1</t>
         </is>
       </c>
       <c r="G59" s="27" t="inlineStr">
@@ -20167,7 +20188,7 @@
       </c>
       <c r="F62" s="28" t="inlineStr">
         <is>
-          <t>2140-4b</t>
+          <t>2140-4</t>
         </is>
       </c>
       <c r="G62" s="28" t="inlineStr">
@@ -20217,7 +20238,7 @@
       </c>
       <c r="F63" s="27" t="inlineStr">
         <is>
-          <t>2140-8</t>
+          <t>2140-5</t>
         </is>
       </c>
       <c r="G63" s="27" t="inlineStr">
@@ -20267,7 +20288,7 @@
       </c>
       <c r="F64" s="28" t="inlineStr">
         <is>
-          <t>2140-3b</t>
+          <t>2140-6</t>
         </is>
       </c>
       <c r="G64" s="28" t="inlineStr">
@@ -20317,7 +20338,7 @@
       </c>
       <c r="F65" s="27" t="inlineStr">
         <is>
-          <t>2140-1</t>
+          <t>2140-7</t>
         </is>
       </c>
       <c r="G65" s="27" t="inlineStr">
@@ -20367,7 +20388,7 @@
       </c>
       <c r="F66" s="28" t="inlineStr">
         <is>
-          <t>2140-2b</t>
+          <t>2140-8</t>
         </is>
       </c>
       <c r="G66" s="28" t="inlineStr">
@@ -20417,7 +20438,7 @@
       </c>
       <c r="F67" s="27" t="inlineStr">
         <is>
-          <t>2140-5</t>
+          <t>2140-9</t>
         </is>
       </c>
       <c r="G67" s="27" t="inlineStr">
@@ -20517,7 +20538,7 @@
       </c>
       <c r="F69" s="27" t="inlineStr">
         <is>
-          <t>2140-4</t>
+          <t>2140-10</t>
         </is>
       </c>
       <c r="G69" s="27" t="inlineStr">
@@ -20567,7 +20588,7 @@
       </c>
       <c r="F70" s="28" t="inlineStr">
         <is>
-          <t>2140-5b</t>
+          <t>2140-11</t>
         </is>
       </c>
       <c r="G70" s="28" t="inlineStr">
@@ -20617,7 +20638,7 @@
       </c>
       <c r="F71" s="27" t="inlineStr">
         <is>
-          <t>2140-6</t>
+          <t>2140-12</t>
         </is>
       </c>
       <c r="G71" s="27" t="inlineStr">
@@ -20667,7 +20688,7 @@
       </c>
       <c r="F72" s="28" t="inlineStr">
         <is>
-          <t>2140-7b</t>
+          <t>2140-13</t>
         </is>
       </c>
       <c r="G72" s="28" t="inlineStr">
@@ -20717,7 +20738,7 @@
       </c>
       <c r="F73" s="27" t="inlineStr">
         <is>
-          <t>2140-7</t>
+          <t>2140-14</t>
         </is>
       </c>
       <c r="G73" s="27" t="inlineStr">
@@ -20967,7 +20988,7 @@
       </c>
       <c r="F78" s="28" t="inlineStr">
         <is>
-          <t>2140-6b</t>
+          <t>2140-15</t>
         </is>
       </c>
       <c r="G78" s="28" t="inlineStr">
@@ -21417,7 +21438,7 @@
       </c>
       <c r="F87" s="27" t="inlineStr">
         <is>
-          <t>41P-15</t>
+          <t>41P-14</t>
         </is>
       </c>
       <c r="G87" s="27" t="inlineStr">
@@ -21467,7 +21488,7 @@
       </c>
       <c r="F88" s="28" t="inlineStr">
         <is>
-          <t>41P-14</t>
+          <t>41P-15</t>
         </is>
       </c>
       <c r="G88" s="28" t="inlineStr">

--- a/Ekta_Schedule_With_Matchups.xlsx
+++ b/Ekta_Schedule_With_Matchups.xlsx
@@ -3463,6 +3463,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="55" t="inlineStr">
         <is>
@@ -4022,6 +4023,7 @@
         <v>22</v>
       </c>
     </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="78" t="inlineStr">
         <is>
@@ -4205,6 +4207,7 @@
       </c>
       <c r="E40" s="77" t="n"/>
     </row>
+    <row r="41"/>
     <row r="42">
       <c r="A42" s="55" t="inlineStr">
         <is>
@@ -4219,6 +4222,7 @@
         </is>
       </c>
     </row>
+    <row r="44"/>
     <row r="45">
       <c r="A45" s="74" t="inlineStr">
         <is>
@@ -4506,6 +4510,7 @@
       <c r="F59" s="88" t="n"/>
       <c r="G59" s="84" t="n"/>
     </row>
+    <row r="60"/>
     <row r="61" ht="30" customHeight="1">
       <c r="A61" s="83" t="inlineStr">
         <is>
@@ -4678,6 +4683,7 @@
         <v>2</v>
       </c>
     </row>
+    <row r="70"/>
     <row r="71" ht="30" customHeight="1">
       <c r="A71" s="85" t="inlineStr">
         <is>
@@ -9828,6 +9834,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="20.1" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
@@ -9835,6 +9842,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6" ht="17.1" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
         <is>
@@ -9907,7 +9915,7 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Rahul Garg &amp; Nilesh Mahtre</t>
+          <t>Rahul Garg &amp; Nilesh Mhatre</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -9934,6 +9942,8 @@
         <v>45</v>
       </c>
     </row>
+    <row r="16"/>
+    <row r="17"/>
     <row r="18" ht="20.1" customHeight="1">
       <c r="A18" s="16" t="inlineStr">
         <is>
@@ -10089,7 +10099,7 @@
       </c>
       <c r="J21" s="28" t="inlineStr">
         <is>
-          <t>Rahul Garg &amp; Nilesh Mahtre</t>
+          <t>Rahul Garg &amp; Nilesh Mhatre</t>
         </is>
       </c>
     </row>
@@ -13390,6 +13400,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6" ht="17.1" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
         <is>
@@ -13459,6 +13470,8 @@
         <v>68</v>
       </c>
     </row>
+    <row r="13"/>
+    <row r="14"/>
     <row r="15" ht="20.1" customHeight="1">
       <c r="A15" s="16" t="inlineStr">
         <is>
@@ -14115,6 +14128,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="20.1" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
@@ -14122,6 +14136,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6" ht="17.1" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
         <is>
@@ -14291,6 +14306,7 @@
         <v>47</v>
       </c>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="25" t="inlineStr">
         <is>
@@ -14298,6 +14314,7 @@
         </is>
       </c>
     </row>
+    <row r="25"/>
     <row r="26" ht="20.1" customHeight="1">
       <c r="A26" s="16" t="inlineStr">
         <is>

--- a/Ekta_Schedule_With_Matchups.xlsx
+++ b/Ekta_Schedule_With_Matchups.xlsx
@@ -1398,7 +1398,7 @@
       </c>
       <c r="E25" s="63" t="inlineStr">
         <is>
-          <t>Aug16 5:45PM</t>
+          <t>Aug16 6:14PM</t>
         </is>
       </c>
       <c r="F25" s="31" t="n"/>
@@ -3463,7 +3463,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="55" t="inlineStr">
         <is>
@@ -3529,12 +3528,12 @@
       </c>
       <c r="B7" s="75" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Above 46</t>
         </is>
       </c>
       <c r="C7" s="75" t="inlineStr">
         <is>
-          <t>SR-FINAL</t>
+          <t>A46-FINAL</t>
         </is>
       </c>
       <c r="D7" s="75" t="n">
@@ -3575,12 +3574,12 @@
       </c>
       <c r="B9" s="75" t="inlineStr">
         <is>
-          <t>Under 32</t>
+          <t>Under 26</t>
         </is>
       </c>
       <c r="C9" s="75" t="inlineStr">
         <is>
-          <t>U32-FINAL</t>
+          <t>U26-FINAL</t>
         </is>
       </c>
       <c r="D9" s="75" t="n">
@@ -4023,7 +4022,6 @@
         <v>22</v>
       </c>
     </row>
-    <row r="29"/>
     <row r="30">
       <c r="A30" s="78" t="inlineStr">
         <is>
@@ -4207,7 +4205,6 @@
       </c>
       <c r="E40" s="77" t="n"/>
     </row>
-    <row r="41"/>
     <row r="42">
       <c r="A42" s="55" t="inlineStr">
         <is>
@@ -4222,7 +4219,6 @@
         </is>
       </c>
     </row>
-    <row r="44"/>
     <row r="45">
       <c r="A45" s="74" t="inlineStr">
         <is>
@@ -4510,7 +4506,6 @@
       <c r="F59" s="88" t="n"/>
       <c r="G59" s="84" t="n"/>
     </row>
-    <row r="60"/>
     <row r="61" ht="30" customHeight="1">
       <c r="A61" s="83" t="inlineStr">
         <is>
@@ -4683,7 +4678,6 @@
         <v>2</v>
       </c>
     </row>
-    <row r="70"/>
     <row r="71" ht="30" customHeight="1">
       <c r="A71" s="85" t="inlineStr">
         <is>
@@ -4772,7 +4766,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6" ht="17.1" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
         <is>
@@ -4864,8 +4857,6 @@
         <v>58</v>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13"/>
     <row r="14" ht="20.1" customHeight="1">
       <c r="A14" s="16" t="inlineStr">
         <is>
@@ -5720,7 +5711,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="23" t="inlineStr">
         <is>
-          <t>5 age bands, each Group Stage → Semifinal → Final (Under 32 is a single Americano pool) · Best of 3, Final Best of 5 · 2 Tables</t>
+          <t>5 age bands, each Group Stage → Semifinal → Final (Under 26 is a single Americano pool) · Best of 3, Final Best of 5 · 2 Tables</t>
         </is>
       </c>
     </row>
@@ -5732,7 +5723,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6" ht="17.1" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
         <is>
@@ -5758,7 +5748,7 @@
           <t>Shaurya Tripathi</t>
         </is>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="4" t="n">
         <v>10</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -5766,7 +5756,7 @@
           <t>Viaan Neema</t>
         </is>
       </c>
-      <c r="E8" s="1" t="n">
+      <c r="E8" s="4" t="n">
         <v>12</v>
       </c>
     </row>
@@ -5776,7 +5766,7 @@
           <t>Parth yadav</t>
         </is>
       </c>
-      <c r="B9" s="2" t="n">
+      <c r="B9" s="6" t="n">
         <v>10</v>
       </c>
       <c r="D9" s="6" t="inlineStr">
@@ -5784,7 +5774,7 @@
           <t>Yash agarwal</t>
         </is>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="E9" s="6" t="n">
         <v>13</v>
       </c>
     </row>
@@ -5794,7 +5784,7 @@
           <t>Aadit Joshi</t>
         </is>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="4" t="n">
         <v>12</v>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -5802,15 +5792,14 @@
           <t>Hridh jhala</t>
         </is>
       </c>
-      <c r="E10" s="1" t="n">
+      <c r="E10" s="4" t="n">
         <v>13</v>
       </c>
     </row>
-    <row r="11"/>
     <row r="12" ht="17.1" customHeight="1">
       <c r="A12" s="24" t="inlineStr">
         <is>
-          <t>Under 32 (single pool, Americano)</t>
+          <t>Under 26 (single pool, Americano)</t>
         </is>
       </c>
     </row>
@@ -5832,7 +5821,7 @@
           <t>Yuvraj jain</t>
         </is>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="4" t="n">
         <v>16</v>
       </c>
     </row>
@@ -5842,7 +5831,7 @@
           <t>Aaditya Kumar</t>
         </is>
       </c>
-      <c r="B15" s="2" t="n">
+      <c r="B15" s="6" t="n">
         <v>17</v>
       </c>
     </row>
@@ -5852,7 +5841,7 @@
           <t>Hryday Goyal</t>
         </is>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="4" t="n">
         <v>20</v>
       </c>
     </row>
@@ -5862,7 +5851,7 @@
           <t>Pranit Shriyan</t>
         </is>
       </c>
-      <c r="B17" s="2" t="n">
+      <c r="B17" s="6" t="n">
         <v>25</v>
       </c>
     </row>
@@ -5872,11 +5861,10 @@
           <t>Rahul Garg</t>
         </is>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="4" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="19"/>
     <row r="20" ht="17.1" customHeight="1">
       <c r="A20" s="24" t="inlineStr">
         <is>
@@ -5902,15 +5890,15 @@
           <t>Jashit Bajaj</t>
         </is>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="4" t="n">
         <v>28</v>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>Tej</t>
-        </is>
-      </c>
-      <c r="E22" s="1" t="n">
+          <t>Prakshal Shah</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="n">
         <v>32</v>
       </c>
     </row>
@@ -5920,16 +5908,16 @@
           <t>Ravi Modi</t>
         </is>
       </c>
-      <c r="B23" s="2" t="n">
+      <c r="B23" s="6" t="n">
         <v>29</v>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>Dr Rahul Modi</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="n">
-        <v>36</v>
+          <t>Amar Parulekar</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>32</v>
       </c>
     </row>
     <row r="24">
@@ -5938,234 +5926,242 @@
           <t>Tapabrata Dutta</t>
         </is>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="4" t="n">
         <v>31</v>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
+          <t>Tej</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="n"/>
+      <c r="B25" s="2" t="n"/>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="2" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="24" t="inlineStr">
+        <is>
+          <t>Under 46</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t>Group A</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="inlineStr">
+        <is>
+          <t>Group B</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="17.1" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Dr Rahul Modi</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>Nikunj Jhala</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
           <t>Ankur Mahante</t>
         </is>
       </c>
-      <c r="E24" s="1" t="n">
+      <c r="B29" s="6" t="n">
         <v>38</v>
       </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>Prakshal Shah</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>Sudip Parui</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="n">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>Amar Parulekar</t>
-        </is>
-      </c>
-      <c r="B26" s="1" t="n">
-        <v>32</v>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>Tanmay Sharma</t>
-        </is>
-      </c>
-      <c r="E26" s="1" t="n">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="27"/>
-    <row r="28" ht="17.1" customHeight="1">
-      <c r="A28" s="24" t="inlineStr">
-        <is>
-          <t>Under 46</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="11" t="inlineStr">
-        <is>
-          <t>Group A</t>
-        </is>
-      </c>
-      <c r="D29" s="11" t="inlineStr">
-        <is>
-          <t>Group B</t>
-        </is>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>Piyush Makharia</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="n">
+        <v>43</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>Anuj Shah</t>
-        </is>
-      </c>
-      <c r="B30" s="1" t="n">
-        <v>39</v>
+          <t>Sudip Parui</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="n">
+        <v>38</v>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>Amit Ranka</t>
-        </is>
-      </c>
-      <c r="E30" s="1" t="n">
-        <v>45</v>
+          <t>Vinit Padia</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="n">
+        <v>44</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>Nikunj Jhala</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="n">
-        <v>40</v>
+          <t>Tanmay Sharma</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n">
+        <v>39</v>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>Mukul Joshi</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="n">
-        <v>51</v>
+          <t>Nilesh Bagaria</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>44</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>Piyush Makharia</t>
-        </is>
-      </c>
-      <c r="B32" s="1" t="n">
-        <v>43</v>
+          <t>Anuj Shah</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="n">
+        <v>39</v>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
+          <t>Amit Ranka</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="n"/>
+      <c r="B33" s="2" t="n"/>
+      <c r="D33" s="6" t="n"/>
+      <c r="E33" s="2" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="24" t="inlineStr">
+        <is>
+          <t>Above 46</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t>Group A</t>
+        </is>
+      </c>
+      <c r="D35" s="11" t="inlineStr">
+        <is>
+          <t>Group B</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="17.1" customHeight="1">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Mukul Joshi</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>Sanjay Kumar</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
           <t>Adil Khan</t>
         </is>
       </c>
-      <c r="E32" s="1" t="n">
+      <c r="B37" s="6" t="n">
         <v>51</v>
       </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>Vinit Padia</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="D33" s="6" t="inlineStr">
-        <is>
-          <t>Vinod Agrawal</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="n">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>Nilesh Bagaria</t>
-        </is>
-      </c>
-      <c r="B34" s="1" t="n">
-        <v>44</v>
-      </c>
-      <c r="D34" s="4" t="n"/>
-      <c r="E34" s="1" t="n"/>
-    </row>
-    <row r="35"/>
-    <row r="36" ht="17.1" customHeight="1">
-      <c r="A36" s="24" t="inlineStr">
-        <is>
-          <t>Senior</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="11" t="inlineStr">
-        <is>
-          <t>Group A</t>
-        </is>
-      </c>
-      <c r="D37" s="11" t="inlineStr">
-        <is>
-          <t>Group B</t>
-        </is>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>Sushil Dashpute</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="n">
+        <v>62</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>Ajit nair</t>
-        </is>
-      </c>
-      <c r="B38" s="1" t="n">
-        <v>59</v>
+          <t>Vinod Agrawal</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="n">
+        <v>55</v>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>Sushil Dashpute</t>
-        </is>
-      </c>
-      <c r="E38" s="1" t="n">
+          <t>HARSHAPRABHAT SHETTY</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="n">
         <v>62</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>Ghansyam nawani</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="n">
-        <v>60</v>
+          <t>Ajit nair</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="n">
+        <v>59</v>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>HARSHAPRABHAT SHETTY</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="n">
-        <v>62</v>
+          <t>Kishore Kumar</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="n">
+        <v>70</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>Sanjay Kumar</t>
-        </is>
-      </c>
-      <c r="B40" s="1" t="n">
-        <v>61</v>
-      </c>
-      <c r="D40" s="4" t="inlineStr">
-        <is>
-          <t>Kishore Kumar</t>
-        </is>
-      </c>
-      <c r="E40" s="1" t="n">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="41"/>
-    <row r="42"/>
+          <t>Ghansyam nawani</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="D40" s="4" t="n"/>
+      <c r="E40" s="1" t="n"/>
+    </row>
     <row r="43" ht="20.1" customHeight="1">
       <c r="A43" s="16" t="inlineStr">
         <is>
@@ -6243,7 +6239,7 @@
       </c>
       <c r="D45" s="27" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Above 46</t>
         </is>
       </c>
       <c r="E45" s="27" t="n">
@@ -6251,7 +6247,7 @@
       </c>
       <c r="F45" s="27" t="inlineStr">
         <is>
-          <t>SR-GA-1</t>
+          <t>A46-GA-1</t>
         </is>
       </c>
       <c r="G45" s="27" t="inlineStr">
@@ -6261,7 +6257,7 @@
       </c>
       <c r="H45" s="27" t="inlineStr">
         <is>
-          <t>Ajit nair</t>
+          <t>Mukul Joshi</t>
         </is>
       </c>
       <c r="I45" s="27" t="inlineStr">
@@ -6271,7 +6267,7 @@
       </c>
       <c r="J45" s="27" t="inlineStr">
         <is>
-          <t>Ghansyam nawani</t>
+          <t>Adil Khan</t>
         </is>
       </c>
     </row>
@@ -6293,7 +6289,7 @@
       </c>
       <c r="D46" s="28" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Above 46</t>
         </is>
       </c>
       <c r="E46" s="28" t="n">
@@ -6301,7 +6297,7 @@
       </c>
       <c r="F46" s="28" t="inlineStr">
         <is>
-          <t>SR-GB-1</t>
+          <t>A46-GA-8</t>
         </is>
       </c>
       <c r="G46" s="28" t="inlineStr">
@@ -6311,7 +6307,7 @@
       </c>
       <c r="H46" s="28" t="inlineStr">
         <is>
-          <t>Sushil Dashpute</t>
+          <t>Vinod Agrawal</t>
         </is>
       </c>
       <c r="I46" s="28" t="inlineStr">
@@ -6321,7 +6317,7 @@
       </c>
       <c r="J46" s="28" t="inlineStr">
         <is>
-          <t>HARSHAPRABHAT SHETTY</t>
+          <t>Ajit nair</t>
         </is>
       </c>
     </row>
@@ -6333,17 +6329,17 @@
       </c>
       <c r="B47" s="27" t="inlineStr">
         <is>
-          <t>8:25AM</t>
+          <t>8:15AM</t>
         </is>
       </c>
       <c r="C47" s="27" t="inlineStr">
         <is>
-          <t>8:40AM</t>
+          <t>8:30AM</t>
         </is>
       </c>
       <c r="D47" s="27" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Above 46</t>
         </is>
       </c>
       <c r="E47" s="27" t="n">
@@ -6351,7 +6347,7 @@
       </c>
       <c r="F47" s="27" t="inlineStr">
         <is>
-          <t>SR-GA-2</t>
+          <t>A46-GB-1</t>
         </is>
       </c>
       <c r="G47" s="27" t="inlineStr">
@@ -6361,7 +6357,7 @@
       </c>
       <c r="H47" s="27" t="inlineStr">
         <is>
-          <t>Ajit nair</t>
+          <t>Sanjay Kumar</t>
         </is>
       </c>
       <c r="I47" s="27" t="inlineStr">
@@ -6371,7 +6367,7 @@
       </c>
       <c r="J47" s="27" t="inlineStr">
         <is>
-          <t>Sanjay Kumar</t>
+          <t>Sushil Dashpute</t>
         </is>
       </c>
     </row>
@@ -6383,17 +6379,17 @@
       </c>
       <c r="B48" s="28" t="inlineStr">
         <is>
-          <t>8:25AM</t>
+          <t>8:15AM</t>
         </is>
       </c>
       <c r="C48" s="28" t="inlineStr">
         <is>
-          <t>8:40AM</t>
+          <t>8:30AM</t>
         </is>
       </c>
       <c r="D48" s="28" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Above 46</t>
         </is>
       </c>
       <c r="E48" s="28" t="n">
@@ -6401,7 +6397,7 @@
       </c>
       <c r="F48" s="28" t="inlineStr">
         <is>
-          <t>SR-GB-2</t>
+          <t>A46-GB-6</t>
         </is>
       </c>
       <c r="G48" s="28" t="inlineStr">
@@ -6411,7 +6407,7 @@
       </c>
       <c r="H48" s="28" t="inlineStr">
         <is>
-          <t>Sushil Dashpute</t>
+          <t>HARSHAPRABHAT SHETTY</t>
         </is>
       </c>
       <c r="I48" s="28" t="inlineStr">
@@ -6433,17 +6429,17 @@
       </c>
       <c r="B49" s="27" t="inlineStr">
         <is>
-          <t>8:50AM</t>
+          <t>8:30AM</t>
         </is>
       </c>
       <c r="C49" s="27" t="inlineStr">
         <is>
-          <t>9:05AM</t>
+          <t>8:45AM</t>
         </is>
       </c>
       <c r="D49" s="27" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Above 46</t>
         </is>
       </c>
       <c r="E49" s="27" t="n">
@@ -6451,7 +6447,7 @@
       </c>
       <c r="F49" s="27" t="inlineStr">
         <is>
-          <t>SR-GA-3</t>
+          <t>A46-GA-2</t>
         </is>
       </c>
       <c r="G49" s="27" t="inlineStr">
@@ -6461,7 +6457,7 @@
       </c>
       <c r="H49" s="27" t="inlineStr">
         <is>
-          <t>Ghansyam nawani</t>
+          <t>Mukul Joshi</t>
         </is>
       </c>
       <c r="I49" s="27" t="inlineStr">
@@ -6471,7 +6467,7 @@
       </c>
       <c r="J49" s="27" t="inlineStr">
         <is>
-          <t>Sanjay Kumar</t>
+          <t>Vinod Agrawal</t>
         </is>
       </c>
     </row>
@@ -6483,17 +6479,17 @@
       </c>
       <c r="B50" s="28" t="inlineStr">
         <is>
-          <t>8:50AM</t>
+          <t>8:30AM</t>
         </is>
       </c>
       <c r="C50" s="28" t="inlineStr">
         <is>
-          <t>9:05AM</t>
+          <t>8:45AM</t>
         </is>
       </c>
       <c r="D50" s="28" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Above 46</t>
         </is>
       </c>
       <c r="E50" s="28" t="n">
@@ -6501,7 +6497,7 @@
       </c>
       <c r="F50" s="28" t="inlineStr">
         <is>
-          <t>SR-GB-3</t>
+          <t>A46-GA-6</t>
         </is>
       </c>
       <c r="G50" s="28" t="inlineStr">
@@ -6511,7 +6507,7 @@
       </c>
       <c r="H50" s="28" t="inlineStr">
         <is>
-          <t>HARSHAPRABHAT SHETTY</t>
+          <t>Adil Khan</t>
         </is>
       </c>
       <c r="I50" s="28" t="inlineStr">
@@ -6521,7 +6517,7 @@
       </c>
       <c r="J50" s="28" t="inlineStr">
         <is>
-          <t>Kishore Kumar</t>
+          <t>Ajit nair</t>
         </is>
       </c>
     </row>
@@ -6533,17 +6529,17 @@
       </c>
       <c r="B51" s="27" t="inlineStr">
         <is>
-          <t>4:00PM</t>
+          <t>8:45AM</t>
         </is>
       </c>
       <c r="C51" s="27" t="inlineStr">
         <is>
-          <t>4:15PM</t>
+          <t>9:00AM</t>
         </is>
       </c>
       <c r="D51" s="27" t="inlineStr">
         <is>
-          <t>Under 36</t>
+          <t>Above 46</t>
         </is>
       </c>
       <c r="E51" s="27" t="n">
@@ -6551,7 +6547,7 @@
       </c>
       <c r="F51" s="27" t="inlineStr">
         <is>
-          <t>U36-GA-1</t>
+          <t>A46-GB-2</t>
         </is>
       </c>
       <c r="G51" s="27" t="inlineStr">
@@ -6561,7 +6557,7 @@
       </c>
       <c r="H51" s="27" t="inlineStr">
         <is>
-          <t>Tapabrata Dutta</t>
+          <t>Sanjay Kumar</t>
         </is>
       </c>
       <c r="I51" s="27" t="inlineStr">
@@ -6571,7 +6567,7 @@
       </c>
       <c r="J51" s="27" t="inlineStr">
         <is>
-          <t>Prakshal Shah</t>
+          <t>HARSHAPRABHAT SHETTY</t>
         </is>
       </c>
     </row>
@@ -6583,17 +6579,17 @@
       </c>
       <c r="B52" s="28" t="inlineStr">
         <is>
-          <t>4:30PM</t>
+          <t>8:45AM</t>
         </is>
       </c>
       <c r="C52" s="28" t="inlineStr">
         <is>
-          <t>4:45PM</t>
+          <t>9:00AM</t>
         </is>
       </c>
       <c r="D52" s="28" t="inlineStr">
         <is>
-          <t>Under 36</t>
+          <t>Above 46</t>
         </is>
       </c>
       <c r="E52" s="28" t="n">
@@ -6601,17 +6597,17 @@
       </c>
       <c r="F52" s="28" t="inlineStr">
         <is>
-          <t>U36-GA-2</t>
+          <t>A46-GB-5</t>
         </is>
       </c>
       <c r="G52" s="28" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H52" s="28" t="inlineStr">
         <is>
-          <t>Jashit Bajaj</t>
+          <t>Sushil Dashpute</t>
         </is>
       </c>
       <c r="I52" s="28" t="inlineStr">
@@ -6621,7 +6617,7 @@
       </c>
       <c r="J52" s="28" t="inlineStr">
         <is>
-          <t>Ravi Modi</t>
+          <t>Kishore Kumar</t>
         </is>
       </c>
     </row>
@@ -6633,17 +6629,17 @@
       </c>
       <c r="B53" s="27" t="inlineStr">
         <is>
-          <t>4:30PM</t>
+          <t>9:00AM</t>
         </is>
       </c>
       <c r="C53" s="27" t="inlineStr">
         <is>
-          <t>4:45PM</t>
+          <t>9:15AM</t>
         </is>
       </c>
       <c r="D53" s="27" t="inlineStr">
         <is>
-          <t>Under 36</t>
+          <t>Above 46</t>
         </is>
       </c>
       <c r="E53" s="27" t="n">
@@ -6651,17 +6647,17 @@
       </c>
       <c r="F53" s="27" t="inlineStr">
         <is>
-          <t>U36-GB-1</t>
+          <t>A46-GA-3</t>
         </is>
       </c>
       <c r="G53" s="27" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H53" s="27" t="inlineStr">
         <is>
-          <t>Tej</t>
+          <t>Mukul Joshi</t>
         </is>
       </c>
       <c r="I53" s="27" t="inlineStr">
@@ -6671,7 +6667,7 @@
       </c>
       <c r="J53" s="27" t="inlineStr">
         <is>
-          <t>Dr Rahul Modi</t>
+          <t>Ajit nair</t>
         </is>
       </c>
     </row>
@@ -6683,17 +6679,17 @@
       </c>
       <c r="B54" s="28" t="inlineStr">
         <is>
-          <t>4:45PM</t>
+          <t>9:00AM</t>
         </is>
       </c>
       <c r="C54" s="28" t="inlineStr">
         <is>
-          <t>5:00PM</t>
+          <t>9:15AM</t>
         </is>
       </c>
       <c r="D54" s="28" t="inlineStr">
         <is>
-          <t>Under 36</t>
+          <t>Above 46</t>
         </is>
       </c>
       <c r="E54" s="28" t="n">
@@ -6701,7 +6697,7 @@
       </c>
       <c r="F54" s="28" t="inlineStr">
         <is>
-          <t>U36-GB-2</t>
+          <t>A46-GA-5</t>
         </is>
       </c>
       <c r="G54" s="28" t="inlineStr">
@@ -6711,7 +6707,7 @@
       </c>
       <c r="H54" s="28" t="inlineStr">
         <is>
-          <t>Ankur Mahante</t>
+          <t>Adil Khan</t>
         </is>
       </c>
       <c r="I54" s="28" t="inlineStr">
@@ -6721,7 +6717,7 @@
       </c>
       <c r="J54" s="28" t="inlineStr">
         <is>
-          <t>Sudip Parui</t>
+          <t>Vinod Agrawal</t>
         </is>
       </c>
     </row>
@@ -6733,17 +6729,17 @@
       </c>
       <c r="B55" s="27" t="inlineStr">
         <is>
-          <t>4:55PM</t>
+          <t>9:15AM</t>
         </is>
       </c>
       <c r="C55" s="27" t="inlineStr">
         <is>
-          <t>5:10PM</t>
+          <t>9:30AM</t>
         </is>
       </c>
       <c r="D55" s="27" t="inlineStr">
         <is>
-          <t>Under 36</t>
+          <t>Above 46</t>
         </is>
       </c>
       <c r="E55" s="27" t="n">
@@ -6751,7 +6747,7 @@
       </c>
       <c r="F55" s="27" t="inlineStr">
         <is>
-          <t>U36-GA-3</t>
+          <t>A46-GB-3</t>
         </is>
       </c>
       <c r="G55" s="27" t="inlineStr">
@@ -6761,7 +6757,7 @@
       </c>
       <c r="H55" s="27" t="inlineStr">
         <is>
-          <t>Ravi Modi</t>
+          <t>Sanjay Kumar</t>
         </is>
       </c>
       <c r="I55" s="27" t="inlineStr">
@@ -6771,7 +6767,7 @@
       </c>
       <c r="J55" s="27" t="inlineStr">
         <is>
-          <t>Amar Parulekar</t>
+          <t>Kishore Kumar</t>
         </is>
       </c>
     </row>
@@ -6783,17 +6779,17 @@
       </c>
       <c r="B56" s="28" t="inlineStr">
         <is>
-          <t>5:10PM</t>
+          <t>9:15AM</t>
         </is>
       </c>
       <c r="C56" s="28" t="inlineStr">
         <is>
-          <t>5:25PM</t>
+          <t>9:30AM</t>
         </is>
       </c>
       <c r="D56" s="28" t="inlineStr">
         <is>
-          <t>Under 36</t>
+          <t>Above 46</t>
         </is>
       </c>
       <c r="E56" s="28" t="n">
@@ -6801,17 +6797,17 @@
       </c>
       <c r="F56" s="28" t="inlineStr">
         <is>
-          <t>U36-GA-4</t>
+          <t>A46-GB-4</t>
         </is>
       </c>
       <c r="G56" s="28" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H56" s="28" t="inlineStr">
         <is>
-          <t>Jashit Bajaj</t>
+          <t>Sushil Dashpute</t>
         </is>
       </c>
       <c r="I56" s="28" t="inlineStr">
@@ -6821,7 +6817,7 @@
       </c>
       <c r="J56" s="28" t="inlineStr">
         <is>
-          <t>Tapabrata Dutta</t>
+          <t>HARSHAPRABHAT SHETTY</t>
         </is>
       </c>
     </row>
@@ -6833,17 +6829,17 @@
       </c>
       <c r="B57" s="27" t="inlineStr">
         <is>
-          <t>5:20PM</t>
+          <t>11:50AM</t>
         </is>
       </c>
       <c r="C57" s="27" t="inlineStr">
         <is>
-          <t>5:35PM</t>
+          <t>12:05PM</t>
         </is>
       </c>
       <c r="D57" s="27" t="inlineStr">
         <is>
-          <t>Under 36</t>
+          <t>Above 46</t>
         </is>
       </c>
       <c r="E57" s="27" t="n">
@@ -6851,17 +6847,17 @@
       </c>
       <c r="F57" s="27" t="inlineStr">
         <is>
-          <t>U36-GA-5</t>
+          <t>A46-GA-4</t>
         </is>
       </c>
       <c r="G57" s="27" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H57" s="27" t="inlineStr">
         <is>
-          <t>Prakshal Shah</t>
+          <t>Mukul Joshi</t>
         </is>
       </c>
       <c r="I57" s="27" t="inlineStr">
@@ -6871,7 +6867,7 @@
       </c>
       <c r="J57" s="27" t="inlineStr">
         <is>
-          <t>Amar Parulekar</t>
+          <t>Ghansyam nawani</t>
         </is>
       </c>
     </row>
@@ -6883,17 +6879,17 @@
       </c>
       <c r="B58" s="28" t="inlineStr">
         <is>
-          <t>5:45PM</t>
+          <t>11:50AM</t>
         </is>
       </c>
       <c r="C58" s="28" t="inlineStr">
         <is>
-          <t>6:00PM</t>
+          <t>12:05PM</t>
         </is>
       </c>
       <c r="D58" s="28" t="inlineStr">
         <is>
-          <t>Under 36</t>
+          <t>Under 15</t>
         </is>
       </c>
       <c r="E58" s="28" t="n">
@@ -6901,17 +6897,17 @@
       </c>
       <c r="F58" s="28" t="inlineStr">
         <is>
-          <t>U36-GA-6</t>
+          <t>U15-GA-2</t>
         </is>
       </c>
       <c r="G58" s="28" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H58" s="28" t="inlineStr">
         <is>
-          <t>Jashit Bajaj</t>
+          <t>Shaurya Tripathi</t>
         </is>
       </c>
       <c r="I58" s="28" t="inlineStr">
@@ -6921,7 +6917,7 @@
       </c>
       <c r="J58" s="28" t="inlineStr">
         <is>
-          <t>Prakshal Shah</t>
+          <t>Aadit Joshi</t>
         </is>
       </c>
     </row>
@@ -6933,17 +6929,17 @@
       </c>
       <c r="B59" s="27" t="inlineStr">
         <is>
-          <t>5:53PM</t>
+          <t>3:55PM</t>
         </is>
       </c>
       <c r="C59" s="27" t="inlineStr">
         <is>
-          <t>6:08PM</t>
+          <t>4:10PM</t>
         </is>
       </c>
       <c r="D59" s="27" t="inlineStr">
         <is>
-          <t>Under 36</t>
+          <t>Above 46</t>
         </is>
       </c>
       <c r="E59" s="27" t="n">
@@ -6951,17 +6947,17 @@
       </c>
       <c r="F59" s="27" t="inlineStr">
         <is>
-          <t>U36-GB-3</t>
+          <t>A46-GA-7</t>
         </is>
       </c>
       <c r="G59" s="27" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H59" s="27" t="inlineStr">
         <is>
-          <t>Dr Rahul Modi</t>
+          <t>Adil Khan</t>
         </is>
       </c>
       <c r="I59" s="27" t="inlineStr">
@@ -6971,7 +6967,7 @@
       </c>
       <c r="J59" s="27" t="inlineStr">
         <is>
-          <t>Tanmay Sharma</t>
+          <t>Ghansyam nawani</t>
         </is>
       </c>
     </row>
@@ -6983,17 +6979,17 @@
       </c>
       <c r="B60" s="28" t="inlineStr">
         <is>
-          <t>6:00PM</t>
+          <t>4:10PM</t>
         </is>
       </c>
       <c r="C60" s="28" t="inlineStr">
         <is>
-          <t>6:15PM</t>
+          <t>4:25PM</t>
         </is>
       </c>
       <c r="D60" s="28" t="inlineStr">
         <is>
-          <t>Under 36</t>
+          <t>Under 15</t>
         </is>
       </c>
       <c r="E60" s="28" t="n">
@@ -7001,17 +6997,17 @@
       </c>
       <c r="F60" s="28" t="inlineStr">
         <is>
-          <t>U36-GB-4</t>
+          <t>U15-GA-3</t>
         </is>
       </c>
       <c r="G60" s="28" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H60" s="28" t="inlineStr">
         <is>
-          <t>Tej</t>
+          <t>Parth yadav</t>
         </is>
       </c>
       <c r="I60" s="28" t="inlineStr">
@@ -7021,7 +7017,7 @@
       </c>
       <c r="J60" s="28" t="inlineStr">
         <is>
-          <t>Ankur Mahante</t>
+          <t>Aadit Joshi</t>
         </is>
       </c>
     </row>
@@ -7033,17 +7029,17 @@
       </c>
       <c r="B61" s="27" t="inlineStr">
         <is>
-          <t>6:15PM</t>
+          <t>4:20PM</t>
         </is>
       </c>
       <c r="C61" s="27" t="inlineStr">
         <is>
-          <t>6:30PM</t>
+          <t>4:35PM</t>
         </is>
       </c>
       <c r="D61" s="27" t="inlineStr">
         <is>
-          <t>Under 36</t>
+          <t>Above 46</t>
         </is>
       </c>
       <c r="E61" s="27" t="n">
@@ -7051,7 +7047,7 @@
       </c>
       <c r="F61" s="27" t="inlineStr">
         <is>
-          <t>U36-GA-7</t>
+          <t>A46-GA-9</t>
         </is>
       </c>
       <c r="G61" s="27" t="inlineStr">
@@ -7061,7 +7057,7 @@
       </c>
       <c r="H61" s="27" t="inlineStr">
         <is>
-          <t>Ravi Modi</t>
+          <t>Vinod Agrawal</t>
         </is>
       </c>
       <c r="I61" s="27" t="inlineStr">
@@ -7071,7 +7067,7 @@
       </c>
       <c r="J61" s="27" t="inlineStr">
         <is>
-          <t>Tapabrata Dutta</t>
+          <t>Ghansyam nawani</t>
         </is>
       </c>
     </row>
@@ -7083,17 +7079,17 @@
       </c>
       <c r="B62" s="28" t="inlineStr">
         <is>
-          <t>6:18PM</t>
+          <t>4:25PM</t>
         </is>
       </c>
       <c r="C62" s="28" t="inlineStr">
         <is>
-          <t>6:33PM</t>
+          <t>4:40PM</t>
         </is>
       </c>
       <c r="D62" s="28" t="inlineStr">
         <is>
-          <t>Under 36</t>
+          <t>Under 15</t>
         </is>
       </c>
       <c r="E62" s="28" t="n">
@@ -7101,7 +7097,7 @@
       </c>
       <c r="F62" s="28" t="inlineStr">
         <is>
-          <t>U36-GB-5</t>
+          <t>U15-GB-2</t>
         </is>
       </c>
       <c r="G62" s="28" t="inlineStr">
@@ -7111,7 +7107,7 @@
       </c>
       <c r="H62" s="28" t="inlineStr">
         <is>
-          <t>Sudip Parui</t>
+          <t>Viaan Neema</t>
         </is>
       </c>
       <c r="I62" s="28" t="inlineStr">
@@ -7121,7 +7117,7 @@
       </c>
       <c r="J62" s="28" t="inlineStr">
         <is>
-          <t>Tanmay Sharma</t>
+          <t>Hridh jhala</t>
         </is>
       </c>
     </row>
@@ -7133,17 +7129,17 @@
       </c>
       <c r="B63" s="27" t="inlineStr">
         <is>
-          <t>6:33PM</t>
+          <t>4:40PM</t>
         </is>
       </c>
       <c r="C63" s="27" t="inlineStr">
         <is>
-          <t>6:48PM</t>
+          <t>4:55PM</t>
         </is>
       </c>
       <c r="D63" s="27" t="inlineStr">
         <is>
-          <t>Under 36</t>
+          <t>Under 26</t>
         </is>
       </c>
       <c r="E63" s="27" t="n">
@@ -7151,7 +7147,7 @@
       </c>
       <c r="F63" s="27" t="inlineStr">
         <is>
-          <t>U36-GB-6</t>
+          <t>U26-1</t>
         </is>
       </c>
       <c r="G63" s="27" t="inlineStr">
@@ -7161,7 +7157,7 @@
       </c>
       <c r="H63" s="27" t="inlineStr">
         <is>
-          <t>Dr Rahul Modi</t>
+          <t>Yuvraj jain</t>
         </is>
       </c>
       <c r="I63" s="27" t="inlineStr">
@@ -7171,7 +7167,7 @@
       </c>
       <c r="J63" s="27" t="inlineStr">
         <is>
-          <t>Ankur Mahante</t>
+          <t>Aaditya Kumar</t>
         </is>
       </c>
     </row>
@@ -7183,17 +7179,17 @@
       </c>
       <c r="B64" s="28" t="inlineStr">
         <is>
-          <t>6:40PM</t>
+          <t>4:45PM</t>
         </is>
       </c>
       <c r="C64" s="28" t="inlineStr">
         <is>
-          <t>6:55PM</t>
+          <t>5:00PM</t>
         </is>
       </c>
       <c r="D64" s="28" t="inlineStr">
         <is>
-          <t>Under 36</t>
+          <t>Above 46</t>
         </is>
       </c>
       <c r="E64" s="28" t="n">
@@ -7201,7 +7197,7 @@
       </c>
       <c r="F64" s="28" t="inlineStr">
         <is>
-          <t>U36-GA-8</t>
+          <t>A46-GA-10</t>
         </is>
       </c>
       <c r="G64" s="28" t="inlineStr">
@@ -7211,7 +7207,7 @@
       </c>
       <c r="H64" s="28" t="inlineStr">
         <is>
-          <t>Tapabrata Dutta</t>
+          <t>Ajit nair</t>
         </is>
       </c>
       <c r="I64" s="28" t="inlineStr">
@@ -7221,7 +7217,7 @@
       </c>
       <c r="J64" s="28" t="inlineStr">
         <is>
-          <t>Amar Parulekar</t>
+          <t>Ghansyam nawani</t>
         </is>
       </c>
     </row>
@@ -7233,17 +7229,17 @@
       </c>
       <c r="B65" s="27" t="inlineStr">
         <is>
-          <t>6:58PM</t>
+          <t>4:55PM</t>
         </is>
       </c>
       <c r="C65" s="27" t="inlineStr">
         <is>
-          <t>7:13PM</t>
+          <t>5:10PM</t>
         </is>
       </c>
       <c r="D65" s="27" t="inlineStr">
         <is>
-          <t>Under 36</t>
+          <t>Under 26</t>
         </is>
       </c>
       <c r="E65" s="27" t="n">
@@ -7251,7 +7247,7 @@
       </c>
       <c r="F65" s="27" t="inlineStr">
         <is>
-          <t>U36-GB-7</t>
+          <t>U26-8</t>
         </is>
       </c>
       <c r="G65" s="27" t="inlineStr">
@@ -7261,7 +7257,7 @@
       </c>
       <c r="H65" s="27" t="inlineStr">
         <is>
-          <t>Ankur Mahante</t>
+          <t>Hryday Goyal</t>
         </is>
       </c>
       <c r="I65" s="27" t="inlineStr">
@@ -7271,7 +7267,7 @@
       </c>
       <c r="J65" s="27" t="inlineStr">
         <is>
-          <t>Tanmay Sharma</t>
+          <t>Pranit Shriyan</t>
         </is>
       </c>
     </row>
@@ -7283,12 +7279,12 @@
       </c>
       <c r="B66" s="28" t="inlineStr">
         <is>
-          <t>7:05PM</t>
+          <t>5:00PM</t>
         </is>
       </c>
       <c r="C66" s="28" t="inlineStr">
         <is>
-          <t>7:20PM</t>
+          <t>5:15PM</t>
         </is>
       </c>
       <c r="D66" s="28" t="inlineStr">
@@ -7301,7 +7297,7 @@
       </c>
       <c r="F66" s="28" t="inlineStr">
         <is>
-          <t>U36-GA-9</t>
+          <t>U36-GA-1</t>
         </is>
       </c>
       <c r="G66" s="28" t="inlineStr">
@@ -7321,7 +7317,7 @@
       </c>
       <c r="J66" s="28" t="inlineStr">
         <is>
-          <t>Amar Parulekar</t>
+          <t>Ravi Modi</t>
         </is>
       </c>
     </row>
@@ -7333,17 +7329,17 @@
       </c>
       <c r="B67" s="27" t="inlineStr">
         <is>
-          <t>7:15PM</t>
+          <t>5:10PM</t>
         </is>
       </c>
       <c r="C67" s="27" t="inlineStr">
         <is>
-          <t>7:30PM</t>
+          <t>5:25PM</t>
         </is>
       </c>
       <c r="D67" s="27" t="inlineStr">
         <is>
-          <t>Under 46</t>
+          <t>Under 15</t>
         </is>
       </c>
       <c r="E67" s="27" t="n">
@@ -7351,7 +7347,7 @@
       </c>
       <c r="F67" s="27" t="inlineStr">
         <is>
-          <t>U46-GB-1</t>
+          <t>U15-GA-1</t>
         </is>
       </c>
       <c r="G67" s="27" t="inlineStr">
@@ -7361,7 +7357,7 @@
       </c>
       <c r="H67" s="27" t="inlineStr">
         <is>
-          <t>Mukul Joshi</t>
+          <t>Shaurya Tripathi</t>
         </is>
       </c>
       <c r="I67" s="27" t="inlineStr">
@@ -7371,7 +7367,7 @@
       </c>
       <c r="J67" s="27" t="inlineStr">
         <is>
-          <t>Vinod Agrawal</t>
+          <t>Parth yadav</t>
         </is>
       </c>
     </row>
@@ -7383,17 +7379,17 @@
       </c>
       <c r="B68" s="28" t="inlineStr">
         <is>
-          <t>7:40PM</t>
+          <t>5:15PM</t>
         </is>
       </c>
       <c r="C68" s="28" t="inlineStr">
         <is>
-          <t>7:55PM</t>
+          <t>5:30PM</t>
         </is>
       </c>
       <c r="D68" s="28" t="inlineStr">
         <is>
-          <t>Under 46</t>
+          <t>Under 15</t>
         </is>
       </c>
       <c r="E68" s="28" t="n">
@@ -7401,7 +7397,7 @@
       </c>
       <c r="F68" s="28" t="inlineStr">
         <is>
-          <t>U46-GB-2</t>
+          <t>U15-GB-1</t>
         </is>
       </c>
       <c r="G68" s="28" t="inlineStr">
@@ -7411,7 +7407,7 @@
       </c>
       <c r="H68" s="28" t="inlineStr">
         <is>
-          <t>Amit Ranka</t>
+          <t>Viaan Neema</t>
         </is>
       </c>
       <c r="I68" s="28" t="inlineStr">
@@ -7421,7 +7417,7 @@
       </c>
       <c r="J68" s="28" t="inlineStr">
         <is>
-          <t>Mukul Joshi</t>
+          <t>Yash agarwal</t>
         </is>
       </c>
     </row>
@@ -7433,17 +7429,17 @@
       </c>
       <c r="B69" s="27" t="inlineStr">
         <is>
-          <t>7:50PM</t>
+          <t>5:25PM</t>
         </is>
       </c>
       <c r="C69" s="27" t="inlineStr">
         <is>
-          <t>8:05PM</t>
+          <t>5:40PM</t>
         </is>
       </c>
       <c r="D69" s="27" t="inlineStr">
         <is>
-          <t>Under 36</t>
+          <t>Under 26</t>
         </is>
       </c>
       <c r="E69" s="27" t="n">
@@ -7451,7 +7447,7 @@
       </c>
       <c r="F69" s="27" t="inlineStr">
         <is>
-          <t>U36-GB-8</t>
+          <t>U26-2</t>
         </is>
       </c>
       <c r="G69" s="27" t="inlineStr">
@@ -7461,7 +7457,7 @@
       </c>
       <c r="H69" s="27" t="inlineStr">
         <is>
-          <t>Tej</t>
+          <t>Yuvraj jain</t>
         </is>
       </c>
       <c r="I69" s="27" t="inlineStr">
@@ -7471,7 +7467,7 @@
       </c>
       <c r="J69" s="27" t="inlineStr">
         <is>
-          <t>Sudip Parui</t>
+          <t>Hryday Goyal</t>
         </is>
       </c>
     </row>
@@ -7483,17 +7479,17 @@
       </c>
       <c r="B70" s="28" t="inlineStr">
         <is>
-          <t>7:55PM</t>
+          <t>5:30PM</t>
         </is>
       </c>
       <c r="C70" s="28" t="inlineStr">
         <is>
-          <t>8:10PM</t>
+          <t>5:45PM</t>
         </is>
       </c>
       <c r="D70" s="28" t="inlineStr">
         <is>
-          <t>Under 36</t>
+          <t>Under 26</t>
         </is>
       </c>
       <c r="E70" s="28" t="n">
@@ -7501,7 +7497,7 @@
       </c>
       <c r="F70" s="28" t="inlineStr">
         <is>
-          <t>U36-GA-10</t>
+          <t>U26-6</t>
         </is>
       </c>
       <c r="G70" s="28" t="inlineStr">
@@ -7511,7 +7507,7 @@
       </c>
       <c r="H70" s="28" t="inlineStr">
         <is>
-          <t>Ravi Modi</t>
+          <t>Aaditya Kumar</t>
         </is>
       </c>
       <c r="I70" s="28" t="inlineStr">
@@ -7521,7 +7517,7 @@
       </c>
       <c r="J70" s="28" t="inlineStr">
         <is>
-          <t>Prakshal Shah</t>
+          <t>Pranit Shriyan</t>
         </is>
       </c>
     </row>
@@ -7533,17 +7529,17 @@
       </c>
       <c r="B71" s="27" t="inlineStr">
         <is>
-          <t>8:05PM</t>
+          <t>5:40PM</t>
         </is>
       </c>
       <c r="C71" s="27" t="inlineStr">
         <is>
-          <t>8:20PM</t>
+          <t>5:55PM</t>
         </is>
       </c>
       <c r="D71" s="27" t="inlineStr">
         <is>
-          <t>Under 46</t>
+          <t>Under 15</t>
         </is>
       </c>
       <c r="E71" s="27" t="n">
@@ -7551,7 +7547,7 @@
       </c>
       <c r="F71" s="27" t="inlineStr">
         <is>
-          <t>U46-GA-1</t>
+          <t>U15-GB-3</t>
         </is>
       </c>
       <c r="G71" s="27" t="inlineStr">
@@ -7561,7 +7557,7 @@
       </c>
       <c r="H71" s="27" t="inlineStr">
         <is>
-          <t>Anuj Shah</t>
+          <t>Yash agarwal</t>
         </is>
       </c>
       <c r="I71" s="27" t="inlineStr">
@@ -7571,7 +7567,7 @@
       </c>
       <c r="J71" s="27" t="inlineStr">
         <is>
-          <t>Nikunj Jhala</t>
+          <t>Hridh jhala</t>
         </is>
       </c>
     </row>
@@ -7583,17 +7579,17 @@
       </c>
       <c r="B72" s="28" t="inlineStr">
         <is>
-          <t>8:20PM</t>
+          <t>5:45PM</t>
         </is>
       </c>
       <c r="C72" s="28" t="inlineStr">
         <is>
-          <t>8:35PM</t>
+          <t>6:00PM</t>
         </is>
       </c>
       <c r="D72" s="28" t="inlineStr">
         <is>
-          <t>Under 46</t>
+          <t>Under 36</t>
         </is>
       </c>
       <c r="E72" s="28" t="n">
@@ -7601,17 +7597,17 @@
       </c>
       <c r="F72" s="28" t="inlineStr">
         <is>
-          <t>U46-GB-3</t>
+          <t>U36-GA-2</t>
         </is>
       </c>
       <c r="G72" s="28" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H72" s="28" t="inlineStr">
         <is>
-          <t>Amit Ranka</t>
+          <t>Jashit Bajaj</t>
         </is>
       </c>
       <c r="I72" s="28" t="inlineStr">
@@ -7621,7 +7617,7 @@
       </c>
       <c r="J72" s="28" t="inlineStr">
         <is>
-          <t>Vinod Agrawal</t>
+          <t>Tapabrata Dutta</t>
         </is>
       </c>
     </row>
@@ -7633,17 +7629,17 @@
       </c>
       <c r="B73" s="27" t="inlineStr">
         <is>
-          <t>8:30PM</t>
+          <t>5:55PM</t>
         </is>
       </c>
       <c r="C73" s="27" t="inlineStr">
         <is>
-          <t>8:45PM</t>
+          <t>6:10PM</t>
         </is>
       </c>
       <c r="D73" s="27" t="inlineStr">
         <is>
-          <t>Under 46</t>
+          <t>Under 26</t>
         </is>
       </c>
       <c r="E73" s="27" t="n">
@@ -7651,17 +7647,17 @@
       </c>
       <c r="F73" s="27" t="inlineStr">
         <is>
-          <t>U46-GA-2</t>
+          <t>U26-3</t>
         </is>
       </c>
       <c r="G73" s="27" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H73" s="27" t="inlineStr">
         <is>
-          <t>Nikunj Jhala</t>
+          <t>Yuvraj jain</t>
         </is>
       </c>
       <c r="I73" s="27" t="inlineStr">
@@ -7671,7 +7667,7 @@
       </c>
       <c r="J73" s="27" t="inlineStr">
         <is>
-          <t>Nilesh Bagaria</t>
+          <t>Pranit Shriyan</t>
         </is>
       </c>
     </row>
@@ -7683,17 +7679,17 @@
       </c>
       <c r="B74" s="28" t="inlineStr">
         <is>
-          <t>8:35PM</t>
+          <t>6:00PM</t>
         </is>
       </c>
       <c r="C74" s="28" t="inlineStr">
         <is>
-          <t>8:50PM</t>
+          <t>6:15PM</t>
         </is>
       </c>
       <c r="D74" s="28" t="inlineStr">
         <is>
-          <t>Under 36</t>
+          <t>Under 26</t>
         </is>
       </c>
       <c r="E74" s="28" t="n">
@@ -7701,17 +7697,17 @@
       </c>
       <c r="F74" s="28" t="inlineStr">
         <is>
-          <t>U36-GB-9</t>
+          <t>U26-5</t>
         </is>
       </c>
       <c r="G74" s="28" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H74" s="28" t="inlineStr">
         <is>
-          <t>Dr Rahul Modi</t>
+          <t>Aaditya Kumar</t>
         </is>
       </c>
       <c r="I74" s="28" t="inlineStr">
@@ -7721,7 +7717,7 @@
       </c>
       <c r="J74" s="28" t="inlineStr">
         <is>
-          <t>Sudip Parui</t>
+          <t>Hryday Goyal</t>
         </is>
       </c>
     </row>
@@ -7733,12 +7729,12 @@
       </c>
       <c r="B75" s="27" t="inlineStr">
         <is>
-          <t>8:45PM</t>
+          <t>6:10PM</t>
         </is>
       </c>
       <c r="C75" s="27" t="inlineStr">
         <is>
-          <t>9:00PM</t>
+          <t>6:25PM</t>
         </is>
       </c>
       <c r="D75" s="27" t="inlineStr">
@@ -7751,17 +7747,17 @@
       </c>
       <c r="F75" s="27" t="inlineStr">
         <is>
-          <t>U36-GB-10</t>
+          <t>U36-GB-1</t>
         </is>
       </c>
       <c r="G75" s="27" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H75" s="27" t="inlineStr">
         <is>
-          <t>Tej</t>
+          <t>Prakshal Shah</t>
         </is>
       </c>
       <c r="I75" s="27" t="inlineStr">
@@ -7771,7 +7767,7 @@
       </c>
       <c r="J75" s="27" t="inlineStr">
         <is>
-          <t>Tanmay Sharma</t>
+          <t>Amar Parulekar</t>
         </is>
       </c>
     </row>
@@ -7783,17 +7779,17 @@
       </c>
       <c r="B76" s="28" t="inlineStr">
         <is>
-          <t>8:50PM</t>
+          <t>6:15PM</t>
         </is>
       </c>
       <c r="C76" s="28" t="inlineStr">
         <is>
-          <t>9:05PM</t>
+          <t>6:30PM</t>
         </is>
       </c>
       <c r="D76" s="28" t="inlineStr">
         <is>
-          <t>Under 15</t>
+          <t>Under 46</t>
         </is>
       </c>
       <c r="E76" s="28" t="n">
@@ -7801,17 +7797,17 @@
       </c>
       <c r="F76" s="28" t="inlineStr">
         <is>
-          <t>U15-GA-1</t>
+          <t>U46-GA-1</t>
         </is>
       </c>
       <c r="G76" s="28" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H76" s="28" t="inlineStr">
         <is>
-          <t>Shaurya Tripathi</t>
+          <t>Dr Rahul Modi</t>
         </is>
       </c>
       <c r="I76" s="28" t="inlineStr">
@@ -7821,7 +7817,7 @@
       </c>
       <c r="J76" s="28" t="inlineStr">
         <is>
-          <t>Parth yadav</t>
+          <t>Ankur Mahante</t>
         </is>
       </c>
     </row>
@@ -7833,17 +7829,17 @@
       </c>
       <c r="B77" s="27" t="inlineStr">
         <is>
-          <t>9:00PM</t>
+          <t>6:25PM</t>
         </is>
       </c>
       <c r="C77" s="27" t="inlineStr">
         <is>
-          <t>9:15PM</t>
+          <t>6:40PM</t>
         </is>
       </c>
       <c r="D77" s="27" t="inlineStr">
         <is>
-          <t>Under 46</t>
+          <t>Under 26</t>
         </is>
       </c>
       <c r="E77" s="27" t="n">
@@ -7851,17 +7847,17 @@
       </c>
       <c r="F77" s="27" t="inlineStr">
         <is>
-          <t>U46-GA-3</t>
+          <t>U26-4</t>
         </is>
       </c>
       <c r="G77" s="27" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H77" s="27" t="inlineStr">
         <is>
-          <t>Vinit Padia</t>
+          <t>Yuvraj jain</t>
         </is>
       </c>
       <c r="I77" s="27" t="inlineStr">
@@ -7871,7 +7867,7 @@
       </c>
       <c r="J77" s="27" t="inlineStr">
         <is>
-          <t>Nilesh Bagaria</t>
+          <t>Rahul Garg</t>
         </is>
       </c>
     </row>
@@ -7883,17 +7879,17 @@
       </c>
       <c r="B78" s="28" t="inlineStr">
         <is>
-          <t>9:25PM</t>
+          <t>6:30PM</t>
         </is>
       </c>
       <c r="C78" s="28" t="inlineStr">
         <is>
-          <t>9:40PM</t>
+          <t>6:45PM</t>
         </is>
       </c>
       <c r="D78" s="28" t="inlineStr">
         <is>
-          <t>Under 46</t>
+          <t>Under 36</t>
         </is>
       </c>
       <c r="E78" s="28" t="n">
@@ -7901,7 +7897,7 @@
       </c>
       <c r="F78" s="28" t="inlineStr">
         <is>
-          <t>U46-GB-4</t>
+          <t>U36-GA-3</t>
         </is>
       </c>
       <c r="G78" s="28" t="inlineStr">
@@ -7911,7 +7907,7 @@
       </c>
       <c r="H78" s="28" t="inlineStr">
         <is>
-          <t>Adil Khan</t>
+          <t>Ravi Modi</t>
         </is>
       </c>
       <c r="I78" s="28" t="inlineStr">
@@ -7921,7 +7917,7 @@
       </c>
       <c r="J78" s="28" t="inlineStr">
         <is>
-          <t>Vinod Agrawal</t>
+          <t>Tapabrata Dutta</t>
         </is>
       </c>
     </row>
@@ -7933,12 +7929,12 @@
       </c>
       <c r="B79" s="27" t="inlineStr">
         <is>
-          <t>9:25PM</t>
+          <t>6:40PM</t>
         </is>
       </c>
       <c r="C79" s="27" t="inlineStr">
         <is>
-          <t>9:40PM</t>
+          <t>6:55PM</t>
         </is>
       </c>
       <c r="D79" s="27" t="inlineStr">
@@ -7951,7 +7947,7 @@
       </c>
       <c r="F79" s="27" t="inlineStr">
         <is>
-          <t>U46-GA-4</t>
+          <t>U46-GA-2</t>
         </is>
       </c>
       <c r="G79" s="27" t="inlineStr">
@@ -7961,7 +7957,7 @@
       </c>
       <c r="H79" s="27" t="inlineStr">
         <is>
-          <t>Anuj Shah</t>
+          <t>Dr Rahul Modi</t>
         </is>
       </c>
       <c r="I79" s="27" t="inlineStr">
@@ -7971,7 +7967,7 @@
       </c>
       <c r="J79" s="27" t="inlineStr">
         <is>
-          <t>Nilesh Bagaria</t>
+          <t>Sudip Parui</t>
         </is>
       </c>
     </row>
@@ -7983,17 +7979,17 @@
       </c>
       <c r="B80" s="28" t="inlineStr">
         <is>
-          <t>9:40PM</t>
+          <t>6:45PM</t>
         </is>
       </c>
       <c r="C80" s="28" t="inlineStr">
         <is>
-          <t>9:55PM</t>
+          <t>7:00PM</t>
         </is>
       </c>
       <c r="D80" s="28" t="inlineStr">
         <is>
-          <t>Under 15</t>
+          <t>Under 46</t>
         </is>
       </c>
       <c r="E80" s="28" t="n">
@@ -8001,17 +7997,17 @@
       </c>
       <c r="F80" s="28" t="inlineStr">
         <is>
-          <t>U15-GB-1</t>
+          <t>U46-GA-6</t>
         </is>
       </c>
       <c r="G80" s="28" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H80" s="28" t="inlineStr">
         <is>
-          <t>Viaan Neema</t>
+          <t>Ankur Mahante</t>
         </is>
       </c>
       <c r="I80" s="28" t="inlineStr">
@@ -8021,7 +8017,7 @@
       </c>
       <c r="J80" s="28" t="inlineStr">
         <is>
-          <t>Yash agarwal</t>
+          <t>Tanmay Sharma</t>
         </is>
       </c>
     </row>
@@ -8033,12 +8029,12 @@
       </c>
       <c r="B81" s="27" t="inlineStr">
         <is>
-          <t>9:50PM</t>
+          <t>6:55PM</t>
         </is>
       </c>
       <c r="C81" s="27" t="inlineStr">
         <is>
-          <t>10:05PM</t>
+          <t>7:10PM</t>
         </is>
       </c>
       <c r="D81" s="27" t="inlineStr">
@@ -8051,17 +8047,17 @@
       </c>
       <c r="F81" s="27" t="inlineStr">
         <is>
-          <t>U46-GB-5</t>
+          <t>U46-GB-8</t>
         </is>
       </c>
       <c r="G81" s="27" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H81" s="27" t="inlineStr">
         <is>
-          <t>Amit Ranka</t>
+          <t>Vinit Padia</t>
         </is>
       </c>
       <c r="I81" s="27" t="inlineStr">
@@ -8071,7 +8067,7 @@
       </c>
       <c r="J81" s="27" t="inlineStr">
         <is>
-          <t>Adil Khan</t>
+          <t>Nilesh Bagaria</t>
         </is>
       </c>
     </row>
@@ -8083,17 +8079,17 @@
       </c>
       <c r="B82" s="28" t="inlineStr">
         <is>
-          <t>9:55PM</t>
+          <t>7:05PM</t>
         </is>
       </c>
       <c r="C82" s="28" t="inlineStr">
         <is>
-          <t>10:10PM</t>
+          <t>7:20PM</t>
         </is>
       </c>
       <c r="D82" s="28" t="inlineStr">
         <is>
-          <t>Under 15</t>
+          <t>Under 46</t>
         </is>
       </c>
       <c r="E82" s="28" t="n">
@@ -8101,17 +8097,17 @@
       </c>
       <c r="F82" s="28" t="inlineStr">
         <is>
-          <t>U15-GA-2</t>
+          <t>U46-GA-4</t>
         </is>
       </c>
       <c r="G82" s="28" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H82" s="28" t="inlineStr">
         <is>
-          <t>Shaurya Tripathi</t>
+          <t>Dr Rahul Modi</t>
         </is>
       </c>
       <c r="I82" s="28" t="inlineStr">
@@ -8121,24 +8117,24 @@
       </c>
       <c r="J82" s="28" t="inlineStr">
         <is>
-          <t>Aadit Joshi</t>
+          <t>Anuj Shah</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="27" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="B83" s="27" t="inlineStr">
         <is>
-          <t>8:00AM</t>
+          <t>7:10PM</t>
         </is>
       </c>
       <c r="C83" s="27" t="inlineStr">
         <is>
-          <t>8:15AM</t>
+          <t>7:25PM</t>
         </is>
       </c>
       <c r="D83" s="27" t="inlineStr">
@@ -8151,17 +8147,17 @@
       </c>
       <c r="F83" s="27" t="inlineStr">
         <is>
-          <t>U46-GB-6</t>
+          <t>U46-GA-5</t>
         </is>
       </c>
       <c r="G83" s="27" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H83" s="27" t="inlineStr">
         <is>
-          <t>Mukul Joshi</t>
+          <t>Ankur Mahante</t>
         </is>
       </c>
       <c r="I83" s="27" t="inlineStr">
@@ -8171,29 +8167,29 @@
       </c>
       <c r="J83" s="27" t="inlineStr">
         <is>
-          <t>Adil Khan</t>
+          <t>Sudip Parui</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="28" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="B84" s="28" t="inlineStr">
         <is>
-          <t>8:00AM</t>
+          <t>7:35PM</t>
         </is>
       </c>
       <c r="C84" s="28" t="inlineStr">
         <is>
-          <t>8:15AM</t>
+          <t>7:50PM</t>
         </is>
       </c>
       <c r="D84" s="28" t="inlineStr">
         <is>
-          <t>Under 15</t>
+          <t>Under 46</t>
         </is>
       </c>
       <c r="E84" s="28" t="n">
@@ -8201,17 +8197,17 @@
       </c>
       <c r="F84" s="28" t="inlineStr">
         <is>
-          <t>U15-GA-3</t>
+          <t>U46-GA-7</t>
         </is>
       </c>
       <c r="G84" s="28" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H84" s="28" t="inlineStr">
         <is>
-          <t>Parth yadav</t>
+          <t>Ankur Mahante</t>
         </is>
       </c>
       <c r="I84" s="28" t="inlineStr">
@@ -8221,29 +8217,29 @@
       </c>
       <c r="J84" s="28" t="inlineStr">
         <is>
-          <t>Aadit Joshi</t>
+          <t>Anuj Shah</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="27" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="B85" s="27" t="inlineStr">
         <is>
-          <t>8:15AM</t>
+          <t>7:40PM</t>
         </is>
       </c>
       <c r="C85" s="27" t="inlineStr">
         <is>
-          <t>8:30AM</t>
+          <t>7:55PM</t>
         </is>
       </c>
       <c r="D85" s="27" t="inlineStr">
         <is>
-          <t>Under 46</t>
+          <t>Under 26</t>
         </is>
       </c>
       <c r="E85" s="27" t="n">
@@ -8251,17 +8247,17 @@
       </c>
       <c r="F85" s="27" t="inlineStr">
         <is>
-          <t>U46-GA-5</t>
+          <t>U26-10</t>
         </is>
       </c>
       <c r="G85" s="27" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H85" s="27" t="inlineStr">
         <is>
-          <t>Piyush Makharia</t>
+          <t>Pranit Shriyan</t>
         </is>
       </c>
       <c r="I85" s="27" t="inlineStr">
@@ -8271,24 +8267,24 @@
       </c>
       <c r="J85" s="27" t="inlineStr">
         <is>
-          <t>Vinit Padia</t>
+          <t>Rahul Garg</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="28" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="B86" s="28" t="inlineStr">
         <is>
-          <t>8:40AM</t>
+          <t>7:50PM</t>
         </is>
       </c>
       <c r="C86" s="28" t="inlineStr">
         <is>
-          <t>8:55AM</t>
+          <t>8:05PM</t>
         </is>
       </c>
       <c r="D86" s="28" t="inlineStr">
@@ -8301,7 +8297,7 @@
       </c>
       <c r="F86" s="28" t="inlineStr">
         <is>
-          <t>U46-GA-6</t>
+          <t>U46-GB-9</t>
         </is>
       </c>
       <c r="G86" s="28" t="inlineStr">
@@ -8311,7 +8307,7 @@
       </c>
       <c r="H86" s="28" t="inlineStr">
         <is>
-          <t>Anuj Shah</t>
+          <t>Vinit Padia</t>
         </is>
       </c>
       <c r="I86" s="28" t="inlineStr">
@@ -8321,29 +8317,29 @@
       </c>
       <c r="J86" s="28" t="inlineStr">
         <is>
-          <t>Piyush Makharia</t>
+          <t>Amit Ranka</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="27" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="B87" s="27" t="inlineStr">
         <is>
-          <t>8:40AM</t>
+          <t>8:00PM</t>
         </is>
       </c>
       <c r="C87" s="27" t="inlineStr">
         <is>
-          <t>8:55AM</t>
+          <t>8:15PM</t>
         </is>
       </c>
       <c r="D87" s="27" t="inlineStr">
         <is>
-          <t>Under 46</t>
+          <t>Under 36</t>
         </is>
       </c>
       <c r="E87" s="27" t="n">
@@ -8351,7 +8347,7 @@
       </c>
       <c r="F87" s="27" t="inlineStr">
         <is>
-          <t>U46-GA-7</t>
+          <t>U36-GB-2</t>
         </is>
       </c>
       <c r="G87" s="27" t="inlineStr">
@@ -8361,7 +8357,7 @@
       </c>
       <c r="H87" s="27" t="inlineStr">
         <is>
-          <t>Nikunj Jhala</t>
+          <t>Prakshal Shah</t>
         </is>
       </c>
       <c r="I87" s="27" t="inlineStr">
@@ -8371,29 +8367,29 @@
       </c>
       <c r="J87" s="27" t="inlineStr">
         <is>
-          <t>Vinit Padia</t>
+          <t>Tej</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="28" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="B88" s="28" t="inlineStr">
         <is>
-          <t>9:05AM</t>
+          <t>8:05PM</t>
         </is>
       </c>
       <c r="C88" s="28" t="inlineStr">
         <is>
-          <t>9:20AM</t>
+          <t>8:20PM</t>
         </is>
       </c>
       <c r="D88" s="28" t="inlineStr">
         <is>
-          <t>Under 46</t>
+          <t>Under 26</t>
         </is>
       </c>
       <c r="E88" s="28" t="n">
@@ -8401,7 +8397,7 @@
       </c>
       <c r="F88" s="28" t="inlineStr">
         <is>
-          <t>U46-GA-8</t>
+          <t>U26-7</t>
         </is>
       </c>
       <c r="G88" s="28" t="inlineStr">
@@ -8411,7 +8407,7 @@
       </c>
       <c r="H88" s="28" t="inlineStr">
         <is>
-          <t>Nikunj Jhala</t>
+          <t>Aaditya Kumar</t>
         </is>
       </c>
       <c r="I88" s="28" t="inlineStr">
@@ -8421,24 +8417,24 @@
       </c>
       <c r="J88" s="28" t="inlineStr">
         <is>
-          <t>Piyush Makharia</t>
+          <t>Rahul Garg</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="27" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="B89" s="27" t="inlineStr">
         <is>
-          <t>9:05AM</t>
+          <t>8:15PM</t>
         </is>
       </c>
       <c r="C89" s="27" t="inlineStr">
         <is>
-          <t>9:20AM</t>
+          <t>8:30PM</t>
         </is>
       </c>
       <c r="D89" s="27" t="inlineStr">
@@ -8451,7 +8447,7 @@
       </c>
       <c r="F89" s="27" t="inlineStr">
         <is>
-          <t>U46-GA-9</t>
+          <t>U46-GA-3</t>
         </is>
       </c>
       <c r="G89" s="27" t="inlineStr">
@@ -8461,7 +8457,7 @@
       </c>
       <c r="H89" s="27" t="inlineStr">
         <is>
-          <t>Anuj Shah</t>
+          <t>Dr Rahul Modi</t>
         </is>
       </c>
       <c r="I89" s="27" t="inlineStr">
@@ -8471,29 +8467,29 @@
       </c>
       <c r="J89" s="27" t="inlineStr">
         <is>
-          <t>Vinit Padia</t>
+          <t>Tanmay Sharma</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="28" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="B90" s="28" t="inlineStr">
         <is>
-          <t>9:20AM</t>
+          <t>8:20PM</t>
         </is>
       </c>
       <c r="C90" s="28" t="inlineStr">
         <is>
-          <t>9:35AM</t>
+          <t>8:35PM</t>
         </is>
       </c>
       <c r="D90" s="28" t="inlineStr">
         <is>
-          <t>Under 15</t>
+          <t>Under 46</t>
         </is>
       </c>
       <c r="E90" s="28" t="n">
@@ -8501,17 +8497,17 @@
       </c>
       <c r="F90" s="28" t="inlineStr">
         <is>
-          <t>U15-GB-2</t>
+          <t>U46-GA-9</t>
         </is>
       </c>
       <c r="G90" s="28" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H90" s="28" t="inlineStr">
         <is>
-          <t>Viaan Neema</t>
+          <t>Sudip Parui</t>
         </is>
       </c>
       <c r="I90" s="28" t="inlineStr">
@@ -8521,29 +8517,29 @@
       </c>
       <c r="J90" s="28" t="inlineStr">
         <is>
-          <t>Hridh jhala</t>
+          <t>Anuj Shah</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="27" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="B91" s="27" t="inlineStr">
         <is>
-          <t>9:30AM</t>
+          <t>8:30PM</t>
         </is>
       </c>
       <c r="C91" s="27" t="inlineStr">
         <is>
-          <t>9:45AM</t>
+          <t>8:45PM</t>
         </is>
       </c>
       <c r="D91" s="27" t="inlineStr">
         <is>
-          <t>Under 46</t>
+          <t>Under 36</t>
         </is>
       </c>
       <c r="E91" s="27" t="n">
@@ -8551,17 +8547,17 @@
       </c>
       <c r="F91" s="27" t="inlineStr">
         <is>
-          <t>U46-GA-10</t>
+          <t>U36-GB-3</t>
         </is>
       </c>
       <c r="G91" s="27" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H91" s="27" t="inlineStr">
         <is>
-          <t>Piyush Makharia</t>
+          <t>Amar Parulekar</t>
         </is>
       </c>
       <c r="I91" s="27" t="inlineStr">
@@ -8571,29 +8567,29 @@
       </c>
       <c r="J91" s="27" t="inlineStr">
         <is>
-          <t>Nilesh Bagaria</t>
+          <t>Tej</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="28" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="B92" s="28" t="inlineStr">
         <is>
-          <t>9:35AM</t>
+          <t>8:35PM</t>
         </is>
       </c>
       <c r="C92" s="28" t="inlineStr">
         <is>
-          <t>9:50AM</t>
+          <t>8:50PM</t>
         </is>
       </c>
       <c r="D92" s="28" t="inlineStr">
         <is>
-          <t>Under 32</t>
+          <t>Under 46</t>
         </is>
       </c>
       <c r="E92" s="28" t="n">
@@ -8601,17 +8597,17 @@
       </c>
       <c r="F92" s="28" t="inlineStr">
         <is>
-          <t>U32-1</t>
+          <t>U46-GB-3</t>
         </is>
       </c>
       <c r="G92" s="28" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H92" s="28" t="inlineStr">
         <is>
-          <t>Yuvraj jain</t>
+          <t>Nikunj Jhala</t>
         </is>
       </c>
       <c r="I92" s="28" t="inlineStr">
@@ -8621,29 +8617,29 @@
       </c>
       <c r="J92" s="28" t="inlineStr">
         <is>
-          <t>Aaditya Kumar</t>
+          <t>Nilesh Bagaria</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="27" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="B93" s="27" t="inlineStr">
         <is>
-          <t>9:45AM</t>
+          <t>8:45PM</t>
         </is>
       </c>
       <c r="C93" s="27" t="inlineStr">
         <is>
-          <t>10:00AM</t>
+          <t>9:00PM</t>
         </is>
       </c>
       <c r="D93" s="27" t="inlineStr">
         <is>
-          <t>Under 15</t>
+          <t>Under 46</t>
         </is>
       </c>
       <c r="E93" s="27" t="n">
@@ -8651,17 +8647,17 @@
       </c>
       <c r="F93" s="27" t="inlineStr">
         <is>
-          <t>U15-GB-3</t>
+          <t>U46-GA-8</t>
         </is>
       </c>
       <c r="G93" s="27" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H93" s="27" t="inlineStr">
         <is>
-          <t>Yash agarwal</t>
+          <t>Sudip Parui</t>
         </is>
       </c>
       <c r="I93" s="27" t="inlineStr">
@@ -8671,29 +8667,29 @@
       </c>
       <c r="J93" s="27" t="inlineStr">
         <is>
-          <t>Hridh jhala</t>
+          <t>Tanmay Sharma</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="28" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="B94" s="28" t="inlineStr">
         <is>
-          <t>10:00AM</t>
+          <t>9:00PM</t>
         </is>
       </c>
       <c r="C94" s="28" t="inlineStr">
         <is>
-          <t>10:15AM</t>
+          <t>9:15PM</t>
         </is>
       </c>
       <c r="D94" s="28" t="inlineStr">
         <is>
-          <t>Under 32</t>
+          <t>Under 46</t>
         </is>
       </c>
       <c r="E94" s="28" t="n">
@@ -8701,7 +8697,7 @@
       </c>
       <c r="F94" s="28" t="inlineStr">
         <is>
-          <t>U32-3</t>
+          <t>U46-GB-4</t>
         </is>
       </c>
       <c r="G94" s="28" t="inlineStr">
@@ -8711,7 +8707,7 @@
       </c>
       <c r="H94" s="28" t="inlineStr">
         <is>
-          <t>Hryday Goyal</t>
+          <t>Nikunj Jhala</t>
         </is>
       </c>
       <c r="I94" s="28" t="inlineStr">
@@ -8721,29 +8717,29 @@
       </c>
       <c r="J94" s="28" t="inlineStr">
         <is>
-          <t>Pranit Shriyan</t>
+          <t>Amit Ranka</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="27" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="B95" s="27" t="inlineStr">
         <is>
-          <t>10:00AM</t>
+          <t>9:10PM</t>
         </is>
       </c>
       <c r="C95" s="27" t="inlineStr">
         <is>
-          <t>10:15AM</t>
+          <t>9:25PM</t>
         </is>
       </c>
       <c r="D95" s="27" t="inlineStr">
         <is>
-          <t>Under 32</t>
+          <t>Under 26</t>
         </is>
       </c>
       <c r="E95" s="27" t="n">
@@ -8751,7 +8747,7 @@
       </c>
       <c r="F95" s="27" t="inlineStr">
         <is>
-          <t>U32-2</t>
+          <t>U26-9</t>
         </is>
       </c>
       <c r="G95" s="27" t="inlineStr">
@@ -8761,7 +8757,7 @@
       </c>
       <c r="H95" s="27" t="inlineStr">
         <is>
-          <t>Yuvraj jain</t>
+          <t>Hryday Goyal</t>
         </is>
       </c>
       <c r="I95" s="27" t="inlineStr">
@@ -8778,22 +8774,22 @@
     <row r="96">
       <c r="A96" s="28" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="B96" s="28" t="inlineStr">
         <is>
-          <t>10:25AM</t>
+          <t>9:15PM</t>
         </is>
       </c>
       <c r="C96" s="28" t="inlineStr">
         <is>
-          <t>10:40AM</t>
+          <t>9:30PM</t>
         </is>
       </c>
       <c r="D96" s="28" t="inlineStr">
         <is>
-          <t>Under 32</t>
+          <t>Under 46</t>
         </is>
       </c>
       <c r="E96" s="28" t="n">
@@ -8801,17 +8797,17 @@
       </c>
       <c r="F96" s="28" t="inlineStr">
         <is>
-          <t>U32-4</t>
+          <t>U46-GA-10</t>
         </is>
       </c>
       <c r="G96" s="28" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H96" s="28" t="inlineStr">
         <is>
-          <t>Yuvraj jain</t>
+          <t>Tanmay Sharma</t>
         </is>
       </c>
       <c r="I96" s="28" t="inlineStr">
@@ -8821,29 +8817,29 @@
       </c>
       <c r="J96" s="28" t="inlineStr">
         <is>
-          <t>Hryday Goyal</t>
+          <t>Anuj Shah</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="27" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="B97" s="27" t="inlineStr">
         <is>
-          <t>10:40AM</t>
+          <t>9:25PM</t>
         </is>
       </c>
       <c r="C97" s="27" t="inlineStr">
         <is>
-          <t>10:55AM</t>
+          <t>9:40PM</t>
         </is>
       </c>
       <c r="D97" s="27" t="inlineStr">
         <is>
-          <t>Under 32</t>
+          <t>Under 46</t>
         </is>
       </c>
       <c r="E97" s="27" t="n">
@@ -8851,7 +8847,7 @@
       </c>
       <c r="F97" s="27" t="inlineStr">
         <is>
-          <t>U32-5</t>
+          <t>U46-GB-10</t>
         </is>
       </c>
       <c r="G97" s="27" t="inlineStr">
@@ -8861,7 +8857,7 @@
       </c>
       <c r="H97" s="27" t="inlineStr">
         <is>
-          <t>Aaditya Kumar</t>
+          <t>Nilesh Bagaria</t>
         </is>
       </c>
       <c r="I97" s="27" t="inlineStr">
@@ -8871,7 +8867,7 @@
       </c>
       <c r="J97" s="27" t="inlineStr">
         <is>
-          <t>Pranit Shriyan</t>
+          <t>Amit Ranka</t>
         </is>
       </c>
     </row>
@@ -8883,17 +8879,17 @@
       </c>
       <c r="B98" s="28" t="inlineStr">
         <is>
-          <t>10:50AM</t>
+          <t>8:00AM</t>
         </is>
       </c>
       <c r="C98" s="28" t="inlineStr">
         <is>
-          <t>11:05AM</t>
+          <t>8:15AM</t>
         </is>
       </c>
       <c r="D98" s="28" t="inlineStr">
         <is>
-          <t>Under 32</t>
+          <t>Under 46</t>
         </is>
       </c>
       <c r="E98" s="28" t="n">
@@ -8901,7 +8897,7 @@
       </c>
       <c r="F98" s="28" t="inlineStr">
         <is>
-          <t>U32-6</t>
+          <t>U46-GB-1</t>
         </is>
       </c>
       <c r="G98" s="28" t="inlineStr">
@@ -8911,7 +8907,7 @@
       </c>
       <c r="H98" s="28" t="inlineStr">
         <is>
-          <t>Hryday Goyal</t>
+          <t>Nikunj Jhala</t>
         </is>
       </c>
       <c r="I98" s="28" t="inlineStr">
@@ -8921,7 +8917,7 @@
       </c>
       <c r="J98" s="28" t="inlineStr">
         <is>
-          <t>Rahul Garg</t>
+          <t>Piyush Makharia</t>
         </is>
       </c>
     </row>
@@ -8933,17 +8929,17 @@
       </c>
       <c r="B99" s="27" t="inlineStr">
         <is>
-          <t>11:05AM</t>
+          <t>8:25AM</t>
         </is>
       </c>
       <c r="C99" s="27" t="inlineStr">
         <is>
-          <t>11:20AM</t>
+          <t>8:40AM</t>
         </is>
       </c>
       <c r="D99" s="27" t="inlineStr">
         <is>
-          <t>Under 32</t>
+          <t>Under 46</t>
         </is>
       </c>
       <c r="E99" s="27" t="n">
@@ -8951,17 +8947,17 @@
       </c>
       <c r="F99" s="27" t="inlineStr">
         <is>
-          <t>U32-7</t>
+          <t>U46-GB-2</t>
         </is>
       </c>
       <c r="G99" s="27" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H99" s="27" t="inlineStr">
         <is>
-          <t>Yuvraj jain</t>
+          <t>Nikunj Jhala</t>
         </is>
       </c>
       <c r="I99" s="27" t="inlineStr">
@@ -8971,7 +8967,7 @@
       </c>
       <c r="J99" s="27" t="inlineStr">
         <is>
-          <t>Pranit Shriyan</t>
+          <t>Vinit Padia</t>
         </is>
       </c>
     </row>
@@ -8983,17 +8979,17 @@
       </c>
       <c r="B100" s="28" t="inlineStr">
         <is>
-          <t>11:15AM</t>
+          <t>8:25AM</t>
         </is>
       </c>
       <c r="C100" s="28" t="inlineStr">
         <is>
-          <t>11:30AM</t>
+          <t>8:40AM</t>
         </is>
       </c>
       <c r="D100" s="28" t="inlineStr">
         <is>
-          <t>Under 32</t>
+          <t>Under 46</t>
         </is>
       </c>
       <c r="E100" s="28" t="n">
@@ -9001,17 +8997,17 @@
       </c>
       <c r="F100" s="28" t="inlineStr">
         <is>
-          <t>U32-8</t>
+          <t>U46-GB-6</t>
         </is>
       </c>
       <c r="G100" s="28" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H100" s="28" t="inlineStr">
         <is>
-          <t>Aaditya Kumar</t>
+          <t>Piyush Makharia</t>
         </is>
       </c>
       <c r="I100" s="28" t="inlineStr">
@@ -9021,7 +9017,7 @@
       </c>
       <c r="J100" s="28" t="inlineStr">
         <is>
-          <t>Rahul Garg</t>
+          <t>Nilesh Bagaria</t>
         </is>
       </c>
     </row>
@@ -9033,17 +9029,17 @@
       </c>
       <c r="B101" s="27" t="inlineStr">
         <is>
-          <t>11:40AM</t>
+          <t>8:50AM</t>
         </is>
       </c>
       <c r="C101" s="27" t="inlineStr">
         <is>
-          <t>11:55AM</t>
+          <t>9:05AM</t>
         </is>
       </c>
       <c r="D101" s="27" t="inlineStr">
         <is>
-          <t>Under 32</t>
+          <t>Under 46</t>
         </is>
       </c>
       <c r="E101" s="27" t="n">
@@ -9051,7 +9047,7 @@
       </c>
       <c r="F101" s="27" t="inlineStr">
         <is>
-          <t>U32-10</t>
+          <t>U46-GB-5</t>
         </is>
       </c>
       <c r="G101" s="27" t="inlineStr">
@@ -9061,7 +9057,7 @@
       </c>
       <c r="H101" s="27" t="inlineStr">
         <is>
-          <t>Aaditya Kumar</t>
+          <t>Piyush Makharia</t>
         </is>
       </c>
       <c r="I101" s="27" t="inlineStr">
@@ -9071,7 +9067,7 @@
       </c>
       <c r="J101" s="27" t="inlineStr">
         <is>
-          <t>Hryday Goyal</t>
+          <t>Vinit Padia</t>
         </is>
       </c>
     </row>
@@ -9083,17 +9079,17 @@
       </c>
       <c r="B102" s="28" t="inlineStr">
         <is>
-          <t>11:40AM</t>
+          <t>9:15AM</t>
         </is>
       </c>
       <c r="C102" s="28" t="inlineStr">
         <is>
-          <t>11:55AM</t>
+          <t>9:30AM</t>
         </is>
       </c>
       <c r="D102" s="28" t="inlineStr">
         <is>
-          <t>Under 32</t>
+          <t>Under 46</t>
         </is>
       </c>
       <c r="E102" s="28" t="n">
@@ -9101,17 +9097,17 @@
       </c>
       <c r="F102" s="28" t="inlineStr">
         <is>
-          <t>U32-9</t>
+          <t>U46-GB-7</t>
         </is>
       </c>
       <c r="G102" s="28" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H102" s="28" t="inlineStr">
         <is>
-          <t>Pranit Shriyan</t>
+          <t>Piyush Makharia</t>
         </is>
       </c>
       <c r="I102" s="28" t="inlineStr">
@@ -9121,7 +9117,7 @@
       </c>
       <c r="J102" s="28" t="inlineStr">
         <is>
-          <t>Rahul Garg</t>
+          <t>Amit Ranka</t>
         </is>
       </c>
     </row>
@@ -9133,17 +9129,17 @@
       </c>
       <c r="B103" s="27" t="inlineStr">
         <is>
-          <t>3:20PM</t>
+          <t>3:50PM</t>
         </is>
       </c>
       <c r="C103" s="27" t="inlineStr">
         <is>
-          <t>3:35PM</t>
+          <t>4:05PM</t>
         </is>
       </c>
       <c r="D103" s="27" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Under 15</t>
         </is>
       </c>
       <c r="E103" s="27" t="n">
@@ -9151,7 +9147,7 @@
       </c>
       <c r="F103" s="27" t="inlineStr">
         <is>
-          <t>SR-SF1</t>
+          <t>U15-SF1</t>
         </is>
       </c>
       <c r="G103" s="27" t="inlineStr">
@@ -9183,17 +9179,17 @@
       </c>
       <c r="B104" s="28" t="inlineStr">
         <is>
-          <t>3:35PM</t>
+          <t>4:00PM</t>
         </is>
       </c>
       <c r="C104" s="28" t="inlineStr">
         <is>
-          <t>3:50PM</t>
+          <t>4:15PM</t>
         </is>
       </c>
       <c r="D104" s="28" t="inlineStr">
         <is>
-          <t>Under 46</t>
+          <t>Under 15</t>
         </is>
       </c>
       <c r="E104" s="28" t="n">
@@ -9201,17 +9197,17 @@
       </c>
       <c r="F104" s="28" t="inlineStr">
         <is>
-          <t>U46-SF1</t>
+          <t>U15-SF2</t>
         </is>
       </c>
       <c r="G104" s="28" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H104" s="28" t="inlineStr">
         <is>
-          <t>Group B 1st</t>
+          <t>Group A 1st</t>
         </is>
       </c>
       <c r="I104" s="28" t="inlineStr">
@@ -9221,7 +9217,7 @@
       </c>
       <c r="J104" s="28" t="inlineStr">
         <is>
-          <t>Group A 2nd</t>
+          <t>Group B 2nd</t>
         </is>
       </c>
     </row>
@@ -9233,17 +9229,17 @@
       </c>
       <c r="B105" s="27" t="inlineStr">
         <is>
-          <t>3:50PM</t>
+          <t>4:15PM</t>
         </is>
       </c>
       <c r="C105" s="27" t="inlineStr">
         <is>
-          <t>4:05PM</t>
+          <t>4:30PM</t>
         </is>
       </c>
       <c r="D105" s="27" t="inlineStr">
         <is>
-          <t>Under 36</t>
+          <t>Under 26</t>
         </is>
       </c>
       <c r="E105" s="27" t="n">
@@ -9251,17 +9247,17 @@
       </c>
       <c r="F105" s="27" t="inlineStr">
         <is>
-          <t>U36-SF1</t>
+          <t>U26-FINAL</t>
         </is>
       </c>
       <c r="G105" s="27" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H105" s="27" t="inlineStr">
         <is>
-          <t>Group B 1st</t>
+          <t>Pool 1st</t>
         </is>
       </c>
       <c r="I105" s="27" t="inlineStr">
@@ -9271,7 +9267,7 @@
       </c>
       <c r="J105" s="27" t="inlineStr">
         <is>
-          <t>Group A 2nd</t>
+          <t>Pool 2nd</t>
         </is>
       </c>
     </row>
@@ -9283,17 +9279,17 @@
       </c>
       <c r="B106" s="28" t="inlineStr">
         <is>
-          <t>4:00PM</t>
+          <t>4:24PM</t>
         </is>
       </c>
       <c r="C106" s="28" t="inlineStr">
         <is>
-          <t>4:15PM</t>
+          <t>4:39PM</t>
         </is>
       </c>
       <c r="D106" s="28" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Under 36</t>
         </is>
       </c>
       <c r="E106" s="28" t="n">
@@ -9301,17 +9297,17 @@
       </c>
       <c r="F106" s="28" t="inlineStr">
         <is>
-          <t>SR-SF2</t>
+          <t>U36-SF1</t>
         </is>
       </c>
       <c r="G106" s="28" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H106" s="28" t="inlineStr">
         <is>
-          <t>Group A 1st</t>
+          <t>Group B 1st</t>
         </is>
       </c>
       <c r="I106" s="28" t="inlineStr">
@@ -9321,7 +9317,7 @@
       </c>
       <c r="J106" s="28" t="inlineStr">
         <is>
-          <t>Group B 2nd</t>
+          <t>Group A 2nd</t>
         </is>
       </c>
     </row>
@@ -9333,17 +9329,17 @@
       </c>
       <c r="B107" s="27" t="inlineStr">
         <is>
-          <t>4:05PM</t>
+          <t>4:30PM</t>
         </is>
       </c>
       <c r="C107" s="27" t="inlineStr">
         <is>
-          <t>4:20PM</t>
+          <t>4:45PM</t>
         </is>
       </c>
       <c r="D107" s="27" t="inlineStr">
         <is>
-          <t>Under 32</t>
+          <t>Under 15</t>
         </is>
       </c>
       <c r="E107" s="27" t="n">
@@ -9351,17 +9347,17 @@
       </c>
       <c r="F107" s="27" t="inlineStr">
         <is>
-          <t>U32-FINAL</t>
+          <t>U15-FINAL</t>
         </is>
       </c>
       <c r="G107" s="27" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H107" s="27" t="inlineStr">
         <is>
-          <t>Pool 1st</t>
+          <t>Winner SF1</t>
         </is>
       </c>
       <c r="I107" s="27" t="inlineStr">
@@ -9371,7 +9367,7 @@
       </c>
       <c r="J107" s="27" t="inlineStr">
         <is>
-          <t>Pool 2nd</t>
+          <t>Winner SF2</t>
         </is>
       </c>
     </row>
@@ -9383,17 +9379,17 @@
       </c>
       <c r="B108" s="28" t="inlineStr">
         <is>
-          <t>4:15PM</t>
+          <t>4:39PM</t>
         </is>
       </c>
       <c r="C108" s="28" t="inlineStr">
         <is>
-          <t>4:30PM</t>
+          <t>4:54PM</t>
         </is>
       </c>
       <c r="D108" s="28" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Under 36</t>
         </is>
       </c>
       <c r="E108" s="28" t="n">
@@ -9401,17 +9397,17 @@
       </c>
       <c r="F108" s="28" t="inlineStr">
         <is>
-          <t>SR-FINAL</t>
+          <t>U36-SF2</t>
         </is>
       </c>
       <c r="G108" s="28" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H108" s="28" t="inlineStr">
         <is>
-          <t>Winner SF1</t>
+          <t>Group A 1st</t>
         </is>
       </c>
       <c r="I108" s="28" t="inlineStr">
@@ -9421,7 +9417,7 @@
       </c>
       <c r="J108" s="28" t="inlineStr">
         <is>
-          <t>Winner SF2</t>
+          <t>Group B 2nd</t>
         </is>
       </c>
     </row>
@@ -9433,17 +9429,17 @@
       </c>
       <c r="B109" s="27" t="inlineStr">
         <is>
-          <t>4:20PM</t>
+          <t>5:04PM</t>
         </is>
       </c>
       <c r="C109" s="27" t="inlineStr">
         <is>
-          <t>4:35PM</t>
+          <t>5:19PM</t>
         </is>
       </c>
       <c r="D109" s="27" t="inlineStr">
         <is>
-          <t>Under 15</t>
+          <t>Under 36</t>
         </is>
       </c>
       <c r="E109" s="27" t="n">
@@ -9451,17 +9447,17 @@
       </c>
       <c r="F109" s="27" t="inlineStr">
         <is>
-          <t>U15-SF1</t>
+          <t>U36-FINAL</t>
         </is>
       </c>
       <c r="G109" s="27" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H109" s="27" t="inlineStr">
         <is>
-          <t>Group B 1st</t>
+          <t>Winner SF1</t>
         </is>
       </c>
       <c r="I109" s="27" t="inlineStr">
@@ -9471,7 +9467,7 @@
       </c>
       <c r="J109" s="27" t="inlineStr">
         <is>
-          <t>Group A 2nd</t>
+          <t>Winner SF2</t>
         </is>
       </c>
     </row>
@@ -9483,12 +9479,12 @@
       </c>
       <c r="B110" s="28" t="inlineStr">
         <is>
-          <t>4:30PM</t>
+          <t>5:10PM</t>
         </is>
       </c>
       <c r="C110" s="28" t="inlineStr">
         <is>
-          <t>4:45PM</t>
+          <t>5:25PM</t>
         </is>
       </c>
       <c r="D110" s="28" t="inlineStr">
@@ -9501,17 +9497,17 @@
       </c>
       <c r="F110" s="28" t="inlineStr">
         <is>
-          <t>U46-SF2</t>
+          <t>U46-SF1</t>
         </is>
       </c>
       <c r="G110" s="28" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H110" s="28" t="inlineStr">
         <is>
-          <t>Group A 1st</t>
+          <t>Group B 1st</t>
         </is>
       </c>
       <c r="I110" s="28" t="inlineStr">
@@ -9521,7 +9517,7 @@
       </c>
       <c r="J110" s="28" t="inlineStr">
         <is>
-          <t>Group B 2nd</t>
+          <t>Group A 2nd</t>
         </is>
       </c>
     </row>
@@ -9533,17 +9529,17 @@
       </c>
       <c r="B111" s="27" t="inlineStr">
         <is>
-          <t>4:45PM</t>
+          <t>5:19PM</t>
         </is>
       </c>
       <c r="C111" s="27" t="inlineStr">
         <is>
-          <t>5:00PM</t>
+          <t>5:34PM</t>
         </is>
       </c>
       <c r="D111" s="27" t="inlineStr">
         <is>
-          <t>Under 36</t>
+          <t>Under 46</t>
         </is>
       </c>
       <c r="E111" s="27" t="n">
@@ -9551,7 +9547,7 @@
       </c>
       <c r="F111" s="27" t="inlineStr">
         <is>
-          <t>U36-SF2</t>
+          <t>U46-SF2</t>
         </is>
       </c>
       <c r="G111" s="27" t="inlineStr">
@@ -9583,17 +9579,17 @@
       </c>
       <c r="B112" s="28" t="inlineStr">
         <is>
-          <t>5:00PM</t>
+          <t>5:25PM</t>
         </is>
       </c>
       <c r="C112" s="28" t="inlineStr">
         <is>
-          <t>5:15PM</t>
+          <t>5:40PM</t>
         </is>
       </c>
       <c r="D112" s="28" t="inlineStr">
         <is>
-          <t>Under 36</t>
+          <t>Above 46</t>
         </is>
       </c>
       <c r="E112" s="28" t="n">
@@ -9601,17 +9597,17 @@
       </c>
       <c r="F112" s="28" t="inlineStr">
         <is>
-          <t>U36-FINAL</t>
+          <t>A46-SF1</t>
         </is>
       </c>
       <c r="G112" s="28" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H112" s="28" t="inlineStr">
         <is>
-          <t>Winner SF1</t>
+          <t>Group B 1st</t>
         </is>
       </c>
       <c r="I112" s="28" t="inlineStr">
@@ -9621,7 +9617,7 @@
       </c>
       <c r="J112" s="28" t="inlineStr">
         <is>
-          <t>Winner SF2</t>
+          <t>Group A 2nd</t>
         </is>
       </c>
     </row>
@@ -9633,17 +9629,17 @@
       </c>
       <c r="B113" s="27" t="inlineStr">
         <is>
-          <t>5:15PM</t>
+          <t>5:34PM</t>
         </is>
       </c>
       <c r="C113" s="27" t="inlineStr">
         <is>
-          <t>5:30PM</t>
+          <t>5:49PM</t>
         </is>
       </c>
       <c r="D113" s="27" t="inlineStr">
         <is>
-          <t>Under 15</t>
+          <t>Above 46</t>
         </is>
       </c>
       <c r="E113" s="27" t="n">
@@ -9651,7 +9647,7 @@
       </c>
       <c r="F113" s="27" t="inlineStr">
         <is>
-          <t>U15-SF2</t>
+          <t>A46-SF2</t>
         </is>
       </c>
       <c r="G113" s="27" t="inlineStr">
@@ -9683,12 +9679,12 @@
       </c>
       <c r="B114" s="28" t="inlineStr">
         <is>
-          <t>5:30PM</t>
+          <t>5:44PM</t>
         </is>
       </c>
       <c r="C114" s="28" t="inlineStr">
         <is>
-          <t>5:45PM</t>
+          <t>5:59PM</t>
         </is>
       </c>
       <c r="D114" s="28" t="inlineStr">
@@ -9706,7 +9702,7 @@
       </c>
       <c r="G114" s="28" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H114" s="28" t="inlineStr">
@@ -9733,17 +9729,17 @@
       </c>
       <c r="B115" s="27" t="inlineStr">
         <is>
-          <t>5:30PM</t>
+          <t>5:59PM</t>
         </is>
       </c>
       <c r="C115" s="27" t="inlineStr">
         <is>
-          <t>5:45PM</t>
+          <t>6:14PM</t>
         </is>
       </c>
       <c r="D115" s="27" t="inlineStr">
         <is>
-          <t>Under 15</t>
+          <t>Above 46</t>
         </is>
       </c>
       <c r="E115" s="27" t="n">
@@ -9751,12 +9747,12 @@
       </c>
       <c r="F115" s="27" t="inlineStr">
         <is>
-          <t>U15-FINAL</t>
+          <t>A46-FINAL</t>
         </is>
       </c>
       <c r="G115" s="27" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H115" s="27" t="inlineStr">
@@ -9779,20 +9775,20 @@
   <mergeCells count="17">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A36:J36"/>
     <mergeCell ref="D7:E7"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="D37:E37"/>
-    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="A34:J34"/>
     <mergeCell ref="A12:J12"/>
     <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A43:J43"/>
     <mergeCell ref="A20:J20"/>
-    <mergeCell ref="A43:J43"/>
     <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A28:J28"/>
+    <mergeCell ref="A26:J26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="D35:E35"/>
     <mergeCell ref="D21:E21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9834,7 +9830,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="20.1" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
@@ -9842,7 +9837,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6" ht="17.1" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
         <is>
@@ -9942,8 +9936,6 @@
         <v>45</v>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17"/>
     <row r="18" ht="20.1" customHeight="1">
       <c r="A18" s="16" t="inlineStr">
         <is>
@@ -10408,7 +10400,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6" ht="17.1" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
         <is>
@@ -10458,7 +10449,6 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11"/>
     <row r="12" ht="17.1" customHeight="1">
       <c r="A12" s="24" t="inlineStr">
         <is>
@@ -10586,7 +10576,6 @@
         <v>45</v>
       </c>
     </row>
-    <row r="20"/>
     <row r="21" ht="17.1" customHeight="1">
       <c r="A21" s="24" t="inlineStr">
         <is>
@@ -10678,8 +10667,6 @@
         <v>65</v>
       </c>
     </row>
-    <row r="27"/>
-    <row r="28"/>
     <row r="29" ht="20.1" customHeight="1">
       <c r="A29" s="16" t="inlineStr">
         <is>
@@ -13400,7 +13387,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6" ht="17.1" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
         <is>
@@ -13470,8 +13456,6 @@
         <v>68</v>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14"/>
     <row r="15" ht="20.1" customHeight="1">
       <c r="A15" s="16" t="inlineStr">
         <is>
@@ -14128,7 +14112,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="20.1" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
@@ -14136,7 +14119,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6" ht="17.1" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
         <is>
@@ -14306,7 +14288,6 @@
         <v>47</v>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="25" t="inlineStr">
         <is>
@@ -14314,7 +14295,6 @@
         </is>
       </c>
     </row>
-    <row r="25"/>
     <row r="26" ht="20.1" customHeight="1">
       <c r="A26" s="16" t="inlineStr">
         <is>
@@ -15122,7 +15102,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="20.1" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
@@ -15130,7 +15109,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6" ht="17.1" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
         <is>
@@ -15240,7 +15218,6 @@
         <v>39</v>
       </c>
     </row>
-    <row r="13"/>
     <row r="14" ht="17.1" customHeight="1">
       <c r="A14" s="24" t="inlineStr">
         <is>
@@ -15350,7 +15327,6 @@
         <v>61</v>
       </c>
     </row>
-    <row r="21"/>
     <row r="22" ht="17.1" customHeight="1">
       <c r="A22" s="24" t="inlineStr">
         <is>
@@ -15442,8 +15418,6 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28"/>
-    <row r="29"/>
     <row r="30" ht="20.1" customHeight="1">
       <c r="A30" s="16" t="inlineStr">
         <is>

--- a/Ekta_Schedule_With_Matchups.xlsx
+++ b/Ekta_Schedule_With_Matchups.xlsx
@@ -26,7 +26,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="25">
+  <fonts count="26">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -161,8 +161,13 @@
       <color rgb="00B45309"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="10.5"/>
+    </font>
   </fonts>
-  <fills count="13">
+  <fills count="17">
     <fill>
       <patternFill/>
     </fill>
@@ -222,6 +227,26 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00334155"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2E8F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00155E75"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F1F5F9"/>
       </patternFill>
     </fill>
   </fills>
@@ -349,7 +374,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -593,6 +618,29 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1194,7 +1242,7 @@
       </c>
       <c r="C15" s="64" t="inlineStr">
         <is>
-          <t>League stage continues. Carrom Women's Singles (done ~11:00 AM) and TT Women's Singles (done ~4:10 PM) each finish in full today — their knockouts run right after their own league stage ends, no waiting for other events.</t>
+          <t>League stage continues. Carrom Women's Singles (done ~11:00 AM) and TT Women's Singles (done ~11:00 AM) each finish in full today — their knockouts run right after their own league stage ends, no waiting for other events.</t>
         </is>
       </c>
       <c r="H15" s="31" t="n"/>
@@ -1234,7 +1282,7 @@
       </c>
       <c r="C17" s="64" t="inlineStr">
         <is>
-          <t>Both Doubles events run once their own players are free — Carrom Doubles 9:30-11:50 AM; TT Doubles now starts 11:55 AM (TT tables are shared with TT Men's Singles, whose league stage runs until then).</t>
+          <t>Both Doubles events run once their own players are free — Carrom Doubles 9:30-11:50 AM; TT Doubles starts 9:05 AM and interleaves with TT Men's Singles on the shared tables, wrapping by 3:45 PM.</t>
         </is>
       </c>
       <c r="H17" s="31" t="n"/>
@@ -1363,12 +1411,12 @@
       </c>
       <c r="D24" s="63" t="inlineStr">
         <is>
-          <t>Aug15 10:30AM</t>
+          <t>Aug15 8:00AM</t>
         </is>
       </c>
       <c r="E24" s="63" t="inlineStr">
         <is>
-          <t>Aug15 4:10PM</t>
+          <t>Aug15 11:00AM</t>
         </is>
       </c>
       <c r="F24" s="31" t="n"/>
@@ -1384,7 +1432,7 @@
         </is>
       </c>
       <c r="B25" s="63" t="n">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="C25" s="63" t="inlineStr">
         <is>
@@ -1393,12 +1441,12 @@
       </c>
       <c r="D25" s="63" t="inlineStr">
         <is>
-          <t>Aug15 8:00AM</t>
+          <t>Aug15 10:45AM</t>
         </is>
       </c>
       <c r="E25" s="63" t="inlineStr">
         <is>
-          <t>Aug16 6:14PM</t>
+          <t>Aug16 4:45PM</t>
         </is>
       </c>
       <c r="F25" s="31" t="n"/>
@@ -1423,12 +1471,12 @@
       </c>
       <c r="D26" s="63" t="inlineStr">
         <is>
-          <t>Aug16 11:55AM</t>
+          <t>Aug16 9:05AM</t>
         </is>
       </c>
       <c r="E26" s="63" t="inlineStr">
         <is>
-          <t>Aug16 4:00PM</t>
+          <t>Aug16 3:45PM</t>
         </is>
       </c>
       <c r="F26" s="31" t="n"/>
@@ -1632,7 +1680,7 @@
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="86" t="inlineStr">
         <is>
-          <t>Overall tournament span: Aug 15, 8:00 AM start → Aug 16, 5:45 PM finish — comfortably inside the Aug 16, 10 PM cap.</t>
+          <t>Overall tournament span: Aug 15, 8:00 AM start → Aug 16, 5:00 PM finish — comfortably inside the Aug 16, 10 PM cap.</t>
         </is>
       </c>
       <c r="F34" s="31" t="n"/>
@@ -4917,750 +4965,750 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="27" t="inlineStr">
+      <c r="A16" s="94" t="inlineStr">
         <is>
           <t>Aug 15</t>
         </is>
       </c>
-      <c r="B16" s="27" t="inlineStr">
+      <c r="B16" s="94" t="inlineStr">
+        <is>
+          <t>8:00AM</t>
+        </is>
+      </c>
+      <c r="C16" s="94" t="inlineStr">
+        <is>
+          <t>8:15AM</t>
+        </is>
+      </c>
+      <c r="D16" s="94" t="inlineStr">
+        <is>
+          <t>TT Womens Singles</t>
+        </is>
+      </c>
+      <c r="E16" s="94" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="94" t="inlineStr">
+        <is>
+          <t>GA-M1</t>
+        </is>
+      </c>
+      <c r="G16" s="94" t="inlineStr">
+        <is>
+          <t>Table 1</t>
+        </is>
+      </c>
+      <c r="H16" s="94" t="inlineStr">
+        <is>
+          <t>Nitika Aggarwal</t>
+        </is>
+      </c>
+      <c r="I16" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J16" s="94" t="inlineStr">
+        <is>
+          <t>Deepali Acharya</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B17" s="95" t="inlineStr">
+        <is>
+          <t>8:00AM</t>
+        </is>
+      </c>
+      <c r="C17" s="95" t="inlineStr">
+        <is>
+          <t>8:15AM</t>
+        </is>
+      </c>
+      <c r="D17" s="95" t="inlineStr">
+        <is>
+          <t>TT Womens Singles</t>
+        </is>
+      </c>
+      <c r="E17" s="95" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" s="95" t="inlineStr">
+        <is>
+          <t>GA-M2</t>
+        </is>
+      </c>
+      <c r="G17" s="95" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="H17" s="95" t="inlineStr">
+        <is>
+          <t>Nidhi Sharma</t>
+        </is>
+      </c>
+      <c r="I17" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J17" s="95" t="inlineStr">
+        <is>
+          <t>Dr Divya patel</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B18" s="94" t="inlineStr">
+        <is>
+          <t>8:15AM</t>
+        </is>
+      </c>
+      <c r="C18" s="94" t="inlineStr">
+        <is>
+          <t>8:30AM</t>
+        </is>
+      </c>
+      <c r="D18" s="94" t="inlineStr">
+        <is>
+          <t>TT Womens Singles</t>
+        </is>
+      </c>
+      <c r="E18" s="94" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" s="94" t="inlineStr">
+        <is>
+          <t>GB-M1</t>
+        </is>
+      </c>
+      <c r="G18" s="94" t="inlineStr">
+        <is>
+          <t>Table 1</t>
+        </is>
+      </c>
+      <c r="H18" s="94" t="inlineStr">
+        <is>
+          <t>Shubhanjali Bisht</t>
+        </is>
+      </c>
+      <c r="I18" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J18" s="94" t="inlineStr">
+        <is>
+          <t>Miloni Parekh</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B19" s="95" t="inlineStr">
+        <is>
+          <t>8:15AM</t>
+        </is>
+      </c>
+      <c r="C19" s="95" t="inlineStr">
+        <is>
+          <t>8:30AM</t>
+        </is>
+      </c>
+      <c r="D19" s="95" t="inlineStr">
+        <is>
+          <t>TT Womens Singles</t>
+        </is>
+      </c>
+      <c r="E19" s="95" t="n">
+        <v>4</v>
+      </c>
+      <c r="F19" s="95" t="inlineStr">
+        <is>
+          <t>GB-M2</t>
+        </is>
+      </c>
+      <c r="G19" s="95" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="H19" s="95" t="inlineStr">
+        <is>
+          <t>Renuka Tripathi</t>
+        </is>
+      </c>
+      <c r="I19" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J19" s="95" t="inlineStr">
+        <is>
+          <t>Shama Gosalia</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B20" s="94" t="inlineStr">
+        <is>
+          <t>8:30AM</t>
+        </is>
+      </c>
+      <c r="C20" s="94" t="inlineStr">
+        <is>
+          <t>8:45AM</t>
+        </is>
+      </c>
+      <c r="D20" s="94" t="inlineStr">
+        <is>
+          <t>TT Womens Singles</t>
+        </is>
+      </c>
+      <c r="E20" s="94" t="n">
+        <v>5</v>
+      </c>
+      <c r="F20" s="94" t="inlineStr">
+        <is>
+          <t>GA-M3</t>
+        </is>
+      </c>
+      <c r="G20" s="94" t="inlineStr">
+        <is>
+          <t>Table 1</t>
+        </is>
+      </c>
+      <c r="H20" s="94" t="inlineStr">
+        <is>
+          <t>Nidhi Sharma</t>
+        </is>
+      </c>
+      <c r="I20" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J20" s="94" t="inlineStr">
+        <is>
+          <t>Nitika Aggarwal</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B21" s="95" t="inlineStr">
+        <is>
+          <t>8:30AM</t>
+        </is>
+      </c>
+      <c r="C21" s="95" t="inlineStr">
+        <is>
+          <t>8:45AM</t>
+        </is>
+      </c>
+      <c r="D21" s="95" t="inlineStr">
+        <is>
+          <t>TT Womens Singles</t>
+        </is>
+      </c>
+      <c r="E21" s="95" t="n">
+        <v>6</v>
+      </c>
+      <c r="F21" s="95" t="inlineStr">
+        <is>
+          <t>GA-M4</t>
+        </is>
+      </c>
+      <c r="G21" s="95" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="H21" s="95" t="inlineStr">
+        <is>
+          <t>Dr Divya patel</t>
+        </is>
+      </c>
+      <c r="I21" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J21" s="95" t="inlineStr">
+        <is>
+          <t>Deepali Acharya</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B22" s="94" t="inlineStr">
+        <is>
+          <t>8:45AM</t>
+        </is>
+      </c>
+      <c r="C22" s="94" t="inlineStr">
+        <is>
+          <t>9:00AM</t>
+        </is>
+      </c>
+      <c r="D22" s="94" t="inlineStr">
+        <is>
+          <t>TT Womens Singles</t>
+        </is>
+      </c>
+      <c r="E22" s="94" t="n">
+        <v>7</v>
+      </c>
+      <c r="F22" s="94" t="inlineStr">
+        <is>
+          <t>GB-M3</t>
+        </is>
+      </c>
+      <c r="G22" s="94" t="inlineStr">
+        <is>
+          <t>Table 1</t>
+        </is>
+      </c>
+      <c r="H22" s="94" t="inlineStr">
+        <is>
+          <t>Shubhanjali Bisht</t>
+        </is>
+      </c>
+      <c r="I22" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J22" s="94" t="inlineStr">
+        <is>
+          <t>Renuka Tripathi</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B23" s="95" t="inlineStr">
+        <is>
+          <t>8:45AM</t>
+        </is>
+      </c>
+      <c r="C23" s="95" t="inlineStr">
+        <is>
+          <t>9:00AM</t>
+        </is>
+      </c>
+      <c r="D23" s="95" t="inlineStr">
+        <is>
+          <t>TT Womens Singles</t>
+        </is>
+      </c>
+      <c r="E23" s="95" t="n">
+        <v>8</v>
+      </c>
+      <c r="F23" s="95" t="inlineStr">
+        <is>
+          <t>GB-M4</t>
+        </is>
+      </c>
+      <c r="G23" s="95" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="H23" s="95" t="inlineStr">
+        <is>
+          <t>Miloni Parekh</t>
+        </is>
+      </c>
+      <c r="I23" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J23" s="95" t="inlineStr">
+        <is>
+          <t>Shama Gosalia</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B24" s="94" t="inlineStr">
+        <is>
+          <t>9:00AM</t>
+        </is>
+      </c>
+      <c r="C24" s="94" t="inlineStr">
+        <is>
+          <t>9:15AM</t>
+        </is>
+      </c>
+      <c r="D24" s="94" t="inlineStr">
+        <is>
+          <t>TT Womens Singles</t>
+        </is>
+      </c>
+      <c r="E24" s="94" t="n">
+        <v>9</v>
+      </c>
+      <c r="F24" s="94" t="inlineStr">
+        <is>
+          <t>GA-M5</t>
+        </is>
+      </c>
+      <c r="G24" s="94" t="inlineStr">
+        <is>
+          <t>Table 1</t>
+        </is>
+      </c>
+      <c r="H24" s="94" t="inlineStr">
+        <is>
+          <t>Nidhi Sharma</t>
+        </is>
+      </c>
+      <c r="I24" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J24" s="94" t="inlineStr">
+        <is>
+          <t>Deepali Acharya</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B25" s="95" t="inlineStr">
+        <is>
+          <t>9:00AM</t>
+        </is>
+      </c>
+      <c r="C25" s="95" t="inlineStr">
+        <is>
+          <t>9:15AM</t>
+        </is>
+      </c>
+      <c r="D25" s="95" t="inlineStr">
+        <is>
+          <t>TT Womens Singles</t>
+        </is>
+      </c>
+      <c r="E25" s="95" t="n">
+        <v>10</v>
+      </c>
+      <c r="F25" s="95" t="inlineStr">
+        <is>
+          <t>GA-M6</t>
+        </is>
+      </c>
+      <c r="G25" s="95" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="H25" s="95" t="inlineStr">
+        <is>
+          <t>Dr Divya patel</t>
+        </is>
+      </c>
+      <c r="I25" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J25" s="95" t="inlineStr">
+        <is>
+          <t>Nitika Aggarwal</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B26" s="94" t="inlineStr">
+        <is>
+          <t>9:15AM</t>
+        </is>
+      </c>
+      <c r="C26" s="94" t="inlineStr">
+        <is>
+          <t>9:30AM</t>
+        </is>
+      </c>
+      <c r="D26" s="94" t="inlineStr">
+        <is>
+          <t>TT Womens Singles</t>
+        </is>
+      </c>
+      <c r="E26" s="94" t="n">
+        <v>11</v>
+      </c>
+      <c r="F26" s="94" t="inlineStr">
+        <is>
+          <t>GB-M5</t>
+        </is>
+      </c>
+      <c r="G26" s="94" t="inlineStr">
+        <is>
+          <t>Table 1</t>
+        </is>
+      </c>
+      <c r="H26" s="94" t="inlineStr">
+        <is>
+          <t>Shubhanjali Bisht</t>
+        </is>
+      </c>
+      <c r="I26" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J26" s="94" t="inlineStr">
+        <is>
+          <t>Shama Gosalia</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B27" s="95" t="inlineStr">
+        <is>
+          <t>9:15AM</t>
+        </is>
+      </c>
+      <c r="C27" s="95" t="inlineStr">
+        <is>
+          <t>9:30AM</t>
+        </is>
+      </c>
+      <c r="D27" s="95" t="inlineStr">
+        <is>
+          <t>TT Womens Singles</t>
+        </is>
+      </c>
+      <c r="E27" s="95" t="n">
+        <v>12</v>
+      </c>
+      <c r="F27" s="95" t="inlineStr">
+        <is>
+          <t>GB-M6</t>
+        </is>
+      </c>
+      <c r="G27" s="95" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="H27" s="95" t="inlineStr">
+        <is>
+          <t>Miloni Parekh</t>
+        </is>
+      </c>
+      <c r="I27" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J27" s="95" t="inlineStr">
+        <is>
+          <t>Renuka Tripathi</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B28" s="94" t="inlineStr">
         <is>
           <t>10:30AM</t>
         </is>
       </c>
-      <c r="C16" s="27" t="inlineStr">
+      <c r="C28" s="94" t="inlineStr">
         <is>
           <t>10:45AM</t>
         </is>
       </c>
-      <c r="D16" s="27" t="inlineStr">
+      <c r="D28" s="94" t="inlineStr">
         <is>
           <t>TT Womens Singles</t>
         </is>
       </c>
-      <c r="E16" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" s="27" t="inlineStr">
-        <is>
-          <t>GA-M1</t>
-        </is>
-      </c>
-      <c r="G16" s="27" t="inlineStr">
+      <c r="E28" s="94" t="n">
+        <v>13</v>
+      </c>
+      <c r="F28" s="94" t="inlineStr">
+        <is>
+          <t>SF1</t>
+        </is>
+      </c>
+      <c r="G28" s="94" t="inlineStr">
         <is>
           <t>Table 1</t>
         </is>
       </c>
-      <c r="H16" s="27" t="inlineStr">
-        <is>
-          <t>Nitika Aggarwal</t>
-        </is>
-      </c>
-      <c r="I16" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J16" s="27" t="inlineStr">
-        <is>
-          <t>Deepali Acharya</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="28" t="inlineStr">
+      <c r="H28" s="94" t="inlineStr">
+        <is>
+          <t>1st of Group A</t>
+        </is>
+      </c>
+      <c r="I28" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J28" s="94" t="inlineStr">
+        <is>
+          <t>2nd of Group B</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="95" t="inlineStr">
         <is>
           <t>Aug 15</t>
         </is>
       </c>
-      <c r="B17" s="28" t="inlineStr">
+      <c r="B29" s="95" t="inlineStr">
         <is>
           <t>10:30AM</t>
         </is>
       </c>
-      <c r="C17" s="28" t="inlineStr">
+      <c r="C29" s="95" t="inlineStr">
         <is>
           <t>10:45AM</t>
         </is>
       </c>
-      <c r="D17" s="28" t="inlineStr">
+      <c r="D29" s="95" t="inlineStr">
         <is>
           <t>TT Womens Singles</t>
         </is>
       </c>
-      <c r="E17" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="F17" s="28" t="inlineStr">
-        <is>
-          <t>GA-M2</t>
-        </is>
-      </c>
-      <c r="G17" s="28" t="inlineStr">
+      <c r="E29" s="95" t="n">
+        <v>14</v>
+      </c>
+      <c r="F29" s="95" t="inlineStr">
+        <is>
+          <t>SF2</t>
+        </is>
+      </c>
+      <c r="G29" s="95" t="inlineStr">
         <is>
           <t>Table 2</t>
         </is>
       </c>
-      <c r="H17" s="28" t="inlineStr">
-        <is>
-          <t>Nidhi Sharma</t>
-        </is>
-      </c>
-      <c r="I17" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J17" s="28" t="inlineStr">
-        <is>
-          <t>Dr Divya patel</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="27" t="inlineStr">
+      <c r="H29" s="95" t="inlineStr">
+        <is>
+          <t>1st of Group B</t>
+        </is>
+      </c>
+      <c r="I29" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J29" s="95" t="inlineStr">
+        <is>
+          <t>2nd of Group A</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="94" t="inlineStr">
         <is>
           <t>Aug 15</t>
         </is>
       </c>
-      <c r="B18" s="27" t="inlineStr">
-        <is>
-          <t>10:55AM</t>
-        </is>
-      </c>
-      <c r="C18" s="27" t="inlineStr">
-        <is>
-          <t>11:10AM</t>
-        </is>
-      </c>
-      <c r="D18" s="27" t="inlineStr">
+      <c r="B30" s="94" t="inlineStr">
+        <is>
+          <t>10:45AM</t>
+        </is>
+      </c>
+      <c r="C30" s="94" t="inlineStr">
+        <is>
+          <t>11:00AM</t>
+        </is>
+      </c>
+      <c r="D30" s="94" t="inlineStr">
         <is>
           <t>TT Womens Singles</t>
         </is>
       </c>
-      <c r="E18" s="27" t="n">
-        <v>3</v>
-      </c>
-      <c r="F18" s="27" t="inlineStr">
-        <is>
-          <t>GA-M3</t>
-        </is>
-      </c>
-      <c r="G18" s="27" t="inlineStr">
+      <c r="E30" s="94" t="n">
+        <v>15</v>
+      </c>
+      <c r="F30" s="94" t="inlineStr">
+        <is>
+          <t>FINAL</t>
+        </is>
+      </c>
+      <c r="G30" s="94" t="inlineStr">
         <is>
           <t>Table 1</t>
         </is>
       </c>
-      <c r="H18" s="27" t="inlineStr">
-        <is>
-          <t>Nidhi Sharma</t>
-        </is>
-      </c>
-      <c r="I18" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J18" s="27" t="inlineStr">
-        <is>
-          <t>Nitika Aggarwal</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="28" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B19" s="28" t="inlineStr">
-        <is>
-          <t>10:55AM</t>
-        </is>
-      </c>
-      <c r="C19" s="28" t="inlineStr">
-        <is>
-          <t>11:10AM</t>
-        </is>
-      </c>
-      <c r="D19" s="28" t="inlineStr">
-        <is>
-          <t>TT Womens Singles</t>
-        </is>
-      </c>
-      <c r="E19" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="F19" s="28" t="inlineStr">
-        <is>
-          <t>GA-M4</t>
-        </is>
-      </c>
-      <c r="G19" s="28" t="inlineStr">
-        <is>
-          <t>Table 2</t>
-        </is>
-      </c>
-      <c r="H19" s="28" t="inlineStr">
-        <is>
-          <t>Dr Divya patel</t>
-        </is>
-      </c>
-      <c r="I19" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J19" s="28" t="inlineStr">
-        <is>
-          <t>Deepali Acharya</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="27" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B20" s="27" t="inlineStr">
-        <is>
-          <t>11:20AM</t>
-        </is>
-      </c>
-      <c r="C20" s="27" t="inlineStr">
-        <is>
-          <t>11:35AM</t>
-        </is>
-      </c>
-      <c r="D20" s="27" t="inlineStr">
-        <is>
-          <t>TT Womens Singles</t>
-        </is>
-      </c>
-      <c r="E20" s="27" t="n">
-        <v>5</v>
-      </c>
-      <c r="F20" s="27" t="inlineStr">
-        <is>
-          <t>GA-M5</t>
-        </is>
-      </c>
-      <c r="G20" s="27" t="inlineStr">
-        <is>
-          <t>Table 1</t>
-        </is>
-      </c>
-      <c r="H20" s="27" t="inlineStr">
-        <is>
-          <t>Nidhi Sharma</t>
-        </is>
-      </c>
-      <c r="I20" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J20" s="27" t="inlineStr">
-        <is>
-          <t>Deepali Acharya</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="28" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B21" s="28" t="inlineStr">
-        <is>
-          <t>11:20AM</t>
-        </is>
-      </c>
-      <c r="C21" s="28" t="inlineStr">
-        <is>
-          <t>11:35AM</t>
-        </is>
-      </c>
-      <c r="D21" s="28" t="inlineStr">
-        <is>
-          <t>TT Womens Singles</t>
-        </is>
-      </c>
-      <c r="E21" s="28" t="n">
-        <v>6</v>
-      </c>
-      <c r="F21" s="28" t="inlineStr">
-        <is>
-          <t>GA-M6</t>
-        </is>
-      </c>
-      <c r="G21" s="28" t="inlineStr">
-        <is>
-          <t>Table 2</t>
-        </is>
-      </c>
-      <c r="H21" s="28" t="inlineStr">
-        <is>
-          <t>Dr Divya patel</t>
-        </is>
-      </c>
-      <c r="I21" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J21" s="28" t="inlineStr">
-        <is>
-          <t>Nitika Aggarwal</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="27" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B22" s="27" t="inlineStr">
-        <is>
-          <t>11:35AM</t>
-        </is>
-      </c>
-      <c r="C22" s="27" t="inlineStr">
-        <is>
-          <t>11:50AM</t>
-        </is>
-      </c>
-      <c r="D22" s="27" t="inlineStr">
-        <is>
-          <t>TT Womens Singles</t>
-        </is>
-      </c>
-      <c r="E22" s="27" t="n">
-        <v>7</v>
-      </c>
-      <c r="F22" s="27" t="inlineStr">
-        <is>
-          <t>GB-M1</t>
-        </is>
-      </c>
-      <c r="G22" s="27" t="inlineStr">
-        <is>
-          <t>Table 1</t>
-        </is>
-      </c>
-      <c r="H22" s="27" t="inlineStr">
-        <is>
-          <t>Shubhanjali Bisht</t>
-        </is>
-      </c>
-      <c r="I22" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J22" s="27" t="inlineStr">
-        <is>
-          <t>Miloni Parekh</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="28" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B23" s="28" t="inlineStr">
-        <is>
-          <t>11:35AM</t>
-        </is>
-      </c>
-      <c r="C23" s="28" t="inlineStr">
-        <is>
-          <t>11:50AM</t>
-        </is>
-      </c>
-      <c r="D23" s="28" t="inlineStr">
-        <is>
-          <t>TT Womens Singles</t>
-        </is>
-      </c>
-      <c r="E23" s="28" t="n">
-        <v>8</v>
-      </c>
-      <c r="F23" s="28" t="inlineStr">
-        <is>
-          <t>GB-M2</t>
-        </is>
-      </c>
-      <c r="G23" s="28" t="inlineStr">
-        <is>
-          <t>Table 2</t>
-        </is>
-      </c>
-      <c r="H23" s="28" t="inlineStr">
-        <is>
-          <t>Renuka Tripathi</t>
-        </is>
-      </c>
-      <c r="I23" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J23" s="28" t="inlineStr">
-        <is>
-          <t>Shama Gosalia</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="27" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B24" s="27" t="inlineStr">
-        <is>
-          <t>3:00PM</t>
-        </is>
-      </c>
-      <c r="C24" s="27" t="inlineStr">
-        <is>
-          <t>3:15PM</t>
-        </is>
-      </c>
-      <c r="D24" s="27" t="inlineStr">
-        <is>
-          <t>TT Womens Singles</t>
-        </is>
-      </c>
-      <c r="E24" s="27" t="n">
-        <v>9</v>
-      </c>
-      <c r="F24" s="27" t="inlineStr">
-        <is>
-          <t>GB-M3</t>
-        </is>
-      </c>
-      <c r="G24" s="27" t="inlineStr">
-        <is>
-          <t>Table 1</t>
-        </is>
-      </c>
-      <c r="H24" s="27" t="inlineStr">
-        <is>
-          <t>Shubhanjali Bisht</t>
-        </is>
-      </c>
-      <c r="I24" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J24" s="27" t="inlineStr">
-        <is>
-          <t>Renuka Tripathi</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="28" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B25" s="28" t="inlineStr">
-        <is>
-          <t>3:00PM</t>
-        </is>
-      </c>
-      <c r="C25" s="28" t="inlineStr">
-        <is>
-          <t>3:15PM</t>
-        </is>
-      </c>
-      <c r="D25" s="28" t="inlineStr">
-        <is>
-          <t>TT Womens Singles</t>
-        </is>
-      </c>
-      <c r="E25" s="28" t="n">
-        <v>10</v>
-      </c>
-      <c r="F25" s="28" t="inlineStr">
-        <is>
-          <t>GB-M4</t>
-        </is>
-      </c>
-      <c r="G25" s="28" t="inlineStr">
-        <is>
-          <t>Table 2</t>
-        </is>
-      </c>
-      <c r="H25" s="28" t="inlineStr">
-        <is>
-          <t>Miloni Parekh</t>
-        </is>
-      </c>
-      <c r="I25" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J25" s="28" t="inlineStr">
-        <is>
-          <t>Shama Gosalia</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="27" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B26" s="27" t="inlineStr">
-        <is>
-          <t>3:25PM</t>
-        </is>
-      </c>
-      <c r="C26" s="27" t="inlineStr">
-        <is>
-          <t>3:40PM</t>
-        </is>
-      </c>
-      <c r="D26" s="27" t="inlineStr">
-        <is>
-          <t>TT Womens Singles</t>
-        </is>
-      </c>
-      <c r="E26" s="27" t="n">
-        <v>11</v>
-      </c>
-      <c r="F26" s="27" t="inlineStr">
-        <is>
-          <t>GB-M5</t>
-        </is>
-      </c>
-      <c r="G26" s="27" t="inlineStr">
-        <is>
-          <t>Table 1</t>
-        </is>
-      </c>
-      <c r="H26" s="27" t="inlineStr">
-        <is>
-          <t>Shubhanjali Bisht</t>
-        </is>
-      </c>
-      <c r="I26" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J26" s="27" t="inlineStr">
-        <is>
-          <t>Shama Gosalia</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="28" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B27" s="28" t="inlineStr">
-        <is>
-          <t>3:25PM</t>
-        </is>
-      </c>
-      <c r="C27" s="28" t="inlineStr">
-        <is>
-          <t>3:40PM</t>
-        </is>
-      </c>
-      <c r="D27" s="28" t="inlineStr">
-        <is>
-          <t>TT Womens Singles</t>
-        </is>
-      </c>
-      <c r="E27" s="28" t="n">
-        <v>12</v>
-      </c>
-      <c r="F27" s="28" t="inlineStr">
-        <is>
-          <t>GB-M6</t>
-        </is>
-      </c>
-      <c r="G27" s="28" t="inlineStr">
-        <is>
-          <t>Table 2</t>
-        </is>
-      </c>
-      <c r="H27" s="28" t="inlineStr">
-        <is>
-          <t>Miloni Parekh</t>
-        </is>
-      </c>
-      <c r="I27" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J27" s="28" t="inlineStr">
-        <is>
-          <t>Renuka Tripathi</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="27" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B28" s="27" t="inlineStr">
-        <is>
-          <t>3:40PM</t>
-        </is>
-      </c>
-      <c r="C28" s="27" t="inlineStr">
-        <is>
-          <t>3:55PM</t>
-        </is>
-      </c>
-      <c r="D28" s="27" t="inlineStr">
-        <is>
-          <t>TT Womens Singles</t>
-        </is>
-      </c>
-      <c r="E28" s="27" t="n">
-        <v>13</v>
-      </c>
-      <c r="F28" s="27" t="inlineStr">
-        <is>
-          <t>SF1</t>
-        </is>
-      </c>
-      <c r="G28" s="27" t="inlineStr">
-        <is>
-          <t>Table 1</t>
-        </is>
-      </c>
-      <c r="H28" s="27" t="inlineStr">
-        <is>
-          <t>1st of Group A</t>
-        </is>
-      </c>
-      <c r="I28" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J28" s="27" t="inlineStr">
-        <is>
-          <t>2nd of Group B</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="28" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B29" s="28" t="inlineStr">
-        <is>
-          <t>3:40PM</t>
-        </is>
-      </c>
-      <c r="C29" s="28" t="inlineStr">
-        <is>
-          <t>3:55PM</t>
-        </is>
-      </c>
-      <c r="D29" s="28" t="inlineStr">
-        <is>
-          <t>TT Womens Singles</t>
-        </is>
-      </c>
-      <c r="E29" s="28" t="n">
-        <v>14</v>
-      </c>
-      <c r="F29" s="28" t="inlineStr">
-        <is>
-          <t>SF2</t>
-        </is>
-      </c>
-      <c r="G29" s="28" t="inlineStr">
-        <is>
-          <t>Table 2</t>
-        </is>
-      </c>
-      <c r="H29" s="28" t="inlineStr">
-        <is>
-          <t>1st of Group B</t>
-        </is>
-      </c>
-      <c r="I29" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J29" s="28" t="inlineStr">
-        <is>
-          <t>2nd of Group A</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="27" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B30" s="27" t="inlineStr">
-        <is>
-          <t>3:55PM</t>
-        </is>
-      </c>
-      <c r="C30" s="27" t="inlineStr">
-        <is>
-          <t>4:10PM</t>
-        </is>
-      </c>
-      <c r="D30" s="27" t="inlineStr">
-        <is>
-          <t>TT Womens Singles</t>
-        </is>
-      </c>
-      <c r="E30" s="27" t="n">
-        <v>15</v>
-      </c>
-      <c r="F30" s="27" t="inlineStr">
-        <is>
-          <t>FINAL</t>
-        </is>
-      </c>
-      <c r="G30" s="27" t="inlineStr">
-        <is>
-          <t>Table 2</t>
-        </is>
-      </c>
-      <c r="H30" s="27" t="inlineStr">
+      <c r="H30" s="94" t="inlineStr">
         <is>
           <t>Winner SF1</t>
         </is>
       </c>
-      <c r="I30" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J30" s="27" t="inlineStr">
+      <c r="I30" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J30" s="94" t="inlineStr">
         <is>
           <t>Winner SF2</t>
         </is>
@@ -5711,7 +5759,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="23" t="inlineStr">
         <is>
-          <t>5 age bands, each Group Stage → Semifinal → Final (Under 26 is a single Americano pool) · Best of 3, Final Best of 5 · 2 Tables</t>
+          <t>4 age bands (Under 15/26/36/46) run Group Stage → Semifinal → Final (Under 26 is a single Americano pool); Above 46 is a Single-Elimination Knockout (Bye: Sanjay Kumar) · Best of 3, Final Best of 5 · 2 Tables</t>
         </is>
       </c>
     </row>
@@ -6060,3736 +6108,3440 @@
       <c r="E33" s="2" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="24" t="inlineStr">
+      <c r="A34" s="96" t="inlineStr">
         <is>
           <t>Above 46</t>
         </is>
       </c>
+      <c r="I34" s="31" t="n"/>
+      <c r="J34" s="31" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="11" t="inlineStr">
-        <is>
-          <t>Group A</t>
-        </is>
-      </c>
-      <c r="D35" s="11" t="inlineStr">
-        <is>
-          <t>Group B</t>
-        </is>
-      </c>
+      <c r="A35" s="97" t="inlineStr">
+        <is>
+          <t>Single-Elimination Knockout (Bye: Sanjay Kumar → Quarterfinal)</t>
+        </is>
+      </c>
+      <c r="I35" s="31" t="n"/>
+      <c r="J35" s="31" t="n"/>
     </row>
     <row r="36" ht="17.1" customHeight="1">
-      <c r="A36" s="4" t="inlineStr">
+      <c r="A36" s="93" t="inlineStr">
+        <is>
+          <t>S.No</t>
+        </is>
+      </c>
+      <c r="B36" s="93" t="inlineStr">
+        <is>
+          <t>Player Name</t>
+        </is>
+      </c>
+      <c r="C36" s="93" t="inlineStr">
+        <is>
+          <t>Age</t>
+        </is>
+      </c>
+      <c r="D36" s="93" t="inlineStr">
+        <is>
+          <t>Bracket Slot</t>
+        </is>
+      </c>
+      <c r="E36" s="31" t="n"/>
+      <c r="F36" s="31" t="n"/>
+      <c r="G36" s="31" t="n"/>
+      <c r="H36" s="31" t="n"/>
+      <c r="I36" s="31" t="n"/>
+      <c r="J36" s="31" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="75" t="n">
+        <v>1</v>
+      </c>
+      <c r="B37" s="75" t="inlineStr">
+        <is>
+          <t>Adil Khan</t>
+        </is>
+      </c>
+      <c r="C37" s="75" t="n">
+        <v>51</v>
+      </c>
+      <c r="D37" s="75" t="inlineStr">
+        <is>
+          <t>Round 1</t>
+        </is>
+      </c>
+      <c r="E37" s="31" t="n"/>
+      <c r="F37" s="31" t="n"/>
+      <c r="G37" s="31" t="n"/>
+      <c r="H37" s="31" t="n"/>
+      <c r="I37" s="31" t="n"/>
+      <c r="J37" s="31" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="75" t="n">
+        <v>2</v>
+      </c>
+      <c r="B38" s="75" t="inlineStr">
+        <is>
+          <t>Ajit nair</t>
+        </is>
+      </c>
+      <c r="C38" s="75" t="n">
+        <v>59</v>
+      </c>
+      <c r="D38" s="75" t="inlineStr">
+        <is>
+          <t>Round 1</t>
+        </is>
+      </c>
+      <c r="E38" s="31" t="n"/>
+      <c r="F38" s="31" t="n"/>
+      <c r="G38" s="31" t="n"/>
+      <c r="H38" s="31" t="n"/>
+      <c r="I38" s="31" t="n"/>
+      <c r="J38" s="31" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="75" t="n">
+        <v>3</v>
+      </c>
+      <c r="B39" s="75" t="inlineStr">
+        <is>
+          <t>Sanjay Kumar</t>
+        </is>
+      </c>
+      <c r="C39" s="75" t="n">
+        <v>61</v>
+      </c>
+      <c r="D39" s="75" t="inlineStr">
+        <is>
+          <t>Bye → Quarterfinal</t>
+        </is>
+      </c>
+      <c r="E39" s="31" t="n"/>
+      <c r="F39" s="31" t="n"/>
+      <c r="G39" s="31" t="n"/>
+      <c r="H39" s="31" t="n"/>
+      <c r="I39" s="31" t="n"/>
+      <c r="J39" s="31" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="75" t="n">
+        <v>4</v>
+      </c>
+      <c r="B40" s="75" t="inlineStr">
+        <is>
+          <t>Vinod Agrawal</t>
+        </is>
+      </c>
+      <c r="C40" s="75" t="n">
+        <v>55</v>
+      </c>
+      <c r="D40" s="75" t="inlineStr">
+        <is>
+          <t>Quarterfinal</t>
+        </is>
+      </c>
+      <c r="E40" s="31" t="n"/>
+      <c r="F40" s="31" t="n"/>
+      <c r="G40" s="31" t="n"/>
+      <c r="H40" s="31" t="n"/>
+      <c r="I40" s="31" t="n"/>
+      <c r="J40" s="31" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="75" t="n">
+        <v>5</v>
+      </c>
+      <c r="B41" s="75" t="inlineStr">
+        <is>
+          <t>Kishore Kumar</t>
+        </is>
+      </c>
+      <c r="C41" s="75" t="n">
+        <v>70</v>
+      </c>
+      <c r="D41" s="75" t="inlineStr">
+        <is>
+          <t>Quarterfinal</t>
+        </is>
+      </c>
+      <c r="E41" s="31" t="n"/>
+      <c r="F41" s="31" t="n"/>
+      <c r="G41" s="31" t="n"/>
+      <c r="H41" s="31" t="n"/>
+      <c r="I41" s="31" t="n"/>
+      <c r="J41" s="31" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="75" t="n">
+        <v>6</v>
+      </c>
+      <c r="B42" s="75" t="inlineStr">
+        <is>
+          <t>Ghansyam nawani</t>
+        </is>
+      </c>
+      <c r="C42" s="75" t="n">
+        <v>60</v>
+      </c>
+      <c r="D42" s="75" t="inlineStr">
+        <is>
+          <t>Quarterfinal</t>
+        </is>
+      </c>
+      <c r="E42" s="31" t="n"/>
+      <c r="F42" s="31" t="n"/>
+      <c r="G42" s="31" t="n"/>
+      <c r="H42" s="31" t="n"/>
+      <c r="I42" s="31" t="n"/>
+      <c r="J42" s="31" t="n"/>
+    </row>
+    <row r="43" ht="20.1" customHeight="1">
+      <c r="A43" s="75" t="n">
+        <v>7</v>
+      </c>
+      <c r="B43" s="75" t="inlineStr">
+        <is>
+          <t>HARSHAPRABHAT SHETTY</t>
+        </is>
+      </c>
+      <c r="C43" s="75" t="n">
+        <v>62</v>
+      </c>
+      <c r="D43" s="75" t="inlineStr">
+        <is>
+          <t>Quarterfinal</t>
+        </is>
+      </c>
+      <c r="E43" s="31" t="n"/>
+      <c r="F43" s="31" t="n"/>
+      <c r="G43" s="31" t="n"/>
+      <c r="H43" s="31" t="n"/>
+      <c r="I43" s="31" t="n"/>
+      <c r="J43" s="31" t="n"/>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="75" t="n">
+        <v>8</v>
+      </c>
+      <c r="B44" s="75" t="inlineStr">
         <is>
           <t>Mukul Joshi</t>
         </is>
       </c>
-      <c r="B36" s="4" t="n">
+      <c r="C44" s="75" t="n">
         <v>51</v>
       </c>
-      <c r="D36" s="4" t="inlineStr">
+      <c r="D44" s="75" t="inlineStr">
+        <is>
+          <t>Quarterfinal</t>
+        </is>
+      </c>
+      <c r="E44" s="31" t="n"/>
+      <c r="F44" s="31" t="n"/>
+      <c r="G44" s="31" t="n"/>
+      <c r="H44" s="31" t="n"/>
+      <c r="I44" s="31" t="n"/>
+      <c r="J44" s="31" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="75" t="n">
+        <v>9</v>
+      </c>
+      <c r="B45" s="75" t="inlineStr">
+        <is>
+          <t>Sushil Dashpute</t>
+        </is>
+      </c>
+      <c r="C45" s="75" t="n">
+        <v>62</v>
+      </c>
+      <c r="D45" s="75" t="inlineStr">
+        <is>
+          <t>Quarterfinal</t>
+        </is>
+      </c>
+      <c r="E45" s="31" t="n"/>
+      <c r="F45" s="31" t="n"/>
+      <c r="G45" s="31" t="n"/>
+      <c r="H45" s="31" t="n"/>
+      <c r="I45" s="31" t="n"/>
+      <c r="J45" s="31" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="31" t="n"/>
+      <c r="B46" s="31" t="n"/>
+      <c r="C46" s="31" t="n"/>
+      <c r="D46" s="31" t="n"/>
+      <c r="E46" s="31" t="n"/>
+      <c r="F46" s="31" t="n"/>
+      <c r="G46" s="31" t="n"/>
+      <c r="H46" s="31" t="n"/>
+      <c r="I46" s="31" t="n"/>
+      <c r="J46" s="31" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="70" t="inlineStr">
+        <is>
+          <t>MATCH SCHEDULE (chronological, interleaved with other sports to avoid player conflicts)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="74" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="B48" s="74" t="inlineStr">
+        <is>
+          <t>Start</t>
+        </is>
+      </c>
+      <c r="C48" s="74" t="inlineStr">
+        <is>
+          <t>End</t>
+        </is>
+      </c>
+      <c r="D48" s="74" t="inlineStr">
+        <is>
+          <t>Band</t>
+        </is>
+      </c>
+      <c r="E48" s="74" t="inlineStr">
+        <is>
+          <t>Match #</t>
+        </is>
+      </c>
+      <c r="F48" s="74" t="inlineStr">
+        <is>
+          <t>Match</t>
+        </is>
+      </c>
+      <c r="G48" s="74" t="inlineStr">
+        <is>
+          <t>Resource</t>
+        </is>
+      </c>
+      <c r="H48" s="74" t="inlineStr">
+        <is>
+          <t>Player A</t>
+        </is>
+      </c>
+      <c r="I48" s="74" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J48" s="74" t="inlineStr">
+        <is>
+          <t>Player B</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B49" s="94" t="inlineStr">
+        <is>
+          <t>10:45AM</t>
+        </is>
+      </c>
+      <c r="C49" s="94" t="inlineStr">
+        <is>
+          <t>11:00AM</t>
+        </is>
+      </c>
+      <c r="D49" s="94" t="inlineStr">
+        <is>
+          <t>Under 36</t>
+        </is>
+      </c>
+      <c r="E49" s="94" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" s="94" t="inlineStr">
+        <is>
+          <t>U36-GB-1</t>
+        </is>
+      </c>
+      <c r="G49" s="94" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="H49" s="94" t="inlineStr">
+        <is>
+          <t>Prakshal Shah</t>
+        </is>
+      </c>
+      <c r="I49" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J49" s="94" t="inlineStr">
+        <is>
+          <t>Amar Parulekar</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B50" s="95" t="inlineStr">
+        <is>
+          <t>11:00AM</t>
+        </is>
+      </c>
+      <c r="C50" s="95" t="inlineStr">
+        <is>
+          <t>11:15AM</t>
+        </is>
+      </c>
+      <c r="D50" s="95" t="inlineStr">
+        <is>
+          <t>Above 46</t>
+        </is>
+      </c>
+      <c r="E50" s="95" t="n">
+        <v>2</v>
+      </c>
+      <c r="F50" s="95" t="inlineStr">
+        <is>
+          <t>A46-QF3</t>
+        </is>
+      </c>
+      <c r="G50" s="95" t="inlineStr">
+        <is>
+          <t>Table 1</t>
+        </is>
+      </c>
+      <c r="H50" s="95" t="inlineStr">
+        <is>
+          <t>Ghansyam nawani</t>
+        </is>
+      </c>
+      <c r="I50" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J50" s="95" t="inlineStr">
+        <is>
+          <t>HARSHAPRABHAT SHETTY</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B51" s="94" t="inlineStr">
+        <is>
+          <t>3:38PM</t>
+        </is>
+      </c>
+      <c r="C51" s="94" t="inlineStr">
+        <is>
+          <t>3:53PM</t>
+        </is>
+      </c>
+      <c r="D51" s="94" t="inlineStr">
+        <is>
+          <t>Under 26</t>
+        </is>
+      </c>
+      <c r="E51" s="94" t="n">
+        <v>3</v>
+      </c>
+      <c r="F51" s="94" t="inlineStr">
+        <is>
+          <t>U26-2</t>
+        </is>
+      </c>
+      <c r="G51" s="94" t="inlineStr">
+        <is>
+          <t>Table 1</t>
+        </is>
+      </c>
+      <c r="H51" s="94" t="inlineStr">
+        <is>
+          <t>Yuvraj jain</t>
+        </is>
+      </c>
+      <c r="I51" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J51" s="94" t="inlineStr">
+        <is>
+          <t>Hryday Goyal</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B52" s="95" t="inlineStr">
+        <is>
+          <t>4:00PM</t>
+        </is>
+      </c>
+      <c r="C52" s="95" t="inlineStr">
+        <is>
+          <t>4:15PM</t>
+        </is>
+      </c>
+      <c r="D52" s="95" t="inlineStr">
+        <is>
+          <t>Under 36</t>
+        </is>
+      </c>
+      <c r="E52" s="95" t="n">
+        <v>4</v>
+      </c>
+      <c r="F52" s="95" t="inlineStr">
+        <is>
+          <t>U36-GA-2</t>
+        </is>
+      </c>
+      <c r="G52" s="95" t="inlineStr">
+        <is>
+          <t>Table 1</t>
+        </is>
+      </c>
+      <c r="H52" s="95" t="inlineStr">
+        <is>
+          <t>Jashit Bajaj</t>
+        </is>
+      </c>
+      <c r="I52" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J52" s="95" t="inlineStr">
+        <is>
+          <t>Tapabrata Dutta</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B53" s="94" t="inlineStr">
+        <is>
+          <t>4:10PM</t>
+        </is>
+      </c>
+      <c r="C53" s="94" t="inlineStr">
+        <is>
+          <t>4:25PM</t>
+        </is>
+      </c>
+      <c r="D53" s="94" t="inlineStr">
+        <is>
+          <t>Under 46</t>
+        </is>
+      </c>
+      <c r="E53" s="94" t="n">
+        <v>5</v>
+      </c>
+      <c r="F53" s="94" t="inlineStr">
+        <is>
+          <t>U46-GA-9</t>
+        </is>
+      </c>
+      <c r="G53" s="94" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="H53" s="94" t="inlineStr">
+        <is>
+          <t>Sudip Parui</t>
+        </is>
+      </c>
+      <c r="I53" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J53" s="94" t="inlineStr">
+        <is>
+          <t>Anuj Shah</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B54" s="95" t="inlineStr">
+        <is>
+          <t>5:00PM</t>
+        </is>
+      </c>
+      <c r="C54" s="95" t="inlineStr">
+        <is>
+          <t>5:15PM</t>
+        </is>
+      </c>
+      <c r="D54" s="95" t="inlineStr">
+        <is>
+          <t>Under 15</t>
+        </is>
+      </c>
+      <c r="E54" s="95" t="n">
+        <v>6</v>
+      </c>
+      <c r="F54" s="95" t="inlineStr">
+        <is>
+          <t>U15-GA-1</t>
+        </is>
+      </c>
+      <c r="G54" s="95" t="inlineStr">
+        <is>
+          <t>Table 1</t>
+        </is>
+      </c>
+      <c r="H54" s="95" t="inlineStr">
+        <is>
+          <t>Shaurya Tripathi</t>
+        </is>
+      </c>
+      <c r="I54" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J54" s="95" t="inlineStr">
+        <is>
+          <t>Parth yadav</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B55" s="94" t="inlineStr">
+        <is>
+          <t>5:00PM</t>
+        </is>
+      </c>
+      <c r="C55" s="94" t="inlineStr">
+        <is>
+          <t>5:15PM</t>
+        </is>
+      </c>
+      <c r="D55" s="94" t="inlineStr">
+        <is>
+          <t>Under 15</t>
+        </is>
+      </c>
+      <c r="E55" s="94" t="n">
+        <v>7</v>
+      </c>
+      <c r="F55" s="94" t="inlineStr">
+        <is>
+          <t>U15-GB-1</t>
+        </is>
+      </c>
+      <c r="G55" s="94" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="H55" s="94" t="inlineStr">
+        <is>
+          <t>Viaan Neema</t>
+        </is>
+      </c>
+      <c r="I55" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J55" s="94" t="inlineStr">
+        <is>
+          <t>Yash agarwal</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B56" s="95" t="inlineStr">
+        <is>
+          <t>5:30PM</t>
+        </is>
+      </c>
+      <c r="C56" s="95" t="inlineStr">
+        <is>
+          <t>5:45PM</t>
+        </is>
+      </c>
+      <c r="D56" s="95" t="inlineStr">
+        <is>
+          <t>Under 46</t>
+        </is>
+      </c>
+      <c r="E56" s="95" t="n">
+        <v>8</v>
+      </c>
+      <c r="F56" s="95" t="inlineStr">
+        <is>
+          <t>U46-GA-5</t>
+        </is>
+      </c>
+      <c r="G56" s="95" t="inlineStr">
+        <is>
+          <t>Table 1</t>
+        </is>
+      </c>
+      <c r="H56" s="95" t="inlineStr">
+        <is>
+          <t>Ankur Mahante</t>
+        </is>
+      </c>
+      <c r="I56" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J56" s="95" t="inlineStr">
+        <is>
+          <t>Sudip Parui</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B57" s="94" t="inlineStr">
+        <is>
+          <t>5:55PM</t>
+        </is>
+      </c>
+      <c r="C57" s="94" t="inlineStr">
+        <is>
+          <t>6:10PM</t>
+        </is>
+      </c>
+      <c r="D57" s="94" t="inlineStr">
+        <is>
+          <t>Under 46</t>
+        </is>
+      </c>
+      <c r="E57" s="94" t="n">
+        <v>9</v>
+      </c>
+      <c r="F57" s="94" t="inlineStr">
+        <is>
+          <t>U46-GA-7</t>
+        </is>
+      </c>
+      <c r="G57" s="94" t="inlineStr">
+        <is>
+          <t>Table 1</t>
+        </is>
+      </c>
+      <c r="H57" s="94" t="inlineStr">
+        <is>
+          <t>Ankur Mahante</t>
+        </is>
+      </c>
+      <c r="I57" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J57" s="94" t="inlineStr">
+        <is>
+          <t>Anuj Shah</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B58" s="95" t="inlineStr">
+        <is>
+          <t>6:11PM</t>
+        </is>
+      </c>
+      <c r="C58" s="95" t="inlineStr">
+        <is>
+          <t>6:26PM</t>
+        </is>
+      </c>
+      <c r="D58" s="95" t="inlineStr">
+        <is>
+          <t>Under 36</t>
+        </is>
+      </c>
+      <c r="E58" s="95" t="n">
+        <v>10</v>
+      </c>
+      <c r="F58" s="95" t="inlineStr">
+        <is>
+          <t>U36-GA-1</t>
+        </is>
+      </c>
+      <c r="G58" s="95" t="inlineStr">
+        <is>
+          <t>Table 1</t>
+        </is>
+      </c>
+      <c r="H58" s="95" t="inlineStr">
+        <is>
+          <t>Jashit Bajaj</t>
+        </is>
+      </c>
+      <c r="I58" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J58" s="95" t="inlineStr">
+        <is>
+          <t>Ravi Modi</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B59" s="94" t="inlineStr">
+        <is>
+          <t>6:36PM</t>
+        </is>
+      </c>
+      <c r="C59" s="94" t="inlineStr">
+        <is>
+          <t>6:51PM</t>
+        </is>
+      </c>
+      <c r="D59" s="94" t="inlineStr">
+        <is>
+          <t>Under 36</t>
+        </is>
+      </c>
+      <c r="E59" s="94" t="n">
+        <v>11</v>
+      </c>
+      <c r="F59" s="94" t="inlineStr">
+        <is>
+          <t>U36-GA-3</t>
+        </is>
+      </c>
+      <c r="G59" s="94" t="inlineStr">
+        <is>
+          <t>Table 1</t>
+        </is>
+      </c>
+      <c r="H59" s="94" t="inlineStr">
+        <is>
+          <t>Ravi Modi</t>
+        </is>
+      </c>
+      <c r="I59" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J59" s="94" t="inlineStr">
+        <is>
+          <t>Tapabrata Dutta</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B60" s="95" t="inlineStr">
+        <is>
+          <t>6:40PM</t>
+        </is>
+      </c>
+      <c r="C60" s="95" t="inlineStr">
+        <is>
+          <t>6:55PM</t>
+        </is>
+      </c>
+      <c r="D60" s="95" t="inlineStr">
+        <is>
+          <t>Above 46</t>
+        </is>
+      </c>
+      <c r="E60" s="95" t="n">
+        <v>12</v>
+      </c>
+      <c r="F60" s="95" t="inlineStr">
+        <is>
+          <t>A46-QF2</t>
+        </is>
+      </c>
+      <c r="G60" s="95" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="H60" s="95" t="inlineStr">
+        <is>
+          <t>Vinod Agrawal</t>
+        </is>
+      </c>
+      <c r="I60" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J60" s="95" t="inlineStr">
+        <is>
+          <t>Kishore Kumar</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B61" s="94" t="inlineStr">
+        <is>
+          <t>6:57PM</t>
+        </is>
+      </c>
+      <c r="C61" s="94" t="inlineStr">
+        <is>
+          <t>7:12PM</t>
+        </is>
+      </c>
+      <c r="D61" s="94" t="inlineStr">
+        <is>
+          <t>Under 15</t>
+        </is>
+      </c>
+      <c r="E61" s="94" t="n">
+        <v>13</v>
+      </c>
+      <c r="F61" s="94" t="inlineStr">
+        <is>
+          <t>U15-GB-2</t>
+        </is>
+      </c>
+      <c r="G61" s="94" t="inlineStr">
+        <is>
+          <t>Table 1</t>
+        </is>
+      </c>
+      <c r="H61" s="94" t="inlineStr">
+        <is>
+          <t>Viaan Neema</t>
+        </is>
+      </c>
+      <c r="I61" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J61" s="94" t="inlineStr">
+        <is>
+          <t>Hridh jhala</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B62" s="95" t="inlineStr">
+        <is>
+          <t>7:22PM</t>
+        </is>
+      </c>
+      <c r="C62" s="95" t="inlineStr">
+        <is>
+          <t>7:37PM</t>
+        </is>
+      </c>
+      <c r="D62" s="95" t="inlineStr">
+        <is>
+          <t>Under 15</t>
+        </is>
+      </c>
+      <c r="E62" s="95" t="n">
+        <v>14</v>
+      </c>
+      <c r="F62" s="95" t="inlineStr">
+        <is>
+          <t>U15-GB-3</t>
+        </is>
+      </c>
+      <c r="G62" s="95" t="inlineStr">
+        <is>
+          <t>Table 1</t>
+        </is>
+      </c>
+      <c r="H62" s="95" t="inlineStr">
+        <is>
+          <t>Yash agarwal</t>
+        </is>
+      </c>
+      <c r="I62" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J62" s="95" t="inlineStr">
+        <is>
+          <t>Hridh jhala</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B63" s="94" t="inlineStr">
+        <is>
+          <t>7:35PM</t>
+        </is>
+      </c>
+      <c r="C63" s="94" t="inlineStr">
+        <is>
+          <t>7:50PM</t>
+        </is>
+      </c>
+      <c r="D63" s="94" t="inlineStr">
+        <is>
+          <t>Under 46</t>
+        </is>
+      </c>
+      <c r="E63" s="94" t="n">
+        <v>15</v>
+      </c>
+      <c r="F63" s="94" t="inlineStr">
+        <is>
+          <t>U46-GB-10</t>
+        </is>
+      </c>
+      <c r="G63" s="94" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="H63" s="94" t="inlineStr">
+        <is>
+          <t>Nilesh Bagaria</t>
+        </is>
+      </c>
+      <c r="I63" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J63" s="94" t="inlineStr">
+        <is>
+          <t>Amit Ranka</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B64" s="95" t="inlineStr">
+        <is>
+          <t>7:50PM</t>
+        </is>
+      </c>
+      <c r="C64" s="95" t="inlineStr">
+        <is>
+          <t>8:05PM</t>
+        </is>
+      </c>
+      <c r="D64" s="95" t="inlineStr">
+        <is>
+          <t>Under 36</t>
+        </is>
+      </c>
+      <c r="E64" s="95" t="n">
+        <v>16</v>
+      </c>
+      <c r="F64" s="95" t="inlineStr">
+        <is>
+          <t>U36-GB-2</t>
+        </is>
+      </c>
+      <c r="G64" s="95" t="inlineStr">
+        <is>
+          <t>Table 1</t>
+        </is>
+      </c>
+      <c r="H64" s="95" t="inlineStr">
+        <is>
+          <t>Prakshal Shah</t>
+        </is>
+      </c>
+      <c r="I64" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J64" s="95" t="inlineStr">
+        <is>
+          <t>Tej</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B65" s="94" t="inlineStr">
+        <is>
+          <t>7:55PM</t>
+        </is>
+      </c>
+      <c r="C65" s="94" t="inlineStr">
+        <is>
+          <t>8:10PM</t>
+        </is>
+      </c>
+      <c r="D65" s="94" t="inlineStr">
+        <is>
+          <t>Under 46</t>
+        </is>
+      </c>
+      <c r="E65" s="94" t="n">
+        <v>17</v>
+      </c>
+      <c r="F65" s="94" t="inlineStr">
+        <is>
+          <t>U46-GA-1</t>
+        </is>
+      </c>
+      <c r="G65" s="94" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="H65" s="94" t="inlineStr">
+        <is>
+          <t>Dr Rahul Modi</t>
+        </is>
+      </c>
+      <c r="I65" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J65" s="94" t="inlineStr">
+        <is>
+          <t>Ankur Mahante</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B66" s="95" t="inlineStr">
+        <is>
+          <t>8:05PM</t>
+        </is>
+      </c>
+      <c r="C66" s="95" t="inlineStr">
+        <is>
+          <t>8:20PM</t>
+        </is>
+      </c>
+      <c r="D66" s="95" t="inlineStr">
+        <is>
+          <t>Under 46</t>
+        </is>
+      </c>
+      <c r="E66" s="95" t="n">
+        <v>18</v>
+      </c>
+      <c r="F66" s="95" t="inlineStr">
+        <is>
+          <t>U46-GB-3</t>
+        </is>
+      </c>
+      <c r="G66" s="95" t="inlineStr">
+        <is>
+          <t>Table 1</t>
+        </is>
+      </c>
+      <c r="H66" s="95" t="inlineStr">
+        <is>
+          <t>Nikunj Jhala</t>
+        </is>
+      </c>
+      <c r="I66" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J66" s="95" t="inlineStr">
+        <is>
+          <t>Nilesh Bagaria</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B67" s="94" t="inlineStr">
+        <is>
+          <t>8:10PM</t>
+        </is>
+      </c>
+      <c r="C67" s="94" t="inlineStr">
+        <is>
+          <t>8:25PM</t>
+        </is>
+      </c>
+      <c r="D67" s="94" t="inlineStr">
+        <is>
+          <t>Under 36</t>
+        </is>
+      </c>
+      <c r="E67" s="94" t="n">
+        <v>19</v>
+      </c>
+      <c r="F67" s="94" t="inlineStr">
+        <is>
+          <t>U36-GB-3</t>
+        </is>
+      </c>
+      <c r="G67" s="94" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="H67" s="94" t="inlineStr">
+        <is>
+          <t>Amar Parulekar</t>
+        </is>
+      </c>
+      <c r="I67" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J67" s="94" t="inlineStr">
+        <is>
+          <t>Tej</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B68" s="95" t="inlineStr">
+        <is>
+          <t>8:20PM</t>
+        </is>
+      </c>
+      <c r="C68" s="95" t="inlineStr">
+        <is>
+          <t>8:35PM</t>
+        </is>
+      </c>
+      <c r="D68" s="95" t="inlineStr">
+        <is>
+          <t>Under 46</t>
+        </is>
+      </c>
+      <c r="E68" s="95" t="n">
+        <v>20</v>
+      </c>
+      <c r="F68" s="95" t="inlineStr">
+        <is>
+          <t>U46-GA-2</t>
+        </is>
+      </c>
+      <c r="G68" s="95" t="inlineStr">
+        <is>
+          <t>Table 1</t>
+        </is>
+      </c>
+      <c r="H68" s="95" t="inlineStr">
+        <is>
+          <t>Dr Rahul Modi</t>
+        </is>
+      </c>
+      <c r="I68" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J68" s="95" t="inlineStr">
+        <is>
+          <t>Sudip Parui</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B69" s="94" t="inlineStr">
+        <is>
+          <t>8:25PM</t>
+        </is>
+      </c>
+      <c r="C69" s="94" t="inlineStr">
+        <is>
+          <t>8:40PM</t>
+        </is>
+      </c>
+      <c r="D69" s="94" t="inlineStr">
+        <is>
+          <t>Under 46</t>
+        </is>
+      </c>
+      <c r="E69" s="94" t="n">
+        <v>21</v>
+      </c>
+      <c r="F69" s="94" t="inlineStr">
+        <is>
+          <t>U46-GA-6</t>
+        </is>
+      </c>
+      <c r="G69" s="94" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="H69" s="94" t="inlineStr">
+        <is>
+          <t>Ankur Mahante</t>
+        </is>
+      </c>
+      <c r="I69" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J69" s="94" t="inlineStr">
+        <is>
+          <t>Tanmay Sharma</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B70" s="95" t="inlineStr">
+        <is>
+          <t>8:35PM</t>
+        </is>
+      </c>
+      <c r="C70" s="95" t="inlineStr">
+        <is>
+          <t>8:50PM</t>
+        </is>
+      </c>
+      <c r="D70" s="95" t="inlineStr">
+        <is>
+          <t>Under 46</t>
+        </is>
+      </c>
+      <c r="E70" s="95" t="n">
+        <v>22</v>
+      </c>
+      <c r="F70" s="95" t="inlineStr">
+        <is>
+          <t>U46-GB-4</t>
+        </is>
+      </c>
+      <c r="G70" s="95" t="inlineStr">
+        <is>
+          <t>Table 1</t>
+        </is>
+      </c>
+      <c r="H70" s="95" t="inlineStr">
+        <is>
+          <t>Nikunj Jhala</t>
+        </is>
+      </c>
+      <c r="I70" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J70" s="95" t="inlineStr">
+        <is>
+          <t>Amit Ranka</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B71" s="94" t="inlineStr">
+        <is>
+          <t>8:40PM</t>
+        </is>
+      </c>
+      <c r="C71" s="94" t="inlineStr">
+        <is>
+          <t>8:55PM</t>
+        </is>
+      </c>
+      <c r="D71" s="94" t="inlineStr">
+        <is>
+          <t>Under 46</t>
+        </is>
+      </c>
+      <c r="E71" s="94" t="n">
+        <v>23</v>
+      </c>
+      <c r="F71" s="94" t="inlineStr">
+        <is>
+          <t>U46-GA-4</t>
+        </is>
+      </c>
+      <c r="G71" s="94" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="H71" s="94" t="inlineStr">
+        <is>
+          <t>Dr Rahul Modi</t>
+        </is>
+      </c>
+      <c r="I71" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J71" s="94" t="inlineStr">
+        <is>
+          <t>Anuj Shah</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B72" s="95" t="inlineStr">
+        <is>
+          <t>8:50PM</t>
+        </is>
+      </c>
+      <c r="C72" s="95" t="inlineStr">
+        <is>
+          <t>9:05PM</t>
+        </is>
+      </c>
+      <c r="D72" s="95" t="inlineStr">
+        <is>
+          <t>Under 46</t>
+        </is>
+      </c>
+      <c r="E72" s="95" t="n">
+        <v>24</v>
+      </c>
+      <c r="F72" s="95" t="inlineStr">
+        <is>
+          <t>U46-GA-8</t>
+        </is>
+      </c>
+      <c r="G72" s="95" t="inlineStr">
+        <is>
+          <t>Table 1</t>
+        </is>
+      </c>
+      <c r="H72" s="95" t="inlineStr">
+        <is>
+          <t>Sudip Parui</t>
+        </is>
+      </c>
+      <c r="I72" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J72" s="95" t="inlineStr">
+        <is>
+          <t>Tanmay Sharma</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B73" s="94" t="inlineStr">
+        <is>
+          <t>8:55PM</t>
+        </is>
+      </c>
+      <c r="C73" s="94" t="inlineStr">
+        <is>
+          <t>9:10PM</t>
+        </is>
+      </c>
+      <c r="D73" s="94" t="inlineStr">
+        <is>
+          <t>Under 36</t>
+        </is>
+      </c>
+      <c r="E73" s="94" t="n">
+        <v>25</v>
+      </c>
+      <c r="F73" s="94" t="inlineStr">
+        <is>
+          <t>U36-SF1</t>
+        </is>
+      </c>
+      <c r="G73" s="94" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="H73" s="94" t="inlineStr">
+        <is>
+          <t>Group B 1st</t>
+        </is>
+      </c>
+      <c r="I73" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J73" s="94" t="inlineStr">
+        <is>
+          <t>Group A 2nd</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B74" s="95" t="inlineStr">
+        <is>
+          <t>9:05PM</t>
+        </is>
+      </c>
+      <c r="C74" s="95" t="inlineStr">
+        <is>
+          <t>9:20PM</t>
+        </is>
+      </c>
+      <c r="D74" s="95" t="inlineStr">
+        <is>
+          <t>Under 36</t>
+        </is>
+      </c>
+      <c r="E74" s="95" t="n">
+        <v>26</v>
+      </c>
+      <c r="F74" s="95" t="inlineStr">
+        <is>
+          <t>U36-SF2</t>
+        </is>
+      </c>
+      <c r="G74" s="95" t="inlineStr">
+        <is>
+          <t>Table 1</t>
+        </is>
+      </c>
+      <c r="H74" s="95" t="inlineStr">
+        <is>
+          <t>Group A 1st</t>
+        </is>
+      </c>
+      <c r="I74" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J74" s="95" t="inlineStr">
+        <is>
+          <t>Group B 2nd</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B75" s="94" t="inlineStr">
+        <is>
+          <t>9:10PM</t>
+        </is>
+      </c>
+      <c r="C75" s="94" t="inlineStr">
+        <is>
+          <t>9:25PM</t>
+        </is>
+      </c>
+      <c r="D75" s="94" t="inlineStr">
+        <is>
+          <t>Under 46</t>
+        </is>
+      </c>
+      <c r="E75" s="94" t="n">
+        <v>27</v>
+      </c>
+      <c r="F75" s="94" t="inlineStr">
+        <is>
+          <t>U46-GA-3</t>
+        </is>
+      </c>
+      <c r="G75" s="94" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="H75" s="94" t="inlineStr">
+        <is>
+          <t>Dr Rahul Modi</t>
+        </is>
+      </c>
+      <c r="I75" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J75" s="94" t="inlineStr">
+        <is>
+          <t>Tanmay Sharma</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B76" s="95" t="inlineStr">
+        <is>
+          <t>9:20PM</t>
+        </is>
+      </c>
+      <c r="C76" s="95" t="inlineStr">
+        <is>
+          <t>9:35PM</t>
+        </is>
+      </c>
+      <c r="D76" s="95" t="inlineStr">
+        <is>
+          <t>Under 36</t>
+        </is>
+      </c>
+      <c r="E76" s="95" t="n">
+        <v>28</v>
+      </c>
+      <c r="F76" s="95" t="inlineStr">
+        <is>
+          <t>U36-FINAL</t>
+        </is>
+      </c>
+      <c r="G76" s="95" t="inlineStr">
+        <is>
+          <t>Table 1</t>
+        </is>
+      </c>
+      <c r="H76" s="95" t="inlineStr">
+        <is>
+          <t>Winner SF1</t>
+        </is>
+      </c>
+      <c r="I76" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J76" s="95" t="inlineStr">
+        <is>
+          <t>Winner SF2</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B77" s="94" t="inlineStr">
+        <is>
+          <t>9:25PM</t>
+        </is>
+      </c>
+      <c r="C77" s="94" t="inlineStr">
+        <is>
+          <t>9:40PM</t>
+        </is>
+      </c>
+      <c r="D77" s="94" t="inlineStr">
+        <is>
+          <t>Above 46</t>
+        </is>
+      </c>
+      <c r="E77" s="94" t="n">
+        <v>29</v>
+      </c>
+      <c r="F77" s="94" t="inlineStr">
+        <is>
+          <t>A46-QF4</t>
+        </is>
+      </c>
+      <c r="G77" s="94" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="H77" s="94" t="inlineStr">
+        <is>
+          <t>Mukul Joshi</t>
+        </is>
+      </c>
+      <c r="I77" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J77" s="94" t="inlineStr">
+        <is>
+          <t>Sushil Dashpute</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B78" s="95" t="inlineStr">
+        <is>
+          <t>9:35PM</t>
+        </is>
+      </c>
+      <c r="C78" s="95" t="inlineStr">
+        <is>
+          <t>9:50PM</t>
+        </is>
+      </c>
+      <c r="D78" s="95" t="inlineStr">
+        <is>
+          <t>Under 46</t>
+        </is>
+      </c>
+      <c r="E78" s="95" t="n">
+        <v>30</v>
+      </c>
+      <c r="F78" s="95" t="inlineStr">
+        <is>
+          <t>U46-GA-10</t>
+        </is>
+      </c>
+      <c r="G78" s="95" t="inlineStr">
+        <is>
+          <t>Table 1</t>
+        </is>
+      </c>
+      <c r="H78" s="95" t="inlineStr">
+        <is>
+          <t>Tanmay Sharma</t>
+        </is>
+      </c>
+      <c r="I78" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J78" s="95" t="inlineStr">
+        <is>
+          <t>Anuj Shah</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B79" s="94" t="inlineStr">
+        <is>
+          <t>9:40PM</t>
+        </is>
+      </c>
+      <c r="C79" s="94" t="inlineStr">
+        <is>
+          <t>9:55PM</t>
+        </is>
+      </c>
+      <c r="D79" s="94" t="inlineStr">
+        <is>
+          <t>Above 46</t>
+        </is>
+      </c>
+      <c r="E79" s="94" t="n">
+        <v>31</v>
+      </c>
+      <c r="F79" s="94" t="inlineStr">
+        <is>
+          <t>A46-SF2</t>
+        </is>
+      </c>
+      <c r="G79" s="94" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="H79" s="94" t="inlineStr">
+        <is>
+          <t>Winner QF3</t>
+        </is>
+      </c>
+      <c r="I79" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J79" s="94" t="inlineStr">
+        <is>
+          <t>Winner QF4</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="95" t="inlineStr">
+        <is>
+          <t>Aug 16</t>
+        </is>
+      </c>
+      <c r="B80" s="95" t="inlineStr">
+        <is>
+          <t>8:00AM</t>
+        </is>
+      </c>
+      <c r="C80" s="95" t="inlineStr">
+        <is>
+          <t>8:15AM</t>
+        </is>
+      </c>
+      <c r="D80" s="95" t="inlineStr">
+        <is>
+          <t>Under 46</t>
+        </is>
+      </c>
+      <c r="E80" s="95" t="n">
+        <v>32</v>
+      </c>
+      <c r="F80" s="95" t="inlineStr">
+        <is>
+          <t>U46-GB-8</t>
+        </is>
+      </c>
+      <c r="G80" s="95" t="inlineStr">
+        <is>
+          <t>Table 1</t>
+        </is>
+      </c>
+      <c r="H80" s="95" t="inlineStr">
+        <is>
+          <t>Vinit Padia</t>
+        </is>
+      </c>
+      <c r="I80" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J80" s="95" t="inlineStr">
+        <is>
+          <t>Nilesh Bagaria</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="94" t="inlineStr">
+        <is>
+          <t>Aug 16</t>
+        </is>
+      </c>
+      <c r="B81" s="94" t="inlineStr">
+        <is>
+          <t>8:25AM</t>
+        </is>
+      </c>
+      <c r="C81" s="94" t="inlineStr">
+        <is>
+          <t>8:40AM</t>
+        </is>
+      </c>
+      <c r="D81" s="94" t="inlineStr">
+        <is>
+          <t>Under 46</t>
+        </is>
+      </c>
+      <c r="E81" s="94" t="n">
+        <v>33</v>
+      </c>
+      <c r="F81" s="94" t="inlineStr">
+        <is>
+          <t>U46-GB-9</t>
+        </is>
+      </c>
+      <c r="G81" s="94" t="inlineStr">
+        <is>
+          <t>Table 1</t>
+        </is>
+      </c>
+      <c r="H81" s="94" t="inlineStr">
+        <is>
+          <t>Vinit Padia</t>
+        </is>
+      </c>
+      <c r="I81" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J81" s="94" t="inlineStr">
+        <is>
+          <t>Amit Ranka</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="95" t="inlineStr">
+        <is>
+          <t>Aug 16</t>
+        </is>
+      </c>
+      <c r="B82" s="95" t="inlineStr">
+        <is>
+          <t>8:50AM</t>
+        </is>
+      </c>
+      <c r="C82" s="95" t="inlineStr">
+        <is>
+          <t>9:05AM</t>
+        </is>
+      </c>
+      <c r="D82" s="95" t="inlineStr">
+        <is>
+          <t>Under 26</t>
+        </is>
+      </c>
+      <c r="E82" s="95" t="n">
+        <v>34</v>
+      </c>
+      <c r="F82" s="95" t="inlineStr">
+        <is>
+          <t>U26-8</t>
+        </is>
+      </c>
+      <c r="G82" s="95" t="inlineStr">
+        <is>
+          <t>Table 1</t>
+        </is>
+      </c>
+      <c r="H82" s="95" t="inlineStr">
+        <is>
+          <t>Hryday Goyal</t>
+        </is>
+      </c>
+      <c r="I82" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J82" s="95" t="inlineStr">
+        <is>
+          <t>Pranit Shriyan</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="94" t="inlineStr">
+        <is>
+          <t>Aug 16</t>
+        </is>
+      </c>
+      <c r="B83" s="94" t="inlineStr">
+        <is>
+          <t>8:50AM</t>
+        </is>
+      </c>
+      <c r="C83" s="94" t="inlineStr">
+        <is>
+          <t>9:05AM</t>
+        </is>
+      </c>
+      <c r="D83" s="94" t="inlineStr">
+        <is>
+          <t>Under 46</t>
+        </is>
+      </c>
+      <c r="E83" s="94" t="n">
+        <v>35</v>
+      </c>
+      <c r="F83" s="94" t="inlineStr">
+        <is>
+          <t>U46-GB-2</t>
+        </is>
+      </c>
+      <c r="G83" s="94" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="H83" s="94" t="inlineStr">
+        <is>
+          <t>Nikunj Jhala</t>
+        </is>
+      </c>
+      <c r="I83" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J83" s="94" t="inlineStr">
+        <is>
+          <t>Vinit Padia</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="95" t="inlineStr">
+        <is>
+          <t>Aug 16</t>
+        </is>
+      </c>
+      <c r="B84" s="95" t="inlineStr">
+        <is>
+          <t>9:10AM</t>
+        </is>
+      </c>
+      <c r="C84" s="95" t="inlineStr">
+        <is>
+          <t>9:25AM</t>
+        </is>
+      </c>
+      <c r="D84" s="95" t="inlineStr">
+        <is>
+          <t>Under 15</t>
+        </is>
+      </c>
+      <c r="E84" s="95" t="n">
+        <v>36</v>
+      </c>
+      <c r="F84" s="95" t="inlineStr">
+        <is>
+          <t>U15-GA-2</t>
+        </is>
+      </c>
+      <c r="G84" s="95" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="H84" s="95" t="inlineStr">
+        <is>
+          <t>Shaurya Tripathi</t>
+        </is>
+      </c>
+      <c r="I84" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J84" s="95" t="inlineStr">
+        <is>
+          <t>Aadit Joshi</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="94" t="inlineStr">
+        <is>
+          <t>Aug 16</t>
+        </is>
+      </c>
+      <c r="B85" s="94" t="inlineStr">
+        <is>
+          <t>9:20AM</t>
+        </is>
+      </c>
+      <c r="C85" s="94" t="inlineStr">
+        <is>
+          <t>9:35AM</t>
+        </is>
+      </c>
+      <c r="D85" s="94" t="inlineStr">
+        <is>
+          <t>Under 26</t>
+        </is>
+      </c>
+      <c r="E85" s="94" t="n">
+        <v>37</v>
+      </c>
+      <c r="F85" s="94" t="inlineStr">
+        <is>
+          <t>U26-3</t>
+        </is>
+      </c>
+      <c r="G85" s="94" t="inlineStr">
+        <is>
+          <t>Table 1</t>
+        </is>
+      </c>
+      <c r="H85" s="94" t="inlineStr">
+        <is>
+          <t>Yuvraj jain</t>
+        </is>
+      </c>
+      <c r="I85" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J85" s="94" t="inlineStr">
+        <is>
+          <t>Pranit Shriyan</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="95" t="inlineStr">
+        <is>
+          <t>Aug 16</t>
+        </is>
+      </c>
+      <c r="B86" s="95" t="inlineStr">
+        <is>
+          <t>9:35AM</t>
+        </is>
+      </c>
+      <c r="C86" s="95" t="inlineStr">
+        <is>
+          <t>9:50AM</t>
+        </is>
+      </c>
+      <c r="D86" s="95" t="inlineStr">
+        <is>
+          <t>Under 15</t>
+        </is>
+      </c>
+      <c r="E86" s="95" t="n">
+        <v>38</v>
+      </c>
+      <c r="F86" s="95" t="inlineStr">
+        <is>
+          <t>U15-GA-3</t>
+        </is>
+      </c>
+      <c r="G86" s="95" t="inlineStr">
+        <is>
+          <t>Table 1</t>
+        </is>
+      </c>
+      <c r="H86" s="95" t="inlineStr">
+        <is>
+          <t>Parth yadav</t>
+        </is>
+      </c>
+      <c r="I86" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J86" s="95" t="inlineStr">
+        <is>
+          <t>Aadit Joshi</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="94" t="inlineStr">
+        <is>
+          <t>Aug 16</t>
+        </is>
+      </c>
+      <c r="B87" s="94" t="inlineStr">
+        <is>
+          <t>9:50AM</t>
+        </is>
+      </c>
+      <c r="C87" s="94" t="inlineStr">
+        <is>
+          <t>10:05AM</t>
+        </is>
+      </c>
+      <c r="D87" s="94" t="inlineStr">
+        <is>
+          <t>Under 15</t>
+        </is>
+      </c>
+      <c r="E87" s="94" t="n">
+        <v>39</v>
+      </c>
+      <c r="F87" s="94" t="inlineStr">
+        <is>
+          <t>U15-SF1</t>
+        </is>
+      </c>
+      <c r="G87" s="94" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="H87" s="94" t="inlineStr">
+        <is>
+          <t>Group B 1st</t>
+        </is>
+      </c>
+      <c r="I87" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J87" s="94" t="inlineStr">
+        <is>
+          <t>Group A 2nd</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="95" t="inlineStr">
+        <is>
+          <t>Aug 16</t>
+        </is>
+      </c>
+      <c r="B88" s="95" t="inlineStr">
+        <is>
+          <t>9:50AM</t>
+        </is>
+      </c>
+      <c r="C88" s="95" t="inlineStr">
+        <is>
+          <t>10:05AM</t>
+        </is>
+      </c>
+      <c r="D88" s="95" t="inlineStr">
+        <is>
+          <t>Under 26</t>
+        </is>
+      </c>
+      <c r="E88" s="95" t="n">
+        <v>40</v>
+      </c>
+      <c r="F88" s="95" t="inlineStr">
+        <is>
+          <t>U26-4</t>
+        </is>
+      </c>
+      <c r="G88" s="95" t="inlineStr">
+        <is>
+          <t>Table 1</t>
+        </is>
+      </c>
+      <c r="H88" s="95" t="inlineStr">
+        <is>
+          <t>Yuvraj jain</t>
+        </is>
+      </c>
+      <c r="I88" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J88" s="95" t="inlineStr">
+        <is>
+          <t>Rahul Garg</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="94" t="inlineStr">
+        <is>
+          <t>Aug 16</t>
+        </is>
+      </c>
+      <c r="B89" s="94" t="inlineStr">
+        <is>
+          <t>10:05AM</t>
+        </is>
+      </c>
+      <c r="C89" s="94" t="inlineStr">
+        <is>
+          <t>10:20AM</t>
+        </is>
+      </c>
+      <c r="D89" s="94" t="inlineStr">
+        <is>
+          <t>Under 15</t>
+        </is>
+      </c>
+      <c r="E89" s="94" t="n">
+        <v>41</v>
+      </c>
+      <c r="F89" s="94" t="inlineStr">
+        <is>
+          <t>U15-SF2</t>
+        </is>
+      </c>
+      <c r="G89" s="94" t="inlineStr">
+        <is>
+          <t>Table 1</t>
+        </is>
+      </c>
+      <c r="H89" s="94" t="inlineStr">
+        <is>
+          <t>Group A 1st</t>
+        </is>
+      </c>
+      <c r="I89" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J89" s="94" t="inlineStr">
+        <is>
+          <t>Group B 2nd</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="95" t="inlineStr">
+        <is>
+          <t>Aug 16</t>
+        </is>
+      </c>
+      <c r="B90" s="95" t="inlineStr">
+        <is>
+          <t>10:10AM</t>
+        </is>
+      </c>
+      <c r="C90" s="95" t="inlineStr">
+        <is>
+          <t>10:25AM</t>
+        </is>
+      </c>
+      <c r="D90" s="95" t="inlineStr">
+        <is>
+          <t>Under 26</t>
+        </is>
+      </c>
+      <c r="E90" s="95" t="n">
+        <v>42</v>
+      </c>
+      <c r="F90" s="95" t="inlineStr">
+        <is>
+          <t>U26-6</t>
+        </is>
+      </c>
+      <c r="G90" s="95" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="H90" s="95" t="inlineStr">
+        <is>
+          <t>Aaditya Kumar</t>
+        </is>
+      </c>
+      <c r="I90" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J90" s="95" t="inlineStr">
+        <is>
+          <t>Pranit Shriyan</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="94" t="inlineStr">
+        <is>
+          <t>Aug 16</t>
+        </is>
+      </c>
+      <c r="B91" s="94" t="inlineStr">
+        <is>
+          <t>10:20AM</t>
+        </is>
+      </c>
+      <c r="C91" s="94" t="inlineStr">
+        <is>
+          <t>10:35AM</t>
+        </is>
+      </c>
+      <c r="D91" s="94" t="inlineStr">
+        <is>
+          <t>Under 26</t>
+        </is>
+      </c>
+      <c r="E91" s="94" t="n">
+        <v>43</v>
+      </c>
+      <c r="F91" s="94" t="inlineStr">
+        <is>
+          <t>U26-9</t>
+        </is>
+      </c>
+      <c r="G91" s="94" t="inlineStr">
+        <is>
+          <t>Table 1</t>
+        </is>
+      </c>
+      <c r="H91" s="94" t="inlineStr">
+        <is>
+          <t>Hryday Goyal</t>
+        </is>
+      </c>
+      <c r="I91" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J91" s="94" t="inlineStr">
+        <is>
+          <t>Rahul Garg</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="95" t="inlineStr">
+        <is>
+          <t>Aug 16</t>
+        </is>
+      </c>
+      <c r="B92" s="95" t="inlineStr">
+        <is>
+          <t>10:25AM</t>
+        </is>
+      </c>
+      <c r="C92" s="95" t="inlineStr">
+        <is>
+          <t>10:40AM</t>
+        </is>
+      </c>
+      <c r="D92" s="95" t="inlineStr">
+        <is>
+          <t>Under 15</t>
+        </is>
+      </c>
+      <c r="E92" s="95" t="n">
+        <v>44</v>
+      </c>
+      <c r="F92" s="95" t="inlineStr">
+        <is>
+          <t>U15-FINAL</t>
+        </is>
+      </c>
+      <c r="G92" s="95" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="H92" s="95" t="inlineStr">
+        <is>
+          <t>Winner SF1</t>
+        </is>
+      </c>
+      <c r="I92" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J92" s="95" t="inlineStr">
+        <is>
+          <t>Winner SF2</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="94" t="inlineStr">
+        <is>
+          <t>Aug 16</t>
+        </is>
+      </c>
+      <c r="B93" s="94" t="inlineStr">
+        <is>
+          <t>10:35AM</t>
+        </is>
+      </c>
+      <c r="C93" s="94" t="inlineStr">
+        <is>
+          <t>10:50AM</t>
+        </is>
+      </c>
+      <c r="D93" s="94" t="inlineStr">
+        <is>
+          <t>Under 26</t>
+        </is>
+      </c>
+      <c r="E93" s="94" t="n">
+        <v>45</v>
+      </c>
+      <c r="F93" s="94" t="inlineStr">
+        <is>
+          <t>U26-1</t>
+        </is>
+      </c>
+      <c r="G93" s="94" t="inlineStr">
+        <is>
+          <t>Table 1</t>
+        </is>
+      </c>
+      <c r="H93" s="94" t="inlineStr">
+        <is>
+          <t>Yuvraj jain</t>
+        </is>
+      </c>
+      <c r="I93" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J93" s="94" t="inlineStr">
+        <is>
+          <t>Aaditya Kumar</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="95" t="inlineStr">
+        <is>
+          <t>Aug 16</t>
+        </is>
+      </c>
+      <c r="B94" s="95" t="inlineStr">
+        <is>
+          <t>10:40AM</t>
+        </is>
+      </c>
+      <c r="C94" s="95" t="inlineStr">
+        <is>
+          <t>10:55AM</t>
+        </is>
+      </c>
+      <c r="D94" s="95" t="inlineStr">
+        <is>
+          <t>Under 26</t>
+        </is>
+      </c>
+      <c r="E94" s="95" t="n">
+        <v>46</v>
+      </c>
+      <c r="F94" s="95" t="inlineStr">
+        <is>
+          <t>U26-10</t>
+        </is>
+      </c>
+      <c r="G94" s="95" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="H94" s="95" t="inlineStr">
+        <is>
+          <t>Pranit Shriyan</t>
+        </is>
+      </c>
+      <c r="I94" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J94" s="95" t="inlineStr">
+        <is>
+          <t>Rahul Garg</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="94" t="inlineStr">
+        <is>
+          <t>Aug 16</t>
+        </is>
+      </c>
+      <c r="B95" s="94" t="inlineStr">
+        <is>
+          <t>10:55AM</t>
+        </is>
+      </c>
+      <c r="C95" s="94" t="inlineStr">
+        <is>
+          <t>11:10AM</t>
+        </is>
+      </c>
+      <c r="D95" s="94" t="inlineStr">
+        <is>
+          <t>Under 26</t>
+        </is>
+      </c>
+      <c r="E95" s="94" t="n">
+        <v>47</v>
+      </c>
+      <c r="F95" s="94" t="inlineStr">
+        <is>
+          <t>U26-5</t>
+        </is>
+      </c>
+      <c r="G95" s="94" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="H95" s="94" t="inlineStr">
+        <is>
+          <t>Aaditya Kumar</t>
+        </is>
+      </c>
+      <c r="I95" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J95" s="94" t="inlineStr">
+        <is>
+          <t>Hryday Goyal</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="95" t="inlineStr">
+        <is>
+          <t>Aug 16</t>
+        </is>
+      </c>
+      <c r="B96" s="95" t="inlineStr">
+        <is>
+          <t>11:05AM</t>
+        </is>
+      </c>
+      <c r="C96" s="95" t="inlineStr">
+        <is>
+          <t>11:20AM</t>
+        </is>
+      </c>
+      <c r="D96" s="95" t="inlineStr">
+        <is>
+          <t>Under 46</t>
+        </is>
+      </c>
+      <c r="E96" s="95" t="n">
+        <v>48</v>
+      </c>
+      <c r="F96" s="95" t="inlineStr">
+        <is>
+          <t>U46-GB-1</t>
+        </is>
+      </c>
+      <c r="G96" s="95" t="inlineStr">
+        <is>
+          <t>Table 1</t>
+        </is>
+      </c>
+      <c r="H96" s="95" t="inlineStr">
+        <is>
+          <t>Nikunj Jhala</t>
+        </is>
+      </c>
+      <c r="I96" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J96" s="95" t="inlineStr">
+        <is>
+          <t>Piyush Makharia</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="94" t="inlineStr">
+        <is>
+          <t>Aug 16</t>
+        </is>
+      </c>
+      <c r="B97" s="94" t="inlineStr">
+        <is>
+          <t>11:20AM</t>
+        </is>
+      </c>
+      <c r="C97" s="94" t="inlineStr">
+        <is>
+          <t>11:35AM</t>
+        </is>
+      </c>
+      <c r="D97" s="94" t="inlineStr">
+        <is>
+          <t>Under 26</t>
+        </is>
+      </c>
+      <c r="E97" s="94" t="n">
+        <v>49</v>
+      </c>
+      <c r="F97" s="94" t="inlineStr">
+        <is>
+          <t>U26-7</t>
+        </is>
+      </c>
+      <c r="G97" s="94" t="inlineStr">
+        <is>
+          <t>Table 1</t>
+        </is>
+      </c>
+      <c r="H97" s="94" t="inlineStr">
+        <is>
+          <t>Aaditya Kumar</t>
+        </is>
+      </c>
+      <c r="I97" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J97" s="94" t="inlineStr">
+        <is>
+          <t>Rahul Garg</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="95" t="inlineStr">
+        <is>
+          <t>Aug 16</t>
+        </is>
+      </c>
+      <c r="B98" s="95" t="inlineStr">
+        <is>
+          <t>11:25AM</t>
+        </is>
+      </c>
+      <c r="C98" s="95" t="inlineStr">
+        <is>
+          <t>11:40AM</t>
+        </is>
+      </c>
+      <c r="D98" s="95" t="inlineStr">
+        <is>
+          <t>Under 46</t>
+        </is>
+      </c>
+      <c r="E98" s="95" t="n">
+        <v>50</v>
+      </c>
+      <c r="F98" s="95" t="inlineStr">
+        <is>
+          <t>U46-GB-6</t>
+        </is>
+      </c>
+      <c r="G98" s="95" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="H98" s="95" t="inlineStr">
+        <is>
+          <t>Piyush Makharia</t>
+        </is>
+      </c>
+      <c r="I98" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J98" s="95" t="inlineStr">
+        <is>
+          <t>Nilesh Bagaria</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="94" t="inlineStr">
+        <is>
+          <t>Aug 16</t>
+        </is>
+      </c>
+      <c r="B99" s="94" t="inlineStr">
+        <is>
+          <t>11:35AM</t>
+        </is>
+      </c>
+      <c r="C99" s="94" t="inlineStr">
+        <is>
+          <t>11:50AM</t>
+        </is>
+      </c>
+      <c r="D99" s="94" t="inlineStr">
+        <is>
+          <t>Under 26</t>
+        </is>
+      </c>
+      <c r="E99" s="94" t="n">
+        <v>51</v>
+      </c>
+      <c r="F99" s="94" t="inlineStr">
+        <is>
+          <t>U26-FINAL</t>
+        </is>
+      </c>
+      <c r="G99" s="94" t="inlineStr">
+        <is>
+          <t>Table 1</t>
+        </is>
+      </c>
+      <c r="H99" s="94" t="inlineStr">
+        <is>
+          <t>Pool 1st</t>
+        </is>
+      </c>
+      <c r="I99" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J99" s="94" t="inlineStr">
+        <is>
+          <t>Pool 2nd</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="95" t="inlineStr">
+        <is>
+          <t>Aug 16</t>
+        </is>
+      </c>
+      <c r="B100" s="95" t="inlineStr">
+        <is>
+          <t>11:50AM</t>
+        </is>
+      </c>
+      <c r="C100" s="95" t="inlineStr">
+        <is>
+          <t>12:05PM</t>
+        </is>
+      </c>
+      <c r="D100" s="95" t="inlineStr">
+        <is>
+          <t>Under 46</t>
+        </is>
+      </c>
+      <c r="E100" s="95" t="n">
+        <v>52</v>
+      </c>
+      <c r="F100" s="95" t="inlineStr">
+        <is>
+          <t>U46-GB-5</t>
+        </is>
+      </c>
+      <c r="G100" s="95" t="inlineStr">
+        <is>
+          <t>Table 1</t>
+        </is>
+      </c>
+      <c r="H100" s="95" t="inlineStr">
+        <is>
+          <t>Piyush Makharia</t>
+        </is>
+      </c>
+      <c r="I100" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J100" s="95" t="inlineStr">
+        <is>
+          <t>Vinit Padia</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="94" t="inlineStr">
+        <is>
+          <t>Aug 16</t>
+        </is>
+      </c>
+      <c r="B101" s="94" t="inlineStr">
+        <is>
+          <t>3:00PM</t>
+        </is>
+      </c>
+      <c r="C101" s="94" t="inlineStr">
+        <is>
+          <t>3:15PM</t>
+        </is>
+      </c>
+      <c r="D101" s="94" t="inlineStr">
+        <is>
+          <t>Under 46</t>
+        </is>
+      </c>
+      <c r="E101" s="94" t="n">
+        <v>53</v>
+      </c>
+      <c r="F101" s="94" t="inlineStr">
+        <is>
+          <t>U46-GB-7</t>
+        </is>
+      </c>
+      <c r="G101" s="94" t="inlineStr">
+        <is>
+          <t>Table 1</t>
+        </is>
+      </c>
+      <c r="H101" s="94" t="inlineStr">
+        <is>
+          <t>Piyush Makharia</t>
+        </is>
+      </c>
+      <c r="I101" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J101" s="94" t="inlineStr">
+        <is>
+          <t>Amit Ranka</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="95" t="inlineStr">
+        <is>
+          <t>Aug 16</t>
+        </is>
+      </c>
+      <c r="B102" s="95" t="inlineStr">
+        <is>
+          <t>3:15PM</t>
+        </is>
+      </c>
+      <c r="C102" s="95" t="inlineStr">
+        <is>
+          <t>3:30PM</t>
+        </is>
+      </c>
+      <c r="D102" s="95" t="inlineStr">
+        <is>
+          <t>Under 46</t>
+        </is>
+      </c>
+      <c r="E102" s="95" t="n">
+        <v>54</v>
+      </c>
+      <c r="F102" s="95" t="inlineStr">
+        <is>
+          <t>U46-SF1</t>
+        </is>
+      </c>
+      <c r="G102" s="95" t="inlineStr">
+        <is>
+          <t>Table 1</t>
+        </is>
+      </c>
+      <c r="H102" s="95" t="inlineStr">
+        <is>
+          <t>Group B 1st</t>
+        </is>
+      </c>
+      <c r="I102" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J102" s="95" t="inlineStr">
+        <is>
+          <t>Group A 2nd</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="94" t="inlineStr">
+        <is>
+          <t>Aug 16</t>
+        </is>
+      </c>
+      <c r="B103" s="94" t="inlineStr">
+        <is>
+          <t>3:15PM</t>
+        </is>
+      </c>
+      <c r="C103" s="94" t="inlineStr">
+        <is>
+          <t>3:30PM</t>
+        </is>
+      </c>
+      <c r="D103" s="94" t="inlineStr">
+        <is>
+          <t>Under 46</t>
+        </is>
+      </c>
+      <c r="E103" s="94" t="n">
+        <v>55</v>
+      </c>
+      <c r="F103" s="94" t="inlineStr">
+        <is>
+          <t>U46-SF2</t>
+        </is>
+      </c>
+      <c r="G103" s="94" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="H103" s="94" t="inlineStr">
+        <is>
+          <t>Group A 1st</t>
+        </is>
+      </c>
+      <c r="I103" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J103" s="94" t="inlineStr">
+        <is>
+          <t>Group B 2nd</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="95" t="inlineStr">
+        <is>
+          <t>Aug 16</t>
+        </is>
+      </c>
+      <c r="B104" s="95" t="inlineStr">
+        <is>
+          <t>3:30PM</t>
+        </is>
+      </c>
+      <c r="C104" s="95" t="inlineStr">
+        <is>
+          <t>3:45PM</t>
+        </is>
+      </c>
+      <c r="D104" s="95" t="inlineStr">
+        <is>
+          <t>Under 46</t>
+        </is>
+      </c>
+      <c r="E104" s="95" t="n">
+        <v>56</v>
+      </c>
+      <c r="F104" s="95" t="inlineStr">
+        <is>
+          <t>U46-FINAL</t>
+        </is>
+      </c>
+      <c r="G104" s="95" t="inlineStr">
+        <is>
+          <t>Table 1</t>
+        </is>
+      </c>
+      <c r="H104" s="95" t="inlineStr">
+        <is>
+          <t>Winner SF1</t>
+        </is>
+      </c>
+      <c r="I104" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J104" s="95" t="inlineStr">
+        <is>
+          <t>Winner SF2</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="94" t="inlineStr">
+        <is>
+          <t>Aug 16</t>
+        </is>
+      </c>
+      <c r="B105" s="94" t="inlineStr">
+        <is>
+          <t>3:45PM</t>
+        </is>
+      </c>
+      <c r="C105" s="94" t="inlineStr">
+        <is>
+          <t>4:00PM</t>
+        </is>
+      </c>
+      <c r="D105" s="94" t="inlineStr">
+        <is>
+          <t>Above 46</t>
+        </is>
+      </c>
+      <c r="E105" s="94" t="n">
+        <v>57</v>
+      </c>
+      <c r="F105" s="94" t="inlineStr">
+        <is>
+          <t>A46-R1</t>
+        </is>
+      </c>
+      <c r="G105" s="94" t="inlineStr">
+        <is>
+          <t>Table 1</t>
+        </is>
+      </c>
+      <c r="H105" s="94" t="inlineStr">
+        <is>
+          <t>Adil Khan</t>
+        </is>
+      </c>
+      <c r="I105" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J105" s="94" t="inlineStr">
+        <is>
+          <t>Ajit nair</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="95" t="inlineStr">
+        <is>
+          <t>Aug 16</t>
+        </is>
+      </c>
+      <c r="B106" s="95" t="inlineStr">
+        <is>
+          <t>4:00PM</t>
+        </is>
+      </c>
+      <c r="C106" s="95" t="inlineStr">
+        <is>
+          <t>4:15PM</t>
+        </is>
+      </c>
+      <c r="D106" s="95" t="inlineStr">
+        <is>
+          <t>Above 46</t>
+        </is>
+      </c>
+      <c r="E106" s="95" t="n">
+        <v>58</v>
+      </c>
+      <c r="F106" s="95" t="inlineStr">
+        <is>
+          <t>A46-QF1</t>
+        </is>
+      </c>
+      <c r="G106" s="95" t="inlineStr">
+        <is>
+          <t>Table 1</t>
+        </is>
+      </c>
+      <c r="H106" s="95" t="inlineStr">
+        <is>
+          <t>Winner R1</t>
+        </is>
+      </c>
+      <c r="I106" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J106" s="95" t="inlineStr">
         <is>
           <t>Sanjay Kumar</t>
         </is>
       </c>
-      <c r="E36" s="4" t="n">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="6" t="inlineStr">
-        <is>
-          <t>Adil Khan</t>
-        </is>
-      </c>
-      <c r="B37" s="6" t="n">
-        <v>51</v>
-      </c>
-      <c r="D37" s="6" t="inlineStr">
-        <is>
-          <t>Sushil Dashpute</t>
-        </is>
-      </c>
-      <c r="E37" s="6" t="n">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>Vinod Agrawal</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="n">
-        <v>55</v>
-      </c>
-      <c r="D38" s="4" t="inlineStr">
-        <is>
-          <t>HARSHAPRABHAT SHETTY</t>
-        </is>
-      </c>
-      <c r="E38" s="4" t="n">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="6" t="inlineStr">
-        <is>
-          <t>Ajit nair</t>
-        </is>
-      </c>
-      <c r="B39" s="6" t="n">
+    </row>
+    <row r="107">
+      <c r="A107" s="94" t="inlineStr">
+        <is>
+          <t>Aug 16</t>
+        </is>
+      </c>
+      <c r="B107" s="94" t="inlineStr">
+        <is>
+          <t>4:15PM</t>
+        </is>
+      </c>
+      <c r="C107" s="94" t="inlineStr">
+        <is>
+          <t>4:30PM</t>
+        </is>
+      </c>
+      <c r="D107" s="94" t="inlineStr">
+        <is>
+          <t>Above 46</t>
+        </is>
+      </c>
+      <c r="E107" s="94" t="n">
         <v>59</v>
       </c>
-      <c r="D39" s="6" t="inlineStr">
-        <is>
-          <t>Kishore Kumar</t>
-        </is>
-      </c>
-      <c r="E39" s="6" t="n">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>Ghansyam nawani</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="n">
+      <c r="F107" s="94" t="inlineStr">
+        <is>
+          <t>A46-SF1</t>
+        </is>
+      </c>
+      <c r="G107" s="94" t="inlineStr">
+        <is>
+          <t>Table 1</t>
+        </is>
+      </c>
+      <c r="H107" s="94" t="inlineStr">
+        <is>
+          <t>Winner QF1</t>
+        </is>
+      </c>
+      <c r="I107" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J107" s="94" t="inlineStr">
+        <is>
+          <t>Winner QF2</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="95" t="inlineStr">
+        <is>
+          <t>Aug 16</t>
+        </is>
+      </c>
+      <c r="B108" s="95" t="inlineStr">
+        <is>
+          <t>4:30PM</t>
+        </is>
+      </c>
+      <c r="C108" s="95" t="inlineStr">
+        <is>
+          <t>4:45PM</t>
+        </is>
+      </c>
+      <c r="D108" s="95" t="inlineStr">
+        <is>
+          <t>Above 46</t>
+        </is>
+      </c>
+      <c r="E108" s="95" t="n">
         <v>60</v>
       </c>
-      <c r="D40" s="4" t="n"/>
-      <c r="E40" s="1" t="n"/>
-    </row>
-    <row r="43" ht="20.1" customHeight="1">
-      <c r="A43" s="16" t="inlineStr">
-        <is>
-          <t>MATCH SCHEDULE (chronological, interleaved with other sports to avoid player conflicts)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="26" t="inlineStr">
-        <is>
-          <t>Day</t>
-        </is>
-      </c>
-      <c r="B44" s="26" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="C44" s="26" t="inlineStr">
-        <is>
-          <t>End</t>
-        </is>
-      </c>
-      <c r="D44" s="26" t="inlineStr">
-        <is>
-          <t>Band</t>
-        </is>
-      </c>
-      <c r="E44" s="26" t="inlineStr">
-        <is>
-          <t>Match #</t>
-        </is>
-      </c>
-      <c r="F44" s="26" t="inlineStr">
-        <is>
-          <t>Match</t>
-        </is>
-      </c>
-      <c r="G44" s="26" t="inlineStr">
-        <is>
-          <t>Resource</t>
-        </is>
-      </c>
-      <c r="H44" s="26" t="inlineStr">
-        <is>
-          <t>Player A</t>
-        </is>
-      </c>
-      <c r="I44" s="26" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J44" s="26" t="inlineStr">
-        <is>
-          <t>Player B</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="27" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B45" s="27" t="inlineStr">
-        <is>
-          <t>8:00AM</t>
-        </is>
-      </c>
-      <c r="C45" s="27" t="inlineStr">
-        <is>
-          <t>8:15AM</t>
-        </is>
-      </c>
-      <c r="D45" s="27" t="inlineStr">
-        <is>
-          <t>Above 46</t>
-        </is>
-      </c>
-      <c r="E45" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="F45" s="27" t="inlineStr">
-        <is>
-          <t>A46-GA-1</t>
-        </is>
-      </c>
-      <c r="G45" s="27" t="inlineStr">
+      <c r="F108" s="95" t="inlineStr">
+        <is>
+          <t>A46-FINAL</t>
+        </is>
+      </c>
+      <c r="G108" s="95" t="inlineStr">
         <is>
           <t>Table 1</t>
         </is>
       </c>
-      <c r="H45" s="27" t="inlineStr">
-        <is>
-          <t>Mukul Joshi</t>
-        </is>
-      </c>
-      <c r="I45" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J45" s="27" t="inlineStr">
-        <is>
-          <t>Adil Khan</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="28" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B46" s="28" t="inlineStr">
-        <is>
-          <t>8:00AM</t>
-        </is>
-      </c>
-      <c r="C46" s="28" t="inlineStr">
-        <is>
-          <t>8:15AM</t>
-        </is>
-      </c>
-      <c r="D46" s="28" t="inlineStr">
-        <is>
-          <t>Above 46</t>
-        </is>
-      </c>
-      <c r="E46" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="F46" s="28" t="inlineStr">
-        <is>
-          <t>A46-GA-8</t>
-        </is>
-      </c>
-      <c r="G46" s="28" t="inlineStr">
-        <is>
-          <t>Table 2</t>
-        </is>
-      </c>
-      <c r="H46" s="28" t="inlineStr">
-        <is>
-          <t>Vinod Agrawal</t>
-        </is>
-      </c>
-      <c r="I46" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J46" s="28" t="inlineStr">
-        <is>
-          <t>Ajit nair</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="27" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B47" s="27" t="inlineStr">
-        <is>
-          <t>8:15AM</t>
-        </is>
-      </c>
-      <c r="C47" s="27" t="inlineStr">
-        <is>
-          <t>8:30AM</t>
-        </is>
-      </c>
-      <c r="D47" s="27" t="inlineStr">
-        <is>
-          <t>Above 46</t>
-        </is>
-      </c>
-      <c r="E47" s="27" t="n">
-        <v>3</v>
-      </c>
-      <c r="F47" s="27" t="inlineStr">
-        <is>
-          <t>A46-GB-1</t>
-        </is>
-      </c>
-      <c r="G47" s="27" t="inlineStr">
-        <is>
-          <t>Table 1</t>
-        </is>
-      </c>
-      <c r="H47" s="27" t="inlineStr">
-        <is>
-          <t>Sanjay Kumar</t>
-        </is>
-      </c>
-      <c r="I47" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J47" s="27" t="inlineStr">
-        <is>
-          <t>Sushil Dashpute</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="28" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B48" s="28" t="inlineStr">
-        <is>
-          <t>8:15AM</t>
-        </is>
-      </c>
-      <c r="C48" s="28" t="inlineStr">
-        <is>
-          <t>8:30AM</t>
-        </is>
-      </c>
-      <c r="D48" s="28" t="inlineStr">
-        <is>
-          <t>Above 46</t>
-        </is>
-      </c>
-      <c r="E48" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="F48" s="28" t="inlineStr">
-        <is>
-          <t>A46-GB-6</t>
-        </is>
-      </c>
-      <c r="G48" s="28" t="inlineStr">
-        <is>
-          <t>Table 2</t>
-        </is>
-      </c>
-      <c r="H48" s="28" t="inlineStr">
-        <is>
-          <t>HARSHAPRABHAT SHETTY</t>
-        </is>
-      </c>
-      <c r="I48" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J48" s="28" t="inlineStr">
-        <is>
-          <t>Kishore Kumar</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="27" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B49" s="27" t="inlineStr">
-        <is>
-          <t>8:30AM</t>
-        </is>
-      </c>
-      <c r="C49" s="27" t="inlineStr">
-        <is>
-          <t>8:45AM</t>
-        </is>
-      </c>
-      <c r="D49" s="27" t="inlineStr">
-        <is>
-          <t>Above 46</t>
-        </is>
-      </c>
-      <c r="E49" s="27" t="n">
-        <v>5</v>
-      </c>
-      <c r="F49" s="27" t="inlineStr">
-        <is>
-          <t>A46-GA-2</t>
-        </is>
-      </c>
-      <c r="G49" s="27" t="inlineStr">
-        <is>
-          <t>Table 1</t>
-        </is>
-      </c>
-      <c r="H49" s="27" t="inlineStr">
-        <is>
-          <t>Mukul Joshi</t>
-        </is>
-      </c>
-      <c r="I49" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J49" s="27" t="inlineStr">
-        <is>
-          <t>Vinod Agrawal</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="28" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B50" s="28" t="inlineStr">
-        <is>
-          <t>8:30AM</t>
-        </is>
-      </c>
-      <c r="C50" s="28" t="inlineStr">
-        <is>
-          <t>8:45AM</t>
-        </is>
-      </c>
-      <c r="D50" s="28" t="inlineStr">
-        <is>
-          <t>Above 46</t>
-        </is>
-      </c>
-      <c r="E50" s="28" t="n">
-        <v>6</v>
-      </c>
-      <c r="F50" s="28" t="inlineStr">
-        <is>
-          <t>A46-GA-6</t>
-        </is>
-      </c>
-      <c r="G50" s="28" t="inlineStr">
-        <is>
-          <t>Table 2</t>
-        </is>
-      </c>
-      <c r="H50" s="28" t="inlineStr">
-        <is>
-          <t>Adil Khan</t>
-        </is>
-      </c>
-      <c r="I50" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J50" s="28" t="inlineStr">
-        <is>
-          <t>Ajit nair</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="27" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B51" s="27" t="inlineStr">
-        <is>
-          <t>8:45AM</t>
-        </is>
-      </c>
-      <c r="C51" s="27" t="inlineStr">
-        <is>
-          <t>9:00AM</t>
-        </is>
-      </c>
-      <c r="D51" s="27" t="inlineStr">
-        <is>
-          <t>Above 46</t>
-        </is>
-      </c>
-      <c r="E51" s="27" t="n">
-        <v>7</v>
-      </c>
-      <c r="F51" s="27" t="inlineStr">
-        <is>
-          <t>A46-GB-2</t>
-        </is>
-      </c>
-      <c r="G51" s="27" t="inlineStr">
-        <is>
-          <t>Table 1</t>
-        </is>
-      </c>
-      <c r="H51" s="27" t="inlineStr">
-        <is>
-          <t>Sanjay Kumar</t>
-        </is>
-      </c>
-      <c r="I51" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J51" s="27" t="inlineStr">
-        <is>
-          <t>HARSHAPRABHAT SHETTY</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="28" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B52" s="28" t="inlineStr">
-        <is>
-          <t>8:45AM</t>
-        </is>
-      </c>
-      <c r="C52" s="28" t="inlineStr">
-        <is>
-          <t>9:00AM</t>
-        </is>
-      </c>
-      <c r="D52" s="28" t="inlineStr">
-        <is>
-          <t>Above 46</t>
-        </is>
-      </c>
-      <c r="E52" s="28" t="n">
-        <v>8</v>
-      </c>
-      <c r="F52" s="28" t="inlineStr">
-        <is>
-          <t>A46-GB-5</t>
-        </is>
-      </c>
-      <c r="G52" s="28" t="inlineStr">
-        <is>
-          <t>Table 2</t>
-        </is>
-      </c>
-      <c r="H52" s="28" t="inlineStr">
-        <is>
-          <t>Sushil Dashpute</t>
-        </is>
-      </c>
-      <c r="I52" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J52" s="28" t="inlineStr">
-        <is>
-          <t>Kishore Kumar</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="27" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B53" s="27" t="inlineStr">
-        <is>
-          <t>9:00AM</t>
-        </is>
-      </c>
-      <c r="C53" s="27" t="inlineStr">
-        <is>
-          <t>9:15AM</t>
-        </is>
-      </c>
-      <c r="D53" s="27" t="inlineStr">
-        <is>
-          <t>Above 46</t>
-        </is>
-      </c>
-      <c r="E53" s="27" t="n">
-        <v>9</v>
-      </c>
-      <c r="F53" s="27" t="inlineStr">
-        <is>
-          <t>A46-GA-3</t>
-        </is>
-      </c>
-      <c r="G53" s="27" t="inlineStr">
-        <is>
-          <t>Table 1</t>
-        </is>
-      </c>
-      <c r="H53" s="27" t="inlineStr">
-        <is>
-          <t>Mukul Joshi</t>
-        </is>
-      </c>
-      <c r="I53" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J53" s="27" t="inlineStr">
-        <is>
-          <t>Ajit nair</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="28" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B54" s="28" t="inlineStr">
-        <is>
-          <t>9:00AM</t>
-        </is>
-      </c>
-      <c r="C54" s="28" t="inlineStr">
-        <is>
-          <t>9:15AM</t>
-        </is>
-      </c>
-      <c r="D54" s="28" t="inlineStr">
-        <is>
-          <t>Above 46</t>
-        </is>
-      </c>
-      <c r="E54" s="28" t="n">
-        <v>10</v>
-      </c>
-      <c r="F54" s="28" t="inlineStr">
-        <is>
-          <t>A46-GA-5</t>
-        </is>
-      </c>
-      <c r="G54" s="28" t="inlineStr">
-        <is>
-          <t>Table 2</t>
-        </is>
-      </c>
-      <c r="H54" s="28" t="inlineStr">
-        <is>
-          <t>Adil Khan</t>
-        </is>
-      </c>
-      <c r="I54" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J54" s="28" t="inlineStr">
-        <is>
-          <t>Vinod Agrawal</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="27" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B55" s="27" t="inlineStr">
-        <is>
-          <t>9:15AM</t>
-        </is>
-      </c>
-      <c r="C55" s="27" t="inlineStr">
-        <is>
-          <t>9:30AM</t>
-        </is>
-      </c>
-      <c r="D55" s="27" t="inlineStr">
-        <is>
-          <t>Above 46</t>
-        </is>
-      </c>
-      <c r="E55" s="27" t="n">
-        <v>11</v>
-      </c>
-      <c r="F55" s="27" t="inlineStr">
-        <is>
-          <t>A46-GB-3</t>
-        </is>
-      </c>
-      <c r="G55" s="27" t="inlineStr">
-        <is>
-          <t>Table 1</t>
-        </is>
-      </c>
-      <c r="H55" s="27" t="inlineStr">
-        <is>
-          <t>Sanjay Kumar</t>
-        </is>
-      </c>
-      <c r="I55" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J55" s="27" t="inlineStr">
-        <is>
-          <t>Kishore Kumar</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="28" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B56" s="28" t="inlineStr">
-        <is>
-          <t>9:15AM</t>
-        </is>
-      </c>
-      <c r="C56" s="28" t="inlineStr">
-        <is>
-          <t>9:30AM</t>
-        </is>
-      </c>
-      <c r="D56" s="28" t="inlineStr">
-        <is>
-          <t>Above 46</t>
-        </is>
-      </c>
-      <c r="E56" s="28" t="n">
-        <v>12</v>
-      </c>
-      <c r="F56" s="28" t="inlineStr">
-        <is>
-          <t>A46-GB-4</t>
-        </is>
-      </c>
-      <c r="G56" s="28" t="inlineStr">
-        <is>
-          <t>Table 2</t>
-        </is>
-      </c>
-      <c r="H56" s="28" t="inlineStr">
-        <is>
-          <t>Sushil Dashpute</t>
-        </is>
-      </c>
-      <c r="I56" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J56" s="28" t="inlineStr">
-        <is>
-          <t>HARSHAPRABHAT SHETTY</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="27" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B57" s="27" t="inlineStr">
-        <is>
-          <t>11:50AM</t>
-        </is>
-      </c>
-      <c r="C57" s="27" t="inlineStr">
-        <is>
-          <t>12:05PM</t>
-        </is>
-      </c>
-      <c r="D57" s="27" t="inlineStr">
-        <is>
-          <t>Above 46</t>
-        </is>
-      </c>
-      <c r="E57" s="27" t="n">
-        <v>13</v>
-      </c>
-      <c r="F57" s="27" t="inlineStr">
-        <is>
-          <t>A46-GA-4</t>
-        </is>
-      </c>
-      <c r="G57" s="27" t="inlineStr">
-        <is>
-          <t>Table 1</t>
-        </is>
-      </c>
-      <c r="H57" s="27" t="inlineStr">
-        <is>
-          <t>Mukul Joshi</t>
-        </is>
-      </c>
-      <c r="I57" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J57" s="27" t="inlineStr">
-        <is>
-          <t>Ghansyam nawani</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="28" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B58" s="28" t="inlineStr">
-        <is>
-          <t>11:50AM</t>
-        </is>
-      </c>
-      <c r="C58" s="28" t="inlineStr">
-        <is>
-          <t>12:05PM</t>
-        </is>
-      </c>
-      <c r="D58" s="28" t="inlineStr">
-        <is>
-          <t>Under 15</t>
-        </is>
-      </c>
-      <c r="E58" s="28" t="n">
-        <v>14</v>
-      </c>
-      <c r="F58" s="28" t="inlineStr">
-        <is>
-          <t>U15-GA-2</t>
-        </is>
-      </c>
-      <c r="G58" s="28" t="inlineStr">
-        <is>
-          <t>Table 2</t>
-        </is>
-      </c>
-      <c r="H58" s="28" t="inlineStr">
-        <is>
-          <t>Shaurya Tripathi</t>
-        </is>
-      </c>
-      <c r="I58" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J58" s="28" t="inlineStr">
-        <is>
-          <t>Aadit Joshi</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="27" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B59" s="27" t="inlineStr">
-        <is>
-          <t>3:55PM</t>
-        </is>
-      </c>
-      <c r="C59" s="27" t="inlineStr">
-        <is>
-          <t>4:10PM</t>
-        </is>
-      </c>
-      <c r="D59" s="27" t="inlineStr">
-        <is>
-          <t>Above 46</t>
-        </is>
-      </c>
-      <c r="E59" s="27" t="n">
-        <v>15</v>
-      </c>
-      <c r="F59" s="27" t="inlineStr">
-        <is>
-          <t>A46-GA-7</t>
-        </is>
-      </c>
-      <c r="G59" s="27" t="inlineStr">
-        <is>
-          <t>Table 1</t>
-        </is>
-      </c>
-      <c r="H59" s="27" t="inlineStr">
-        <is>
-          <t>Adil Khan</t>
-        </is>
-      </c>
-      <c r="I59" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J59" s="27" t="inlineStr">
-        <is>
-          <t>Ghansyam nawani</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="28" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B60" s="28" t="inlineStr">
-        <is>
-          <t>4:10PM</t>
-        </is>
-      </c>
-      <c r="C60" s="28" t="inlineStr">
-        <is>
-          <t>4:25PM</t>
-        </is>
-      </c>
-      <c r="D60" s="28" t="inlineStr">
-        <is>
-          <t>Under 15</t>
-        </is>
-      </c>
-      <c r="E60" s="28" t="n">
-        <v>16</v>
-      </c>
-      <c r="F60" s="28" t="inlineStr">
-        <is>
-          <t>U15-GA-3</t>
-        </is>
-      </c>
-      <c r="G60" s="28" t="inlineStr">
-        <is>
-          <t>Table 2</t>
-        </is>
-      </c>
-      <c r="H60" s="28" t="inlineStr">
-        <is>
-          <t>Parth yadav</t>
-        </is>
-      </c>
-      <c r="I60" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J60" s="28" t="inlineStr">
-        <is>
-          <t>Aadit Joshi</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="27" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B61" s="27" t="inlineStr">
-        <is>
-          <t>4:20PM</t>
-        </is>
-      </c>
-      <c r="C61" s="27" t="inlineStr">
-        <is>
-          <t>4:35PM</t>
-        </is>
-      </c>
-      <c r="D61" s="27" t="inlineStr">
-        <is>
-          <t>Above 46</t>
-        </is>
-      </c>
-      <c r="E61" s="27" t="n">
-        <v>17</v>
-      </c>
-      <c r="F61" s="27" t="inlineStr">
-        <is>
-          <t>A46-GA-9</t>
-        </is>
-      </c>
-      <c r="G61" s="27" t="inlineStr">
-        <is>
-          <t>Table 1</t>
-        </is>
-      </c>
-      <c r="H61" s="27" t="inlineStr">
-        <is>
-          <t>Vinod Agrawal</t>
-        </is>
-      </c>
-      <c r="I61" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J61" s="27" t="inlineStr">
-        <is>
-          <t>Ghansyam nawani</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="28" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B62" s="28" t="inlineStr">
-        <is>
-          <t>4:25PM</t>
-        </is>
-      </c>
-      <c r="C62" s="28" t="inlineStr">
-        <is>
-          <t>4:40PM</t>
-        </is>
-      </c>
-      <c r="D62" s="28" t="inlineStr">
-        <is>
-          <t>Under 15</t>
-        </is>
-      </c>
-      <c r="E62" s="28" t="n">
-        <v>18</v>
-      </c>
-      <c r="F62" s="28" t="inlineStr">
-        <is>
-          <t>U15-GB-2</t>
-        </is>
-      </c>
-      <c r="G62" s="28" t="inlineStr">
-        <is>
-          <t>Table 2</t>
-        </is>
-      </c>
-      <c r="H62" s="28" t="inlineStr">
-        <is>
-          <t>Viaan Neema</t>
-        </is>
-      </c>
-      <c r="I62" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J62" s="28" t="inlineStr">
-        <is>
-          <t>Hridh jhala</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="27" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B63" s="27" t="inlineStr">
-        <is>
-          <t>4:40PM</t>
-        </is>
-      </c>
-      <c r="C63" s="27" t="inlineStr">
-        <is>
-          <t>4:55PM</t>
-        </is>
-      </c>
-      <c r="D63" s="27" t="inlineStr">
-        <is>
-          <t>Under 26</t>
-        </is>
-      </c>
-      <c r="E63" s="27" t="n">
-        <v>19</v>
-      </c>
-      <c r="F63" s="27" t="inlineStr">
-        <is>
-          <t>U26-1</t>
-        </is>
-      </c>
-      <c r="G63" s="27" t="inlineStr">
-        <is>
-          <t>Table 2</t>
-        </is>
-      </c>
-      <c r="H63" s="27" t="inlineStr">
-        <is>
-          <t>Yuvraj jain</t>
-        </is>
-      </c>
-      <c r="I63" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J63" s="27" t="inlineStr">
-        <is>
-          <t>Aaditya Kumar</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="28" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B64" s="28" t="inlineStr">
-        <is>
-          <t>4:45PM</t>
-        </is>
-      </c>
-      <c r="C64" s="28" t="inlineStr">
-        <is>
-          <t>5:00PM</t>
-        </is>
-      </c>
-      <c r="D64" s="28" t="inlineStr">
-        <is>
-          <t>Above 46</t>
-        </is>
-      </c>
-      <c r="E64" s="28" t="n">
-        <v>20</v>
-      </c>
-      <c r="F64" s="28" t="inlineStr">
-        <is>
-          <t>A46-GA-10</t>
-        </is>
-      </c>
-      <c r="G64" s="28" t="inlineStr">
-        <is>
-          <t>Table 1</t>
-        </is>
-      </c>
-      <c r="H64" s="28" t="inlineStr">
-        <is>
-          <t>Ajit nair</t>
-        </is>
-      </c>
-      <c r="I64" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J64" s="28" t="inlineStr">
-        <is>
-          <t>Ghansyam nawani</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="27" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B65" s="27" t="inlineStr">
-        <is>
-          <t>4:55PM</t>
-        </is>
-      </c>
-      <c r="C65" s="27" t="inlineStr">
-        <is>
-          <t>5:10PM</t>
-        </is>
-      </c>
-      <c r="D65" s="27" t="inlineStr">
-        <is>
-          <t>Under 26</t>
-        </is>
-      </c>
-      <c r="E65" s="27" t="n">
-        <v>21</v>
-      </c>
-      <c r="F65" s="27" t="inlineStr">
-        <is>
-          <t>U26-8</t>
-        </is>
-      </c>
-      <c r="G65" s="27" t="inlineStr">
-        <is>
-          <t>Table 2</t>
-        </is>
-      </c>
-      <c r="H65" s="27" t="inlineStr">
-        <is>
-          <t>Hryday Goyal</t>
-        </is>
-      </c>
-      <c r="I65" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J65" s="27" t="inlineStr">
-        <is>
-          <t>Pranit Shriyan</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="28" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B66" s="28" t="inlineStr">
-        <is>
-          <t>5:00PM</t>
-        </is>
-      </c>
-      <c r="C66" s="28" t="inlineStr">
-        <is>
-          <t>5:15PM</t>
-        </is>
-      </c>
-      <c r="D66" s="28" t="inlineStr">
-        <is>
-          <t>Under 36</t>
-        </is>
-      </c>
-      <c r="E66" s="28" t="n">
-        <v>22</v>
-      </c>
-      <c r="F66" s="28" t="inlineStr">
-        <is>
-          <t>U36-GA-1</t>
-        </is>
-      </c>
-      <c r="G66" s="28" t="inlineStr">
-        <is>
-          <t>Table 1</t>
-        </is>
-      </c>
-      <c r="H66" s="28" t="inlineStr">
-        <is>
-          <t>Jashit Bajaj</t>
-        </is>
-      </c>
-      <c r="I66" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J66" s="28" t="inlineStr">
-        <is>
-          <t>Ravi Modi</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="27" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B67" s="27" t="inlineStr">
-        <is>
-          <t>5:10PM</t>
-        </is>
-      </c>
-      <c r="C67" s="27" t="inlineStr">
-        <is>
-          <t>5:25PM</t>
-        </is>
-      </c>
-      <c r="D67" s="27" t="inlineStr">
-        <is>
-          <t>Under 15</t>
-        </is>
-      </c>
-      <c r="E67" s="27" t="n">
-        <v>23</v>
-      </c>
-      <c r="F67" s="27" t="inlineStr">
-        <is>
-          <t>U15-GA-1</t>
-        </is>
-      </c>
-      <c r="G67" s="27" t="inlineStr">
-        <is>
-          <t>Table 2</t>
-        </is>
-      </c>
-      <c r="H67" s="27" t="inlineStr">
-        <is>
-          <t>Shaurya Tripathi</t>
-        </is>
-      </c>
-      <c r="I67" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J67" s="27" t="inlineStr">
-        <is>
-          <t>Parth yadav</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="28" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B68" s="28" t="inlineStr">
-        <is>
-          <t>5:15PM</t>
-        </is>
-      </c>
-      <c r="C68" s="28" t="inlineStr">
-        <is>
-          <t>5:30PM</t>
-        </is>
-      </c>
-      <c r="D68" s="28" t="inlineStr">
-        <is>
-          <t>Under 15</t>
-        </is>
-      </c>
-      <c r="E68" s="28" t="n">
-        <v>24</v>
-      </c>
-      <c r="F68" s="28" t="inlineStr">
-        <is>
-          <t>U15-GB-1</t>
-        </is>
-      </c>
-      <c r="G68" s="28" t="inlineStr">
-        <is>
-          <t>Table 1</t>
-        </is>
-      </c>
-      <c r="H68" s="28" t="inlineStr">
-        <is>
-          <t>Viaan Neema</t>
-        </is>
-      </c>
-      <c r="I68" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J68" s="28" t="inlineStr">
-        <is>
-          <t>Yash agarwal</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="27" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B69" s="27" t="inlineStr">
-        <is>
-          <t>5:25PM</t>
-        </is>
-      </c>
-      <c r="C69" s="27" t="inlineStr">
-        <is>
-          <t>5:40PM</t>
-        </is>
-      </c>
-      <c r="D69" s="27" t="inlineStr">
-        <is>
-          <t>Under 26</t>
-        </is>
-      </c>
-      <c r="E69" s="27" t="n">
-        <v>25</v>
-      </c>
-      <c r="F69" s="27" t="inlineStr">
-        <is>
-          <t>U26-2</t>
-        </is>
-      </c>
-      <c r="G69" s="27" t="inlineStr">
-        <is>
-          <t>Table 2</t>
-        </is>
-      </c>
-      <c r="H69" s="27" t="inlineStr">
-        <is>
-          <t>Yuvraj jain</t>
-        </is>
-      </c>
-      <c r="I69" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J69" s="27" t="inlineStr">
-        <is>
-          <t>Hryday Goyal</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="28" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B70" s="28" t="inlineStr">
-        <is>
-          <t>5:30PM</t>
-        </is>
-      </c>
-      <c r="C70" s="28" t="inlineStr">
-        <is>
-          <t>5:45PM</t>
-        </is>
-      </c>
-      <c r="D70" s="28" t="inlineStr">
-        <is>
-          <t>Under 26</t>
-        </is>
-      </c>
-      <c r="E70" s="28" t="n">
-        <v>26</v>
-      </c>
-      <c r="F70" s="28" t="inlineStr">
-        <is>
-          <t>U26-6</t>
-        </is>
-      </c>
-      <c r="G70" s="28" t="inlineStr">
-        <is>
-          <t>Table 1</t>
-        </is>
-      </c>
-      <c r="H70" s="28" t="inlineStr">
-        <is>
-          <t>Aaditya Kumar</t>
-        </is>
-      </c>
-      <c r="I70" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J70" s="28" t="inlineStr">
-        <is>
-          <t>Pranit Shriyan</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="27" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B71" s="27" t="inlineStr">
-        <is>
-          <t>5:40PM</t>
-        </is>
-      </c>
-      <c r="C71" s="27" t="inlineStr">
-        <is>
-          <t>5:55PM</t>
-        </is>
-      </c>
-      <c r="D71" s="27" t="inlineStr">
-        <is>
-          <t>Under 15</t>
-        </is>
-      </c>
-      <c r="E71" s="27" t="n">
-        <v>27</v>
-      </c>
-      <c r="F71" s="27" t="inlineStr">
-        <is>
-          <t>U15-GB-3</t>
-        </is>
-      </c>
-      <c r="G71" s="27" t="inlineStr">
-        <is>
-          <t>Table 2</t>
-        </is>
-      </c>
-      <c r="H71" s="27" t="inlineStr">
-        <is>
-          <t>Yash agarwal</t>
-        </is>
-      </c>
-      <c r="I71" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J71" s="27" t="inlineStr">
-        <is>
-          <t>Hridh jhala</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="28" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B72" s="28" t="inlineStr">
-        <is>
-          <t>5:45PM</t>
-        </is>
-      </c>
-      <c r="C72" s="28" t="inlineStr">
-        <is>
-          <t>6:00PM</t>
-        </is>
-      </c>
-      <c r="D72" s="28" t="inlineStr">
-        <is>
-          <t>Under 36</t>
-        </is>
-      </c>
-      <c r="E72" s="28" t="n">
-        <v>28</v>
-      </c>
-      <c r="F72" s="28" t="inlineStr">
-        <is>
-          <t>U36-GA-2</t>
-        </is>
-      </c>
-      <c r="G72" s="28" t="inlineStr">
-        <is>
-          <t>Table 1</t>
-        </is>
-      </c>
-      <c r="H72" s="28" t="inlineStr">
-        <is>
-          <t>Jashit Bajaj</t>
-        </is>
-      </c>
-      <c r="I72" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J72" s="28" t="inlineStr">
-        <is>
-          <t>Tapabrata Dutta</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="27" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B73" s="27" t="inlineStr">
-        <is>
-          <t>5:55PM</t>
-        </is>
-      </c>
-      <c r="C73" s="27" t="inlineStr">
-        <is>
-          <t>6:10PM</t>
-        </is>
-      </c>
-      <c r="D73" s="27" t="inlineStr">
-        <is>
-          <t>Under 26</t>
-        </is>
-      </c>
-      <c r="E73" s="27" t="n">
-        <v>29</v>
-      </c>
-      <c r="F73" s="27" t="inlineStr">
-        <is>
-          <t>U26-3</t>
-        </is>
-      </c>
-      <c r="G73" s="27" t="inlineStr">
-        <is>
-          <t>Table 2</t>
-        </is>
-      </c>
-      <c r="H73" s="27" t="inlineStr">
-        <is>
-          <t>Yuvraj jain</t>
-        </is>
-      </c>
-      <c r="I73" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J73" s="27" t="inlineStr">
-        <is>
-          <t>Pranit Shriyan</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="28" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B74" s="28" t="inlineStr">
-        <is>
-          <t>6:00PM</t>
-        </is>
-      </c>
-      <c r="C74" s="28" t="inlineStr">
-        <is>
-          <t>6:15PM</t>
-        </is>
-      </c>
-      <c r="D74" s="28" t="inlineStr">
-        <is>
-          <t>Under 26</t>
-        </is>
-      </c>
-      <c r="E74" s="28" t="n">
-        <v>30</v>
-      </c>
-      <c r="F74" s="28" t="inlineStr">
-        <is>
-          <t>U26-5</t>
-        </is>
-      </c>
-      <c r="G74" s="28" t="inlineStr">
-        <is>
-          <t>Table 1</t>
-        </is>
-      </c>
-      <c r="H74" s="28" t="inlineStr">
-        <is>
-          <t>Aaditya Kumar</t>
-        </is>
-      </c>
-      <c r="I74" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J74" s="28" t="inlineStr">
-        <is>
-          <t>Hryday Goyal</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="27" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B75" s="27" t="inlineStr">
-        <is>
-          <t>6:10PM</t>
-        </is>
-      </c>
-      <c r="C75" s="27" t="inlineStr">
-        <is>
-          <t>6:25PM</t>
-        </is>
-      </c>
-      <c r="D75" s="27" t="inlineStr">
-        <is>
-          <t>Under 36</t>
-        </is>
-      </c>
-      <c r="E75" s="27" t="n">
-        <v>31</v>
-      </c>
-      <c r="F75" s="27" t="inlineStr">
-        <is>
-          <t>U36-GB-1</t>
-        </is>
-      </c>
-      <c r="G75" s="27" t="inlineStr">
-        <is>
-          <t>Table 2</t>
-        </is>
-      </c>
-      <c r="H75" s="27" t="inlineStr">
-        <is>
-          <t>Prakshal Shah</t>
-        </is>
-      </c>
-      <c r="I75" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J75" s="27" t="inlineStr">
-        <is>
-          <t>Amar Parulekar</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="28" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B76" s="28" t="inlineStr">
-        <is>
-          <t>6:15PM</t>
-        </is>
-      </c>
-      <c r="C76" s="28" t="inlineStr">
-        <is>
-          <t>6:30PM</t>
-        </is>
-      </c>
-      <c r="D76" s="28" t="inlineStr">
-        <is>
-          <t>Under 46</t>
-        </is>
-      </c>
-      <c r="E76" s="28" t="n">
-        <v>32</v>
-      </c>
-      <c r="F76" s="28" t="inlineStr">
-        <is>
-          <t>U46-GA-1</t>
-        </is>
-      </c>
-      <c r="G76" s="28" t="inlineStr">
-        <is>
-          <t>Table 1</t>
-        </is>
-      </c>
-      <c r="H76" s="28" t="inlineStr">
-        <is>
-          <t>Dr Rahul Modi</t>
-        </is>
-      </c>
-      <c r="I76" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J76" s="28" t="inlineStr">
-        <is>
-          <t>Ankur Mahante</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="27" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B77" s="27" t="inlineStr">
-        <is>
-          <t>6:25PM</t>
-        </is>
-      </c>
-      <c r="C77" s="27" t="inlineStr">
-        <is>
-          <t>6:40PM</t>
-        </is>
-      </c>
-      <c r="D77" s="27" t="inlineStr">
-        <is>
-          <t>Under 26</t>
-        </is>
-      </c>
-      <c r="E77" s="27" t="n">
-        <v>33</v>
-      </c>
-      <c r="F77" s="27" t="inlineStr">
-        <is>
-          <t>U26-4</t>
-        </is>
-      </c>
-      <c r="G77" s="27" t="inlineStr">
-        <is>
-          <t>Table 2</t>
-        </is>
-      </c>
-      <c r="H77" s="27" t="inlineStr">
-        <is>
-          <t>Yuvraj jain</t>
-        </is>
-      </c>
-      <c r="I77" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J77" s="27" t="inlineStr">
-        <is>
-          <t>Rahul Garg</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="28" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B78" s="28" t="inlineStr">
-        <is>
-          <t>6:30PM</t>
-        </is>
-      </c>
-      <c r="C78" s="28" t="inlineStr">
-        <is>
-          <t>6:45PM</t>
-        </is>
-      </c>
-      <c r="D78" s="28" t="inlineStr">
-        <is>
-          <t>Under 36</t>
-        </is>
-      </c>
-      <c r="E78" s="28" t="n">
-        <v>34</v>
-      </c>
-      <c r="F78" s="28" t="inlineStr">
-        <is>
-          <t>U36-GA-3</t>
-        </is>
-      </c>
-      <c r="G78" s="28" t="inlineStr">
-        <is>
-          <t>Table 1</t>
-        </is>
-      </c>
-      <c r="H78" s="28" t="inlineStr">
-        <is>
-          <t>Ravi Modi</t>
-        </is>
-      </c>
-      <c r="I78" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J78" s="28" t="inlineStr">
-        <is>
-          <t>Tapabrata Dutta</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="27" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B79" s="27" t="inlineStr">
-        <is>
-          <t>6:40PM</t>
-        </is>
-      </c>
-      <c r="C79" s="27" t="inlineStr">
-        <is>
-          <t>6:55PM</t>
-        </is>
-      </c>
-      <c r="D79" s="27" t="inlineStr">
-        <is>
-          <t>Under 46</t>
-        </is>
-      </c>
-      <c r="E79" s="27" t="n">
-        <v>35</v>
-      </c>
-      <c r="F79" s="27" t="inlineStr">
-        <is>
-          <t>U46-GA-2</t>
-        </is>
-      </c>
-      <c r="G79" s="27" t="inlineStr">
-        <is>
-          <t>Table 2</t>
-        </is>
-      </c>
-      <c r="H79" s="27" t="inlineStr">
-        <is>
-          <t>Dr Rahul Modi</t>
-        </is>
-      </c>
-      <c r="I79" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J79" s="27" t="inlineStr">
-        <is>
-          <t>Sudip Parui</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="28" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B80" s="28" t="inlineStr">
-        <is>
-          <t>6:45PM</t>
-        </is>
-      </c>
-      <c r="C80" s="28" t="inlineStr">
-        <is>
-          <t>7:00PM</t>
-        </is>
-      </c>
-      <c r="D80" s="28" t="inlineStr">
-        <is>
-          <t>Under 46</t>
-        </is>
-      </c>
-      <c r="E80" s="28" t="n">
-        <v>36</v>
-      </c>
-      <c r="F80" s="28" t="inlineStr">
-        <is>
-          <t>U46-GA-6</t>
-        </is>
-      </c>
-      <c r="G80" s="28" t="inlineStr">
-        <is>
-          <t>Table 1</t>
-        </is>
-      </c>
-      <c r="H80" s="28" t="inlineStr">
-        <is>
-          <t>Ankur Mahante</t>
-        </is>
-      </c>
-      <c r="I80" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J80" s="28" t="inlineStr">
-        <is>
-          <t>Tanmay Sharma</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="27" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B81" s="27" t="inlineStr">
-        <is>
-          <t>6:55PM</t>
-        </is>
-      </c>
-      <c r="C81" s="27" t="inlineStr">
-        <is>
-          <t>7:10PM</t>
-        </is>
-      </c>
-      <c r="D81" s="27" t="inlineStr">
-        <is>
-          <t>Under 46</t>
-        </is>
-      </c>
-      <c r="E81" s="27" t="n">
-        <v>37</v>
-      </c>
-      <c r="F81" s="27" t="inlineStr">
-        <is>
-          <t>U46-GB-8</t>
-        </is>
-      </c>
-      <c r="G81" s="27" t="inlineStr">
-        <is>
-          <t>Table 2</t>
-        </is>
-      </c>
-      <c r="H81" s="27" t="inlineStr">
-        <is>
-          <t>Vinit Padia</t>
-        </is>
-      </c>
-      <c r="I81" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J81" s="27" t="inlineStr">
-        <is>
-          <t>Nilesh Bagaria</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="28" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B82" s="28" t="inlineStr">
-        <is>
-          <t>7:05PM</t>
-        </is>
-      </c>
-      <c r="C82" s="28" t="inlineStr">
-        <is>
-          <t>7:20PM</t>
-        </is>
-      </c>
-      <c r="D82" s="28" t="inlineStr">
-        <is>
-          <t>Under 46</t>
-        </is>
-      </c>
-      <c r="E82" s="28" t="n">
-        <v>38</v>
-      </c>
-      <c r="F82" s="28" t="inlineStr">
-        <is>
-          <t>U46-GA-4</t>
-        </is>
-      </c>
-      <c r="G82" s="28" t="inlineStr">
-        <is>
-          <t>Table 1</t>
-        </is>
-      </c>
-      <c r="H82" s="28" t="inlineStr">
-        <is>
-          <t>Dr Rahul Modi</t>
-        </is>
-      </c>
-      <c r="I82" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J82" s="28" t="inlineStr">
-        <is>
-          <t>Anuj Shah</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="27" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B83" s="27" t="inlineStr">
-        <is>
-          <t>7:10PM</t>
-        </is>
-      </c>
-      <c r="C83" s="27" t="inlineStr">
-        <is>
-          <t>7:25PM</t>
-        </is>
-      </c>
-      <c r="D83" s="27" t="inlineStr">
-        <is>
-          <t>Under 46</t>
-        </is>
-      </c>
-      <c r="E83" s="27" t="n">
-        <v>39</v>
-      </c>
-      <c r="F83" s="27" t="inlineStr">
-        <is>
-          <t>U46-GA-5</t>
-        </is>
-      </c>
-      <c r="G83" s="27" t="inlineStr">
-        <is>
-          <t>Table 2</t>
-        </is>
-      </c>
-      <c r="H83" s="27" t="inlineStr">
-        <is>
-          <t>Ankur Mahante</t>
-        </is>
-      </c>
-      <c r="I83" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J83" s="27" t="inlineStr">
-        <is>
-          <t>Sudip Parui</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="28" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B84" s="28" t="inlineStr">
-        <is>
-          <t>7:35PM</t>
-        </is>
-      </c>
-      <c r="C84" s="28" t="inlineStr">
-        <is>
-          <t>7:50PM</t>
-        </is>
-      </c>
-      <c r="D84" s="28" t="inlineStr">
-        <is>
-          <t>Under 46</t>
-        </is>
-      </c>
-      <c r="E84" s="28" t="n">
-        <v>40</v>
-      </c>
-      <c r="F84" s="28" t="inlineStr">
-        <is>
-          <t>U46-GA-7</t>
-        </is>
-      </c>
-      <c r="G84" s="28" t="inlineStr">
-        <is>
-          <t>Table 1</t>
-        </is>
-      </c>
-      <c r="H84" s="28" t="inlineStr">
-        <is>
-          <t>Ankur Mahante</t>
-        </is>
-      </c>
-      <c r="I84" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J84" s="28" t="inlineStr">
-        <is>
-          <t>Anuj Shah</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="27" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B85" s="27" t="inlineStr">
-        <is>
-          <t>7:40PM</t>
-        </is>
-      </c>
-      <c r="C85" s="27" t="inlineStr">
-        <is>
-          <t>7:55PM</t>
-        </is>
-      </c>
-      <c r="D85" s="27" t="inlineStr">
-        <is>
-          <t>Under 26</t>
-        </is>
-      </c>
-      <c r="E85" s="27" t="n">
-        <v>41</v>
-      </c>
-      <c r="F85" s="27" t="inlineStr">
-        <is>
-          <t>U26-10</t>
-        </is>
-      </c>
-      <c r="G85" s="27" t="inlineStr">
-        <is>
-          <t>Table 2</t>
-        </is>
-      </c>
-      <c r="H85" s="27" t="inlineStr">
-        <is>
-          <t>Pranit Shriyan</t>
-        </is>
-      </c>
-      <c r="I85" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J85" s="27" t="inlineStr">
-        <is>
-          <t>Rahul Garg</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="28" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B86" s="28" t="inlineStr">
-        <is>
-          <t>7:50PM</t>
-        </is>
-      </c>
-      <c r="C86" s="28" t="inlineStr">
-        <is>
-          <t>8:05PM</t>
-        </is>
-      </c>
-      <c r="D86" s="28" t="inlineStr">
-        <is>
-          <t>Under 46</t>
-        </is>
-      </c>
-      <c r="E86" s="28" t="n">
-        <v>42</v>
-      </c>
-      <c r="F86" s="28" t="inlineStr">
-        <is>
-          <t>U46-GB-9</t>
-        </is>
-      </c>
-      <c r="G86" s="28" t="inlineStr">
-        <is>
-          <t>Table 1</t>
-        </is>
-      </c>
-      <c r="H86" s="28" t="inlineStr">
-        <is>
-          <t>Vinit Padia</t>
-        </is>
-      </c>
-      <c r="I86" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J86" s="28" t="inlineStr">
-        <is>
-          <t>Amit Ranka</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="27" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B87" s="27" t="inlineStr">
-        <is>
-          <t>8:00PM</t>
-        </is>
-      </c>
-      <c r="C87" s="27" t="inlineStr">
-        <is>
-          <t>8:15PM</t>
-        </is>
-      </c>
-      <c r="D87" s="27" t="inlineStr">
-        <is>
-          <t>Under 36</t>
-        </is>
-      </c>
-      <c r="E87" s="27" t="n">
-        <v>43</v>
-      </c>
-      <c r="F87" s="27" t="inlineStr">
-        <is>
-          <t>U36-GB-2</t>
-        </is>
-      </c>
-      <c r="G87" s="27" t="inlineStr">
-        <is>
-          <t>Table 2</t>
-        </is>
-      </c>
-      <c r="H87" s="27" t="inlineStr">
-        <is>
-          <t>Prakshal Shah</t>
-        </is>
-      </c>
-      <c r="I87" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J87" s="27" t="inlineStr">
-        <is>
-          <t>Tej</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="28" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B88" s="28" t="inlineStr">
-        <is>
-          <t>8:05PM</t>
-        </is>
-      </c>
-      <c r="C88" s="28" t="inlineStr">
-        <is>
-          <t>8:20PM</t>
-        </is>
-      </c>
-      <c r="D88" s="28" t="inlineStr">
-        <is>
-          <t>Under 26</t>
-        </is>
-      </c>
-      <c r="E88" s="28" t="n">
-        <v>44</v>
-      </c>
-      <c r="F88" s="28" t="inlineStr">
-        <is>
-          <t>U26-7</t>
-        </is>
-      </c>
-      <c r="G88" s="28" t="inlineStr">
-        <is>
-          <t>Table 1</t>
-        </is>
-      </c>
-      <c r="H88" s="28" t="inlineStr">
-        <is>
-          <t>Aaditya Kumar</t>
-        </is>
-      </c>
-      <c r="I88" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J88" s="28" t="inlineStr">
-        <is>
-          <t>Rahul Garg</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="27" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B89" s="27" t="inlineStr">
-        <is>
-          <t>8:15PM</t>
-        </is>
-      </c>
-      <c r="C89" s="27" t="inlineStr">
-        <is>
-          <t>8:30PM</t>
-        </is>
-      </c>
-      <c r="D89" s="27" t="inlineStr">
-        <is>
-          <t>Under 46</t>
-        </is>
-      </c>
-      <c r="E89" s="27" t="n">
-        <v>45</v>
-      </c>
-      <c r="F89" s="27" t="inlineStr">
-        <is>
-          <t>U46-GA-3</t>
-        </is>
-      </c>
-      <c r="G89" s="27" t="inlineStr">
-        <is>
-          <t>Table 2</t>
-        </is>
-      </c>
-      <c r="H89" s="27" t="inlineStr">
-        <is>
-          <t>Dr Rahul Modi</t>
-        </is>
-      </c>
-      <c r="I89" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J89" s="27" t="inlineStr">
-        <is>
-          <t>Tanmay Sharma</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="28" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B90" s="28" t="inlineStr">
-        <is>
-          <t>8:20PM</t>
-        </is>
-      </c>
-      <c r="C90" s="28" t="inlineStr">
-        <is>
-          <t>8:35PM</t>
-        </is>
-      </c>
-      <c r="D90" s="28" t="inlineStr">
-        <is>
-          <t>Under 46</t>
-        </is>
-      </c>
-      <c r="E90" s="28" t="n">
-        <v>46</v>
-      </c>
-      <c r="F90" s="28" t="inlineStr">
-        <is>
-          <t>U46-GA-9</t>
-        </is>
-      </c>
-      <c r="G90" s="28" t="inlineStr">
-        <is>
-          <t>Table 1</t>
-        </is>
-      </c>
-      <c r="H90" s="28" t="inlineStr">
-        <is>
-          <t>Sudip Parui</t>
-        </is>
-      </c>
-      <c r="I90" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J90" s="28" t="inlineStr">
-        <is>
-          <t>Anuj Shah</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="27" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B91" s="27" t="inlineStr">
-        <is>
-          <t>8:30PM</t>
-        </is>
-      </c>
-      <c r="C91" s="27" t="inlineStr">
-        <is>
-          <t>8:45PM</t>
-        </is>
-      </c>
-      <c r="D91" s="27" t="inlineStr">
-        <is>
-          <t>Under 36</t>
-        </is>
-      </c>
-      <c r="E91" s="27" t="n">
-        <v>47</v>
-      </c>
-      <c r="F91" s="27" t="inlineStr">
-        <is>
-          <t>U36-GB-3</t>
-        </is>
-      </c>
-      <c r="G91" s="27" t="inlineStr">
-        <is>
-          <t>Table 2</t>
-        </is>
-      </c>
-      <c r="H91" s="27" t="inlineStr">
-        <is>
-          <t>Amar Parulekar</t>
-        </is>
-      </c>
-      <c r="I91" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J91" s="27" t="inlineStr">
-        <is>
-          <t>Tej</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="28" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B92" s="28" t="inlineStr">
-        <is>
-          <t>8:35PM</t>
-        </is>
-      </c>
-      <c r="C92" s="28" t="inlineStr">
-        <is>
-          <t>8:50PM</t>
-        </is>
-      </c>
-      <c r="D92" s="28" t="inlineStr">
-        <is>
-          <t>Under 46</t>
-        </is>
-      </c>
-      <c r="E92" s="28" t="n">
-        <v>48</v>
-      </c>
-      <c r="F92" s="28" t="inlineStr">
-        <is>
-          <t>U46-GB-3</t>
-        </is>
-      </c>
-      <c r="G92" s="28" t="inlineStr">
-        <is>
-          <t>Table 1</t>
-        </is>
-      </c>
-      <c r="H92" s="28" t="inlineStr">
-        <is>
-          <t>Nikunj Jhala</t>
-        </is>
-      </c>
-      <c r="I92" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J92" s="28" t="inlineStr">
-        <is>
-          <t>Nilesh Bagaria</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="27" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B93" s="27" t="inlineStr">
-        <is>
-          <t>8:45PM</t>
-        </is>
-      </c>
-      <c r="C93" s="27" t="inlineStr">
-        <is>
-          <t>9:00PM</t>
-        </is>
-      </c>
-      <c r="D93" s="27" t="inlineStr">
-        <is>
-          <t>Under 46</t>
-        </is>
-      </c>
-      <c r="E93" s="27" t="n">
-        <v>49</v>
-      </c>
-      <c r="F93" s="27" t="inlineStr">
-        <is>
-          <t>U46-GA-8</t>
-        </is>
-      </c>
-      <c r="G93" s="27" t="inlineStr">
-        <is>
-          <t>Table 2</t>
-        </is>
-      </c>
-      <c r="H93" s="27" t="inlineStr">
-        <is>
-          <t>Sudip Parui</t>
-        </is>
-      </c>
-      <c r="I93" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J93" s="27" t="inlineStr">
-        <is>
-          <t>Tanmay Sharma</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="28" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B94" s="28" t="inlineStr">
-        <is>
-          <t>9:00PM</t>
-        </is>
-      </c>
-      <c r="C94" s="28" t="inlineStr">
-        <is>
-          <t>9:15PM</t>
-        </is>
-      </c>
-      <c r="D94" s="28" t="inlineStr">
-        <is>
-          <t>Under 46</t>
-        </is>
-      </c>
-      <c r="E94" s="28" t="n">
-        <v>50</v>
-      </c>
-      <c r="F94" s="28" t="inlineStr">
-        <is>
-          <t>U46-GB-4</t>
-        </is>
-      </c>
-      <c r="G94" s="28" t="inlineStr">
-        <is>
-          <t>Table 1</t>
-        </is>
-      </c>
-      <c r="H94" s="28" t="inlineStr">
-        <is>
-          <t>Nikunj Jhala</t>
-        </is>
-      </c>
-      <c r="I94" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J94" s="28" t="inlineStr">
-        <is>
-          <t>Amit Ranka</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="27" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B95" s="27" t="inlineStr">
-        <is>
-          <t>9:10PM</t>
-        </is>
-      </c>
-      <c r="C95" s="27" t="inlineStr">
-        <is>
-          <t>9:25PM</t>
-        </is>
-      </c>
-      <c r="D95" s="27" t="inlineStr">
-        <is>
-          <t>Under 26</t>
-        </is>
-      </c>
-      <c r="E95" s="27" t="n">
-        <v>51</v>
-      </c>
-      <c r="F95" s="27" t="inlineStr">
-        <is>
-          <t>U26-9</t>
-        </is>
-      </c>
-      <c r="G95" s="27" t="inlineStr">
-        <is>
-          <t>Table 2</t>
-        </is>
-      </c>
-      <c r="H95" s="27" t="inlineStr">
-        <is>
-          <t>Hryday Goyal</t>
-        </is>
-      </c>
-      <c r="I95" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J95" s="27" t="inlineStr">
-        <is>
-          <t>Rahul Garg</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="28" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B96" s="28" t="inlineStr">
-        <is>
-          <t>9:15PM</t>
-        </is>
-      </c>
-      <c r="C96" s="28" t="inlineStr">
-        <is>
-          <t>9:30PM</t>
-        </is>
-      </c>
-      <c r="D96" s="28" t="inlineStr">
-        <is>
-          <t>Under 46</t>
-        </is>
-      </c>
-      <c r="E96" s="28" t="n">
-        <v>52</v>
-      </c>
-      <c r="F96" s="28" t="inlineStr">
-        <is>
-          <t>U46-GA-10</t>
-        </is>
-      </c>
-      <c r="G96" s="28" t="inlineStr">
-        <is>
-          <t>Table 1</t>
-        </is>
-      </c>
-      <c r="H96" s="28" t="inlineStr">
-        <is>
-          <t>Tanmay Sharma</t>
-        </is>
-      </c>
-      <c r="I96" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J96" s="28" t="inlineStr">
-        <is>
-          <t>Anuj Shah</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="27" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B97" s="27" t="inlineStr">
-        <is>
-          <t>9:25PM</t>
-        </is>
-      </c>
-      <c r="C97" s="27" t="inlineStr">
-        <is>
-          <t>9:40PM</t>
-        </is>
-      </c>
-      <c r="D97" s="27" t="inlineStr">
-        <is>
-          <t>Under 46</t>
-        </is>
-      </c>
-      <c r="E97" s="27" t="n">
-        <v>53</v>
-      </c>
-      <c r="F97" s="27" t="inlineStr">
-        <is>
-          <t>U46-GB-10</t>
-        </is>
-      </c>
-      <c r="G97" s="27" t="inlineStr">
-        <is>
-          <t>Table 2</t>
-        </is>
-      </c>
-      <c r="H97" s="27" t="inlineStr">
-        <is>
-          <t>Nilesh Bagaria</t>
-        </is>
-      </c>
-      <c r="I97" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J97" s="27" t="inlineStr">
-        <is>
-          <t>Amit Ranka</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="28" t="inlineStr">
-        <is>
-          <t>Aug 16</t>
-        </is>
-      </c>
-      <c r="B98" s="28" t="inlineStr">
-        <is>
-          <t>8:00AM</t>
-        </is>
-      </c>
-      <c r="C98" s="28" t="inlineStr">
-        <is>
-          <t>8:15AM</t>
-        </is>
-      </c>
-      <c r="D98" s="28" t="inlineStr">
-        <is>
-          <t>Under 46</t>
-        </is>
-      </c>
-      <c r="E98" s="28" t="n">
-        <v>54</v>
-      </c>
-      <c r="F98" s="28" t="inlineStr">
-        <is>
-          <t>U46-GB-1</t>
-        </is>
-      </c>
-      <c r="G98" s="28" t="inlineStr">
-        <is>
-          <t>Table 1</t>
-        </is>
-      </c>
-      <c r="H98" s="28" t="inlineStr">
-        <is>
-          <t>Nikunj Jhala</t>
-        </is>
-      </c>
-      <c r="I98" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J98" s="28" t="inlineStr">
-        <is>
-          <t>Piyush Makharia</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="27" t="inlineStr">
-        <is>
-          <t>Aug 16</t>
-        </is>
-      </c>
-      <c r="B99" s="27" t="inlineStr">
-        <is>
-          <t>8:25AM</t>
-        </is>
-      </c>
-      <c r="C99" s="27" t="inlineStr">
-        <is>
-          <t>8:40AM</t>
-        </is>
-      </c>
-      <c r="D99" s="27" t="inlineStr">
-        <is>
-          <t>Under 46</t>
-        </is>
-      </c>
-      <c r="E99" s="27" t="n">
-        <v>55</v>
-      </c>
-      <c r="F99" s="27" t="inlineStr">
-        <is>
-          <t>U46-GB-2</t>
-        </is>
-      </c>
-      <c r="G99" s="27" t="inlineStr">
-        <is>
-          <t>Table 1</t>
-        </is>
-      </c>
-      <c r="H99" s="27" t="inlineStr">
-        <is>
-          <t>Nikunj Jhala</t>
-        </is>
-      </c>
-      <c r="I99" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J99" s="27" t="inlineStr">
-        <is>
-          <t>Vinit Padia</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="28" t="inlineStr">
-        <is>
-          <t>Aug 16</t>
-        </is>
-      </c>
-      <c r="B100" s="28" t="inlineStr">
-        <is>
-          <t>8:25AM</t>
-        </is>
-      </c>
-      <c r="C100" s="28" t="inlineStr">
-        <is>
-          <t>8:40AM</t>
-        </is>
-      </c>
-      <c r="D100" s="28" t="inlineStr">
-        <is>
-          <t>Under 46</t>
-        </is>
-      </c>
-      <c r="E100" s="28" t="n">
-        <v>56</v>
-      </c>
-      <c r="F100" s="28" t="inlineStr">
-        <is>
-          <t>U46-GB-6</t>
-        </is>
-      </c>
-      <c r="G100" s="28" t="inlineStr">
-        <is>
-          <t>Table 2</t>
-        </is>
-      </c>
-      <c r="H100" s="28" t="inlineStr">
-        <is>
-          <t>Piyush Makharia</t>
-        </is>
-      </c>
-      <c r="I100" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J100" s="28" t="inlineStr">
-        <is>
-          <t>Nilesh Bagaria</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="27" t="inlineStr">
-        <is>
-          <t>Aug 16</t>
-        </is>
-      </c>
-      <c r="B101" s="27" t="inlineStr">
-        <is>
-          <t>8:50AM</t>
-        </is>
-      </c>
-      <c r="C101" s="27" t="inlineStr">
-        <is>
-          <t>9:05AM</t>
-        </is>
-      </c>
-      <c r="D101" s="27" t="inlineStr">
-        <is>
-          <t>Under 46</t>
-        </is>
-      </c>
-      <c r="E101" s="27" t="n">
-        <v>57</v>
-      </c>
-      <c r="F101" s="27" t="inlineStr">
-        <is>
-          <t>U46-GB-5</t>
-        </is>
-      </c>
-      <c r="G101" s="27" t="inlineStr">
-        <is>
-          <t>Table 1</t>
-        </is>
-      </c>
-      <c r="H101" s="27" t="inlineStr">
-        <is>
-          <t>Piyush Makharia</t>
-        </is>
-      </c>
-      <c r="I101" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J101" s="27" t="inlineStr">
-        <is>
-          <t>Vinit Padia</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="28" t="inlineStr">
-        <is>
-          <t>Aug 16</t>
-        </is>
-      </c>
-      <c r="B102" s="28" t="inlineStr">
-        <is>
-          <t>9:15AM</t>
-        </is>
-      </c>
-      <c r="C102" s="28" t="inlineStr">
-        <is>
-          <t>9:30AM</t>
-        </is>
-      </c>
-      <c r="D102" s="28" t="inlineStr">
-        <is>
-          <t>Under 46</t>
-        </is>
-      </c>
-      <c r="E102" s="28" t="n">
-        <v>58</v>
-      </c>
-      <c r="F102" s="28" t="inlineStr">
-        <is>
-          <t>U46-GB-7</t>
-        </is>
-      </c>
-      <c r="G102" s="28" t="inlineStr">
-        <is>
-          <t>Table 1</t>
-        </is>
-      </c>
-      <c r="H102" s="28" t="inlineStr">
-        <is>
-          <t>Piyush Makharia</t>
-        </is>
-      </c>
-      <c r="I102" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J102" s="28" t="inlineStr">
-        <is>
-          <t>Amit Ranka</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="27" t="inlineStr">
-        <is>
-          <t>Aug 16</t>
-        </is>
-      </c>
-      <c r="B103" s="27" t="inlineStr">
-        <is>
-          <t>3:50PM</t>
-        </is>
-      </c>
-      <c r="C103" s="27" t="inlineStr">
-        <is>
-          <t>4:05PM</t>
-        </is>
-      </c>
-      <c r="D103" s="27" t="inlineStr">
-        <is>
-          <t>Under 15</t>
-        </is>
-      </c>
-      <c r="E103" s="27" t="n">
-        <v>59</v>
-      </c>
-      <c r="F103" s="27" t="inlineStr">
-        <is>
-          <t>U15-SF1</t>
-        </is>
-      </c>
-      <c r="G103" s="27" t="inlineStr">
-        <is>
-          <t>Table 2</t>
-        </is>
-      </c>
-      <c r="H103" s="27" t="inlineStr">
-        <is>
-          <t>Group B 1st</t>
-        </is>
-      </c>
-      <c r="I103" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J103" s="27" t="inlineStr">
-        <is>
-          <t>Group A 2nd</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="28" t="inlineStr">
-        <is>
-          <t>Aug 16</t>
-        </is>
-      </c>
-      <c r="B104" s="28" t="inlineStr">
-        <is>
-          <t>4:00PM</t>
-        </is>
-      </c>
-      <c r="C104" s="28" t="inlineStr">
-        <is>
-          <t>4:15PM</t>
-        </is>
-      </c>
-      <c r="D104" s="28" t="inlineStr">
-        <is>
-          <t>Under 15</t>
-        </is>
-      </c>
-      <c r="E104" s="28" t="n">
-        <v>60</v>
-      </c>
-      <c r="F104" s="28" t="inlineStr">
-        <is>
-          <t>U15-SF2</t>
-        </is>
-      </c>
-      <c r="G104" s="28" t="inlineStr">
-        <is>
-          <t>Table 1</t>
-        </is>
-      </c>
-      <c r="H104" s="28" t="inlineStr">
-        <is>
-          <t>Group A 1st</t>
-        </is>
-      </c>
-      <c r="I104" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J104" s="28" t="inlineStr">
-        <is>
-          <t>Group B 2nd</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="27" t="inlineStr">
-        <is>
-          <t>Aug 16</t>
-        </is>
-      </c>
-      <c r="B105" s="27" t="inlineStr">
-        <is>
-          <t>4:15PM</t>
-        </is>
-      </c>
-      <c r="C105" s="27" t="inlineStr">
-        <is>
-          <t>4:30PM</t>
-        </is>
-      </c>
-      <c r="D105" s="27" t="inlineStr">
-        <is>
-          <t>Under 26</t>
-        </is>
-      </c>
-      <c r="E105" s="27" t="n">
-        <v>61</v>
-      </c>
-      <c r="F105" s="27" t="inlineStr">
-        <is>
-          <t>U26-FINAL</t>
-        </is>
-      </c>
-      <c r="G105" s="27" t="inlineStr">
-        <is>
-          <t>Table 1</t>
-        </is>
-      </c>
-      <c r="H105" s="27" t="inlineStr">
-        <is>
-          <t>Pool 1st</t>
-        </is>
-      </c>
-      <c r="I105" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J105" s="27" t="inlineStr">
-        <is>
-          <t>Pool 2nd</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="28" t="inlineStr">
-        <is>
-          <t>Aug 16</t>
-        </is>
-      </c>
-      <c r="B106" s="28" t="inlineStr">
-        <is>
-          <t>4:24PM</t>
-        </is>
-      </c>
-      <c r="C106" s="28" t="inlineStr">
-        <is>
-          <t>4:39PM</t>
-        </is>
-      </c>
-      <c r="D106" s="28" t="inlineStr">
-        <is>
-          <t>Under 36</t>
-        </is>
-      </c>
-      <c r="E106" s="28" t="n">
-        <v>62</v>
-      </c>
-      <c r="F106" s="28" t="inlineStr">
-        <is>
-          <t>U36-SF1</t>
-        </is>
-      </c>
-      <c r="G106" s="28" t="inlineStr">
-        <is>
-          <t>Table 2</t>
-        </is>
-      </c>
-      <c r="H106" s="28" t="inlineStr">
-        <is>
-          <t>Group B 1st</t>
-        </is>
-      </c>
-      <c r="I106" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J106" s="28" t="inlineStr">
-        <is>
-          <t>Group A 2nd</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="27" t="inlineStr">
-        <is>
-          <t>Aug 16</t>
-        </is>
-      </c>
-      <c r="B107" s="27" t="inlineStr">
-        <is>
-          <t>4:30PM</t>
-        </is>
-      </c>
-      <c r="C107" s="27" t="inlineStr">
-        <is>
-          <t>4:45PM</t>
-        </is>
-      </c>
-      <c r="D107" s="27" t="inlineStr">
-        <is>
-          <t>Under 15</t>
-        </is>
-      </c>
-      <c r="E107" s="27" t="n">
-        <v>63</v>
-      </c>
-      <c r="F107" s="27" t="inlineStr">
-        <is>
-          <t>U15-FINAL</t>
-        </is>
-      </c>
-      <c r="G107" s="27" t="inlineStr">
-        <is>
-          <t>Table 1</t>
-        </is>
-      </c>
-      <c r="H107" s="27" t="inlineStr">
+      <c r="H108" s="95" t="inlineStr">
         <is>
           <t>Winner SF1</t>
         </is>
       </c>
-      <c r="I107" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J107" s="27" t="inlineStr">
+      <c r="I108" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J108" s="95" t="inlineStr">
         <is>
           <t>Winner SF2</t>
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="28" t="inlineStr">
-        <is>
-          <t>Aug 16</t>
-        </is>
-      </c>
-      <c r="B108" s="28" t="inlineStr">
-        <is>
-          <t>4:39PM</t>
-        </is>
-      </c>
-      <c r="C108" s="28" t="inlineStr">
-        <is>
-          <t>4:54PM</t>
-        </is>
-      </c>
-      <c r="D108" s="28" t="inlineStr">
-        <is>
-          <t>Under 36</t>
-        </is>
-      </c>
-      <c r="E108" s="28" t="n">
-        <v>64</v>
-      </c>
-      <c r="F108" s="28" t="inlineStr">
-        <is>
-          <t>U36-SF2</t>
-        </is>
-      </c>
-      <c r="G108" s="28" t="inlineStr">
-        <is>
-          <t>Table 2</t>
-        </is>
-      </c>
-      <c r="H108" s="28" t="inlineStr">
-        <is>
-          <t>Group A 1st</t>
-        </is>
-      </c>
-      <c r="I108" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J108" s="28" t="inlineStr">
-        <is>
-          <t>Group B 2nd</t>
-        </is>
-      </c>
-    </row>
     <row r="109">
-      <c r="A109" s="27" t="inlineStr">
-        <is>
-          <t>Aug 16</t>
-        </is>
-      </c>
-      <c r="B109" s="27" t="inlineStr">
-        <is>
-          <t>5:04PM</t>
-        </is>
-      </c>
-      <c r="C109" s="27" t="inlineStr">
-        <is>
-          <t>5:19PM</t>
-        </is>
-      </c>
-      <c r="D109" s="27" t="inlineStr">
-        <is>
-          <t>Under 36</t>
-        </is>
-      </c>
-      <c r="E109" s="27" t="n">
-        <v>65</v>
-      </c>
-      <c r="F109" s="27" t="inlineStr">
-        <is>
-          <t>U36-FINAL</t>
-        </is>
-      </c>
-      <c r="G109" s="27" t="inlineStr">
-        <is>
-          <t>Table 1</t>
-        </is>
-      </c>
-      <c r="H109" s="27" t="inlineStr">
-        <is>
-          <t>Winner SF1</t>
-        </is>
-      </c>
-      <c r="I109" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J109" s="27" t="inlineStr">
-        <is>
-          <t>Winner SF2</t>
-        </is>
-      </c>
+      <c r="A109" s="31" t="n"/>
+      <c r="B109" s="31" t="n"/>
+      <c r="C109" s="31" t="n"/>
+      <c r="D109" s="31" t="n"/>
+      <c r="E109" s="31" t="n"/>
+      <c r="F109" s="31" t="n"/>
+      <c r="G109" s="31" t="n"/>
+      <c r="H109" s="31" t="n"/>
+      <c r="I109" s="31" t="n"/>
+      <c r="J109" s="31" t="n"/>
     </row>
     <row r="110">
-      <c r="A110" s="28" t="inlineStr">
-        <is>
-          <t>Aug 16</t>
-        </is>
-      </c>
-      <c r="B110" s="28" t="inlineStr">
-        <is>
-          <t>5:10PM</t>
-        </is>
-      </c>
-      <c r="C110" s="28" t="inlineStr">
-        <is>
-          <t>5:25PM</t>
-        </is>
-      </c>
-      <c r="D110" s="28" t="inlineStr">
-        <is>
-          <t>Under 46</t>
-        </is>
-      </c>
-      <c r="E110" s="28" t="n">
-        <v>66</v>
-      </c>
-      <c r="F110" s="28" t="inlineStr">
-        <is>
-          <t>U46-SF1</t>
-        </is>
-      </c>
-      <c r="G110" s="28" t="inlineStr">
-        <is>
-          <t>Table 2</t>
-        </is>
-      </c>
-      <c r="H110" s="28" t="inlineStr">
-        <is>
-          <t>Group B 1st</t>
-        </is>
-      </c>
-      <c r="I110" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J110" s="28" t="inlineStr">
-        <is>
-          <t>Group A 2nd</t>
-        </is>
-      </c>
+      <c r="A110" s="31" t="n"/>
+      <c r="B110" s="31" t="n"/>
+      <c r="C110" s="31" t="n"/>
+      <c r="D110" s="31" t="n"/>
+      <c r="E110" s="31" t="n"/>
+      <c r="F110" s="31" t="n"/>
+      <c r="G110" s="31" t="n"/>
+      <c r="H110" s="31" t="n"/>
+      <c r="I110" s="31" t="n"/>
+      <c r="J110" s="31" t="n"/>
     </row>
     <row r="111">
-      <c r="A111" s="27" t="inlineStr">
-        <is>
-          <t>Aug 16</t>
-        </is>
-      </c>
-      <c r="B111" s="27" t="inlineStr">
-        <is>
-          <t>5:19PM</t>
-        </is>
-      </c>
-      <c r="C111" s="27" t="inlineStr">
-        <is>
-          <t>5:34PM</t>
-        </is>
-      </c>
-      <c r="D111" s="27" t="inlineStr">
-        <is>
-          <t>Under 46</t>
-        </is>
-      </c>
-      <c r="E111" s="27" t="n">
-        <v>67</v>
-      </c>
-      <c r="F111" s="27" t="inlineStr">
-        <is>
-          <t>U46-SF2</t>
-        </is>
-      </c>
-      <c r="G111" s="27" t="inlineStr">
-        <is>
-          <t>Table 1</t>
-        </is>
-      </c>
-      <c r="H111" s="27" t="inlineStr">
-        <is>
-          <t>Group A 1st</t>
-        </is>
-      </c>
-      <c r="I111" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J111" s="27" t="inlineStr">
-        <is>
-          <t>Group B 2nd</t>
-        </is>
-      </c>
+      <c r="A111" s="31" t="n"/>
+      <c r="B111" s="31" t="n"/>
+      <c r="C111" s="31" t="n"/>
+      <c r="D111" s="31" t="n"/>
+      <c r="E111" s="31" t="n"/>
+      <c r="F111" s="31" t="n"/>
+      <c r="G111" s="31" t="n"/>
+      <c r="H111" s="31" t="n"/>
+      <c r="I111" s="31" t="n"/>
+      <c r="J111" s="31" t="n"/>
     </row>
     <row r="112">
-      <c r="A112" s="28" t="inlineStr">
-        <is>
-          <t>Aug 16</t>
-        </is>
-      </c>
-      <c r="B112" s="28" t="inlineStr">
-        <is>
-          <t>5:25PM</t>
-        </is>
-      </c>
-      <c r="C112" s="28" t="inlineStr">
-        <is>
-          <t>5:40PM</t>
-        </is>
-      </c>
-      <c r="D112" s="28" t="inlineStr">
-        <is>
-          <t>Above 46</t>
-        </is>
-      </c>
-      <c r="E112" s="28" t="n">
-        <v>68</v>
-      </c>
-      <c r="F112" s="28" t="inlineStr">
-        <is>
-          <t>A46-SF1</t>
-        </is>
-      </c>
-      <c r="G112" s="28" t="inlineStr">
-        <is>
-          <t>Table 2</t>
-        </is>
-      </c>
-      <c r="H112" s="28" t="inlineStr">
-        <is>
-          <t>Group B 1st</t>
-        </is>
-      </c>
-      <c r="I112" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J112" s="28" t="inlineStr">
-        <is>
-          <t>Group A 2nd</t>
-        </is>
-      </c>
+      <c r="A112" s="31" t="n"/>
+      <c r="B112" s="31" t="n"/>
+      <c r="C112" s="31" t="n"/>
+      <c r="D112" s="31" t="n"/>
+      <c r="E112" s="31" t="n"/>
+      <c r="F112" s="31" t="n"/>
+      <c r="G112" s="31" t="n"/>
+      <c r="H112" s="31" t="n"/>
+      <c r="I112" s="31" t="n"/>
+      <c r="J112" s="31" t="n"/>
     </row>
     <row r="113">
-      <c r="A113" s="27" t="inlineStr">
-        <is>
-          <t>Aug 16</t>
-        </is>
-      </c>
-      <c r="B113" s="27" t="inlineStr">
-        <is>
-          <t>5:34PM</t>
-        </is>
-      </c>
-      <c r="C113" s="27" t="inlineStr">
-        <is>
-          <t>5:49PM</t>
-        </is>
-      </c>
-      <c r="D113" s="27" t="inlineStr">
-        <is>
-          <t>Above 46</t>
-        </is>
-      </c>
-      <c r="E113" s="27" t="n">
-        <v>69</v>
-      </c>
-      <c r="F113" s="27" t="inlineStr">
-        <is>
-          <t>A46-SF2</t>
-        </is>
-      </c>
-      <c r="G113" s="27" t="inlineStr">
-        <is>
-          <t>Table 1</t>
-        </is>
-      </c>
-      <c r="H113" s="27" t="inlineStr">
-        <is>
-          <t>Group A 1st</t>
-        </is>
-      </c>
-      <c r="I113" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J113" s="27" t="inlineStr">
-        <is>
-          <t>Group B 2nd</t>
-        </is>
-      </c>
+      <c r="A113" s="31" t="n"/>
+      <c r="B113" s="31" t="n"/>
+      <c r="C113" s="31" t="n"/>
+      <c r="D113" s="31" t="n"/>
+      <c r="E113" s="31" t="n"/>
+      <c r="F113" s="31" t="n"/>
+      <c r="G113" s="31" t="n"/>
+      <c r="H113" s="31" t="n"/>
+      <c r="I113" s="31" t="n"/>
+      <c r="J113" s="31" t="n"/>
     </row>
     <row r="114">
-      <c r="A114" s="28" t="inlineStr">
-        <is>
-          <t>Aug 16</t>
-        </is>
-      </c>
-      <c r="B114" s="28" t="inlineStr">
-        <is>
-          <t>5:44PM</t>
-        </is>
-      </c>
-      <c r="C114" s="28" t="inlineStr">
-        <is>
-          <t>5:59PM</t>
-        </is>
-      </c>
-      <c r="D114" s="28" t="inlineStr">
-        <is>
-          <t>Under 46</t>
-        </is>
-      </c>
-      <c r="E114" s="28" t="n">
-        <v>70</v>
-      </c>
-      <c r="F114" s="28" t="inlineStr">
-        <is>
-          <t>U46-FINAL</t>
-        </is>
-      </c>
-      <c r="G114" s="28" t="inlineStr">
-        <is>
-          <t>Table 2</t>
-        </is>
-      </c>
-      <c r="H114" s="28" t="inlineStr">
-        <is>
-          <t>Winner SF1</t>
-        </is>
-      </c>
-      <c r="I114" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J114" s="28" t="inlineStr">
-        <is>
-          <t>Winner SF2</t>
-        </is>
-      </c>
+      <c r="A114" s="31" t="n"/>
+      <c r="B114" s="31" t="n"/>
+      <c r="C114" s="31" t="n"/>
+      <c r="D114" s="31" t="n"/>
+      <c r="E114" s="31" t="n"/>
+      <c r="F114" s="31" t="n"/>
+      <c r="G114" s="31" t="n"/>
+      <c r="H114" s="31" t="n"/>
+      <c r="I114" s="31" t="n"/>
+      <c r="J114" s="31" t="n"/>
     </row>
     <row r="115">
-      <c r="A115" s="27" t="inlineStr">
-        <is>
-          <t>Aug 16</t>
-        </is>
-      </c>
-      <c r="B115" s="27" t="inlineStr">
-        <is>
-          <t>5:59PM</t>
-        </is>
-      </c>
-      <c r="C115" s="27" t="inlineStr">
-        <is>
-          <t>6:14PM</t>
-        </is>
-      </c>
-      <c r="D115" s="27" t="inlineStr">
-        <is>
-          <t>Above 46</t>
-        </is>
-      </c>
-      <c r="E115" s="27" t="n">
-        <v>71</v>
-      </c>
-      <c r="F115" s="27" t="inlineStr">
-        <is>
-          <t>A46-FINAL</t>
-        </is>
-      </c>
-      <c r="G115" s="27" t="inlineStr">
-        <is>
-          <t>Table 1</t>
-        </is>
-      </c>
-      <c r="H115" s="27" t="inlineStr">
-        <is>
-          <t>Winner SF1</t>
-        </is>
-      </c>
-      <c r="I115" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J115" s="27" t="inlineStr">
-        <is>
-          <t>Winner SF2</t>
-        </is>
-      </c>
+      <c r="A115" s="31" t="n"/>
+      <c r="B115" s="31" t="n"/>
+      <c r="C115" s="31" t="n"/>
+      <c r="D115" s="31" t="n"/>
+      <c r="E115" s="31" t="n"/>
+      <c r="F115" s="31" t="n"/>
+      <c r="G115" s="31" t="n"/>
+      <c r="H115" s="31" t="n"/>
+      <c r="I115" s="31" t="n"/>
+      <c r="J115" s="31" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="16">
+    <mergeCell ref="A47:J47"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="D7:E7"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A35:H35"/>
+    <mergeCell ref="D21:E21"/>
     <mergeCell ref="D27:E27"/>
-    <mergeCell ref="A34:J34"/>
     <mergeCell ref="A12:J12"/>
     <mergeCell ref="A4:J4"/>
-    <mergeCell ref="A43:J43"/>
     <mergeCell ref="A20:J20"/>
+    <mergeCell ref="A26:J26"/>
     <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A26:J26"/>
     <mergeCell ref="A27:B27"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="A34:H34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9996,350 +9748,350 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="27" t="inlineStr">
+      <c r="A20" s="94" t="inlineStr">
         <is>
           <t>Aug 16</t>
         </is>
       </c>
-      <c r="B20" s="27" t="inlineStr">
+      <c r="B20" s="94" t="inlineStr">
+        <is>
+          <t>9:05AM</t>
+        </is>
+      </c>
+      <c r="C20" s="94" t="inlineStr">
+        <is>
+          <t>9:20AM</t>
+        </is>
+      </c>
+      <c r="D20" s="94" t="inlineStr">
+        <is>
+          <t>TT Doubles</t>
+        </is>
+      </c>
+      <c r="E20" s="94" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="94" t="inlineStr">
+        <is>
+          <t>QF3</t>
+        </is>
+      </c>
+      <c r="G20" s="94" t="inlineStr">
+        <is>
+          <t>Table 1</t>
+        </is>
+      </c>
+      <c r="H20" s="94" t="inlineStr">
+        <is>
+          <t>Mayank Aggarwal &amp; Sudip Parui</t>
+        </is>
+      </c>
+      <c r="I20" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J20" s="94" t="inlineStr">
+        <is>
+          <t>Nidhi Sharma &amp; Tushar</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="95" t="inlineStr">
+        <is>
+          <t>Aug 16</t>
+        </is>
+      </c>
+      <c r="B21" s="95" t="inlineStr">
+        <is>
+          <t>10:50AM</t>
+        </is>
+      </c>
+      <c r="C21" s="95" t="inlineStr">
+        <is>
+          <t>11:05AM</t>
+        </is>
+      </c>
+      <c r="D21" s="95" t="inlineStr">
+        <is>
+          <t>TT Doubles</t>
+        </is>
+      </c>
+      <c r="E21" s="95" t="n">
+        <v>2</v>
+      </c>
+      <c r="F21" s="95" t="inlineStr">
+        <is>
+          <t>QF2</t>
+        </is>
+      </c>
+      <c r="G21" s="95" t="inlineStr">
+        <is>
+          <t>Table 1</t>
+        </is>
+      </c>
+      <c r="H21" s="95" t="inlineStr">
+        <is>
+          <t>Nilesh Bagaria &amp; Parthiv</t>
+        </is>
+      </c>
+      <c r="I21" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J21" s="95" t="inlineStr">
+        <is>
+          <t>Rahul Garg &amp; Nilesh Mhatre</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="94" t="inlineStr">
+        <is>
+          <t>Aug 16</t>
+        </is>
+      </c>
+      <c r="B22" s="94" t="inlineStr">
+        <is>
+          <t>11:10AM</t>
+        </is>
+      </c>
+      <c r="C22" s="94" t="inlineStr">
+        <is>
+          <t>11:25AM</t>
+        </is>
+      </c>
+      <c r="D22" s="94" t="inlineStr">
+        <is>
+          <t>TT Doubles</t>
+        </is>
+      </c>
+      <c r="E22" s="94" t="n">
+        <v>3</v>
+      </c>
+      <c r="F22" s="94" t="inlineStr">
+        <is>
+          <t>QF4</t>
+        </is>
+      </c>
+      <c r="G22" s="94" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="H22" s="94" t="inlineStr">
+        <is>
+          <t>Adil Khan &amp; Anuj Shah</t>
+        </is>
+      </c>
+      <c r="I22" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J22" s="94" t="inlineStr">
+        <is>
+          <t>Vinit Padia &amp; Pratik Haldiya</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="95" t="inlineStr">
+        <is>
+          <t>Aug 16</t>
+        </is>
+      </c>
+      <c r="B23" s="95" t="inlineStr">
+        <is>
+          <t>11:40AM</t>
+        </is>
+      </c>
+      <c r="C23" s="95" t="inlineStr">
         <is>
           <t>11:55AM</t>
         </is>
       </c>
-      <c r="C20" s="27" t="inlineStr">
+      <c r="D23" s="95" t="inlineStr">
+        <is>
+          <t>TT Doubles</t>
+        </is>
+      </c>
+      <c r="E23" s="95" t="n">
+        <v>4</v>
+      </c>
+      <c r="F23" s="95" t="inlineStr">
+        <is>
+          <t>QF1</t>
+        </is>
+      </c>
+      <c r="G23" s="95" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="H23" s="95" t="inlineStr">
+        <is>
+          <t>Tanmay Sharma &amp; Sankalp</t>
+        </is>
+      </c>
+      <c r="I23" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J23" s="95" t="inlineStr">
+        <is>
+          <t>Ravi Modi &amp; Dr Rahul Modi</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="94" t="inlineStr">
+        <is>
+          <t>Aug 16</t>
+        </is>
+      </c>
+      <c r="B24" s="94" t="inlineStr">
+        <is>
+          <t>11:55AM</t>
+        </is>
+      </c>
+      <c r="C24" s="94" t="inlineStr">
         <is>
           <t>12:10PM</t>
         </is>
       </c>
-      <c r="D20" s="27" t="inlineStr">
+      <c r="D24" s="94" t="inlineStr">
         <is>
           <t>TT Doubles</t>
         </is>
       </c>
-      <c r="E20" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" s="27" t="inlineStr">
-        <is>
-          <t>QF1</t>
-        </is>
-      </c>
-      <c r="G20" s="27" t="inlineStr">
-        <is>
-          <t>Table 1</t>
-        </is>
-      </c>
-      <c r="H20" s="27" t="inlineStr">
-        <is>
-          <t>Tanmay Sharma &amp; Sankalp</t>
-        </is>
-      </c>
-      <c r="I20" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J20" s="27" t="inlineStr">
-        <is>
-          <t>Ravi Modi &amp; Dr Rahul Modi</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="28" t="inlineStr">
+      <c r="E24" s="94" t="n">
+        <v>5</v>
+      </c>
+      <c r="F24" s="94" t="inlineStr">
+        <is>
+          <t>SF1</t>
+        </is>
+      </c>
+      <c r="G24" s="94" t="inlineStr">
+        <is>
+          <t>Table 2</t>
+        </is>
+      </c>
+      <c r="H24" s="94" t="inlineStr">
+        <is>
+          <t>Winner QF2</t>
+        </is>
+      </c>
+      <c r="I24" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J24" s="94" t="inlineStr">
+        <is>
+          <t>Winner QF3</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="95" t="inlineStr">
         <is>
           <t>Aug 16</t>
         </is>
       </c>
-      <c r="B21" s="28" t="inlineStr">
-        <is>
-          <t>11:55AM</t>
-        </is>
-      </c>
-      <c r="C21" s="28" t="inlineStr">
-        <is>
-          <t>12:10PM</t>
-        </is>
-      </c>
-      <c r="D21" s="28" t="inlineStr">
+      <c r="B25" s="95" t="inlineStr">
+        <is>
+          <t>3:00PM</t>
+        </is>
+      </c>
+      <c r="C25" s="95" t="inlineStr">
+        <is>
+          <t>3:15PM</t>
+        </is>
+      </c>
+      <c r="D25" s="95" t="inlineStr">
         <is>
           <t>TT Doubles</t>
         </is>
       </c>
-      <c r="E21" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="F21" s="28" t="inlineStr">
-        <is>
-          <t>QF2</t>
-        </is>
-      </c>
-      <c r="G21" s="28" t="inlineStr">
+      <c r="E25" s="95" t="n">
+        <v>6</v>
+      </c>
+      <c r="F25" s="95" t="inlineStr">
+        <is>
+          <t>SF2</t>
+        </is>
+      </c>
+      <c r="G25" s="95" t="inlineStr">
         <is>
           <t>Table 2</t>
         </is>
       </c>
-      <c r="H21" s="28" t="inlineStr">
-        <is>
-          <t>Nilesh Bagaria &amp; Parthiv</t>
-        </is>
-      </c>
-      <c r="I21" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J21" s="28" t="inlineStr">
-        <is>
-          <t>Rahul Garg &amp; Nilesh Mhatre</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="27" t="inlineStr">
+      <c r="H25" s="95" t="inlineStr">
+        <is>
+          <t>Winner QF4</t>
+        </is>
+      </c>
+      <c r="I25" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J25" s="95" t="inlineStr">
+        <is>
+          <t>Winner QF1</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="94" t="inlineStr">
         <is>
           <t>Aug 16</t>
         </is>
       </c>
-      <c r="B22" s="27" t="inlineStr">
-        <is>
-          <t>3:00PM</t>
-        </is>
-      </c>
-      <c r="C22" s="27" t="inlineStr">
-        <is>
-          <t>3:15PM</t>
-        </is>
-      </c>
-      <c r="D22" s="27" t="inlineStr">
+      <c r="B26" s="94" t="inlineStr">
+        <is>
+          <t>3:30PM</t>
+        </is>
+      </c>
+      <c r="C26" s="94" t="inlineStr">
+        <is>
+          <t>3:45PM</t>
+        </is>
+      </c>
+      <c r="D26" s="94" t="inlineStr">
         <is>
           <t>TT Doubles</t>
         </is>
       </c>
-      <c r="E22" s="27" t="n">
-        <v>3</v>
-      </c>
-      <c r="F22" s="27" t="inlineStr">
-        <is>
-          <t>QF3</t>
-        </is>
-      </c>
-      <c r="G22" s="27" t="inlineStr">
-        <is>
-          <t>Table 1</t>
-        </is>
-      </c>
-      <c r="H22" s="27" t="inlineStr">
-        <is>
-          <t>Mayank Aggarwal &amp; Sudip Parui</t>
-        </is>
-      </c>
-      <c r="I22" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J22" s="27" t="inlineStr">
-        <is>
-          <t>Nidhi Sharma &amp; Tushar</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="28" t="inlineStr">
-        <is>
-          <t>Aug 16</t>
-        </is>
-      </c>
-      <c r="B23" s="28" t="inlineStr">
-        <is>
-          <t>3:15PM</t>
-        </is>
-      </c>
-      <c r="C23" s="28" t="inlineStr">
-        <is>
-          <t>3:30PM</t>
-        </is>
-      </c>
-      <c r="D23" s="28" t="inlineStr">
-        <is>
-          <t>TT Doubles</t>
-        </is>
-      </c>
-      <c r="E23" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="F23" s="28" t="inlineStr">
-        <is>
-          <t>QF4</t>
-        </is>
-      </c>
-      <c r="G23" s="28" t="inlineStr">
-        <is>
-          <t>Table 1</t>
-        </is>
-      </c>
-      <c r="H23" s="28" t="inlineStr">
-        <is>
-          <t>Adil Khan &amp; Anuj Shah</t>
-        </is>
-      </c>
-      <c r="I23" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J23" s="28" t="inlineStr">
-        <is>
-          <t>Vinit Padia &amp; Pratik Haldiya</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="27" t="inlineStr">
-        <is>
-          <t>Aug 16</t>
-        </is>
-      </c>
-      <c r="B24" s="27" t="inlineStr">
-        <is>
-          <t>3:15PM</t>
-        </is>
-      </c>
-      <c r="C24" s="27" t="inlineStr">
-        <is>
-          <t>3:30PM</t>
-        </is>
-      </c>
-      <c r="D24" s="27" t="inlineStr">
-        <is>
-          <t>TT Doubles</t>
-        </is>
-      </c>
-      <c r="E24" s="27" t="n">
-        <v>5</v>
-      </c>
-      <c r="F24" s="27" t="inlineStr">
-        <is>
-          <t>SF1</t>
-        </is>
-      </c>
-      <c r="G24" s="27" t="inlineStr">
+      <c r="E26" s="94" t="n">
+        <v>7</v>
+      </c>
+      <c r="F26" s="94" t="inlineStr">
+        <is>
+          <t>FINAL</t>
+        </is>
+      </c>
+      <c r="G26" s="94" t="inlineStr">
         <is>
           <t>Table 2</t>
         </is>
       </c>
-      <c r="H24" s="27" t="inlineStr">
-        <is>
-          <t>Winner QF2</t>
-        </is>
-      </c>
-      <c r="I24" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J24" s="27" t="inlineStr">
-        <is>
-          <t>Winner QF3</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="28" t="inlineStr">
-        <is>
-          <t>Aug 16</t>
-        </is>
-      </c>
-      <c r="B25" s="28" t="inlineStr">
-        <is>
-          <t>3:30PM</t>
-        </is>
-      </c>
-      <c r="C25" s="28" t="inlineStr">
-        <is>
-          <t>3:45PM</t>
-        </is>
-      </c>
-      <c r="D25" s="28" t="inlineStr">
-        <is>
-          <t>TT Doubles</t>
-        </is>
-      </c>
-      <c r="E25" s="28" t="n">
-        <v>6</v>
-      </c>
-      <c r="F25" s="28" t="inlineStr">
-        <is>
-          <t>SF2</t>
-        </is>
-      </c>
-      <c r="G25" s="28" t="inlineStr">
-        <is>
-          <t>Table 1</t>
-        </is>
-      </c>
-      <c r="H25" s="28" t="inlineStr">
-        <is>
-          <t>Winner QF4</t>
-        </is>
-      </c>
-      <c r="I25" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J25" s="28" t="inlineStr">
-        <is>
-          <t>Winner QF1</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="27" t="inlineStr">
-        <is>
-          <t>Aug 16</t>
-        </is>
-      </c>
-      <c r="B26" s="27" t="inlineStr">
-        <is>
-          <t>3:45PM</t>
-        </is>
-      </c>
-      <c r="C26" s="27" t="inlineStr">
-        <is>
-          <t>4:00PM</t>
-        </is>
-      </c>
-      <c r="D26" s="27" t="inlineStr">
-        <is>
-          <t>TT Doubles</t>
-        </is>
-      </c>
-      <c r="E26" s="27" t="n">
-        <v>7</v>
-      </c>
-      <c r="F26" s="27" t="inlineStr">
-        <is>
-          <t>FINAL</t>
-        </is>
-      </c>
-      <c r="G26" s="27" t="inlineStr">
-        <is>
-          <t>Table 1</t>
-        </is>
-      </c>
-      <c r="H26" s="27" t="inlineStr">
+      <c r="H26" s="94" t="inlineStr">
         <is>
           <t>Winner SF1</t>
         </is>
       </c>
-      <c r="I26" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J26" s="27" t="inlineStr">
+      <c r="I26" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J26" s="94" t="inlineStr">
         <is>
           <t>Winner SF2</t>
         </is>

--- a/Ekta_Schedule_With_Matchups.xlsx
+++ b/Ekta_Schedule_With_Matchups.xlsx
@@ -1242,7 +1242,7 @@
       </c>
       <c r="C15" s="64" t="inlineStr">
         <is>
-          <t>League stage continues. Carrom Women's Singles (done ~11:00 AM) and TT Women's Singles (done ~11:00 AM) each finish in full today — their knockouts run right after their own league stage ends, no waiting for other events.</t>
+          <t>League stage continues. Carrom Women's Singles (done ~11:00 AM) and TT Women's Singles (done ~11:15 AM) each finish in full today — their knockouts run right after their own league stage ends, no waiting for other events. TT Men's Above 46 knockout leads off the morning on Table 1 at 8:00 AM.</t>
         </is>
       </c>
       <c r="H15" s="31" t="n"/>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="C17" s="64" t="inlineStr">
         <is>
-          <t>Both Doubles events run once their own players are free — Carrom Doubles 9:30-11:50 AM; TT Doubles starts 9:05 AM and interleaves with TT Men's Singles on the shared tables, wrapping by 3:45 PM.</t>
+          <t>Both Doubles events run once their own players are free — Carrom Doubles 9:30-11:50 AM; TT Doubles starts 9:05 AM and interleaves with TT Men's Singles on the shared tables, wrapping by 4:30 PM.</t>
         </is>
       </c>
       <c r="H17" s="31" t="n"/>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="E24" s="63" t="inlineStr">
         <is>
-          <t>Aug15 11:00AM</t>
+          <t>Aug15 11:15AM</t>
         </is>
       </c>
       <c r="F24" s="31" t="n"/>
@@ -1441,12 +1441,12 @@
       </c>
       <c r="D25" s="63" t="inlineStr">
         <is>
-          <t>Aug15 10:45AM</t>
+          <t>Aug15 8:00AM</t>
         </is>
       </c>
       <c r="E25" s="63" t="inlineStr">
         <is>
-          <t>Aug16 4:45PM</t>
+          <t>Aug16 4:00PM</t>
         </is>
       </c>
       <c r="F25" s="31" t="n"/>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="E26" s="63" t="inlineStr">
         <is>
-          <t>Aug16 3:45PM</t>
+          <t>Aug16 4:30PM</t>
         </is>
       </c>
       <c r="F26" s="31" t="n"/>
@@ -4995,7 +4995,7 @@
       </c>
       <c r="G16" s="94" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H16" s="94" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="B17" s="95" t="inlineStr">
         <is>
-          <t>8:00AM</t>
+          <t>8:15AM</t>
         </is>
       </c>
       <c r="C17" s="95" t="inlineStr">
         <is>
-          <t>8:15AM</t>
+          <t>8:30AM</t>
         </is>
       </c>
       <c r="D17" s="95" t="inlineStr">
@@ -5045,7 +5045,7 @@
       </c>
       <c r="G17" s="95" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H17" s="95" t="inlineStr">
@@ -5095,7 +5095,7 @@
       </c>
       <c r="G18" s="94" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H18" s="94" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="B19" s="95" t="inlineStr">
         <is>
-          <t>8:15AM</t>
+          <t>8:30AM</t>
         </is>
       </c>
       <c r="C19" s="95" t="inlineStr">
         <is>
-          <t>8:30AM</t>
+          <t>8:45AM</t>
         </is>
       </c>
       <c r="D19" s="95" t="inlineStr">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="G19" s="95" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H19" s="95" t="inlineStr">
@@ -5172,12 +5172,12 @@
       </c>
       <c r="B20" s="94" t="inlineStr">
         <is>
-          <t>8:30AM</t>
+          <t>8:45AM</t>
         </is>
       </c>
       <c r="C20" s="94" t="inlineStr">
         <is>
-          <t>8:45AM</t>
+          <t>9:00AM</t>
         </is>
       </c>
       <c r="D20" s="94" t="inlineStr">
@@ -5222,12 +5222,12 @@
       </c>
       <c r="B21" s="95" t="inlineStr">
         <is>
-          <t>8:30AM</t>
+          <t>8:45AM</t>
         </is>
       </c>
       <c r="C21" s="95" t="inlineStr">
         <is>
-          <t>8:45AM</t>
+          <t>9:00AM</t>
         </is>
       </c>
       <c r="D21" s="95" t="inlineStr">
@@ -5272,12 +5272,12 @@
       </c>
       <c r="B22" s="94" t="inlineStr">
         <is>
-          <t>8:45AM</t>
+          <t>9:00AM</t>
         </is>
       </c>
       <c r="C22" s="94" t="inlineStr">
         <is>
-          <t>9:00AM</t>
+          <t>9:15AM</t>
         </is>
       </c>
       <c r="D22" s="94" t="inlineStr">
@@ -5322,12 +5322,12 @@
       </c>
       <c r="B23" s="95" t="inlineStr">
         <is>
-          <t>8:45AM</t>
+          <t>9:00AM</t>
         </is>
       </c>
       <c r="C23" s="95" t="inlineStr">
         <is>
-          <t>9:00AM</t>
+          <t>9:15AM</t>
         </is>
       </c>
       <c r="D23" s="95" t="inlineStr">
@@ -5372,12 +5372,12 @@
       </c>
       <c r="B24" s="94" t="inlineStr">
         <is>
-          <t>9:00AM</t>
+          <t>9:15AM</t>
         </is>
       </c>
       <c r="C24" s="94" t="inlineStr">
         <is>
-          <t>9:15AM</t>
+          <t>9:30AM</t>
         </is>
       </c>
       <c r="D24" s="94" t="inlineStr">
@@ -5422,12 +5422,12 @@
       </c>
       <c r="B25" s="95" t="inlineStr">
         <is>
-          <t>9:00AM</t>
+          <t>9:15AM</t>
         </is>
       </c>
       <c r="C25" s="95" t="inlineStr">
         <is>
-          <t>9:15AM</t>
+          <t>9:30AM</t>
         </is>
       </c>
       <c r="D25" s="95" t="inlineStr">
@@ -5472,12 +5472,12 @@
       </c>
       <c r="B26" s="94" t="inlineStr">
         <is>
-          <t>9:15AM</t>
+          <t>10:30AM</t>
         </is>
       </c>
       <c r="C26" s="94" t="inlineStr">
         <is>
-          <t>9:30AM</t>
+          <t>10:45AM</t>
         </is>
       </c>
       <c r="D26" s="94" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="B27" s="95" t="inlineStr">
         <is>
-          <t>9:15AM</t>
+          <t>10:30AM</t>
         </is>
       </c>
       <c r="C27" s="95" t="inlineStr">
         <is>
-          <t>9:30AM</t>
+          <t>10:45AM</t>
         </is>
       </c>
       <c r="D27" s="95" t="inlineStr">
@@ -5572,12 +5572,12 @@
       </c>
       <c r="B28" s="94" t="inlineStr">
         <is>
-          <t>10:30AM</t>
+          <t>10:45AM</t>
         </is>
       </c>
       <c r="C28" s="94" t="inlineStr">
         <is>
-          <t>10:45AM</t>
+          <t>11:00AM</t>
         </is>
       </c>
       <c r="D28" s="94" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="B29" s="95" t="inlineStr">
         <is>
-          <t>10:30AM</t>
+          <t>10:45AM</t>
         </is>
       </c>
       <c r="C29" s="95" t="inlineStr">
         <is>
-          <t>10:45AM</t>
+          <t>11:00AM</t>
         </is>
       </c>
       <c r="D29" s="95" t="inlineStr">
@@ -5672,12 +5672,12 @@
       </c>
       <c r="B30" s="94" t="inlineStr">
         <is>
-          <t>10:45AM</t>
+          <t>11:00AM</t>
         </is>
       </c>
       <c r="C30" s="94" t="inlineStr">
         <is>
-          <t>11:00AM</t>
+          <t>11:15AM</t>
         </is>
       </c>
       <c r="D30" s="94" t="inlineStr">
@@ -6448,17 +6448,17 @@
       </c>
       <c r="B49" s="94" t="inlineStr">
         <is>
-          <t>10:45AM</t>
+          <t>8:00AM</t>
         </is>
       </c>
       <c r="C49" s="94" t="inlineStr">
         <is>
-          <t>11:00AM</t>
+          <t>8:15AM</t>
         </is>
       </c>
       <c r="D49" s="94" t="inlineStr">
         <is>
-          <t>Under 36</t>
+          <t>Above 46</t>
         </is>
       </c>
       <c r="E49" s="94" t="n">
@@ -6466,17 +6466,17 @@
       </c>
       <c r="F49" s="94" t="inlineStr">
         <is>
-          <t>U36-GB-1</t>
+          <t>A46-QF3</t>
         </is>
       </c>
       <c r="G49" s="94" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H49" s="94" t="inlineStr">
         <is>
-          <t>Prakshal Shah</t>
+          <t>Ghansyam nawani</t>
         </is>
       </c>
       <c r="I49" s="94" t="inlineStr">
@@ -6486,7 +6486,7 @@
       </c>
       <c r="J49" s="94" t="inlineStr">
         <is>
-          <t>Amar Parulekar</t>
+          <t>HARSHAPRABHAT SHETTY</t>
         </is>
       </c>
     </row>
@@ -6498,17 +6498,17 @@
       </c>
       <c r="B50" s="95" t="inlineStr">
         <is>
-          <t>11:00AM</t>
+          <t>8:30AM</t>
         </is>
       </c>
       <c r="C50" s="95" t="inlineStr">
         <is>
-          <t>11:15AM</t>
+          <t>8:45AM</t>
         </is>
       </c>
       <c r="D50" s="95" t="inlineStr">
         <is>
-          <t>Above 46</t>
+          <t>Under 36</t>
         </is>
       </c>
       <c r="E50" s="95" t="n">
@@ -6516,17 +6516,17 @@
       </c>
       <c r="F50" s="95" t="inlineStr">
         <is>
-          <t>A46-QF3</t>
+          <t>U36-GB-1</t>
         </is>
       </c>
       <c r="G50" s="95" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H50" s="95" t="inlineStr">
         <is>
-          <t>Ghansyam nawani</t>
+          <t>Prakshal Shah</t>
         </is>
       </c>
       <c r="I50" s="95" t="inlineStr">
@@ -6536,7 +6536,7 @@
       </c>
       <c r="J50" s="95" t="inlineStr">
         <is>
-          <t>HARSHAPRABHAT SHETTY</t>
+          <t>Amar Parulekar</t>
         </is>
       </c>
     </row>
@@ -7808,7 +7808,7 @@
       </c>
       <c r="D76" s="95" t="inlineStr">
         <is>
-          <t>Under 36</t>
+          <t>Above 46</t>
         </is>
       </c>
       <c r="E76" s="95" t="n">
@@ -7816,7 +7816,7 @@
       </c>
       <c r="F76" s="95" t="inlineStr">
         <is>
-          <t>U36-FINAL</t>
+          <t>A46-QF4</t>
         </is>
       </c>
       <c r="G76" s="95" t="inlineStr">
@@ -7826,7 +7826,7 @@
       </c>
       <c r="H76" s="95" t="inlineStr">
         <is>
-          <t>Winner SF1</t>
+          <t>Mukul Joshi</t>
         </is>
       </c>
       <c r="I76" s="95" t="inlineStr">
@@ -7836,7 +7836,7 @@
       </c>
       <c r="J76" s="95" t="inlineStr">
         <is>
-          <t>Winner SF2</t>
+          <t>Sushil Dashpute</t>
         </is>
       </c>
     </row>
@@ -7858,7 +7858,7 @@
       </c>
       <c r="D77" s="94" t="inlineStr">
         <is>
-          <t>Above 46</t>
+          <t>Under 36</t>
         </is>
       </c>
       <c r="E77" s="94" t="n">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="F77" s="94" t="inlineStr">
         <is>
-          <t>A46-QF4</t>
+          <t>U36-FINAL</t>
         </is>
       </c>
       <c r="G77" s="94" t="inlineStr">
@@ -7876,7 +7876,7 @@
       </c>
       <c r="H77" s="94" t="inlineStr">
         <is>
-          <t>Mukul Joshi</t>
+          <t>Winner SF1</t>
         </is>
       </c>
       <c r="I77" s="94" t="inlineStr">
@@ -7886,7 +7886,7 @@
       </c>
       <c r="J77" s="94" t="inlineStr">
         <is>
-          <t>Sushil Dashpute</t>
+          <t>Winner SF2</t>
         </is>
       </c>
     </row>
@@ -7908,7 +7908,7 @@
       </c>
       <c r="D78" s="95" t="inlineStr">
         <is>
-          <t>Under 46</t>
+          <t>Above 46</t>
         </is>
       </c>
       <c r="E78" s="95" t="n">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="F78" s="95" t="inlineStr">
         <is>
-          <t>U46-GA-10</t>
+          <t>A46-SF2</t>
         </is>
       </c>
       <c r="G78" s="95" t="inlineStr">
@@ -7926,7 +7926,7 @@
       </c>
       <c r="H78" s="95" t="inlineStr">
         <is>
-          <t>Tanmay Sharma</t>
+          <t>Winner QF3</t>
         </is>
       </c>
       <c r="I78" s="95" t="inlineStr">
@@ -7936,7 +7936,7 @@
       </c>
       <c r="J78" s="95" t="inlineStr">
         <is>
-          <t>Anuj Shah</t>
+          <t>Winner QF4</t>
         </is>
       </c>
     </row>
@@ -7958,7 +7958,7 @@
       </c>
       <c r="D79" s="94" t="inlineStr">
         <is>
-          <t>Above 46</t>
+          <t>Under 46</t>
         </is>
       </c>
       <c r="E79" s="94" t="n">
@@ -7966,7 +7966,7 @@
       </c>
       <c r="F79" s="94" t="inlineStr">
         <is>
-          <t>A46-SF2</t>
+          <t>U46-GA-10</t>
         </is>
       </c>
       <c r="G79" s="94" t="inlineStr">
@@ -7976,7 +7976,7 @@
       </c>
       <c r="H79" s="94" t="inlineStr">
         <is>
-          <t>Winner QF3</t>
+          <t>Tanmay Sharma</t>
         </is>
       </c>
       <c r="I79" s="94" t="inlineStr">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="J79" s="94" t="inlineStr">
         <is>
-          <t>Winner QF4</t>
+          <t>Anuj Shah</t>
         </is>
       </c>
     </row>
@@ -9058,7 +9058,7 @@
       </c>
       <c r="D101" s="94" t="inlineStr">
         <is>
-          <t>Under 46</t>
+          <t>Above 46</t>
         </is>
       </c>
       <c r="E101" s="94" t="n">
@@ -9066,7 +9066,7 @@
       </c>
       <c r="F101" s="94" t="inlineStr">
         <is>
-          <t>U46-GB-7</t>
+          <t>A46-R1</t>
         </is>
       </c>
       <c r="G101" s="94" t="inlineStr">
@@ -9076,7 +9076,7 @@
       </c>
       <c r="H101" s="94" t="inlineStr">
         <is>
-          <t>Piyush Makharia</t>
+          <t>Adil Khan</t>
         </is>
       </c>
       <c r="I101" s="94" t="inlineStr">
@@ -9086,7 +9086,7 @@
       </c>
       <c r="J101" s="94" t="inlineStr">
         <is>
-          <t>Amit Ranka</t>
+          <t>Ajit nair</t>
         </is>
       </c>
     </row>
@@ -9098,12 +9098,12 @@
       </c>
       <c r="B102" s="95" t="inlineStr">
         <is>
+          <t>3:00PM</t>
+        </is>
+      </c>
+      <c r="C102" s="95" t="inlineStr">
+        <is>
           <t>3:15PM</t>
-        </is>
-      </c>
-      <c r="C102" s="95" t="inlineStr">
-        <is>
-          <t>3:30PM</t>
         </is>
       </c>
       <c r="D102" s="95" t="inlineStr">
@@ -9116,17 +9116,17 @@
       </c>
       <c r="F102" s="95" t="inlineStr">
         <is>
-          <t>U46-SF1</t>
+          <t>U46-GB-7</t>
         </is>
       </c>
       <c r="G102" s="95" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H102" s="95" t="inlineStr">
         <is>
-          <t>Group B 1st</t>
+          <t>Piyush Makharia</t>
         </is>
       </c>
       <c r="I102" s="95" t="inlineStr">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="J102" s="95" t="inlineStr">
         <is>
-          <t>Group A 2nd</t>
+          <t>Amit Ranka</t>
         </is>
       </c>
     </row>
@@ -9158,7 +9158,7 @@
       </c>
       <c r="D103" s="94" t="inlineStr">
         <is>
-          <t>Under 46</t>
+          <t>Above 46</t>
         </is>
       </c>
       <c r="E103" s="94" t="n">
@@ -9166,17 +9166,17 @@
       </c>
       <c r="F103" s="94" t="inlineStr">
         <is>
-          <t>U46-SF2</t>
+          <t>A46-QF1</t>
         </is>
       </c>
       <c r="G103" s="94" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H103" s="94" t="inlineStr">
         <is>
-          <t>Group A 1st</t>
+          <t>Winner R1</t>
         </is>
       </c>
       <c r="I103" s="94" t="inlineStr">
@@ -9186,7 +9186,7 @@
       </c>
       <c r="J103" s="94" t="inlineStr">
         <is>
-          <t>Group B 2nd</t>
+          <t>Sanjay Kumar</t>
         </is>
       </c>
     </row>
@@ -9198,12 +9198,12 @@
       </c>
       <c r="B104" s="95" t="inlineStr">
         <is>
+          <t>3:15PM</t>
+        </is>
+      </c>
+      <c r="C104" s="95" t="inlineStr">
+        <is>
           <t>3:30PM</t>
-        </is>
-      </c>
-      <c r="C104" s="95" t="inlineStr">
-        <is>
-          <t>3:45PM</t>
         </is>
       </c>
       <c r="D104" s="95" t="inlineStr">
@@ -9216,17 +9216,17 @@
       </c>
       <c r="F104" s="95" t="inlineStr">
         <is>
-          <t>U46-FINAL</t>
+          <t>U46-SF1</t>
         </is>
       </c>
       <c r="G104" s="95" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H104" s="95" t="inlineStr">
         <is>
-          <t>Winner SF1</t>
+          <t>Group B 1st</t>
         </is>
       </c>
       <c r="I104" s="95" t="inlineStr">
@@ -9236,7 +9236,7 @@
       </c>
       <c r="J104" s="95" t="inlineStr">
         <is>
-          <t>Winner SF2</t>
+          <t>Group A 2nd</t>
         </is>
       </c>
     </row>
@@ -9248,12 +9248,12 @@
       </c>
       <c r="B105" s="94" t="inlineStr">
         <is>
+          <t>3:30PM</t>
+        </is>
+      </c>
+      <c r="C105" s="94" t="inlineStr">
+        <is>
           <t>3:45PM</t>
-        </is>
-      </c>
-      <c r="C105" s="94" t="inlineStr">
-        <is>
-          <t>4:00PM</t>
         </is>
       </c>
       <c r="D105" s="94" t="inlineStr">
@@ -9266,7 +9266,7 @@
       </c>
       <c r="F105" s="94" t="inlineStr">
         <is>
-          <t>A46-R1</t>
+          <t>A46-SF1</t>
         </is>
       </c>
       <c r="G105" s="94" t="inlineStr">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="H105" s="94" t="inlineStr">
         <is>
-          <t>Adil Khan</t>
+          <t>Winner QF1</t>
         </is>
       </c>
       <c r="I105" s="94" t="inlineStr">
@@ -9286,7 +9286,7 @@
       </c>
       <c r="J105" s="94" t="inlineStr">
         <is>
-          <t>Ajit nair</t>
+          <t>Winner QF2</t>
         </is>
       </c>
     </row>
@@ -9298,17 +9298,17 @@
       </c>
       <c r="B106" s="95" t="inlineStr">
         <is>
-          <t>4:00PM</t>
+          <t>3:30PM</t>
         </is>
       </c>
       <c r="C106" s="95" t="inlineStr">
         <is>
-          <t>4:15PM</t>
+          <t>3:45PM</t>
         </is>
       </c>
       <c r="D106" s="95" t="inlineStr">
         <is>
-          <t>Above 46</t>
+          <t>Under 46</t>
         </is>
       </c>
       <c r="E106" s="95" t="n">
@@ -9316,17 +9316,17 @@
       </c>
       <c r="F106" s="95" t="inlineStr">
         <is>
-          <t>A46-QF1</t>
+          <t>U46-SF2</t>
         </is>
       </c>
       <c r="G106" s="95" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H106" s="95" t="inlineStr">
         <is>
-          <t>Winner R1</t>
+          <t>Group A 1st</t>
         </is>
       </c>
       <c r="I106" s="95" t="inlineStr">
@@ -9336,7 +9336,7 @@
       </c>
       <c r="J106" s="95" t="inlineStr">
         <is>
-          <t>Sanjay Kumar</t>
+          <t>Group B 2nd</t>
         </is>
       </c>
     </row>
@@ -9348,12 +9348,12 @@
       </c>
       <c r="B107" s="94" t="inlineStr">
         <is>
-          <t>4:15PM</t>
+          <t>3:45PM</t>
         </is>
       </c>
       <c r="C107" s="94" t="inlineStr">
         <is>
-          <t>4:30PM</t>
+          <t>4:00PM</t>
         </is>
       </c>
       <c r="D107" s="94" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="F107" s="94" t="inlineStr">
         <is>
-          <t>A46-SF1</t>
+          <t>A46-FINAL</t>
         </is>
       </c>
       <c r="G107" s="94" t="inlineStr">
@@ -9376,7 +9376,7 @@
       </c>
       <c r="H107" s="94" t="inlineStr">
         <is>
-          <t>Winner QF1</t>
+          <t>Winner SF1</t>
         </is>
       </c>
       <c r="I107" s="94" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="J107" s="94" t="inlineStr">
         <is>
-          <t>Winner QF2</t>
+          <t>Winner SF2</t>
         </is>
       </c>
     </row>
@@ -9398,17 +9398,17 @@
       </c>
       <c r="B108" s="95" t="inlineStr">
         <is>
-          <t>4:30PM</t>
+          <t>3:45PM</t>
         </is>
       </c>
       <c r="C108" s="95" t="inlineStr">
         <is>
-          <t>4:45PM</t>
+          <t>4:00PM</t>
         </is>
       </c>
       <c r="D108" s="95" t="inlineStr">
         <is>
-          <t>Above 46</t>
+          <t>Under 46</t>
         </is>
       </c>
       <c r="E108" s="95" t="n">
@@ -9416,12 +9416,12 @@
       </c>
       <c r="F108" s="95" t="inlineStr">
         <is>
-          <t>A46-FINAL</t>
+          <t>U46-FINAL</t>
         </is>
       </c>
       <c r="G108" s="95" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H108" s="95" t="inlineStr">
@@ -9533,7 +9533,7 @@
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="A35:H35"/>
-    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="A34:H34"/>
     <mergeCell ref="D27:E27"/>
     <mergeCell ref="A12:J12"/>
     <mergeCell ref="A4:J4"/>
@@ -9541,7 +9541,7 @@
     <mergeCell ref="A26:J26"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A34:H34"/>
+    <mergeCell ref="D21:E21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10005,12 +10005,12 @@
       </c>
       <c r="B25" s="95" t="inlineStr">
         <is>
-          <t>3:00PM</t>
+          <t>4:00PM</t>
         </is>
       </c>
       <c r="C25" s="95" t="inlineStr">
         <is>
-          <t>3:15PM</t>
+          <t>4:15PM</t>
         </is>
       </c>
       <c r="D25" s="95" t="inlineStr">
@@ -10028,7 +10028,7 @@
       </c>
       <c r="G25" s="95" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H25" s="95" t="inlineStr">
@@ -10055,12 +10055,12 @@
       </c>
       <c r="B26" s="94" t="inlineStr">
         <is>
-          <t>3:30PM</t>
+          <t>4:15PM</t>
         </is>
       </c>
       <c r="C26" s="94" t="inlineStr">
         <is>
-          <t>3:45PM</t>
+          <t>4:30PM</t>
         </is>
       </c>
       <c r="D26" s="94" t="inlineStr">
@@ -10078,7 +10078,7 @@
       </c>
       <c r="G26" s="94" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H26" s="94" t="inlineStr">

--- a/Ekta_Schedule_With_Matchups.xlsx
+++ b/Ekta_Schedule_With_Matchups.xlsx
@@ -1262,7 +1262,7 @@
       </c>
       <c r="C16" s="64" t="inlineStr">
         <is>
-          <t>Remaining league matches continue (TT Men's, Carrom Men's, Pool, Chess). Pool's knockouts follow immediately once Pool's own league stage ends (~10:10 AM); Squash's Under 15 + 15-25 Bracket knockouts likewise follow right after Squash's own league stage (~6:39 PM Aug 15).</t>
+          <t>Remaining league matches continue (TT Men's, Carrom Men's, Pool). Chess's entire pool stage, semifinals, and final now complete by Aug 16 8:20 AM (reflowed to use real gaps in players' other-sport schedules — previously ran until 5:00 PM). Pool's knockouts follow immediately once Pool's own league stage ends (~10:10 AM); Squash's Under 15 + 15-25 Bracket knockouts likewise follow right after Squash's own league stage (~6:39 PM Aug 15).</t>
         </is>
       </c>
       <c r="H16" s="31" t="n"/>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="C19" s="64" t="inlineStr">
         <is>
-          <t>Once every event's league stage is finished, the remaining Semis/Finals begin: Carrom Men's Singles, TT Men's Singles, Chess, and Squash's Above 25 Bracket.</t>
+          <t>Once every event's league stage is finished, the remaining Semis/Finals begin: Carrom Men's Singles and Squash's Above 25 Bracket (Chess now finishes much earlier, by 8:20 AM Aug 16).</t>
         </is>
       </c>
       <c r="H19" s="31" t="n"/>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E28" s="63" t="inlineStr">
         <is>
-          <t>Aug16 5:00PM</t>
+          <t>Aug16 8:20AM</t>
         </is>
       </c>
       <c r="F28" s="31" t="n"/>
@@ -1680,7 +1680,7 @@
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="86" t="inlineStr">
         <is>
-          <t>Overall tournament span: Aug 15, 8:00 AM start → Aug 16, 5:00 PM finish — comfortably inside the Aug 16, 10 PM cap.</t>
+          <t>Overall tournament span: Aug 15, 8:00 AM start → Aug 16, 4:30 PM finish — comfortably inside the Aug 16, 10 PM cap.</t>
         </is>
       </c>
       <c r="F34" s="31" t="n"/>
@@ -18956,2902 +18956,2902 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="27" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B43" s="27" t="inlineStr">
+      <c r="A43" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B43" s="94" t="inlineStr">
         <is>
           <t>8:00AM</t>
         </is>
       </c>
-      <c r="C43" s="27" t="inlineStr">
+      <c r="C43" s="94" t="inlineStr">
         <is>
           <t>8:20AM</t>
         </is>
       </c>
-      <c r="D43" s="27" t="inlineStr">
+      <c r="D43" s="94" t="inlineStr">
         <is>
           <t>Under 11</t>
         </is>
       </c>
-      <c r="E43" s="27" t="n">
+      <c r="E43" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="F43" s="27" t="inlineStr">
+      <c r="F43" s="94" t="inlineStr">
         <is>
           <t>U11-1</t>
         </is>
       </c>
-      <c r="G43" s="27" t="inlineStr">
+      <c r="G43" s="94" t="inlineStr">
         <is>
           <t>Board 1</t>
         </is>
       </c>
-      <c r="H43" s="27" t="inlineStr">
+      <c r="H43" s="94" t="inlineStr">
         <is>
           <t>Rushabh</t>
         </is>
       </c>
-      <c r="I43" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J43" s="27" t="inlineStr">
+      <c r="I43" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J43" s="94" t="inlineStr">
         <is>
           <t>Neev Chauhan</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="28" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B44" s="28" t="inlineStr">
+      <c r="A44" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B44" s="95" t="inlineStr">
         <is>
           <t>8:00AM</t>
         </is>
       </c>
-      <c r="C44" s="28" t="inlineStr">
+      <c r="C44" s="95" t="inlineStr">
         <is>
           <t>8:20AM</t>
         </is>
       </c>
-      <c r="D44" s="28" t="inlineStr">
+      <c r="D44" s="95" t="inlineStr">
         <is>
           <t>Under 11</t>
         </is>
       </c>
-      <c r="E44" s="28" t="n">
+      <c r="E44" s="95" t="n">
         <v>2</v>
       </c>
-      <c r="F44" s="28" t="inlineStr">
+      <c r="F44" s="95" t="inlineStr">
         <is>
           <t>U11-2</t>
         </is>
       </c>
-      <c r="G44" s="28" t="inlineStr">
+      <c r="G44" s="95" t="inlineStr">
         <is>
           <t>Board 2</t>
         </is>
       </c>
-      <c r="H44" s="28" t="inlineStr">
+      <c r="H44" s="95" t="inlineStr">
         <is>
           <t>Kartik Relan</t>
         </is>
       </c>
-      <c r="I44" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J44" s="28" t="inlineStr">
+      <c r="I44" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J44" s="95" t="inlineStr">
         <is>
           <t>Parth yadav</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="27" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B45" s="27" t="inlineStr">
-        <is>
-          <t>8:30AM</t>
-        </is>
-      </c>
-      <c r="C45" s="27" t="inlineStr">
-        <is>
-          <t>8:50AM</t>
-        </is>
-      </c>
-      <c r="D45" s="27" t="inlineStr">
+      <c r="A45" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B45" s="94" t="inlineStr">
+        <is>
+          <t>8:20AM</t>
+        </is>
+      </c>
+      <c r="C45" s="94" t="inlineStr">
+        <is>
+          <t>8:40AM</t>
+        </is>
+      </c>
+      <c r="D45" s="94" t="inlineStr">
+        <is>
+          <t>12 to 20</t>
+        </is>
+      </c>
+      <c r="E45" s="94" t="n">
+        <v>3</v>
+      </c>
+      <c r="F45" s="94" t="inlineStr">
+        <is>
+          <t>1220-2</t>
+        </is>
+      </c>
+      <c r="G45" s="94" t="inlineStr">
+        <is>
+          <t>Board 1</t>
+        </is>
+      </c>
+      <c r="H45" s="94" t="inlineStr">
+        <is>
+          <t>Aaditya Kumar</t>
+        </is>
+      </c>
+      <c r="I45" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J45" s="94" t="inlineStr">
+        <is>
+          <t>Hryday Goyal</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B46" s="95" t="inlineStr">
+        <is>
+          <t>8:20AM</t>
+        </is>
+      </c>
+      <c r="C46" s="95" t="inlineStr">
+        <is>
+          <t>8:40AM</t>
+        </is>
+      </c>
+      <c r="D46" s="95" t="inlineStr">
+        <is>
+          <t>21 to 40</t>
+        </is>
+      </c>
+      <c r="E46" s="95" t="n">
+        <v>4</v>
+      </c>
+      <c r="F46" s="95" t="inlineStr">
+        <is>
+          <t>2140-2</t>
+        </is>
+      </c>
+      <c r="G46" s="95" t="inlineStr">
+        <is>
+          <t>Board 2</t>
+        </is>
+      </c>
+      <c r="H46" s="95" t="inlineStr">
+        <is>
+          <t>Swati Tripathi</t>
+        </is>
+      </c>
+      <c r="I46" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J46" s="95" t="inlineStr">
+        <is>
+          <t>Amit Nawandhar</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B47" s="94" t="inlineStr">
+        <is>
+          <t>8:40AM</t>
+        </is>
+      </c>
+      <c r="C47" s="94" t="inlineStr">
+        <is>
+          <t>9:00AM</t>
+        </is>
+      </c>
+      <c r="D47" s="94" t="inlineStr">
         <is>
           <t>Under 11</t>
         </is>
       </c>
-      <c r="E45" s="27" t="n">
-        <v>3</v>
-      </c>
-      <c r="F45" s="27" t="inlineStr">
+      <c r="E47" s="94" t="n">
+        <v>5</v>
+      </c>
+      <c r="F47" s="94" t="inlineStr">
         <is>
           <t>U11-3</t>
         </is>
       </c>
-      <c r="G45" s="27" t="inlineStr">
+      <c r="G47" s="94" t="inlineStr">
         <is>
           <t>Board 1</t>
         </is>
       </c>
-      <c r="H45" s="27" t="inlineStr">
+      <c r="H47" s="94" t="inlineStr">
         <is>
           <t>Rushabh</t>
         </is>
       </c>
-      <c r="I45" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J45" s="27" t="inlineStr">
+      <c r="I47" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J47" s="94" t="inlineStr">
         <is>
           <t>Kartik Relan</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="28" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B46" s="28" t="inlineStr">
-        <is>
-          <t>8:30AM</t>
-        </is>
-      </c>
-      <c r="C46" s="28" t="inlineStr">
-        <is>
-          <t>8:50AM</t>
-        </is>
-      </c>
-      <c r="D46" s="28" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B48" s="95" t="inlineStr">
+        <is>
+          <t>8:40AM</t>
+        </is>
+      </c>
+      <c r="C48" s="95" t="inlineStr">
+        <is>
+          <t>9:00AM</t>
+        </is>
+      </c>
+      <c r="D48" s="95" t="inlineStr">
         <is>
           <t>Under 11</t>
         </is>
       </c>
-      <c r="E46" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="F46" s="28" t="inlineStr">
+      <c r="E48" s="95" t="n">
+        <v>6</v>
+      </c>
+      <c r="F48" s="95" t="inlineStr">
         <is>
           <t>U11-4</t>
         </is>
       </c>
-      <c r="G46" s="28" t="inlineStr">
+      <c r="G48" s="95" t="inlineStr">
         <is>
           <t>Board 2</t>
         </is>
       </c>
-      <c r="H46" s="28" t="inlineStr">
+      <c r="H48" s="95" t="inlineStr">
         <is>
           <t>Neev Chauhan</t>
         </is>
       </c>
-      <c r="I46" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J46" s="28" t="inlineStr">
+      <c r="I48" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J48" s="95" t="inlineStr">
         <is>
           <t>Jimit Relan</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="27" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B47" s="27" t="inlineStr">
-        <is>
-          <t>8:50AM</t>
-        </is>
-      </c>
-      <c r="C47" s="27" t="inlineStr">
-        <is>
-          <t>9:10AM</t>
-        </is>
-      </c>
-      <c r="D47" s="27" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B49" s="94" t="inlineStr">
+        <is>
+          <t>9:00AM</t>
+        </is>
+      </c>
+      <c r="C49" s="94" t="inlineStr">
+        <is>
+          <t>9:20AM</t>
+        </is>
+      </c>
+      <c r="D49" s="94" t="inlineStr">
         <is>
           <t>12 to 20</t>
         </is>
       </c>
-      <c r="E47" s="27" t="n">
-        <v>5</v>
-      </c>
-      <c r="F47" s="27" t="inlineStr">
+      <c r="E49" s="94" t="n">
+        <v>7</v>
+      </c>
+      <c r="F49" s="94" t="inlineStr">
         <is>
           <t>1220-1</t>
         </is>
       </c>
-      <c r="G47" s="27" t="inlineStr">
+      <c r="G49" s="94" t="inlineStr">
         <is>
           <t>Board 1</t>
         </is>
       </c>
-      <c r="H47" s="27" t="inlineStr">
+      <c r="H49" s="94" t="inlineStr">
         <is>
           <t>Aadit Joshi</t>
         </is>
       </c>
-      <c r="I47" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J47" s="27" t="inlineStr">
+      <c r="I49" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J49" s="94" t="inlineStr">
         <is>
           <t>Maitreya Manvik</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="28" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B48" s="28" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B50" s="95" t="inlineStr">
         <is>
           <t>9:00AM</t>
         </is>
       </c>
-      <c r="C48" s="28" t="inlineStr">
+      <c r="C50" s="95" t="inlineStr">
         <is>
           <t>9:20AM</t>
         </is>
       </c>
-      <c r="D48" s="28" t="inlineStr">
+      <c r="D50" s="95" t="inlineStr">
+        <is>
+          <t>21 to 40</t>
+        </is>
+      </c>
+      <c r="E50" s="95" t="n">
+        <v>8</v>
+      </c>
+      <c r="F50" s="95" t="inlineStr">
+        <is>
+          <t>2140-6</t>
+        </is>
+      </c>
+      <c r="G50" s="95" t="inlineStr">
+        <is>
+          <t>Board 2</t>
+        </is>
+      </c>
+      <c r="H50" s="95" t="inlineStr">
+        <is>
+          <t>Tej</t>
+        </is>
+      </c>
+      <c r="I50" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J50" s="95" t="inlineStr">
+        <is>
+          <t>Swati Tripathi</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B51" s="94" t="inlineStr">
+        <is>
+          <t>9:20AM</t>
+        </is>
+      </c>
+      <c r="C51" s="94" t="inlineStr">
+        <is>
+          <t>9:40AM</t>
+        </is>
+      </c>
+      <c r="D51" s="94" t="inlineStr">
         <is>
           <t>Under 11</t>
         </is>
       </c>
-      <c r="E48" s="28" t="n">
-        <v>6</v>
-      </c>
-      <c r="F48" s="28" t="inlineStr">
+      <c r="E51" s="94" t="n">
+        <v>9</v>
+      </c>
+      <c r="F51" s="94" t="inlineStr">
         <is>
           <t>U11-5</t>
         </is>
       </c>
-      <c r="G48" s="28" t="inlineStr">
+      <c r="G51" s="94" t="inlineStr">
+        <is>
+          <t>Board 1</t>
+        </is>
+      </c>
+      <c r="H51" s="94" t="inlineStr">
+        <is>
+          <t>Kartik Relan</t>
+        </is>
+      </c>
+      <c r="I51" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J51" s="94" t="inlineStr">
+        <is>
+          <t>Jimit Relan</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B52" s="95" t="inlineStr">
+        <is>
+          <t>9:20AM</t>
+        </is>
+      </c>
+      <c r="C52" s="95" t="inlineStr">
+        <is>
+          <t>9:40AM</t>
+        </is>
+      </c>
+      <c r="D52" s="95" t="inlineStr">
+        <is>
+          <t>Under 11</t>
+        </is>
+      </c>
+      <c r="E52" s="95" t="n">
+        <v>10</v>
+      </c>
+      <c r="F52" s="95" t="inlineStr">
+        <is>
+          <t>U11-6</t>
+        </is>
+      </c>
+      <c r="G52" s="95" t="inlineStr">
         <is>
           <t>Board 2</t>
         </is>
       </c>
-      <c r="H48" s="28" t="inlineStr">
+      <c r="H52" s="95" t="inlineStr">
+        <is>
+          <t>Rushabh</t>
+        </is>
+      </c>
+      <c r="I52" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J52" s="95" t="inlineStr">
+        <is>
+          <t>Parth yadav</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B53" s="94" t="inlineStr">
+        <is>
+          <t>10:30AM</t>
+        </is>
+      </c>
+      <c r="C53" s="94" t="inlineStr">
+        <is>
+          <t>10:50AM</t>
+        </is>
+      </c>
+      <c r="D53" s="94" t="inlineStr">
+        <is>
+          <t>Under 11</t>
+        </is>
+      </c>
+      <c r="E53" s="94" t="n">
+        <v>11</v>
+      </c>
+      <c r="F53" s="94" t="inlineStr">
+        <is>
+          <t>U11-7</t>
+        </is>
+      </c>
+      <c r="G53" s="94" t="inlineStr">
+        <is>
+          <t>Board 1</t>
+        </is>
+      </c>
+      <c r="H53" s="94" t="inlineStr">
+        <is>
+          <t>Rushabh</t>
+        </is>
+      </c>
+      <c r="I53" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J53" s="94" t="inlineStr">
+        <is>
+          <t>Jimit Relan</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B54" s="95" t="inlineStr">
+        <is>
+          <t>10:30AM</t>
+        </is>
+      </c>
+      <c r="C54" s="95" t="inlineStr">
+        <is>
+          <t>10:50AM</t>
+        </is>
+      </c>
+      <c r="D54" s="95" t="inlineStr">
+        <is>
+          <t>Under 11</t>
+        </is>
+      </c>
+      <c r="E54" s="95" t="n">
+        <v>12</v>
+      </c>
+      <c r="F54" s="95" t="inlineStr">
+        <is>
+          <t>U11-8</t>
+        </is>
+      </c>
+      <c r="G54" s="95" t="inlineStr">
+        <is>
+          <t>Board 2</t>
+        </is>
+      </c>
+      <c r="H54" s="95" t="inlineStr">
+        <is>
+          <t>Neev Chauhan</t>
+        </is>
+      </c>
+      <c r="I54" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J54" s="95" t="inlineStr">
         <is>
           <t>Kartik Relan</t>
         </is>
       </c>
-      <c r="I48" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J48" s="28" t="inlineStr">
+    </row>
+    <row r="55">
+      <c r="A55" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B55" s="94" t="inlineStr">
+        <is>
+          <t>10:50AM</t>
+        </is>
+      </c>
+      <c r="C55" s="94" t="inlineStr">
+        <is>
+          <t>11:10AM</t>
+        </is>
+      </c>
+      <c r="D55" s="94" t="inlineStr">
+        <is>
+          <t>12 to 20</t>
+        </is>
+      </c>
+      <c r="E55" s="94" t="n">
+        <v>13</v>
+      </c>
+      <c r="F55" s="94" t="inlineStr">
+        <is>
+          <t>1220-3</t>
+        </is>
+      </c>
+      <c r="G55" s="94" t="inlineStr">
+        <is>
+          <t>Board 1</t>
+        </is>
+      </c>
+      <c r="H55" s="94" t="inlineStr">
+        <is>
+          <t>Aadit Joshi</t>
+        </is>
+      </c>
+      <c r="I55" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J55" s="94" t="inlineStr">
+        <is>
+          <t>Aaditya Kumar</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B56" s="95" t="inlineStr">
+        <is>
+          <t>10:50AM</t>
+        </is>
+      </c>
+      <c r="C56" s="95" t="inlineStr">
+        <is>
+          <t>11:10AM</t>
+        </is>
+      </c>
+      <c r="D56" s="95" t="inlineStr">
+        <is>
+          <t>12 to 20</t>
+        </is>
+      </c>
+      <c r="E56" s="95" t="n">
+        <v>14</v>
+      </c>
+      <c r="F56" s="95" t="inlineStr">
+        <is>
+          <t>1220-4</t>
+        </is>
+      </c>
+      <c r="G56" s="95" t="inlineStr">
+        <is>
+          <t>Board 2</t>
+        </is>
+      </c>
+      <c r="H56" s="95" t="inlineStr">
+        <is>
+          <t>Maitreya Manvik</t>
+        </is>
+      </c>
+      <c r="I56" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J56" s="95" t="inlineStr">
+        <is>
+          <t>Hryday Goyal</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B57" s="94" t="inlineStr">
+        <is>
+          <t>11:10AM</t>
+        </is>
+      </c>
+      <c r="C57" s="94" t="inlineStr">
+        <is>
+          <t>11:30AM</t>
+        </is>
+      </c>
+      <c r="D57" s="94" t="inlineStr">
+        <is>
+          <t>21 to 40</t>
+        </is>
+      </c>
+      <c r="E57" s="94" t="n">
+        <v>15</v>
+      </c>
+      <c r="F57" s="94" t="inlineStr">
+        <is>
+          <t>2140-3</t>
+        </is>
+      </c>
+      <c r="G57" s="94" t="inlineStr">
+        <is>
+          <t>Board 2</t>
+        </is>
+      </c>
+      <c r="H57" s="94" t="inlineStr">
+        <is>
+          <t>Rahul Garg</t>
+        </is>
+      </c>
+      <c r="I57" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J57" s="94" t="inlineStr">
+        <is>
+          <t>Amit Nawandhar</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B58" s="95" t="inlineStr">
+        <is>
+          <t>11:10AM</t>
+        </is>
+      </c>
+      <c r="C58" s="95" t="inlineStr">
+        <is>
+          <t>11:30AM</t>
+        </is>
+      </c>
+      <c r="D58" s="95" t="inlineStr">
+        <is>
+          <t>Under 11</t>
+        </is>
+      </c>
+      <c r="E58" s="95" t="n">
+        <v>16</v>
+      </c>
+      <c r="F58" s="95" t="inlineStr">
+        <is>
+          <t>U11-9</t>
+        </is>
+      </c>
+      <c r="G58" s="95" t="inlineStr">
+        <is>
+          <t>Board 1</t>
+        </is>
+      </c>
+      <c r="H58" s="95" t="inlineStr">
+        <is>
+          <t>Neev Chauhan</t>
+        </is>
+      </c>
+      <c r="I58" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J58" s="95" t="inlineStr">
+        <is>
+          <t>Parth yadav</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B59" s="94" t="inlineStr">
+        <is>
+          <t>11:30AM</t>
+        </is>
+      </c>
+      <c r="C59" s="94" t="inlineStr">
+        <is>
+          <t>11:50AM</t>
+        </is>
+      </c>
+      <c r="D59" s="94" t="inlineStr">
+        <is>
+          <t>12 to 20</t>
+        </is>
+      </c>
+      <c r="E59" s="94" t="n">
+        <v>17</v>
+      </c>
+      <c r="F59" s="94" t="inlineStr">
+        <is>
+          <t>1220-5</t>
+        </is>
+      </c>
+      <c r="G59" s="94" t="inlineStr">
+        <is>
+          <t>Board 1</t>
+        </is>
+      </c>
+      <c r="H59" s="94" t="inlineStr">
+        <is>
+          <t>Aadit Joshi</t>
+        </is>
+      </c>
+      <c r="I59" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J59" s="94" t="inlineStr">
+        <is>
+          <t>Hryday Goyal</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B60" s="95" t="inlineStr">
+        <is>
+          <t>11:30AM</t>
+        </is>
+      </c>
+      <c r="C60" s="95" t="inlineStr">
+        <is>
+          <t>11:50AM</t>
+        </is>
+      </c>
+      <c r="D60" s="95" t="inlineStr">
+        <is>
+          <t>12 to 20</t>
+        </is>
+      </c>
+      <c r="E60" s="95" t="n">
+        <v>18</v>
+      </c>
+      <c r="F60" s="95" t="inlineStr">
+        <is>
+          <t>1220-6</t>
+        </is>
+      </c>
+      <c r="G60" s="95" t="inlineStr">
+        <is>
+          <t>Board 2</t>
+        </is>
+      </c>
+      <c r="H60" s="95" t="inlineStr">
+        <is>
+          <t>Maitreya Manvik</t>
+        </is>
+      </c>
+      <c r="I60" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J60" s="95" t="inlineStr">
+        <is>
+          <t>Aaditya Kumar</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B61" s="94" t="inlineStr">
+        <is>
+          <t>11:50AM</t>
+        </is>
+      </c>
+      <c r="C61" s="94" t="inlineStr">
+        <is>
+          <t>12:10PM</t>
+        </is>
+      </c>
+      <c r="D61" s="94" t="inlineStr">
+        <is>
+          <t>21 to 40</t>
+        </is>
+      </c>
+      <c r="E61" s="94" t="n">
+        <v>19</v>
+      </c>
+      <c r="F61" s="94" t="inlineStr">
+        <is>
+          <t>2140-1</t>
+        </is>
+      </c>
+      <c r="G61" s="94" t="inlineStr">
+        <is>
+          <t>Board 2</t>
+        </is>
+      </c>
+      <c r="H61" s="94" t="inlineStr">
+        <is>
+          <t>Tej</t>
+        </is>
+      </c>
+      <c r="I61" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J61" s="94" t="inlineStr">
+        <is>
+          <t>Tejas doshi</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B62" s="95" t="inlineStr">
+        <is>
+          <t>11:50AM</t>
+        </is>
+      </c>
+      <c r="C62" s="95" t="inlineStr">
+        <is>
+          <t>12:10PM</t>
+        </is>
+      </c>
+      <c r="D62" s="95" t="inlineStr">
+        <is>
+          <t>Under 11</t>
+        </is>
+      </c>
+      <c r="E62" s="95" t="n">
+        <v>20</v>
+      </c>
+      <c r="F62" s="95" t="inlineStr">
+        <is>
+          <t>U11-10</t>
+        </is>
+      </c>
+      <c r="G62" s="95" t="inlineStr">
+        <is>
+          <t>Board 1</t>
+        </is>
+      </c>
+      <c r="H62" s="95" t="inlineStr">
+        <is>
+          <t>Parth yadav</t>
+        </is>
+      </c>
+      <c r="I62" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J62" s="95" t="inlineStr">
         <is>
           <t>Jimit Relan</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="27" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B49" s="27" t="inlineStr">
-        <is>
-          <t>9:10AM</t>
-        </is>
-      </c>
-      <c r="C49" s="27" t="inlineStr">
-        <is>
-          <t>9:30AM</t>
-        </is>
-      </c>
-      <c r="D49" s="27" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B63" s="94" t="inlineStr">
+        <is>
+          <t>3:00PM</t>
+        </is>
+      </c>
+      <c r="C63" s="94" t="inlineStr">
+        <is>
+          <t>3:20PM</t>
+        </is>
+      </c>
+      <c r="D63" s="94" t="inlineStr">
+        <is>
+          <t>21 to 40</t>
+        </is>
+      </c>
+      <c r="E63" s="94" t="n">
+        <v>21</v>
+      </c>
+      <c r="F63" s="94" t="inlineStr">
+        <is>
+          <t>2140-4</t>
+        </is>
+      </c>
+      <c r="G63" s="94" t="inlineStr">
+        <is>
+          <t>Board 1</t>
+        </is>
+      </c>
+      <c r="H63" s="94" t="inlineStr">
+        <is>
+          <t>Swati Tripathi</t>
+        </is>
+      </c>
+      <c r="I63" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J63" s="94" t="inlineStr">
+        <is>
+          <t>Tejas doshi</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B64" s="95" t="inlineStr">
+        <is>
+          <t>3:00PM</t>
+        </is>
+      </c>
+      <c r="C64" s="95" t="inlineStr">
+        <is>
+          <t>3:20PM</t>
+        </is>
+      </c>
+      <c r="D64" s="95" t="inlineStr">
+        <is>
+          <t>41 and above</t>
+        </is>
+      </c>
+      <c r="E64" s="95" t="n">
+        <v>22</v>
+      </c>
+      <c r="F64" s="95" t="inlineStr">
+        <is>
+          <t>41P-1</t>
+        </is>
+      </c>
+      <c r="G64" s="95" t="inlineStr">
+        <is>
+          <t>Board 2</t>
+        </is>
+      </c>
+      <c r="H64" s="95" t="inlineStr">
+        <is>
+          <t>Piyush Makharia</t>
+        </is>
+      </c>
+      <c r="I64" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J64" s="95" t="inlineStr">
+        <is>
+          <t>Ajit nair</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B65" s="94" t="inlineStr">
+        <is>
+          <t>3:20PM</t>
+        </is>
+      </c>
+      <c r="C65" s="94" t="inlineStr">
+        <is>
+          <t>3:40PM</t>
+        </is>
+      </c>
+      <c r="D65" s="94" t="inlineStr">
+        <is>
+          <t>21 to 40</t>
+        </is>
+      </c>
+      <c r="E65" s="94" t="n">
+        <v>23</v>
+      </c>
+      <c r="F65" s="94" t="inlineStr">
+        <is>
+          <t>2140-10</t>
+        </is>
+      </c>
+      <c r="G65" s="94" t="inlineStr">
+        <is>
+          <t>Board 1</t>
+        </is>
+      </c>
+      <c r="H65" s="94" t="inlineStr">
+        <is>
+          <t>Amit Nawandhar</t>
+        </is>
+      </c>
+      <c r="I65" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J65" s="94" t="inlineStr">
+        <is>
+          <t>Nikunj Jhala</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B66" s="95" t="inlineStr">
+        <is>
+          <t>3:20PM</t>
+        </is>
+      </c>
+      <c r="C66" s="95" t="inlineStr">
+        <is>
+          <t>3:40PM</t>
+        </is>
+      </c>
+      <c r="D66" s="95" t="inlineStr">
+        <is>
+          <t>41 and above</t>
+        </is>
+      </c>
+      <c r="E66" s="95" t="n">
+        <v>24</v>
+      </c>
+      <c r="F66" s="95" t="inlineStr">
+        <is>
+          <t>41P-8</t>
+        </is>
+      </c>
+      <c r="G66" s="95" t="inlineStr">
+        <is>
+          <t>Board 2</t>
+        </is>
+      </c>
+      <c r="H66" s="95" t="inlineStr">
+        <is>
+          <t>Prasad Akshintala</t>
+        </is>
+      </c>
+      <c r="I66" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J66" s="95" t="inlineStr">
+        <is>
+          <t>Sanjay Kumar</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B67" s="94" t="inlineStr">
+        <is>
+          <t>3:40PM</t>
+        </is>
+      </c>
+      <c r="C67" s="94" t="inlineStr">
+        <is>
+          <t>4:00PM</t>
+        </is>
+      </c>
+      <c r="D67" s="94" t="inlineStr">
+        <is>
+          <t>21 to 40</t>
+        </is>
+      </c>
+      <c r="E67" s="94" t="n">
+        <v>25</v>
+      </c>
+      <c r="F67" s="94" t="inlineStr">
+        <is>
+          <t>2140-9</t>
+        </is>
+      </c>
+      <c r="G67" s="94" t="inlineStr">
+        <is>
+          <t>Board 1</t>
+        </is>
+      </c>
+      <c r="H67" s="94" t="inlineStr">
+        <is>
+          <t>Rahul Garg</t>
+        </is>
+      </c>
+      <c r="I67" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J67" s="94" t="inlineStr">
+        <is>
+          <t>Tej</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B68" s="95" t="inlineStr">
+        <is>
+          <t>3:40PM</t>
+        </is>
+      </c>
+      <c r="C68" s="95" t="inlineStr">
+        <is>
+          <t>4:00PM</t>
+        </is>
+      </c>
+      <c r="D68" s="95" t="inlineStr">
+        <is>
+          <t>41 and above</t>
+        </is>
+      </c>
+      <c r="E68" s="95" t="n">
+        <v>26</v>
+      </c>
+      <c r="F68" s="95" t="inlineStr">
+        <is>
+          <t>41P-12</t>
+        </is>
+      </c>
+      <c r="G68" s="95" t="inlineStr">
+        <is>
+          <t>Board 2</t>
+        </is>
+      </c>
+      <c r="H68" s="95" t="inlineStr">
+        <is>
+          <t>Adil Khan</t>
+        </is>
+      </c>
+      <c r="I68" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J68" s="95" t="inlineStr">
+        <is>
+          <t>Ajit nair</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B69" s="94" t="inlineStr">
+        <is>
+          <t>4:00PM</t>
+        </is>
+      </c>
+      <c r="C69" s="94" t="inlineStr">
+        <is>
+          <t>4:20PM</t>
+        </is>
+      </c>
+      <c r="D69" s="94" t="inlineStr">
+        <is>
+          <t>21 to 40</t>
+        </is>
+      </c>
+      <c r="E69" s="94" t="n">
+        <v>27</v>
+      </c>
+      <c r="F69" s="94" t="inlineStr">
+        <is>
+          <t>2140-5</t>
+        </is>
+      </c>
+      <c r="G69" s="94" t="inlineStr">
+        <is>
+          <t>Board 1</t>
+        </is>
+      </c>
+      <c r="H69" s="94" t="inlineStr">
+        <is>
+          <t>Amit Nawandhar</t>
+        </is>
+      </c>
+      <c r="I69" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J69" s="94" t="inlineStr">
+        <is>
+          <t>Tejas doshi</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B70" s="95" t="inlineStr">
+        <is>
+          <t>4:00PM</t>
+        </is>
+      </c>
+      <c r="C70" s="95" t="inlineStr">
+        <is>
+          <t>4:20PM</t>
+        </is>
+      </c>
+      <c r="D70" s="95" t="inlineStr">
+        <is>
+          <t>41 and above</t>
+        </is>
+      </c>
+      <c r="E70" s="95" t="n">
+        <v>28</v>
+      </c>
+      <c r="F70" s="95" t="inlineStr">
+        <is>
+          <t>41P-3</t>
+        </is>
+      </c>
+      <c r="G70" s="95" t="inlineStr">
+        <is>
+          <t>Board 2</t>
+        </is>
+      </c>
+      <c r="H70" s="95" t="inlineStr">
+        <is>
+          <t>Piyush Makharia</t>
+        </is>
+      </c>
+      <c r="I70" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J70" s="95" t="inlineStr">
+        <is>
+          <t>Prasad Akshintala</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B71" s="94" t="inlineStr">
+        <is>
+          <t>4:20PM</t>
+        </is>
+      </c>
+      <c r="C71" s="94" t="inlineStr">
+        <is>
+          <t>4:40PM</t>
+        </is>
+      </c>
+      <c r="D71" s="94" t="inlineStr">
+        <is>
+          <t>21 to 40</t>
+        </is>
+      </c>
+      <c r="E71" s="94" t="n">
+        <v>29</v>
+      </c>
+      <c r="F71" s="94" t="inlineStr">
+        <is>
+          <t>2140-13</t>
+        </is>
+      </c>
+      <c r="G71" s="94" t="inlineStr">
+        <is>
+          <t>Board 1</t>
+        </is>
+      </c>
+      <c r="H71" s="94" t="inlineStr">
+        <is>
+          <t>Rahul Garg</t>
+        </is>
+      </c>
+      <c r="I71" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J71" s="94" t="inlineStr">
+        <is>
+          <t>Swati Tripathi</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B72" s="95" t="inlineStr">
+        <is>
+          <t>4:20PM</t>
+        </is>
+      </c>
+      <c r="C72" s="95" t="inlineStr">
+        <is>
+          <t>4:40PM</t>
+        </is>
+      </c>
+      <c r="D72" s="95" t="inlineStr">
+        <is>
+          <t>41 and above</t>
+        </is>
+      </c>
+      <c r="E72" s="95" t="n">
+        <v>30</v>
+      </c>
+      <c r="F72" s="95" t="inlineStr">
+        <is>
+          <t>41P-2</t>
+        </is>
+      </c>
+      <c r="G72" s="95" t="inlineStr">
+        <is>
+          <t>Board 2</t>
+        </is>
+      </c>
+      <c r="H72" s="95" t="inlineStr">
+        <is>
+          <t>Ajit nair</t>
+        </is>
+      </c>
+      <c r="I72" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J72" s="95" t="inlineStr">
+        <is>
+          <t>Sanjay Kumar</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B73" s="94" t="inlineStr">
+        <is>
+          <t>4:40PM</t>
+        </is>
+      </c>
+      <c r="C73" s="94" t="inlineStr">
+        <is>
+          <t>5:00PM</t>
+        </is>
+      </c>
+      <c r="D73" s="94" t="inlineStr">
+        <is>
+          <t>21 to 40</t>
+        </is>
+      </c>
+      <c r="E73" s="94" t="n">
+        <v>31</v>
+      </c>
+      <c r="F73" s="94" t="inlineStr">
+        <is>
+          <t>2140-12</t>
+        </is>
+      </c>
+      <c r="G73" s="94" t="inlineStr">
+        <is>
+          <t>Board 1</t>
+        </is>
+      </c>
+      <c r="H73" s="94" t="inlineStr">
+        <is>
+          <t>Tej</t>
+        </is>
+      </c>
+      <c r="I73" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J73" s="94" t="inlineStr">
+        <is>
+          <t>Amit Nawandhar</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B74" s="95" t="inlineStr">
+        <is>
+          <t>4:40PM</t>
+        </is>
+      </c>
+      <c r="C74" s="95" t="inlineStr">
+        <is>
+          <t>5:00PM</t>
+        </is>
+      </c>
+      <c r="D74" s="95" t="inlineStr">
+        <is>
+          <t>41 and above</t>
+        </is>
+      </c>
+      <c r="E74" s="95" t="n">
+        <v>32</v>
+      </c>
+      <c r="F74" s="95" t="inlineStr">
+        <is>
+          <t>41P-6</t>
+        </is>
+      </c>
+      <c r="G74" s="95" t="inlineStr">
+        <is>
+          <t>Board 2</t>
+        </is>
+      </c>
+      <c r="H74" s="95" t="inlineStr">
+        <is>
+          <t>Piyush Makharia</t>
+        </is>
+      </c>
+      <c r="I74" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J74" s="95" t="inlineStr">
+        <is>
+          <t>Adil Khan</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B75" s="94" t="inlineStr">
+        <is>
+          <t>5:00PM</t>
+        </is>
+      </c>
+      <c r="C75" s="94" t="inlineStr">
+        <is>
+          <t>5:20PM</t>
+        </is>
+      </c>
+      <c r="D75" s="94" t="inlineStr">
+        <is>
+          <t>21 to 40</t>
+        </is>
+      </c>
+      <c r="E75" s="94" t="n">
+        <v>33</v>
+      </c>
+      <c r="F75" s="94" t="inlineStr">
+        <is>
+          <t>2140-15</t>
+        </is>
+      </c>
+      <c r="G75" s="94" t="inlineStr">
+        <is>
+          <t>Board 1</t>
+        </is>
+      </c>
+      <c r="H75" s="94" t="inlineStr">
+        <is>
+          <t>Rahul Garg</t>
+        </is>
+      </c>
+      <c r="I75" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J75" s="94" t="inlineStr">
+        <is>
+          <t>Tejas doshi</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B76" s="95" t="inlineStr">
+        <is>
+          <t>5:00PM</t>
+        </is>
+      </c>
+      <c r="C76" s="95" t="inlineStr">
+        <is>
+          <t>5:20PM</t>
+        </is>
+      </c>
+      <c r="D76" s="95" t="inlineStr">
+        <is>
+          <t>41 and above</t>
+        </is>
+      </c>
+      <c r="E76" s="95" t="n">
+        <v>34</v>
+      </c>
+      <c r="F76" s="95" t="inlineStr">
+        <is>
+          <t>41P-11</t>
+        </is>
+      </c>
+      <c r="G76" s="95" t="inlineStr">
+        <is>
+          <t>Board 2</t>
+        </is>
+      </c>
+      <c r="H76" s="95" t="inlineStr">
+        <is>
+          <t>Sachin Malgadnkar</t>
+        </is>
+      </c>
+      <c r="I76" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J76" s="95" t="inlineStr">
+        <is>
+          <t>Sanjay Kumar</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B77" s="94" t="inlineStr">
+        <is>
+          <t>5:20PM</t>
+        </is>
+      </c>
+      <c r="C77" s="94" t="inlineStr">
+        <is>
+          <t>5:40PM</t>
+        </is>
+      </c>
+      <c r="D77" s="94" t="inlineStr">
+        <is>
+          <t>21 to 40</t>
+        </is>
+      </c>
+      <c r="E77" s="94" t="n">
+        <v>35</v>
+      </c>
+      <c r="F77" s="94" t="inlineStr">
+        <is>
+          <t>2140-11</t>
+        </is>
+      </c>
+      <c r="G77" s="94" t="inlineStr">
+        <is>
+          <t>Board 1</t>
+        </is>
+      </c>
+      <c r="H77" s="94" t="inlineStr">
+        <is>
+          <t>Swati Tripathi</t>
+        </is>
+      </c>
+      <c r="I77" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J77" s="94" t="inlineStr">
+        <is>
+          <t>Nikunj Jhala</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B78" s="95" t="inlineStr">
+        <is>
+          <t>5:20PM</t>
+        </is>
+      </c>
+      <c r="C78" s="95" t="inlineStr">
+        <is>
+          <t>5:40PM</t>
+        </is>
+      </c>
+      <c r="D78" s="95" t="inlineStr">
+        <is>
+          <t>41 and above</t>
+        </is>
+      </c>
+      <c r="E78" s="95" t="n">
+        <v>36</v>
+      </c>
+      <c r="F78" s="95" t="inlineStr">
+        <is>
+          <t>41P-16</t>
+        </is>
+      </c>
+      <c r="G78" s="95" t="inlineStr">
+        <is>
+          <t>Board 2</t>
+        </is>
+      </c>
+      <c r="H78" s="95" t="inlineStr">
+        <is>
+          <t>Adil Khan</t>
+        </is>
+      </c>
+      <c r="I78" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J78" s="95" t="inlineStr">
+        <is>
+          <t>Harkishin malkan</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B79" s="94" t="inlineStr">
+        <is>
+          <t>5:40PM</t>
+        </is>
+      </c>
+      <c r="C79" s="94" t="inlineStr">
+        <is>
+          <t>6:00PM</t>
+        </is>
+      </c>
+      <c r="D79" s="94" t="inlineStr">
+        <is>
+          <t>12 to 20</t>
+        </is>
+      </c>
+      <c r="E79" s="94" t="n">
+        <v>37</v>
+      </c>
+      <c r="F79" s="94" t="inlineStr">
+        <is>
+          <t>1220-FINAL</t>
+        </is>
+      </c>
+      <c r="G79" s="94" t="inlineStr">
+        <is>
+          <t>Board 2</t>
+        </is>
+      </c>
+      <c r="H79" s="94" t="inlineStr">
+        <is>
+          <t>Pool 1st</t>
+        </is>
+      </c>
+      <c r="I79" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J79" s="94" t="inlineStr">
+        <is>
+          <t>Pool 2nd</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B80" s="95" t="inlineStr">
+        <is>
+          <t>5:40PM</t>
+        </is>
+      </c>
+      <c r="C80" s="95" t="inlineStr">
+        <is>
+          <t>6:00PM</t>
+        </is>
+      </c>
+      <c r="D80" s="95" t="inlineStr">
+        <is>
+          <t>41 and above</t>
+        </is>
+      </c>
+      <c r="E80" s="95" t="n">
+        <v>38</v>
+      </c>
+      <c r="F80" s="95" t="inlineStr">
+        <is>
+          <t>41P-17</t>
+        </is>
+      </c>
+      <c r="G80" s="95" t="inlineStr">
+        <is>
+          <t>Board 1</t>
+        </is>
+      </c>
+      <c r="H80" s="95" t="inlineStr">
+        <is>
+          <t>Sachin Malgadnkar</t>
+        </is>
+      </c>
+      <c r="I80" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J80" s="95" t="inlineStr">
+        <is>
+          <t>Ajit nair</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B81" s="94" t="inlineStr">
+        <is>
+          <t>6:00PM</t>
+        </is>
+      </c>
+      <c r="C81" s="94" t="inlineStr">
+        <is>
+          <t>6:20PM</t>
+        </is>
+      </c>
+      <c r="D81" s="94" t="inlineStr">
+        <is>
+          <t>21 to 40</t>
+        </is>
+      </c>
+      <c r="E81" s="94" t="n">
+        <v>39</v>
+      </c>
+      <c r="F81" s="94" t="inlineStr">
+        <is>
+          <t>2140-7</t>
+        </is>
+      </c>
+      <c r="G81" s="94" t="inlineStr">
+        <is>
+          <t>Board 1</t>
+        </is>
+      </c>
+      <c r="H81" s="94" t="inlineStr">
+        <is>
+          <t>Rahul Garg</t>
+        </is>
+      </c>
+      <c r="I81" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J81" s="94" t="inlineStr">
+        <is>
+          <t>Nikunj Jhala</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B82" s="95" t="inlineStr">
+        <is>
+          <t>6:00PM</t>
+        </is>
+      </c>
+      <c r="C82" s="95" t="inlineStr">
+        <is>
+          <t>6:20PM</t>
+        </is>
+      </c>
+      <c r="D82" s="95" t="inlineStr">
+        <is>
+          <t>41 and above</t>
+        </is>
+      </c>
+      <c r="E82" s="95" t="n">
+        <v>40</v>
+      </c>
+      <c r="F82" s="95" t="inlineStr">
+        <is>
+          <t>41P-18</t>
+        </is>
+      </c>
+      <c r="G82" s="95" t="inlineStr">
+        <is>
+          <t>Board 2</t>
+        </is>
+      </c>
+      <c r="H82" s="95" t="inlineStr">
+        <is>
+          <t>Piyush Makharia</t>
+        </is>
+      </c>
+      <c r="I82" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J82" s="95" t="inlineStr">
+        <is>
+          <t>Harkishin malkan</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B83" s="94" t="inlineStr">
+        <is>
+          <t>6:20PM</t>
+        </is>
+      </c>
+      <c r="C83" s="94" t="inlineStr">
+        <is>
+          <t>6:40PM</t>
+        </is>
+      </c>
+      <c r="D83" s="94" t="inlineStr">
         <is>
           <t>Under 11</t>
         </is>
       </c>
-      <c r="E49" s="27" t="n">
-        <v>7</v>
-      </c>
-      <c r="F49" s="27" t="inlineStr">
-        <is>
-          <t>U11-6</t>
-        </is>
-      </c>
-      <c r="G49" s="27" t="inlineStr">
+      <c r="E83" s="94" t="n">
+        <v>41</v>
+      </c>
+      <c r="F83" s="94" t="inlineStr">
+        <is>
+          <t>U11-FINAL</t>
+        </is>
+      </c>
+      <c r="G83" s="94" t="inlineStr">
         <is>
           <t>Board 1</t>
         </is>
       </c>
-      <c r="H49" s="27" t="inlineStr">
-        <is>
-          <t>Rushabh</t>
-        </is>
-      </c>
-      <c r="I49" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J49" s="27" t="inlineStr">
-        <is>
-          <t>Parth yadav</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="28" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B50" s="28" t="inlineStr">
-        <is>
-          <t>10:30AM</t>
-        </is>
-      </c>
-      <c r="C50" s="28" t="inlineStr">
-        <is>
-          <t>10:50AM</t>
-        </is>
-      </c>
-      <c r="D50" s="28" t="inlineStr">
-        <is>
-          <t>Under 11</t>
-        </is>
-      </c>
-      <c r="E50" s="28" t="n">
-        <v>8</v>
-      </c>
-      <c r="F50" s="28" t="inlineStr">
-        <is>
-          <t>U11-7</t>
-        </is>
-      </c>
-      <c r="G50" s="28" t="inlineStr">
+      <c r="H83" s="94" t="inlineStr">
+        <is>
+          <t>Pool 1st</t>
+        </is>
+      </c>
+      <c r="I83" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J83" s="94" t="inlineStr">
+        <is>
+          <t>Pool 2nd</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B84" s="95" t="inlineStr">
+        <is>
+          <t>6:30PM</t>
+        </is>
+      </c>
+      <c r="C84" s="95" t="inlineStr">
+        <is>
+          <t>6:50PM</t>
+        </is>
+      </c>
+      <c r="D84" s="95" t="inlineStr">
+        <is>
+          <t>21 to 40</t>
+        </is>
+      </c>
+      <c r="E84" s="95" t="n">
+        <v>42</v>
+      </c>
+      <c r="F84" s="95" t="inlineStr">
+        <is>
+          <t>2140-14</t>
+        </is>
+      </c>
+      <c r="G84" s="95" t="inlineStr">
+        <is>
+          <t>Board 2</t>
+        </is>
+      </c>
+      <c r="H84" s="95" t="inlineStr">
+        <is>
+          <t>Tej</t>
+        </is>
+      </c>
+      <c r="I84" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J84" s="95" t="inlineStr">
+        <is>
+          <t>Nikunj Jhala</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B85" s="94" t="inlineStr">
+        <is>
+          <t>6:40PM</t>
+        </is>
+      </c>
+      <c r="C85" s="94" t="inlineStr">
+        <is>
+          <t>7:00PM</t>
+        </is>
+      </c>
+      <c r="D85" s="94" t="inlineStr">
+        <is>
+          <t>41 and above</t>
+        </is>
+      </c>
+      <c r="E85" s="94" t="n">
+        <v>43</v>
+      </c>
+      <c r="F85" s="94" t="inlineStr">
+        <is>
+          <t>41P-7</t>
+        </is>
+      </c>
+      <c r="G85" s="94" t="inlineStr">
         <is>
           <t>Board 1</t>
         </is>
       </c>
-      <c r="H50" s="28" t="inlineStr">
-        <is>
-          <t>Rushabh</t>
-        </is>
-      </c>
-      <c r="I50" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J50" s="28" t="inlineStr">
-        <is>
-          <t>Jimit Relan</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="27" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B51" s="27" t="inlineStr">
-        <is>
-          <t>10:30AM</t>
-        </is>
-      </c>
-      <c r="C51" s="27" t="inlineStr">
-        <is>
-          <t>10:50AM</t>
-        </is>
-      </c>
-      <c r="D51" s="27" t="inlineStr">
-        <is>
-          <t>Under 11</t>
-        </is>
-      </c>
-      <c r="E51" s="27" t="n">
-        <v>9</v>
-      </c>
-      <c r="F51" s="27" t="inlineStr">
-        <is>
-          <t>U11-8</t>
-        </is>
-      </c>
-      <c r="G51" s="27" t="inlineStr">
+      <c r="H85" s="94" t="inlineStr">
+        <is>
+          <t>Piyush Makharia</t>
+        </is>
+      </c>
+      <c r="I85" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J85" s="94" t="inlineStr">
+        <is>
+          <t>Sachin Malgadnkar</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B86" s="95" t="inlineStr">
+        <is>
+          <t>6:50PM</t>
+        </is>
+      </c>
+      <c r="C86" s="95" t="inlineStr">
+        <is>
+          <t>7:10PM</t>
+        </is>
+      </c>
+      <c r="D86" s="95" t="inlineStr">
+        <is>
+          <t>41 and above</t>
+        </is>
+      </c>
+      <c r="E86" s="95" t="n">
+        <v>44</v>
+      </c>
+      <c r="F86" s="95" t="inlineStr">
+        <is>
+          <t>41P-20</t>
+        </is>
+      </c>
+      <c r="G86" s="95" t="inlineStr">
         <is>
           <t>Board 2</t>
         </is>
       </c>
-      <c r="H51" s="27" t="inlineStr">
-        <is>
-          <t>Neev Chauhan</t>
-        </is>
-      </c>
-      <c r="I51" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J51" s="27" t="inlineStr">
-        <is>
-          <t>Kartik Relan</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="28" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B52" s="28" t="inlineStr">
-        <is>
-          <t>10:50AM</t>
-        </is>
-      </c>
-      <c r="C52" s="28" t="inlineStr">
-        <is>
-          <t>11:10AM</t>
-        </is>
-      </c>
-      <c r="D52" s="28" t="inlineStr">
-        <is>
-          <t>12 to 20</t>
-        </is>
-      </c>
-      <c r="E52" s="28" t="n">
-        <v>10</v>
-      </c>
-      <c r="F52" s="28" t="inlineStr">
-        <is>
-          <t>1220-2</t>
-        </is>
-      </c>
-      <c r="G52" s="28" t="inlineStr">
+      <c r="H86" s="95" t="inlineStr">
+        <is>
+          <t>Ajit nair</t>
+        </is>
+      </c>
+      <c r="I86" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J86" s="95" t="inlineStr">
+        <is>
+          <t>Harkishin malkan</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B87" s="94" t="inlineStr">
+        <is>
+          <t>7:00PM</t>
+        </is>
+      </c>
+      <c r="C87" s="94" t="inlineStr">
+        <is>
+          <t>7:20PM</t>
+        </is>
+      </c>
+      <c r="D87" s="94" t="inlineStr">
+        <is>
+          <t>21 to 40</t>
+        </is>
+      </c>
+      <c r="E87" s="94" t="n">
+        <v>45</v>
+      </c>
+      <c r="F87" s="94" t="inlineStr">
+        <is>
+          <t>2140-8</t>
+        </is>
+      </c>
+      <c r="G87" s="94" t="inlineStr">
         <is>
           <t>Board 1</t>
         </is>
       </c>
-      <c r="H52" s="28" t="inlineStr">
-        <is>
-          <t>Aaditya Kumar</t>
-        </is>
-      </c>
-      <c r="I52" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J52" s="28" t="inlineStr">
-        <is>
-          <t>Hryday Goyal</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="27" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B53" s="27" t="inlineStr">
-        <is>
-          <t>11:00AM</t>
-        </is>
-      </c>
-      <c r="C53" s="27" t="inlineStr">
-        <is>
-          <t>11:20AM</t>
-        </is>
-      </c>
-      <c r="D53" s="27" t="inlineStr">
-        <is>
-          <t>Under 11</t>
-        </is>
-      </c>
-      <c r="E53" s="27" t="n">
-        <v>11</v>
-      </c>
-      <c r="F53" s="27" t="inlineStr">
-        <is>
-          <t>U11-9</t>
-        </is>
-      </c>
-      <c r="G53" s="27" t="inlineStr">
+      <c r="H87" s="94" t="inlineStr">
+        <is>
+          <t>Tejas doshi</t>
+        </is>
+      </c>
+      <c r="I87" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J87" s="94" t="inlineStr">
+        <is>
+          <t>Nikunj Jhala</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B88" s="95" t="inlineStr">
+        <is>
+          <t>7:10PM</t>
+        </is>
+      </c>
+      <c r="C88" s="95" t="inlineStr">
+        <is>
+          <t>7:30PM</t>
+        </is>
+      </c>
+      <c r="D88" s="95" t="inlineStr">
+        <is>
+          <t>41 and above</t>
+        </is>
+      </c>
+      <c r="E88" s="95" t="n">
+        <v>46</v>
+      </c>
+      <c r="F88" s="95" t="inlineStr">
+        <is>
+          <t>41P-10</t>
+        </is>
+      </c>
+      <c r="G88" s="95" t="inlineStr">
         <is>
           <t>Board 2</t>
         </is>
       </c>
-      <c r="H53" s="27" t="inlineStr">
-        <is>
-          <t>Neev Chauhan</t>
-        </is>
-      </c>
-      <c r="I53" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J53" s="27" t="inlineStr">
-        <is>
-          <t>Parth yadav</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="28" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B54" s="28" t="inlineStr">
-        <is>
-          <t>11:20AM</t>
-        </is>
-      </c>
-      <c r="C54" s="28" t="inlineStr">
-        <is>
-          <t>11:40AM</t>
-        </is>
-      </c>
-      <c r="D54" s="28" t="inlineStr">
-        <is>
-          <t>12 to 20</t>
-        </is>
-      </c>
-      <c r="E54" s="28" t="n">
-        <v>12</v>
-      </c>
-      <c r="F54" s="28" t="inlineStr">
-        <is>
-          <t>1220-3</t>
-        </is>
-      </c>
-      <c r="G54" s="28" t="inlineStr">
+      <c r="H88" s="95" t="inlineStr">
+        <is>
+          <t>Adil Khan</t>
+        </is>
+      </c>
+      <c r="I88" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J88" s="95" t="inlineStr">
+        <is>
+          <t>Prasad Akshintala</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B89" s="94" t="inlineStr">
+        <is>
+          <t>7:20PM</t>
+        </is>
+      </c>
+      <c r="C89" s="94" t="inlineStr">
+        <is>
+          <t>7:40PM</t>
+        </is>
+      </c>
+      <c r="D89" s="94" t="inlineStr">
+        <is>
+          <t>41 and above</t>
+        </is>
+      </c>
+      <c r="E89" s="94" t="n">
+        <v>47</v>
+      </c>
+      <c r="F89" s="94" t="inlineStr">
+        <is>
+          <t>41P-14</t>
+        </is>
+      </c>
+      <c r="G89" s="94" t="inlineStr">
         <is>
           <t>Board 1</t>
         </is>
       </c>
-      <c r="H54" s="28" t="inlineStr">
-        <is>
-          <t>Aadit Joshi</t>
-        </is>
-      </c>
-      <c r="I54" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J54" s="28" t="inlineStr">
-        <is>
-          <t>Aaditya Kumar</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="27" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B55" s="27" t="inlineStr">
-        <is>
-          <t>11:30AM</t>
-        </is>
-      </c>
-      <c r="C55" s="27" t="inlineStr">
-        <is>
-          <t>11:50AM</t>
-        </is>
-      </c>
-      <c r="D55" s="27" t="inlineStr">
-        <is>
-          <t>Under 11</t>
-        </is>
-      </c>
-      <c r="E55" s="27" t="n">
-        <v>13</v>
-      </c>
-      <c r="F55" s="27" t="inlineStr">
-        <is>
-          <t>U11-10</t>
-        </is>
-      </c>
-      <c r="G55" s="27" t="inlineStr">
+      <c r="H89" s="94" t="inlineStr">
+        <is>
+          <t>Sanjay Kumar</t>
+        </is>
+      </c>
+      <c r="I89" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J89" s="94" t="inlineStr">
+        <is>
+          <t>Harkishin malkan</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B90" s="95" t="inlineStr">
+        <is>
+          <t>7:30PM</t>
+        </is>
+      </c>
+      <c r="C90" s="95" t="inlineStr">
+        <is>
+          <t>7:50PM</t>
+        </is>
+      </c>
+      <c r="D90" s="95" t="inlineStr">
+        <is>
+          <t>21 to 40</t>
+        </is>
+      </c>
+      <c r="E90" s="95" t="n">
+        <v>48</v>
+      </c>
+      <c r="F90" s="95" t="inlineStr">
+        <is>
+          <t>2140-FINAL</t>
+        </is>
+      </c>
+      <c r="G90" s="95" t="inlineStr">
         <is>
           <t>Board 2</t>
         </is>
       </c>
-      <c r="H55" s="27" t="inlineStr">
-        <is>
-          <t>Parth yadav</t>
-        </is>
-      </c>
-      <c r="I55" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J55" s="27" t="inlineStr">
-        <is>
-          <t>Jimit Relan</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="28" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B56" s="28" t="inlineStr">
-        <is>
-          <t>11:50AM</t>
-        </is>
-      </c>
-      <c r="C56" s="28" t="inlineStr">
-        <is>
-          <t>12:10PM</t>
-        </is>
-      </c>
-      <c r="D56" s="28" t="inlineStr">
-        <is>
-          <t>12 to 20</t>
-        </is>
-      </c>
-      <c r="E56" s="28" t="n">
-        <v>14</v>
-      </c>
-      <c r="F56" s="28" t="inlineStr">
-        <is>
-          <t>1220-4</t>
-        </is>
-      </c>
-      <c r="G56" s="28" t="inlineStr">
+      <c r="H90" s="95" t="inlineStr">
+        <is>
+          <t>Pool 1st</t>
+        </is>
+      </c>
+      <c r="I90" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J90" s="95" t="inlineStr">
+        <is>
+          <t>Pool 2nd</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B91" s="94" t="inlineStr">
+        <is>
+          <t>7:40PM</t>
+        </is>
+      </c>
+      <c r="C91" s="94" t="inlineStr">
+        <is>
+          <t>8:00PM</t>
+        </is>
+      </c>
+      <c r="D91" s="94" t="inlineStr">
+        <is>
+          <t>41 and above</t>
+        </is>
+      </c>
+      <c r="E91" s="94" t="n">
+        <v>49</v>
+      </c>
+      <c r="F91" s="94" t="inlineStr">
+        <is>
+          <t>41P-5</t>
+        </is>
+      </c>
+      <c r="G91" s="94" t="inlineStr">
+        <is>
+          <t>Board 1</t>
+        </is>
+      </c>
+      <c r="H91" s="94" t="inlineStr">
+        <is>
+          <t>Prasad Akshintala</t>
+        </is>
+      </c>
+      <c r="I91" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J91" s="94" t="inlineStr">
+        <is>
+          <t>Ajit nair</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B92" s="95" t="inlineStr">
+        <is>
+          <t>7:50PM</t>
+        </is>
+      </c>
+      <c r="C92" s="95" t="inlineStr">
+        <is>
+          <t>8:10PM</t>
+        </is>
+      </c>
+      <c r="D92" s="95" t="inlineStr">
+        <is>
+          <t>41 and above</t>
+        </is>
+      </c>
+      <c r="E92" s="95" t="n">
+        <v>50</v>
+      </c>
+      <c r="F92" s="95" t="inlineStr">
+        <is>
+          <t>41P-21</t>
+        </is>
+      </c>
+      <c r="G92" s="95" t="inlineStr">
         <is>
           <t>Board 2</t>
         </is>
       </c>
-      <c r="H56" s="28" t="inlineStr">
-        <is>
-          <t>Maitreya Manvik</t>
-        </is>
-      </c>
-      <c r="I56" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J56" s="28" t="inlineStr">
-        <is>
-          <t>Hryday Goyal</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="27" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B57" s="27" t="inlineStr">
-        <is>
-          <t>3:00PM</t>
-        </is>
-      </c>
-      <c r="C57" s="27" t="inlineStr">
-        <is>
-          <t>3:20PM</t>
-        </is>
-      </c>
-      <c r="D57" s="27" t="inlineStr">
-        <is>
-          <t>12 to 20</t>
-        </is>
-      </c>
-      <c r="E57" s="27" t="n">
-        <v>15</v>
-      </c>
-      <c r="F57" s="27" t="inlineStr">
-        <is>
-          <t>1220-5</t>
-        </is>
-      </c>
-      <c r="G57" s="27" t="inlineStr">
+      <c r="H92" s="95" t="inlineStr">
+        <is>
+          <t>Sachin Malgadnkar</t>
+        </is>
+      </c>
+      <c r="I92" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J92" s="95" t="inlineStr">
+        <is>
+          <t>Harkishin malkan</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B93" s="94" t="inlineStr">
+        <is>
+          <t>8:10PM</t>
+        </is>
+      </c>
+      <c r="C93" s="94" t="inlineStr">
+        <is>
+          <t>8:30PM</t>
+        </is>
+      </c>
+      <c r="D93" s="94" t="inlineStr">
+        <is>
+          <t>41 and above</t>
+        </is>
+      </c>
+      <c r="E93" s="94" t="n">
+        <v>51</v>
+      </c>
+      <c r="F93" s="94" t="inlineStr">
+        <is>
+          <t>41P-4</t>
+        </is>
+      </c>
+      <c r="G93" s="94" t="inlineStr">
         <is>
           <t>Board 1</t>
         </is>
       </c>
-      <c r="H57" s="27" t="inlineStr">
-        <is>
-          <t>Aadit Joshi</t>
-        </is>
-      </c>
-      <c r="I57" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J57" s="27" t="inlineStr">
-        <is>
-          <t>Hryday Goyal</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="28" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B58" s="28" t="inlineStr">
-        <is>
-          <t>3:00PM</t>
-        </is>
-      </c>
-      <c r="C58" s="28" t="inlineStr">
-        <is>
-          <t>3:20PM</t>
-        </is>
-      </c>
-      <c r="D58" s="28" t="inlineStr">
-        <is>
-          <t>12 to 20</t>
-        </is>
-      </c>
-      <c r="E58" s="28" t="n">
-        <v>16</v>
-      </c>
-      <c r="F58" s="28" t="inlineStr">
-        <is>
-          <t>1220-6</t>
-        </is>
-      </c>
-      <c r="G58" s="28" t="inlineStr">
+      <c r="H93" s="94" t="inlineStr">
+        <is>
+          <t>Piyush Makharia</t>
+        </is>
+      </c>
+      <c r="I93" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J93" s="94" t="inlineStr">
+        <is>
+          <t>Sanjay Kumar</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B94" s="95" t="inlineStr">
+        <is>
+          <t>8:20PM</t>
+        </is>
+      </c>
+      <c r="C94" s="95" t="inlineStr">
+        <is>
+          <t>8:40PM</t>
+        </is>
+      </c>
+      <c r="D94" s="95" t="inlineStr">
+        <is>
+          <t>41 and above</t>
+        </is>
+      </c>
+      <c r="E94" s="95" t="n">
+        <v>52</v>
+      </c>
+      <c r="F94" s="95" t="inlineStr">
+        <is>
+          <t>41P-13</t>
+        </is>
+      </c>
+      <c r="G94" s="95" t="inlineStr">
         <is>
           <t>Board 2</t>
         </is>
       </c>
-      <c r="H58" s="28" t="inlineStr">
-        <is>
-          <t>Maitreya Manvik</t>
-        </is>
-      </c>
-      <c r="I58" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J58" s="28" t="inlineStr">
-        <is>
-          <t>Aaditya Kumar</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="27" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B59" s="27" t="inlineStr">
-        <is>
-          <t>3:20PM</t>
-        </is>
-      </c>
-      <c r="C59" s="27" t="inlineStr">
-        <is>
-          <t>3:40PM</t>
-        </is>
-      </c>
-      <c r="D59" s="27" t="inlineStr">
-        <is>
-          <t>21 to 40</t>
-        </is>
-      </c>
-      <c r="E59" s="27" t="n">
-        <v>17</v>
-      </c>
-      <c r="F59" s="27" t="inlineStr">
-        <is>
-          <t>2140-1</t>
-        </is>
-      </c>
-      <c r="G59" s="27" t="inlineStr">
+      <c r="H94" s="95" t="inlineStr">
+        <is>
+          <t>Sachin Malgadnkar</t>
+        </is>
+      </c>
+      <c r="I94" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J94" s="95" t="inlineStr">
+        <is>
+          <t>Prasad Akshintala</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B95" s="94" t="inlineStr">
+        <is>
+          <t>8:55PM</t>
+        </is>
+      </c>
+      <c r="C95" s="94" t="inlineStr">
+        <is>
+          <t>9:15PM</t>
+        </is>
+      </c>
+      <c r="D95" s="94" t="inlineStr">
+        <is>
+          <t>41 and above</t>
+        </is>
+      </c>
+      <c r="E95" s="94" t="n">
+        <v>53</v>
+      </c>
+      <c r="F95" s="94" t="inlineStr">
+        <is>
+          <t>41P-15</t>
+        </is>
+      </c>
+      <c r="G95" s="94" t="inlineStr">
         <is>
           <t>Board 1</t>
         </is>
       </c>
-      <c r="H59" s="27" t="inlineStr">
-        <is>
-          <t>Tej</t>
-        </is>
-      </c>
-      <c r="I59" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J59" s="27" t="inlineStr">
-        <is>
-          <t>Tejas doshi</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="28" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B60" s="28" t="inlineStr">
-        <is>
-          <t>3:20PM</t>
-        </is>
-      </c>
-      <c r="C60" s="28" t="inlineStr">
-        <is>
-          <t>3:40PM</t>
-        </is>
-      </c>
-      <c r="D60" s="28" t="inlineStr">
-        <is>
-          <t>21 to 40</t>
-        </is>
-      </c>
-      <c r="E60" s="28" t="n">
-        <v>18</v>
-      </c>
-      <c r="F60" s="28" t="inlineStr">
-        <is>
-          <t>2140-2</t>
-        </is>
-      </c>
-      <c r="G60" s="28" t="inlineStr">
+      <c r="H95" s="94" t="inlineStr">
+        <is>
+          <t>Adil Khan</t>
+        </is>
+      </c>
+      <c r="I95" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J95" s="94" t="inlineStr">
+        <is>
+          <t>Sachin Malgadnkar</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B96" s="95" t="inlineStr">
+        <is>
+          <t>9:35PM</t>
+        </is>
+      </c>
+      <c r="C96" s="95" t="inlineStr">
+        <is>
+          <t>9:55PM</t>
+        </is>
+      </c>
+      <c r="D96" s="95" t="inlineStr">
+        <is>
+          <t>41 and above</t>
+        </is>
+      </c>
+      <c r="E96" s="95" t="n">
+        <v>54</v>
+      </c>
+      <c r="F96" s="95" t="inlineStr">
+        <is>
+          <t>41P-19</t>
+        </is>
+      </c>
+      <c r="G96" s="95" t="inlineStr">
         <is>
           <t>Board 2</t>
         </is>
       </c>
-      <c r="H60" s="28" t="inlineStr">
-        <is>
-          <t>Swati Tripathi</t>
-        </is>
-      </c>
-      <c r="I60" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J60" s="28" t="inlineStr">
-        <is>
-          <t>Amit Nawandhar</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="27" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B61" s="27" t="inlineStr">
-        <is>
-          <t>3:50PM</t>
-        </is>
-      </c>
-      <c r="C61" s="27" t="inlineStr">
-        <is>
-          <t>4:10PM</t>
-        </is>
-      </c>
-      <c r="D61" s="27" t="inlineStr">
-        <is>
-          <t>21 to 40</t>
-        </is>
-      </c>
-      <c r="E61" s="27" t="n">
-        <v>19</v>
-      </c>
-      <c r="F61" s="27" t="inlineStr">
-        <is>
-          <t>2140-3</t>
-        </is>
-      </c>
-      <c r="G61" s="27" t="inlineStr">
+      <c r="H96" s="95" t="inlineStr">
+        <is>
+          <t>Prasad Akshintala</t>
+        </is>
+      </c>
+      <c r="I96" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J96" s="95" t="inlineStr">
+        <is>
+          <t>Harkishin malkan</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B97" s="94" t="inlineStr">
+        <is>
+          <t>9:35PM</t>
+        </is>
+      </c>
+      <c r="C97" s="94" t="inlineStr">
+        <is>
+          <t>9:55PM</t>
+        </is>
+      </c>
+      <c r="D97" s="94" t="inlineStr">
+        <is>
+          <t>41 and above</t>
+        </is>
+      </c>
+      <c r="E97" s="94" t="n">
+        <v>55</v>
+      </c>
+      <c r="F97" s="94" t="inlineStr">
+        <is>
+          <t>41P-9</t>
+        </is>
+      </c>
+      <c r="G97" s="94" t="inlineStr">
         <is>
           <t>Board 1</t>
         </is>
       </c>
-      <c r="H61" s="27" t="inlineStr">
-        <is>
-          <t>Rahul Garg</t>
-        </is>
-      </c>
-      <c r="I61" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J61" s="27" t="inlineStr">
-        <is>
-          <t>Amit Nawandhar</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="28" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B62" s="28" t="inlineStr">
-        <is>
-          <t>3:50PM</t>
-        </is>
-      </c>
-      <c r="C62" s="28" t="inlineStr">
-        <is>
-          <t>4:10PM</t>
-        </is>
-      </c>
-      <c r="D62" s="28" t="inlineStr">
-        <is>
-          <t>21 to 40</t>
-        </is>
-      </c>
-      <c r="E62" s="28" t="n">
-        <v>20</v>
-      </c>
-      <c r="F62" s="28" t="inlineStr">
-        <is>
-          <t>2140-4</t>
-        </is>
-      </c>
-      <c r="G62" s="28" t="inlineStr">
+      <c r="H97" s="94" t="inlineStr">
+        <is>
+          <t>Adil Khan</t>
+        </is>
+      </c>
+      <c r="I97" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J97" s="94" t="inlineStr">
+        <is>
+          <t>Sanjay Kumar</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B98" s="95" t="inlineStr">
+        <is>
+          <t>9:55PM</t>
+        </is>
+      </c>
+      <c r="C98" s="95" t="inlineStr">
+        <is>
+          <t>10:15PM</t>
+        </is>
+      </c>
+      <c r="D98" s="95" t="inlineStr">
+        <is>
+          <t>41 and above</t>
+        </is>
+      </c>
+      <c r="E98" s="95" t="n">
+        <v>56</v>
+      </c>
+      <c r="F98" s="95" t="inlineStr">
+        <is>
+          <t>41P-SF1</t>
+        </is>
+      </c>
+      <c r="G98" s="95" t="inlineStr">
+        <is>
+          <t>Board 1</t>
+        </is>
+      </c>
+      <c r="H98" s="95" t="inlineStr">
+        <is>
+          <t>Round Robin 1st</t>
+        </is>
+      </c>
+      <c r="I98" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J98" s="95" t="inlineStr">
+        <is>
+          <t>Round Robin 4th</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B99" s="94" t="inlineStr">
+        <is>
+          <t>9:55PM</t>
+        </is>
+      </c>
+      <c r="C99" s="94" t="inlineStr">
+        <is>
+          <t>10:15PM</t>
+        </is>
+      </c>
+      <c r="D99" s="94" t="inlineStr">
+        <is>
+          <t>41 and above</t>
+        </is>
+      </c>
+      <c r="E99" s="94" t="n">
+        <v>57</v>
+      </c>
+      <c r="F99" s="94" t="inlineStr">
+        <is>
+          <t>41P-SF2</t>
+        </is>
+      </c>
+      <c r="G99" s="94" t="inlineStr">
         <is>
           <t>Board 2</t>
         </is>
       </c>
-      <c r="H62" s="28" t="inlineStr">
-        <is>
-          <t>Swati Tripathi</t>
-        </is>
-      </c>
-      <c r="I62" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J62" s="28" t="inlineStr">
-        <is>
-          <t>Tejas doshi</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="27" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B63" s="27" t="inlineStr">
-        <is>
-          <t>4:20PM</t>
-        </is>
-      </c>
-      <c r="C63" s="27" t="inlineStr">
-        <is>
-          <t>4:40PM</t>
-        </is>
-      </c>
-      <c r="D63" s="27" t="inlineStr">
-        <is>
-          <t>21 to 40</t>
-        </is>
-      </c>
-      <c r="E63" s="27" t="n">
-        <v>21</v>
-      </c>
-      <c r="F63" s="27" t="inlineStr">
-        <is>
-          <t>2140-5</t>
-        </is>
-      </c>
-      <c r="G63" s="27" t="inlineStr">
-        <is>
-          <t>Board 2</t>
-        </is>
-      </c>
-      <c r="H63" s="27" t="inlineStr">
-        <is>
-          <t>Amit Nawandhar</t>
-        </is>
-      </c>
-      <c r="I63" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J63" s="27" t="inlineStr">
-        <is>
-          <t>Tejas doshi</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="28" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B64" s="28" t="inlineStr">
-        <is>
-          <t>4:45PM</t>
-        </is>
-      </c>
-      <c r="C64" s="28" t="inlineStr">
-        <is>
-          <t>5:05PM</t>
-        </is>
-      </c>
-      <c r="D64" s="28" t="inlineStr">
-        <is>
-          <t>21 to 40</t>
-        </is>
-      </c>
-      <c r="E64" s="28" t="n">
-        <v>22</v>
-      </c>
-      <c r="F64" s="28" t="inlineStr">
-        <is>
-          <t>2140-6</t>
-        </is>
-      </c>
-      <c r="G64" s="28" t="inlineStr">
-        <is>
-          <t>Board 2</t>
-        </is>
-      </c>
-      <c r="H64" s="28" t="inlineStr">
-        <is>
-          <t>Tej</t>
-        </is>
-      </c>
-      <c r="I64" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J64" s="28" t="inlineStr">
-        <is>
-          <t>Swati Tripathi</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="27" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B65" s="27" t="inlineStr">
-        <is>
-          <t>5:10PM</t>
-        </is>
-      </c>
-      <c r="C65" s="27" t="inlineStr">
-        <is>
-          <t>5:30PM</t>
-        </is>
-      </c>
-      <c r="D65" s="27" t="inlineStr">
-        <is>
-          <t>21 to 40</t>
-        </is>
-      </c>
-      <c r="E65" s="27" t="n">
-        <v>23</v>
-      </c>
-      <c r="F65" s="27" t="inlineStr">
-        <is>
-          <t>2140-7</t>
-        </is>
-      </c>
-      <c r="G65" s="27" t="inlineStr">
+      <c r="H99" s="94" t="inlineStr">
+        <is>
+          <t>Round Robin 2nd</t>
+        </is>
+      </c>
+      <c r="I99" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J99" s="94" t="inlineStr">
+        <is>
+          <t>Round Robin 3rd</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="95" t="inlineStr">
+        <is>
+          <t>Aug 16</t>
+        </is>
+      </c>
+      <c r="B100" s="95" t="inlineStr">
+        <is>
+          <t>8:00AM</t>
+        </is>
+      </c>
+      <c r="C100" s="95" t="inlineStr">
+        <is>
+          <t>8:20AM</t>
+        </is>
+      </c>
+      <c r="D100" s="95" t="inlineStr">
+        <is>
+          <t>41 and above</t>
+        </is>
+      </c>
+      <c r="E100" s="95" t="n">
+        <v>58</v>
+      </c>
+      <c r="F100" s="95" t="inlineStr">
+        <is>
+          <t>41P-FINAL</t>
+        </is>
+      </c>
+      <c r="G100" s="95" t="inlineStr">
         <is>
           <t>Board 1</t>
         </is>
       </c>
-      <c r="H65" s="27" t="inlineStr">
-        <is>
-          <t>Rahul Garg</t>
-        </is>
-      </c>
-      <c r="I65" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J65" s="27" t="inlineStr">
-        <is>
-          <t>Nikunj Jhala</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="28" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B66" s="28" t="inlineStr">
-        <is>
-          <t>5:40PM</t>
-        </is>
-      </c>
-      <c r="C66" s="28" t="inlineStr">
-        <is>
-          <t>6:00PM</t>
-        </is>
-      </c>
-      <c r="D66" s="28" t="inlineStr">
-        <is>
-          <t>21 to 40</t>
-        </is>
-      </c>
-      <c r="E66" s="28" t="n">
-        <v>24</v>
-      </c>
-      <c r="F66" s="28" t="inlineStr">
-        <is>
-          <t>2140-8</t>
-        </is>
-      </c>
-      <c r="G66" s="28" t="inlineStr">
-        <is>
-          <t>Board 1</t>
-        </is>
-      </c>
-      <c r="H66" s="28" t="inlineStr">
-        <is>
-          <t>Tejas doshi</t>
-        </is>
-      </c>
-      <c r="I66" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J66" s="28" t="inlineStr">
-        <is>
-          <t>Nikunj Jhala</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="27" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B67" s="27" t="inlineStr">
-        <is>
-          <t>5:40PM</t>
-        </is>
-      </c>
-      <c r="C67" s="27" t="inlineStr">
-        <is>
-          <t>6:00PM</t>
-        </is>
-      </c>
-      <c r="D67" s="27" t="inlineStr">
-        <is>
-          <t>21 to 40</t>
-        </is>
-      </c>
-      <c r="E67" s="27" t="n">
-        <v>25</v>
-      </c>
-      <c r="F67" s="27" t="inlineStr">
-        <is>
-          <t>2140-9</t>
-        </is>
-      </c>
-      <c r="G67" s="27" t="inlineStr">
-        <is>
-          <t>Board 2</t>
-        </is>
-      </c>
-      <c r="H67" s="27" t="inlineStr">
-        <is>
-          <t>Rahul Garg</t>
-        </is>
-      </c>
-      <c r="I67" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J67" s="27" t="inlineStr">
-        <is>
-          <t>Tej</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="28" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B68" s="28" t="inlineStr">
-        <is>
-          <t>6:00PM</t>
-        </is>
-      </c>
-      <c r="C68" s="28" t="inlineStr">
-        <is>
-          <t>6:20PM</t>
-        </is>
-      </c>
-      <c r="D68" s="28" t="inlineStr">
-        <is>
-          <t>41 and above</t>
-        </is>
-      </c>
-      <c r="E68" s="28" t="n">
-        <v>26</v>
-      </c>
-      <c r="F68" s="28" t="inlineStr">
-        <is>
-          <t>41P-1</t>
-        </is>
-      </c>
-      <c r="G68" s="28" t="inlineStr">
-        <is>
-          <t>Board 2</t>
-        </is>
-      </c>
-      <c r="H68" s="28" t="inlineStr">
-        <is>
-          <t>Piyush Makharia</t>
-        </is>
-      </c>
-      <c r="I68" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J68" s="28" t="inlineStr">
-        <is>
-          <t>Ajit nair</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="27" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B69" s="27" t="inlineStr">
-        <is>
-          <t>6:10PM</t>
-        </is>
-      </c>
-      <c r="C69" s="27" t="inlineStr">
-        <is>
-          <t>6:30PM</t>
-        </is>
-      </c>
-      <c r="D69" s="27" t="inlineStr">
-        <is>
-          <t>21 to 40</t>
-        </is>
-      </c>
-      <c r="E69" s="27" t="n">
-        <v>27</v>
-      </c>
-      <c r="F69" s="27" t="inlineStr">
-        <is>
-          <t>2140-10</t>
-        </is>
-      </c>
-      <c r="G69" s="27" t="inlineStr">
-        <is>
-          <t>Board 1</t>
-        </is>
-      </c>
-      <c r="H69" s="27" t="inlineStr">
-        <is>
-          <t>Amit Nawandhar</t>
-        </is>
-      </c>
-      <c r="I69" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J69" s="27" t="inlineStr">
-        <is>
-          <t>Nikunj Jhala</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="28" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B70" s="28" t="inlineStr">
-        <is>
-          <t>6:40PM</t>
-        </is>
-      </c>
-      <c r="C70" s="28" t="inlineStr">
-        <is>
-          <t>7:00PM</t>
-        </is>
-      </c>
-      <c r="D70" s="28" t="inlineStr">
-        <is>
-          <t>21 to 40</t>
-        </is>
-      </c>
-      <c r="E70" s="28" t="n">
-        <v>28</v>
-      </c>
-      <c r="F70" s="28" t="inlineStr">
-        <is>
-          <t>2140-11</t>
-        </is>
-      </c>
-      <c r="G70" s="28" t="inlineStr">
-        <is>
-          <t>Board 1</t>
-        </is>
-      </c>
-      <c r="H70" s="28" t="inlineStr">
-        <is>
-          <t>Swati Tripathi</t>
-        </is>
-      </c>
-      <c r="I70" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J70" s="28" t="inlineStr">
-        <is>
-          <t>Nikunj Jhala</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="27" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B71" s="27" t="inlineStr">
-        <is>
-          <t>7:00PM</t>
-        </is>
-      </c>
-      <c r="C71" s="27" t="inlineStr">
-        <is>
-          <t>7:20PM</t>
-        </is>
-      </c>
-      <c r="D71" s="27" t="inlineStr">
-        <is>
-          <t>21 to 40</t>
-        </is>
-      </c>
-      <c r="E71" s="27" t="n">
-        <v>29</v>
-      </c>
-      <c r="F71" s="27" t="inlineStr">
-        <is>
-          <t>2140-12</t>
-        </is>
-      </c>
-      <c r="G71" s="27" t="inlineStr">
-        <is>
-          <t>Board 1</t>
-        </is>
-      </c>
-      <c r="H71" s="27" t="inlineStr">
-        <is>
-          <t>Tej</t>
-        </is>
-      </c>
-      <c r="I71" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J71" s="27" t="inlineStr">
-        <is>
-          <t>Amit Nawandhar</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="28" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B72" s="28" t="inlineStr">
-        <is>
-          <t>7:10PM</t>
-        </is>
-      </c>
-      <c r="C72" s="28" t="inlineStr">
-        <is>
-          <t>7:30PM</t>
-        </is>
-      </c>
-      <c r="D72" s="28" t="inlineStr">
-        <is>
-          <t>21 to 40</t>
-        </is>
-      </c>
-      <c r="E72" s="28" t="n">
-        <v>30</v>
-      </c>
-      <c r="F72" s="28" t="inlineStr">
-        <is>
-          <t>2140-13</t>
-        </is>
-      </c>
-      <c r="G72" s="28" t="inlineStr">
-        <is>
-          <t>Board 2</t>
-        </is>
-      </c>
-      <c r="H72" s="28" t="inlineStr">
-        <is>
-          <t>Rahul Garg</t>
-        </is>
-      </c>
-      <c r="I72" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J72" s="28" t="inlineStr">
-        <is>
-          <t>Swati Tripathi</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="27" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B73" s="27" t="inlineStr">
-        <is>
-          <t>7:30PM</t>
-        </is>
-      </c>
-      <c r="C73" s="27" t="inlineStr">
-        <is>
-          <t>7:50PM</t>
-        </is>
-      </c>
-      <c r="D73" s="27" t="inlineStr">
-        <is>
-          <t>21 to 40</t>
-        </is>
-      </c>
-      <c r="E73" s="27" t="n">
-        <v>31</v>
-      </c>
-      <c r="F73" s="27" t="inlineStr">
-        <is>
-          <t>2140-14</t>
-        </is>
-      </c>
-      <c r="G73" s="27" t="inlineStr">
-        <is>
-          <t>Board 1</t>
-        </is>
-      </c>
-      <c r="H73" s="27" t="inlineStr">
-        <is>
-          <t>Tej</t>
-        </is>
-      </c>
-      <c r="I73" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J73" s="27" t="inlineStr">
-        <is>
-          <t>Nikunj Jhala</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="28" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B74" s="28" t="inlineStr">
-        <is>
-          <t>7:30PM</t>
-        </is>
-      </c>
-      <c r="C74" s="28" t="inlineStr">
-        <is>
-          <t>7:50PM</t>
-        </is>
-      </c>
-      <c r="D74" s="28" t="inlineStr">
-        <is>
-          <t>41 and above</t>
-        </is>
-      </c>
-      <c r="E74" s="28" t="n">
-        <v>32</v>
-      </c>
-      <c r="F74" s="28" t="inlineStr">
-        <is>
-          <t>41P-2</t>
-        </is>
-      </c>
-      <c r="G74" s="28" t="inlineStr">
-        <is>
-          <t>Board 2</t>
-        </is>
-      </c>
-      <c r="H74" s="28" t="inlineStr">
-        <is>
-          <t>Ajit nair</t>
-        </is>
-      </c>
-      <c r="I74" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J74" s="28" t="inlineStr">
-        <is>
-          <t>Sanjay Kumar</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="27" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B75" s="27" t="inlineStr">
-        <is>
-          <t>7:50PM</t>
-        </is>
-      </c>
-      <c r="C75" s="27" t="inlineStr">
-        <is>
-          <t>8:10PM</t>
-        </is>
-      </c>
-      <c r="D75" s="27" t="inlineStr">
-        <is>
-          <t>41 and above</t>
-        </is>
-      </c>
-      <c r="E75" s="27" t="n">
-        <v>33</v>
-      </c>
-      <c r="F75" s="27" t="inlineStr">
-        <is>
-          <t>41P-3</t>
-        </is>
-      </c>
-      <c r="G75" s="27" t="inlineStr">
-        <is>
-          <t>Board 1</t>
-        </is>
-      </c>
-      <c r="H75" s="27" t="inlineStr">
-        <is>
-          <t>Piyush Makharia</t>
-        </is>
-      </c>
-      <c r="I75" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J75" s="27" t="inlineStr">
-        <is>
-          <t>Prasad Akshintala</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="28" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B76" s="28" t="inlineStr">
-        <is>
-          <t>8:20PM</t>
-        </is>
-      </c>
-      <c r="C76" s="28" t="inlineStr">
-        <is>
-          <t>8:40PM</t>
-        </is>
-      </c>
-      <c r="D76" s="28" t="inlineStr">
-        <is>
-          <t>41 and above</t>
-        </is>
-      </c>
-      <c r="E76" s="28" t="n">
-        <v>34</v>
-      </c>
-      <c r="F76" s="28" t="inlineStr">
-        <is>
-          <t>41P-4</t>
-        </is>
-      </c>
-      <c r="G76" s="28" t="inlineStr">
-        <is>
-          <t>Board 1</t>
-        </is>
-      </c>
-      <c r="H76" s="28" t="inlineStr">
-        <is>
-          <t>Piyush Makharia</t>
-        </is>
-      </c>
-      <c r="I76" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J76" s="28" t="inlineStr">
-        <is>
-          <t>Sanjay Kumar</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="27" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B77" s="27" t="inlineStr">
-        <is>
-          <t>8:20PM</t>
-        </is>
-      </c>
-      <c r="C77" s="27" t="inlineStr">
-        <is>
-          <t>8:40PM</t>
-        </is>
-      </c>
-      <c r="D77" s="27" t="inlineStr">
-        <is>
-          <t>41 and above</t>
-        </is>
-      </c>
-      <c r="E77" s="27" t="n">
-        <v>35</v>
-      </c>
-      <c r="F77" s="27" t="inlineStr">
-        <is>
-          <t>41P-5</t>
-        </is>
-      </c>
-      <c r="G77" s="27" t="inlineStr">
-        <is>
-          <t>Board 2</t>
-        </is>
-      </c>
-      <c r="H77" s="27" t="inlineStr">
-        <is>
-          <t>Prasad Akshintala</t>
-        </is>
-      </c>
-      <c r="I77" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J77" s="27" t="inlineStr">
-        <is>
-          <t>Ajit nair</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="28" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B78" s="28" t="inlineStr">
-        <is>
-          <t>8:40PM</t>
-        </is>
-      </c>
-      <c r="C78" s="28" t="inlineStr">
-        <is>
-          <t>9:00PM</t>
-        </is>
-      </c>
-      <c r="D78" s="28" t="inlineStr">
-        <is>
-          <t>21 to 40</t>
-        </is>
-      </c>
-      <c r="E78" s="28" t="n">
-        <v>36</v>
-      </c>
-      <c r="F78" s="28" t="inlineStr">
-        <is>
-          <t>2140-15</t>
-        </is>
-      </c>
-      <c r="G78" s="28" t="inlineStr">
-        <is>
-          <t>Board 1</t>
-        </is>
-      </c>
-      <c r="H78" s="28" t="inlineStr">
-        <is>
-          <t>Rahul Garg</t>
-        </is>
-      </c>
-      <c r="I78" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J78" s="28" t="inlineStr">
-        <is>
-          <t>Tejas doshi</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="27" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B79" s="27" t="inlineStr">
-        <is>
-          <t>8:55PM</t>
-        </is>
-      </c>
-      <c r="C79" s="27" t="inlineStr">
-        <is>
-          <t>9:15PM</t>
-        </is>
-      </c>
-      <c r="D79" s="27" t="inlineStr">
-        <is>
-          <t>41 and above</t>
-        </is>
-      </c>
-      <c r="E79" s="27" t="n">
-        <v>37</v>
-      </c>
-      <c r="F79" s="27" t="inlineStr">
-        <is>
-          <t>41P-6</t>
-        </is>
-      </c>
-      <c r="G79" s="27" t="inlineStr">
-        <is>
-          <t>Board 2</t>
-        </is>
-      </c>
-      <c r="H79" s="27" t="inlineStr">
-        <is>
-          <t>Piyush Makharia</t>
-        </is>
-      </c>
-      <c r="I79" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J79" s="27" t="inlineStr">
-        <is>
-          <t>Adil Khan</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="28" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B80" s="28" t="inlineStr">
-        <is>
-          <t>9:25PM</t>
-        </is>
-      </c>
-      <c r="C80" s="28" t="inlineStr">
-        <is>
-          <t>9:45PM</t>
-        </is>
-      </c>
-      <c r="D80" s="28" t="inlineStr">
-        <is>
-          <t>41 and above</t>
-        </is>
-      </c>
-      <c r="E80" s="28" t="n">
-        <v>38</v>
-      </c>
-      <c r="F80" s="28" t="inlineStr">
-        <is>
-          <t>41P-7</t>
-        </is>
-      </c>
-      <c r="G80" s="28" t="inlineStr">
-        <is>
-          <t>Board 2</t>
-        </is>
-      </c>
-      <c r="H80" s="28" t="inlineStr">
-        <is>
-          <t>Piyush Makharia</t>
-        </is>
-      </c>
-      <c r="I80" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J80" s="28" t="inlineStr">
-        <is>
-          <t>Sachin Malgadnkar</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="27" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B81" s="27" t="inlineStr">
-        <is>
-          <t>9:45PM</t>
-        </is>
-      </c>
-      <c r="C81" s="27" t="inlineStr">
-        <is>
-          <t>10:05PM</t>
-        </is>
-      </c>
-      <c r="D81" s="27" t="inlineStr">
-        <is>
-          <t>41 and above</t>
-        </is>
-      </c>
-      <c r="E81" s="27" t="n">
-        <v>39</v>
-      </c>
-      <c r="F81" s="27" t="inlineStr">
-        <is>
-          <t>41P-8</t>
-        </is>
-      </c>
-      <c r="G81" s="27" t="inlineStr">
-        <is>
-          <t>Board 2</t>
-        </is>
-      </c>
-      <c r="H81" s="27" t="inlineStr">
-        <is>
-          <t>Prasad Akshintala</t>
-        </is>
-      </c>
-      <c r="I81" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J81" s="27" t="inlineStr">
-        <is>
-          <t>Sanjay Kumar</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="28" t="inlineStr">
-        <is>
-          <t>Aug 16</t>
-        </is>
-      </c>
-      <c r="B82" s="28" t="inlineStr">
-        <is>
-          <t>8:15AM</t>
-        </is>
-      </c>
-      <c r="C82" s="28" t="inlineStr">
-        <is>
-          <t>8:35AM</t>
-        </is>
-      </c>
-      <c r="D82" s="28" t="inlineStr">
-        <is>
-          <t>41 and above</t>
-        </is>
-      </c>
-      <c r="E82" s="28" t="n">
-        <v>40</v>
-      </c>
-      <c r="F82" s="28" t="inlineStr">
-        <is>
-          <t>41P-9</t>
-        </is>
-      </c>
-      <c r="G82" s="28" t="inlineStr">
-        <is>
-          <t>Board 2</t>
-        </is>
-      </c>
-      <c r="H82" s="28" t="inlineStr">
-        <is>
-          <t>Adil Khan</t>
-        </is>
-      </c>
-      <c r="I82" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J82" s="28" t="inlineStr">
-        <is>
-          <t>Sanjay Kumar</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="27" t="inlineStr">
-        <is>
-          <t>Aug 16</t>
-        </is>
-      </c>
-      <c r="B83" s="27" t="inlineStr">
-        <is>
-          <t>8:45AM</t>
-        </is>
-      </c>
-      <c r="C83" s="27" t="inlineStr">
-        <is>
-          <t>9:05AM</t>
-        </is>
-      </c>
-      <c r="D83" s="27" t="inlineStr">
-        <is>
-          <t>41 and above</t>
-        </is>
-      </c>
-      <c r="E83" s="27" t="n">
-        <v>41</v>
-      </c>
-      <c r="F83" s="27" t="inlineStr">
-        <is>
-          <t>41P-10</t>
-        </is>
-      </c>
-      <c r="G83" s="27" t="inlineStr">
-        <is>
-          <t>Board 1</t>
-        </is>
-      </c>
-      <c r="H83" s="27" t="inlineStr">
-        <is>
-          <t>Adil Khan</t>
-        </is>
-      </c>
-      <c r="I83" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J83" s="27" t="inlineStr">
-        <is>
-          <t>Prasad Akshintala</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="28" t="inlineStr">
-        <is>
-          <t>Aug 16</t>
-        </is>
-      </c>
-      <c r="B84" s="28" t="inlineStr">
-        <is>
-          <t>8:45AM</t>
-        </is>
-      </c>
-      <c r="C84" s="28" t="inlineStr">
-        <is>
-          <t>9:05AM</t>
-        </is>
-      </c>
-      <c r="D84" s="28" t="inlineStr">
-        <is>
-          <t>41 and above</t>
-        </is>
-      </c>
-      <c r="E84" s="28" t="n">
-        <v>42</v>
-      </c>
-      <c r="F84" s="28" t="inlineStr">
-        <is>
-          <t>41P-11</t>
-        </is>
-      </c>
-      <c r="G84" s="28" t="inlineStr">
-        <is>
-          <t>Board 2</t>
-        </is>
-      </c>
-      <c r="H84" s="28" t="inlineStr">
-        <is>
-          <t>Sachin Malgadnkar</t>
-        </is>
-      </c>
-      <c r="I84" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J84" s="28" t="inlineStr">
-        <is>
-          <t>Sanjay Kumar</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="27" t="inlineStr">
-        <is>
-          <t>Aug 16</t>
-        </is>
-      </c>
-      <c r="B85" s="27" t="inlineStr">
-        <is>
-          <t>9:15AM</t>
-        </is>
-      </c>
-      <c r="C85" s="27" t="inlineStr">
-        <is>
-          <t>9:35AM</t>
-        </is>
-      </c>
-      <c r="D85" s="27" t="inlineStr">
-        <is>
-          <t>41 and above</t>
-        </is>
-      </c>
-      <c r="E85" s="27" t="n">
-        <v>43</v>
-      </c>
-      <c r="F85" s="27" t="inlineStr">
-        <is>
-          <t>41P-12</t>
-        </is>
-      </c>
-      <c r="G85" s="27" t="inlineStr">
-        <is>
-          <t>Board 1</t>
-        </is>
-      </c>
-      <c r="H85" s="27" t="inlineStr">
-        <is>
-          <t>Adil Khan</t>
-        </is>
-      </c>
-      <c r="I85" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J85" s="27" t="inlineStr">
-        <is>
-          <t>Ajit nair</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="28" t="inlineStr">
-        <is>
-          <t>Aug 16</t>
-        </is>
-      </c>
-      <c r="B86" s="28" t="inlineStr">
-        <is>
-          <t>9:15AM</t>
-        </is>
-      </c>
-      <c r="C86" s="28" t="inlineStr">
-        <is>
-          <t>9:35AM</t>
-        </is>
-      </c>
-      <c r="D86" s="28" t="inlineStr">
-        <is>
-          <t>41 and above</t>
-        </is>
-      </c>
-      <c r="E86" s="28" t="n">
-        <v>44</v>
-      </c>
-      <c r="F86" s="28" t="inlineStr">
-        <is>
-          <t>41P-13</t>
-        </is>
-      </c>
-      <c r="G86" s="28" t="inlineStr">
-        <is>
-          <t>Board 2</t>
-        </is>
-      </c>
-      <c r="H86" s="28" t="inlineStr">
-        <is>
-          <t>Sachin Malgadnkar</t>
-        </is>
-      </c>
-      <c r="I86" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J86" s="28" t="inlineStr">
-        <is>
-          <t>Prasad Akshintala</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="27" t="inlineStr">
-        <is>
-          <t>Aug 16</t>
-        </is>
-      </c>
-      <c r="B87" s="27" t="inlineStr">
-        <is>
-          <t>9:35AM</t>
-        </is>
-      </c>
-      <c r="C87" s="27" t="inlineStr">
-        <is>
-          <t>9:55AM</t>
-        </is>
-      </c>
-      <c r="D87" s="27" t="inlineStr">
-        <is>
-          <t>41 and above</t>
-        </is>
-      </c>
-      <c r="E87" s="27" t="n">
-        <v>45</v>
-      </c>
-      <c r="F87" s="27" t="inlineStr">
-        <is>
-          <t>41P-14</t>
-        </is>
-      </c>
-      <c r="G87" s="27" t="inlineStr">
-        <is>
-          <t>Board 2</t>
-        </is>
-      </c>
-      <c r="H87" s="27" t="inlineStr">
-        <is>
-          <t>Sanjay Kumar</t>
-        </is>
-      </c>
-      <c r="I87" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J87" s="27" t="inlineStr">
-        <is>
-          <t>Harkishin malkan</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="28" t="inlineStr">
-        <is>
-          <t>Aug 16</t>
-        </is>
-      </c>
-      <c r="B88" s="28" t="inlineStr">
-        <is>
-          <t>9:45AM</t>
-        </is>
-      </c>
-      <c r="C88" s="28" t="inlineStr">
-        <is>
-          <t>10:05AM</t>
-        </is>
-      </c>
-      <c r="D88" s="28" t="inlineStr">
-        <is>
-          <t>41 and above</t>
-        </is>
-      </c>
-      <c r="E88" s="28" t="n">
-        <v>46</v>
-      </c>
-      <c r="F88" s="28" t="inlineStr">
-        <is>
-          <t>41P-15</t>
-        </is>
-      </c>
-      <c r="G88" s="28" t="inlineStr">
-        <is>
-          <t>Board 1</t>
-        </is>
-      </c>
-      <c r="H88" s="28" t="inlineStr">
-        <is>
-          <t>Adil Khan</t>
-        </is>
-      </c>
-      <c r="I88" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J88" s="28" t="inlineStr">
-        <is>
-          <t>Sachin Malgadnkar</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="27" t="inlineStr">
-        <is>
-          <t>Aug 16</t>
-        </is>
-      </c>
-      <c r="B89" s="27" t="inlineStr">
-        <is>
-          <t>10:15AM</t>
-        </is>
-      </c>
-      <c r="C89" s="27" t="inlineStr">
-        <is>
-          <t>10:35AM</t>
-        </is>
-      </c>
-      <c r="D89" s="27" t="inlineStr">
-        <is>
-          <t>41 and above</t>
-        </is>
-      </c>
-      <c r="E89" s="27" t="n">
-        <v>47</v>
-      </c>
-      <c r="F89" s="27" t="inlineStr">
-        <is>
-          <t>41P-16</t>
-        </is>
-      </c>
-      <c r="G89" s="27" t="inlineStr">
-        <is>
-          <t>Board 1</t>
-        </is>
-      </c>
-      <c r="H89" s="27" t="inlineStr">
-        <is>
-          <t>Adil Khan</t>
-        </is>
-      </c>
-      <c r="I89" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J89" s="27" t="inlineStr">
-        <is>
-          <t>Harkishin malkan</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="28" t="inlineStr">
-        <is>
-          <t>Aug 16</t>
-        </is>
-      </c>
-      <c r="B90" s="28" t="inlineStr">
-        <is>
-          <t>10:15AM</t>
-        </is>
-      </c>
-      <c r="C90" s="28" t="inlineStr">
-        <is>
-          <t>10:35AM</t>
-        </is>
-      </c>
-      <c r="D90" s="28" t="inlineStr">
-        <is>
-          <t>41 and above</t>
-        </is>
-      </c>
-      <c r="E90" s="28" t="n">
-        <v>48</v>
-      </c>
-      <c r="F90" s="28" t="inlineStr">
-        <is>
-          <t>41P-17</t>
-        </is>
-      </c>
-      <c r="G90" s="28" t="inlineStr">
-        <is>
-          <t>Board 2</t>
-        </is>
-      </c>
-      <c r="H90" s="28" t="inlineStr">
-        <is>
-          <t>Sachin Malgadnkar</t>
-        </is>
-      </c>
-      <c r="I90" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J90" s="28" t="inlineStr">
-        <is>
-          <t>Ajit nair</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="27" t="inlineStr">
-        <is>
-          <t>Aug 16</t>
-        </is>
-      </c>
-      <c r="B91" s="27" t="inlineStr">
-        <is>
-          <t>10:45AM</t>
-        </is>
-      </c>
-      <c r="C91" s="27" t="inlineStr">
-        <is>
-          <t>11:05AM</t>
-        </is>
-      </c>
-      <c r="D91" s="27" t="inlineStr">
-        <is>
-          <t>41 and above</t>
-        </is>
-      </c>
-      <c r="E91" s="27" t="n">
-        <v>49</v>
-      </c>
-      <c r="F91" s="27" t="inlineStr">
-        <is>
-          <t>41P-18</t>
-        </is>
-      </c>
-      <c r="G91" s="27" t="inlineStr">
-        <is>
-          <t>Board 1</t>
-        </is>
-      </c>
-      <c r="H91" s="27" t="inlineStr">
-        <is>
-          <t>Piyush Makharia</t>
-        </is>
-      </c>
-      <c r="I91" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J91" s="27" t="inlineStr">
-        <is>
-          <t>Harkishin malkan</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="28" t="inlineStr">
-        <is>
-          <t>Aug 16</t>
-        </is>
-      </c>
-      <c r="B92" s="28" t="inlineStr">
-        <is>
-          <t>11:15AM</t>
-        </is>
-      </c>
-      <c r="C92" s="28" t="inlineStr">
-        <is>
-          <t>11:35AM</t>
-        </is>
-      </c>
-      <c r="D92" s="28" t="inlineStr">
-        <is>
-          <t>41 and above</t>
-        </is>
-      </c>
-      <c r="E92" s="28" t="n">
-        <v>50</v>
-      </c>
-      <c r="F92" s="28" t="inlineStr">
-        <is>
-          <t>41P-19</t>
-        </is>
-      </c>
-      <c r="G92" s="28" t="inlineStr">
-        <is>
-          <t>Board 1</t>
-        </is>
-      </c>
-      <c r="H92" s="28" t="inlineStr">
-        <is>
-          <t>Prasad Akshintala</t>
-        </is>
-      </c>
-      <c r="I92" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J92" s="28" t="inlineStr">
-        <is>
-          <t>Harkishin malkan</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="27" t="inlineStr">
-        <is>
-          <t>Aug 16</t>
-        </is>
-      </c>
-      <c r="B93" s="27" t="inlineStr">
-        <is>
-          <t>11:45AM</t>
-        </is>
-      </c>
-      <c r="C93" s="27" t="inlineStr">
-        <is>
-          <t>12:05PM</t>
-        </is>
-      </c>
-      <c r="D93" s="27" t="inlineStr">
-        <is>
-          <t>41 and above</t>
-        </is>
-      </c>
-      <c r="E93" s="27" t="n">
-        <v>51</v>
-      </c>
-      <c r="F93" s="27" t="inlineStr">
-        <is>
-          <t>41P-20</t>
-        </is>
-      </c>
-      <c r="G93" s="27" t="inlineStr">
-        <is>
-          <t>Board 1</t>
-        </is>
-      </c>
-      <c r="H93" s="27" t="inlineStr">
-        <is>
-          <t>Ajit nair</t>
-        </is>
-      </c>
-      <c r="I93" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J93" s="27" t="inlineStr">
-        <is>
-          <t>Harkishin malkan</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="28" t="inlineStr">
-        <is>
-          <t>Aug 16</t>
-        </is>
-      </c>
-      <c r="B94" s="28" t="inlineStr">
-        <is>
-          <t>3:00PM</t>
-        </is>
-      </c>
-      <c r="C94" s="28" t="inlineStr">
-        <is>
-          <t>3:20PM</t>
-        </is>
-      </c>
-      <c r="D94" s="28" t="inlineStr">
-        <is>
-          <t>41 and above</t>
-        </is>
-      </c>
-      <c r="E94" s="28" t="n">
-        <v>52</v>
-      </c>
-      <c r="F94" s="28" t="inlineStr">
-        <is>
-          <t>41P-21</t>
-        </is>
-      </c>
-      <c r="G94" s="28" t="inlineStr">
-        <is>
-          <t>Board 1</t>
-        </is>
-      </c>
-      <c r="H94" s="28" t="inlineStr">
-        <is>
-          <t>Sachin Malgadnkar</t>
-        </is>
-      </c>
-      <c r="I94" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J94" s="28" t="inlineStr">
-        <is>
-          <t>Harkishin malkan</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="27" t="inlineStr">
-        <is>
-          <t>Aug 16</t>
-        </is>
-      </c>
-      <c r="B95" s="27" t="inlineStr">
-        <is>
-          <t>3:20PM</t>
-        </is>
-      </c>
-      <c r="C95" s="27" t="inlineStr">
-        <is>
-          <t>3:40PM</t>
-        </is>
-      </c>
-      <c r="D95" s="27" t="inlineStr">
-        <is>
-          <t>12 to 20</t>
-        </is>
-      </c>
-      <c r="E95" s="27" t="n">
-        <v>53</v>
-      </c>
-      <c r="F95" s="27" t="inlineStr">
-        <is>
-          <t>1220-FINAL</t>
-        </is>
-      </c>
-      <c r="G95" s="27" t="inlineStr">
-        <is>
-          <t>Board 1</t>
-        </is>
-      </c>
-      <c r="H95" s="27" t="inlineStr">
-        <is>
-          <t>Pool 1st</t>
-        </is>
-      </c>
-      <c r="I95" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J95" s="27" t="inlineStr">
-        <is>
-          <t>Pool 2nd</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="28" t="inlineStr">
-        <is>
-          <t>Aug 16</t>
-        </is>
-      </c>
-      <c r="B96" s="28" t="inlineStr">
-        <is>
-          <t>3:20PM</t>
-        </is>
-      </c>
-      <c r="C96" s="28" t="inlineStr">
-        <is>
-          <t>3:40PM</t>
-        </is>
-      </c>
-      <c r="D96" s="28" t="inlineStr">
-        <is>
-          <t>Under 11</t>
-        </is>
-      </c>
-      <c r="E96" s="28" t="n">
-        <v>54</v>
-      </c>
-      <c r="F96" s="28" t="inlineStr">
-        <is>
-          <t>U11-FINAL</t>
-        </is>
-      </c>
-      <c r="G96" s="28" t="inlineStr">
-        <is>
-          <t>Board 2</t>
-        </is>
-      </c>
-      <c r="H96" s="28" t="inlineStr">
-        <is>
-          <t>Pool 1st</t>
-        </is>
-      </c>
-      <c r="I96" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J96" s="28" t="inlineStr">
-        <is>
-          <t>Pool 2nd</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="27" t="inlineStr">
-        <is>
-          <t>Aug 16</t>
-        </is>
-      </c>
-      <c r="B97" s="27" t="inlineStr">
-        <is>
-          <t>3:40PM</t>
-        </is>
-      </c>
-      <c r="C97" s="27" t="inlineStr">
-        <is>
-          <t>4:00PM</t>
-        </is>
-      </c>
-      <c r="D97" s="27" t="inlineStr">
-        <is>
-          <t>21 to 40</t>
-        </is>
-      </c>
-      <c r="E97" s="27" t="n">
-        <v>55</v>
-      </c>
-      <c r="F97" s="27" t="inlineStr">
-        <is>
-          <t>2140-FINAL</t>
-        </is>
-      </c>
-      <c r="G97" s="27" t="inlineStr">
-        <is>
-          <t>Board 1</t>
-        </is>
-      </c>
-      <c r="H97" s="27" t="inlineStr">
-        <is>
-          <t>Pool 1st</t>
-        </is>
-      </c>
-      <c r="I97" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J97" s="27" t="inlineStr">
-        <is>
-          <t>Pool 2nd</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="28" t="inlineStr">
-        <is>
-          <t>Aug 16</t>
-        </is>
-      </c>
-      <c r="B98" s="28" t="inlineStr">
-        <is>
-          <t>4:00PM</t>
-        </is>
-      </c>
-      <c r="C98" s="28" t="inlineStr">
-        <is>
-          <t>4:20PM</t>
-        </is>
-      </c>
-      <c r="D98" s="28" t="inlineStr">
-        <is>
-          <t>41 and above</t>
-        </is>
-      </c>
-      <c r="E98" s="28" t="n">
-        <v>56</v>
-      </c>
-      <c r="F98" s="28" t="inlineStr">
-        <is>
-          <t>41P-SF1</t>
-        </is>
-      </c>
-      <c r="G98" s="28" t="inlineStr">
-        <is>
-          <t>Board 1</t>
-        </is>
-      </c>
-      <c r="H98" s="28" t="inlineStr">
-        <is>
-          <t>Round Robin 1st</t>
-        </is>
-      </c>
-      <c r="I98" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J98" s="28" t="inlineStr">
-        <is>
-          <t>Round Robin 4th</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="27" t="inlineStr">
-        <is>
-          <t>Aug 16</t>
-        </is>
-      </c>
-      <c r="B99" s="27" t="inlineStr">
-        <is>
-          <t>4:20PM</t>
-        </is>
-      </c>
-      <c r="C99" s="27" t="inlineStr">
-        <is>
-          <t>4:40PM</t>
-        </is>
-      </c>
-      <c r="D99" s="27" t="inlineStr">
-        <is>
-          <t>41 and above</t>
-        </is>
-      </c>
-      <c r="E99" s="27" t="n">
-        <v>57</v>
-      </c>
-      <c r="F99" s="27" t="inlineStr">
-        <is>
-          <t>41P-SF2</t>
-        </is>
-      </c>
-      <c r="G99" s="27" t="inlineStr">
-        <is>
-          <t>Board 1</t>
-        </is>
-      </c>
-      <c r="H99" s="27" t="inlineStr">
-        <is>
-          <t>Round Robin 2nd</t>
-        </is>
-      </c>
-      <c r="I99" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J99" s="27" t="inlineStr">
-        <is>
-          <t>Round Robin 3rd</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="28" t="inlineStr">
-        <is>
-          <t>Aug 16</t>
-        </is>
-      </c>
-      <c r="B100" s="28" t="inlineStr">
-        <is>
-          <t>4:40PM</t>
-        </is>
-      </c>
-      <c r="C100" s="28" t="inlineStr">
-        <is>
-          <t>5:00PM</t>
-        </is>
-      </c>
-      <c r="D100" s="28" t="inlineStr">
-        <is>
-          <t>41 and above</t>
-        </is>
-      </c>
-      <c r="E100" s="28" t="n">
-        <v>58</v>
-      </c>
-      <c r="F100" s="28" t="inlineStr">
-        <is>
-          <t>41P-FINAL</t>
-        </is>
-      </c>
-      <c r="G100" s="28" t="inlineStr">
-        <is>
-          <t>Board 1</t>
-        </is>
-      </c>
-      <c r="H100" s="28" t="inlineStr">
-        <is>
-          <t>Winner 41P-SF1</t>
-        </is>
-      </c>
-      <c r="I100" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J100" s="28" t="inlineStr">
-        <is>
-          <t>Winner 41P-SF2</t>
+      <c r="H100" s="95" t="inlineStr">
+        <is>
+          <t>Winner SF1</t>
+        </is>
+      </c>
+      <c r="I100" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J100" s="95" t="inlineStr">
+        <is>
+          <t>Winner SF2</t>
         </is>
       </c>
     </row>

--- a/Ekta_Schedule_With_Matchups.xlsx
+++ b/Ekta_Schedule_With_Matchups.xlsx
@@ -1242,7 +1242,7 @@
       </c>
       <c r="C15" s="64" t="inlineStr">
         <is>
-          <t>League stage continues. Carrom Women's Singles (done ~11:30 AM) and TT Women's Singles (done ~11:15 AM) each finish in full today — their knockouts run right after their own league stage ends, no waiting for other events. TT Men's Above 46 knockout leads off the morning on Table 1 at 8:00 AM. Carrom Men's Singles and Pool now also finish entirely today — Carrom Men's by ~5:45 PM and Pool by ~10:00 PM — both reflowed to fill real gaps in players' other-sport schedules instead of spilling into Aug 16.</t>
+          <t>League stage continues. TT Women's Singles (done 12:00 PM) and Carrom Women's Singles (done ~11:30 AM) each finish in full today. TT Men's Singles (Above 46 knockout leads off Table 2 at 8:00 AM) and Carrom Men's Singles (done ~5:45 PM) both now run almost entirely today too, with Chess and Pool likewise wrapping up today or overnight — all five were reflowed to use real gaps in players' other-sport schedules instead of sitting on idle tables/boards.</t>
         </is>
       </c>
       <c r="H15" s="31" t="n"/>
@@ -1262,7 +1262,7 @@
       </c>
       <c r="C16" s="64" t="inlineStr">
         <is>
-          <t>Remaining league matches continue for TT Men's Singles (the only group/pool stage still running past Aug 15). Chess's entire pool stage, semifinals, and final complete by 8:20 AM (reflowed — previously ran until 5:00 PM). Squash's Under 15 + 15-25 Bracket knockouts follow right after Squash's own league stage (~6:39 PM Aug 15).</t>
+          <t>Only a handful of matches remain from Aug 15: TT Men's Singles' Under 46 Final (8:00-8:15 AM) and Chess's 41-and-above Final (8:20 AM) both wrap up within the first half hour. Squash's own league stage continues (its Under 15 + 15-25 Bracket knockouts followed right after Squash's own league stage ~6:39 PM Aug 15; its Above 25 Bracket is the one event still running its group stage into Aug 16).</t>
         </is>
       </c>
       <c r="H16" s="31" t="n"/>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="C17" s="64" t="inlineStr">
         <is>
-          <t>Both Doubles events run once their own players are free — Carrom Doubles 9:30-11:50 AM; TT Doubles starts 9:05 AM and interleaves with TT Men's Singles on the shared tables, wrapping by 4:30 PM.</t>
+          <t>Both Doubles events run once their own players are free — TT Doubles wraps up 9:00-10:15 AM; Carrom Doubles runs 9:00 AM-10:30 AM, both far ahead of their old finish times since neither table time nor board time is the constraint anymore.</t>
         </is>
       </c>
       <c r="H17" s="31" t="n"/>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="C19" s="64" t="inlineStr">
         <is>
-          <t>Once TT Men's Singles' own league stage is finished, its remaining Semis/Finals begin, alongside Squash's Above 25 Bracket (the only two events whose semis/finals now land this late — Carrom Men's Singles and Chess both wrapped up during Aug 15/early Aug 16).</t>
+          <t>Squash's Above 25 Bracket is now the only semis/finals still gated behind a same-day group stage — every other event's semis/finals landed on Aug 15 evening or the first hour of Aug 16.</t>
         </is>
       </c>
       <c r="H19" s="31" t="n"/>
@@ -1411,12 +1411,12 @@
       </c>
       <c r="D24" s="63" t="inlineStr">
         <is>
-          <t>Aug15 8:00AM</t>
+          <t>Aug15 8:45AM</t>
         </is>
       </c>
       <c r="E24" s="63" t="inlineStr">
         <is>
-          <t>Aug15 11:15AM</t>
+          <t>Aug15 12:00PM</t>
         </is>
       </c>
       <c r="F24" s="31" t="n"/>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="E25" s="63" t="inlineStr">
         <is>
-          <t>Aug16 4:00PM</t>
+          <t>Aug16 8:15AM</t>
         </is>
       </c>
       <c r="F25" s="31" t="n"/>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="D26" s="63" t="inlineStr">
         <is>
-          <t>Aug16 9:05AM</t>
+          <t>Aug16 9:00AM</t>
         </is>
       </c>
       <c r="E26" s="63" t="inlineStr">
         <is>
-          <t>Aug16 4:30PM</t>
+          <t>Aug16 10:15AM</t>
         </is>
       </c>
       <c r="F26" s="31" t="n"/>
@@ -1680,7 +1680,7 @@
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="86" t="inlineStr">
         <is>
-          <t>Overall tournament span: Aug 15, 8:00 AM start → Aug 16, 4:30 PM finish — comfortably inside the Aug 16, 10 PM cap.</t>
+          <t>Overall tournament span: Aug 15, 8:00 AM start → Aug 16, 4:14 PM finish — comfortably inside the Aug 16, 10 PM cap.</t>
         </is>
       </c>
       <c r="F34" s="31" t="n"/>
@@ -4972,12 +4972,12 @@
       </c>
       <c r="B16" s="94" t="inlineStr">
         <is>
-          <t>8:00AM</t>
+          <t>8:45AM</t>
         </is>
       </c>
       <c r="C16" s="94" t="inlineStr">
         <is>
-          <t>8:15AM</t>
+          <t>9:00AM</t>
         </is>
       </c>
       <c r="D16" s="94" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="B17" s="95" t="inlineStr">
         <is>
-          <t>8:15AM</t>
+          <t>9:00AM</t>
         </is>
       </c>
       <c r="C17" s="95" t="inlineStr">
         <is>
-          <t>8:30AM</t>
+          <t>9:15AM</t>
         </is>
       </c>
       <c r="D17" s="95" t="inlineStr">
@@ -5045,7 +5045,7 @@
       </c>
       <c r="G17" s="95" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H17" s="95" t="inlineStr">
@@ -5072,12 +5072,12 @@
       </c>
       <c r="B18" s="94" t="inlineStr">
         <is>
-          <t>8:15AM</t>
+          <t>9:15AM</t>
         </is>
       </c>
       <c r="C18" s="94" t="inlineStr">
         <is>
-          <t>8:30AM</t>
+          <t>9:30AM</t>
         </is>
       </c>
       <c r="D18" s="94" t="inlineStr">
@@ -5095,7 +5095,7 @@
       </c>
       <c r="G18" s="94" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H18" s="94" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="B19" s="95" t="inlineStr">
         <is>
-          <t>8:30AM</t>
+          <t>9:15AM</t>
         </is>
       </c>
       <c r="C19" s="95" t="inlineStr">
         <is>
-          <t>8:45AM</t>
+          <t>9:30AM</t>
         </is>
       </c>
       <c r="D19" s="95" t="inlineStr">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="G19" s="95" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H19" s="95" t="inlineStr">
@@ -5172,12 +5172,12 @@
       </c>
       <c r="B20" s="94" t="inlineStr">
         <is>
-          <t>8:45AM</t>
+          <t>10:30AM</t>
         </is>
       </c>
       <c r="C20" s="94" t="inlineStr">
         <is>
-          <t>9:00AM</t>
+          <t>10:45AM</t>
         </is>
       </c>
       <c r="D20" s="94" t="inlineStr">
@@ -5222,12 +5222,12 @@
       </c>
       <c r="B21" s="95" t="inlineStr">
         <is>
-          <t>8:45AM</t>
+          <t>10:30AM</t>
         </is>
       </c>
       <c r="C21" s="95" t="inlineStr">
         <is>
-          <t>9:00AM</t>
+          <t>10:45AM</t>
         </is>
       </c>
       <c r="D21" s="95" t="inlineStr">
@@ -5272,12 +5272,12 @@
       </c>
       <c r="B22" s="94" t="inlineStr">
         <is>
-          <t>9:00AM</t>
+          <t>10:45AM</t>
         </is>
       </c>
       <c r="C22" s="94" t="inlineStr">
         <is>
-          <t>9:15AM</t>
+          <t>11:00AM</t>
         </is>
       </c>
       <c r="D22" s="94" t="inlineStr">
@@ -5322,12 +5322,12 @@
       </c>
       <c r="B23" s="95" t="inlineStr">
         <is>
-          <t>9:00AM</t>
+          <t>10:45AM</t>
         </is>
       </c>
       <c r="C23" s="95" t="inlineStr">
         <is>
-          <t>9:15AM</t>
+          <t>11:00AM</t>
         </is>
       </c>
       <c r="D23" s="95" t="inlineStr">
@@ -5372,12 +5372,12 @@
       </c>
       <c r="B24" s="94" t="inlineStr">
         <is>
-          <t>9:15AM</t>
+          <t>11:00AM</t>
         </is>
       </c>
       <c r="C24" s="94" t="inlineStr">
         <is>
-          <t>9:30AM</t>
+          <t>11:15AM</t>
         </is>
       </c>
       <c r="D24" s="94" t="inlineStr">
@@ -5422,12 +5422,12 @@
       </c>
       <c r="B25" s="95" t="inlineStr">
         <is>
-          <t>9:15AM</t>
+          <t>11:00AM</t>
         </is>
       </c>
       <c r="C25" s="95" t="inlineStr">
         <is>
-          <t>9:30AM</t>
+          <t>11:15AM</t>
         </is>
       </c>
       <c r="D25" s="95" t="inlineStr">
@@ -5472,12 +5472,12 @@
       </c>
       <c r="B26" s="94" t="inlineStr">
         <is>
-          <t>10:30AM</t>
+          <t>11:15AM</t>
         </is>
       </c>
       <c r="C26" s="94" t="inlineStr">
         <is>
-          <t>10:45AM</t>
+          <t>11:30AM</t>
         </is>
       </c>
       <c r="D26" s="94" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="B27" s="95" t="inlineStr">
         <is>
-          <t>10:30AM</t>
+          <t>11:15AM</t>
         </is>
       </c>
       <c r="C27" s="95" t="inlineStr">
         <is>
-          <t>10:45AM</t>
+          <t>11:30AM</t>
         </is>
       </c>
       <c r="D27" s="95" t="inlineStr">
@@ -5572,12 +5572,12 @@
       </c>
       <c r="B28" s="94" t="inlineStr">
         <is>
-          <t>10:45AM</t>
+          <t>11:30AM</t>
         </is>
       </c>
       <c r="C28" s="94" t="inlineStr">
         <is>
-          <t>11:00AM</t>
+          <t>11:45AM</t>
         </is>
       </c>
       <c r="D28" s="94" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="B29" s="95" t="inlineStr">
         <is>
-          <t>10:45AM</t>
+          <t>11:30AM</t>
         </is>
       </c>
       <c r="C29" s="95" t="inlineStr">
         <is>
-          <t>11:00AM</t>
+          <t>11:45AM</t>
         </is>
       </c>
       <c r="D29" s="95" t="inlineStr">
@@ -5672,12 +5672,12 @@
       </c>
       <c r="B30" s="94" t="inlineStr">
         <is>
-          <t>11:00AM</t>
+          <t>11:45AM</t>
         </is>
       </c>
       <c r="C30" s="94" t="inlineStr">
         <is>
-          <t>11:15AM</t>
+          <t>12:00PM</t>
         </is>
       </c>
       <c r="D30" s="94" t="inlineStr">
@@ -6466,17 +6466,17 @@
       </c>
       <c r="F49" s="94" t="inlineStr">
         <is>
-          <t>A46-QF3</t>
+          <t>A46-QF2</t>
         </is>
       </c>
       <c r="G49" s="94" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H49" s="94" t="inlineStr">
         <is>
-          <t>Ghansyam nawani</t>
+          <t>Vinod Agrawal</t>
         </is>
       </c>
       <c r="I49" s="94" t="inlineStr">
@@ -6486,7 +6486,7 @@
       </c>
       <c r="J49" s="94" t="inlineStr">
         <is>
-          <t>HARSHAPRABHAT SHETTY</t>
+          <t>Kishore Kumar</t>
         </is>
       </c>
     </row>
@@ -6498,17 +6498,17 @@
       </c>
       <c r="B50" s="95" t="inlineStr">
         <is>
-          <t>8:30AM</t>
+          <t>8:00AM</t>
         </is>
       </c>
       <c r="C50" s="95" t="inlineStr">
         <is>
-          <t>8:45AM</t>
+          <t>8:15AM</t>
         </is>
       </c>
       <c r="D50" s="95" t="inlineStr">
         <is>
-          <t>Under 36</t>
+          <t>Above 46</t>
         </is>
       </c>
       <c r="E50" s="95" t="n">
@@ -6516,17 +6516,17 @@
       </c>
       <c r="F50" s="95" t="inlineStr">
         <is>
-          <t>U36-GB-1</t>
+          <t>A46-R1</t>
         </is>
       </c>
       <c r="G50" s="95" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H50" s="95" t="inlineStr">
         <is>
-          <t>Prakshal Shah</t>
+          <t>Adil Khan</t>
         </is>
       </c>
       <c r="I50" s="95" t="inlineStr">
@@ -6536,7 +6536,7 @@
       </c>
       <c r="J50" s="95" t="inlineStr">
         <is>
-          <t>Amar Parulekar</t>
+          <t>Ajit nair</t>
         </is>
       </c>
     </row>
@@ -6548,17 +6548,17 @@
       </c>
       <c r="B51" s="94" t="inlineStr">
         <is>
-          <t>3:38PM</t>
+          <t>8:15AM</t>
         </is>
       </c>
       <c r="C51" s="94" t="inlineStr">
         <is>
-          <t>3:53PM</t>
+          <t>8:30AM</t>
         </is>
       </c>
       <c r="D51" s="94" t="inlineStr">
         <is>
-          <t>Under 26</t>
+          <t>Above 46</t>
         </is>
       </c>
       <c r="E51" s="94" t="n">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F51" s="94" t="inlineStr">
         <is>
-          <t>U26-2</t>
+          <t>A46-QF1</t>
         </is>
       </c>
       <c r="G51" s="94" t="inlineStr">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="H51" s="94" t="inlineStr">
         <is>
-          <t>Yuvraj jain</t>
+          <t>Winner R1</t>
         </is>
       </c>
       <c r="I51" s="94" t="inlineStr">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="J51" s="94" t="inlineStr">
         <is>
-          <t>Hryday Goyal</t>
+          <t>Sanjay Kumar</t>
         </is>
       </c>
     </row>
@@ -6598,17 +6598,17 @@
       </c>
       <c r="B52" s="95" t="inlineStr">
         <is>
-          <t>4:00PM</t>
+          <t>8:15AM</t>
         </is>
       </c>
       <c r="C52" s="95" t="inlineStr">
         <is>
-          <t>4:15PM</t>
+          <t>8:30AM</t>
         </is>
       </c>
       <c r="D52" s="95" t="inlineStr">
         <is>
-          <t>Under 36</t>
+          <t>Above 46</t>
         </is>
       </c>
       <c r="E52" s="95" t="n">
@@ -6616,17 +6616,17 @@
       </c>
       <c r="F52" s="95" t="inlineStr">
         <is>
-          <t>U36-GA-2</t>
+          <t>A46-QF3</t>
         </is>
       </c>
       <c r="G52" s="95" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H52" s="95" t="inlineStr">
         <is>
-          <t>Jashit Bajaj</t>
+          <t>Ghansyam nawani</t>
         </is>
       </c>
       <c r="I52" s="95" t="inlineStr">
@@ -6636,7 +6636,7 @@
       </c>
       <c r="J52" s="95" t="inlineStr">
         <is>
-          <t>Tapabrata Dutta</t>
+          <t>HARSHAPRABHAT SHETTY</t>
         </is>
       </c>
     </row>
@@ -6648,17 +6648,17 @@
       </c>
       <c r="B53" s="94" t="inlineStr">
         <is>
-          <t>4:10PM</t>
+          <t>8:30AM</t>
         </is>
       </c>
       <c r="C53" s="94" t="inlineStr">
         <is>
-          <t>4:25PM</t>
+          <t>8:45AM</t>
         </is>
       </c>
       <c r="D53" s="94" t="inlineStr">
         <is>
-          <t>Under 46</t>
+          <t>Above 46</t>
         </is>
       </c>
       <c r="E53" s="94" t="n">
@@ -6666,17 +6666,17 @@
       </c>
       <c r="F53" s="94" t="inlineStr">
         <is>
-          <t>U46-GA-9</t>
+          <t>A46-QF4</t>
         </is>
       </c>
       <c r="G53" s="94" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H53" s="94" t="inlineStr">
         <is>
-          <t>Sudip Parui</t>
+          <t>Mukul Joshi</t>
         </is>
       </c>
       <c r="I53" s="94" t="inlineStr">
@@ -6686,7 +6686,7 @@
       </c>
       <c r="J53" s="94" t="inlineStr">
         <is>
-          <t>Anuj Shah</t>
+          <t>Sushil Dashpute</t>
         </is>
       </c>
     </row>
@@ -6698,17 +6698,17 @@
       </c>
       <c r="B54" s="95" t="inlineStr">
         <is>
-          <t>5:00PM</t>
+          <t>8:30AM</t>
         </is>
       </c>
       <c r="C54" s="95" t="inlineStr">
         <is>
-          <t>5:15PM</t>
+          <t>8:45AM</t>
         </is>
       </c>
       <c r="D54" s="95" t="inlineStr">
         <is>
-          <t>Under 15</t>
+          <t>Above 46</t>
         </is>
       </c>
       <c r="E54" s="95" t="n">
@@ -6716,17 +6716,17 @@
       </c>
       <c r="F54" s="95" t="inlineStr">
         <is>
-          <t>U15-GA-1</t>
+          <t>A46-SF1</t>
         </is>
       </c>
       <c r="G54" s="95" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H54" s="95" t="inlineStr">
         <is>
-          <t>Shaurya Tripathi</t>
+          <t>Winner QF1</t>
         </is>
       </c>
       <c r="I54" s="95" t="inlineStr">
@@ -6736,7 +6736,7 @@
       </c>
       <c r="J54" s="95" t="inlineStr">
         <is>
-          <t>Parth yadav</t>
+          <t>Winner QF2</t>
         </is>
       </c>
     </row>
@@ -6748,17 +6748,17 @@
       </c>
       <c r="B55" s="94" t="inlineStr">
         <is>
-          <t>5:00PM</t>
+          <t>8:45AM</t>
         </is>
       </c>
       <c r="C55" s="94" t="inlineStr">
         <is>
-          <t>5:15PM</t>
+          <t>9:00AM</t>
         </is>
       </c>
       <c r="D55" s="94" t="inlineStr">
         <is>
-          <t>Under 15</t>
+          <t>Above 46</t>
         </is>
       </c>
       <c r="E55" s="94" t="n">
@@ -6766,17 +6766,17 @@
       </c>
       <c r="F55" s="94" t="inlineStr">
         <is>
-          <t>U15-GB-1</t>
+          <t>A46-SF2</t>
         </is>
       </c>
       <c r="G55" s="94" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H55" s="94" t="inlineStr">
         <is>
-          <t>Viaan Neema</t>
+          <t>Winner QF3</t>
         </is>
       </c>
       <c r="I55" s="94" t="inlineStr">
@@ -6786,7 +6786,7 @@
       </c>
       <c r="J55" s="94" t="inlineStr">
         <is>
-          <t>Yash agarwal</t>
+          <t>Winner QF4</t>
         </is>
       </c>
     </row>
@@ -6798,17 +6798,17 @@
       </c>
       <c r="B56" s="95" t="inlineStr">
         <is>
-          <t>5:30PM</t>
+          <t>9:00AM</t>
         </is>
       </c>
       <c r="C56" s="95" t="inlineStr">
         <is>
-          <t>5:45PM</t>
+          <t>9:15AM</t>
         </is>
       </c>
       <c r="D56" s="95" t="inlineStr">
         <is>
-          <t>Under 46</t>
+          <t>Above 46</t>
         </is>
       </c>
       <c r="E56" s="95" t="n">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="F56" s="95" t="inlineStr">
         <is>
-          <t>U46-GA-5</t>
+          <t>A46-FINAL</t>
         </is>
       </c>
       <c r="G56" s="95" t="inlineStr">
@@ -6826,7 +6826,7 @@
       </c>
       <c r="H56" s="95" t="inlineStr">
         <is>
-          <t>Ankur Mahante</t>
+          <t>Winner SF1</t>
         </is>
       </c>
       <c r="I56" s="95" t="inlineStr">
@@ -6836,7 +6836,7 @@
       </c>
       <c r="J56" s="95" t="inlineStr">
         <is>
-          <t>Sudip Parui</t>
+          <t>Winner SF2</t>
         </is>
       </c>
     </row>
@@ -6848,17 +6848,17 @@
       </c>
       <c r="B57" s="94" t="inlineStr">
         <is>
-          <t>5:55PM</t>
+          <t>11:45AM</t>
         </is>
       </c>
       <c r="C57" s="94" t="inlineStr">
         <is>
-          <t>6:10PM</t>
+          <t>12:00PM</t>
         </is>
       </c>
       <c r="D57" s="94" t="inlineStr">
         <is>
-          <t>Under 46</t>
+          <t>Under 36</t>
         </is>
       </c>
       <c r="E57" s="94" t="n">
@@ -6866,17 +6866,17 @@
       </c>
       <c r="F57" s="94" t="inlineStr">
         <is>
-          <t>U46-GA-7</t>
+          <t>U36-GB-1</t>
         </is>
       </c>
       <c r="G57" s="94" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H57" s="94" t="inlineStr">
         <is>
-          <t>Ankur Mahante</t>
+          <t>Prakshal Shah</t>
         </is>
       </c>
       <c r="I57" s="94" t="inlineStr">
@@ -6886,7 +6886,7 @@
       </c>
       <c r="J57" s="94" t="inlineStr">
         <is>
-          <t>Anuj Shah</t>
+          <t>Amar Parulekar</t>
         </is>
       </c>
     </row>
@@ -6898,17 +6898,17 @@
       </c>
       <c r="B58" s="95" t="inlineStr">
         <is>
-          <t>6:11PM</t>
+          <t>3:00PM</t>
         </is>
       </c>
       <c r="C58" s="95" t="inlineStr">
         <is>
-          <t>6:26PM</t>
+          <t>3:15PM</t>
         </is>
       </c>
       <c r="D58" s="95" t="inlineStr">
         <is>
-          <t>Under 36</t>
+          <t>Under 26</t>
         </is>
       </c>
       <c r="E58" s="95" t="n">
@@ -6916,7 +6916,7 @@
       </c>
       <c r="F58" s="95" t="inlineStr">
         <is>
-          <t>U36-GA-1</t>
+          <t>U26-2</t>
         </is>
       </c>
       <c r="G58" s="95" t="inlineStr">
@@ -6926,7 +6926,7 @@
       </c>
       <c r="H58" s="95" t="inlineStr">
         <is>
-          <t>Jashit Bajaj</t>
+          <t>Yuvraj jain</t>
         </is>
       </c>
       <c r="I58" s="95" t="inlineStr">
@@ -6936,7 +6936,7 @@
       </c>
       <c r="J58" s="95" t="inlineStr">
         <is>
-          <t>Ravi Modi</t>
+          <t>Hryday Goyal</t>
         </is>
       </c>
     </row>
@@ -6948,12 +6948,12 @@
       </c>
       <c r="B59" s="94" t="inlineStr">
         <is>
-          <t>6:36PM</t>
+          <t>3:00PM</t>
         </is>
       </c>
       <c r="C59" s="94" t="inlineStr">
         <is>
-          <t>6:51PM</t>
+          <t>3:15PM</t>
         </is>
       </c>
       <c r="D59" s="94" t="inlineStr">
@@ -6966,17 +6966,17 @@
       </c>
       <c r="F59" s="94" t="inlineStr">
         <is>
-          <t>U36-GA-3</t>
+          <t>U36-GA-2</t>
         </is>
       </c>
       <c r="G59" s="94" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H59" s="94" t="inlineStr">
         <is>
-          <t>Ravi Modi</t>
+          <t>Jashit Bajaj</t>
         </is>
       </c>
       <c r="I59" s="94" t="inlineStr">
@@ -6998,17 +6998,17 @@
       </c>
       <c r="B60" s="95" t="inlineStr">
         <is>
-          <t>6:40PM</t>
+          <t>3:15PM</t>
         </is>
       </c>
       <c r="C60" s="95" t="inlineStr">
         <is>
-          <t>6:55PM</t>
+          <t>3:30PM</t>
         </is>
       </c>
       <c r="D60" s="95" t="inlineStr">
         <is>
-          <t>Above 46</t>
+          <t>Under 15</t>
         </is>
       </c>
       <c r="E60" s="95" t="n">
@@ -7016,7 +7016,7 @@
       </c>
       <c r="F60" s="95" t="inlineStr">
         <is>
-          <t>A46-QF2</t>
+          <t>U15-GA-1</t>
         </is>
       </c>
       <c r="G60" s="95" t="inlineStr">
@@ -7026,7 +7026,7 @@
       </c>
       <c r="H60" s="95" t="inlineStr">
         <is>
-          <t>Vinod Agrawal</t>
+          <t>Shaurya Tripathi</t>
         </is>
       </c>
       <c r="I60" s="95" t="inlineStr">
@@ -7036,7 +7036,7 @@
       </c>
       <c r="J60" s="95" t="inlineStr">
         <is>
-          <t>Kishore Kumar</t>
+          <t>Parth yadav</t>
         </is>
       </c>
     </row>
@@ -7048,17 +7048,17 @@
       </c>
       <c r="B61" s="94" t="inlineStr">
         <is>
-          <t>6:57PM</t>
+          <t>3:15PM</t>
         </is>
       </c>
       <c r="C61" s="94" t="inlineStr">
         <is>
-          <t>7:12PM</t>
+          <t>3:30PM</t>
         </is>
       </c>
       <c r="D61" s="94" t="inlineStr">
         <is>
-          <t>Under 15</t>
+          <t>Under 46</t>
         </is>
       </c>
       <c r="E61" s="94" t="n">
@@ -7066,7 +7066,7 @@
       </c>
       <c r="F61" s="94" t="inlineStr">
         <is>
-          <t>U15-GB-2</t>
+          <t>U46-GA-9</t>
         </is>
       </c>
       <c r="G61" s="94" t="inlineStr">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="H61" s="94" t="inlineStr">
         <is>
-          <t>Viaan Neema</t>
+          <t>Sudip Parui</t>
         </is>
       </c>
       <c r="I61" s="94" t="inlineStr">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="J61" s="94" t="inlineStr">
         <is>
-          <t>Hridh jhala</t>
+          <t>Anuj Shah</t>
         </is>
       </c>
     </row>
@@ -7098,12 +7098,12 @@
       </c>
       <c r="B62" s="95" t="inlineStr">
         <is>
-          <t>7:22PM</t>
+          <t>3:30PM</t>
         </is>
       </c>
       <c r="C62" s="95" t="inlineStr">
         <is>
-          <t>7:37PM</t>
+          <t>3:45PM</t>
         </is>
       </c>
       <c r="D62" s="95" t="inlineStr">
@@ -7116,7 +7116,7 @@
       </c>
       <c r="F62" s="95" t="inlineStr">
         <is>
-          <t>U15-GB-3</t>
+          <t>U15-GB-1</t>
         </is>
       </c>
       <c r="G62" s="95" t="inlineStr">
@@ -7126,17 +7126,17 @@
       </c>
       <c r="H62" s="95" t="inlineStr">
         <is>
+          <t>Viaan Neema</t>
+        </is>
+      </c>
+      <c r="I62" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J62" s="95" t="inlineStr">
+        <is>
           <t>Yash agarwal</t>
-        </is>
-      </c>
-      <c r="I62" s="95" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J62" s="95" t="inlineStr">
-        <is>
-          <t>Hridh jhala</t>
         </is>
       </c>
     </row>
@@ -7148,12 +7148,12 @@
       </c>
       <c r="B63" s="94" t="inlineStr">
         <is>
-          <t>7:35PM</t>
+          <t>3:30PM</t>
         </is>
       </c>
       <c r="C63" s="94" t="inlineStr">
         <is>
-          <t>7:50PM</t>
+          <t>3:45PM</t>
         </is>
       </c>
       <c r="D63" s="94" t="inlineStr">
@@ -7166,7 +7166,7 @@
       </c>
       <c r="F63" s="94" t="inlineStr">
         <is>
-          <t>U46-GB-10</t>
+          <t>U46-GB-8</t>
         </is>
       </c>
       <c r="G63" s="94" t="inlineStr">
@@ -7176,17 +7176,17 @@
       </c>
       <c r="H63" s="94" t="inlineStr">
         <is>
+          <t>Vinit Padia</t>
+        </is>
+      </c>
+      <c r="I63" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J63" s="94" t="inlineStr">
+        <is>
           <t>Nilesh Bagaria</t>
-        </is>
-      </c>
-      <c r="I63" s="94" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J63" s="94" t="inlineStr">
-        <is>
-          <t>Amit Ranka</t>
         </is>
       </c>
     </row>
@@ -7198,17 +7198,17 @@
       </c>
       <c r="B64" s="95" t="inlineStr">
         <is>
-          <t>7:50PM</t>
+          <t>3:45PM</t>
         </is>
       </c>
       <c r="C64" s="95" t="inlineStr">
         <is>
-          <t>8:05PM</t>
+          <t>4:00PM</t>
         </is>
       </c>
       <c r="D64" s="95" t="inlineStr">
         <is>
-          <t>Under 36</t>
+          <t>Under 26</t>
         </is>
       </c>
       <c r="E64" s="95" t="n">
@@ -7216,17 +7216,17 @@
       </c>
       <c r="F64" s="95" t="inlineStr">
         <is>
-          <t>U36-GB-2</t>
+          <t>U26-8</t>
         </is>
       </c>
       <c r="G64" s="95" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H64" s="95" t="inlineStr">
         <is>
-          <t>Prakshal Shah</t>
+          <t>Hryday Goyal</t>
         </is>
       </c>
       <c r="I64" s="95" t="inlineStr">
@@ -7236,7 +7236,7 @@
       </c>
       <c r="J64" s="95" t="inlineStr">
         <is>
-          <t>Tej</t>
+          <t>Pranit Shriyan</t>
         </is>
       </c>
     </row>
@@ -7248,12 +7248,12 @@
       </c>
       <c r="B65" s="94" t="inlineStr">
         <is>
-          <t>7:55PM</t>
+          <t>3:45PM</t>
         </is>
       </c>
       <c r="C65" s="94" t="inlineStr">
         <is>
-          <t>8:10PM</t>
+          <t>4:00PM</t>
         </is>
       </c>
       <c r="D65" s="94" t="inlineStr">
@@ -7266,17 +7266,17 @@
       </c>
       <c r="F65" s="94" t="inlineStr">
         <is>
-          <t>U46-GA-1</t>
+          <t>U46-GA-8</t>
         </is>
       </c>
       <c r="G65" s="94" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H65" s="94" t="inlineStr">
         <is>
-          <t>Dr Rahul Modi</t>
+          <t>Sudip Parui</t>
         </is>
       </c>
       <c r="I65" s="94" t="inlineStr">
@@ -7286,7 +7286,7 @@
       </c>
       <c r="J65" s="94" t="inlineStr">
         <is>
-          <t>Ankur Mahante</t>
+          <t>Tanmay Sharma</t>
         </is>
       </c>
     </row>
@@ -7298,17 +7298,17 @@
       </c>
       <c r="B66" s="95" t="inlineStr">
         <is>
-          <t>8:05PM</t>
+          <t>4:00PM</t>
         </is>
       </c>
       <c r="C66" s="95" t="inlineStr">
         <is>
-          <t>8:20PM</t>
+          <t>4:15PM</t>
         </is>
       </c>
       <c r="D66" s="95" t="inlineStr">
         <is>
-          <t>Under 46</t>
+          <t>Under 15</t>
         </is>
       </c>
       <c r="E66" s="95" t="n">
@@ -7316,17 +7316,17 @@
       </c>
       <c r="F66" s="95" t="inlineStr">
         <is>
-          <t>U46-GB-3</t>
+          <t>U15-GB-2</t>
         </is>
       </c>
       <c r="G66" s="95" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H66" s="95" t="inlineStr">
         <is>
-          <t>Nikunj Jhala</t>
+          <t>Viaan Neema</t>
         </is>
       </c>
       <c r="I66" s="95" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="J66" s="95" t="inlineStr">
         <is>
-          <t>Nilesh Bagaria</t>
+          <t>Hridh jhala</t>
         </is>
       </c>
     </row>
@@ -7348,12 +7348,12 @@
       </c>
       <c r="B67" s="94" t="inlineStr">
         <is>
-          <t>8:10PM</t>
+          <t>4:00PM</t>
         </is>
       </c>
       <c r="C67" s="94" t="inlineStr">
         <is>
-          <t>8:25PM</t>
+          <t>4:15PM</t>
         </is>
       </c>
       <c r="D67" s="94" t="inlineStr">
@@ -7366,17 +7366,17 @@
       </c>
       <c r="F67" s="94" t="inlineStr">
         <is>
-          <t>U36-GB-3</t>
+          <t>U36-GA-1</t>
         </is>
       </c>
       <c r="G67" s="94" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H67" s="94" t="inlineStr">
         <is>
-          <t>Amar Parulekar</t>
+          <t>Jashit Bajaj</t>
         </is>
       </c>
       <c r="I67" s="94" t="inlineStr">
@@ -7386,7 +7386,7 @@
       </c>
       <c r="J67" s="94" t="inlineStr">
         <is>
-          <t>Tej</t>
+          <t>Ravi Modi</t>
         </is>
       </c>
     </row>
@@ -7398,17 +7398,17 @@
       </c>
       <c r="B68" s="95" t="inlineStr">
         <is>
-          <t>8:20PM</t>
+          <t>4:15PM</t>
         </is>
       </c>
       <c r="C68" s="95" t="inlineStr">
         <is>
-          <t>8:35PM</t>
+          <t>4:30PM</t>
         </is>
       </c>
       <c r="D68" s="95" t="inlineStr">
         <is>
-          <t>Under 46</t>
+          <t>Under 36</t>
         </is>
       </c>
       <c r="E68" s="95" t="n">
@@ -7416,7 +7416,7 @@
       </c>
       <c r="F68" s="95" t="inlineStr">
         <is>
-          <t>U46-GA-2</t>
+          <t>U36-GB-2</t>
         </is>
       </c>
       <c r="G68" s="95" t="inlineStr">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="H68" s="95" t="inlineStr">
         <is>
-          <t>Dr Rahul Modi</t>
+          <t>Prakshal Shah</t>
         </is>
       </c>
       <c r="I68" s="95" t="inlineStr">
@@ -7436,7 +7436,7 @@
       </c>
       <c r="J68" s="95" t="inlineStr">
         <is>
-          <t>Sudip Parui</t>
+          <t>Tej</t>
         </is>
       </c>
     </row>
@@ -7448,12 +7448,12 @@
       </c>
       <c r="B69" s="94" t="inlineStr">
         <is>
-          <t>8:25PM</t>
+          <t>4:15PM</t>
         </is>
       </c>
       <c r="C69" s="94" t="inlineStr">
         <is>
-          <t>8:40PM</t>
+          <t>4:30PM</t>
         </is>
       </c>
       <c r="D69" s="94" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="F69" s="94" t="inlineStr">
         <is>
-          <t>U46-GA-6</t>
+          <t>U46-GA-2</t>
         </is>
       </c>
       <c r="G69" s="94" t="inlineStr">
@@ -7476,7 +7476,7 @@
       </c>
       <c r="H69" s="94" t="inlineStr">
         <is>
-          <t>Ankur Mahante</t>
+          <t>Dr Rahul Modi</t>
         </is>
       </c>
       <c r="I69" s="94" t="inlineStr">
@@ -7486,7 +7486,7 @@
       </c>
       <c r="J69" s="94" t="inlineStr">
         <is>
-          <t>Tanmay Sharma</t>
+          <t>Sudip Parui</t>
         </is>
       </c>
     </row>
@@ -7498,17 +7498,17 @@
       </c>
       <c r="B70" s="95" t="inlineStr">
         <is>
-          <t>8:35PM</t>
+          <t>4:30PM</t>
         </is>
       </c>
       <c r="C70" s="95" t="inlineStr">
         <is>
-          <t>8:50PM</t>
+          <t>4:45PM</t>
         </is>
       </c>
       <c r="D70" s="95" t="inlineStr">
         <is>
-          <t>Under 46</t>
+          <t>Under 15</t>
         </is>
       </c>
       <c r="E70" s="95" t="n">
@@ -7516,7 +7516,7 @@
       </c>
       <c r="F70" s="95" t="inlineStr">
         <is>
-          <t>U46-GB-4</t>
+          <t>U15-GB-3</t>
         </is>
       </c>
       <c r="G70" s="95" t="inlineStr">
@@ -7526,7 +7526,7 @@
       </c>
       <c r="H70" s="95" t="inlineStr">
         <is>
-          <t>Nikunj Jhala</t>
+          <t>Yash agarwal</t>
         </is>
       </c>
       <c r="I70" s="95" t="inlineStr">
@@ -7536,7 +7536,7 @@
       </c>
       <c r="J70" s="95" t="inlineStr">
         <is>
-          <t>Amit Ranka</t>
+          <t>Hridh jhala</t>
         </is>
       </c>
     </row>
@@ -7548,12 +7548,12 @@
       </c>
       <c r="B71" s="94" t="inlineStr">
         <is>
-          <t>8:40PM</t>
+          <t>4:30PM</t>
         </is>
       </c>
       <c r="C71" s="94" t="inlineStr">
         <is>
-          <t>8:55PM</t>
+          <t>4:45PM</t>
         </is>
       </c>
       <c r="D71" s="94" t="inlineStr">
@@ -7566,7 +7566,7 @@
       </c>
       <c r="F71" s="94" t="inlineStr">
         <is>
-          <t>U46-GA-4</t>
+          <t>U46-GB-3</t>
         </is>
       </c>
       <c r="G71" s="94" t="inlineStr">
@@ -7576,7 +7576,7 @@
       </c>
       <c r="H71" s="94" t="inlineStr">
         <is>
-          <t>Dr Rahul Modi</t>
+          <t>Nikunj Jhala</t>
         </is>
       </c>
       <c r="I71" s="94" t="inlineStr">
@@ -7586,7 +7586,7 @@
       </c>
       <c r="J71" s="94" t="inlineStr">
         <is>
-          <t>Anuj Shah</t>
+          <t>Nilesh Bagaria</t>
         </is>
       </c>
     </row>
@@ -7598,17 +7598,17 @@
       </c>
       <c r="B72" s="95" t="inlineStr">
         <is>
-          <t>8:50PM</t>
+          <t>4:45PM</t>
         </is>
       </c>
       <c r="C72" s="95" t="inlineStr">
         <is>
-          <t>9:05PM</t>
+          <t>5:00PM</t>
         </is>
       </c>
       <c r="D72" s="95" t="inlineStr">
         <is>
-          <t>Under 46</t>
+          <t>Under 36</t>
         </is>
       </c>
       <c r="E72" s="95" t="n">
@@ -7616,7 +7616,7 @@
       </c>
       <c r="F72" s="95" t="inlineStr">
         <is>
-          <t>U46-GA-8</t>
+          <t>U36-GA-3</t>
         </is>
       </c>
       <c r="G72" s="95" t="inlineStr">
@@ -7626,7 +7626,7 @@
       </c>
       <c r="H72" s="95" t="inlineStr">
         <is>
-          <t>Sudip Parui</t>
+          <t>Ravi Modi</t>
         </is>
       </c>
       <c r="I72" s="95" t="inlineStr">
@@ -7636,7 +7636,7 @@
       </c>
       <c r="J72" s="95" t="inlineStr">
         <is>
-          <t>Tanmay Sharma</t>
+          <t>Tapabrata Dutta</t>
         </is>
       </c>
     </row>
@@ -7648,17 +7648,17 @@
       </c>
       <c r="B73" s="94" t="inlineStr">
         <is>
-          <t>8:55PM</t>
+          <t>4:45PM</t>
         </is>
       </c>
       <c r="C73" s="94" t="inlineStr">
         <is>
-          <t>9:10PM</t>
+          <t>5:00PM</t>
         </is>
       </c>
       <c r="D73" s="94" t="inlineStr">
         <is>
-          <t>Under 36</t>
+          <t>Under 46</t>
         </is>
       </c>
       <c r="E73" s="94" t="n">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="F73" s="94" t="inlineStr">
         <is>
-          <t>U36-SF1</t>
+          <t>U46-GA-4</t>
         </is>
       </c>
       <c r="G73" s="94" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="H73" s="94" t="inlineStr">
         <is>
-          <t>Group B 1st</t>
+          <t>Dr Rahul Modi</t>
         </is>
       </c>
       <c r="I73" s="94" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="J73" s="94" t="inlineStr">
         <is>
-          <t>Group A 2nd</t>
+          <t>Anuj Shah</t>
         </is>
       </c>
     </row>
@@ -7698,17 +7698,17 @@
       </c>
       <c r="B74" s="95" t="inlineStr">
         <is>
-          <t>9:05PM</t>
+          <t>5:00PM</t>
         </is>
       </c>
       <c r="C74" s="95" t="inlineStr">
         <is>
-          <t>9:20PM</t>
+          <t>5:15PM</t>
         </is>
       </c>
       <c r="D74" s="95" t="inlineStr">
         <is>
-          <t>Under 36</t>
+          <t>Under 46</t>
         </is>
       </c>
       <c r="E74" s="95" t="n">
@@ -7716,7 +7716,7 @@
       </c>
       <c r="F74" s="95" t="inlineStr">
         <is>
-          <t>U36-SF2</t>
+          <t>U46-GA-5</t>
         </is>
       </c>
       <c r="G74" s="95" t="inlineStr">
@@ -7726,7 +7726,7 @@
       </c>
       <c r="H74" s="95" t="inlineStr">
         <is>
-          <t>Group A 1st</t>
+          <t>Ankur Mahante</t>
         </is>
       </c>
       <c r="I74" s="95" t="inlineStr">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="J74" s="95" t="inlineStr">
         <is>
-          <t>Group B 2nd</t>
+          <t>Sudip Parui</t>
         </is>
       </c>
     </row>
@@ -7748,12 +7748,12 @@
       </c>
       <c r="B75" s="94" t="inlineStr">
         <is>
-          <t>9:10PM</t>
+          <t>5:00PM</t>
         </is>
       </c>
       <c r="C75" s="94" t="inlineStr">
         <is>
-          <t>9:25PM</t>
+          <t>5:15PM</t>
         </is>
       </c>
       <c r="D75" s="94" t="inlineStr">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="F75" s="94" t="inlineStr">
         <is>
-          <t>U46-GA-3</t>
+          <t>U46-GB-10</t>
         </is>
       </c>
       <c r="G75" s="94" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="H75" s="94" t="inlineStr">
         <is>
-          <t>Dr Rahul Modi</t>
+          <t>Nilesh Bagaria</t>
         </is>
       </c>
       <c r="I75" s="94" t="inlineStr">
@@ -7786,7 +7786,7 @@
       </c>
       <c r="J75" s="94" t="inlineStr">
         <is>
-          <t>Tanmay Sharma</t>
+          <t>Amit Ranka</t>
         </is>
       </c>
     </row>
@@ -7798,17 +7798,17 @@
       </c>
       <c r="B76" s="95" t="inlineStr">
         <is>
-          <t>9:20PM</t>
+          <t>5:15PM</t>
         </is>
       </c>
       <c r="C76" s="95" t="inlineStr">
         <is>
-          <t>9:35PM</t>
+          <t>5:30PM</t>
         </is>
       </c>
       <c r="D76" s="95" t="inlineStr">
         <is>
-          <t>Above 46</t>
+          <t>Under 15</t>
         </is>
       </c>
       <c r="E76" s="95" t="n">
@@ -7816,17 +7816,17 @@
       </c>
       <c r="F76" s="95" t="inlineStr">
         <is>
-          <t>A46-QF4</t>
+          <t>U15-GA-2</t>
         </is>
       </c>
       <c r="G76" s="95" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H76" s="95" t="inlineStr">
         <is>
-          <t>Mukul Joshi</t>
+          <t>Shaurya Tripathi</t>
         </is>
       </c>
       <c r="I76" s="95" t="inlineStr">
@@ -7836,7 +7836,7 @@
       </c>
       <c r="J76" s="95" t="inlineStr">
         <is>
-          <t>Sushil Dashpute</t>
+          <t>Aadit Joshi</t>
         </is>
       </c>
     </row>
@@ -7848,17 +7848,17 @@
       </c>
       <c r="B77" s="94" t="inlineStr">
         <is>
-          <t>9:25PM</t>
+          <t>5:15PM</t>
         </is>
       </c>
       <c r="C77" s="94" t="inlineStr">
         <is>
-          <t>9:40PM</t>
+          <t>5:30PM</t>
         </is>
       </c>
       <c r="D77" s="94" t="inlineStr">
         <is>
-          <t>Under 36</t>
+          <t>Under 46</t>
         </is>
       </c>
       <c r="E77" s="94" t="n">
@@ -7866,17 +7866,17 @@
       </c>
       <c r="F77" s="94" t="inlineStr">
         <is>
-          <t>U36-FINAL</t>
+          <t>U46-GA-3</t>
         </is>
       </c>
       <c r="G77" s="94" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H77" s="94" t="inlineStr">
         <is>
-          <t>Winner SF1</t>
+          <t>Dr Rahul Modi</t>
         </is>
       </c>
       <c r="I77" s="94" t="inlineStr">
@@ -7886,7 +7886,7 @@
       </c>
       <c r="J77" s="94" t="inlineStr">
         <is>
-          <t>Winner SF2</t>
+          <t>Tanmay Sharma</t>
         </is>
       </c>
     </row>
@@ -7898,17 +7898,17 @@
       </c>
       <c r="B78" s="95" t="inlineStr">
         <is>
-          <t>9:35PM</t>
+          <t>5:30PM</t>
         </is>
       </c>
       <c r="C78" s="95" t="inlineStr">
         <is>
-          <t>9:50PM</t>
+          <t>5:45PM</t>
         </is>
       </c>
       <c r="D78" s="95" t="inlineStr">
         <is>
-          <t>Above 46</t>
+          <t>Under 36</t>
         </is>
       </c>
       <c r="E78" s="95" t="n">
@@ -7916,17 +7916,17 @@
       </c>
       <c r="F78" s="95" t="inlineStr">
         <is>
-          <t>A46-SF2</t>
+          <t>U36-GB-3</t>
         </is>
       </c>
       <c r="G78" s="95" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H78" s="95" t="inlineStr">
         <is>
-          <t>Winner QF3</t>
+          <t>Amar Parulekar</t>
         </is>
       </c>
       <c r="I78" s="95" t="inlineStr">
@@ -7936,7 +7936,7 @@
       </c>
       <c r="J78" s="95" t="inlineStr">
         <is>
-          <t>Winner QF4</t>
+          <t>Tej</t>
         </is>
       </c>
     </row>
@@ -7948,12 +7948,12 @@
       </c>
       <c r="B79" s="94" t="inlineStr">
         <is>
-          <t>9:40PM</t>
+          <t>5:30PM</t>
         </is>
       </c>
       <c r="C79" s="94" t="inlineStr">
         <is>
-          <t>9:55PM</t>
+          <t>5:45PM</t>
         </is>
       </c>
       <c r="D79" s="94" t="inlineStr">
@@ -7966,17 +7966,17 @@
       </c>
       <c r="F79" s="94" t="inlineStr">
         <is>
-          <t>U46-GA-10</t>
+          <t>U46-GA-7</t>
         </is>
       </c>
       <c r="G79" s="94" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H79" s="94" t="inlineStr">
         <is>
-          <t>Tanmay Sharma</t>
+          <t>Ankur Mahante</t>
         </is>
       </c>
       <c r="I79" s="94" t="inlineStr">
@@ -7993,22 +7993,22 @@
     <row r="80">
       <c r="A80" s="95" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="B80" s="95" t="inlineStr">
         <is>
-          <t>8:00AM</t>
+          <t>5:45PM</t>
         </is>
       </c>
       <c r="C80" s="95" t="inlineStr">
         <is>
-          <t>8:15AM</t>
+          <t>6:00PM</t>
         </is>
       </c>
       <c r="D80" s="95" t="inlineStr">
         <is>
-          <t>Under 46</t>
+          <t>Under 36</t>
         </is>
       </c>
       <c r="E80" s="95" t="n">
@@ -8016,17 +8016,17 @@
       </c>
       <c r="F80" s="95" t="inlineStr">
         <is>
-          <t>U46-GB-8</t>
+          <t>U36-SF1</t>
         </is>
       </c>
       <c r="G80" s="95" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H80" s="95" t="inlineStr">
         <is>
-          <t>Vinit Padia</t>
+          <t>Group B 1st</t>
         </is>
       </c>
       <c r="I80" s="95" t="inlineStr">
@@ -8036,24 +8036,24 @@
       </c>
       <c r="J80" s="95" t="inlineStr">
         <is>
-          <t>Nilesh Bagaria</t>
+          <t>Group A 2nd</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="94" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="B81" s="94" t="inlineStr">
         <is>
-          <t>8:25AM</t>
+          <t>5:45PM</t>
         </is>
       </c>
       <c r="C81" s="94" t="inlineStr">
         <is>
-          <t>8:40AM</t>
+          <t>6:00PM</t>
         </is>
       </c>
       <c r="D81" s="94" t="inlineStr">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="F81" s="94" t="inlineStr">
         <is>
-          <t>U46-GB-9</t>
+          <t>U46-GB-4</t>
         </is>
       </c>
       <c r="G81" s="94" t="inlineStr">
@@ -8076,7 +8076,7 @@
       </c>
       <c r="H81" s="94" t="inlineStr">
         <is>
-          <t>Vinit Padia</t>
+          <t>Nikunj Jhala</t>
         </is>
       </c>
       <c r="I81" s="94" t="inlineStr">
@@ -8093,17 +8093,17 @@
     <row r="82">
       <c r="A82" s="95" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="B82" s="95" t="inlineStr">
         <is>
-          <t>8:50AM</t>
+          <t>6:00PM</t>
         </is>
       </c>
       <c r="C82" s="95" t="inlineStr">
         <is>
-          <t>9:05AM</t>
+          <t>6:15PM</t>
         </is>
       </c>
       <c r="D82" s="95" t="inlineStr">
@@ -8116,17 +8116,17 @@
       </c>
       <c r="F82" s="95" t="inlineStr">
         <is>
-          <t>U26-8</t>
+          <t>U26-3</t>
         </is>
       </c>
       <c r="G82" s="95" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H82" s="95" t="inlineStr">
         <is>
-          <t>Hryday Goyal</t>
+          <t>Yuvraj jain</t>
         </is>
       </c>
       <c r="I82" s="95" t="inlineStr">
@@ -8143,22 +8143,22 @@
     <row r="83">
       <c r="A83" s="94" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="B83" s="94" t="inlineStr">
         <is>
-          <t>8:50AM</t>
+          <t>6:00PM</t>
         </is>
       </c>
       <c r="C83" s="94" t="inlineStr">
         <is>
-          <t>9:05AM</t>
+          <t>6:15PM</t>
         </is>
       </c>
       <c r="D83" s="94" t="inlineStr">
         <is>
-          <t>Under 46</t>
+          <t>Under 36</t>
         </is>
       </c>
       <c r="E83" s="94" t="n">
@@ -8166,17 +8166,17 @@
       </c>
       <c r="F83" s="94" t="inlineStr">
         <is>
-          <t>U46-GB-2</t>
+          <t>U36-SF2</t>
         </is>
       </c>
       <c r="G83" s="94" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H83" s="94" t="inlineStr">
         <is>
-          <t>Nikunj Jhala</t>
+          <t>Group A 1st</t>
         </is>
       </c>
       <c r="I83" s="94" t="inlineStr">
@@ -8186,29 +8186,29 @@
       </c>
       <c r="J83" s="94" t="inlineStr">
         <is>
-          <t>Vinit Padia</t>
+          <t>Group B 2nd</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="95" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="B84" s="95" t="inlineStr">
         <is>
-          <t>9:10AM</t>
+          <t>6:15PM</t>
         </is>
       </c>
       <c r="C84" s="95" t="inlineStr">
         <is>
-          <t>9:25AM</t>
+          <t>6:30PM</t>
         </is>
       </c>
       <c r="D84" s="95" t="inlineStr">
         <is>
-          <t>Under 15</t>
+          <t>Under 26</t>
         </is>
       </c>
       <c r="E84" s="95" t="n">
@@ -8216,7 +8216,7 @@
       </c>
       <c r="F84" s="95" t="inlineStr">
         <is>
-          <t>U15-GA-2</t>
+          <t>U26-5</t>
         </is>
       </c>
       <c r="G84" s="95" t="inlineStr">
@@ -8226,7 +8226,7 @@
       </c>
       <c r="H84" s="95" t="inlineStr">
         <is>
-          <t>Shaurya Tripathi</t>
+          <t>Aaditya Kumar</t>
         </is>
       </c>
       <c r="I84" s="95" t="inlineStr">
@@ -8236,29 +8236,29 @@
       </c>
       <c r="J84" s="95" t="inlineStr">
         <is>
-          <t>Aadit Joshi</t>
+          <t>Hryday Goyal</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="94" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="B85" s="94" t="inlineStr">
         <is>
-          <t>9:20AM</t>
+          <t>6:15PM</t>
         </is>
       </c>
       <c r="C85" s="94" t="inlineStr">
         <is>
-          <t>9:35AM</t>
+          <t>6:30PM</t>
         </is>
       </c>
       <c r="D85" s="94" t="inlineStr">
         <is>
-          <t>Under 26</t>
+          <t>Under 36</t>
         </is>
       </c>
       <c r="E85" s="94" t="n">
@@ -8266,7 +8266,7 @@
       </c>
       <c r="F85" s="94" t="inlineStr">
         <is>
-          <t>U26-3</t>
+          <t>U36-FINAL</t>
         </is>
       </c>
       <c r="G85" s="94" t="inlineStr">
@@ -8276,7 +8276,7 @@
       </c>
       <c r="H85" s="94" t="inlineStr">
         <is>
-          <t>Yuvraj jain</t>
+          <t>Winner SF1</t>
         </is>
       </c>
       <c r="I85" s="94" t="inlineStr">
@@ -8286,29 +8286,29 @@
       </c>
       <c r="J85" s="94" t="inlineStr">
         <is>
-          <t>Pranit Shriyan</t>
+          <t>Winner SF2</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="95" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="B86" s="95" t="inlineStr">
         <is>
-          <t>9:35AM</t>
+          <t>6:30PM</t>
         </is>
       </c>
       <c r="C86" s="95" t="inlineStr">
         <is>
-          <t>9:50AM</t>
+          <t>6:45PM</t>
         </is>
       </c>
       <c r="D86" s="95" t="inlineStr">
         <is>
-          <t>Under 15</t>
+          <t>Under 46</t>
         </is>
       </c>
       <c r="E86" s="95" t="n">
@@ -8316,7 +8316,7 @@
       </c>
       <c r="F86" s="95" t="inlineStr">
         <is>
-          <t>U15-GA-3</t>
+          <t>U46-GA-1</t>
         </is>
       </c>
       <c r="G86" s="95" t="inlineStr">
@@ -8326,7 +8326,7 @@
       </c>
       <c r="H86" s="95" t="inlineStr">
         <is>
-          <t>Parth yadav</t>
+          <t>Dr Rahul Modi</t>
         </is>
       </c>
       <c r="I86" s="95" t="inlineStr">
@@ -8336,29 +8336,29 @@
       </c>
       <c r="J86" s="95" t="inlineStr">
         <is>
-          <t>Aadit Joshi</t>
+          <t>Ankur Mahante</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="94" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="B87" s="94" t="inlineStr">
         <is>
-          <t>9:50AM</t>
+          <t>6:30PM</t>
         </is>
       </c>
       <c r="C87" s="94" t="inlineStr">
         <is>
-          <t>10:05AM</t>
+          <t>6:45PM</t>
         </is>
       </c>
       <c r="D87" s="94" t="inlineStr">
         <is>
-          <t>Under 15</t>
+          <t>Under 46</t>
         </is>
       </c>
       <c r="E87" s="94" t="n">
@@ -8366,7 +8366,7 @@
       </c>
       <c r="F87" s="94" t="inlineStr">
         <is>
-          <t>U15-SF1</t>
+          <t>U46-GA-10</t>
         </is>
       </c>
       <c r="G87" s="94" t="inlineStr">
@@ -8376,7 +8376,7 @@
       </c>
       <c r="H87" s="94" t="inlineStr">
         <is>
-          <t>Group B 1st</t>
+          <t>Tanmay Sharma</t>
         </is>
       </c>
       <c r="I87" s="94" t="inlineStr">
@@ -8386,29 +8386,29 @@
       </c>
       <c r="J87" s="94" t="inlineStr">
         <is>
-          <t>Group A 2nd</t>
+          <t>Anuj Shah</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="95" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="B88" s="95" t="inlineStr">
         <is>
-          <t>9:50AM</t>
+          <t>6:45PM</t>
         </is>
       </c>
       <c r="C88" s="95" t="inlineStr">
         <is>
-          <t>10:05AM</t>
+          <t>7:00PM</t>
         </is>
       </c>
       <c r="D88" s="95" t="inlineStr">
         <is>
-          <t>Under 26</t>
+          <t>Under 15</t>
         </is>
       </c>
       <c r="E88" s="95" t="n">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="F88" s="95" t="inlineStr">
         <is>
-          <t>U26-4</t>
+          <t>U15-GA-3</t>
         </is>
       </c>
       <c r="G88" s="95" t="inlineStr">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="H88" s="95" t="inlineStr">
         <is>
-          <t>Yuvraj jain</t>
+          <t>Parth yadav</t>
         </is>
       </c>
       <c r="I88" s="95" t="inlineStr">
@@ -8436,29 +8436,29 @@
       </c>
       <c r="J88" s="95" t="inlineStr">
         <is>
-          <t>Rahul Garg</t>
+          <t>Aadit Joshi</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="94" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="B89" s="94" t="inlineStr">
         <is>
-          <t>10:05AM</t>
+          <t>6:45PM</t>
         </is>
       </c>
       <c r="C89" s="94" t="inlineStr">
         <is>
-          <t>10:20AM</t>
+          <t>7:00PM</t>
         </is>
       </c>
       <c r="D89" s="94" t="inlineStr">
         <is>
-          <t>Under 15</t>
+          <t>Under 26</t>
         </is>
       </c>
       <c r="E89" s="94" t="n">
@@ -8466,17 +8466,17 @@
       </c>
       <c r="F89" s="94" t="inlineStr">
         <is>
-          <t>U15-SF2</t>
+          <t>U26-4</t>
         </is>
       </c>
       <c r="G89" s="94" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H89" s="94" t="inlineStr">
         <is>
-          <t>Group A 1st</t>
+          <t>Yuvraj jain</t>
         </is>
       </c>
       <c r="I89" s="94" t="inlineStr">
@@ -8486,29 +8486,29 @@
       </c>
       <c r="J89" s="94" t="inlineStr">
         <is>
-          <t>Group B 2nd</t>
+          <t>Rahul Garg</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="95" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="B90" s="95" t="inlineStr">
         <is>
-          <t>10:10AM</t>
+          <t>7:00PM</t>
         </is>
       </c>
       <c r="C90" s="95" t="inlineStr">
         <is>
-          <t>10:25AM</t>
+          <t>7:15PM</t>
         </is>
       </c>
       <c r="D90" s="95" t="inlineStr">
         <is>
-          <t>Under 26</t>
+          <t>Under 46</t>
         </is>
       </c>
       <c r="E90" s="95" t="n">
@@ -8516,17 +8516,17 @@
       </c>
       <c r="F90" s="95" t="inlineStr">
         <is>
-          <t>U26-6</t>
+          <t>U46-GA-6</t>
         </is>
       </c>
       <c r="G90" s="95" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H90" s="95" t="inlineStr">
         <is>
-          <t>Aaditya Kumar</t>
+          <t>Ankur Mahante</t>
         </is>
       </c>
       <c r="I90" s="95" t="inlineStr">
@@ -8536,29 +8536,29 @@
       </c>
       <c r="J90" s="95" t="inlineStr">
         <is>
-          <t>Pranit Shriyan</t>
+          <t>Tanmay Sharma</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="94" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="B91" s="94" t="inlineStr">
         <is>
-          <t>10:20AM</t>
+          <t>7:00PM</t>
         </is>
       </c>
       <c r="C91" s="94" t="inlineStr">
         <is>
-          <t>10:35AM</t>
+          <t>7:15PM</t>
         </is>
       </c>
       <c r="D91" s="94" t="inlineStr">
         <is>
-          <t>Under 26</t>
+          <t>Under 46</t>
         </is>
       </c>
       <c r="E91" s="94" t="n">
@@ -8566,17 +8566,17 @@
       </c>
       <c r="F91" s="94" t="inlineStr">
         <is>
-          <t>U26-9</t>
+          <t>U46-GB-9</t>
         </is>
       </c>
       <c r="G91" s="94" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H91" s="94" t="inlineStr">
         <is>
-          <t>Hryday Goyal</t>
+          <t>Vinit Padia</t>
         </is>
       </c>
       <c r="I91" s="94" t="inlineStr">
@@ -8586,24 +8586,24 @@
       </c>
       <c r="J91" s="94" t="inlineStr">
         <is>
-          <t>Rahul Garg</t>
+          <t>Amit Ranka</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="95" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="B92" s="95" t="inlineStr">
         <is>
-          <t>10:25AM</t>
+          <t>7:15PM</t>
         </is>
       </c>
       <c r="C92" s="95" t="inlineStr">
         <is>
-          <t>10:40AM</t>
+          <t>7:30PM</t>
         </is>
       </c>
       <c r="D92" s="95" t="inlineStr">
@@ -8616,17 +8616,17 @@
       </c>
       <c r="F92" s="95" t="inlineStr">
         <is>
-          <t>U15-FINAL</t>
+          <t>U15-SF1</t>
         </is>
       </c>
       <c r="G92" s="95" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H92" s="95" t="inlineStr">
         <is>
-          <t>Winner SF1</t>
+          <t>Group B 1st</t>
         </is>
       </c>
       <c r="I92" s="95" t="inlineStr">
@@ -8636,29 +8636,29 @@
       </c>
       <c r="J92" s="95" t="inlineStr">
         <is>
-          <t>Winner SF2</t>
+          <t>Group A 2nd</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="94" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="B93" s="94" t="inlineStr">
         <is>
-          <t>10:35AM</t>
+          <t>7:15PM</t>
         </is>
       </c>
       <c r="C93" s="94" t="inlineStr">
         <is>
-          <t>10:50AM</t>
+          <t>7:30PM</t>
         </is>
       </c>
       <c r="D93" s="94" t="inlineStr">
         <is>
-          <t>Under 26</t>
+          <t>Under 15</t>
         </is>
       </c>
       <c r="E93" s="94" t="n">
@@ -8666,17 +8666,17 @@
       </c>
       <c r="F93" s="94" t="inlineStr">
         <is>
-          <t>U26-1</t>
+          <t>U15-SF2</t>
         </is>
       </c>
       <c r="G93" s="94" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H93" s="94" t="inlineStr">
         <is>
-          <t>Yuvraj jain</t>
+          <t>Group A 1st</t>
         </is>
       </c>
       <c r="I93" s="94" t="inlineStr">
@@ -8686,29 +8686,29 @@
       </c>
       <c r="J93" s="94" t="inlineStr">
         <is>
-          <t>Aaditya Kumar</t>
+          <t>Group B 2nd</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="95" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="B94" s="95" t="inlineStr">
         <is>
-          <t>10:40AM</t>
+          <t>7:30PM</t>
         </is>
       </c>
       <c r="C94" s="95" t="inlineStr">
         <is>
-          <t>10:55AM</t>
+          <t>7:45PM</t>
         </is>
       </c>
       <c r="D94" s="95" t="inlineStr">
         <is>
-          <t>Under 26</t>
+          <t>Under 15</t>
         </is>
       </c>
       <c r="E94" s="95" t="n">
@@ -8716,7 +8716,7 @@
       </c>
       <c r="F94" s="95" t="inlineStr">
         <is>
-          <t>U26-10</t>
+          <t>U15-FINAL</t>
         </is>
       </c>
       <c r="G94" s="95" t="inlineStr">
@@ -8726,7 +8726,7 @@
       </c>
       <c r="H94" s="95" t="inlineStr">
         <is>
-          <t>Pranit Shriyan</t>
+          <t>Winner SF1</t>
         </is>
       </c>
       <c r="I94" s="95" t="inlineStr">
@@ -8736,24 +8736,24 @@
       </c>
       <c r="J94" s="95" t="inlineStr">
         <is>
-          <t>Rahul Garg</t>
+          <t>Winner SF2</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="94" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="B95" s="94" t="inlineStr">
         <is>
-          <t>10:55AM</t>
+          <t>7:30PM</t>
         </is>
       </c>
       <c r="C95" s="94" t="inlineStr">
         <is>
-          <t>11:10AM</t>
+          <t>7:45PM</t>
         </is>
       </c>
       <c r="D95" s="94" t="inlineStr">
@@ -8766,17 +8766,17 @@
       </c>
       <c r="F95" s="94" t="inlineStr">
         <is>
-          <t>U26-5</t>
+          <t>U26-9</t>
         </is>
       </c>
       <c r="G95" s="94" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H95" s="94" t="inlineStr">
         <is>
-          <t>Aaditya Kumar</t>
+          <t>Hryday Goyal</t>
         </is>
       </c>
       <c r="I95" s="94" t="inlineStr">
@@ -8786,29 +8786,29 @@
       </c>
       <c r="J95" s="94" t="inlineStr">
         <is>
-          <t>Hryday Goyal</t>
+          <t>Rahul Garg</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="95" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="B96" s="95" t="inlineStr">
         <is>
-          <t>11:05AM</t>
+          <t>7:45PM</t>
         </is>
       </c>
       <c r="C96" s="95" t="inlineStr">
         <is>
-          <t>11:20AM</t>
+          <t>8:00PM</t>
         </is>
       </c>
       <c r="D96" s="95" t="inlineStr">
         <is>
-          <t>Under 46</t>
+          <t>Under 26</t>
         </is>
       </c>
       <c r="E96" s="95" t="n">
@@ -8816,17 +8816,17 @@
       </c>
       <c r="F96" s="95" t="inlineStr">
         <is>
-          <t>U46-GB-1</t>
+          <t>U26-6</t>
         </is>
       </c>
       <c r="G96" s="95" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H96" s="95" t="inlineStr">
         <is>
-          <t>Nikunj Jhala</t>
+          <t>Aaditya Kumar</t>
         </is>
       </c>
       <c r="I96" s="95" t="inlineStr">
@@ -8836,29 +8836,29 @@
       </c>
       <c r="J96" s="95" t="inlineStr">
         <is>
-          <t>Piyush Makharia</t>
+          <t>Pranit Shriyan</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="94" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="B97" s="94" t="inlineStr">
         <is>
-          <t>11:20AM</t>
+          <t>7:45PM</t>
         </is>
       </c>
       <c r="C97" s="94" t="inlineStr">
         <is>
-          <t>11:35AM</t>
+          <t>8:00PM</t>
         </is>
       </c>
       <c r="D97" s="94" t="inlineStr">
         <is>
-          <t>Under 26</t>
+          <t>Under 46</t>
         </is>
       </c>
       <c r="E97" s="94" t="n">
@@ -8866,7 +8866,7 @@
       </c>
       <c r="F97" s="94" t="inlineStr">
         <is>
-          <t>U26-7</t>
+          <t>U46-GB-2</t>
         </is>
       </c>
       <c r="G97" s="94" t="inlineStr">
@@ -8876,7 +8876,7 @@
       </c>
       <c r="H97" s="94" t="inlineStr">
         <is>
-          <t>Aaditya Kumar</t>
+          <t>Nikunj Jhala</t>
         </is>
       </c>
       <c r="I97" s="94" t="inlineStr">
@@ -8886,29 +8886,29 @@
       </c>
       <c r="J97" s="94" t="inlineStr">
         <is>
-          <t>Rahul Garg</t>
+          <t>Vinit Padia</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="95" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="B98" s="95" t="inlineStr">
         <is>
-          <t>11:25AM</t>
+          <t>8:10PM</t>
         </is>
       </c>
       <c r="C98" s="95" t="inlineStr">
         <is>
-          <t>11:40AM</t>
+          <t>8:25PM</t>
         </is>
       </c>
       <c r="D98" s="95" t="inlineStr">
         <is>
-          <t>Under 46</t>
+          <t>Under 26</t>
         </is>
       </c>
       <c r="E98" s="95" t="n">
@@ -8916,17 +8916,17 @@
       </c>
       <c r="F98" s="95" t="inlineStr">
         <is>
-          <t>U46-GB-6</t>
+          <t>U26-1</t>
         </is>
       </c>
       <c r="G98" s="95" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H98" s="95" t="inlineStr">
         <is>
-          <t>Piyush Makharia</t>
+          <t>Yuvraj jain</t>
         </is>
       </c>
       <c r="I98" s="95" t="inlineStr">
@@ -8936,24 +8936,24 @@
       </c>
       <c r="J98" s="95" t="inlineStr">
         <is>
-          <t>Nilesh Bagaria</t>
+          <t>Aaditya Kumar</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="94" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="B99" s="94" t="inlineStr">
         <is>
-          <t>11:35AM</t>
+          <t>8:20PM</t>
         </is>
       </c>
       <c r="C99" s="94" t="inlineStr">
         <is>
-          <t>11:50AM</t>
+          <t>8:35PM</t>
         </is>
       </c>
       <c r="D99" s="94" t="inlineStr">
@@ -8966,17 +8966,17 @@
       </c>
       <c r="F99" s="94" t="inlineStr">
         <is>
-          <t>U26-FINAL</t>
+          <t>U26-10</t>
         </is>
       </c>
       <c r="G99" s="94" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H99" s="94" t="inlineStr">
         <is>
-          <t>Pool 1st</t>
+          <t>Pranit Shriyan</t>
         </is>
       </c>
       <c r="I99" s="94" t="inlineStr">
@@ -8986,24 +8986,24 @@
       </c>
       <c r="J99" s="94" t="inlineStr">
         <is>
-          <t>Pool 2nd</t>
+          <t>Rahul Garg</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="95" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="B100" s="95" t="inlineStr">
         <is>
-          <t>11:50AM</t>
+          <t>8:30PM</t>
         </is>
       </c>
       <c r="C100" s="95" t="inlineStr">
         <is>
-          <t>12:05PM</t>
+          <t>8:45PM</t>
         </is>
       </c>
       <c r="D100" s="95" t="inlineStr">
@@ -9016,7 +9016,7 @@
       </c>
       <c r="F100" s="95" t="inlineStr">
         <is>
-          <t>U46-GB-5</t>
+          <t>U46-GB-1</t>
         </is>
       </c>
       <c r="G100" s="95" t="inlineStr">
@@ -9026,39 +9026,39 @@
       </c>
       <c r="H100" s="95" t="inlineStr">
         <is>
+          <t>Nikunj Jhala</t>
+        </is>
+      </c>
+      <c r="I100" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J100" s="95" t="inlineStr">
+        <is>
           <t>Piyush Makharia</t>
-        </is>
-      </c>
-      <c r="I100" s="95" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J100" s="95" t="inlineStr">
-        <is>
-          <t>Vinit Padia</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="94" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="B101" s="94" t="inlineStr">
         <is>
-          <t>3:00PM</t>
+          <t>8:55PM</t>
         </is>
       </c>
       <c r="C101" s="94" t="inlineStr">
         <is>
-          <t>3:15PM</t>
+          <t>9:10PM</t>
         </is>
       </c>
       <c r="D101" s="94" t="inlineStr">
         <is>
-          <t>Above 46</t>
+          <t>Under 46</t>
         </is>
       </c>
       <c r="E101" s="94" t="n">
@@ -9066,7 +9066,7 @@
       </c>
       <c r="F101" s="94" t="inlineStr">
         <is>
-          <t>A46-R1</t>
+          <t>U46-GB-6</t>
         </is>
       </c>
       <c r="G101" s="94" t="inlineStr">
@@ -9076,7 +9076,7 @@
       </c>
       <c r="H101" s="94" t="inlineStr">
         <is>
-          <t>Adil Khan</t>
+          <t>Piyush Makharia</t>
         </is>
       </c>
       <c r="I101" s="94" t="inlineStr">
@@ -9086,29 +9086,29 @@
       </c>
       <c r="J101" s="94" t="inlineStr">
         <is>
-          <t>Ajit nair</t>
+          <t>Nilesh Bagaria</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="95" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="B102" s="95" t="inlineStr">
         <is>
-          <t>3:00PM</t>
+          <t>9:00PM</t>
         </is>
       </c>
       <c r="C102" s="95" t="inlineStr">
         <is>
-          <t>3:15PM</t>
+          <t>9:15PM</t>
         </is>
       </c>
       <c r="D102" s="95" t="inlineStr">
         <is>
-          <t>Under 46</t>
+          <t>Under 26</t>
         </is>
       </c>
       <c r="E102" s="95" t="n">
@@ -9116,7 +9116,7 @@
       </c>
       <c r="F102" s="95" t="inlineStr">
         <is>
-          <t>U46-GB-7</t>
+          <t>U26-7</t>
         </is>
       </c>
       <c r="G102" s="95" t="inlineStr">
@@ -9126,7 +9126,7 @@
       </c>
       <c r="H102" s="95" t="inlineStr">
         <is>
-          <t>Piyush Makharia</t>
+          <t>Aaditya Kumar</t>
         </is>
       </c>
       <c r="I102" s="95" t="inlineStr">
@@ -9136,29 +9136,29 @@
       </c>
       <c r="J102" s="95" t="inlineStr">
         <is>
-          <t>Amit Ranka</t>
+          <t>Rahul Garg</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="94" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="B103" s="94" t="inlineStr">
         <is>
-          <t>3:15PM</t>
+          <t>9:15PM</t>
         </is>
       </c>
       <c r="C103" s="94" t="inlineStr">
         <is>
-          <t>3:30PM</t>
+          <t>9:30PM</t>
         </is>
       </c>
       <c r="D103" s="94" t="inlineStr">
         <is>
-          <t>Above 46</t>
+          <t>Under 26</t>
         </is>
       </c>
       <c r="E103" s="94" t="n">
@@ -9166,7 +9166,7 @@
       </c>
       <c r="F103" s="94" t="inlineStr">
         <is>
-          <t>A46-QF1</t>
+          <t>U26-FINAL</t>
         </is>
       </c>
       <c r="G103" s="94" t="inlineStr">
@@ -9176,7 +9176,7 @@
       </c>
       <c r="H103" s="94" t="inlineStr">
         <is>
-          <t>Winner R1</t>
+          <t>Pool 1st</t>
         </is>
       </c>
       <c r="I103" s="94" t="inlineStr">
@@ -9186,24 +9186,24 @@
       </c>
       <c r="J103" s="94" t="inlineStr">
         <is>
-          <t>Sanjay Kumar</t>
+          <t>Pool 2nd</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="95" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="B104" s="95" t="inlineStr">
         <is>
-          <t>3:15PM</t>
+          <t>9:15PM</t>
         </is>
       </c>
       <c r="C104" s="95" t="inlineStr">
         <is>
-          <t>3:30PM</t>
+          <t>9:30PM</t>
         </is>
       </c>
       <c r="D104" s="95" t="inlineStr">
@@ -9216,7 +9216,7 @@
       </c>
       <c r="F104" s="95" t="inlineStr">
         <is>
-          <t>U46-SF1</t>
+          <t>U46-GB-5</t>
         </is>
       </c>
       <c r="G104" s="95" t="inlineStr">
@@ -9226,7 +9226,7 @@
       </c>
       <c r="H104" s="95" t="inlineStr">
         <is>
-          <t>Group B 1st</t>
+          <t>Piyush Makharia</t>
         </is>
       </c>
       <c r="I104" s="95" t="inlineStr">
@@ -9236,29 +9236,29 @@
       </c>
       <c r="J104" s="95" t="inlineStr">
         <is>
-          <t>Group A 2nd</t>
+          <t>Vinit Padia</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="94" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="B105" s="94" t="inlineStr">
         <is>
-          <t>3:30PM</t>
+          <t>9:40PM</t>
         </is>
       </c>
       <c r="C105" s="94" t="inlineStr">
         <is>
-          <t>3:45PM</t>
+          <t>9:55PM</t>
         </is>
       </c>
       <c r="D105" s="94" t="inlineStr">
         <is>
-          <t>Above 46</t>
+          <t>Under 46</t>
         </is>
       </c>
       <c r="E105" s="94" t="n">
@@ -9266,7 +9266,7 @@
       </c>
       <c r="F105" s="94" t="inlineStr">
         <is>
-          <t>A46-SF1</t>
+          <t>U46-GB-7</t>
         </is>
       </c>
       <c r="G105" s="94" t="inlineStr">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="H105" s="94" t="inlineStr">
         <is>
-          <t>Winner QF1</t>
+          <t>Piyush Makharia</t>
         </is>
       </c>
       <c r="I105" s="94" t="inlineStr">
@@ -9286,24 +9286,24 @@
       </c>
       <c r="J105" s="94" t="inlineStr">
         <is>
-          <t>Winner QF2</t>
+          <t>Amit Ranka</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="95" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="B106" s="95" t="inlineStr">
         <is>
-          <t>3:30PM</t>
+          <t>9:55PM</t>
         </is>
       </c>
       <c r="C106" s="95" t="inlineStr">
         <is>
-          <t>3:45PM</t>
+          <t>10:10PM</t>
         </is>
       </c>
       <c r="D106" s="95" t="inlineStr">
@@ -9316,17 +9316,17 @@
       </c>
       <c r="F106" s="95" t="inlineStr">
         <is>
-          <t>U46-SF2</t>
+          <t>U46-SF1</t>
         </is>
       </c>
       <c r="G106" s="95" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H106" s="95" t="inlineStr">
         <is>
-          <t>Group A 1st</t>
+          <t>Group B 1st</t>
         </is>
       </c>
       <c r="I106" s="95" t="inlineStr">
@@ -9336,29 +9336,29 @@
       </c>
       <c r="J106" s="95" t="inlineStr">
         <is>
-          <t>Group B 2nd</t>
+          <t>Group A 2nd</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="94" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="B107" s="94" t="inlineStr">
         <is>
-          <t>3:45PM</t>
+          <t>9:55PM</t>
         </is>
       </c>
       <c r="C107" s="94" t="inlineStr">
         <is>
-          <t>4:00PM</t>
+          <t>10:10PM</t>
         </is>
       </c>
       <c r="D107" s="94" t="inlineStr">
         <is>
-          <t>Above 46</t>
+          <t>Under 46</t>
         </is>
       </c>
       <c r="E107" s="94" t="n">
@@ -9366,17 +9366,17 @@
       </c>
       <c r="F107" s="94" t="inlineStr">
         <is>
-          <t>A46-FINAL</t>
+          <t>U46-SF2</t>
         </is>
       </c>
       <c r="G107" s="94" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H107" s="94" t="inlineStr">
         <is>
-          <t>Winner SF1</t>
+          <t>Group A 1st</t>
         </is>
       </c>
       <c r="I107" s="94" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="J107" s="94" t="inlineStr">
         <is>
-          <t>Winner SF2</t>
+          <t>Group B 2nd</t>
         </is>
       </c>
     </row>
@@ -9398,12 +9398,12 @@
       </c>
       <c r="B108" s="95" t="inlineStr">
         <is>
-          <t>3:45PM</t>
+          <t>8:00AM</t>
         </is>
       </c>
       <c r="C108" s="95" t="inlineStr">
         <is>
-          <t>4:00PM</t>
+          <t>8:15AM</t>
         </is>
       </c>
       <c r="D108" s="95" t="inlineStr">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="G108" s="95" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H108" s="95" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="B20" s="94" t="inlineStr">
         <is>
-          <t>9:05AM</t>
+          <t>9:00AM</t>
         </is>
       </c>
       <c r="C20" s="94" t="inlineStr">
         <is>
-          <t>9:20AM</t>
+          <t>9:15AM</t>
         </is>
       </c>
       <c r="D20" s="94" t="inlineStr">
@@ -9773,17 +9773,17 @@
       </c>
       <c r="F20" s="94" t="inlineStr">
         <is>
-          <t>QF3</t>
+          <t>QF2</t>
         </is>
       </c>
       <c r="G20" s="94" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H20" s="94" t="inlineStr">
         <is>
-          <t>Mayank Aggarwal &amp; Sudip Parui</t>
+          <t>Nilesh Bagaria &amp; Parthiv</t>
         </is>
       </c>
       <c r="I20" s="94" t="inlineStr">
@@ -9793,7 +9793,7 @@
       </c>
       <c r="J20" s="94" t="inlineStr">
         <is>
-          <t>Nidhi Sharma &amp; Tushar</t>
+          <t>Rahul Garg &amp; Nilesh Mhatre</t>
         </is>
       </c>
     </row>
@@ -9805,12 +9805,12 @@
       </c>
       <c r="B21" s="95" t="inlineStr">
         <is>
-          <t>10:50AM</t>
+          <t>9:00AM</t>
         </is>
       </c>
       <c r="C21" s="95" t="inlineStr">
         <is>
-          <t>11:05AM</t>
+          <t>9:15AM</t>
         </is>
       </c>
       <c r="D21" s="95" t="inlineStr">
@@ -9823,7 +9823,7 @@
       </c>
       <c r="F21" s="95" t="inlineStr">
         <is>
-          <t>QF2</t>
+          <t>QF3</t>
         </is>
       </c>
       <c r="G21" s="95" t="inlineStr">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="H21" s="95" t="inlineStr">
         <is>
-          <t>Nilesh Bagaria &amp; Parthiv</t>
+          <t>Mayank Aggarwal &amp; Sudip Parui</t>
         </is>
       </c>
       <c r="I21" s="95" t="inlineStr">
@@ -9843,7 +9843,7 @@
       </c>
       <c r="J21" s="95" t="inlineStr">
         <is>
-          <t>Rahul Garg &amp; Nilesh Mhatre</t>
+          <t>Nidhi Sharma &amp; Tushar</t>
         </is>
       </c>
     </row>
@@ -9855,12 +9855,12 @@
       </c>
       <c r="B22" s="94" t="inlineStr">
         <is>
-          <t>11:10AM</t>
+          <t>9:15AM</t>
         </is>
       </c>
       <c r="C22" s="94" t="inlineStr">
         <is>
-          <t>11:25AM</t>
+          <t>9:30AM</t>
         </is>
       </c>
       <c r="D22" s="94" t="inlineStr">
@@ -9873,17 +9873,17 @@
       </c>
       <c r="F22" s="94" t="inlineStr">
         <is>
-          <t>QF4</t>
+          <t>QF1</t>
         </is>
       </c>
       <c r="G22" s="94" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H22" s="94" t="inlineStr">
         <is>
-          <t>Adil Khan &amp; Anuj Shah</t>
+          <t>Tanmay Sharma &amp; Sankalp</t>
         </is>
       </c>
       <c r="I22" s="94" t="inlineStr">
@@ -9893,7 +9893,7 @@
       </c>
       <c r="J22" s="94" t="inlineStr">
         <is>
-          <t>Vinit Padia &amp; Pratik Haldiya</t>
+          <t>Ravi Modi &amp; Dr Rahul Modi</t>
         </is>
       </c>
     </row>
@@ -9905,12 +9905,12 @@
       </c>
       <c r="B23" s="95" t="inlineStr">
         <is>
-          <t>11:40AM</t>
+          <t>9:30AM</t>
         </is>
       </c>
       <c r="C23" s="95" t="inlineStr">
         <is>
-          <t>11:55AM</t>
+          <t>9:45AM</t>
         </is>
       </c>
       <c r="D23" s="95" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="F23" s="95" t="inlineStr">
         <is>
-          <t>QF1</t>
+          <t>QF4</t>
         </is>
       </c>
       <c r="G23" s="95" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H23" s="95" t="inlineStr">
         <is>
-          <t>Tanmay Sharma &amp; Sankalp</t>
+          <t>Adil Khan &amp; Anuj Shah</t>
         </is>
       </c>
       <c r="I23" s="95" t="inlineStr">
@@ -9943,7 +9943,7 @@
       </c>
       <c r="J23" s="95" t="inlineStr">
         <is>
-          <t>Ravi Modi &amp; Dr Rahul Modi</t>
+          <t>Vinit Padia &amp; Pratik Haldiya</t>
         </is>
       </c>
     </row>
@@ -9955,12 +9955,12 @@
       </c>
       <c r="B24" s="94" t="inlineStr">
         <is>
-          <t>11:55AM</t>
+          <t>9:45AM</t>
         </is>
       </c>
       <c r="C24" s="94" t="inlineStr">
         <is>
-          <t>12:10PM</t>
+          <t>10:00AM</t>
         </is>
       </c>
       <c r="D24" s="94" t="inlineStr">
@@ -9978,7 +9978,7 @@
       </c>
       <c r="G24" s="94" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H24" s="94" t="inlineStr">
@@ -10005,12 +10005,12 @@
       </c>
       <c r="B25" s="95" t="inlineStr">
         <is>
-          <t>4:00PM</t>
+          <t>9:45AM</t>
         </is>
       </c>
       <c r="C25" s="95" t="inlineStr">
         <is>
-          <t>4:15PM</t>
+          <t>10:00AM</t>
         </is>
       </c>
       <c r="D25" s="95" t="inlineStr">
@@ -10028,7 +10028,7 @@
       </c>
       <c r="G25" s="95" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H25" s="95" t="inlineStr">
@@ -10055,12 +10055,12 @@
       </c>
       <c r="B26" s="94" t="inlineStr">
         <is>
-          <t>4:15PM</t>
+          <t>10:00AM</t>
         </is>
       </c>
       <c r="C26" s="94" t="inlineStr">
         <is>
-          <t>4:30PM</t>
+          <t>10:15AM</t>
         </is>
       </c>
       <c r="D26" s="94" t="inlineStr">

--- a/Ekta_Schedule_With_Matchups.xlsx
+++ b/Ekta_Schedule_With_Matchups.xlsx
@@ -1262,7 +1262,7 @@
       </c>
       <c r="C16" s="64" t="inlineStr">
         <is>
-          <t>Only a handful of matches remain from Aug 15: TT Men's Singles' Under 46 Final (8:00-8:15 AM) and Chess's 41-and-above Final (8:20 AM) both wrap up within the first half hour. Squash's own league stage continues (its Under 15 + 15-25 Bracket knockouts followed right after Squash's own league stage ~6:39 PM Aug 15; its Above 25 Bracket is the one event still running its group stage into Aug 16).</t>
+          <t>TT Men's Singles' groups/semis are all done from Aug 15 — its 5 finals (Under 15/26/36/46, Above 46) are deliberately held to 11:00 AM onward alongside the TT Doubles final, so they land together as one dedicated finals session rather than trickling out whenever each semifinal happens to finish. Chess's entire pool stage, semifinals, and final complete by 8:20 AM. Squash's own league stage continues (its Under 15 + 15-25 Bracket knockouts followed right after Squash's own league stage ~6:39 PM Aug 15; its Above 25 Bracket is the one event still running its group stage into Aug 16).</t>
         </is>
       </c>
       <c r="H16" s="31" t="n"/>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="C17" s="64" t="inlineStr">
         <is>
-          <t>Both Doubles events run once their own players are free — TT Doubles wraps up 9:00-10:15 AM; Carrom Doubles runs 9:00 AM-10:30 AM, both far ahead of their old finish times since neither table time nor board time is the constraint anymore.</t>
+          <t>Both Doubles events run once their own players are free — TT Doubles' quarterfinals/semis run 9:00-10:00 AM but its Final is deliberately held to 11:30-11:45 AM, alongside TT Men's Singles' 5 finals; Carrom Doubles runs 9:00 AM-10:30 AM straight through.</t>
         </is>
       </c>
       <c r="H17" s="31" t="n"/>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="C19" s="64" t="inlineStr">
         <is>
-          <t>Squash's Above 25 Bracket is now the only semis/finals still gated behind a same-day group stage — every other event's semis/finals landed on Aug 15 evening or the first hour of Aug 16.</t>
+          <t>TT Men's Singles' 5 finals and the TT Doubles final all land together, 11:00-11:45 AM (deliberately held back rather than scheduled as soon as each was ready). Squash's Above 25 Bracket is the only other semis/finals still gated behind a same-day group stage, landing here around ~3:20 PM.</t>
         </is>
       </c>
       <c r="H19" s="31" t="n"/>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="E25" s="63" t="inlineStr">
         <is>
-          <t>Aug16 8:15AM</t>
+          <t>Aug16 11:45AM</t>
         </is>
       </c>
       <c r="F25" s="31" t="n"/>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="E26" s="63" t="inlineStr">
         <is>
-          <t>Aug16 10:15AM</t>
+          <t>Aug16 11:45AM</t>
         </is>
       </c>
       <c r="F26" s="31" t="n"/>
@@ -5045,7 +5045,7 @@
       </c>
       <c r="G17" s="95" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H17" s="95" t="inlineStr">
@@ -5072,12 +5072,12 @@
       </c>
       <c r="B18" s="94" t="inlineStr">
         <is>
+          <t>9:00AM</t>
+        </is>
+      </c>
+      <c r="C18" s="94" t="inlineStr">
+        <is>
           <t>9:15AM</t>
-        </is>
-      </c>
-      <c r="C18" s="94" t="inlineStr">
-        <is>
-          <t>9:30AM</t>
         </is>
       </c>
       <c r="D18" s="94" t="inlineStr">
@@ -5095,7 +5095,7 @@
       </c>
       <c r="G18" s="94" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H18" s="94" t="inlineStr">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="G19" s="95" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H19" s="95" t="inlineStr">
@@ -6798,17 +6798,17 @@
       </c>
       <c r="B56" s="95" t="inlineStr">
         <is>
-          <t>9:00AM</t>
+          <t>9:15AM</t>
         </is>
       </c>
       <c r="C56" s="95" t="inlineStr">
         <is>
-          <t>9:15AM</t>
+          <t>9:30AM</t>
         </is>
       </c>
       <c r="D56" s="95" t="inlineStr">
         <is>
-          <t>Above 46</t>
+          <t>Under 36</t>
         </is>
       </c>
       <c r="E56" s="95" t="n">
@@ -6816,17 +6816,17 @@
       </c>
       <c r="F56" s="95" t="inlineStr">
         <is>
-          <t>A46-FINAL</t>
+          <t>U36-GB-1</t>
         </is>
       </c>
       <c r="G56" s="95" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H56" s="95" t="inlineStr">
         <is>
-          <t>Winner SF1</t>
+          <t>Prakshal Shah</t>
         </is>
       </c>
       <c r="I56" s="95" t="inlineStr">
@@ -6836,7 +6836,7 @@
       </c>
       <c r="J56" s="95" t="inlineStr">
         <is>
-          <t>Winner SF2</t>
+          <t>Amar Parulekar</t>
         </is>
       </c>
     </row>
@@ -6866,7 +6866,7 @@
       </c>
       <c r="F57" s="94" t="inlineStr">
         <is>
-          <t>U36-GB-1</t>
+          <t>U36-GA-2</t>
         </is>
       </c>
       <c r="G57" s="94" t="inlineStr">
@@ -6876,7 +6876,7 @@
       </c>
       <c r="H57" s="94" t="inlineStr">
         <is>
-          <t>Prakshal Shah</t>
+          <t>Jashit Bajaj</t>
         </is>
       </c>
       <c r="I57" s="94" t="inlineStr">
@@ -6886,7 +6886,7 @@
       </c>
       <c r="J57" s="94" t="inlineStr">
         <is>
-          <t>Amar Parulekar</t>
+          <t>Tapabrata Dutta</t>
         </is>
       </c>
     </row>
@@ -6908,7 +6908,7 @@
       </c>
       <c r="D58" s="95" t="inlineStr">
         <is>
-          <t>Under 26</t>
+          <t>Under 15</t>
         </is>
       </c>
       <c r="E58" s="95" t="n">
@@ -6916,17 +6916,17 @@
       </c>
       <c r="F58" s="95" t="inlineStr">
         <is>
-          <t>U26-2</t>
+          <t>U15-GA-1</t>
         </is>
       </c>
       <c r="G58" s="95" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H58" s="95" t="inlineStr">
         <is>
-          <t>Yuvraj jain</t>
+          <t>Shaurya Tripathi</t>
         </is>
       </c>
       <c r="I58" s="95" t="inlineStr">
@@ -6936,7 +6936,7 @@
       </c>
       <c r="J58" s="95" t="inlineStr">
         <is>
-          <t>Hryday Goyal</t>
+          <t>Parth yadav</t>
         </is>
       </c>
     </row>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="D59" s="94" t="inlineStr">
         <is>
-          <t>Under 36</t>
+          <t>Under 26</t>
         </is>
       </c>
       <c r="E59" s="94" t="n">
@@ -6966,17 +6966,17 @@
       </c>
       <c r="F59" s="94" t="inlineStr">
         <is>
-          <t>U36-GA-2</t>
+          <t>U26-2</t>
         </is>
       </c>
       <c r="G59" s="94" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H59" s="94" t="inlineStr">
         <is>
-          <t>Jashit Bajaj</t>
+          <t>Yuvraj jain</t>
         </is>
       </c>
       <c r="I59" s="94" t="inlineStr">
@@ -6986,7 +6986,7 @@
       </c>
       <c r="J59" s="94" t="inlineStr">
         <is>
-          <t>Tapabrata Dutta</t>
+          <t>Hryday Goyal</t>
         </is>
       </c>
     </row>
@@ -7016,7 +7016,7 @@
       </c>
       <c r="F60" s="95" t="inlineStr">
         <is>
-          <t>U15-GA-1</t>
+          <t>U15-GB-1</t>
         </is>
       </c>
       <c r="G60" s="95" t="inlineStr">
@@ -7026,7 +7026,7 @@
       </c>
       <c r="H60" s="95" t="inlineStr">
         <is>
-          <t>Shaurya Tripathi</t>
+          <t>Viaan Neema</t>
         </is>
       </c>
       <c r="I60" s="95" t="inlineStr">
@@ -7036,7 +7036,7 @@
       </c>
       <c r="J60" s="95" t="inlineStr">
         <is>
-          <t>Parth yadav</t>
+          <t>Yash agarwal</t>
         </is>
       </c>
     </row>
@@ -7108,7 +7108,7 @@
       </c>
       <c r="D62" s="95" t="inlineStr">
         <is>
-          <t>Under 15</t>
+          <t>Under 26</t>
         </is>
       </c>
       <c r="E62" s="95" t="n">
@@ -7116,17 +7116,17 @@
       </c>
       <c r="F62" s="95" t="inlineStr">
         <is>
-          <t>U15-GB-1</t>
+          <t>U26-3</t>
         </is>
       </c>
       <c r="G62" s="95" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H62" s="95" t="inlineStr">
         <is>
-          <t>Viaan Neema</t>
+          <t>Yuvraj jain</t>
         </is>
       </c>
       <c r="I62" s="95" t="inlineStr">
@@ -7136,7 +7136,7 @@
       </c>
       <c r="J62" s="95" t="inlineStr">
         <is>
-          <t>Yash agarwal</t>
+          <t>Pranit Shriyan</t>
         </is>
       </c>
     </row>
@@ -7171,7 +7171,7 @@
       </c>
       <c r="G63" s="94" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H63" s="94" t="inlineStr">
@@ -7208,7 +7208,7 @@
       </c>
       <c r="D64" s="95" t="inlineStr">
         <is>
-          <t>Under 26</t>
+          <t>Under 15</t>
         </is>
       </c>
       <c r="E64" s="95" t="n">
@@ -7216,17 +7216,17 @@
       </c>
       <c r="F64" s="95" t="inlineStr">
         <is>
-          <t>U26-8</t>
+          <t>U15-GB-2</t>
         </is>
       </c>
       <c r="G64" s="95" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H64" s="95" t="inlineStr">
         <is>
-          <t>Hryday Goyal</t>
+          <t>Viaan Neema</t>
         </is>
       </c>
       <c r="I64" s="95" t="inlineStr">
@@ -7236,7 +7236,7 @@
       </c>
       <c r="J64" s="95" t="inlineStr">
         <is>
-          <t>Pranit Shriyan</t>
+          <t>Hridh jhala</t>
         </is>
       </c>
     </row>
@@ -7271,7 +7271,7 @@
       </c>
       <c r="G65" s="94" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H65" s="94" t="inlineStr">
@@ -7308,7 +7308,7 @@
       </c>
       <c r="D66" s="95" t="inlineStr">
         <is>
-          <t>Under 15</t>
+          <t>Under 36</t>
         </is>
       </c>
       <c r="E66" s="95" t="n">
@@ -7316,17 +7316,17 @@
       </c>
       <c r="F66" s="95" t="inlineStr">
         <is>
-          <t>U15-GB-2</t>
+          <t>U36-GA-1</t>
         </is>
       </c>
       <c r="G66" s="95" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H66" s="95" t="inlineStr">
         <is>
-          <t>Viaan Neema</t>
+          <t>Jashit Bajaj</t>
         </is>
       </c>
       <c r="I66" s="95" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="J66" s="95" t="inlineStr">
         <is>
-          <t>Hridh jhala</t>
+          <t>Ravi Modi</t>
         </is>
       </c>
     </row>
@@ -7366,17 +7366,17 @@
       </c>
       <c r="F67" s="94" t="inlineStr">
         <is>
-          <t>U36-GA-1</t>
+          <t>U36-GB-2</t>
         </is>
       </c>
       <c r="G67" s="94" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H67" s="94" t="inlineStr">
         <is>
-          <t>Jashit Bajaj</t>
+          <t>Prakshal Shah</t>
         </is>
       </c>
       <c r="I67" s="94" t="inlineStr">
@@ -7386,7 +7386,7 @@
       </c>
       <c r="J67" s="94" t="inlineStr">
         <is>
-          <t>Ravi Modi</t>
+          <t>Tej</t>
         </is>
       </c>
     </row>
@@ -7408,7 +7408,7 @@
       </c>
       <c r="D68" s="95" t="inlineStr">
         <is>
-          <t>Under 36</t>
+          <t>Under 15</t>
         </is>
       </c>
       <c r="E68" s="95" t="n">
@@ -7416,7 +7416,7 @@
       </c>
       <c r="F68" s="95" t="inlineStr">
         <is>
-          <t>U36-GB-2</t>
+          <t>U15-GB-3</t>
         </is>
       </c>
       <c r="G68" s="95" t="inlineStr">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="H68" s="95" t="inlineStr">
         <is>
-          <t>Prakshal Shah</t>
+          <t>Yash agarwal</t>
         </is>
       </c>
       <c r="I68" s="95" t="inlineStr">
@@ -7436,7 +7436,7 @@
       </c>
       <c r="J68" s="95" t="inlineStr">
         <is>
-          <t>Tej</t>
+          <t>Hridh jhala</t>
         </is>
       </c>
     </row>
@@ -7516,17 +7516,17 @@
       </c>
       <c r="F70" s="95" t="inlineStr">
         <is>
-          <t>U15-GB-3</t>
+          <t>U15-GA-2</t>
         </is>
       </c>
       <c r="G70" s="95" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H70" s="95" t="inlineStr">
         <is>
-          <t>Yash agarwal</t>
+          <t>Shaurya Tripathi</t>
         </is>
       </c>
       <c r="I70" s="95" t="inlineStr">
@@ -7536,7 +7536,7 @@
       </c>
       <c r="J70" s="95" t="inlineStr">
         <is>
-          <t>Hridh jhala</t>
+          <t>Aadit Joshi</t>
         </is>
       </c>
     </row>
@@ -7571,7 +7571,7 @@
       </c>
       <c r="G71" s="94" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H71" s="94" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="D76" s="95" t="inlineStr">
         <is>
-          <t>Under 15</t>
+          <t>Under 26</t>
         </is>
       </c>
       <c r="E76" s="95" t="n">
@@ -7816,7 +7816,7 @@
       </c>
       <c r="F76" s="95" t="inlineStr">
         <is>
-          <t>U15-GA-2</t>
+          <t>U26-8</t>
         </is>
       </c>
       <c r="G76" s="95" t="inlineStr">
@@ -7826,7 +7826,7 @@
       </c>
       <c r="H76" s="95" t="inlineStr">
         <is>
-          <t>Shaurya Tripathi</t>
+          <t>Hryday Goyal</t>
         </is>
       </c>
       <c r="I76" s="95" t="inlineStr">
@@ -7836,7 +7836,7 @@
       </c>
       <c r="J76" s="95" t="inlineStr">
         <is>
-          <t>Aadit Joshi</t>
+          <t>Pranit Shriyan</t>
         </is>
       </c>
     </row>
@@ -8108,7 +8108,7 @@
       </c>
       <c r="D82" s="95" t="inlineStr">
         <is>
-          <t>Under 26</t>
+          <t>Under 15</t>
         </is>
       </c>
       <c r="E82" s="95" t="n">
@@ -8116,7 +8116,7 @@
       </c>
       <c r="F82" s="95" t="inlineStr">
         <is>
-          <t>U26-3</t>
+          <t>U15-GA-3</t>
         </is>
       </c>
       <c r="G82" s="95" t="inlineStr">
@@ -8126,7 +8126,7 @@
       </c>
       <c r="H82" s="95" t="inlineStr">
         <is>
-          <t>Yuvraj jain</t>
+          <t>Parth yadav</t>
         </is>
       </c>
       <c r="I82" s="95" t="inlineStr">
@@ -8136,7 +8136,7 @@
       </c>
       <c r="J82" s="95" t="inlineStr">
         <is>
-          <t>Pranit Shriyan</t>
+          <t>Aadit Joshi</t>
         </is>
       </c>
     </row>
@@ -8208,7 +8208,7 @@
       </c>
       <c r="D84" s="95" t="inlineStr">
         <is>
-          <t>Under 26</t>
+          <t>Under 15</t>
         </is>
       </c>
       <c r="E84" s="95" t="n">
@@ -8216,17 +8216,17 @@
       </c>
       <c r="F84" s="95" t="inlineStr">
         <is>
-          <t>U26-5</t>
+          <t>U15-SF1</t>
         </is>
       </c>
       <c r="G84" s="95" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H84" s="95" t="inlineStr">
         <is>
-          <t>Aaditya Kumar</t>
+          <t>Group B 1st</t>
         </is>
       </c>
       <c r="I84" s="95" t="inlineStr">
@@ -8236,7 +8236,7 @@
       </c>
       <c r="J84" s="95" t="inlineStr">
         <is>
-          <t>Hryday Goyal</t>
+          <t>Group A 2nd</t>
         </is>
       </c>
     </row>
@@ -8258,7 +8258,7 @@
       </c>
       <c r="D85" s="94" t="inlineStr">
         <is>
-          <t>Under 36</t>
+          <t>Under 15</t>
         </is>
       </c>
       <c r="E85" s="94" t="n">
@@ -8266,17 +8266,17 @@
       </c>
       <c r="F85" s="94" t="inlineStr">
         <is>
-          <t>U36-FINAL</t>
+          <t>U15-SF2</t>
         </is>
       </c>
       <c r="G85" s="94" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H85" s="94" t="inlineStr">
         <is>
-          <t>Winner SF1</t>
+          <t>Group A 1st</t>
         </is>
       </c>
       <c r="I85" s="94" t="inlineStr">
@@ -8286,7 +8286,7 @@
       </c>
       <c r="J85" s="94" t="inlineStr">
         <is>
-          <t>Winner SF2</t>
+          <t>Group B 2nd</t>
         </is>
       </c>
     </row>
@@ -8408,7 +8408,7 @@
       </c>
       <c r="D88" s="95" t="inlineStr">
         <is>
-          <t>Under 15</t>
+          <t>Under 26</t>
         </is>
       </c>
       <c r="E88" s="95" t="n">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="F88" s="95" t="inlineStr">
         <is>
-          <t>U15-GA-3</t>
+          <t>U26-4</t>
         </is>
       </c>
       <c r="G88" s="95" t="inlineStr">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="H88" s="95" t="inlineStr">
         <is>
-          <t>Parth yadav</t>
+          <t>Yuvraj jain</t>
         </is>
       </c>
       <c r="I88" s="95" t="inlineStr">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="J88" s="95" t="inlineStr">
         <is>
-          <t>Aadit Joshi</t>
+          <t>Rahul Garg</t>
         </is>
       </c>
     </row>
@@ -8466,7 +8466,7 @@
       </c>
       <c r="F89" s="94" t="inlineStr">
         <is>
-          <t>U26-4</t>
+          <t>U26-6</t>
         </is>
       </c>
       <c r="G89" s="94" t="inlineStr">
@@ -8476,7 +8476,7 @@
       </c>
       <c r="H89" s="94" t="inlineStr">
         <is>
-          <t>Yuvraj jain</t>
+          <t>Aaditya Kumar</t>
         </is>
       </c>
       <c r="I89" s="94" t="inlineStr">
@@ -8486,7 +8486,7 @@
       </c>
       <c r="J89" s="94" t="inlineStr">
         <is>
-          <t>Rahul Garg</t>
+          <t>Pranit Shriyan</t>
         </is>
       </c>
     </row>
@@ -8598,17 +8598,17 @@
       </c>
       <c r="B92" s="95" t="inlineStr">
         <is>
-          <t>7:15PM</t>
+          <t>7:20PM</t>
         </is>
       </c>
       <c r="C92" s="95" t="inlineStr">
         <is>
-          <t>7:30PM</t>
+          <t>7:35PM</t>
         </is>
       </c>
       <c r="D92" s="95" t="inlineStr">
         <is>
-          <t>Under 15</t>
+          <t>Under 26</t>
         </is>
       </c>
       <c r="E92" s="95" t="n">
@@ -8616,7 +8616,7 @@
       </c>
       <c r="F92" s="95" t="inlineStr">
         <is>
-          <t>U15-SF1</t>
+          <t>U26-9</t>
         </is>
       </c>
       <c r="G92" s="95" t="inlineStr">
@@ -8626,7 +8626,7 @@
       </c>
       <c r="H92" s="95" t="inlineStr">
         <is>
-          <t>Group B 1st</t>
+          <t>Hryday Goyal</t>
         </is>
       </c>
       <c r="I92" s="95" t="inlineStr">
@@ -8636,7 +8636,7 @@
       </c>
       <c r="J92" s="95" t="inlineStr">
         <is>
-          <t>Group A 2nd</t>
+          <t>Rahul Garg</t>
         </is>
       </c>
     </row>
@@ -8648,17 +8648,17 @@
       </c>
       <c r="B93" s="94" t="inlineStr">
         <is>
-          <t>7:15PM</t>
+          <t>7:40PM</t>
         </is>
       </c>
       <c r="C93" s="94" t="inlineStr">
         <is>
-          <t>7:30PM</t>
+          <t>7:55PM</t>
         </is>
       </c>
       <c r="D93" s="94" t="inlineStr">
         <is>
-          <t>Under 15</t>
+          <t>Under 26</t>
         </is>
       </c>
       <c r="E93" s="94" t="n">
@@ -8666,7 +8666,7 @@
       </c>
       <c r="F93" s="94" t="inlineStr">
         <is>
-          <t>U15-SF2</t>
+          <t>U26-1</t>
         </is>
       </c>
       <c r="G93" s="94" t="inlineStr">
@@ -8676,7 +8676,7 @@
       </c>
       <c r="H93" s="94" t="inlineStr">
         <is>
-          <t>Group A 1st</t>
+          <t>Yuvraj jain</t>
         </is>
       </c>
       <c r="I93" s="94" t="inlineStr">
@@ -8686,7 +8686,7 @@
       </c>
       <c r="J93" s="94" t="inlineStr">
         <is>
-          <t>Group B 2nd</t>
+          <t>Aaditya Kumar</t>
         </is>
       </c>
     </row>
@@ -8698,17 +8698,17 @@
       </c>
       <c r="B94" s="95" t="inlineStr">
         <is>
-          <t>7:30PM</t>
+          <t>7:40PM</t>
         </is>
       </c>
       <c r="C94" s="95" t="inlineStr">
         <is>
-          <t>7:45PM</t>
+          <t>7:55PM</t>
         </is>
       </c>
       <c r="D94" s="95" t="inlineStr">
         <is>
-          <t>Under 15</t>
+          <t>Under 46</t>
         </is>
       </c>
       <c r="E94" s="95" t="n">
@@ -8716,17 +8716,17 @@
       </c>
       <c r="F94" s="95" t="inlineStr">
         <is>
-          <t>U15-FINAL</t>
+          <t>U46-GB-2</t>
         </is>
       </c>
       <c r="G94" s="95" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H94" s="95" t="inlineStr">
         <is>
-          <t>Winner SF1</t>
+          <t>Nikunj Jhala</t>
         </is>
       </c>
       <c r="I94" s="95" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="J94" s="95" t="inlineStr">
         <is>
-          <t>Winner SF2</t>
+          <t>Vinit Padia</t>
         </is>
       </c>
     </row>
@@ -8748,17 +8748,17 @@
       </c>
       <c r="B95" s="94" t="inlineStr">
         <is>
-          <t>7:30PM</t>
+          <t>7:55PM</t>
         </is>
       </c>
       <c r="C95" s="94" t="inlineStr">
         <is>
-          <t>7:45PM</t>
+          <t>8:10PM</t>
         </is>
       </c>
       <c r="D95" s="94" t="inlineStr">
         <is>
-          <t>Under 26</t>
+          <t>Under 46</t>
         </is>
       </c>
       <c r="E95" s="94" t="n">
@@ -8766,7 +8766,7 @@
       </c>
       <c r="F95" s="94" t="inlineStr">
         <is>
-          <t>U26-9</t>
+          <t>U46-GB-6</t>
         </is>
       </c>
       <c r="G95" s="94" t="inlineStr">
@@ -8776,7 +8776,7 @@
       </c>
       <c r="H95" s="94" t="inlineStr">
         <is>
-          <t>Hryday Goyal</t>
+          <t>Piyush Makharia</t>
         </is>
       </c>
       <c r="I95" s="94" t="inlineStr">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="J95" s="94" t="inlineStr">
         <is>
-          <t>Rahul Garg</t>
+          <t>Nilesh Bagaria</t>
         </is>
       </c>
     </row>
@@ -8798,12 +8798,12 @@
       </c>
       <c r="B96" s="95" t="inlineStr">
         <is>
-          <t>7:45PM</t>
+          <t>8:05PM</t>
         </is>
       </c>
       <c r="C96" s="95" t="inlineStr">
         <is>
-          <t>8:00PM</t>
+          <t>8:20PM</t>
         </is>
       </c>
       <c r="D96" s="95" t="inlineStr">
@@ -8816,7 +8816,7 @@
       </c>
       <c r="F96" s="95" t="inlineStr">
         <is>
-          <t>U26-6</t>
+          <t>U26-5</t>
         </is>
       </c>
       <c r="G96" s="95" t="inlineStr">
@@ -8836,7 +8836,7 @@
       </c>
       <c r="J96" s="95" t="inlineStr">
         <is>
-          <t>Pranit Shriyan</t>
+          <t>Hryday Goyal</t>
         </is>
       </c>
     </row>
@@ -8848,17 +8848,17 @@
       </c>
       <c r="B97" s="94" t="inlineStr">
         <is>
-          <t>7:45PM</t>
+          <t>8:20PM</t>
         </is>
       </c>
       <c r="C97" s="94" t="inlineStr">
         <is>
-          <t>8:00PM</t>
+          <t>8:35PM</t>
         </is>
       </c>
       <c r="D97" s="94" t="inlineStr">
         <is>
-          <t>Under 46</t>
+          <t>Under 26</t>
         </is>
       </c>
       <c r="E97" s="94" t="n">
@@ -8866,7 +8866,7 @@
       </c>
       <c r="F97" s="94" t="inlineStr">
         <is>
-          <t>U46-GB-2</t>
+          <t>U26-10</t>
         </is>
       </c>
       <c r="G97" s="94" t="inlineStr">
@@ -8876,7 +8876,7 @@
       </c>
       <c r="H97" s="94" t="inlineStr">
         <is>
-          <t>Nikunj Jhala</t>
+          <t>Pranit Shriyan</t>
         </is>
       </c>
       <c r="I97" s="94" t="inlineStr">
@@ -8886,7 +8886,7 @@
       </c>
       <c r="J97" s="94" t="inlineStr">
         <is>
-          <t>Vinit Padia</t>
+          <t>Rahul Garg</t>
         </is>
       </c>
     </row>
@@ -8898,17 +8898,17 @@
       </c>
       <c r="B98" s="95" t="inlineStr">
         <is>
-          <t>8:10PM</t>
+          <t>8:30PM</t>
         </is>
       </c>
       <c r="C98" s="95" t="inlineStr">
         <is>
-          <t>8:25PM</t>
+          <t>8:45PM</t>
         </is>
       </c>
       <c r="D98" s="95" t="inlineStr">
         <is>
-          <t>Under 26</t>
+          <t>Under 46</t>
         </is>
       </c>
       <c r="E98" s="95" t="n">
@@ -8916,17 +8916,17 @@
       </c>
       <c r="F98" s="95" t="inlineStr">
         <is>
-          <t>U26-1</t>
+          <t>U46-GB-1</t>
         </is>
       </c>
       <c r="G98" s="95" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H98" s="95" t="inlineStr">
         <is>
-          <t>Yuvraj jain</t>
+          <t>Nikunj Jhala</t>
         </is>
       </c>
       <c r="I98" s="95" t="inlineStr">
@@ -8936,7 +8936,7 @@
       </c>
       <c r="J98" s="95" t="inlineStr">
         <is>
-          <t>Aaditya Kumar</t>
+          <t>Piyush Makharia</t>
         </is>
       </c>
     </row>
@@ -8948,17 +8948,17 @@
       </c>
       <c r="B99" s="94" t="inlineStr">
         <is>
-          <t>8:20PM</t>
+          <t>8:55PM</t>
         </is>
       </c>
       <c r="C99" s="94" t="inlineStr">
         <is>
-          <t>8:35PM</t>
+          <t>9:10PM</t>
         </is>
       </c>
       <c r="D99" s="94" t="inlineStr">
         <is>
-          <t>Under 26</t>
+          <t>Under 46</t>
         </is>
       </c>
       <c r="E99" s="94" t="n">
@@ -8966,17 +8966,17 @@
       </c>
       <c r="F99" s="94" t="inlineStr">
         <is>
-          <t>U26-10</t>
+          <t>U46-GB-5</t>
         </is>
       </c>
       <c r="G99" s="94" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H99" s="94" t="inlineStr">
         <is>
-          <t>Pranit Shriyan</t>
+          <t>Piyush Makharia</t>
         </is>
       </c>
       <c r="I99" s="94" t="inlineStr">
@@ -8986,7 +8986,7 @@
       </c>
       <c r="J99" s="94" t="inlineStr">
         <is>
-          <t>Rahul Garg</t>
+          <t>Vinit Padia</t>
         </is>
       </c>
     </row>
@@ -8998,17 +8998,17 @@
       </c>
       <c r="B100" s="95" t="inlineStr">
         <is>
-          <t>8:30PM</t>
+          <t>9:00PM</t>
         </is>
       </c>
       <c r="C100" s="95" t="inlineStr">
         <is>
-          <t>8:45PM</t>
+          <t>9:15PM</t>
         </is>
       </c>
       <c r="D100" s="95" t="inlineStr">
         <is>
-          <t>Under 46</t>
+          <t>Under 26</t>
         </is>
       </c>
       <c r="E100" s="95" t="n">
@@ -9016,17 +9016,17 @@
       </c>
       <c r="F100" s="95" t="inlineStr">
         <is>
-          <t>U46-GB-1</t>
+          <t>U26-7</t>
         </is>
       </c>
       <c r="G100" s="95" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H100" s="95" t="inlineStr">
         <is>
-          <t>Nikunj Jhala</t>
+          <t>Aaditya Kumar</t>
         </is>
       </c>
       <c r="I100" s="95" t="inlineStr">
@@ -9036,7 +9036,7 @@
       </c>
       <c r="J100" s="95" t="inlineStr">
         <is>
-          <t>Piyush Makharia</t>
+          <t>Rahul Garg</t>
         </is>
       </c>
     </row>
@@ -9048,12 +9048,12 @@
       </c>
       <c r="B101" s="94" t="inlineStr">
         <is>
-          <t>8:55PM</t>
+          <t>9:15PM</t>
         </is>
       </c>
       <c r="C101" s="94" t="inlineStr">
         <is>
-          <t>9:10PM</t>
+          <t>9:30PM</t>
         </is>
       </c>
       <c r="D101" s="94" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="F101" s="94" t="inlineStr">
         <is>
-          <t>U46-GB-6</t>
+          <t>U46-GB-7</t>
         </is>
       </c>
       <c r="G101" s="94" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H101" s="94" t="inlineStr">
@@ -9086,7 +9086,7 @@
       </c>
       <c r="J101" s="94" t="inlineStr">
         <is>
-          <t>Nilesh Bagaria</t>
+          <t>Amit Ranka</t>
         </is>
       </c>
     </row>
@@ -9098,17 +9098,17 @@
       </c>
       <c r="B102" s="95" t="inlineStr">
         <is>
-          <t>9:00PM</t>
+          <t>9:30PM</t>
         </is>
       </c>
       <c r="C102" s="95" t="inlineStr">
         <is>
-          <t>9:15PM</t>
+          <t>9:45PM</t>
         </is>
       </c>
       <c r="D102" s="95" t="inlineStr">
         <is>
-          <t>Under 26</t>
+          <t>Under 46</t>
         </is>
       </c>
       <c r="E102" s="95" t="n">
@@ -9116,17 +9116,17 @@
       </c>
       <c r="F102" s="95" t="inlineStr">
         <is>
-          <t>U26-7</t>
+          <t>U46-SF1</t>
         </is>
       </c>
       <c r="G102" s="95" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H102" s="95" t="inlineStr">
         <is>
-          <t>Aaditya Kumar</t>
+          <t>Group B 1st</t>
         </is>
       </c>
       <c r="I102" s="95" t="inlineStr">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="J102" s="95" t="inlineStr">
         <is>
-          <t>Rahul Garg</t>
+          <t>Group A 2nd</t>
         </is>
       </c>
     </row>
@@ -9148,17 +9148,17 @@
       </c>
       <c r="B103" s="94" t="inlineStr">
         <is>
-          <t>9:15PM</t>
+          <t>9:30PM</t>
         </is>
       </c>
       <c r="C103" s="94" t="inlineStr">
         <is>
-          <t>9:30PM</t>
+          <t>9:45PM</t>
         </is>
       </c>
       <c r="D103" s="94" t="inlineStr">
         <is>
-          <t>Under 26</t>
+          <t>Under 46</t>
         </is>
       </c>
       <c r="E103" s="94" t="n">
@@ -9166,17 +9166,17 @@
       </c>
       <c r="F103" s="94" t="inlineStr">
         <is>
-          <t>U26-FINAL</t>
+          <t>U46-SF2</t>
         </is>
       </c>
       <c r="G103" s="94" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H103" s="94" t="inlineStr">
         <is>
-          <t>Pool 1st</t>
+          <t>Group A 1st</t>
         </is>
       </c>
       <c r="I103" s="94" t="inlineStr">
@@ -9186,29 +9186,29 @@
       </c>
       <c r="J103" s="94" t="inlineStr">
         <is>
-          <t>Pool 2nd</t>
+          <t>Group B 2nd</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="95" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B104" s="95" t="inlineStr">
         <is>
-          <t>9:15PM</t>
+          <t>11:00AM</t>
         </is>
       </c>
       <c r="C104" s="95" t="inlineStr">
         <is>
-          <t>9:30PM</t>
+          <t>11:15AM</t>
         </is>
       </c>
       <c r="D104" s="95" t="inlineStr">
         <is>
-          <t>Under 46</t>
+          <t>Above 46</t>
         </is>
       </c>
       <c r="E104" s="95" t="n">
@@ -9216,17 +9216,17 @@
       </c>
       <c r="F104" s="95" t="inlineStr">
         <is>
-          <t>U46-GB-5</t>
+          <t>A46-FINAL</t>
         </is>
       </c>
       <c r="G104" s="95" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H104" s="95" t="inlineStr">
         <is>
-          <t>Piyush Makharia</t>
+          <t>Winner SF1</t>
         </is>
       </c>
       <c r="I104" s="95" t="inlineStr">
@@ -9236,29 +9236,29 @@
       </c>
       <c r="J104" s="95" t="inlineStr">
         <is>
-          <t>Vinit Padia</t>
+          <t>Winner SF2</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="94" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B105" s="94" t="inlineStr">
         <is>
-          <t>9:40PM</t>
+          <t>11:00AM</t>
         </is>
       </c>
       <c r="C105" s="94" t="inlineStr">
         <is>
-          <t>9:55PM</t>
+          <t>11:15AM</t>
         </is>
       </c>
       <c r="D105" s="94" t="inlineStr">
         <is>
-          <t>Under 46</t>
+          <t>Under 36</t>
         </is>
       </c>
       <c r="E105" s="94" t="n">
@@ -9266,17 +9266,17 @@
       </c>
       <c r="F105" s="94" t="inlineStr">
         <is>
-          <t>U46-GB-7</t>
+          <t>U36-FINAL</t>
         </is>
       </c>
       <c r="G105" s="94" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H105" s="94" t="inlineStr">
         <is>
-          <t>Piyush Makharia</t>
+          <t>Winner SF1</t>
         </is>
       </c>
       <c r="I105" s="94" t="inlineStr">
@@ -9286,29 +9286,29 @@
       </c>
       <c r="J105" s="94" t="inlineStr">
         <is>
-          <t>Amit Ranka</t>
+          <t>Winner SF2</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="95" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B106" s="95" t="inlineStr">
         <is>
-          <t>9:55PM</t>
+          <t>11:15AM</t>
         </is>
       </c>
       <c r="C106" s="95" t="inlineStr">
         <is>
-          <t>10:10PM</t>
+          <t>11:30AM</t>
         </is>
       </c>
       <c r="D106" s="95" t="inlineStr">
         <is>
-          <t>Under 46</t>
+          <t>Under 15</t>
         </is>
       </c>
       <c r="E106" s="95" t="n">
@@ -9316,7 +9316,7 @@
       </c>
       <c r="F106" s="95" t="inlineStr">
         <is>
-          <t>U46-SF1</t>
+          <t>U15-FINAL</t>
         </is>
       </c>
       <c r="G106" s="95" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="H106" s="95" t="inlineStr">
         <is>
-          <t>Group B 1st</t>
+          <t>Winner SF1</t>
         </is>
       </c>
       <c r="I106" s="95" t="inlineStr">
@@ -9336,29 +9336,29 @@
       </c>
       <c r="J106" s="95" t="inlineStr">
         <is>
-          <t>Group A 2nd</t>
+          <t>Winner SF2</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="94" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="B107" s="94" t="inlineStr">
         <is>
-          <t>9:55PM</t>
+          <t>11:15AM</t>
         </is>
       </c>
       <c r="C107" s="94" t="inlineStr">
         <is>
-          <t>10:10PM</t>
+          <t>11:30AM</t>
         </is>
       </c>
       <c r="D107" s="94" t="inlineStr">
         <is>
-          <t>Under 46</t>
+          <t>Under 26</t>
         </is>
       </c>
       <c r="E107" s="94" t="n">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="F107" s="94" t="inlineStr">
         <is>
-          <t>U46-SF2</t>
+          <t>U26-FINAL</t>
         </is>
       </c>
       <c r="G107" s="94" t="inlineStr">
@@ -9376,7 +9376,7 @@
       </c>
       <c r="H107" s="94" t="inlineStr">
         <is>
-          <t>Group A 1st</t>
+          <t>Pool 1st</t>
         </is>
       </c>
       <c r="I107" s="94" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="J107" s="94" t="inlineStr">
         <is>
-          <t>Group B 2nd</t>
+          <t>Pool 2nd</t>
         </is>
       </c>
     </row>
@@ -9398,12 +9398,12 @@
       </c>
       <c r="B108" s="95" t="inlineStr">
         <is>
-          <t>8:00AM</t>
+          <t>11:30AM</t>
         </is>
       </c>
       <c r="C108" s="95" t="inlineStr">
         <is>
-          <t>8:15AM</t>
+          <t>11:45AM</t>
         </is>
       </c>
       <c r="D108" s="95" t="inlineStr">
@@ -10055,12 +10055,12 @@
       </c>
       <c r="B26" s="94" t="inlineStr">
         <is>
-          <t>10:00AM</t>
+          <t>11:30AM</t>
         </is>
       </c>
       <c r="C26" s="94" t="inlineStr">
         <is>
-          <t>10:15AM</t>
+          <t>11:45AM</t>
         </is>
       </c>
       <c r="D26" s="94" t="inlineStr">
@@ -10078,7 +10078,7 @@
       </c>
       <c r="G26" s="94" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H26" s="94" t="inlineStr">

--- a/Ekta_Schedule_With_Matchups.xlsx
+++ b/Ekta_Schedule_With_Matchups.xlsx
@@ -1072,7 +1072,7 @@
     <row r="5">
       <c r="A5" s="69" t="inlineStr">
         <is>
-          <t>Carrom Women's Singles, TT Women's Singles, Pool, and Squash's Under 15 + 15-25 Bracket knockouts each follow</t>
+          <t>Carrom Women's Singles, TT Women's Singles, and Pool each follow immediately once that event's</t>
         </is>
       </c>
       <c r="F5" s="31" t="n"/>
@@ -1084,7 +1084,7 @@
     <row r="6">
       <c r="A6" s="69" t="inlineStr">
         <is>
-          <t>immediately once that event's own league stage is done. Carrom Men's, TT Men's, Chess, and Squash's Above 25</t>
+          <t>own league stage is done. Carrom Men's, TT Men's, and Chess wait for their own gating rule. All</t>
         </is>
       </c>
       <c r="F6" s="31" t="n"/>
@@ -1096,7 +1096,7 @@
     <row r="7">
       <c r="A7" s="69" t="inlineStr">
         <is>
-          <t>Bracket knockouts, plus both entire Doubles events (from 9:00 AM Aug 16), wait for their own gating rule.</t>
+          <t>3 Squash finals and both entire Doubles events are deliberately held to fixed times (see below).</t>
         </is>
       </c>
       <c r="F7" s="31" t="n"/>
@@ -1262,7 +1262,7 @@
       </c>
       <c r="C16" s="64" t="inlineStr">
         <is>
-          <t>TT Men's Singles' groups/semis are all done from Aug 15 — its 5 finals (Under 15/26/36/46, Above 46) are deliberately held to 11:00 AM onward alongside the TT Doubles final, so they land together as one dedicated finals session rather than trickling out whenever each semifinal happens to finish. Chess's entire pool stage, semifinals, and final complete by 8:20 AM. Squash's own league stage continues (its Under 15 + 15-25 Bracket knockouts followed right after Squash's own league stage ~6:39 PM Aug 15; its Above 25 Bracket is the one event still running its group stage into Aug 16).</t>
+          <t>TT Men's Singles' groups/semis are all done from Aug 15 — its 5 finals (Under 15/26/36/46, Above 46) are deliberately held to 11:00 AM onward alongside the TT Doubles final, so they land together as one dedicated finals session rather than trickling out whenever each semifinal happens to finish. Chess's entire pool stage, semifinals, and final complete by 8:20 AM. Squash's entire group/pool stage and semifinals are also done by Aug 15 evening — only its 3 finals remain, held back to the afternoon (see below).</t>
         </is>
       </c>
       <c r="H16" s="31" t="n"/>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="C19" s="64" t="inlineStr">
         <is>
-          <t>TT Men's Singles' 5 finals and the TT Doubles final all land together, 11:00-11:45 AM (deliberately held back rather than scheduled as soon as each was ready). Squash's Above 25 Bracket is the only other semis/finals still gated behind a same-day group stage, landing here around ~3:20 PM.</t>
+          <t>TT Men's Singles' 5 finals and the TT Doubles final all land together, 11:00-11:45 AM (deliberately held back rather than scheduled as soon as each was ready). Squash's 3 finals (Under 15, 15-25 Bracket, Above 25 Bracket) are likewise deliberately held to this afternoon, running back-to-back 3:00-3:54 PM on the single court — the tournament's last matches.</t>
         </is>
       </c>
       <c r="H19" s="31" t="n"/>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="E32" s="63" t="inlineStr">
         <is>
-          <t>Aug16 4:14PM</t>
+          <t>Aug16 3:54PM</t>
         </is>
       </c>
       <c r="F32" s="31" t="n"/>
@@ -1680,7 +1680,7 @@
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="86" t="inlineStr">
         <is>
-          <t>Overall tournament span: Aug 15, 8:00 AM start → Aug 16, 4:14 PM finish — comfortably inside the Aug 16, 10 PM cap.</t>
+          <t>Overall tournament span: Aug 15, 8:00 AM start → Aug 16, 3:54 PM finish — comfortably inside the Aug 16, 10 PM cap.</t>
         </is>
       </c>
       <c r="F34" s="31" t="n"/>
@@ -2514,952 +2514,952 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="27" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B31" s="27" t="inlineStr">
+      <c r="A31" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B31" s="94" t="inlineStr">
         <is>
           <t>8:00AM</t>
         </is>
       </c>
-      <c r="C31" s="27" t="inlineStr">
+      <c r="C31" s="94" t="inlineStr">
         <is>
           <t>8:18AM</t>
         </is>
       </c>
-      <c r="D31" s="27" t="inlineStr">
+      <c r="D31" s="94" t="inlineStr">
         <is>
           <t>15-25 Bracket</t>
         </is>
       </c>
-      <c r="E31" s="27" t="n">
+      <c r="E31" s="94" t="n">
         <v>1</v>
       </c>
-      <c r="F31" s="27" t="inlineStr">
+      <c r="F31" s="94" t="inlineStr">
         <is>
           <t>GC-1</t>
         </is>
       </c>
-      <c r="G31" s="27" t="inlineStr">
+      <c r="G31" s="94" t="inlineStr">
         <is>
           <t>Court 1</t>
         </is>
       </c>
-      <c r="H31" s="27" t="inlineStr">
+      <c r="H31" s="94" t="inlineStr">
         <is>
           <t>Aaditya Kumar</t>
         </is>
       </c>
-      <c r="I31" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J31" s="27" t="inlineStr">
+      <c r="I31" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J31" s="94" t="inlineStr">
         <is>
           <t>Hryday Goyal</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="28" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B32" s="28" t="inlineStr">
+      <c r="A32" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B32" s="95" t="inlineStr">
         <is>
           <t>8:18AM</t>
         </is>
       </c>
-      <c r="C32" s="28" t="inlineStr">
+      <c r="C32" s="95" t="inlineStr">
         <is>
           <t>8:36AM</t>
         </is>
       </c>
-      <c r="D32" s="28" t="inlineStr">
+      <c r="D32" s="95" t="inlineStr">
         <is>
           <t>Under 15</t>
         </is>
       </c>
-      <c r="E32" s="28" t="n">
+      <c r="E32" s="95" t="n">
         <v>2</v>
       </c>
-      <c r="F32" s="28" t="inlineStr">
+      <c r="F32" s="95" t="inlineStr">
         <is>
           <t>U15-R1-M1</t>
         </is>
       </c>
-      <c r="G32" s="28" t="inlineStr">
+      <c r="G32" s="95" t="inlineStr">
         <is>
           <t>Court 1</t>
         </is>
       </c>
-      <c r="H32" s="28" t="inlineStr">
+      <c r="H32" s="95" t="inlineStr">
         <is>
           <t>Peher Krunal Shah</t>
         </is>
       </c>
-      <c r="I32" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J32" s="28" t="inlineStr">
+      <c r="I32" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J32" s="95" t="inlineStr">
         <is>
           <t>Aadit Joshi</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="27" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B33" s="27" t="inlineStr">
+      <c r="A33" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B33" s="94" t="inlineStr">
         <is>
           <t>8:36AM</t>
         </is>
       </c>
-      <c r="C33" s="27" t="inlineStr">
+      <c r="C33" s="94" t="inlineStr">
         <is>
           <t>8:54AM</t>
         </is>
       </c>
-      <c r="D33" s="27" t="inlineStr">
+      <c r="D33" s="94" t="inlineStr">
         <is>
           <t>Under 15</t>
         </is>
       </c>
-      <c r="E33" s="27" t="n">
+      <c r="E33" s="94" t="n">
         <v>3</v>
       </c>
-      <c r="F33" s="27" t="inlineStr">
+      <c r="F33" s="94" t="inlineStr">
         <is>
           <t>U15-R1-M2</t>
         </is>
       </c>
-      <c r="G33" s="27" t="inlineStr">
+      <c r="G33" s="94" t="inlineStr">
         <is>
           <t>Court 1</t>
         </is>
       </c>
-      <c r="H33" s="27" t="inlineStr">
+      <c r="H33" s="94" t="inlineStr">
         <is>
           <t>Shaurya Tripathi</t>
         </is>
       </c>
-      <c r="I33" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J33" s="27" t="inlineStr">
+      <c r="I33" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J33" s="94" t="inlineStr">
         <is>
           <t>Parth yadav</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="28" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B34" s="28" t="inlineStr">
+      <c r="A34" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B34" s="95" t="inlineStr">
         <is>
           <t>8:54AM</t>
         </is>
       </c>
-      <c r="C34" s="28" t="inlineStr">
+      <c r="C34" s="95" t="inlineStr">
         <is>
           <t>9:12AM</t>
         </is>
       </c>
-      <c r="D34" s="28" t="inlineStr">
+      <c r="D34" s="95" t="inlineStr">
         <is>
           <t>Above 25 Bracket</t>
         </is>
       </c>
-      <c r="E34" s="28" t="n">
+      <c r="E34" s="95" t="n">
         <v>4</v>
       </c>
-      <c r="F34" s="28" t="inlineStr">
+      <c r="F34" s="95" t="inlineStr">
         <is>
           <t>GB-1</t>
         </is>
       </c>
-      <c r="G34" s="28" t="inlineStr">
+      <c r="G34" s="95" t="inlineStr">
         <is>
           <t>Court 1</t>
         </is>
       </c>
-      <c r="H34" s="28" t="inlineStr">
+      <c r="H34" s="95" t="inlineStr">
         <is>
           <t>Ravi Modi</t>
         </is>
       </c>
-      <c r="I34" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J34" s="28" t="inlineStr">
+      <c r="I34" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J34" s="95" t="inlineStr">
         <is>
           <t>Tejas doshi</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="27" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B35" s="27" t="inlineStr">
+      <c r="A35" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B35" s="94" t="inlineStr">
         <is>
           <t>9:12AM</t>
         </is>
       </c>
-      <c r="C35" s="27" t="inlineStr">
+      <c r="C35" s="94" t="inlineStr">
         <is>
           <t>9:30AM</t>
         </is>
       </c>
-      <c r="D35" s="27" t="inlineStr">
+      <c r="D35" s="94" t="inlineStr">
         <is>
           <t>15-25 Bracket</t>
         </is>
       </c>
-      <c r="E35" s="27" t="n">
+      <c r="E35" s="94" t="n">
         <v>5</v>
       </c>
-      <c r="F35" s="27" t="inlineStr">
+      <c r="F35" s="94" t="inlineStr">
         <is>
           <t>GC-2</t>
         </is>
       </c>
-      <c r="G35" s="27" t="inlineStr">
+      <c r="G35" s="94" t="inlineStr">
         <is>
           <t>Court 1</t>
         </is>
       </c>
-      <c r="H35" s="27" t="inlineStr">
+      <c r="H35" s="94" t="inlineStr">
         <is>
           <t>Aaditya Kumar</t>
         </is>
       </c>
-      <c r="I35" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J35" s="27" t="inlineStr">
+      <c r="I35" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J35" s="94" t="inlineStr">
         <is>
           <t>Shravan Gajera</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="28" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B36" s="28" t="inlineStr">
+      <c r="A36" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B36" s="95" t="inlineStr">
         <is>
           <t>10:30AM</t>
         </is>
       </c>
-      <c r="C36" s="28" t="inlineStr">
+      <c r="C36" s="95" t="inlineStr">
         <is>
           <t>10:48AM</t>
         </is>
       </c>
-      <c r="D36" s="28" t="inlineStr">
+      <c r="D36" s="95" t="inlineStr">
         <is>
           <t>Under 15</t>
         </is>
       </c>
-      <c r="E36" s="28" t="n">
+      <c r="E36" s="95" t="n">
         <v>6</v>
       </c>
-      <c r="F36" s="28" t="inlineStr">
+      <c r="F36" s="95" t="inlineStr">
         <is>
           <t>U15-R1-M3</t>
         </is>
       </c>
-      <c r="G36" s="28" t="inlineStr">
+      <c r="G36" s="95" t="inlineStr">
         <is>
           <t>Court 1</t>
         </is>
       </c>
-      <c r="H36" s="28" t="inlineStr">
+      <c r="H36" s="95" t="inlineStr">
         <is>
           <t>Viaan Neema</t>
         </is>
       </c>
-      <c r="I36" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J36" s="28" t="inlineStr">
+      <c r="I36" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J36" s="95" t="inlineStr">
         <is>
           <t>Yash agarwal</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="27" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B37" s="27" t="inlineStr">
-        <is>
-          <t>11:00AM</t>
-        </is>
-      </c>
-      <c r="C37" s="27" t="inlineStr">
-        <is>
-          <t>11:18AM</t>
-        </is>
-      </c>
-      <c r="D37" s="27" t="inlineStr">
+      <c r="A37" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B37" s="94" t="inlineStr">
+        <is>
+          <t>10:48AM</t>
+        </is>
+      </c>
+      <c r="C37" s="94" t="inlineStr">
+        <is>
+          <t>11:06AM</t>
+        </is>
+      </c>
+      <c r="D37" s="94" t="inlineStr">
         <is>
           <t>Above 25 Bracket</t>
         </is>
       </c>
-      <c r="E37" s="27" t="n">
+      <c r="E37" s="94" t="n">
         <v>7</v>
       </c>
-      <c r="F37" s="27" t="inlineStr">
+      <c r="F37" s="94" t="inlineStr">
         <is>
           <t>GA-1</t>
         </is>
       </c>
-      <c r="G37" s="27" t="inlineStr">
+      <c r="G37" s="94" t="inlineStr">
         <is>
           <t>Court 1</t>
         </is>
       </c>
-      <c r="H37" s="27" t="inlineStr">
+      <c r="H37" s="94" t="inlineStr">
         <is>
           <t>Dr Rahul Modi</t>
         </is>
       </c>
-      <c r="I37" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J37" s="27" t="inlineStr">
+      <c r="I37" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J37" s="94" t="inlineStr">
         <is>
           <t>Mayank Aggarwal</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="28" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B38" s="28" t="inlineStr">
-        <is>
-          <t>11:28AM</t>
-        </is>
-      </c>
-      <c r="C38" s="28" t="inlineStr">
-        <is>
-          <t>11:46AM</t>
-        </is>
-      </c>
-      <c r="D38" s="28" t="inlineStr">
+      <c r="A38" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B38" s="95" t="inlineStr">
+        <is>
+          <t>11:06AM</t>
+        </is>
+      </c>
+      <c r="C38" s="95" t="inlineStr">
+        <is>
+          <t>11:24AM</t>
+        </is>
+      </c>
+      <c r="D38" s="95" t="inlineStr">
+        <is>
+          <t>Under 15</t>
+        </is>
+      </c>
+      <c r="E38" s="95" t="n">
+        <v>8</v>
+      </c>
+      <c r="F38" s="95" t="inlineStr">
+        <is>
+          <t>U15-SF1</t>
+        </is>
+      </c>
+      <c r="G38" s="95" t="inlineStr">
+        <is>
+          <t>Court 1</t>
+        </is>
+      </c>
+      <c r="H38" s="95" t="inlineStr">
+        <is>
+          <t>Winner R1-M2</t>
+        </is>
+      </c>
+      <c r="I38" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J38" s="95" t="inlineStr">
+        <is>
+          <t>Hridh jhala</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B39" s="94" t="inlineStr">
+        <is>
+          <t>11:24AM</t>
+        </is>
+      </c>
+      <c r="C39" s="94" t="inlineStr">
+        <is>
+          <t>11:42AM</t>
+        </is>
+      </c>
+      <c r="D39" s="94" t="inlineStr">
         <is>
           <t>Above 25 Bracket</t>
         </is>
       </c>
-      <c r="E38" s="28" t="n">
-        <v>8</v>
-      </c>
-      <c r="F38" s="28" t="inlineStr">
+      <c r="E39" s="94" t="n">
+        <v>9</v>
+      </c>
+      <c r="F39" s="94" t="inlineStr">
         <is>
           <t>GA-2</t>
         </is>
       </c>
-      <c r="G38" s="28" t="inlineStr">
+      <c r="G39" s="94" t="inlineStr">
         <is>
           <t>Court 1</t>
         </is>
       </c>
-      <c r="H38" s="28" t="inlineStr">
+      <c r="H39" s="94" t="inlineStr">
         <is>
           <t>Dr Rahul Modi</t>
         </is>
       </c>
-      <c r="I38" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J38" s="28" t="inlineStr">
+      <c r="I39" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J39" s="94" t="inlineStr">
         <is>
           <t>Tanmay Sharma</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="27" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B39" s="27" t="inlineStr">
-        <is>
-          <t>3:20PM</t>
-        </is>
-      </c>
-      <c r="C39" s="27" t="inlineStr">
-        <is>
-          <t>3:38PM</t>
-        </is>
-      </c>
-      <c r="D39" s="27" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B40" s="95" t="inlineStr">
+        <is>
+          <t>11:42AM</t>
+        </is>
+      </c>
+      <c r="C40" s="95" t="inlineStr">
+        <is>
+          <t>12:00PM</t>
+        </is>
+      </c>
+      <c r="D40" s="95" t="inlineStr">
+        <is>
+          <t>Under 15</t>
+        </is>
+      </c>
+      <c r="E40" s="95" t="n">
+        <v>10</v>
+      </c>
+      <c r="F40" s="95" t="inlineStr">
+        <is>
+          <t>U15-SF2</t>
+        </is>
+      </c>
+      <c r="G40" s="95" t="inlineStr">
+        <is>
+          <t>Court 1</t>
+        </is>
+      </c>
+      <c r="H40" s="95" t="inlineStr">
+        <is>
+          <t>Winner R1-M1</t>
+        </is>
+      </c>
+      <c r="I40" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J40" s="95" t="inlineStr">
+        <is>
+          <t>Winner R1-M3</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B41" s="94" t="inlineStr">
+        <is>
+          <t>3:00PM</t>
+        </is>
+      </c>
+      <c r="C41" s="94" t="inlineStr">
+        <is>
+          <t>3:18PM</t>
+        </is>
+      </c>
+      <c r="D41" s="94" t="inlineStr">
+        <is>
+          <t>Above 25 Bracket</t>
+        </is>
+      </c>
+      <c r="E41" s="94" t="n">
+        <v>11</v>
+      </c>
+      <c r="F41" s="94" t="inlineStr">
+        <is>
+          <t>GA-3</t>
+        </is>
+      </c>
+      <c r="G41" s="94" t="inlineStr">
+        <is>
+          <t>Court 1</t>
+        </is>
+      </c>
+      <c r="H41" s="94" t="inlineStr">
+        <is>
+          <t>Tanmay Sharma</t>
+        </is>
+      </c>
+      <c r="I41" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J41" s="94" t="inlineStr">
+        <is>
+          <t>Mayank Aggarwal</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B42" s="95" t="inlineStr">
+        <is>
+          <t>3:18PM</t>
+        </is>
+      </c>
+      <c r="C42" s="95" t="inlineStr">
+        <is>
+          <t>3:36PM</t>
+        </is>
+      </c>
+      <c r="D42" s="95" t="inlineStr">
         <is>
           <t>15-25 Bracket</t>
         </is>
       </c>
-      <c r="E39" s="27" t="n">
-        <v>9</v>
-      </c>
-      <c r="F39" s="27" t="inlineStr">
+      <c r="E42" s="95" t="n">
+        <v>12</v>
+      </c>
+      <c r="F42" s="95" t="inlineStr">
         <is>
           <t>GC-3</t>
         </is>
       </c>
-      <c r="G39" s="27" t="inlineStr">
+      <c r="G42" s="95" t="inlineStr">
         <is>
           <t>Court 1</t>
         </is>
       </c>
-      <c r="H39" s="27" t="inlineStr">
+      <c r="H42" s="95" t="inlineStr">
         <is>
           <t>Hryday Goyal</t>
         </is>
       </c>
-      <c r="I39" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J39" s="27" t="inlineStr">
+      <c r="I42" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J42" s="95" t="inlineStr">
         <is>
           <t>Shravan Gajera</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="28" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B40" s="28" t="inlineStr">
-        <is>
-          <t>5:35PM</t>
-        </is>
-      </c>
-      <c r="C40" s="28" t="inlineStr">
-        <is>
-          <t>5:53PM</t>
-        </is>
-      </c>
-      <c r="D40" s="28" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B43" s="94" t="inlineStr">
+        <is>
+          <t>4:20PM</t>
+        </is>
+      </c>
+      <c r="C43" s="94" t="inlineStr">
+        <is>
+          <t>4:38PM</t>
+        </is>
+      </c>
+      <c r="D43" s="94" t="inlineStr">
         <is>
           <t>Above 25 Bracket</t>
         </is>
       </c>
-      <c r="E40" s="28" t="n">
-        <v>10</v>
-      </c>
-      <c r="F40" s="28" t="inlineStr">
-        <is>
-          <t>GA-3</t>
-        </is>
-      </c>
-      <c r="G40" s="28" t="inlineStr">
+      <c r="E43" s="94" t="n">
+        <v>13</v>
+      </c>
+      <c r="F43" s="94" t="inlineStr">
+        <is>
+          <t>GB-3</t>
+        </is>
+      </c>
+      <c r="G43" s="94" t="inlineStr">
         <is>
           <t>Court 1</t>
         </is>
       </c>
-      <c r="H40" s="28" t="inlineStr">
-        <is>
-          <t>Tanmay Sharma</t>
-        </is>
-      </c>
-      <c r="I40" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J40" s="28" t="inlineStr">
-        <is>
-          <t>Mayank Aggarwal</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="27" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B41" s="27" t="inlineStr">
-        <is>
-          <t>5:53PM</t>
-        </is>
-      </c>
-      <c r="C41" s="27" t="inlineStr">
-        <is>
-          <t>6:11PM</t>
-        </is>
-      </c>
-      <c r="D41" s="27" t="inlineStr">
+      <c r="H43" s="94" t="inlineStr">
+        <is>
+          <t>Tejas doshi</t>
+        </is>
+      </c>
+      <c r="I43" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J43" s="94" t="inlineStr">
+        <is>
+          <t>Vinit Padia</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B44" s="95" t="inlineStr">
+        <is>
+          <t>5:30PM</t>
+        </is>
+      </c>
+      <c r="C44" s="95" t="inlineStr">
+        <is>
+          <t>5:48PM</t>
+        </is>
+      </c>
+      <c r="D44" s="95" t="inlineStr">
         <is>
           <t>Above 25 Bracket</t>
         </is>
       </c>
-      <c r="E41" s="27" t="n">
-        <v>11</v>
-      </c>
-      <c r="F41" s="27" t="inlineStr">
+      <c r="E44" s="95" t="n">
+        <v>14</v>
+      </c>
+      <c r="F44" s="95" t="inlineStr">
         <is>
           <t>GB-2</t>
         </is>
       </c>
-      <c r="G41" s="27" t="inlineStr">
+      <c r="G44" s="95" t="inlineStr">
         <is>
           <t>Court 1</t>
         </is>
       </c>
-      <c r="H41" s="27" t="inlineStr">
+      <c r="H44" s="95" t="inlineStr">
         <is>
           <t>Ravi Modi</t>
         </is>
       </c>
-      <c r="I41" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J41" s="27" t="inlineStr">
+      <c r="I44" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J44" s="95" t="inlineStr">
         <is>
           <t>Vinit Padia</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="28" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B42" s="28" t="inlineStr">
-        <is>
-          <t>6:21PM</t>
-        </is>
-      </c>
-      <c r="C42" s="28" t="inlineStr">
-        <is>
-          <t>6:39PM</t>
-        </is>
-      </c>
-      <c r="D42" s="28" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B45" s="94" t="inlineStr">
+        <is>
+          <t>5:48PM</t>
+        </is>
+      </c>
+      <c r="C45" s="94" t="inlineStr">
+        <is>
+          <t>6:06PM</t>
+        </is>
+      </c>
+      <c r="D45" s="94" t="inlineStr">
         <is>
           <t>Above 25 Bracket</t>
         </is>
       </c>
-      <c r="E42" s="28" t="n">
-        <v>12</v>
-      </c>
-      <c r="F42" s="28" t="inlineStr">
-        <is>
-          <t>GB-3</t>
-        </is>
-      </c>
-      <c r="G42" s="28" t="inlineStr">
+      <c r="E45" s="94" t="n">
+        <v>15</v>
+      </c>
+      <c r="F45" s="94" t="inlineStr">
+        <is>
+          <t>A25-SF1</t>
+        </is>
+      </c>
+      <c r="G45" s="94" t="inlineStr">
         <is>
           <t>Court 1</t>
         </is>
       </c>
-      <c r="H42" s="28" t="inlineStr">
-        <is>
-          <t>Tejas doshi</t>
-        </is>
-      </c>
-      <c r="I42" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J42" s="28" t="inlineStr">
-        <is>
-          <t>Vinit Padia</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="27" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B43" s="27" t="inlineStr">
-        <is>
-          <t>6:39PM</t>
-        </is>
-      </c>
-      <c r="C43" s="27" t="inlineStr">
-        <is>
-          <t>6:57PM</t>
-        </is>
-      </c>
-      <c r="D43" s="27" t="inlineStr">
+      <c r="H45" s="94" t="inlineStr">
+        <is>
+          <t>Group A 1st</t>
+        </is>
+      </c>
+      <c r="I45" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J45" s="94" t="inlineStr">
+        <is>
+          <t>Group B 2nd</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B46" s="95" t="inlineStr">
+        <is>
+          <t>6:06PM</t>
+        </is>
+      </c>
+      <c r="C46" s="95" t="inlineStr">
+        <is>
+          <t>6:24PM</t>
+        </is>
+      </c>
+      <c r="D46" s="95" t="inlineStr">
+        <is>
+          <t>Above 25 Bracket</t>
+        </is>
+      </c>
+      <c r="E46" s="95" t="n">
+        <v>16</v>
+      </c>
+      <c r="F46" s="95" t="inlineStr">
+        <is>
+          <t>A25-SF2</t>
+        </is>
+      </c>
+      <c r="G46" s="95" t="inlineStr">
+        <is>
+          <t>Court 1</t>
+        </is>
+      </c>
+      <c r="H46" s="95" t="inlineStr">
+        <is>
+          <t>Group B 1st</t>
+        </is>
+      </c>
+      <c r="I46" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J46" s="95" t="inlineStr">
+        <is>
+          <t>Group A 2nd</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="94" t="inlineStr">
+        <is>
+          <t>Aug 16</t>
+        </is>
+      </c>
+      <c r="B47" s="94" t="inlineStr">
+        <is>
+          <t>3:00PM</t>
+        </is>
+      </c>
+      <c r="C47" s="94" t="inlineStr">
+        <is>
+          <t>3:18PM</t>
+        </is>
+      </c>
+      <c r="D47" s="94" t="inlineStr">
         <is>
           <t>Under 15</t>
         </is>
       </c>
-      <c r="E43" s="27" t="n">
-        <v>13</v>
-      </c>
-      <c r="F43" s="27" t="inlineStr">
-        <is>
-          <t>U15-SF1</t>
-        </is>
-      </c>
-      <c r="G43" s="27" t="inlineStr">
+      <c r="E47" s="94" t="n">
+        <v>17</v>
+      </c>
+      <c r="F47" s="94" t="inlineStr">
+        <is>
+          <t>U15-FINAL</t>
+        </is>
+      </c>
+      <c r="G47" s="94" t="inlineStr">
         <is>
           <t>Court 1</t>
         </is>
       </c>
-      <c r="H43" s="27" t="inlineStr">
-        <is>
-          <t>Winner U15-R1-M2</t>
-        </is>
-      </c>
-      <c r="I43" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J43" s="27" t="inlineStr">
-        <is>
-          <t>Hridh jhala (BYE)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="28" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B44" s="28" t="inlineStr">
-        <is>
-          <t>6:57PM</t>
-        </is>
-      </c>
-      <c r="C44" s="28" t="inlineStr">
-        <is>
-          <t>7:15PM</t>
-        </is>
-      </c>
-      <c r="D44" s="28" t="inlineStr">
-        <is>
-          <t>Under 15</t>
-        </is>
-      </c>
-      <c r="E44" s="28" t="n">
-        <v>14</v>
-      </c>
-      <c r="F44" s="28" t="inlineStr">
-        <is>
-          <t>U15-SF2</t>
-        </is>
-      </c>
-      <c r="G44" s="28" t="inlineStr">
+      <c r="H47" s="94" t="inlineStr">
+        <is>
+          <t>Winner SF1</t>
+        </is>
+      </c>
+      <c r="I47" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J47" s="94" t="inlineStr">
+        <is>
+          <t>Winner SF2</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="95" t="inlineStr">
+        <is>
+          <t>Aug 16</t>
+        </is>
+      </c>
+      <c r="B48" s="95" t="inlineStr">
+        <is>
+          <t>3:18PM</t>
+        </is>
+      </c>
+      <c r="C48" s="95" t="inlineStr">
+        <is>
+          <t>3:36PM</t>
+        </is>
+      </c>
+      <c r="D48" s="95" t="inlineStr">
+        <is>
+          <t>15-25 Bracket</t>
+        </is>
+      </c>
+      <c r="E48" s="95" t="n">
+        <v>18</v>
+      </c>
+      <c r="F48" s="95" t="inlineStr">
+        <is>
+          <t>GC-FINAL</t>
+        </is>
+      </c>
+      <c r="G48" s="95" t="inlineStr">
         <is>
           <t>Court 1</t>
         </is>
       </c>
-      <c r="H44" s="28" t="inlineStr">
-        <is>
-          <t>Winner U15-R1-M1</t>
-        </is>
-      </c>
-      <c r="I44" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J44" s="28" t="inlineStr">
-        <is>
-          <t>Winner U15-R1-M3</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="27" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B45" s="27" t="inlineStr">
-        <is>
-          <t>7:15PM</t>
-        </is>
-      </c>
-      <c r="C45" s="27" t="inlineStr">
-        <is>
-          <t>7:33PM</t>
-        </is>
-      </c>
-      <c r="D45" s="27" t="inlineStr">
-        <is>
-          <t>Under 15</t>
-        </is>
-      </c>
-      <c r="E45" s="27" t="n">
-        <v>15</v>
-      </c>
-      <c r="F45" s="27" t="inlineStr">
-        <is>
-          <t>U15-FINAL</t>
-        </is>
-      </c>
-      <c r="G45" s="27" t="inlineStr">
+      <c r="H48" s="95" t="inlineStr">
+        <is>
+          <t>Pool 1st</t>
+        </is>
+      </c>
+      <c r="I48" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J48" s="95" t="inlineStr">
+        <is>
+          <t>Pool 2nd</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="94" t="inlineStr">
+        <is>
+          <t>Aug 16</t>
+        </is>
+      </c>
+      <c r="B49" s="94" t="inlineStr">
+        <is>
+          <t>3:36PM</t>
+        </is>
+      </c>
+      <c r="C49" s="94" t="inlineStr">
+        <is>
+          <t>3:54PM</t>
+        </is>
+      </c>
+      <c r="D49" s="94" t="inlineStr">
+        <is>
+          <t>Above 25 Bracket</t>
+        </is>
+      </c>
+      <c r="E49" s="94" t="n">
+        <v>19</v>
+      </c>
+      <c r="F49" s="94" t="inlineStr">
+        <is>
+          <t>A25-FINAL</t>
+        </is>
+      </c>
+      <c r="G49" s="94" t="inlineStr">
         <is>
           <t>Court 1</t>
         </is>
       </c>
-      <c r="H45" s="27" t="inlineStr">
-        <is>
-          <t>Winner U15-SF1</t>
-        </is>
-      </c>
-      <c r="I45" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J45" s="27" t="inlineStr">
-        <is>
-          <t>Winner U15-SF2</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="28" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B46" s="28" t="inlineStr">
-        <is>
-          <t>7:33PM</t>
-        </is>
-      </c>
-      <c r="C46" s="28" t="inlineStr">
-        <is>
-          <t>7:51PM</t>
-        </is>
-      </c>
-      <c r="D46" s="28" t="inlineStr">
-        <is>
-          <t>15-25 Bracket</t>
-        </is>
-      </c>
-      <c r="E46" s="28" t="n">
-        <v>16</v>
-      </c>
-      <c r="F46" s="28" t="inlineStr">
-        <is>
-          <t>GC-FINAL</t>
-        </is>
-      </c>
-      <c r="G46" s="28" t="inlineStr">
-        <is>
-          <t>Court 1</t>
-        </is>
-      </c>
-      <c r="H46" s="28" t="inlineStr">
-        <is>
-          <t>Pool 1st</t>
-        </is>
-      </c>
-      <c r="I46" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J46" s="28" t="inlineStr">
-        <is>
-          <t>Pool 2nd</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="27" t="inlineStr">
-        <is>
-          <t>Aug 16</t>
-        </is>
-      </c>
-      <c r="B47" s="27" t="inlineStr">
-        <is>
-          <t>3:20PM</t>
-        </is>
-      </c>
-      <c r="C47" s="27" t="inlineStr">
-        <is>
-          <t>3:38PM</t>
-        </is>
-      </c>
-      <c r="D47" s="27" t="inlineStr">
-        <is>
-          <t>Above 25 Bracket</t>
-        </is>
-      </c>
-      <c r="E47" s="27" t="n">
-        <v>17</v>
-      </c>
-      <c r="F47" s="27" t="inlineStr">
-        <is>
-          <t>A25-SF1</t>
-        </is>
-      </c>
-      <c r="G47" s="27" t="inlineStr">
-        <is>
-          <t>Court 1</t>
-        </is>
-      </c>
-      <c r="H47" s="27" t="inlineStr">
-        <is>
-          <t>Group A 1st</t>
-        </is>
-      </c>
-      <c r="I47" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J47" s="27" t="inlineStr">
-        <is>
-          <t>Group B 2nd</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="28" t="inlineStr">
-        <is>
-          <t>Aug 16</t>
-        </is>
-      </c>
-      <c r="B48" s="28" t="inlineStr">
-        <is>
-          <t>3:38PM</t>
-        </is>
-      </c>
-      <c r="C48" s="28" t="inlineStr">
-        <is>
-          <t>3:56PM</t>
-        </is>
-      </c>
-      <c r="D48" s="28" t="inlineStr">
-        <is>
-          <t>Above 25 Bracket</t>
-        </is>
-      </c>
-      <c r="E48" s="28" t="n">
-        <v>18</v>
-      </c>
-      <c r="F48" s="28" t="inlineStr">
-        <is>
-          <t>A25-SF2</t>
-        </is>
-      </c>
-      <c r="G48" s="28" t="inlineStr">
-        <is>
-          <t>Court 1</t>
-        </is>
-      </c>
-      <c r="H48" s="28" t="inlineStr">
-        <is>
-          <t>Group B 1st</t>
-        </is>
-      </c>
-      <c r="I48" s="28" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J48" s="28" t="inlineStr">
-        <is>
-          <t>Group A 2nd</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="27" t="inlineStr">
-        <is>
-          <t>Aug 16</t>
-        </is>
-      </c>
-      <c r="B49" s="27" t="inlineStr">
-        <is>
-          <t>3:56PM</t>
-        </is>
-      </c>
-      <c r="C49" s="27" t="inlineStr">
-        <is>
-          <t>4:14PM</t>
-        </is>
-      </c>
-      <c r="D49" s="27" t="inlineStr">
-        <is>
-          <t>Above 25 Bracket</t>
-        </is>
-      </c>
-      <c r="E49" s="27" t="n">
-        <v>19</v>
-      </c>
-      <c r="F49" s="27" t="inlineStr">
-        <is>
-          <t>A25-FINAL</t>
-        </is>
-      </c>
-      <c r="G49" s="27" t="inlineStr">
-        <is>
-          <t>Court 1</t>
-        </is>
-      </c>
-      <c r="H49" s="27" t="inlineStr">
-        <is>
-          <t>Winner A25-SF1</t>
-        </is>
-      </c>
-      <c r="I49" s="27" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J49" s="27" t="inlineStr">
-        <is>
-          <t>Winner A25-SF2</t>
+      <c r="H49" s="94" t="inlineStr">
+        <is>
+          <t>Winner SF1</t>
+        </is>
+      </c>
+      <c r="I49" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J49" s="94" t="inlineStr">
+        <is>
+          <t>Winner SF2</t>
         </is>
       </c>
     </row>

--- a/Ekta_Schedule_With_Matchups.xlsx
+++ b/Ekta_Schedule_With_Matchups.xlsx
@@ -1242,7 +1242,7 @@
       </c>
       <c r="C15" s="64" t="inlineStr">
         <is>
-          <t>League stage continues. TT Women's Singles (done 12:00 PM) and Carrom Women's Singles (done ~11:30 AM) each finish in full today. TT Men's Singles (Above 46 knockout leads off Table 2 at 8:00 AM) and Carrom Men's Singles (done ~5:45 PM) both now run almost entirely today too, with Chess and Pool likewise wrapping up today or overnight — all five were reflowed to use real gaps in players' other-sport schedules instead of sitting on idle tables/boards.</t>
+          <t>League stage continues. TT Women's Singles is deliberately held to start at 10:30 AM (not 8:00 AM), with its semifinal and final held further to 3:00-3:30 PM — both by request, freeing up Table 1/2 all morning for TT Men's Singles (Above 46 knockout leads off Table 2 at 8:00 AM) and Carrom Men's Singles (done ~5:45 PM), with Chess and Pool likewise wrapping up today or overnight — all reflowed to use real gaps in players' other-sport schedules instead of sitting on idle tables/boards.</t>
         </is>
       </c>
       <c r="H15" s="31" t="n"/>
@@ -1411,12 +1411,12 @@
       </c>
       <c r="D24" s="63" t="inlineStr">
         <is>
-          <t>Aug15 8:45AM</t>
+          <t>Aug15 10:30AM</t>
         </is>
       </c>
       <c r="E24" s="63" t="inlineStr">
         <is>
-          <t>Aug15 12:00PM</t>
+          <t>Aug15 3:30PM</t>
         </is>
       </c>
       <c r="F24" s="31" t="n"/>
@@ -4972,12 +4972,12 @@
       </c>
       <c r="B16" s="94" t="inlineStr">
         <is>
-          <t>8:45AM</t>
+          <t>10:30AM</t>
         </is>
       </c>
       <c r="C16" s="94" t="inlineStr">
         <is>
-          <t>9:00AM</t>
+          <t>10:45AM</t>
         </is>
       </c>
       <c r="D16" s="94" t="inlineStr">
@@ -4995,7 +4995,7 @@
       </c>
       <c r="G16" s="94" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H16" s="94" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="B17" s="95" t="inlineStr">
         <is>
-          <t>9:00AM</t>
+          <t>10:30AM</t>
         </is>
       </c>
       <c r="C17" s="95" t="inlineStr">
         <is>
-          <t>9:15AM</t>
+          <t>10:45AM</t>
         </is>
       </c>
       <c r="D17" s="95" t="inlineStr">
@@ -5045,7 +5045,7 @@
       </c>
       <c r="G17" s="95" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H17" s="95" t="inlineStr">
@@ -5072,12 +5072,12 @@
       </c>
       <c r="B18" s="94" t="inlineStr">
         <is>
-          <t>9:00AM</t>
+          <t>10:45AM</t>
         </is>
       </c>
       <c r="C18" s="94" t="inlineStr">
         <is>
-          <t>9:15AM</t>
+          <t>11:00AM</t>
         </is>
       </c>
       <c r="D18" s="94" t="inlineStr">
@@ -5095,7 +5095,7 @@
       </c>
       <c r="G18" s="94" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H18" s="94" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="B19" s="95" t="inlineStr">
         <is>
-          <t>9:15AM</t>
+          <t>10:45AM</t>
         </is>
       </c>
       <c r="C19" s="95" t="inlineStr">
         <is>
-          <t>9:30AM</t>
+          <t>11:00AM</t>
         </is>
       </c>
       <c r="D19" s="95" t="inlineStr">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="G19" s="95" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H19" s="95" t="inlineStr">
@@ -5172,12 +5172,12 @@
       </c>
       <c r="B20" s="94" t="inlineStr">
         <is>
-          <t>10:30AM</t>
+          <t>11:00AM</t>
         </is>
       </c>
       <c r="C20" s="94" t="inlineStr">
         <is>
-          <t>10:45AM</t>
+          <t>11:15AM</t>
         </is>
       </c>
       <c r="D20" s="94" t="inlineStr">
@@ -5222,12 +5222,12 @@
       </c>
       <c r="B21" s="95" t="inlineStr">
         <is>
-          <t>10:30AM</t>
+          <t>11:00AM</t>
         </is>
       </c>
       <c r="C21" s="95" t="inlineStr">
         <is>
-          <t>10:45AM</t>
+          <t>11:15AM</t>
         </is>
       </c>
       <c r="D21" s="95" t="inlineStr">
@@ -5272,12 +5272,12 @@
       </c>
       <c r="B22" s="94" t="inlineStr">
         <is>
-          <t>10:45AM</t>
+          <t>11:15AM</t>
         </is>
       </c>
       <c r="C22" s="94" t="inlineStr">
         <is>
-          <t>11:00AM</t>
+          <t>11:30AM</t>
         </is>
       </c>
       <c r="D22" s="94" t="inlineStr">
@@ -5322,12 +5322,12 @@
       </c>
       <c r="B23" s="95" t="inlineStr">
         <is>
-          <t>10:45AM</t>
+          <t>11:15AM</t>
         </is>
       </c>
       <c r="C23" s="95" t="inlineStr">
         <is>
-          <t>11:00AM</t>
+          <t>11:30AM</t>
         </is>
       </c>
       <c r="D23" s="95" t="inlineStr">
@@ -5372,12 +5372,12 @@
       </c>
       <c r="B24" s="94" t="inlineStr">
         <is>
-          <t>11:00AM</t>
+          <t>11:30AM</t>
         </is>
       </c>
       <c r="C24" s="94" t="inlineStr">
         <is>
-          <t>11:15AM</t>
+          <t>11:45AM</t>
         </is>
       </c>
       <c r="D24" s="94" t="inlineStr">
@@ -5422,12 +5422,12 @@
       </c>
       <c r="B25" s="95" t="inlineStr">
         <is>
-          <t>11:00AM</t>
+          <t>11:30AM</t>
         </is>
       </c>
       <c r="C25" s="95" t="inlineStr">
         <is>
-          <t>11:15AM</t>
+          <t>11:45AM</t>
         </is>
       </c>
       <c r="D25" s="95" t="inlineStr">
@@ -5472,12 +5472,12 @@
       </c>
       <c r="B26" s="94" t="inlineStr">
         <is>
-          <t>11:15AM</t>
+          <t>11:45AM</t>
         </is>
       </c>
       <c r="C26" s="94" t="inlineStr">
         <is>
-          <t>11:30AM</t>
+          <t>12:00PM</t>
         </is>
       </c>
       <c r="D26" s="94" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="B27" s="95" t="inlineStr">
         <is>
-          <t>11:15AM</t>
+          <t>11:45AM</t>
         </is>
       </c>
       <c r="C27" s="95" t="inlineStr">
         <is>
-          <t>11:30AM</t>
+          <t>12:00PM</t>
         </is>
       </c>
       <c r="D27" s="95" t="inlineStr">
@@ -5572,12 +5572,12 @@
       </c>
       <c r="B28" s="94" t="inlineStr">
         <is>
-          <t>11:30AM</t>
+          <t>3:00PM</t>
         </is>
       </c>
       <c r="C28" s="94" t="inlineStr">
         <is>
-          <t>11:45AM</t>
+          <t>3:15PM</t>
         </is>
       </c>
       <c r="D28" s="94" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="B29" s="95" t="inlineStr">
         <is>
-          <t>11:30AM</t>
+          <t>3:00PM</t>
         </is>
       </c>
       <c r="C29" s="95" t="inlineStr">
         <is>
-          <t>11:45AM</t>
+          <t>3:15PM</t>
         </is>
       </c>
       <c r="D29" s="95" t="inlineStr">
@@ -5672,12 +5672,12 @@
       </c>
       <c r="B30" s="94" t="inlineStr">
         <is>
-          <t>11:45AM</t>
+          <t>3:15PM</t>
         </is>
       </c>
       <c r="C30" s="94" t="inlineStr">
         <is>
-          <t>12:00PM</t>
+          <t>3:30PM</t>
         </is>
       </c>
       <c r="D30" s="94" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="B56" s="95" t="inlineStr">
         <is>
-          <t>9:15AM</t>
+          <t>8:45AM</t>
         </is>
       </c>
       <c r="C56" s="95" t="inlineStr">
         <is>
-          <t>9:30AM</t>
+          <t>9:00AM</t>
         </is>
       </c>
       <c r="D56" s="95" t="inlineStr">
@@ -6848,17 +6848,17 @@
       </c>
       <c r="B57" s="94" t="inlineStr">
         <is>
-          <t>11:45AM</t>
+          <t>9:00AM</t>
         </is>
       </c>
       <c r="C57" s="94" t="inlineStr">
         <is>
-          <t>12:00PM</t>
+          <t>9:15AM</t>
         </is>
       </c>
       <c r="D57" s="94" t="inlineStr">
         <is>
-          <t>Under 36</t>
+          <t>Under 15</t>
         </is>
       </c>
       <c r="E57" s="94" t="n">
@@ -6866,7 +6866,7 @@
       </c>
       <c r="F57" s="94" t="inlineStr">
         <is>
-          <t>U36-GA-2</t>
+          <t>U15-GA-1</t>
         </is>
       </c>
       <c r="G57" s="94" t="inlineStr">
@@ -6876,7 +6876,7 @@
       </c>
       <c r="H57" s="94" t="inlineStr">
         <is>
-          <t>Jashit Bajaj</t>
+          <t>Shaurya Tripathi</t>
         </is>
       </c>
       <c r="I57" s="94" t="inlineStr">
@@ -6886,7 +6886,7 @@
       </c>
       <c r="J57" s="94" t="inlineStr">
         <is>
-          <t>Tapabrata Dutta</t>
+          <t>Parth yadav</t>
         </is>
       </c>
     </row>
@@ -6898,17 +6898,17 @@
       </c>
       <c r="B58" s="95" t="inlineStr">
         <is>
-          <t>3:00PM</t>
+          <t>9:00AM</t>
         </is>
       </c>
       <c r="C58" s="95" t="inlineStr">
         <is>
-          <t>3:15PM</t>
+          <t>9:15AM</t>
         </is>
       </c>
       <c r="D58" s="95" t="inlineStr">
         <is>
-          <t>Under 15</t>
+          <t>Under 36</t>
         </is>
       </c>
       <c r="E58" s="95" t="n">
@@ -6916,17 +6916,17 @@
       </c>
       <c r="F58" s="95" t="inlineStr">
         <is>
-          <t>U15-GA-1</t>
+          <t>U36-GA-2</t>
         </is>
       </c>
       <c r="G58" s="95" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H58" s="95" t="inlineStr">
         <is>
-          <t>Shaurya Tripathi</t>
+          <t>Jashit Bajaj</t>
         </is>
       </c>
       <c r="I58" s="95" t="inlineStr">
@@ -6936,7 +6936,7 @@
       </c>
       <c r="J58" s="95" t="inlineStr">
         <is>
-          <t>Parth yadav</t>
+          <t>Tapabrata Dutta</t>
         </is>
       </c>
     </row>
@@ -6948,17 +6948,17 @@
       </c>
       <c r="B59" s="94" t="inlineStr">
         <is>
-          <t>3:00PM</t>
+          <t>9:15AM</t>
         </is>
       </c>
       <c r="C59" s="94" t="inlineStr">
         <is>
-          <t>3:15PM</t>
+          <t>9:30AM</t>
         </is>
       </c>
       <c r="D59" s="94" t="inlineStr">
         <is>
-          <t>Under 26</t>
+          <t>Under 15</t>
         </is>
       </c>
       <c r="E59" s="94" t="n">
@@ -6966,17 +6966,17 @@
       </c>
       <c r="F59" s="94" t="inlineStr">
         <is>
-          <t>U26-2</t>
+          <t>U15-GB-1</t>
         </is>
       </c>
       <c r="G59" s="94" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H59" s="94" t="inlineStr">
         <is>
-          <t>Yuvraj jain</t>
+          <t>Viaan Neema</t>
         </is>
       </c>
       <c r="I59" s="94" t="inlineStr">
@@ -6986,7 +6986,7 @@
       </c>
       <c r="J59" s="94" t="inlineStr">
         <is>
-          <t>Hryday Goyal</t>
+          <t>Yash agarwal</t>
         </is>
       </c>
     </row>
@@ -6998,17 +6998,17 @@
       </c>
       <c r="B60" s="95" t="inlineStr">
         <is>
-          <t>3:15PM</t>
+          <t>9:15AM</t>
         </is>
       </c>
       <c r="C60" s="95" t="inlineStr">
         <is>
-          <t>3:30PM</t>
+          <t>9:30AM</t>
         </is>
       </c>
       <c r="D60" s="95" t="inlineStr">
         <is>
-          <t>Under 15</t>
+          <t>Under 26</t>
         </is>
       </c>
       <c r="E60" s="95" t="n">
@@ -7016,17 +7016,17 @@
       </c>
       <c r="F60" s="95" t="inlineStr">
         <is>
-          <t>U15-GB-1</t>
+          <t>U26-2</t>
         </is>
       </c>
       <c r="G60" s="95" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H60" s="95" t="inlineStr">
         <is>
-          <t>Viaan Neema</t>
+          <t>Yuvraj jain</t>
         </is>
       </c>
       <c r="I60" s="95" t="inlineStr">
@@ -7036,7 +7036,7 @@
       </c>
       <c r="J60" s="95" t="inlineStr">
         <is>
-          <t>Yash agarwal</t>
+          <t>Hryday Goyal</t>
         </is>
       </c>
     </row>
@@ -7071,7 +7071,7 @@
       </c>
       <c r="G61" s="94" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H61" s="94" t="inlineStr">
@@ -7121,7 +7121,7 @@
       </c>
       <c r="G62" s="95" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H62" s="95" t="inlineStr">
@@ -7171,7 +7171,7 @@
       </c>
       <c r="G63" s="94" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H63" s="94" t="inlineStr">
@@ -7521,7 +7521,7 @@
       </c>
       <c r="G70" s="95" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H70" s="95" t="inlineStr">
@@ -7571,7 +7571,7 @@
       </c>
       <c r="G71" s="94" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H71" s="94" t="inlineStr">
@@ -7821,7 +7821,7 @@
       </c>
       <c r="G76" s="95" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H76" s="95" t="inlineStr">
@@ -7871,7 +7871,7 @@
       </c>
       <c r="G77" s="94" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H77" s="94" t="inlineStr">
@@ -7921,7 +7921,7 @@
       </c>
       <c r="G78" s="95" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H78" s="95" t="inlineStr">
@@ -7971,7 +7971,7 @@
       </c>
       <c r="G79" s="94" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H79" s="94" t="inlineStr">
@@ -8021,7 +8021,7 @@
       </c>
       <c r="G80" s="95" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H80" s="95" t="inlineStr">
@@ -8071,7 +8071,7 @@
       </c>
       <c r="G81" s="94" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H81" s="94" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="G82" s="95" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H82" s="95" t="inlineStr">
@@ -8171,7 +8171,7 @@
       </c>
       <c r="G83" s="94" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H83" s="94" t="inlineStr">
@@ -8671,7 +8671,7 @@
       </c>
       <c r="G93" s="94" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H93" s="94" t="inlineStr">
@@ -8721,7 +8721,7 @@
       </c>
       <c r="G94" s="95" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H94" s="95" t="inlineStr">
@@ -9778,7 +9778,7 @@
       </c>
       <c r="G20" s="94" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="H20" s="94" t="inlineStr">
@@ -9828,7 +9828,7 @@
       </c>
       <c r="G21" s="95" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="H21" s="95" t="inlineStr">

--- a/Ekta_Schedule_With_Matchups.xlsx
+++ b/Ekta_Schedule_With_Matchups.xlsx
@@ -7,16 +7,17 @@
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="TT Women's Singles" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Table Tennis Singles Men" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Table Tennis Doubles" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Carrom Singles Men" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Carrom Singles Women" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Carrom Doubles" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Pool" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Chess" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Squash" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Trophies &amp; Medals" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Hourly Grid" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="TT Women's Singles" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Table Tennis Singles Men" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Table Tennis Doubles" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Carrom Singles Men" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Carrom Singles Women" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Carrom Doubles" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Pool" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Chess" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Squash" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Trophies &amp; Medals" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -26,7 +27,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="26">
+  <fonts count="31">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -166,8 +167,32 @@
       <color rgb="000F172A"/>
       <sz val="10.5"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <color rgb="00CBD5E1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <color rgb="000F172A"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <i val="1"/>
+      <color rgb="00991B1B"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="17">
+  <fills count="20">
     <fill>
       <patternFill/>
     </fill>
@@ -247,6 +272,21 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F1F5F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00203864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEE2E2"/>
       </patternFill>
     </fill>
   </fills>
@@ -374,7 +414,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="107">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -639,6 +679,31 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="14" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="15" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="19" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="19" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2037,6 +2102,3577 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:J100"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25.3" bestFit="1" customWidth="1" style="14" min="1" max="1"/>
+    <col width="10" customWidth="1" style="14" min="2" max="3"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" style="14" min="4" max="4"/>
+    <col width="10" customWidth="1" style="14" min="5" max="5"/>
+    <col width="12" customWidth="1" style="14" min="6" max="6"/>
+    <col width="11" customWidth="1" style="14" min="7" max="7"/>
+    <col width="27" customWidth="1" style="14" min="8" max="8"/>
+    <col width="4" customWidth="1" style="14" min="9" max="9"/>
+    <col width="27" customWidth="1" style="14" min="10" max="16384"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="27.95" customHeight="1">
+      <c r="A1" s="29" t="inlineStr">
+        <is>
+          <t>CHESS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15" customHeight="1">
+      <c r="A2" s="30" t="inlineStr">
+        <is>
+          <t>4 age bands, all single-pool Americano · Best of 3, Final Best of 5 · 2 Boards</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="31" t="n"/>
+      <c r="B3" s="31" t="n"/>
+      <c r="C3" s="31" t="n"/>
+      <c r="D3" s="31" t="n"/>
+      <c r="E3" s="31" t="n"/>
+      <c r="F3" s="31" t="n"/>
+      <c r="G3" s="31" t="n"/>
+      <c r="H3" s="31" t="n"/>
+      <c r="I3" s="31" t="n"/>
+    </row>
+    <row r="4" ht="20.1" customHeight="1">
+      <c r="A4" s="32" t="inlineStr">
+        <is>
+          <t>PLAYER GROUPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="31" t="n"/>
+      <c r="B5" s="31" t="n"/>
+      <c r="C5" s="31" t="n"/>
+      <c r="D5" s="31" t="n"/>
+      <c r="E5" s="31" t="n"/>
+      <c r="F5" s="31" t="n"/>
+      <c r="G5" s="31" t="n"/>
+      <c r="H5" s="31" t="n"/>
+      <c r="I5" s="31" t="n"/>
+    </row>
+    <row r="6" ht="17.1" customHeight="1">
+      <c r="A6" s="33" t="inlineStr">
+        <is>
+          <t>Under 11 (single pool, Americano)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="34" t="inlineStr">
+        <is>
+          <t>Player</t>
+        </is>
+      </c>
+      <c r="B7" s="34" t="inlineStr">
+        <is>
+          <t>Age</t>
+        </is>
+      </c>
+      <c r="C7" s="31" t="n"/>
+      <c r="D7" s="31" t="n"/>
+      <c r="E7" s="31" t="n"/>
+      <c r="F7" s="31" t="n"/>
+      <c r="G7" s="31" t="n"/>
+      <c r="H7" s="31" t="n"/>
+      <c r="I7" s="31" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="27" t="inlineStr">
+        <is>
+          <t>Rushabh</t>
+        </is>
+      </c>
+      <c r="B8" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="C8" s="31" t="n"/>
+      <c r="D8" s="31" t="n"/>
+      <c r="E8" s="31" t="n"/>
+      <c r="F8" s="31" t="n"/>
+      <c r="G8" s="31" t="n"/>
+      <c r="H8" s="31" t="n"/>
+      <c r="I8" s="31" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="28" t="inlineStr">
+        <is>
+          <t>Neev Chauhan</t>
+        </is>
+      </c>
+      <c r="B9" s="36" t="n">
+        <v>8</v>
+      </c>
+      <c r="C9" s="31" t="n"/>
+      <c r="D9" s="31" t="n"/>
+      <c r="E9" s="31" t="n"/>
+      <c r="F9" s="31" t="n"/>
+      <c r="G9" s="31" t="n"/>
+      <c r="H9" s="31" t="n"/>
+      <c r="I9" s="31" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="27" t="inlineStr">
+        <is>
+          <t>Kartik Relan</t>
+        </is>
+      </c>
+      <c r="B10" s="35" t="n">
+        <v>9</v>
+      </c>
+      <c r="C10" s="31" t="n"/>
+      <c r="D10" s="31" t="n"/>
+      <c r="E10" s="31" t="n"/>
+      <c r="F10" s="31" t="n"/>
+      <c r="G10" s="31" t="n"/>
+      <c r="H10" s="31" t="n"/>
+      <c r="I10" s="31" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="28" t="inlineStr">
+        <is>
+          <t>Parth yadav</t>
+        </is>
+      </c>
+      <c r="B11" s="36" t="n">
+        <v>10</v>
+      </c>
+      <c r="C11" s="31" t="n"/>
+      <c r="D11" s="31" t="n"/>
+      <c r="E11" s="31" t="n"/>
+      <c r="F11" s="31" t="n"/>
+      <c r="G11" s="31" t="n"/>
+      <c r="H11" s="31" t="n"/>
+      <c r="I11" s="31" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="27" t="inlineStr">
+        <is>
+          <t>Jimit Relan</t>
+        </is>
+      </c>
+      <c r="B12" s="35" t="n">
+        <v>11</v>
+      </c>
+      <c r="C12" s="31" t="n"/>
+      <c r="D12" s="31" t="n"/>
+      <c r="E12" s="31" t="n"/>
+      <c r="F12" s="31" t="n"/>
+      <c r="G12" s="31" t="n"/>
+      <c r="H12" s="31" t="n"/>
+      <c r="I12" s="31" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="31" t="n"/>
+      <c r="B13" s="31" t="n"/>
+      <c r="C13" s="31" t="n"/>
+      <c r="D13" s="31" t="n"/>
+      <c r="E13" s="31" t="n"/>
+      <c r="F13" s="31" t="n"/>
+      <c r="G13" s="31" t="n"/>
+      <c r="H13" s="31" t="n"/>
+      <c r="I13" s="31" t="n"/>
+    </row>
+    <row r="14" ht="17.1" customHeight="1">
+      <c r="A14" s="33" t="inlineStr">
+        <is>
+          <t>12 to 20 (single pool, Americano)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="34" t="inlineStr">
+        <is>
+          <t>Player</t>
+        </is>
+      </c>
+      <c r="B15" s="34" t="inlineStr">
+        <is>
+          <t>Age</t>
+        </is>
+      </c>
+      <c r="C15" s="31" t="n"/>
+      <c r="D15" s="31" t="n"/>
+      <c r="E15" s="31" t="n"/>
+      <c r="F15" s="31" t="n"/>
+      <c r="G15" s="31" t="n"/>
+      <c r="H15" s="31" t="n"/>
+      <c r="I15" s="31" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="27" t="inlineStr">
+        <is>
+          <t>Aadit Joshi</t>
+        </is>
+      </c>
+      <c r="B16" s="35" t="n">
+        <v>12</v>
+      </c>
+      <c r="C16" s="31" t="n"/>
+      <c r="D16" s="31" t="n"/>
+      <c r="E16" s="31" t="n"/>
+      <c r="F16" s="31" t="n"/>
+      <c r="G16" s="31" t="n"/>
+      <c r="H16" s="31" t="n"/>
+      <c r="I16" s="31" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="28" t="inlineStr">
+        <is>
+          <t>Maitreya Manvik</t>
+        </is>
+      </c>
+      <c r="B17" s="36" t="n">
+        <v>14</v>
+      </c>
+      <c r="C17" s="31" t="n"/>
+      <c r="D17" s="31" t="n"/>
+      <c r="E17" s="31" t="n"/>
+      <c r="F17" s="31" t="n"/>
+      <c r="G17" s="31" t="n"/>
+      <c r="H17" s="31" t="n"/>
+      <c r="I17" s="31" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="27" t="inlineStr">
+        <is>
+          <t>Aaditya Kumar</t>
+        </is>
+      </c>
+      <c r="B18" s="35" t="n">
+        <v>17</v>
+      </c>
+      <c r="C18" s="31" t="n"/>
+      <c r="D18" s="31" t="n"/>
+      <c r="E18" s="31" t="n"/>
+      <c r="F18" s="31" t="n"/>
+      <c r="G18" s="31" t="n"/>
+      <c r="H18" s="31" t="n"/>
+      <c r="I18" s="31" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="28" t="inlineStr">
+        <is>
+          <t>Hryday Goyal</t>
+        </is>
+      </c>
+      <c r="B19" s="36" t="n">
+        <v>20</v>
+      </c>
+      <c r="C19" s="31" t="n"/>
+      <c r="D19" s="31" t="n"/>
+      <c r="E19" s="31" t="n"/>
+      <c r="F19" s="31" t="n"/>
+      <c r="G19" s="31" t="n"/>
+      <c r="H19" s="31" t="n"/>
+      <c r="I19" s="31" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="31" t="n"/>
+      <c r="B20" s="31" t="n"/>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="31" t="n"/>
+      <c r="E20" s="31" t="n"/>
+      <c r="F20" s="31" t="n"/>
+      <c r="G20" s="31" t="n"/>
+      <c r="H20" s="31" t="n"/>
+      <c r="I20" s="31" t="n"/>
+    </row>
+    <row r="21" ht="17.1" customHeight="1">
+      <c r="A21" s="33" t="inlineStr">
+        <is>
+          <t>21 to 40 (single pool, Americano)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="34" t="inlineStr">
+        <is>
+          <t>Player</t>
+        </is>
+      </c>
+      <c r="B22" s="34" t="inlineStr">
+        <is>
+          <t>Age</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+      <c r="E22" s="31" t="n"/>
+      <c r="F22" s="31" t="n"/>
+      <c r="G22" s="31" t="n"/>
+      <c r="H22" s="31" t="n"/>
+      <c r="I22" s="31" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="27" t="inlineStr">
+        <is>
+          <t>Rahul Garg</t>
+        </is>
+      </c>
+      <c r="B23" s="35" t="n">
+        <v>25</v>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+      <c r="E23" s="31" t="n"/>
+      <c r="F23" s="31" t="n"/>
+      <c r="G23" s="31" t="n"/>
+      <c r="H23" s="31" t="n"/>
+      <c r="I23" s="31" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="28" t="inlineStr">
+        <is>
+          <t>Tej</t>
+        </is>
+      </c>
+      <c r="B24" s="36" t="n">
+        <v>32</v>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+      <c r="E24" s="31" t="n"/>
+      <c r="F24" s="31" t="n"/>
+      <c r="G24" s="31" t="n"/>
+      <c r="H24" s="31" t="n"/>
+      <c r="I24" s="31" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="27" t="inlineStr">
+        <is>
+          <t>Swati Tripathi</t>
+        </is>
+      </c>
+      <c r="B25" s="35" t="n">
+        <v>38</v>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+      <c r="E25" s="31" t="n"/>
+      <c r="F25" s="31" t="n"/>
+      <c r="G25" s="31" t="n"/>
+      <c r="H25" s="31" t="n"/>
+      <c r="I25" s="31" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="28" t="inlineStr">
+        <is>
+          <t>Amit Nawandhar</t>
+        </is>
+      </c>
+      <c r="B26" s="36" t="n">
+        <v>39</v>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+      <c r="E26" s="31" t="n"/>
+      <c r="F26" s="31" t="n"/>
+      <c r="G26" s="31" t="n"/>
+      <c r="H26" s="31" t="n"/>
+      <c r="I26" s="31" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="27" t="inlineStr">
+        <is>
+          <t>Tejas doshi</t>
+        </is>
+      </c>
+      <c r="B27" s="35" t="n">
+        <v>40</v>
+      </c>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+      <c r="E27" s="31" t="n"/>
+      <c r="F27" s="31" t="n"/>
+      <c r="G27" s="31" t="n"/>
+      <c r="H27" s="31" t="n"/>
+      <c r="I27" s="31" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="28" t="inlineStr">
+        <is>
+          <t>Nikunj Jhala</t>
+        </is>
+      </c>
+      <c r="B28" s="36" t="n">
+        <v>40</v>
+      </c>
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="31" t="n"/>
+      <c r="E28" s="31" t="n"/>
+      <c r="F28" s="31" t="n"/>
+      <c r="G28" s="31" t="n"/>
+      <c r="H28" s="31" t="n"/>
+      <c r="I28" s="31" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="31" t="n"/>
+      <c r="B29" s="31" t="n"/>
+      <c r="C29" s="31" t="n"/>
+      <c r="D29" s="31" t="n"/>
+      <c r="E29" s="31" t="n"/>
+      <c r="F29" s="31" t="n"/>
+      <c r="G29" s="31" t="n"/>
+      <c r="H29" s="31" t="n"/>
+      <c r="I29" s="31" t="n"/>
+    </row>
+    <row r="30" ht="17.1" customHeight="1">
+      <c r="A30" s="33" t="inlineStr">
+        <is>
+          <t>41 and above (single pool, Americano)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="34" t="inlineStr">
+        <is>
+          <t>Player</t>
+        </is>
+      </c>
+      <c r="B31" s="34" t="inlineStr">
+        <is>
+          <t>Age</t>
+        </is>
+      </c>
+      <c r="C31" s="31" t="n"/>
+      <c r="D31" s="31" t="n"/>
+      <c r="E31" s="31" t="n"/>
+      <c r="F31" s="31" t="n"/>
+      <c r="G31" s="31" t="n"/>
+      <c r="H31" s="31" t="n"/>
+      <c r="I31" s="31" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="27" t="inlineStr">
+        <is>
+          <t>Piyush Makharia</t>
+        </is>
+      </c>
+      <c r="B32" s="35" t="n">
+        <v>43</v>
+      </c>
+      <c r="C32" s="31" t="n"/>
+      <c r="D32" s="31" t="n"/>
+      <c r="E32" s="31" t="n"/>
+      <c r="F32" s="31" t="n"/>
+      <c r="G32" s="31" t="n"/>
+      <c r="H32" s="31" t="n"/>
+      <c r="I32" s="31" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="28" t="inlineStr">
+        <is>
+          <t>Adil Khan</t>
+        </is>
+      </c>
+      <c r="B33" s="36" t="n">
+        <v>51</v>
+      </c>
+      <c r="C33" s="31" t="n"/>
+      <c r="D33" s="31" t="n"/>
+      <c r="E33" s="31" t="n"/>
+      <c r="F33" s="31" t="n"/>
+      <c r="G33" s="31" t="n"/>
+      <c r="H33" s="31" t="n"/>
+      <c r="I33" s="31" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="27" t="inlineStr">
+        <is>
+          <t>Sachin Malgadnkar</t>
+        </is>
+      </c>
+      <c r="B34" s="35" t="n">
+        <v>52</v>
+      </c>
+      <c r="C34" s="31" t="n"/>
+      <c r="D34" s="31" t="n"/>
+      <c r="E34" s="31" t="n"/>
+      <c r="F34" s="31" t="n"/>
+      <c r="G34" s="31" t="n"/>
+      <c r="H34" s="31" t="n"/>
+      <c r="I34" s="31" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="28" t="inlineStr">
+        <is>
+          <t>Prasad Akshintala</t>
+        </is>
+      </c>
+      <c r="B35" s="36" t="n">
+        <v>56</v>
+      </c>
+      <c r="C35" s="31" t="n"/>
+      <c r="D35" s="31" t="n"/>
+      <c r="E35" s="31" t="n"/>
+      <c r="F35" s="31" t="n"/>
+      <c r="G35" s="31" t="n"/>
+      <c r="H35" s="31" t="n"/>
+      <c r="I35" s="31" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="27" t="inlineStr">
+        <is>
+          <t>Ajit nair</t>
+        </is>
+      </c>
+      <c r="B36" s="35" t="n">
+        <v>59</v>
+      </c>
+      <c r="C36" s="31" t="n"/>
+      <c r="D36" s="31" t="n"/>
+      <c r="E36" s="31" t="n"/>
+      <c r="F36" s="31" t="n"/>
+      <c r="G36" s="31" t="n"/>
+      <c r="H36" s="31" t="n"/>
+      <c r="I36" s="31" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="28" t="inlineStr">
+        <is>
+          <t>Sanjay Kumar</t>
+        </is>
+      </c>
+      <c r="B37" s="36" t="n">
+        <v>61</v>
+      </c>
+      <c r="C37" s="31" t="n"/>
+      <c r="D37" s="31" t="n"/>
+      <c r="E37" s="31" t="n"/>
+      <c r="F37" s="31" t="n"/>
+      <c r="G37" s="31" t="n"/>
+      <c r="H37" s="31" t="n"/>
+      <c r="I37" s="31" t="n"/>
+    </row>
+    <row r="38" ht="20.1" customHeight="1">
+      <c r="A38" s="27" t="inlineStr">
+        <is>
+          <t>Harkishin malkan</t>
+        </is>
+      </c>
+      <c r="B38" s="35" t="n">
+        <v>76</v>
+      </c>
+      <c r="C38" s="31" t="n"/>
+      <c r="D38" s="31" t="n"/>
+      <c r="E38" s="31" t="n"/>
+      <c r="F38" s="31" t="n"/>
+      <c r="G38" s="31" t="n"/>
+      <c r="H38" s="31" t="n"/>
+      <c r="I38" s="31" t="n"/>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="31" t="n"/>
+      <c r="B39" s="31" t="n"/>
+      <c r="C39" s="31" t="n"/>
+      <c r="D39" s="31" t="n"/>
+      <c r="E39" s="31" t="n"/>
+      <c r="F39" s="31" t="n"/>
+      <c r="G39" s="31" t="n"/>
+      <c r="H39" s="31" t="n"/>
+      <c r="I39" s="31" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="31" t="n"/>
+      <c r="B40" s="31" t="n"/>
+      <c r="C40" s="31" t="n"/>
+      <c r="D40" s="31" t="n"/>
+      <c r="E40" s="31" t="n"/>
+      <c r="F40" s="31" t="n"/>
+      <c r="G40" s="31" t="n"/>
+      <c r="H40" s="31" t="n"/>
+      <c r="I40" s="31" t="n"/>
+    </row>
+    <row r="41" ht="20.1" customHeight="1">
+      <c r="A41" s="32" t="inlineStr">
+        <is>
+          <t>MATCH SCHEDULE (chronological, interleaved with other sports to avoid player conflicts)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="26" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="B42" s="26" t="inlineStr">
+        <is>
+          <t>Start</t>
+        </is>
+      </c>
+      <c r="C42" s="26" t="inlineStr">
+        <is>
+          <t>End</t>
+        </is>
+      </c>
+      <c r="D42" s="26" t="inlineStr">
+        <is>
+          <t>Band</t>
+        </is>
+      </c>
+      <c r="E42" s="26" t="inlineStr">
+        <is>
+          <t>Match #</t>
+        </is>
+      </c>
+      <c r="F42" s="26" t="inlineStr">
+        <is>
+          <t>Match</t>
+        </is>
+      </c>
+      <c r="G42" s="26" t="inlineStr">
+        <is>
+          <t>Resource</t>
+        </is>
+      </c>
+      <c r="H42" s="26" t="inlineStr">
+        <is>
+          <t>Player A</t>
+        </is>
+      </c>
+      <c r="I42" s="26" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J42" s="26" t="inlineStr">
+        <is>
+          <t>Player B</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B43" s="94" t="inlineStr">
+        <is>
+          <t>8:00AM</t>
+        </is>
+      </c>
+      <c r="C43" s="94" t="inlineStr">
+        <is>
+          <t>8:20AM</t>
+        </is>
+      </c>
+      <c r="D43" s="94" t="inlineStr">
+        <is>
+          <t>Under 11</t>
+        </is>
+      </c>
+      <c r="E43" s="94" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" s="94" t="inlineStr">
+        <is>
+          <t>U11-1</t>
+        </is>
+      </c>
+      <c r="G43" s="94" t="inlineStr">
+        <is>
+          <t>Board 1</t>
+        </is>
+      </c>
+      <c r="H43" s="94" t="inlineStr">
+        <is>
+          <t>Rushabh</t>
+        </is>
+      </c>
+      <c r="I43" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J43" s="94" t="inlineStr">
+        <is>
+          <t>Neev Chauhan</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B44" s="95" t="inlineStr">
+        <is>
+          <t>8:00AM</t>
+        </is>
+      </c>
+      <c r="C44" s="95" t="inlineStr">
+        <is>
+          <t>8:20AM</t>
+        </is>
+      </c>
+      <c r="D44" s="95" t="inlineStr">
+        <is>
+          <t>Under 11</t>
+        </is>
+      </c>
+      <c r="E44" s="95" t="n">
+        <v>2</v>
+      </c>
+      <c r="F44" s="95" t="inlineStr">
+        <is>
+          <t>U11-2</t>
+        </is>
+      </c>
+      <c r="G44" s="95" t="inlineStr">
+        <is>
+          <t>Board 2</t>
+        </is>
+      </c>
+      <c r="H44" s="95" t="inlineStr">
+        <is>
+          <t>Kartik Relan</t>
+        </is>
+      </c>
+      <c r="I44" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J44" s="95" t="inlineStr">
+        <is>
+          <t>Parth yadav</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B45" s="94" t="inlineStr">
+        <is>
+          <t>8:20AM</t>
+        </is>
+      </c>
+      <c r="C45" s="94" t="inlineStr">
+        <is>
+          <t>8:40AM</t>
+        </is>
+      </c>
+      <c r="D45" s="94" t="inlineStr">
+        <is>
+          <t>12 to 20</t>
+        </is>
+      </c>
+      <c r="E45" s="94" t="n">
+        <v>3</v>
+      </c>
+      <c r="F45" s="94" t="inlineStr">
+        <is>
+          <t>1220-2</t>
+        </is>
+      </c>
+      <c r="G45" s="94" t="inlineStr">
+        <is>
+          <t>Board 1</t>
+        </is>
+      </c>
+      <c r="H45" s="94" t="inlineStr">
+        <is>
+          <t>Aaditya Kumar</t>
+        </is>
+      </c>
+      <c r="I45" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J45" s="94" t="inlineStr">
+        <is>
+          <t>Hryday Goyal</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B46" s="95" t="inlineStr">
+        <is>
+          <t>8:20AM</t>
+        </is>
+      </c>
+      <c r="C46" s="95" t="inlineStr">
+        <is>
+          <t>8:40AM</t>
+        </is>
+      </c>
+      <c r="D46" s="95" t="inlineStr">
+        <is>
+          <t>21 to 40</t>
+        </is>
+      </c>
+      <c r="E46" s="95" t="n">
+        <v>4</v>
+      </c>
+      <c r="F46" s="95" t="inlineStr">
+        <is>
+          <t>2140-2</t>
+        </is>
+      </c>
+      <c r="G46" s="95" t="inlineStr">
+        <is>
+          <t>Board 2</t>
+        </is>
+      </c>
+      <c r="H46" s="95" t="inlineStr">
+        <is>
+          <t>Swati Tripathi</t>
+        </is>
+      </c>
+      <c r="I46" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J46" s="95" t="inlineStr">
+        <is>
+          <t>Amit Nawandhar</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B47" s="94" t="inlineStr">
+        <is>
+          <t>8:40AM</t>
+        </is>
+      </c>
+      <c r="C47" s="94" t="inlineStr">
+        <is>
+          <t>9:00AM</t>
+        </is>
+      </c>
+      <c r="D47" s="94" t="inlineStr">
+        <is>
+          <t>Under 11</t>
+        </is>
+      </c>
+      <c r="E47" s="94" t="n">
+        <v>5</v>
+      </c>
+      <c r="F47" s="94" t="inlineStr">
+        <is>
+          <t>U11-3</t>
+        </is>
+      </c>
+      <c r="G47" s="94" t="inlineStr">
+        <is>
+          <t>Board 1</t>
+        </is>
+      </c>
+      <c r="H47" s="94" t="inlineStr">
+        <is>
+          <t>Rushabh</t>
+        </is>
+      </c>
+      <c r="I47" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J47" s="94" t="inlineStr">
+        <is>
+          <t>Kartik Relan</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B48" s="95" t="inlineStr">
+        <is>
+          <t>8:40AM</t>
+        </is>
+      </c>
+      <c r="C48" s="95" t="inlineStr">
+        <is>
+          <t>9:00AM</t>
+        </is>
+      </c>
+      <c r="D48" s="95" t="inlineStr">
+        <is>
+          <t>Under 11</t>
+        </is>
+      </c>
+      <c r="E48" s="95" t="n">
+        <v>6</v>
+      </c>
+      <c r="F48" s="95" t="inlineStr">
+        <is>
+          <t>U11-4</t>
+        </is>
+      </c>
+      <c r="G48" s="95" t="inlineStr">
+        <is>
+          <t>Board 2</t>
+        </is>
+      </c>
+      <c r="H48" s="95" t="inlineStr">
+        <is>
+          <t>Neev Chauhan</t>
+        </is>
+      </c>
+      <c r="I48" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J48" s="95" t="inlineStr">
+        <is>
+          <t>Jimit Relan</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B49" s="94" t="inlineStr">
+        <is>
+          <t>9:00AM</t>
+        </is>
+      </c>
+      <c r="C49" s="94" t="inlineStr">
+        <is>
+          <t>9:20AM</t>
+        </is>
+      </c>
+      <c r="D49" s="94" t="inlineStr">
+        <is>
+          <t>12 to 20</t>
+        </is>
+      </c>
+      <c r="E49" s="94" t="n">
+        <v>7</v>
+      </c>
+      <c r="F49" s="94" t="inlineStr">
+        <is>
+          <t>1220-1</t>
+        </is>
+      </c>
+      <c r="G49" s="94" t="inlineStr">
+        <is>
+          <t>Board 1</t>
+        </is>
+      </c>
+      <c r="H49" s="94" t="inlineStr">
+        <is>
+          <t>Aadit Joshi</t>
+        </is>
+      </c>
+      <c r="I49" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J49" s="94" t="inlineStr">
+        <is>
+          <t>Maitreya Manvik</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B50" s="95" t="inlineStr">
+        <is>
+          <t>9:00AM</t>
+        </is>
+      </c>
+      <c r="C50" s="95" t="inlineStr">
+        <is>
+          <t>9:20AM</t>
+        </is>
+      </c>
+      <c r="D50" s="95" t="inlineStr">
+        <is>
+          <t>21 to 40</t>
+        </is>
+      </c>
+      <c r="E50" s="95" t="n">
+        <v>8</v>
+      </c>
+      <c r="F50" s="95" t="inlineStr">
+        <is>
+          <t>2140-6</t>
+        </is>
+      </c>
+      <c r="G50" s="95" t="inlineStr">
+        <is>
+          <t>Board 2</t>
+        </is>
+      </c>
+      <c r="H50" s="95" t="inlineStr">
+        <is>
+          <t>Tej</t>
+        </is>
+      </c>
+      <c r="I50" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J50" s="95" t="inlineStr">
+        <is>
+          <t>Swati Tripathi</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B51" s="94" t="inlineStr">
+        <is>
+          <t>9:20AM</t>
+        </is>
+      </c>
+      <c r="C51" s="94" t="inlineStr">
+        <is>
+          <t>9:40AM</t>
+        </is>
+      </c>
+      <c r="D51" s="94" t="inlineStr">
+        <is>
+          <t>Under 11</t>
+        </is>
+      </c>
+      <c r="E51" s="94" t="n">
+        <v>9</v>
+      </c>
+      <c r="F51" s="94" t="inlineStr">
+        <is>
+          <t>U11-5</t>
+        </is>
+      </c>
+      <c r="G51" s="94" t="inlineStr">
+        <is>
+          <t>Board 1</t>
+        </is>
+      </c>
+      <c r="H51" s="94" t="inlineStr">
+        <is>
+          <t>Kartik Relan</t>
+        </is>
+      </c>
+      <c r="I51" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J51" s="94" t="inlineStr">
+        <is>
+          <t>Jimit Relan</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B52" s="95" t="inlineStr">
+        <is>
+          <t>9:20AM</t>
+        </is>
+      </c>
+      <c r="C52" s="95" t="inlineStr">
+        <is>
+          <t>9:40AM</t>
+        </is>
+      </c>
+      <c r="D52" s="95" t="inlineStr">
+        <is>
+          <t>Under 11</t>
+        </is>
+      </c>
+      <c r="E52" s="95" t="n">
+        <v>10</v>
+      </c>
+      <c r="F52" s="95" t="inlineStr">
+        <is>
+          <t>U11-6</t>
+        </is>
+      </c>
+      <c r="G52" s="95" t="inlineStr">
+        <is>
+          <t>Board 2</t>
+        </is>
+      </c>
+      <c r="H52" s="95" t="inlineStr">
+        <is>
+          <t>Rushabh</t>
+        </is>
+      </c>
+      <c r="I52" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J52" s="95" t="inlineStr">
+        <is>
+          <t>Parth yadav</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B53" s="94" t="inlineStr">
+        <is>
+          <t>10:30AM</t>
+        </is>
+      </c>
+      <c r="C53" s="94" t="inlineStr">
+        <is>
+          <t>10:50AM</t>
+        </is>
+      </c>
+      <c r="D53" s="94" t="inlineStr">
+        <is>
+          <t>Under 11</t>
+        </is>
+      </c>
+      <c r="E53" s="94" t="n">
+        <v>11</v>
+      </c>
+      <c r="F53" s="94" t="inlineStr">
+        <is>
+          <t>U11-7</t>
+        </is>
+      </c>
+      <c r="G53" s="94" t="inlineStr">
+        <is>
+          <t>Board 1</t>
+        </is>
+      </c>
+      <c r="H53" s="94" t="inlineStr">
+        <is>
+          <t>Rushabh</t>
+        </is>
+      </c>
+      <c r="I53" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J53" s="94" t="inlineStr">
+        <is>
+          <t>Jimit Relan</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B54" s="95" t="inlineStr">
+        <is>
+          <t>10:30AM</t>
+        </is>
+      </c>
+      <c r="C54" s="95" t="inlineStr">
+        <is>
+          <t>10:50AM</t>
+        </is>
+      </c>
+      <c r="D54" s="95" t="inlineStr">
+        <is>
+          <t>Under 11</t>
+        </is>
+      </c>
+      <c r="E54" s="95" t="n">
+        <v>12</v>
+      </c>
+      <c r="F54" s="95" t="inlineStr">
+        <is>
+          <t>U11-8</t>
+        </is>
+      </c>
+      <c r="G54" s="95" t="inlineStr">
+        <is>
+          <t>Board 2</t>
+        </is>
+      </c>
+      <c r="H54" s="95" t="inlineStr">
+        <is>
+          <t>Neev Chauhan</t>
+        </is>
+      </c>
+      <c r="I54" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J54" s="95" t="inlineStr">
+        <is>
+          <t>Kartik Relan</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B55" s="94" t="inlineStr">
+        <is>
+          <t>10:50AM</t>
+        </is>
+      </c>
+      <c r="C55" s="94" t="inlineStr">
+        <is>
+          <t>11:10AM</t>
+        </is>
+      </c>
+      <c r="D55" s="94" t="inlineStr">
+        <is>
+          <t>12 to 20</t>
+        </is>
+      </c>
+      <c r="E55" s="94" t="n">
+        <v>13</v>
+      </c>
+      <c r="F55" s="94" t="inlineStr">
+        <is>
+          <t>1220-3</t>
+        </is>
+      </c>
+      <c r="G55" s="94" t="inlineStr">
+        <is>
+          <t>Board 1</t>
+        </is>
+      </c>
+      <c r="H55" s="94" t="inlineStr">
+        <is>
+          <t>Aadit Joshi</t>
+        </is>
+      </c>
+      <c r="I55" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J55" s="94" t="inlineStr">
+        <is>
+          <t>Aaditya Kumar</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B56" s="95" t="inlineStr">
+        <is>
+          <t>10:50AM</t>
+        </is>
+      </c>
+      <c r="C56" s="95" t="inlineStr">
+        <is>
+          <t>11:10AM</t>
+        </is>
+      </c>
+      <c r="D56" s="95" t="inlineStr">
+        <is>
+          <t>12 to 20</t>
+        </is>
+      </c>
+      <c r="E56" s="95" t="n">
+        <v>14</v>
+      </c>
+      <c r="F56" s="95" t="inlineStr">
+        <is>
+          <t>1220-4</t>
+        </is>
+      </c>
+      <c r="G56" s="95" t="inlineStr">
+        <is>
+          <t>Board 2</t>
+        </is>
+      </c>
+      <c r="H56" s="95" t="inlineStr">
+        <is>
+          <t>Maitreya Manvik</t>
+        </is>
+      </c>
+      <c r="I56" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J56" s="95" t="inlineStr">
+        <is>
+          <t>Hryday Goyal</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B57" s="94" t="inlineStr">
+        <is>
+          <t>11:10AM</t>
+        </is>
+      </c>
+      <c r="C57" s="94" t="inlineStr">
+        <is>
+          <t>11:30AM</t>
+        </is>
+      </c>
+      <c r="D57" s="94" t="inlineStr">
+        <is>
+          <t>21 to 40</t>
+        </is>
+      </c>
+      <c r="E57" s="94" t="n">
+        <v>15</v>
+      </c>
+      <c r="F57" s="94" t="inlineStr">
+        <is>
+          <t>2140-3</t>
+        </is>
+      </c>
+      <c r="G57" s="94" t="inlineStr">
+        <is>
+          <t>Board 2</t>
+        </is>
+      </c>
+      <c r="H57" s="94" t="inlineStr">
+        <is>
+          <t>Rahul Garg</t>
+        </is>
+      </c>
+      <c r="I57" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J57" s="94" t="inlineStr">
+        <is>
+          <t>Amit Nawandhar</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B58" s="95" t="inlineStr">
+        <is>
+          <t>11:10AM</t>
+        </is>
+      </c>
+      <c r="C58" s="95" t="inlineStr">
+        <is>
+          <t>11:30AM</t>
+        </is>
+      </c>
+      <c r="D58" s="95" t="inlineStr">
+        <is>
+          <t>Under 11</t>
+        </is>
+      </c>
+      <c r="E58" s="95" t="n">
+        <v>16</v>
+      </c>
+      <c r="F58" s="95" t="inlineStr">
+        <is>
+          <t>U11-9</t>
+        </is>
+      </c>
+      <c r="G58" s="95" t="inlineStr">
+        <is>
+          <t>Board 1</t>
+        </is>
+      </c>
+      <c r="H58" s="95" t="inlineStr">
+        <is>
+          <t>Neev Chauhan</t>
+        </is>
+      </c>
+      <c r="I58" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J58" s="95" t="inlineStr">
+        <is>
+          <t>Parth yadav</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B59" s="94" t="inlineStr">
+        <is>
+          <t>11:30AM</t>
+        </is>
+      </c>
+      <c r="C59" s="94" t="inlineStr">
+        <is>
+          <t>11:50AM</t>
+        </is>
+      </c>
+      <c r="D59" s="94" t="inlineStr">
+        <is>
+          <t>12 to 20</t>
+        </is>
+      </c>
+      <c r="E59" s="94" t="n">
+        <v>17</v>
+      </c>
+      <c r="F59" s="94" t="inlineStr">
+        <is>
+          <t>1220-5</t>
+        </is>
+      </c>
+      <c r="G59" s="94" t="inlineStr">
+        <is>
+          <t>Board 1</t>
+        </is>
+      </c>
+      <c r="H59" s="94" t="inlineStr">
+        <is>
+          <t>Aadit Joshi</t>
+        </is>
+      </c>
+      <c r="I59" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J59" s="94" t="inlineStr">
+        <is>
+          <t>Hryday Goyal</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B60" s="95" t="inlineStr">
+        <is>
+          <t>11:30AM</t>
+        </is>
+      </c>
+      <c r="C60" s="95" t="inlineStr">
+        <is>
+          <t>11:50AM</t>
+        </is>
+      </c>
+      <c r="D60" s="95" t="inlineStr">
+        <is>
+          <t>12 to 20</t>
+        </is>
+      </c>
+      <c r="E60" s="95" t="n">
+        <v>18</v>
+      </c>
+      <c r="F60" s="95" t="inlineStr">
+        <is>
+          <t>1220-6</t>
+        </is>
+      </c>
+      <c r="G60" s="95" t="inlineStr">
+        <is>
+          <t>Board 2</t>
+        </is>
+      </c>
+      <c r="H60" s="95" t="inlineStr">
+        <is>
+          <t>Maitreya Manvik</t>
+        </is>
+      </c>
+      <c r="I60" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J60" s="95" t="inlineStr">
+        <is>
+          <t>Aaditya Kumar</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B61" s="94" t="inlineStr">
+        <is>
+          <t>11:50AM</t>
+        </is>
+      </c>
+      <c r="C61" s="94" t="inlineStr">
+        <is>
+          <t>12:10PM</t>
+        </is>
+      </c>
+      <c r="D61" s="94" t="inlineStr">
+        <is>
+          <t>21 to 40</t>
+        </is>
+      </c>
+      <c r="E61" s="94" t="n">
+        <v>19</v>
+      </c>
+      <c r="F61" s="94" t="inlineStr">
+        <is>
+          <t>2140-1</t>
+        </is>
+      </c>
+      <c r="G61" s="94" t="inlineStr">
+        <is>
+          <t>Board 2</t>
+        </is>
+      </c>
+      <c r="H61" s="94" t="inlineStr">
+        <is>
+          <t>Tej</t>
+        </is>
+      </c>
+      <c r="I61" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J61" s="94" t="inlineStr">
+        <is>
+          <t>Tejas doshi</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B62" s="95" t="inlineStr">
+        <is>
+          <t>11:50AM</t>
+        </is>
+      </c>
+      <c r="C62" s="95" t="inlineStr">
+        <is>
+          <t>12:10PM</t>
+        </is>
+      </c>
+      <c r="D62" s="95" t="inlineStr">
+        <is>
+          <t>Under 11</t>
+        </is>
+      </c>
+      <c r="E62" s="95" t="n">
+        <v>20</v>
+      </c>
+      <c r="F62" s="95" t="inlineStr">
+        <is>
+          <t>U11-10</t>
+        </is>
+      </c>
+      <c r="G62" s="95" t="inlineStr">
+        <is>
+          <t>Board 1</t>
+        </is>
+      </c>
+      <c r="H62" s="95" t="inlineStr">
+        <is>
+          <t>Parth yadav</t>
+        </is>
+      </c>
+      <c r="I62" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J62" s="95" t="inlineStr">
+        <is>
+          <t>Jimit Relan</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B63" s="94" t="inlineStr">
+        <is>
+          <t>3:00PM</t>
+        </is>
+      </c>
+      <c r="C63" s="94" t="inlineStr">
+        <is>
+          <t>3:20PM</t>
+        </is>
+      </c>
+      <c r="D63" s="94" t="inlineStr">
+        <is>
+          <t>21 to 40</t>
+        </is>
+      </c>
+      <c r="E63" s="94" t="n">
+        <v>21</v>
+      </c>
+      <c r="F63" s="94" t="inlineStr">
+        <is>
+          <t>2140-4</t>
+        </is>
+      </c>
+      <c r="G63" s="94" t="inlineStr">
+        <is>
+          <t>Board 1</t>
+        </is>
+      </c>
+      <c r="H63" s="94" t="inlineStr">
+        <is>
+          <t>Swati Tripathi</t>
+        </is>
+      </c>
+      <c r="I63" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J63" s="94" t="inlineStr">
+        <is>
+          <t>Tejas doshi</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B64" s="95" t="inlineStr">
+        <is>
+          <t>3:00PM</t>
+        </is>
+      </c>
+      <c r="C64" s="95" t="inlineStr">
+        <is>
+          <t>3:20PM</t>
+        </is>
+      </c>
+      <c r="D64" s="95" t="inlineStr">
+        <is>
+          <t>41 and above</t>
+        </is>
+      </c>
+      <c r="E64" s="95" t="n">
+        <v>22</v>
+      </c>
+      <c r="F64" s="95" t="inlineStr">
+        <is>
+          <t>41P-1</t>
+        </is>
+      </c>
+      <c r="G64" s="95" t="inlineStr">
+        <is>
+          <t>Board 2</t>
+        </is>
+      </c>
+      <c r="H64" s="95" t="inlineStr">
+        <is>
+          <t>Piyush Makharia</t>
+        </is>
+      </c>
+      <c r="I64" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J64" s="95" t="inlineStr">
+        <is>
+          <t>Ajit nair</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B65" s="94" t="inlineStr">
+        <is>
+          <t>3:20PM</t>
+        </is>
+      </c>
+      <c r="C65" s="94" t="inlineStr">
+        <is>
+          <t>3:40PM</t>
+        </is>
+      </c>
+      <c r="D65" s="94" t="inlineStr">
+        <is>
+          <t>21 to 40</t>
+        </is>
+      </c>
+      <c r="E65" s="94" t="n">
+        <v>23</v>
+      </c>
+      <c r="F65" s="94" t="inlineStr">
+        <is>
+          <t>2140-10</t>
+        </is>
+      </c>
+      <c r="G65" s="94" t="inlineStr">
+        <is>
+          <t>Board 1</t>
+        </is>
+      </c>
+      <c r="H65" s="94" t="inlineStr">
+        <is>
+          <t>Amit Nawandhar</t>
+        </is>
+      </c>
+      <c r="I65" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J65" s="94" t="inlineStr">
+        <is>
+          <t>Nikunj Jhala</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B66" s="95" t="inlineStr">
+        <is>
+          <t>3:20PM</t>
+        </is>
+      </c>
+      <c r="C66" s="95" t="inlineStr">
+        <is>
+          <t>3:40PM</t>
+        </is>
+      </c>
+      <c r="D66" s="95" t="inlineStr">
+        <is>
+          <t>41 and above</t>
+        </is>
+      </c>
+      <c r="E66" s="95" t="n">
+        <v>24</v>
+      </c>
+      <c r="F66" s="95" t="inlineStr">
+        <is>
+          <t>41P-8</t>
+        </is>
+      </c>
+      <c r="G66" s="95" t="inlineStr">
+        <is>
+          <t>Board 2</t>
+        </is>
+      </c>
+      <c r="H66" s="95" t="inlineStr">
+        <is>
+          <t>Prasad Akshintala</t>
+        </is>
+      </c>
+      <c r="I66" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J66" s="95" t="inlineStr">
+        <is>
+          <t>Sanjay Kumar</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B67" s="94" t="inlineStr">
+        <is>
+          <t>3:40PM</t>
+        </is>
+      </c>
+      <c r="C67" s="94" t="inlineStr">
+        <is>
+          <t>4:00PM</t>
+        </is>
+      </c>
+      <c r="D67" s="94" t="inlineStr">
+        <is>
+          <t>21 to 40</t>
+        </is>
+      </c>
+      <c r="E67" s="94" t="n">
+        <v>25</v>
+      </c>
+      <c r="F67" s="94" t="inlineStr">
+        <is>
+          <t>2140-9</t>
+        </is>
+      </c>
+      <c r="G67" s="94" t="inlineStr">
+        <is>
+          <t>Board 1</t>
+        </is>
+      </c>
+      <c r="H67" s="94" t="inlineStr">
+        <is>
+          <t>Rahul Garg</t>
+        </is>
+      </c>
+      <c r="I67" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J67" s="94" t="inlineStr">
+        <is>
+          <t>Tej</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B68" s="95" t="inlineStr">
+        <is>
+          <t>3:40PM</t>
+        </is>
+      </c>
+      <c r="C68" s="95" t="inlineStr">
+        <is>
+          <t>4:00PM</t>
+        </is>
+      </c>
+      <c r="D68" s="95" t="inlineStr">
+        <is>
+          <t>41 and above</t>
+        </is>
+      </c>
+      <c r="E68" s="95" t="n">
+        <v>26</v>
+      </c>
+      <c r="F68" s="95" t="inlineStr">
+        <is>
+          <t>41P-12</t>
+        </is>
+      </c>
+      <c r="G68" s="95" t="inlineStr">
+        <is>
+          <t>Board 2</t>
+        </is>
+      </c>
+      <c r="H68" s="95" t="inlineStr">
+        <is>
+          <t>Adil Khan</t>
+        </is>
+      </c>
+      <c r="I68" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J68" s="95" t="inlineStr">
+        <is>
+          <t>Ajit nair</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B69" s="94" t="inlineStr">
+        <is>
+          <t>4:00PM</t>
+        </is>
+      </c>
+      <c r="C69" s="94" t="inlineStr">
+        <is>
+          <t>4:20PM</t>
+        </is>
+      </c>
+      <c r="D69" s="94" t="inlineStr">
+        <is>
+          <t>21 to 40</t>
+        </is>
+      </c>
+      <c r="E69" s="94" t="n">
+        <v>27</v>
+      </c>
+      <c r="F69" s="94" t="inlineStr">
+        <is>
+          <t>2140-5</t>
+        </is>
+      </c>
+      <c r="G69" s="94" t="inlineStr">
+        <is>
+          <t>Board 1</t>
+        </is>
+      </c>
+      <c r="H69" s="94" t="inlineStr">
+        <is>
+          <t>Amit Nawandhar</t>
+        </is>
+      </c>
+      <c r="I69" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J69" s="94" t="inlineStr">
+        <is>
+          <t>Tejas doshi</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B70" s="95" t="inlineStr">
+        <is>
+          <t>4:00PM</t>
+        </is>
+      </c>
+      <c r="C70" s="95" t="inlineStr">
+        <is>
+          <t>4:20PM</t>
+        </is>
+      </c>
+      <c r="D70" s="95" t="inlineStr">
+        <is>
+          <t>41 and above</t>
+        </is>
+      </c>
+      <c r="E70" s="95" t="n">
+        <v>28</v>
+      </c>
+      <c r="F70" s="95" t="inlineStr">
+        <is>
+          <t>41P-3</t>
+        </is>
+      </c>
+      <c r="G70" s="95" t="inlineStr">
+        <is>
+          <t>Board 2</t>
+        </is>
+      </c>
+      <c r="H70" s="95" t="inlineStr">
+        <is>
+          <t>Piyush Makharia</t>
+        </is>
+      </c>
+      <c r="I70" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J70" s="95" t="inlineStr">
+        <is>
+          <t>Prasad Akshintala</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B71" s="94" t="inlineStr">
+        <is>
+          <t>4:20PM</t>
+        </is>
+      </c>
+      <c r="C71" s="94" t="inlineStr">
+        <is>
+          <t>4:40PM</t>
+        </is>
+      </c>
+      <c r="D71" s="94" t="inlineStr">
+        <is>
+          <t>21 to 40</t>
+        </is>
+      </c>
+      <c r="E71" s="94" t="n">
+        <v>29</v>
+      </c>
+      <c r="F71" s="94" t="inlineStr">
+        <is>
+          <t>2140-13</t>
+        </is>
+      </c>
+      <c r="G71" s="94" t="inlineStr">
+        <is>
+          <t>Board 1</t>
+        </is>
+      </c>
+      <c r="H71" s="94" t="inlineStr">
+        <is>
+          <t>Rahul Garg</t>
+        </is>
+      </c>
+      <c r="I71" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J71" s="94" t="inlineStr">
+        <is>
+          <t>Swati Tripathi</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B72" s="95" t="inlineStr">
+        <is>
+          <t>4:20PM</t>
+        </is>
+      </c>
+      <c r="C72" s="95" t="inlineStr">
+        <is>
+          <t>4:40PM</t>
+        </is>
+      </c>
+      <c r="D72" s="95" t="inlineStr">
+        <is>
+          <t>41 and above</t>
+        </is>
+      </c>
+      <c r="E72" s="95" t="n">
+        <v>30</v>
+      </c>
+      <c r="F72" s="95" t="inlineStr">
+        <is>
+          <t>41P-2</t>
+        </is>
+      </c>
+      <c r="G72" s="95" t="inlineStr">
+        <is>
+          <t>Board 2</t>
+        </is>
+      </c>
+      <c r="H72" s="95" t="inlineStr">
+        <is>
+          <t>Ajit nair</t>
+        </is>
+      </c>
+      <c r="I72" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J72" s="95" t="inlineStr">
+        <is>
+          <t>Sanjay Kumar</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B73" s="94" t="inlineStr">
+        <is>
+          <t>4:40PM</t>
+        </is>
+      </c>
+      <c r="C73" s="94" t="inlineStr">
+        <is>
+          <t>5:00PM</t>
+        </is>
+      </c>
+      <c r="D73" s="94" t="inlineStr">
+        <is>
+          <t>21 to 40</t>
+        </is>
+      </c>
+      <c r="E73" s="94" t="n">
+        <v>31</v>
+      </c>
+      <c r="F73" s="94" t="inlineStr">
+        <is>
+          <t>2140-12</t>
+        </is>
+      </c>
+      <c r="G73" s="94" t="inlineStr">
+        <is>
+          <t>Board 1</t>
+        </is>
+      </c>
+      <c r="H73" s="94" t="inlineStr">
+        <is>
+          <t>Tej</t>
+        </is>
+      </c>
+      <c r="I73" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J73" s="94" t="inlineStr">
+        <is>
+          <t>Amit Nawandhar</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B74" s="95" t="inlineStr">
+        <is>
+          <t>4:40PM</t>
+        </is>
+      </c>
+      <c r="C74" s="95" t="inlineStr">
+        <is>
+          <t>5:00PM</t>
+        </is>
+      </c>
+      <c r="D74" s="95" t="inlineStr">
+        <is>
+          <t>41 and above</t>
+        </is>
+      </c>
+      <c r="E74" s="95" t="n">
+        <v>32</v>
+      </c>
+      <c r="F74" s="95" t="inlineStr">
+        <is>
+          <t>41P-6</t>
+        </is>
+      </c>
+      <c r="G74" s="95" t="inlineStr">
+        <is>
+          <t>Board 2</t>
+        </is>
+      </c>
+      <c r="H74" s="95" t="inlineStr">
+        <is>
+          <t>Piyush Makharia</t>
+        </is>
+      </c>
+      <c r="I74" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J74" s="95" t="inlineStr">
+        <is>
+          <t>Adil Khan</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B75" s="94" t="inlineStr">
+        <is>
+          <t>5:00PM</t>
+        </is>
+      </c>
+      <c r="C75" s="94" t="inlineStr">
+        <is>
+          <t>5:20PM</t>
+        </is>
+      </c>
+      <c r="D75" s="94" t="inlineStr">
+        <is>
+          <t>21 to 40</t>
+        </is>
+      </c>
+      <c r="E75" s="94" t="n">
+        <v>33</v>
+      </c>
+      <c r="F75" s="94" t="inlineStr">
+        <is>
+          <t>2140-15</t>
+        </is>
+      </c>
+      <c r="G75" s="94" t="inlineStr">
+        <is>
+          <t>Board 1</t>
+        </is>
+      </c>
+      <c r="H75" s="94" t="inlineStr">
+        <is>
+          <t>Rahul Garg</t>
+        </is>
+      </c>
+      <c r="I75" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J75" s="94" t="inlineStr">
+        <is>
+          <t>Tejas doshi</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B76" s="95" t="inlineStr">
+        <is>
+          <t>5:00PM</t>
+        </is>
+      </c>
+      <c r="C76" s="95" t="inlineStr">
+        <is>
+          <t>5:20PM</t>
+        </is>
+      </c>
+      <c r="D76" s="95" t="inlineStr">
+        <is>
+          <t>41 and above</t>
+        </is>
+      </c>
+      <c r="E76" s="95" t="n">
+        <v>34</v>
+      </c>
+      <c r="F76" s="95" t="inlineStr">
+        <is>
+          <t>41P-11</t>
+        </is>
+      </c>
+      <c r="G76" s="95" t="inlineStr">
+        <is>
+          <t>Board 2</t>
+        </is>
+      </c>
+      <c r="H76" s="95" t="inlineStr">
+        <is>
+          <t>Sachin Malgadnkar</t>
+        </is>
+      </c>
+      <c r="I76" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J76" s="95" t="inlineStr">
+        <is>
+          <t>Sanjay Kumar</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B77" s="94" t="inlineStr">
+        <is>
+          <t>5:20PM</t>
+        </is>
+      </c>
+      <c r="C77" s="94" t="inlineStr">
+        <is>
+          <t>5:40PM</t>
+        </is>
+      </c>
+      <c r="D77" s="94" t="inlineStr">
+        <is>
+          <t>21 to 40</t>
+        </is>
+      </c>
+      <c r="E77" s="94" t="n">
+        <v>35</v>
+      </c>
+      <c r="F77" s="94" t="inlineStr">
+        <is>
+          <t>2140-11</t>
+        </is>
+      </c>
+      <c r="G77" s="94" t="inlineStr">
+        <is>
+          <t>Board 1</t>
+        </is>
+      </c>
+      <c r="H77" s="94" t="inlineStr">
+        <is>
+          <t>Swati Tripathi</t>
+        </is>
+      </c>
+      <c r="I77" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J77" s="94" t="inlineStr">
+        <is>
+          <t>Nikunj Jhala</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B78" s="95" t="inlineStr">
+        <is>
+          <t>5:20PM</t>
+        </is>
+      </c>
+      <c r="C78" s="95" t="inlineStr">
+        <is>
+          <t>5:40PM</t>
+        </is>
+      </c>
+      <c r="D78" s="95" t="inlineStr">
+        <is>
+          <t>41 and above</t>
+        </is>
+      </c>
+      <c r="E78" s="95" t="n">
+        <v>36</v>
+      </c>
+      <c r="F78" s="95" t="inlineStr">
+        <is>
+          <t>41P-16</t>
+        </is>
+      </c>
+      <c r="G78" s="95" t="inlineStr">
+        <is>
+          <t>Board 2</t>
+        </is>
+      </c>
+      <c r="H78" s="95" t="inlineStr">
+        <is>
+          <t>Adil Khan</t>
+        </is>
+      </c>
+      <c r="I78" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J78" s="95" t="inlineStr">
+        <is>
+          <t>Harkishin malkan</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B79" s="94" t="inlineStr">
+        <is>
+          <t>5:40PM</t>
+        </is>
+      </c>
+      <c r="C79" s="94" t="inlineStr">
+        <is>
+          <t>6:00PM</t>
+        </is>
+      </c>
+      <c r="D79" s="94" t="inlineStr">
+        <is>
+          <t>12 to 20</t>
+        </is>
+      </c>
+      <c r="E79" s="94" t="n">
+        <v>37</v>
+      </c>
+      <c r="F79" s="94" t="inlineStr">
+        <is>
+          <t>1220-FINAL</t>
+        </is>
+      </c>
+      <c r="G79" s="94" t="inlineStr">
+        <is>
+          <t>Board 2</t>
+        </is>
+      </c>
+      <c r="H79" s="94" t="inlineStr">
+        <is>
+          <t>Pool 1st</t>
+        </is>
+      </c>
+      <c r="I79" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J79" s="94" t="inlineStr">
+        <is>
+          <t>Pool 2nd</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B80" s="95" t="inlineStr">
+        <is>
+          <t>5:40PM</t>
+        </is>
+      </c>
+      <c r="C80" s="95" t="inlineStr">
+        <is>
+          <t>6:00PM</t>
+        </is>
+      </c>
+      <c r="D80" s="95" t="inlineStr">
+        <is>
+          <t>41 and above</t>
+        </is>
+      </c>
+      <c r="E80" s="95" t="n">
+        <v>38</v>
+      </c>
+      <c r="F80" s="95" t="inlineStr">
+        <is>
+          <t>41P-17</t>
+        </is>
+      </c>
+      <c r="G80" s="95" t="inlineStr">
+        <is>
+          <t>Board 1</t>
+        </is>
+      </c>
+      <c r="H80" s="95" t="inlineStr">
+        <is>
+          <t>Sachin Malgadnkar</t>
+        </is>
+      </c>
+      <c r="I80" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J80" s="95" t="inlineStr">
+        <is>
+          <t>Ajit nair</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B81" s="94" t="inlineStr">
+        <is>
+          <t>6:00PM</t>
+        </is>
+      </c>
+      <c r="C81" s="94" t="inlineStr">
+        <is>
+          <t>6:20PM</t>
+        </is>
+      </c>
+      <c r="D81" s="94" t="inlineStr">
+        <is>
+          <t>21 to 40</t>
+        </is>
+      </c>
+      <c r="E81" s="94" t="n">
+        <v>39</v>
+      </c>
+      <c r="F81" s="94" t="inlineStr">
+        <is>
+          <t>2140-7</t>
+        </is>
+      </c>
+      <c r="G81" s="94" t="inlineStr">
+        <is>
+          <t>Board 1</t>
+        </is>
+      </c>
+      <c r="H81" s="94" t="inlineStr">
+        <is>
+          <t>Rahul Garg</t>
+        </is>
+      </c>
+      <c r="I81" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J81" s="94" t="inlineStr">
+        <is>
+          <t>Nikunj Jhala</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B82" s="95" t="inlineStr">
+        <is>
+          <t>6:00PM</t>
+        </is>
+      </c>
+      <c r="C82" s="95" t="inlineStr">
+        <is>
+          <t>6:20PM</t>
+        </is>
+      </c>
+      <c r="D82" s="95" t="inlineStr">
+        <is>
+          <t>41 and above</t>
+        </is>
+      </c>
+      <c r="E82" s="95" t="n">
+        <v>40</v>
+      </c>
+      <c r="F82" s="95" t="inlineStr">
+        <is>
+          <t>41P-18</t>
+        </is>
+      </c>
+      <c r="G82" s="95" t="inlineStr">
+        <is>
+          <t>Board 2</t>
+        </is>
+      </c>
+      <c r="H82" s="95" t="inlineStr">
+        <is>
+          <t>Piyush Makharia</t>
+        </is>
+      </c>
+      <c r="I82" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J82" s="95" t="inlineStr">
+        <is>
+          <t>Harkishin malkan</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B83" s="94" t="inlineStr">
+        <is>
+          <t>6:20PM</t>
+        </is>
+      </c>
+      <c r="C83" s="94" t="inlineStr">
+        <is>
+          <t>6:40PM</t>
+        </is>
+      </c>
+      <c r="D83" s="94" t="inlineStr">
+        <is>
+          <t>Under 11</t>
+        </is>
+      </c>
+      <c r="E83" s="94" t="n">
+        <v>41</v>
+      </c>
+      <c r="F83" s="94" t="inlineStr">
+        <is>
+          <t>U11-FINAL</t>
+        </is>
+      </c>
+      <c r="G83" s="94" t="inlineStr">
+        <is>
+          <t>Board 1</t>
+        </is>
+      </c>
+      <c r="H83" s="94" t="inlineStr">
+        <is>
+          <t>Pool 1st</t>
+        </is>
+      </c>
+      <c r="I83" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J83" s="94" t="inlineStr">
+        <is>
+          <t>Pool 2nd</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B84" s="95" t="inlineStr">
+        <is>
+          <t>6:30PM</t>
+        </is>
+      </c>
+      <c r="C84" s="95" t="inlineStr">
+        <is>
+          <t>6:50PM</t>
+        </is>
+      </c>
+      <c r="D84" s="95" t="inlineStr">
+        <is>
+          <t>21 to 40</t>
+        </is>
+      </c>
+      <c r="E84" s="95" t="n">
+        <v>42</v>
+      </c>
+      <c r="F84" s="95" t="inlineStr">
+        <is>
+          <t>2140-14</t>
+        </is>
+      </c>
+      <c r="G84" s="95" t="inlineStr">
+        <is>
+          <t>Board 2</t>
+        </is>
+      </c>
+      <c r="H84" s="95" t="inlineStr">
+        <is>
+          <t>Tej</t>
+        </is>
+      </c>
+      <c r="I84" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J84" s="95" t="inlineStr">
+        <is>
+          <t>Nikunj Jhala</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B85" s="94" t="inlineStr">
+        <is>
+          <t>6:40PM</t>
+        </is>
+      </c>
+      <c r="C85" s="94" t="inlineStr">
+        <is>
+          <t>7:00PM</t>
+        </is>
+      </c>
+      <c r="D85" s="94" t="inlineStr">
+        <is>
+          <t>41 and above</t>
+        </is>
+      </c>
+      <c r="E85" s="94" t="n">
+        <v>43</v>
+      </c>
+      <c r="F85" s="94" t="inlineStr">
+        <is>
+          <t>41P-7</t>
+        </is>
+      </c>
+      <c r="G85" s="94" t="inlineStr">
+        <is>
+          <t>Board 1</t>
+        </is>
+      </c>
+      <c r="H85" s="94" t="inlineStr">
+        <is>
+          <t>Piyush Makharia</t>
+        </is>
+      </c>
+      <c r="I85" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J85" s="94" t="inlineStr">
+        <is>
+          <t>Sachin Malgadnkar</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B86" s="95" t="inlineStr">
+        <is>
+          <t>6:50PM</t>
+        </is>
+      </c>
+      <c r="C86" s="95" t="inlineStr">
+        <is>
+          <t>7:10PM</t>
+        </is>
+      </c>
+      <c r="D86" s="95" t="inlineStr">
+        <is>
+          <t>41 and above</t>
+        </is>
+      </c>
+      <c r="E86" s="95" t="n">
+        <v>44</v>
+      </c>
+      <c r="F86" s="95" t="inlineStr">
+        <is>
+          <t>41P-20</t>
+        </is>
+      </c>
+      <c r="G86" s="95" t="inlineStr">
+        <is>
+          <t>Board 2</t>
+        </is>
+      </c>
+      <c r="H86" s="95" t="inlineStr">
+        <is>
+          <t>Ajit nair</t>
+        </is>
+      </c>
+      <c r="I86" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J86" s="95" t="inlineStr">
+        <is>
+          <t>Harkishin malkan</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B87" s="94" t="inlineStr">
+        <is>
+          <t>7:00PM</t>
+        </is>
+      </c>
+      <c r="C87" s="94" t="inlineStr">
+        <is>
+          <t>7:20PM</t>
+        </is>
+      </c>
+      <c r="D87" s="94" t="inlineStr">
+        <is>
+          <t>21 to 40</t>
+        </is>
+      </c>
+      <c r="E87" s="94" t="n">
+        <v>45</v>
+      </c>
+      <c r="F87" s="94" t="inlineStr">
+        <is>
+          <t>2140-8</t>
+        </is>
+      </c>
+      <c r="G87" s="94" t="inlineStr">
+        <is>
+          <t>Board 1</t>
+        </is>
+      </c>
+      <c r="H87" s="94" t="inlineStr">
+        <is>
+          <t>Tejas doshi</t>
+        </is>
+      </c>
+      <c r="I87" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J87" s="94" t="inlineStr">
+        <is>
+          <t>Nikunj Jhala</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B88" s="95" t="inlineStr">
+        <is>
+          <t>7:10PM</t>
+        </is>
+      </c>
+      <c r="C88" s="95" t="inlineStr">
+        <is>
+          <t>7:30PM</t>
+        </is>
+      </c>
+      <c r="D88" s="95" t="inlineStr">
+        <is>
+          <t>41 and above</t>
+        </is>
+      </c>
+      <c r="E88" s="95" t="n">
+        <v>46</v>
+      </c>
+      <c r="F88" s="95" t="inlineStr">
+        <is>
+          <t>41P-10</t>
+        </is>
+      </c>
+      <c r="G88" s="95" t="inlineStr">
+        <is>
+          <t>Board 2</t>
+        </is>
+      </c>
+      <c r="H88" s="95" t="inlineStr">
+        <is>
+          <t>Adil Khan</t>
+        </is>
+      </c>
+      <c r="I88" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J88" s="95" t="inlineStr">
+        <is>
+          <t>Prasad Akshintala</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B89" s="94" t="inlineStr">
+        <is>
+          <t>7:20PM</t>
+        </is>
+      </c>
+      <c r="C89" s="94" t="inlineStr">
+        <is>
+          <t>7:40PM</t>
+        </is>
+      </c>
+      <c r="D89" s="94" t="inlineStr">
+        <is>
+          <t>41 and above</t>
+        </is>
+      </c>
+      <c r="E89" s="94" t="n">
+        <v>47</v>
+      </c>
+      <c r="F89" s="94" t="inlineStr">
+        <is>
+          <t>41P-14</t>
+        </is>
+      </c>
+      <c r="G89" s="94" t="inlineStr">
+        <is>
+          <t>Board 1</t>
+        </is>
+      </c>
+      <c r="H89" s="94" t="inlineStr">
+        <is>
+          <t>Sanjay Kumar</t>
+        </is>
+      </c>
+      <c r="I89" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J89" s="94" t="inlineStr">
+        <is>
+          <t>Harkishin malkan</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B90" s="95" t="inlineStr">
+        <is>
+          <t>7:30PM</t>
+        </is>
+      </c>
+      <c r="C90" s="95" t="inlineStr">
+        <is>
+          <t>7:50PM</t>
+        </is>
+      </c>
+      <c r="D90" s="95" t="inlineStr">
+        <is>
+          <t>21 to 40</t>
+        </is>
+      </c>
+      <c r="E90" s="95" t="n">
+        <v>48</v>
+      </c>
+      <c r="F90" s="95" t="inlineStr">
+        <is>
+          <t>2140-FINAL</t>
+        </is>
+      </c>
+      <c r="G90" s="95" t="inlineStr">
+        <is>
+          <t>Board 2</t>
+        </is>
+      </c>
+      <c r="H90" s="95" t="inlineStr">
+        <is>
+          <t>Pool 1st</t>
+        </is>
+      </c>
+      <c r="I90" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J90" s="95" t="inlineStr">
+        <is>
+          <t>Pool 2nd</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B91" s="94" t="inlineStr">
+        <is>
+          <t>7:40PM</t>
+        </is>
+      </c>
+      <c r="C91" s="94" t="inlineStr">
+        <is>
+          <t>8:00PM</t>
+        </is>
+      </c>
+      <c r="D91" s="94" t="inlineStr">
+        <is>
+          <t>41 and above</t>
+        </is>
+      </c>
+      <c r="E91" s="94" t="n">
+        <v>49</v>
+      </c>
+      <c r="F91" s="94" t="inlineStr">
+        <is>
+          <t>41P-5</t>
+        </is>
+      </c>
+      <c r="G91" s="94" t="inlineStr">
+        <is>
+          <t>Board 1</t>
+        </is>
+      </c>
+      <c r="H91" s="94" t="inlineStr">
+        <is>
+          <t>Prasad Akshintala</t>
+        </is>
+      </c>
+      <c r="I91" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J91" s="94" t="inlineStr">
+        <is>
+          <t>Ajit nair</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B92" s="95" t="inlineStr">
+        <is>
+          <t>7:50PM</t>
+        </is>
+      </c>
+      <c r="C92" s="95" t="inlineStr">
+        <is>
+          <t>8:10PM</t>
+        </is>
+      </c>
+      <c r="D92" s="95" t="inlineStr">
+        <is>
+          <t>41 and above</t>
+        </is>
+      </c>
+      <c r="E92" s="95" t="n">
+        <v>50</v>
+      </c>
+      <c r="F92" s="95" t="inlineStr">
+        <is>
+          <t>41P-21</t>
+        </is>
+      </c>
+      <c r="G92" s="95" t="inlineStr">
+        <is>
+          <t>Board 2</t>
+        </is>
+      </c>
+      <c r="H92" s="95" t="inlineStr">
+        <is>
+          <t>Sachin Malgadnkar</t>
+        </is>
+      </c>
+      <c r="I92" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J92" s="95" t="inlineStr">
+        <is>
+          <t>Harkishin malkan</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B93" s="94" t="inlineStr">
+        <is>
+          <t>8:10PM</t>
+        </is>
+      </c>
+      <c r="C93" s="94" t="inlineStr">
+        <is>
+          <t>8:30PM</t>
+        </is>
+      </c>
+      <c r="D93" s="94" t="inlineStr">
+        <is>
+          <t>41 and above</t>
+        </is>
+      </c>
+      <c r="E93" s="94" t="n">
+        <v>51</v>
+      </c>
+      <c r="F93" s="94" t="inlineStr">
+        <is>
+          <t>41P-4</t>
+        </is>
+      </c>
+      <c r="G93" s="94" t="inlineStr">
+        <is>
+          <t>Board 1</t>
+        </is>
+      </c>
+      <c r="H93" s="94" t="inlineStr">
+        <is>
+          <t>Piyush Makharia</t>
+        </is>
+      </c>
+      <c r="I93" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J93" s="94" t="inlineStr">
+        <is>
+          <t>Sanjay Kumar</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B94" s="95" t="inlineStr">
+        <is>
+          <t>8:20PM</t>
+        </is>
+      </c>
+      <c r="C94" s="95" t="inlineStr">
+        <is>
+          <t>8:40PM</t>
+        </is>
+      </c>
+      <c r="D94" s="95" t="inlineStr">
+        <is>
+          <t>41 and above</t>
+        </is>
+      </c>
+      <c r="E94" s="95" t="n">
+        <v>52</v>
+      </c>
+      <c r="F94" s="95" t="inlineStr">
+        <is>
+          <t>41P-13</t>
+        </is>
+      </c>
+      <c r="G94" s="95" t="inlineStr">
+        <is>
+          <t>Board 2</t>
+        </is>
+      </c>
+      <c r="H94" s="95" t="inlineStr">
+        <is>
+          <t>Sachin Malgadnkar</t>
+        </is>
+      </c>
+      <c r="I94" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J94" s="95" t="inlineStr">
+        <is>
+          <t>Prasad Akshintala</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B95" s="94" t="inlineStr">
+        <is>
+          <t>8:55PM</t>
+        </is>
+      </c>
+      <c r="C95" s="94" t="inlineStr">
+        <is>
+          <t>9:15PM</t>
+        </is>
+      </c>
+      <c r="D95" s="94" t="inlineStr">
+        <is>
+          <t>41 and above</t>
+        </is>
+      </c>
+      <c r="E95" s="94" t="n">
+        <v>53</v>
+      </c>
+      <c r="F95" s="94" t="inlineStr">
+        <is>
+          <t>41P-15</t>
+        </is>
+      </c>
+      <c r="G95" s="94" t="inlineStr">
+        <is>
+          <t>Board 1</t>
+        </is>
+      </c>
+      <c r="H95" s="94" t="inlineStr">
+        <is>
+          <t>Adil Khan</t>
+        </is>
+      </c>
+      <c r="I95" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J95" s="94" t="inlineStr">
+        <is>
+          <t>Sachin Malgadnkar</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B96" s="95" t="inlineStr">
+        <is>
+          <t>9:35PM</t>
+        </is>
+      </c>
+      <c r="C96" s="95" t="inlineStr">
+        <is>
+          <t>9:55PM</t>
+        </is>
+      </c>
+      <c r="D96" s="95" t="inlineStr">
+        <is>
+          <t>41 and above</t>
+        </is>
+      </c>
+      <c r="E96" s="95" t="n">
+        <v>54</v>
+      </c>
+      <c r="F96" s="95" t="inlineStr">
+        <is>
+          <t>41P-19</t>
+        </is>
+      </c>
+      <c r="G96" s="95" t="inlineStr">
+        <is>
+          <t>Board 2</t>
+        </is>
+      </c>
+      <c r="H96" s="95" t="inlineStr">
+        <is>
+          <t>Prasad Akshintala</t>
+        </is>
+      </c>
+      <c r="I96" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J96" s="95" t="inlineStr">
+        <is>
+          <t>Harkishin malkan</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B97" s="94" t="inlineStr">
+        <is>
+          <t>9:35PM</t>
+        </is>
+      </c>
+      <c r="C97" s="94" t="inlineStr">
+        <is>
+          <t>9:55PM</t>
+        </is>
+      </c>
+      <c r="D97" s="94" t="inlineStr">
+        <is>
+          <t>41 and above</t>
+        </is>
+      </c>
+      <c r="E97" s="94" t="n">
+        <v>55</v>
+      </c>
+      <c r="F97" s="94" t="inlineStr">
+        <is>
+          <t>41P-9</t>
+        </is>
+      </c>
+      <c r="G97" s="94" t="inlineStr">
+        <is>
+          <t>Board 1</t>
+        </is>
+      </c>
+      <c r="H97" s="94" t="inlineStr">
+        <is>
+          <t>Adil Khan</t>
+        </is>
+      </c>
+      <c r="I97" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J97" s="94" t="inlineStr">
+        <is>
+          <t>Sanjay Kumar</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="95" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B98" s="95" t="inlineStr">
+        <is>
+          <t>9:55PM</t>
+        </is>
+      </c>
+      <c r="C98" s="95" t="inlineStr">
+        <is>
+          <t>10:15PM</t>
+        </is>
+      </c>
+      <c r="D98" s="95" t="inlineStr">
+        <is>
+          <t>41 and above</t>
+        </is>
+      </c>
+      <c r="E98" s="95" t="n">
+        <v>56</v>
+      </c>
+      <c r="F98" s="95" t="inlineStr">
+        <is>
+          <t>41P-SF1</t>
+        </is>
+      </c>
+      <c r="G98" s="95" t="inlineStr">
+        <is>
+          <t>Board 1</t>
+        </is>
+      </c>
+      <c r="H98" s="95" t="inlineStr">
+        <is>
+          <t>Round Robin 1st</t>
+        </is>
+      </c>
+      <c r="I98" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J98" s="95" t="inlineStr">
+        <is>
+          <t>Round Robin 4th</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="94" t="inlineStr">
+        <is>
+          <t>Aug 15</t>
+        </is>
+      </c>
+      <c r="B99" s="94" t="inlineStr">
+        <is>
+          <t>9:55PM</t>
+        </is>
+      </c>
+      <c r="C99" s="94" t="inlineStr">
+        <is>
+          <t>10:15PM</t>
+        </is>
+      </c>
+      <c r="D99" s="94" t="inlineStr">
+        <is>
+          <t>41 and above</t>
+        </is>
+      </c>
+      <c r="E99" s="94" t="n">
+        <v>57</v>
+      </c>
+      <c r="F99" s="94" t="inlineStr">
+        <is>
+          <t>41P-SF2</t>
+        </is>
+      </c>
+      <c r="G99" s="94" t="inlineStr">
+        <is>
+          <t>Board 2</t>
+        </is>
+      </c>
+      <c r="H99" s="94" t="inlineStr">
+        <is>
+          <t>Round Robin 2nd</t>
+        </is>
+      </c>
+      <c r="I99" s="94" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J99" s="94" t="inlineStr">
+        <is>
+          <t>Round Robin 3rd</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="95" t="inlineStr">
+        <is>
+          <t>Aug 16</t>
+        </is>
+      </c>
+      <c r="B100" s="95" t="inlineStr">
+        <is>
+          <t>8:00AM</t>
+        </is>
+      </c>
+      <c r="C100" s="95" t="inlineStr">
+        <is>
+          <t>8:20AM</t>
+        </is>
+      </c>
+      <c r="D100" s="95" t="inlineStr">
+        <is>
+          <t>41 and above</t>
+        </is>
+      </c>
+      <c r="E100" s="95" t="n">
+        <v>58</v>
+      </c>
+      <c r="F100" s="95" t="inlineStr">
+        <is>
+          <t>41P-FINAL</t>
+        </is>
+      </c>
+      <c r="G100" s="95" t="inlineStr">
+        <is>
+          <t>Board 1</t>
+        </is>
+      </c>
+      <c r="H100" s="95" t="inlineStr">
+        <is>
+          <t>Winner SF1</t>
+        </is>
+      </c>
+      <c r="I100" s="95" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="J100" s="95" t="inlineStr">
+        <is>
+          <t>Winner SF2</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A21:J21"/>
+    <mergeCell ref="A30:J30"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A41:J41"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:J49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3479,7 +7115,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4777,6 +8413,977 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:J28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="98" t="inlineStr">
+        <is>
+          <t>HOURLY MATCH GRID</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="99" t="inlineStr">
+        <is>
+          <t>Which matches are on court/table/board in each 1-hour window, by event. Shaded rows are scheduled breaks (no matches anywhere).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="74" t="inlineStr">
+        <is>
+          <t>Time Slot</t>
+        </is>
+      </c>
+      <c r="B4" s="74" t="inlineStr">
+        <is>
+          <t>TT - Women's</t>
+        </is>
+      </c>
+      <c r="C4" s="74" t="inlineStr">
+        <is>
+          <t>TT - Men's</t>
+        </is>
+      </c>
+      <c r="D4" s="74" t="inlineStr">
+        <is>
+          <t>TT - Doubles</t>
+        </is>
+      </c>
+      <c r="E4" s="74" t="inlineStr">
+        <is>
+          <t>Carrom - Men's</t>
+        </is>
+      </c>
+      <c r="F4" s="74" t="inlineStr">
+        <is>
+          <t>Carrom - Women's</t>
+        </is>
+      </c>
+      <c r="G4" s="74" t="inlineStr">
+        <is>
+          <t>Carrom - Doubles</t>
+        </is>
+      </c>
+      <c r="H4" s="74" t="inlineStr">
+        <is>
+          <t>Pool</t>
+        </is>
+      </c>
+      <c r="I4" s="74" t="inlineStr">
+        <is>
+          <t>Chess</t>
+        </is>
+      </c>
+      <c r="J4" s="74" t="inlineStr">
+        <is>
+          <t>Squash</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="100" t="inlineStr">
+        <is>
+          <t>AUG 15</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="108" customHeight="1">
+      <c r="A6" s="102" t="inlineStr">
+        <is>
+          <t>Aug 15, 8 AM - 9 AM</t>
+        </is>
+      </c>
+      <c r="B6" s="103" t="inlineStr"/>
+      <c r="C6" s="103" t="inlineStr">
+        <is>
+          <t>8:00 AM  M1 A46-QF2: Vinod Agrawal vs Kishore Kumar
+8:00 AM  M2 A46-R1: Adil Khan vs Ajit nair
+8:15 AM  M3 A46-QF1: Winner R1 vs Sanjay Kumar
+8:15 AM  M4 A46-QF3: Ghansyam nawani vs HARSHAPRABHAT SHETTY
+8:30 AM  M5 A46-QF4: Mukul Joshi vs Sushil Dashpute
+8:30 AM  M6 A46-SF1: Winner QF1 vs Winner QF2
+8:45 AM  M7 A46-SF2: Winner QF3 vs Winner QF4
+8:45 AM  M8 U36-GB-1: Prakshal Shah vs Amar Parulekar</t>
+        </is>
+      </c>
+      <c r="D6" s="103" t="inlineStr"/>
+      <c r="E6" s="103" t="inlineStr">
+        <is>
+          <t>8:00 AM  M1 CM-U46-GA-1: Rahul Garg vs Anuj Shah
+8:15 AM  M2 CM-U46-GB-1: Nikunj Jhala vs Nilesh Bagaria
+8:15 AM  M3 CM-U46-GB-2: Mayank Aggarwal vs Amit Ranka
+8:15 AM  M4 CM-U46-GB-3: Amar Jain vs Vinit Padia
+8:30 AM  M5 CM-U46-GA-3: Abhishek Dugar vs Dr Rahul Modi
+8:45 AM  M6 CM-U15-1: Aarav Pilankar vs Yash agarwal
+8:45 AM  M7 CM-U46-GB-4: Nilesh Bagaria vs Amit Ranka
+8:45 AM  M8 CM-U46-GB-5: Mayank Aggarwal vs Vinit Padia</t>
+        </is>
+      </c>
+      <c r="F6" s="103" t="inlineStr">
+        <is>
+          <t>8:00 AM  M1 CW-1: Kaira vs Rashmi Pilankar
+8:00 AM  M2 CW-2: Shraddha malgadnkar vs Poornima Shriyan
+8:30 AM  M3 CW-3: Rashmi Pilankar vs Mohini Sharma
+8:30 AM  M4 CW-4: Kaira vs Shraddha malgadnkar</t>
+        </is>
+      </c>
+      <c r="G6" s="103" t="inlineStr"/>
+      <c r="H6" s="103" t="inlineStr">
+        <is>
+          <t>8:00 AM  M1 2639-GA-1: Suraj Kakkar vs Ravi Modi
+8:00 AM  M2 2639-GB-1: Dr Rahul Modi vs Japan Parikh
+8:20 AM  M3 2639-GA-2: Tapabrata Dutta vs Tej
+8:20 AM  M4 2639-GB-2: Ankur Mahante vs Sudip Parui
+8:40 AM  M5 2639-GA-8: Suraj Kakkar vs Tushar
+8:40 AM  M6 2639-GB-3: Japan Parikh vs Tanmay Sharma</t>
+        </is>
+      </c>
+      <c r="I6" s="103" t="inlineStr">
+        <is>
+          <t>8:00 AM  M1 U11-1: Rushabh vs Neev Chauhan
+8:00 AM  M2 U11-2: Kartik Relan vs Parth yadav
+8:20 AM  M3 1220-2: Aaditya Kumar vs Hryday Goyal
+8:20 AM  M4 2140-2: Swati Tripathi vs Amit Nawandhar
+8:40 AM  M5 U11-3: Rushabh vs Kartik Relan
+8:40 AM  M6 U11-4: Neev Chauhan vs Jimit Relan</t>
+        </is>
+      </c>
+      <c r="J6" s="103" t="inlineStr">
+        <is>
+          <t>8:00 AM  M1 GC-1: Aaditya Kumar vs Hryday Goyal
+8:18 AM  M2 U15-R1-M1: Peher Krunal Shah vs Aadit Joshi
+8:36 AM  M3 U15-R1-M2: Shaurya Tripathi vs Parth yadav
+8:54 AM  M4 GB-1: Ravi Modi vs Tejas doshi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="56" customHeight="1">
+      <c r="A7" s="102" t="inlineStr">
+        <is>
+          <t>Aug 15, 9 AM - 10 AM</t>
+        </is>
+      </c>
+      <c r="B7" s="104" t="inlineStr"/>
+      <c r="C7" s="104" t="inlineStr">
+        <is>
+          <t>9:00 AM  M9 U15-GA-1: Shaurya Tripathi vs Parth yadav
+9:00 AM  M10 U36-GA-2: Jashit Bajaj vs Tapabrata Dutta
+9:15 AM  M11 U15-GB-1: Viaan Neema vs Yash agarwal
+9:15 AM  M12 U26-2: Yuvraj jain vs Hryday Goyal</t>
+        </is>
+      </c>
+      <c r="D7" s="104" t="inlineStr"/>
+      <c r="E7" s="104" t="inlineStr">
+        <is>
+          <t>9:00 AM  M9 CM-U46-GA-2: Ankur Mahante vs Anuj Shah
+9:15 AM  M10 CM-U46-GA-7: Ravi Modi vs Abhishek Dugar
+9:15 AM  M11 CM-U46-GB-6: Nikunj Jhala vs Amar Jain
+9:15 AM  M12 CM-U46-GB-7: Vinit Padia vs Amit Ranka</t>
+        </is>
+      </c>
+      <c r="F7" s="104" t="inlineStr">
+        <is>
+          <t>9:00 AM  M5 CW-5: Poornima Shriyan vs Mohini Sharma
+9:00 AM  M6 CW-6: Rashmi Pilankar vs Shraddha malgadnkar</t>
+        </is>
+      </c>
+      <c r="G7" s="104" t="inlineStr"/>
+      <c r="H7" s="104" t="inlineStr">
+        <is>
+          <t>9:00 AM  M7 2639-GB-8: Dr Rahul Modi vs Sudip Parui
+9:00 AM  M8 40P-GA-1: Mayank Aggarwal vs Piyush Makharia
+9:20 AM  M9 2639-GA-4: Suraj Kakkar vs Tapabrata Dutta
+9:20 AM  M10 2639-GA-5: Tej vs Tushar</t>
+        </is>
+      </c>
+      <c r="I7" s="104" t="inlineStr">
+        <is>
+          <t>9:00 AM  M7 1220-1: Aadit Joshi vs Maitreya Manvik
+9:00 AM  M8 2140-6: Tej vs Swati Tripathi
+9:20 AM  M9 U11-5: Kartik Relan vs Jimit Relan
+9:20 AM  M10 U11-6: Rushabh vs Parth yadav</t>
+        </is>
+      </c>
+      <c r="J7" s="104" t="inlineStr">
+        <is>
+          <t>9:12 AM  M5 GC-2: Aaditya Kumar vs Shravan Gajera</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="56" customHeight="1">
+      <c r="A8" s="102" t="inlineStr">
+        <is>
+          <t>Aug 15, 10 AM - 11 AM</t>
+        </is>
+      </c>
+      <c r="B8" s="103" t="inlineStr">
+        <is>
+          <t>10:30 AM  M1 GA-M1: Nitika Aggarwal vs Deepali Acharya
+10:30 AM  M2 GA-M2: Nidhi Sharma vs Dr Divya patel
+10:45 AM  M3 GB-M1: Shubhanjali Bisht vs Miloni Parekh
+10:45 AM  M4 GB-M2: Renuka Tripathi vs Shama Gosalia</t>
+        </is>
+      </c>
+      <c r="C8" s="103" t="inlineStr"/>
+      <c r="D8" s="103" t="inlineStr"/>
+      <c r="E8" s="103" t="inlineStr">
+        <is>
+          <t>10:30 AM  M13 CM-U46-GA-4: Rahul Garg vs Dr Rahul Modi
+10:45 AM  M14 CM-U15-2: Shaurya Tripathi vs Aarav Pilankar
+10:45 AM  M15 CM-U46-GA-5: Abhishek Dugar vs Anuj Shah
+10:45 AM  M16 CM-U46-GA-8: Ravi Modi vs Ankur Mahante</t>
+        </is>
+      </c>
+      <c r="F8" s="103" t="inlineStr">
+        <is>
+          <t>10:30 AM  M7 CW-7: Kaira vs Poornima Shriyan
+10:30 AM  M8 CW-8: Shraddha malgadnkar vs Mohini Sharma</t>
+        </is>
+      </c>
+      <c r="G8" s="103" t="inlineStr"/>
+      <c r="H8" s="103" t="inlineStr">
+        <is>
+          <t>10:30 AM  M11 2639-GA-6: Suraj Kakkar vs Tej
+10:30 AM  M12 2639-GB-5: Sudip Parui vs Tanmay Sharma
+10:50 AM  M13 2639-GA-7: Tapabrata Dutta vs Tushar
+10:50 AM  M14 40P-GB-1: Vinay Sawant vs Mukul Joshi</t>
+        </is>
+      </c>
+      <c r="I8" s="103" t="inlineStr">
+        <is>
+          <t>10:30 AM  M11 U11-7: Rushabh vs Jimit Relan
+10:30 AM  M12 U11-8: Neev Chauhan vs Kartik Relan
+10:50 AM  M13 1220-3: Aadit Joshi vs Aaditya Kumar
+10:50 AM  M14 1220-4: Maitreya Manvik vs Hryday Goyal</t>
+        </is>
+      </c>
+      <c r="J8" s="103" t="inlineStr">
+        <is>
+          <t>10:30 AM  M6 U15-R1-M3: Viaan Neema vs Yash agarwal
+10:48 AM  M7 GA-1: Dr Rahul Modi vs Mayank Aggarwal</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="121" customHeight="1">
+      <c r="A9" s="102" t="inlineStr">
+        <is>
+          <t>Aug 15, 11 AM - 12 PM</t>
+        </is>
+      </c>
+      <c r="B9" s="104" t="inlineStr">
+        <is>
+          <t>11:00 AM  M5 GA-M3: Nidhi Sharma vs Nitika Aggarwal
+11:00 AM  M6 GA-M4: Dr Divya patel vs Deepali Acharya
+11:15 AM  M7 GB-M3: Shubhanjali Bisht vs Renuka Tripathi
+11:15 AM  M8 GB-M4: Miloni Parekh vs Shama Gosalia
+11:30 AM  M9 GA-M5: Nidhi Sharma vs Deepali Acharya
+11:30 AM  M10 GA-M6: Dr Divya patel vs Nitika Aggarwal
+11:45 AM  M11 GB-M5: Shubhanjali Bisht vs Shama Gosalia
+11:45 AM  M12 GB-M6: Miloni Parekh vs Renuka Tripathi</t>
+        </is>
+      </c>
+      <c r="C9" s="104" t="inlineStr"/>
+      <c r="D9" s="104" t="inlineStr"/>
+      <c r="E9" s="104" t="inlineStr">
+        <is>
+          <t>11:00 AM  M17 CM-U46-GB-8: Nikunj Jhala vs Vinit Padia
+11:15 AM  M18 CM-U46-GA-12: Ravi Modi vs Anuj Shah
+11:15 AM  M19 CM-U46-GA-9: Abhishek Dugar vs Ankur Mahante
+11:30 AM  M20 CM-U15-3: Shaurya Tripathi vs Yash agarwal
+11:30 AM  M21 CM-U46-GB-12: Mayank Aggarwal vs Nikunj Jhala
+11:30 AM  M22 CM-U46-GB-9: Amar Jain vs Nilesh Bagaria
+11:45 AM  M23 CM-A46-GA-1: Adil Khan vs Mr. Hiral Khadepau
+11:45 AM  M24 CM-A46-GB-1: Vinod Agrawal vs Prasad Akshintala
+11:45 AM  M25 CM-U46-GA-10: Rahul Garg vs Ravi Modi</t>
+        </is>
+      </c>
+      <c r="F9" s="104" t="inlineStr">
+        <is>
+          <t>11:00 AM  M9 CW-10: Rashmi Pilankar vs Poornima Shriyan
+11:00 AM  M10 CW-9: Kaira vs Mohini Sharma
+11:15 AM  M11 CW-FINAL: Pool 1st vs Pool 2nd</t>
+        </is>
+      </c>
+      <c r="G9" s="104" t="inlineStr"/>
+      <c r="H9" s="104" t="inlineStr">
+        <is>
+          <t>11:10 AM  M15 2639-GB-6: Japan Parikh vs Sudip Parui
+11:10 AM  M16 40P-GA-3: Piyush Makharia vs Oscar Dsa
+11:30 AM  M17 40P-GA-2: Vinit Padia vs Amit Ranka
+11:30 AM  M18 40P-GB-6: Mukul Joshi vs Sanjay Kumar
+11:50 AM  M19 2639-GB-4: Dr Rahul Modi vs Ankur Mahante
+11:50 AM  M20 U26-GA-1: Sankalp Bhatnagar vs Rutvij sawant</t>
+        </is>
+      </c>
+      <c r="I9" s="104" t="inlineStr">
+        <is>
+          <t>11:10 AM  M15 2140-3: Rahul Garg vs Amit Nawandhar
+11:10 AM  M16 U11-9: Neev Chauhan vs Parth yadav
+11:30 AM  M17 1220-5: Aadit Joshi vs Hryday Goyal
+11:30 AM  M18 1220-6: Maitreya Manvik vs Aaditya Kumar
+11:50 AM  M19 2140-1: Tej vs Tejas doshi
+11:50 AM  M20 U11-10: Parth yadav vs Jimit Relan</t>
+        </is>
+      </c>
+      <c r="J9" s="104" t="inlineStr">
+        <is>
+          <t>11:06 AM  M8 U15-SF1: Winner R1-M2 vs Hridh jhala
+11:24 AM  M9 GA-2: Dr Rahul Modi vs Tanmay Sharma
+11:42 AM  M10 U15-SF2: Winner R1-M1 vs Winner R1-M3</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="105" t="inlineStr">
+        <is>
+          <t>Aug 15, 12 PM - 1 PM</t>
+        </is>
+      </c>
+      <c r="B10" s="106" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK — no matches</t>
+        </is>
+      </c>
+      <c r="C10" s="88" t="n"/>
+      <c r="D10" s="88" t="n"/>
+      <c r="E10" s="88" t="n"/>
+      <c r="F10" s="88" t="n"/>
+      <c r="G10" s="88" t="n"/>
+      <c r="H10" s="88" t="n"/>
+      <c r="I10" s="88" t="n"/>
+      <c r="J10" s="84" t="n"/>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="105" t="inlineStr">
+        <is>
+          <t>Aug 15, 1 PM - 2 PM</t>
+        </is>
+      </c>
+      <c r="B11" s="106" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK — no matches</t>
+        </is>
+      </c>
+      <c r="C11" s="88" t="n"/>
+      <c r="D11" s="88" t="n"/>
+      <c r="E11" s="88" t="n"/>
+      <c r="F11" s="88" t="n"/>
+      <c r="G11" s="88" t="n"/>
+      <c r="H11" s="88" t="n"/>
+      <c r="I11" s="88" t="n"/>
+      <c r="J11" s="84" t="n"/>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="105" t="inlineStr">
+        <is>
+          <t>Aug 15, 2 PM - 3 PM</t>
+        </is>
+      </c>
+      <c r="B12" s="106" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK — no matches</t>
+        </is>
+      </c>
+      <c r="C12" s="88" t="n"/>
+      <c r="D12" s="88" t="n"/>
+      <c r="E12" s="88" t="n"/>
+      <c r="F12" s="88" t="n"/>
+      <c r="G12" s="88" t="n"/>
+      <c r="H12" s="88" t="n"/>
+      <c r="I12" s="88" t="n"/>
+      <c r="J12" s="84" t="n"/>
+    </row>
+    <row r="13" ht="160" customHeight="1">
+      <c r="A13" s="102" t="inlineStr">
+        <is>
+          <t>Aug 15, 3 PM - 4 PM</t>
+        </is>
+      </c>
+      <c r="B13" s="104" t="inlineStr">
+        <is>
+          <t>3:00 PM  M13 SF1: 1st of Group A vs 2nd of Group B
+3:00 PM  M14 SF2: 1st of Group B vs 2nd of Group A
+3:15 PM  M15 FINAL: Winner SF1 vs Winner SF2</t>
+        </is>
+      </c>
+      <c r="C13" s="104" t="inlineStr">
+        <is>
+          <t>3:15 PM  M13 U46-GA-9: Sudip Parui vs Anuj Shah
+3:30 PM  M14 U26-3: Yuvraj jain vs Pranit Shriyan
+3:30 PM  M15 U46-GB-8: Vinit Padia vs Nilesh Bagaria
+3:45 PM  M16 U15-GB-2: Viaan Neema vs Hridh jhala
+3:45 PM  M17 U46-GA-8: Sudip Parui vs Tanmay Sharma</t>
+        </is>
+      </c>
+      <c r="D13" s="104" t="inlineStr"/>
+      <c r="E13" s="104" t="inlineStr">
+        <is>
+          <t>3:00 PM  M26 CM-U46-GA-11: Rahul Garg vs Ankur Mahante
+3:00 PM  M27 CM-U46-GA-6: Dr Rahul Modi vs Anuj Shah
+3:00 PM  M28 CM-U46-GB-10: Vinit Padia vs Nilesh Bagaria
+3:15 PM  M29 CM-A46-GA-2: Vinay Sawant vs Mukul Joshi
+3:15 PM  M30 CM-A46-GB-4: Vinod Agrawal vs Gopal Krishna
+3:15 PM  M31 CM-U46-GB-11: Amar Jain vs Amit Ranka
+3:30 PM  M32 U15-FINAL: Pool 1st vs Pool 2nd
+3:35 PM  M33 CM-U46-GA-15: Dr Rahul Modi vs Ankur Mahante
+3:40 PM  M34 CM-U46-GB-13: Nikunj Jhala vs Amit Ranka
+3:45 PM  M35 CM-A46-GB-2: Sanjay Kumar vs Gopal Krishna
+3:50 PM  M36 CM-U46-GB-14: Mayank Aggarwal vs Amar Jain
+3:55 PM  M37 CM-A46-GA-3: Mukul Joshi vs Mr. Hiral Khadepau</t>
+        </is>
+      </c>
+      <c r="F13" s="104" t="inlineStr"/>
+      <c r="G13" s="104" t="inlineStr"/>
+      <c r="H13" s="104" t="inlineStr">
+        <is>
+          <t>3:00 PM  M21 2639-GA-3: Ravi Modi vs Tushar
+3:00 PM  M22 40P-GB-3: Adil Khan vs Prasad Akshintala
+3:20 PM  M23 40P-GA-7: Mayank Aggarwal vs Oscar Dsa
+3:20 PM  M24 U26-GA-2: Aadit Joshi vs Aaditya Kumar
+3:40 PM  M25 2639-GA-9: Ravi Modi vs Tapabrata Dutta
+3:40 PM  M26 U26-GB-1: Shravan Gajera vs Ishaan Merchant</t>
+        </is>
+      </c>
+      <c r="I13" s="104" t="inlineStr">
+        <is>
+          <t>3:00 PM  M21 2140-4: Swati Tripathi vs Tejas doshi
+3:00 PM  M22 41P-1: Piyush Makharia vs Ajit nair
+3:20 PM  M23 2140-10: Amit Nawandhar vs Nikunj Jhala
+3:20 PM  M24 41P-8: Prasad Akshintala vs Sanjay Kumar
+3:40 PM  M25 2140-9: Rahul Garg vs Tej
+3:40 PM  M26 41P-12: Adil Khan vs Ajit nair</t>
+        </is>
+      </c>
+      <c r="J13" s="104" t="inlineStr">
+        <is>
+          <t>3:00 PM  M11 GA-3: Tanmay Sharma vs Mayank Aggarwal
+3:18 PM  M12 GC-3: Hryday Goyal vs Shravan Gajera</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="121" customHeight="1">
+      <c r="A14" s="102" t="inlineStr">
+        <is>
+          <t>Aug 15, 4 PM - 5 PM</t>
+        </is>
+      </c>
+      <c r="B14" s="103" t="inlineStr"/>
+      <c r="C14" s="103" t="inlineStr">
+        <is>
+          <t>4:00 PM  M18 U36-GA-1: Jashit Bajaj vs Ravi Modi
+4:00 PM  M19 U36-GB-2: Prakshal Shah vs Tej
+4:15 PM  M20 U15-GB-3: Yash agarwal vs Hridh jhala
+4:15 PM  M21 U46-GA-2: Dr Rahul Modi vs Sudip Parui
+4:30 PM  M22 U15-GA-2: Shaurya Tripathi vs Aadit Joshi
+4:30 PM  M23 U46-GB-3: Nikunj Jhala vs Nilesh Bagaria
+4:45 PM  M24 U36-GA-3: Ravi Modi vs Tapabrata Dutta
+4:45 PM  M25 U46-GA-4: Dr Rahul Modi vs Anuj Shah</t>
+        </is>
+      </c>
+      <c r="D14" s="103" t="inlineStr"/>
+      <c r="E14" s="103" t="inlineStr">
+        <is>
+          <t>4:00 PM  M38 CM-U46-GA-14: Rahul Garg vs Abhishek Dugar
+4:05 PM  M39 CM-A46-GB-3: Vinod Agrawal vs Sanjay Kumar
+4:10 PM  M40 CM-U46-GB-15: Mayank Aggarwal vs Nilesh Bagaria
+4:15 PM  M41 CM-A46-GA-4: Vinay Sawant vs Adil Khan
+4:20 PM  M42 CM-A46-GB-5: Prasad Akshintala vs Gopal Krishna
+4:30 PM  M43 CM-U46-GA-13: Ravi Modi vs Dr Rahul Modi
+4:45 PM  M44 CM-A46-GB-6: Prasad Akshintala vs Sanjay Kumar
+4:45 PM  M45 U46-SF1: Group A 1st vs Group B 2nd
+4:45 PM  M46 U46-SF2: Group B 1st vs Group A 2nd</t>
+        </is>
+      </c>
+      <c r="F14" s="103" t="inlineStr"/>
+      <c r="G14" s="103" t="inlineStr"/>
+      <c r="H14" s="103" t="inlineStr">
+        <is>
+          <t>4:00 PM  M27 2639-GB-7: Japan Parikh vs Ankur Mahante
+4:00 PM  M28 40P-GA-4: Amit Ranka vs Oscar Dsa
+4:20 PM  M29 U26-GA-3: Aaditya Kumar vs Rutvij sawant
+4:20 PM  M30 U26-GB-2: Shravan Gajera vs Pranit Shriyan
+4:40 PM  M31 2639-GB-9: Ankur Mahante vs Tanmay Sharma
+4:40 PM  M32 40P-GA-5: Mayank Aggarwal vs Amit Ranka</t>
+        </is>
+      </c>
+      <c r="I14" s="103" t="inlineStr">
+        <is>
+          <t>4:00 PM  M27 2140-5: Amit Nawandhar vs Tejas doshi
+4:00 PM  M28 41P-3: Piyush Makharia vs Prasad Akshintala
+4:20 PM  M29 2140-13: Rahul Garg vs Swati Tripathi
+4:20 PM  M30 41P-2: Ajit nair vs Sanjay Kumar
+4:40 PM  M31 2140-12: Tej vs Amit Nawandhar
+4:40 PM  M32 41P-6: Piyush Makharia vs Adil Khan</t>
+        </is>
+      </c>
+      <c r="J14" s="103" t="inlineStr">
+        <is>
+          <t>4:20 PM  M13 GB-3: Tejas doshi vs Vinit Padia</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="108" customHeight="1">
+      <c r="A15" s="102" t="inlineStr">
+        <is>
+          <t>Aug 15, 5 PM - 6 PM</t>
+        </is>
+      </c>
+      <c r="B15" s="104" t="inlineStr"/>
+      <c r="C15" s="104" t="inlineStr">
+        <is>
+          <t>5:00 PM  M26 U46-GA-5: Ankur Mahante vs Sudip Parui
+5:00 PM  M27 U46-GB-10: Nilesh Bagaria vs Amit Ranka
+5:15 PM  M28 U26-8: Hryday Goyal vs Pranit Shriyan
+5:15 PM  M29 U46-GA-3: Dr Rahul Modi vs Tanmay Sharma
+5:30 PM  M30 U36-GB-3: Amar Parulekar vs Tej
+5:30 PM  M31 U46-GA-7: Ankur Mahante vs Anuj Shah
+5:45 PM  M32 U36-SF1: Group B 1st vs Group A 2nd
+5:45 PM  M33 U46-GB-4: Nikunj Jhala vs Amit Ranka</t>
+        </is>
+      </c>
+      <c r="D15" s="104" t="inlineStr"/>
+      <c r="E15" s="104" t="inlineStr">
+        <is>
+          <t>5:00 PM  M47 CM-A46-GA-5: Vinay Sawant vs Mr. Hiral Khadepau
+5:00 PM  M48 CM-A46-GA-6: Mukul Joshi vs Adil Khan
+5:00 PM  M49 U46-FINAL: Winner SF1 vs Winner SF2
+5:15 PM  M50 A46-SF1: Group A 1st vs Group B 2nd
+5:15 PM  M51 A46-SF2: Group B 1st vs Group A 2nd
+5:30 PM  M52 A46-FINAL: Winner SF1 vs Winner SF2</t>
+        </is>
+      </c>
+      <c r="F15" s="104" t="inlineStr"/>
+      <c r="G15" s="104" t="inlineStr"/>
+      <c r="H15" s="104" t="inlineStr">
+        <is>
+          <t>5:00 PM  M33 2639-GA-10: Ravi Modi vs Tej
+5:00 PM  M34 40P-GA-9: Vinit Padia vs Oscar Dsa
+5:20 PM  M35 40P-GA-6: Piyush Makharia vs Amit Ranka
+5:20 PM  M36 40P-GB-2: Vinay Sawant vs Prasad Akshintala
+5:40 PM  M37 40P-GB-7: Adil Khan vs Sanjay Kumar
+5:40 PM  M38 U26-GB-3: Ishaan Merchant vs Pranit Shriyan</t>
+        </is>
+      </c>
+      <c r="I15" s="104" t="inlineStr">
+        <is>
+          <t>5:00 PM  M33 2140-15: Rahul Garg vs Tejas doshi
+5:00 PM  M34 41P-11: Sachin Malgadnkar vs Sanjay Kumar
+5:20 PM  M35 2140-11: Swati Tripathi vs Nikunj Jhala
+5:20 PM  M36 41P-16: Adil Khan vs Harkishin malkan
+5:40 PM  M37 1220-FINAL: Pool 1st vs Pool 2nd
+5:40 PM  M38 41P-17: Sachin Malgadnkar vs Ajit nair</t>
+        </is>
+      </c>
+      <c r="J15" s="104" t="inlineStr">
+        <is>
+          <t>5:30 PM  M14 GB-2: Ravi Modi vs Vinit Padia
+5:48 PM  M15 A25-SF1: Group A 1st vs Group B 2nd</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="108" customHeight="1">
+      <c r="A16" s="102" t="inlineStr">
+        <is>
+          <t>Aug 15, 6 PM - 7 PM</t>
+        </is>
+      </c>
+      <c r="B16" s="103" t="inlineStr"/>
+      <c r="C16" s="103" t="inlineStr">
+        <is>
+          <t>6:00 PM  M34 U15-GA-3: Parth yadav vs Aadit Joshi
+6:00 PM  M35 U36-SF2: Group A 1st vs Group B 2nd
+6:15 PM  M36 U15-SF1: Group B 1st vs Group A 2nd
+6:15 PM  M37 U15-SF2: Group A 1st vs Group B 2nd
+6:30 PM  M38 U46-GA-1: Dr Rahul Modi vs Ankur Mahante
+6:30 PM  M39 U46-GA-10: Tanmay Sharma vs Anuj Shah
+6:45 PM  M40 U26-4: Yuvraj jain vs Rahul Garg
+6:45 PM  M41 U26-6: Aaditya Kumar vs Pranit Shriyan</t>
+        </is>
+      </c>
+      <c r="D16" s="103" t="inlineStr"/>
+      <c r="E16" s="103" t="inlineStr"/>
+      <c r="F16" s="103" t="inlineStr"/>
+      <c r="G16" s="103" t="inlineStr"/>
+      <c r="H16" s="103" t="inlineStr">
+        <is>
+          <t>6:00 PM  M39 2639-GB-10: Dr Rahul Modi vs Tanmay Sharma
+6:00 PM  M40 40P-GB-10: Mukul Joshi vs Prasad Akshintala
+6:20 PM  M41 40P-GB-4: Vinay Sawant vs Adil Khan
+6:20 PM  M42 U26-GA-4: Aadit Joshi vs Sankalp Bhatnagar
+6:40 PM  M43 40P-GA-8: Mayank Aggarwal vs Vinit Padia
+6:40 PM  M44 40P-GB-5: Prasad Akshintala vs Sanjay Kumar</t>
+        </is>
+      </c>
+      <c r="I16" s="103" t="inlineStr">
+        <is>
+          <t>6:00 PM  M39 2140-7: Rahul Garg vs Nikunj Jhala
+6:00 PM  M40 41P-18: Piyush Makharia vs Harkishin malkan
+6:20 PM  M41 U11-FINAL: Pool 1st vs Pool 2nd
+6:30 PM  M42 2140-14: Tej vs Nikunj Jhala
+6:40 PM  M43 41P-7: Piyush Makharia vs Sachin Malgadnkar
+6:50 PM  M44 41P-20: Ajit nair vs Harkishin malkan</t>
+        </is>
+      </c>
+      <c r="J16" s="103" t="inlineStr">
+        <is>
+          <t>6:06 PM  M16 A25-SF2: Group B 1st vs Group A 2nd</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="82" customHeight="1">
+      <c r="A17" s="102" t="inlineStr">
+        <is>
+          <t>Aug 15, 7 PM - 8 PM</t>
+        </is>
+      </c>
+      <c r="B17" s="104" t="inlineStr"/>
+      <c r="C17" s="104" t="inlineStr">
+        <is>
+          <t>7:00 PM  M42 U46-GA-6: Ankur Mahante vs Tanmay Sharma
+7:00 PM  M43 U46-GB-9: Vinit Padia vs Amit Ranka
+7:20 PM  M44 U26-9: Hryday Goyal vs Rahul Garg
+7:40 PM  M45 U26-1: Yuvraj jain vs Aaditya Kumar
+7:40 PM  M46 U46-GB-2: Nikunj Jhala vs Vinit Padia
+7:55 PM  M47 U46-GB-6: Piyush Makharia vs Nilesh Bagaria</t>
+        </is>
+      </c>
+      <c r="D17" s="104" t="inlineStr"/>
+      <c r="E17" s="104" t="inlineStr"/>
+      <c r="F17" s="104" t="inlineStr"/>
+      <c r="G17" s="104" t="inlineStr"/>
+      <c r="H17" s="104" t="inlineStr">
+        <is>
+          <t>7:00 PM  M45 U26-GA-5: Aadit Joshi vs Rutvij sawant
+7:00 PM  M46 U26-GB-4: Pranit Shriyan vs Rahul Garg
+7:20 PM  M47 40P-GA-10: Piyush Makharia vs Vinit Padia
+7:20 PM  M48 U26-GA-6: Aaditya Kumar vs Sankalp Bhatnagar
+7:40 PM  M49 40P-GB-8: Mukul Joshi vs Adil Khan
+7:40 PM  M50 40P-GB-9: Vinay Sawant vs Sanjay Kumar</t>
+        </is>
+      </c>
+      <c r="I17" s="104" t="inlineStr">
+        <is>
+          <t>7:00 PM  M45 2140-8: Tejas doshi vs Nikunj Jhala
+7:10 PM  M46 41P-10: Adil Khan vs Prasad Akshintala
+7:20 PM  M47 41P-14: Sanjay Kumar vs Harkishin malkan
+7:30 PM  M48 2140-FINAL: Pool 1st vs Pool 2nd
+7:40 PM  M49 41P-5: Prasad Akshintala vs Ajit nair
+7:50 PM  M50 41P-21: Sachin Malgadnkar vs Harkishin malkan</t>
+        </is>
+      </c>
+      <c r="J17" s="104" t="inlineStr"/>
+    </row>
+    <row r="18" ht="82" customHeight="1">
+      <c r="A18" s="102" t="inlineStr">
+        <is>
+          <t>Aug 15, 8 PM - 9 PM</t>
+        </is>
+      </c>
+      <c r="B18" s="103" t="inlineStr"/>
+      <c r="C18" s="103" t="inlineStr">
+        <is>
+          <t>8:05 PM  M48 U26-5: Aaditya Kumar vs Hryday Goyal
+8:20 PM  M49 U26-10: Pranit Shriyan vs Rahul Garg
+8:30 PM  M50 U46-GB-1: Nikunj Jhala vs Piyush Makharia
+8:55 PM  M51 U46-GB-5: Piyush Makharia vs Vinit Padia</t>
+        </is>
+      </c>
+      <c r="D18" s="103" t="inlineStr"/>
+      <c r="E18" s="103" t="inlineStr"/>
+      <c r="F18" s="103" t="inlineStr"/>
+      <c r="G18" s="103" t="inlineStr"/>
+      <c r="H18" s="103" t="inlineStr">
+        <is>
+          <t>8:00 PM  M51 2639-SF1: Group A 1st vs Group B 2nd
+8:00 PM  M52 U26-GB-5: Ishaan Merchant vs Rahul Garg
+8:20 PM  M53 2639-SF2: Group B 1st vs Group A 2nd
+8:20 PM  M54 40P-SF1: Group B 1st vs Group A 2nd
+8:40 PM  M55 2639-FINAL: Winner SF1 vs Winner SF2
+8:40 PM  M56 U26-GB-6: Shravan Gajera vs Rahul Garg</t>
+        </is>
+      </c>
+      <c r="I18" s="103" t="inlineStr">
+        <is>
+          <t>8:10 PM  M51 41P-4: Piyush Makharia vs Sanjay Kumar
+8:20 PM  M52 41P-13: Sachin Malgadnkar vs Prasad Akshintala
+8:55 PM  M53 41P-15: Adil Khan vs Sachin Malgadnkar</t>
+        </is>
+      </c>
+      <c r="J18" s="103" t="inlineStr"/>
+    </row>
+    <row r="19" ht="69" customHeight="1">
+      <c r="A19" s="102" t="inlineStr">
+        <is>
+          <t>Aug 15, 9 PM - 10 PM</t>
+        </is>
+      </c>
+      <c r="B19" s="104" t="inlineStr"/>
+      <c r="C19" s="104" t="inlineStr">
+        <is>
+          <t>9:00 PM  M52 U26-7: Aaditya Kumar vs Rahul Garg
+9:15 PM  M53 U46-GB-7: Piyush Makharia vs Amit Ranka
+9:30 PM  M54 U46-SF1: Group B 1st vs Group A 2nd
+9:30 PM  M55 U46-SF2: Group A 1st vs Group B 2nd</t>
+        </is>
+      </c>
+      <c r="D19" s="104" t="inlineStr"/>
+      <c r="E19" s="104" t="inlineStr"/>
+      <c r="F19" s="104" t="inlineStr"/>
+      <c r="G19" s="104" t="inlineStr"/>
+      <c r="H19" s="104" t="inlineStr">
+        <is>
+          <t>9:00 PM  M57 U26-SF1: Group A 1st vs Group B 2nd
+9:00 PM  M58 U26-SF2: Group B 1st vs Group A 2nd
+9:20 PM  M59 40P-SF2: Group A 1st vs Group B 2nd
+9:20 PM  M60 U26-FINAL: Winner SF1 vs Winner SF2
+9:40 PM  M61 40P-FINAL: Winner SF1 vs Winner SF2</t>
+        </is>
+      </c>
+      <c r="I19" s="104" t="inlineStr">
+        <is>
+          <t>9:35 PM  M54 41P-19: Prasad Akshintala vs Harkishin malkan
+9:35 PM  M55 41P-9: Adil Khan vs Sanjay Kumar
+9:55 PM  M56 41P-SF1: Round Robin 1st vs Round Robin 4th
+9:55 PM  M57 41P-SF2: Round Robin 2nd vs Round Robin 3rd</t>
+        </is>
+      </c>
+      <c r="J19" s="104" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="100" t="inlineStr">
+        <is>
+          <t>AUG 16</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="102" t="inlineStr">
+        <is>
+          <t>Aug 16, 8 AM - 9 AM</t>
+        </is>
+      </c>
+      <c r="B21" s="103" t="inlineStr"/>
+      <c r="C21" s="103" t="inlineStr"/>
+      <c r="D21" s="103" t="inlineStr"/>
+      <c r="E21" s="103" t="inlineStr"/>
+      <c r="F21" s="103" t="inlineStr"/>
+      <c r="G21" s="103" t="inlineStr"/>
+      <c r="H21" s="103" t="inlineStr"/>
+      <c r="I21" s="103" t="inlineStr">
+        <is>
+          <t>8:00 AM  M58 41P-FINAL: Winner SF1 vs Winner SF2</t>
+        </is>
+      </c>
+      <c r="J21" s="103" t="inlineStr"/>
+    </row>
+    <row r="22" ht="160" customHeight="1">
+      <c r="A22" s="102" t="inlineStr">
+        <is>
+          <t>Aug 16, 9 AM - 10 AM</t>
+        </is>
+      </c>
+      <c r="B22" s="104" t="inlineStr"/>
+      <c r="C22" s="104" t="inlineStr"/>
+      <c r="D22" s="104" t="inlineStr">
+        <is>
+          <t>9:00 AM  M1 QF2: Nilesh Bagaria &amp; Parthiv vs Rahul Garg &amp; Nilesh Mhatre
+9:00 AM  M2 QF3: Mayank Aggarwal &amp; Sudip Parui vs Nidhi Sharma &amp; Tushar
+9:15 AM  M3 QF1: Tanmay Sharma &amp; Sankalp vs Ravi Modi &amp; Dr Rahul Modi
+9:30 AM  M4 QF4: Adil Khan &amp; Anuj Shah vs Vinit Padia &amp; Pratik Haldiya
+9:45 AM  M5 SF1: Winner QF2 vs Winner QF3
+9:45 AM  M6 SF2: Winner QF4 vs Winner QF1</t>
+        </is>
+      </c>
+      <c r="E22" s="104" t="inlineStr"/>
+      <c r="F22" s="104" t="inlineStr"/>
+      <c r="G22" s="104" t="inlineStr">
+        <is>
+          <t>9:00 AM  M1 M1: Vinod Agrawal &amp; Vrinda Agrawal vs Vinit Padia &amp; Pratik Haldiya
+9:00 AM  M2 M2: Poornima Shriyan &amp; Shreya Shriyan vs Renuka Tripathi &amp; Swati Tripathi
+9:00 AM  M3 M3: Mayank Aggarwal &amp; Naresh Aggarwal vs Vinay Sawant &amp; Amar Jain
+9:15 AM  M4 M4: Nilesh Bagaria &amp; Parthiv vs Prasad Akshintala &amp; Suvarna Akshintala
+9:15 AM  M5 M5: Rahul Garg &amp; Parthiv Mody vs Sankalp Bhatnagar &amp; Jitin Bhatnagar
+9:15 AM  M6 M6: Radhika &amp; Prashant vs Adil Khan &amp; Anuj Shah
+9:30 AM  M7 M7: Tejas doshi &amp; Krutika vs Shraddha malgadnkar &amp; Sachin Malgadnkar
+9:30 AM  M8 QF1: Winner M5 vs Winner M1
+9:30 AM  M9 QF2: Winner M6 vs Winner M4
+9:45 AM  M10 QF3: Winner M2 vs Winner M3
+9:45 AM  M11 QF4: Winner M7 vs Ravi Modi &amp; Dr Rahul Modi
+9:45 AM  M12 SF1: Winner QF1 vs Winner QF2</t>
+        </is>
+      </c>
+      <c r="H22" s="104" t="inlineStr"/>
+      <c r="I22" s="104" t="inlineStr"/>
+      <c r="J22" s="104" t="inlineStr"/>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="102" t="inlineStr">
+        <is>
+          <t>Aug 16, 10 AM - 11 AM</t>
+        </is>
+      </c>
+      <c r="B23" s="103" t="inlineStr"/>
+      <c r="C23" s="103" t="inlineStr"/>
+      <c r="D23" s="103" t="inlineStr"/>
+      <c r="E23" s="103" t="inlineStr"/>
+      <c r="F23" s="103" t="inlineStr"/>
+      <c r="G23" s="103" t="inlineStr">
+        <is>
+          <t>10:00 AM  M13 SF2: Winner QF3 vs Winner QF4
+10:15 AM  M14 FINAL: Winner SF1 vs Winner SF2</t>
+        </is>
+      </c>
+      <c r="H23" s="103" t="inlineStr"/>
+      <c r="I23" s="103" t="inlineStr"/>
+      <c r="J23" s="103" t="inlineStr"/>
+    </row>
+    <row r="24" ht="69" customHeight="1">
+      <c r="A24" s="102" t="inlineStr">
+        <is>
+          <t>Aug 16, 11 AM - 12 PM</t>
+        </is>
+      </c>
+      <c r="B24" s="104" t="inlineStr"/>
+      <c r="C24" s="104" t="inlineStr">
+        <is>
+          <t>11:00 AM  M56 A46-FINAL: Winner SF1 vs Winner SF2
+11:00 AM  M57 U36-FINAL: Winner SF1 vs Winner SF2
+11:15 AM  M58 U15-FINAL: Winner SF1 vs Winner SF2
+11:15 AM  M59 U26-FINAL: Pool 1st vs Pool 2nd
+11:30 AM  M60 U46-FINAL: Winner SF1 vs Winner SF2</t>
+        </is>
+      </c>
+      <c r="D24" s="104" t="inlineStr">
+        <is>
+          <t>11:30 AM  M7 FINAL: Winner SF1 vs Winner SF2</t>
+        </is>
+      </c>
+      <c r="E24" s="104" t="inlineStr"/>
+      <c r="F24" s="104" t="inlineStr"/>
+      <c r="G24" s="104" t="inlineStr"/>
+      <c r="H24" s="104" t="inlineStr"/>
+      <c r="I24" s="104" t="inlineStr"/>
+      <c r="J24" s="104" t="inlineStr"/>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="105" t="inlineStr">
+        <is>
+          <t>Aug 16, 12 PM - 1 PM</t>
+        </is>
+      </c>
+      <c r="B25" s="106" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK — no matches</t>
+        </is>
+      </c>
+      <c r="C25" s="88" t="n"/>
+      <c r="D25" s="88" t="n"/>
+      <c r="E25" s="88" t="n"/>
+      <c r="F25" s="88" t="n"/>
+      <c r="G25" s="88" t="n"/>
+      <c r="H25" s="88" t="n"/>
+      <c r="I25" s="88" t="n"/>
+      <c r="J25" s="84" t="n"/>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="105" t="inlineStr">
+        <is>
+          <t>Aug 16, 1 PM - 2 PM</t>
+        </is>
+      </c>
+      <c r="B26" s="106" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK — no matches</t>
+        </is>
+      </c>
+      <c r="C26" s="88" t="n"/>
+      <c r="D26" s="88" t="n"/>
+      <c r="E26" s="88" t="n"/>
+      <c r="F26" s="88" t="n"/>
+      <c r="G26" s="88" t="n"/>
+      <c r="H26" s="88" t="n"/>
+      <c r="I26" s="88" t="n"/>
+      <c r="J26" s="84" t="n"/>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="105" t="inlineStr">
+        <is>
+          <t>Aug 16, 2 PM - 3 PM</t>
+        </is>
+      </c>
+      <c r="B27" s="106" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK — no matches</t>
+        </is>
+      </c>
+      <c r="C27" s="88" t="n"/>
+      <c r="D27" s="88" t="n"/>
+      <c r="E27" s="88" t="n"/>
+      <c r="F27" s="88" t="n"/>
+      <c r="G27" s="88" t="n"/>
+      <c r="H27" s="88" t="n"/>
+      <c r="I27" s="88" t="n"/>
+      <c r="J27" s="84" t="n"/>
+    </row>
+    <row r="28" ht="43" customHeight="1">
+      <c r="A28" s="102" t="inlineStr">
+        <is>
+          <t>Aug 16, 3 PM - 4 PM</t>
+        </is>
+      </c>
+      <c r="B28" s="104" t="inlineStr"/>
+      <c r="C28" s="104" t="inlineStr"/>
+      <c r="D28" s="104" t="inlineStr"/>
+      <c r="E28" s="104" t="inlineStr"/>
+      <c r="F28" s="104" t="inlineStr"/>
+      <c r="G28" s="104" t="inlineStr"/>
+      <c r="H28" s="104" t="inlineStr"/>
+      <c r="I28" s="104" t="inlineStr"/>
+      <c r="J28" s="104" t="inlineStr">
+        <is>
+          <t>3:00 PM  M17 U15-FINAL: Winner SF1 vs Winner SF2
+3:18 PM  M18 GC-FINAL: Pool 1st vs Pool 2nd
+3:36 PM  M19 A25-FINAL: Winner SF1 vs Winner SF2</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="B25:J25"/>
+    <mergeCell ref="B11:J11"/>
+    <mergeCell ref="B10:J10"/>
+    <mergeCell ref="B26:J26"/>
+    <mergeCell ref="B27:J27"/>
+    <mergeCell ref="A20:J20"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="B12:J12"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -5728,7 +10335,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9547,7 +14154,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10109,7 +14716,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13096,7 +17703,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13829,7 +18436,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14819,7 +19426,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -18297,3575 +22904,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J100"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="25.3" bestFit="1" customWidth="1" style="14" min="1" max="1"/>
-    <col width="10" customWidth="1" style="14" min="2" max="3"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" style="14" min="4" max="4"/>
-    <col width="10" customWidth="1" style="14" min="5" max="5"/>
-    <col width="12" customWidth="1" style="14" min="6" max="6"/>
-    <col width="11" customWidth="1" style="14" min="7" max="7"/>
-    <col width="27" customWidth="1" style="14" min="8" max="8"/>
-    <col width="4" customWidth="1" style="14" min="9" max="9"/>
-    <col width="27" customWidth="1" style="14" min="10" max="16384"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="27.95" customHeight="1">
-      <c r="A1" s="29" t="inlineStr">
-        <is>
-          <t>CHESS</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="30" t="inlineStr">
-        <is>
-          <t>4 age bands, all single-pool Americano · Best of 3, Final Best of 5 · 2 Boards</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="31" t="n"/>
-      <c r="B3" s="31" t="n"/>
-      <c r="C3" s="31" t="n"/>
-      <c r="D3" s="31" t="n"/>
-      <c r="E3" s="31" t="n"/>
-      <c r="F3" s="31" t="n"/>
-      <c r="G3" s="31" t="n"/>
-      <c r="H3" s="31" t="n"/>
-      <c r="I3" s="31" t="n"/>
-    </row>
-    <row r="4" ht="20.1" customHeight="1">
-      <c r="A4" s="32" t="inlineStr">
-        <is>
-          <t>PLAYER GROUPS</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="31" t="n"/>
-      <c r="B5" s="31" t="n"/>
-      <c r="C5" s="31" t="n"/>
-      <c r="D5" s="31" t="n"/>
-      <c r="E5" s="31" t="n"/>
-      <c r="F5" s="31" t="n"/>
-      <c r="G5" s="31" t="n"/>
-      <c r="H5" s="31" t="n"/>
-      <c r="I5" s="31" t="n"/>
-    </row>
-    <row r="6" ht="17.1" customHeight="1">
-      <c r="A6" s="33" t="inlineStr">
-        <is>
-          <t>Under 11 (single pool, Americano)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="34" t="inlineStr">
-        <is>
-          <t>Player</t>
-        </is>
-      </c>
-      <c r="B7" s="34" t="inlineStr">
-        <is>
-          <t>Age</t>
-        </is>
-      </c>
-      <c r="C7" s="31" t="n"/>
-      <c r="D7" s="31" t="n"/>
-      <c r="E7" s="31" t="n"/>
-      <c r="F7" s="31" t="n"/>
-      <c r="G7" s="31" t="n"/>
-      <c r="H7" s="31" t="n"/>
-      <c r="I7" s="31" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="27" t="inlineStr">
-        <is>
-          <t>Rushabh</t>
-        </is>
-      </c>
-      <c r="B8" s="35" t="n">
-        <v>8</v>
-      </c>
-      <c r="C8" s="31" t="n"/>
-      <c r="D8" s="31" t="n"/>
-      <c r="E8" s="31" t="n"/>
-      <c r="F8" s="31" t="n"/>
-      <c r="G8" s="31" t="n"/>
-      <c r="H8" s="31" t="n"/>
-      <c r="I8" s="31" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="28" t="inlineStr">
-        <is>
-          <t>Neev Chauhan</t>
-        </is>
-      </c>
-      <c r="B9" s="36" t="n">
-        <v>8</v>
-      </c>
-      <c r="C9" s="31" t="n"/>
-      <c r="D9" s="31" t="n"/>
-      <c r="E9" s="31" t="n"/>
-      <c r="F9" s="31" t="n"/>
-      <c r="G9" s="31" t="n"/>
-      <c r="H9" s="31" t="n"/>
-      <c r="I9" s="31" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="27" t="inlineStr">
-        <is>
-          <t>Kartik Relan</t>
-        </is>
-      </c>
-      <c r="B10" s="35" t="n">
-        <v>9</v>
-      </c>
-      <c r="C10" s="31" t="n"/>
-      <c r="D10" s="31" t="n"/>
-      <c r="E10" s="31" t="n"/>
-      <c r="F10" s="31" t="n"/>
-      <c r="G10" s="31" t="n"/>
-      <c r="H10" s="31" t="n"/>
-      <c r="I10" s="31" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="28" t="inlineStr">
-        <is>
-          <t>Parth yadav</t>
-        </is>
-      </c>
-      <c r="B11" s="36" t="n">
-        <v>10</v>
-      </c>
-      <c r="C11" s="31" t="n"/>
-      <c r="D11" s="31" t="n"/>
-      <c r="E11" s="31" t="n"/>
-      <c r="F11" s="31" t="n"/>
-      <c r="G11" s="31" t="n"/>
-      <c r="H11" s="31" t="n"/>
-      <c r="I11" s="31" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="27" t="inlineStr">
-        <is>
-          <t>Jimit Relan</t>
-        </is>
-      </c>
-      <c r="B12" s="35" t="n">
-        <v>11</v>
-      </c>
-      <c r="C12" s="31" t="n"/>
-      <c r="D12" s="31" t="n"/>
-      <c r="E12" s="31" t="n"/>
-      <c r="F12" s="31" t="n"/>
-      <c r="G12" s="31" t="n"/>
-      <c r="H12" s="31" t="n"/>
-      <c r="I12" s="31" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="31" t="n"/>
-      <c r="B13" s="31" t="n"/>
-      <c r="C13" s="31" t="n"/>
-      <c r="D13" s="31" t="n"/>
-      <c r="E13" s="31" t="n"/>
-      <c r="F13" s="31" t="n"/>
-      <c r="G13" s="31" t="n"/>
-      <c r="H13" s="31" t="n"/>
-      <c r="I13" s="31" t="n"/>
-    </row>
-    <row r="14" ht="17.1" customHeight="1">
-      <c r="A14" s="33" t="inlineStr">
-        <is>
-          <t>12 to 20 (single pool, Americano)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="34" t="inlineStr">
-        <is>
-          <t>Player</t>
-        </is>
-      </c>
-      <c r="B15" s="34" t="inlineStr">
-        <is>
-          <t>Age</t>
-        </is>
-      </c>
-      <c r="C15" s="31" t="n"/>
-      <c r="D15" s="31" t="n"/>
-      <c r="E15" s="31" t="n"/>
-      <c r="F15" s="31" t="n"/>
-      <c r="G15" s="31" t="n"/>
-      <c r="H15" s="31" t="n"/>
-      <c r="I15" s="31" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="27" t="inlineStr">
-        <is>
-          <t>Aadit Joshi</t>
-        </is>
-      </c>
-      <c r="B16" s="35" t="n">
-        <v>12</v>
-      </c>
-      <c r="C16" s="31" t="n"/>
-      <c r="D16" s="31" t="n"/>
-      <c r="E16" s="31" t="n"/>
-      <c r="F16" s="31" t="n"/>
-      <c r="G16" s="31" t="n"/>
-      <c r="H16" s="31" t="n"/>
-      <c r="I16" s="31" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="28" t="inlineStr">
-        <is>
-          <t>Maitreya Manvik</t>
-        </is>
-      </c>
-      <c r="B17" s="36" t="n">
-        <v>14</v>
-      </c>
-      <c r="C17" s="31" t="n"/>
-      <c r="D17" s="31" t="n"/>
-      <c r="E17" s="31" t="n"/>
-      <c r="F17" s="31" t="n"/>
-      <c r="G17" s="31" t="n"/>
-      <c r="H17" s="31" t="n"/>
-      <c r="I17" s="31" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="27" t="inlineStr">
-        <is>
-          <t>Aaditya Kumar</t>
-        </is>
-      </c>
-      <c r="B18" s="35" t="n">
-        <v>17</v>
-      </c>
-      <c r="C18" s="31" t="n"/>
-      <c r="D18" s="31" t="n"/>
-      <c r="E18" s="31" t="n"/>
-      <c r="F18" s="31" t="n"/>
-      <c r="G18" s="31" t="n"/>
-      <c r="H18" s="31" t="n"/>
-      <c r="I18" s="31" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="28" t="inlineStr">
-        <is>
-          <t>Hryday Goyal</t>
-        </is>
-      </c>
-      <c r="B19" s="36" t="n">
-        <v>20</v>
-      </c>
-      <c r="C19" s="31" t="n"/>
-      <c r="D19" s="31" t="n"/>
-      <c r="E19" s="31" t="n"/>
-      <c r="F19" s="31" t="n"/>
-      <c r="G19" s="31" t="n"/>
-      <c r="H19" s="31" t="n"/>
-      <c r="I19" s="31" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="31" t="n"/>
-      <c r="B20" s="31" t="n"/>
-      <c r="C20" s="31" t="n"/>
-      <c r="D20" s="31" t="n"/>
-      <c r="E20" s="31" t="n"/>
-      <c r="F20" s="31" t="n"/>
-      <c r="G20" s="31" t="n"/>
-      <c r="H20" s="31" t="n"/>
-      <c r="I20" s="31" t="n"/>
-    </row>
-    <row r="21" ht="17.1" customHeight="1">
-      <c r="A21" s="33" t="inlineStr">
-        <is>
-          <t>21 to 40 (single pool, Americano)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="34" t="inlineStr">
-        <is>
-          <t>Player</t>
-        </is>
-      </c>
-      <c r="B22" s="34" t="inlineStr">
-        <is>
-          <t>Age</t>
-        </is>
-      </c>
-      <c r="C22" s="31" t="n"/>
-      <c r="D22" s="31" t="n"/>
-      <c r="E22" s="31" t="n"/>
-      <c r="F22" s="31" t="n"/>
-      <c r="G22" s="31" t="n"/>
-      <c r="H22" s="31" t="n"/>
-      <c r="I22" s="31" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="27" t="inlineStr">
-        <is>
-          <t>Rahul Garg</t>
-        </is>
-      </c>
-      <c r="B23" s="35" t="n">
-        <v>25</v>
-      </c>
-      <c r="C23" s="31" t="n"/>
-      <c r="D23" s="31" t="n"/>
-      <c r="E23" s="31" t="n"/>
-      <c r="F23" s="31" t="n"/>
-      <c r="G23" s="31" t="n"/>
-      <c r="H23" s="31" t="n"/>
-      <c r="I23" s="31" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="28" t="inlineStr">
-        <is>
-          <t>Tej</t>
-        </is>
-      </c>
-      <c r="B24" s="36" t="n">
-        <v>32</v>
-      </c>
-      <c r="C24" s="31" t="n"/>
-      <c r="D24" s="31" t="n"/>
-      <c r="E24" s="31" t="n"/>
-      <c r="F24" s="31" t="n"/>
-      <c r="G24" s="31" t="n"/>
-      <c r="H24" s="31" t="n"/>
-      <c r="I24" s="31" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="27" t="inlineStr">
-        <is>
-          <t>Swati Tripathi</t>
-        </is>
-      </c>
-      <c r="B25" s="35" t="n">
-        <v>38</v>
-      </c>
-      <c r="C25" s="31" t="n"/>
-      <c r="D25" s="31" t="n"/>
-      <c r="E25" s="31" t="n"/>
-      <c r="F25" s="31" t="n"/>
-      <c r="G25" s="31" t="n"/>
-      <c r="H25" s="31" t="n"/>
-      <c r="I25" s="31" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="28" t="inlineStr">
-        <is>
-          <t>Amit Nawandhar</t>
-        </is>
-      </c>
-      <c r="B26" s="36" t="n">
-        <v>39</v>
-      </c>
-      <c r="C26" s="31" t="n"/>
-      <c r="D26" s="31" t="n"/>
-      <c r="E26" s="31" t="n"/>
-      <c r="F26" s="31" t="n"/>
-      <c r="G26" s="31" t="n"/>
-      <c r="H26" s="31" t="n"/>
-      <c r="I26" s="31" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="27" t="inlineStr">
-        <is>
-          <t>Tejas doshi</t>
-        </is>
-      </c>
-      <c r="B27" s="35" t="n">
-        <v>40</v>
-      </c>
-      <c r="C27" s="31" t="n"/>
-      <c r="D27" s="31" t="n"/>
-      <c r="E27" s="31" t="n"/>
-      <c r="F27" s="31" t="n"/>
-      <c r="G27" s="31" t="n"/>
-      <c r="H27" s="31" t="n"/>
-      <c r="I27" s="31" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="28" t="inlineStr">
-        <is>
-          <t>Nikunj Jhala</t>
-        </is>
-      </c>
-      <c r="B28" s="36" t="n">
-        <v>40</v>
-      </c>
-      <c r="C28" s="31" t="n"/>
-      <c r="D28" s="31" t="n"/>
-      <c r="E28" s="31" t="n"/>
-      <c r="F28" s="31" t="n"/>
-      <c r="G28" s="31" t="n"/>
-      <c r="H28" s="31" t="n"/>
-      <c r="I28" s="31" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="31" t="n"/>
-      <c r="B29" s="31" t="n"/>
-      <c r="C29" s="31" t="n"/>
-      <c r="D29" s="31" t="n"/>
-      <c r="E29" s="31" t="n"/>
-      <c r="F29" s="31" t="n"/>
-      <c r="G29" s="31" t="n"/>
-      <c r="H29" s="31" t="n"/>
-      <c r="I29" s="31" t="n"/>
-    </row>
-    <row r="30" ht="17.1" customHeight="1">
-      <c r="A30" s="33" t="inlineStr">
-        <is>
-          <t>41 and above (single pool, Americano)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="34" t="inlineStr">
-        <is>
-          <t>Player</t>
-        </is>
-      </c>
-      <c r="B31" s="34" t="inlineStr">
-        <is>
-          <t>Age</t>
-        </is>
-      </c>
-      <c r="C31" s="31" t="n"/>
-      <c r="D31" s="31" t="n"/>
-      <c r="E31" s="31" t="n"/>
-      <c r="F31" s="31" t="n"/>
-      <c r="G31" s="31" t="n"/>
-      <c r="H31" s="31" t="n"/>
-      <c r="I31" s="31" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="27" t="inlineStr">
-        <is>
-          <t>Piyush Makharia</t>
-        </is>
-      </c>
-      <c r="B32" s="35" t="n">
-        <v>43</v>
-      </c>
-      <c r="C32" s="31" t="n"/>
-      <c r="D32" s="31" t="n"/>
-      <c r="E32" s="31" t="n"/>
-      <c r="F32" s="31" t="n"/>
-      <c r="G32" s="31" t="n"/>
-      <c r="H32" s="31" t="n"/>
-      <c r="I32" s="31" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="28" t="inlineStr">
-        <is>
-          <t>Adil Khan</t>
-        </is>
-      </c>
-      <c r="B33" s="36" t="n">
-        <v>51</v>
-      </c>
-      <c r="C33" s="31" t="n"/>
-      <c r="D33" s="31" t="n"/>
-      <c r="E33" s="31" t="n"/>
-      <c r="F33" s="31" t="n"/>
-      <c r="G33" s="31" t="n"/>
-      <c r="H33" s="31" t="n"/>
-      <c r="I33" s="31" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="27" t="inlineStr">
-        <is>
-          <t>Sachin Malgadnkar</t>
-        </is>
-      </c>
-      <c r="B34" s="35" t="n">
-        <v>52</v>
-      </c>
-      <c r="C34" s="31" t="n"/>
-      <c r="D34" s="31" t="n"/>
-      <c r="E34" s="31" t="n"/>
-      <c r="F34" s="31" t="n"/>
-      <c r="G34" s="31" t="n"/>
-      <c r="H34" s="31" t="n"/>
-      <c r="I34" s="31" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="28" t="inlineStr">
-        <is>
-          <t>Prasad Akshintala</t>
-        </is>
-      </c>
-      <c r="B35" s="36" t="n">
-        <v>56</v>
-      </c>
-      <c r="C35" s="31" t="n"/>
-      <c r="D35" s="31" t="n"/>
-      <c r="E35" s="31" t="n"/>
-      <c r="F35" s="31" t="n"/>
-      <c r="G35" s="31" t="n"/>
-      <c r="H35" s="31" t="n"/>
-      <c r="I35" s="31" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="27" t="inlineStr">
-        <is>
-          <t>Ajit nair</t>
-        </is>
-      </c>
-      <c r="B36" s="35" t="n">
-        <v>59</v>
-      </c>
-      <c r="C36" s="31" t="n"/>
-      <c r="D36" s="31" t="n"/>
-      <c r="E36" s="31" t="n"/>
-      <c r="F36" s="31" t="n"/>
-      <c r="G36" s="31" t="n"/>
-      <c r="H36" s="31" t="n"/>
-      <c r="I36" s="31" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="28" t="inlineStr">
-        <is>
-          <t>Sanjay Kumar</t>
-        </is>
-      </c>
-      <c r="B37" s="36" t="n">
-        <v>61</v>
-      </c>
-      <c r="C37" s="31" t="n"/>
-      <c r="D37" s="31" t="n"/>
-      <c r="E37" s="31" t="n"/>
-      <c r="F37" s="31" t="n"/>
-      <c r="G37" s="31" t="n"/>
-      <c r="H37" s="31" t="n"/>
-      <c r="I37" s="31" t="n"/>
-    </row>
-    <row r="38" ht="20.1" customHeight="1">
-      <c r="A38" s="27" t="inlineStr">
-        <is>
-          <t>Harkishin malkan</t>
-        </is>
-      </c>
-      <c r="B38" s="35" t="n">
-        <v>76</v>
-      </c>
-      <c r="C38" s="31" t="n"/>
-      <c r="D38" s="31" t="n"/>
-      <c r="E38" s="31" t="n"/>
-      <c r="F38" s="31" t="n"/>
-      <c r="G38" s="31" t="n"/>
-      <c r="H38" s="31" t="n"/>
-      <c r="I38" s="31" t="n"/>
-    </row>
-    <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="31" t="n"/>
-      <c r="B39" s="31" t="n"/>
-      <c r="C39" s="31" t="n"/>
-      <c r="D39" s="31" t="n"/>
-      <c r="E39" s="31" t="n"/>
-      <c r="F39" s="31" t="n"/>
-      <c r="G39" s="31" t="n"/>
-      <c r="H39" s="31" t="n"/>
-      <c r="I39" s="31" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="31" t="n"/>
-      <c r="B40" s="31" t="n"/>
-      <c r="C40" s="31" t="n"/>
-      <c r="D40" s="31" t="n"/>
-      <c r="E40" s="31" t="n"/>
-      <c r="F40" s="31" t="n"/>
-      <c r="G40" s="31" t="n"/>
-      <c r="H40" s="31" t="n"/>
-      <c r="I40" s="31" t="n"/>
-    </row>
-    <row r="41" ht="20.1" customHeight="1">
-      <c r="A41" s="32" t="inlineStr">
-        <is>
-          <t>MATCH SCHEDULE (chronological, interleaved with other sports to avoid player conflicts)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="26" t="inlineStr">
-        <is>
-          <t>Day</t>
-        </is>
-      </c>
-      <c r="B42" s="26" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="C42" s="26" t="inlineStr">
-        <is>
-          <t>End</t>
-        </is>
-      </c>
-      <c r="D42" s="26" t="inlineStr">
-        <is>
-          <t>Band</t>
-        </is>
-      </c>
-      <c r="E42" s="26" t="inlineStr">
-        <is>
-          <t>Match #</t>
-        </is>
-      </c>
-      <c r="F42" s="26" t="inlineStr">
-        <is>
-          <t>Match</t>
-        </is>
-      </c>
-      <c r="G42" s="26" t="inlineStr">
-        <is>
-          <t>Resource</t>
-        </is>
-      </c>
-      <c r="H42" s="26" t="inlineStr">
-        <is>
-          <t>Player A</t>
-        </is>
-      </c>
-      <c r="I42" s="26" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J42" s="26" t="inlineStr">
-        <is>
-          <t>Player B</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="94" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B43" s="94" t="inlineStr">
-        <is>
-          <t>8:00AM</t>
-        </is>
-      </c>
-      <c r="C43" s="94" t="inlineStr">
-        <is>
-          <t>8:20AM</t>
-        </is>
-      </c>
-      <c r="D43" s="94" t="inlineStr">
-        <is>
-          <t>Under 11</t>
-        </is>
-      </c>
-      <c r="E43" s="94" t="n">
-        <v>1</v>
-      </c>
-      <c r="F43" s="94" t="inlineStr">
-        <is>
-          <t>U11-1</t>
-        </is>
-      </c>
-      <c r="G43" s="94" t="inlineStr">
-        <is>
-          <t>Board 1</t>
-        </is>
-      </c>
-      <c r="H43" s="94" t="inlineStr">
-        <is>
-          <t>Rushabh</t>
-        </is>
-      </c>
-      <c r="I43" s="94" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J43" s="94" t="inlineStr">
-        <is>
-          <t>Neev Chauhan</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="95" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B44" s="95" t="inlineStr">
-        <is>
-          <t>8:00AM</t>
-        </is>
-      </c>
-      <c r="C44" s="95" t="inlineStr">
-        <is>
-          <t>8:20AM</t>
-        </is>
-      </c>
-      <c r="D44" s="95" t="inlineStr">
-        <is>
-          <t>Under 11</t>
-        </is>
-      </c>
-      <c r="E44" s="95" t="n">
-        <v>2</v>
-      </c>
-      <c r="F44" s="95" t="inlineStr">
-        <is>
-          <t>U11-2</t>
-        </is>
-      </c>
-      <c r="G44" s="95" t="inlineStr">
-        <is>
-          <t>Board 2</t>
-        </is>
-      </c>
-      <c r="H44" s="95" t="inlineStr">
-        <is>
-          <t>Kartik Relan</t>
-        </is>
-      </c>
-      <c r="I44" s="95" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J44" s="95" t="inlineStr">
-        <is>
-          <t>Parth yadav</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="94" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B45" s="94" t="inlineStr">
-        <is>
-          <t>8:20AM</t>
-        </is>
-      </c>
-      <c r="C45" s="94" t="inlineStr">
-        <is>
-          <t>8:40AM</t>
-        </is>
-      </c>
-      <c r="D45" s="94" t="inlineStr">
-        <is>
-          <t>12 to 20</t>
-        </is>
-      </c>
-      <c r="E45" s="94" t="n">
-        <v>3</v>
-      </c>
-      <c r="F45" s="94" t="inlineStr">
-        <is>
-          <t>1220-2</t>
-        </is>
-      </c>
-      <c r="G45" s="94" t="inlineStr">
-        <is>
-          <t>Board 1</t>
-        </is>
-      </c>
-      <c r="H45" s="94" t="inlineStr">
-        <is>
-          <t>Aaditya Kumar</t>
-        </is>
-      </c>
-      <c r="I45" s="94" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J45" s="94" t="inlineStr">
-        <is>
-          <t>Hryday Goyal</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="95" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B46" s="95" t="inlineStr">
-        <is>
-          <t>8:20AM</t>
-        </is>
-      </c>
-      <c r="C46" s="95" t="inlineStr">
-        <is>
-          <t>8:40AM</t>
-        </is>
-      </c>
-      <c r="D46" s="95" t="inlineStr">
-        <is>
-          <t>21 to 40</t>
-        </is>
-      </c>
-      <c r="E46" s="95" t="n">
-        <v>4</v>
-      </c>
-      <c r="F46" s="95" t="inlineStr">
-        <is>
-          <t>2140-2</t>
-        </is>
-      </c>
-      <c r="G46" s="95" t="inlineStr">
-        <is>
-          <t>Board 2</t>
-        </is>
-      </c>
-      <c r="H46" s="95" t="inlineStr">
-        <is>
-          <t>Swati Tripathi</t>
-        </is>
-      </c>
-      <c r="I46" s="95" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J46" s="95" t="inlineStr">
-        <is>
-          <t>Amit Nawandhar</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="94" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B47" s="94" t="inlineStr">
-        <is>
-          <t>8:40AM</t>
-        </is>
-      </c>
-      <c r="C47" s="94" t="inlineStr">
-        <is>
-          <t>9:00AM</t>
-        </is>
-      </c>
-      <c r="D47" s="94" t="inlineStr">
-        <is>
-          <t>Under 11</t>
-        </is>
-      </c>
-      <c r="E47" s="94" t="n">
-        <v>5</v>
-      </c>
-      <c r="F47" s="94" t="inlineStr">
-        <is>
-          <t>U11-3</t>
-        </is>
-      </c>
-      <c r="G47" s="94" t="inlineStr">
-        <is>
-          <t>Board 1</t>
-        </is>
-      </c>
-      <c r="H47" s="94" t="inlineStr">
-        <is>
-          <t>Rushabh</t>
-        </is>
-      </c>
-      <c r="I47" s="94" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J47" s="94" t="inlineStr">
-        <is>
-          <t>Kartik Relan</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="95" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B48" s="95" t="inlineStr">
-        <is>
-          <t>8:40AM</t>
-        </is>
-      </c>
-      <c r="C48" s="95" t="inlineStr">
-        <is>
-          <t>9:00AM</t>
-        </is>
-      </c>
-      <c r="D48" s="95" t="inlineStr">
-        <is>
-          <t>Under 11</t>
-        </is>
-      </c>
-      <c r="E48" s="95" t="n">
-        <v>6</v>
-      </c>
-      <c r="F48" s="95" t="inlineStr">
-        <is>
-          <t>U11-4</t>
-        </is>
-      </c>
-      <c r="G48" s="95" t="inlineStr">
-        <is>
-          <t>Board 2</t>
-        </is>
-      </c>
-      <c r="H48" s="95" t="inlineStr">
-        <is>
-          <t>Neev Chauhan</t>
-        </is>
-      </c>
-      <c r="I48" s="95" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J48" s="95" t="inlineStr">
-        <is>
-          <t>Jimit Relan</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="94" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B49" s="94" t="inlineStr">
-        <is>
-          <t>9:00AM</t>
-        </is>
-      </c>
-      <c r="C49" s="94" t="inlineStr">
-        <is>
-          <t>9:20AM</t>
-        </is>
-      </c>
-      <c r="D49" s="94" t="inlineStr">
-        <is>
-          <t>12 to 20</t>
-        </is>
-      </c>
-      <c r="E49" s="94" t="n">
-        <v>7</v>
-      </c>
-      <c r="F49" s="94" t="inlineStr">
-        <is>
-          <t>1220-1</t>
-        </is>
-      </c>
-      <c r="G49" s="94" t="inlineStr">
-        <is>
-          <t>Board 1</t>
-        </is>
-      </c>
-      <c r="H49" s="94" t="inlineStr">
-        <is>
-          <t>Aadit Joshi</t>
-        </is>
-      </c>
-      <c r="I49" s="94" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J49" s="94" t="inlineStr">
-        <is>
-          <t>Maitreya Manvik</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="95" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B50" s="95" t="inlineStr">
-        <is>
-          <t>9:00AM</t>
-        </is>
-      </c>
-      <c r="C50" s="95" t="inlineStr">
-        <is>
-          <t>9:20AM</t>
-        </is>
-      </c>
-      <c r="D50" s="95" t="inlineStr">
-        <is>
-          <t>21 to 40</t>
-        </is>
-      </c>
-      <c r="E50" s="95" t="n">
-        <v>8</v>
-      </c>
-      <c r="F50" s="95" t="inlineStr">
-        <is>
-          <t>2140-6</t>
-        </is>
-      </c>
-      <c r="G50" s="95" t="inlineStr">
-        <is>
-          <t>Board 2</t>
-        </is>
-      </c>
-      <c r="H50" s="95" t="inlineStr">
-        <is>
-          <t>Tej</t>
-        </is>
-      </c>
-      <c r="I50" s="95" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J50" s="95" t="inlineStr">
-        <is>
-          <t>Swati Tripathi</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="94" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B51" s="94" t="inlineStr">
-        <is>
-          <t>9:20AM</t>
-        </is>
-      </c>
-      <c r="C51" s="94" t="inlineStr">
-        <is>
-          <t>9:40AM</t>
-        </is>
-      </c>
-      <c r="D51" s="94" t="inlineStr">
-        <is>
-          <t>Under 11</t>
-        </is>
-      </c>
-      <c r="E51" s="94" t="n">
-        <v>9</v>
-      </c>
-      <c r="F51" s="94" t="inlineStr">
-        <is>
-          <t>U11-5</t>
-        </is>
-      </c>
-      <c r="G51" s="94" t="inlineStr">
-        <is>
-          <t>Board 1</t>
-        </is>
-      </c>
-      <c r="H51" s="94" t="inlineStr">
-        <is>
-          <t>Kartik Relan</t>
-        </is>
-      </c>
-      <c r="I51" s="94" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J51" s="94" t="inlineStr">
-        <is>
-          <t>Jimit Relan</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="95" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B52" s="95" t="inlineStr">
-        <is>
-          <t>9:20AM</t>
-        </is>
-      </c>
-      <c r="C52" s="95" t="inlineStr">
-        <is>
-          <t>9:40AM</t>
-        </is>
-      </c>
-      <c r="D52" s="95" t="inlineStr">
-        <is>
-          <t>Under 11</t>
-        </is>
-      </c>
-      <c r="E52" s="95" t="n">
-        <v>10</v>
-      </c>
-      <c r="F52" s="95" t="inlineStr">
-        <is>
-          <t>U11-6</t>
-        </is>
-      </c>
-      <c r="G52" s="95" t="inlineStr">
-        <is>
-          <t>Board 2</t>
-        </is>
-      </c>
-      <c r="H52" s="95" t="inlineStr">
-        <is>
-          <t>Rushabh</t>
-        </is>
-      </c>
-      <c r="I52" s="95" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J52" s="95" t="inlineStr">
-        <is>
-          <t>Parth yadav</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="94" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B53" s="94" t="inlineStr">
-        <is>
-          <t>10:30AM</t>
-        </is>
-      </c>
-      <c r="C53" s="94" t="inlineStr">
-        <is>
-          <t>10:50AM</t>
-        </is>
-      </c>
-      <c r="D53" s="94" t="inlineStr">
-        <is>
-          <t>Under 11</t>
-        </is>
-      </c>
-      <c r="E53" s="94" t="n">
-        <v>11</v>
-      </c>
-      <c r="F53" s="94" t="inlineStr">
-        <is>
-          <t>U11-7</t>
-        </is>
-      </c>
-      <c r="G53" s="94" t="inlineStr">
-        <is>
-          <t>Board 1</t>
-        </is>
-      </c>
-      <c r="H53" s="94" t="inlineStr">
-        <is>
-          <t>Rushabh</t>
-        </is>
-      </c>
-      <c r="I53" s="94" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J53" s="94" t="inlineStr">
-        <is>
-          <t>Jimit Relan</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="95" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B54" s="95" t="inlineStr">
-        <is>
-          <t>10:30AM</t>
-        </is>
-      </c>
-      <c r="C54" s="95" t="inlineStr">
-        <is>
-          <t>10:50AM</t>
-        </is>
-      </c>
-      <c r="D54" s="95" t="inlineStr">
-        <is>
-          <t>Under 11</t>
-        </is>
-      </c>
-      <c r="E54" s="95" t="n">
-        <v>12</v>
-      </c>
-      <c r="F54" s="95" t="inlineStr">
-        <is>
-          <t>U11-8</t>
-        </is>
-      </c>
-      <c r="G54" s="95" t="inlineStr">
-        <is>
-          <t>Board 2</t>
-        </is>
-      </c>
-      <c r="H54" s="95" t="inlineStr">
-        <is>
-          <t>Neev Chauhan</t>
-        </is>
-      </c>
-      <c r="I54" s="95" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J54" s="95" t="inlineStr">
-        <is>
-          <t>Kartik Relan</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="94" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B55" s="94" t="inlineStr">
-        <is>
-          <t>10:50AM</t>
-        </is>
-      </c>
-      <c r="C55" s="94" t="inlineStr">
-        <is>
-          <t>11:10AM</t>
-        </is>
-      </c>
-      <c r="D55" s="94" t="inlineStr">
-        <is>
-          <t>12 to 20</t>
-        </is>
-      </c>
-      <c r="E55" s="94" t="n">
-        <v>13</v>
-      </c>
-      <c r="F55" s="94" t="inlineStr">
-        <is>
-          <t>1220-3</t>
-        </is>
-      </c>
-      <c r="G55" s="94" t="inlineStr">
-        <is>
-          <t>Board 1</t>
-        </is>
-      </c>
-      <c r="H55" s="94" t="inlineStr">
-        <is>
-          <t>Aadit Joshi</t>
-        </is>
-      </c>
-      <c r="I55" s="94" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J55" s="94" t="inlineStr">
-        <is>
-          <t>Aaditya Kumar</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="95" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B56" s="95" t="inlineStr">
-        <is>
-          <t>10:50AM</t>
-        </is>
-      </c>
-      <c r="C56" s="95" t="inlineStr">
-        <is>
-          <t>11:10AM</t>
-        </is>
-      </c>
-      <c r="D56" s="95" t="inlineStr">
-        <is>
-          <t>12 to 20</t>
-        </is>
-      </c>
-      <c r="E56" s="95" t="n">
-        <v>14</v>
-      </c>
-      <c r="F56" s="95" t="inlineStr">
-        <is>
-          <t>1220-4</t>
-        </is>
-      </c>
-      <c r="G56" s="95" t="inlineStr">
-        <is>
-          <t>Board 2</t>
-        </is>
-      </c>
-      <c r="H56" s="95" t="inlineStr">
-        <is>
-          <t>Maitreya Manvik</t>
-        </is>
-      </c>
-      <c r="I56" s="95" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J56" s="95" t="inlineStr">
-        <is>
-          <t>Hryday Goyal</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="94" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B57" s="94" t="inlineStr">
-        <is>
-          <t>11:10AM</t>
-        </is>
-      </c>
-      <c r="C57" s="94" t="inlineStr">
-        <is>
-          <t>11:30AM</t>
-        </is>
-      </c>
-      <c r="D57" s="94" t="inlineStr">
-        <is>
-          <t>21 to 40</t>
-        </is>
-      </c>
-      <c r="E57" s="94" t="n">
-        <v>15</v>
-      </c>
-      <c r="F57" s="94" t="inlineStr">
-        <is>
-          <t>2140-3</t>
-        </is>
-      </c>
-      <c r="G57" s="94" t="inlineStr">
-        <is>
-          <t>Board 2</t>
-        </is>
-      </c>
-      <c r="H57" s="94" t="inlineStr">
-        <is>
-          <t>Rahul Garg</t>
-        </is>
-      </c>
-      <c r="I57" s="94" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J57" s="94" t="inlineStr">
-        <is>
-          <t>Amit Nawandhar</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="95" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B58" s="95" t="inlineStr">
-        <is>
-          <t>11:10AM</t>
-        </is>
-      </c>
-      <c r="C58" s="95" t="inlineStr">
-        <is>
-          <t>11:30AM</t>
-        </is>
-      </c>
-      <c r="D58" s="95" t="inlineStr">
-        <is>
-          <t>Under 11</t>
-        </is>
-      </c>
-      <c r="E58" s="95" t="n">
-        <v>16</v>
-      </c>
-      <c r="F58" s="95" t="inlineStr">
-        <is>
-          <t>U11-9</t>
-        </is>
-      </c>
-      <c r="G58" s="95" t="inlineStr">
-        <is>
-          <t>Board 1</t>
-        </is>
-      </c>
-      <c r="H58" s="95" t="inlineStr">
-        <is>
-          <t>Neev Chauhan</t>
-        </is>
-      </c>
-      <c r="I58" s="95" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J58" s="95" t="inlineStr">
-        <is>
-          <t>Parth yadav</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="94" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B59" s="94" t="inlineStr">
-        <is>
-          <t>11:30AM</t>
-        </is>
-      </c>
-      <c r="C59" s="94" t="inlineStr">
-        <is>
-          <t>11:50AM</t>
-        </is>
-      </c>
-      <c r="D59" s="94" t="inlineStr">
-        <is>
-          <t>12 to 20</t>
-        </is>
-      </c>
-      <c r="E59" s="94" t="n">
-        <v>17</v>
-      </c>
-      <c r="F59" s="94" t="inlineStr">
-        <is>
-          <t>1220-5</t>
-        </is>
-      </c>
-      <c r="G59" s="94" t="inlineStr">
-        <is>
-          <t>Board 1</t>
-        </is>
-      </c>
-      <c r="H59" s="94" t="inlineStr">
-        <is>
-          <t>Aadit Joshi</t>
-        </is>
-      </c>
-      <c r="I59" s="94" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J59" s="94" t="inlineStr">
-        <is>
-          <t>Hryday Goyal</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="95" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B60" s="95" t="inlineStr">
-        <is>
-          <t>11:30AM</t>
-        </is>
-      </c>
-      <c r="C60" s="95" t="inlineStr">
-        <is>
-          <t>11:50AM</t>
-        </is>
-      </c>
-      <c r="D60" s="95" t="inlineStr">
-        <is>
-          <t>12 to 20</t>
-        </is>
-      </c>
-      <c r="E60" s="95" t="n">
-        <v>18</v>
-      </c>
-      <c r="F60" s="95" t="inlineStr">
-        <is>
-          <t>1220-6</t>
-        </is>
-      </c>
-      <c r="G60" s="95" t="inlineStr">
-        <is>
-          <t>Board 2</t>
-        </is>
-      </c>
-      <c r="H60" s="95" t="inlineStr">
-        <is>
-          <t>Maitreya Manvik</t>
-        </is>
-      </c>
-      <c r="I60" s="95" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J60" s="95" t="inlineStr">
-        <is>
-          <t>Aaditya Kumar</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="94" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B61" s="94" t="inlineStr">
-        <is>
-          <t>11:50AM</t>
-        </is>
-      </c>
-      <c r="C61" s="94" t="inlineStr">
-        <is>
-          <t>12:10PM</t>
-        </is>
-      </c>
-      <c r="D61" s="94" t="inlineStr">
-        <is>
-          <t>21 to 40</t>
-        </is>
-      </c>
-      <c r="E61" s="94" t="n">
-        <v>19</v>
-      </c>
-      <c r="F61" s="94" t="inlineStr">
-        <is>
-          <t>2140-1</t>
-        </is>
-      </c>
-      <c r="G61" s="94" t="inlineStr">
-        <is>
-          <t>Board 2</t>
-        </is>
-      </c>
-      <c r="H61" s="94" t="inlineStr">
-        <is>
-          <t>Tej</t>
-        </is>
-      </c>
-      <c r="I61" s="94" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J61" s="94" t="inlineStr">
-        <is>
-          <t>Tejas doshi</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="95" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B62" s="95" t="inlineStr">
-        <is>
-          <t>11:50AM</t>
-        </is>
-      </c>
-      <c r="C62" s="95" t="inlineStr">
-        <is>
-          <t>12:10PM</t>
-        </is>
-      </c>
-      <c r="D62" s="95" t="inlineStr">
-        <is>
-          <t>Under 11</t>
-        </is>
-      </c>
-      <c r="E62" s="95" t="n">
-        <v>20</v>
-      </c>
-      <c r="F62" s="95" t="inlineStr">
-        <is>
-          <t>U11-10</t>
-        </is>
-      </c>
-      <c r="G62" s="95" t="inlineStr">
-        <is>
-          <t>Board 1</t>
-        </is>
-      </c>
-      <c r="H62" s="95" t="inlineStr">
-        <is>
-          <t>Parth yadav</t>
-        </is>
-      </c>
-      <c r="I62" s="95" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J62" s="95" t="inlineStr">
-        <is>
-          <t>Jimit Relan</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="94" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B63" s="94" t="inlineStr">
-        <is>
-          <t>3:00PM</t>
-        </is>
-      </c>
-      <c r="C63" s="94" t="inlineStr">
-        <is>
-          <t>3:20PM</t>
-        </is>
-      </c>
-      <c r="D63" s="94" t="inlineStr">
-        <is>
-          <t>21 to 40</t>
-        </is>
-      </c>
-      <c r="E63" s="94" t="n">
-        <v>21</v>
-      </c>
-      <c r="F63" s="94" t="inlineStr">
-        <is>
-          <t>2140-4</t>
-        </is>
-      </c>
-      <c r="G63" s="94" t="inlineStr">
-        <is>
-          <t>Board 1</t>
-        </is>
-      </c>
-      <c r="H63" s="94" t="inlineStr">
-        <is>
-          <t>Swati Tripathi</t>
-        </is>
-      </c>
-      <c r="I63" s="94" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J63" s="94" t="inlineStr">
-        <is>
-          <t>Tejas doshi</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="95" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B64" s="95" t="inlineStr">
-        <is>
-          <t>3:00PM</t>
-        </is>
-      </c>
-      <c r="C64" s="95" t="inlineStr">
-        <is>
-          <t>3:20PM</t>
-        </is>
-      </c>
-      <c r="D64" s="95" t="inlineStr">
-        <is>
-          <t>41 and above</t>
-        </is>
-      </c>
-      <c r="E64" s="95" t="n">
-        <v>22</v>
-      </c>
-      <c r="F64" s="95" t="inlineStr">
-        <is>
-          <t>41P-1</t>
-        </is>
-      </c>
-      <c r="G64" s="95" t="inlineStr">
-        <is>
-          <t>Board 2</t>
-        </is>
-      </c>
-      <c r="H64" s="95" t="inlineStr">
-        <is>
-          <t>Piyush Makharia</t>
-        </is>
-      </c>
-      <c r="I64" s="95" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J64" s="95" t="inlineStr">
-        <is>
-          <t>Ajit nair</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="94" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B65" s="94" t="inlineStr">
-        <is>
-          <t>3:20PM</t>
-        </is>
-      </c>
-      <c r="C65" s="94" t="inlineStr">
-        <is>
-          <t>3:40PM</t>
-        </is>
-      </c>
-      <c r="D65" s="94" t="inlineStr">
-        <is>
-          <t>21 to 40</t>
-        </is>
-      </c>
-      <c r="E65" s="94" t="n">
-        <v>23</v>
-      </c>
-      <c r="F65" s="94" t="inlineStr">
-        <is>
-          <t>2140-10</t>
-        </is>
-      </c>
-      <c r="G65" s="94" t="inlineStr">
-        <is>
-          <t>Board 1</t>
-        </is>
-      </c>
-      <c r="H65" s="94" t="inlineStr">
-        <is>
-          <t>Amit Nawandhar</t>
-        </is>
-      </c>
-      <c r="I65" s="94" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J65" s="94" t="inlineStr">
-        <is>
-          <t>Nikunj Jhala</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="95" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B66" s="95" t="inlineStr">
-        <is>
-          <t>3:20PM</t>
-        </is>
-      </c>
-      <c r="C66" s="95" t="inlineStr">
-        <is>
-          <t>3:40PM</t>
-        </is>
-      </c>
-      <c r="D66" s="95" t="inlineStr">
-        <is>
-          <t>41 and above</t>
-        </is>
-      </c>
-      <c r="E66" s="95" t="n">
-        <v>24</v>
-      </c>
-      <c r="F66" s="95" t="inlineStr">
-        <is>
-          <t>41P-8</t>
-        </is>
-      </c>
-      <c r="G66" s="95" t="inlineStr">
-        <is>
-          <t>Board 2</t>
-        </is>
-      </c>
-      <c r="H66" s="95" t="inlineStr">
-        <is>
-          <t>Prasad Akshintala</t>
-        </is>
-      </c>
-      <c r="I66" s="95" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J66" s="95" t="inlineStr">
-        <is>
-          <t>Sanjay Kumar</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="94" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B67" s="94" t="inlineStr">
-        <is>
-          <t>3:40PM</t>
-        </is>
-      </c>
-      <c r="C67" s="94" t="inlineStr">
-        <is>
-          <t>4:00PM</t>
-        </is>
-      </c>
-      <c r="D67" s="94" t="inlineStr">
-        <is>
-          <t>21 to 40</t>
-        </is>
-      </c>
-      <c r="E67" s="94" t="n">
-        <v>25</v>
-      </c>
-      <c r="F67" s="94" t="inlineStr">
-        <is>
-          <t>2140-9</t>
-        </is>
-      </c>
-      <c r="G67" s="94" t="inlineStr">
-        <is>
-          <t>Board 1</t>
-        </is>
-      </c>
-      <c r="H67" s="94" t="inlineStr">
-        <is>
-          <t>Rahul Garg</t>
-        </is>
-      </c>
-      <c r="I67" s="94" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J67" s="94" t="inlineStr">
-        <is>
-          <t>Tej</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="95" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B68" s="95" t="inlineStr">
-        <is>
-          <t>3:40PM</t>
-        </is>
-      </c>
-      <c r="C68" s="95" t="inlineStr">
-        <is>
-          <t>4:00PM</t>
-        </is>
-      </c>
-      <c r="D68" s="95" t="inlineStr">
-        <is>
-          <t>41 and above</t>
-        </is>
-      </c>
-      <c r="E68" s="95" t="n">
-        <v>26</v>
-      </c>
-      <c r="F68" s="95" t="inlineStr">
-        <is>
-          <t>41P-12</t>
-        </is>
-      </c>
-      <c r="G68" s="95" t="inlineStr">
-        <is>
-          <t>Board 2</t>
-        </is>
-      </c>
-      <c r="H68" s="95" t="inlineStr">
-        <is>
-          <t>Adil Khan</t>
-        </is>
-      </c>
-      <c r="I68" s="95" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J68" s="95" t="inlineStr">
-        <is>
-          <t>Ajit nair</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="94" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B69" s="94" t="inlineStr">
-        <is>
-          <t>4:00PM</t>
-        </is>
-      </c>
-      <c r="C69" s="94" t="inlineStr">
-        <is>
-          <t>4:20PM</t>
-        </is>
-      </c>
-      <c r="D69" s="94" t="inlineStr">
-        <is>
-          <t>21 to 40</t>
-        </is>
-      </c>
-      <c r="E69" s="94" t="n">
-        <v>27</v>
-      </c>
-      <c r="F69" s="94" t="inlineStr">
-        <is>
-          <t>2140-5</t>
-        </is>
-      </c>
-      <c r="G69" s="94" t="inlineStr">
-        <is>
-          <t>Board 1</t>
-        </is>
-      </c>
-      <c r="H69" s="94" t="inlineStr">
-        <is>
-          <t>Amit Nawandhar</t>
-        </is>
-      </c>
-      <c r="I69" s="94" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J69" s="94" t="inlineStr">
-        <is>
-          <t>Tejas doshi</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="95" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B70" s="95" t="inlineStr">
-        <is>
-          <t>4:00PM</t>
-        </is>
-      </c>
-      <c r="C70" s="95" t="inlineStr">
-        <is>
-          <t>4:20PM</t>
-        </is>
-      </c>
-      <c r="D70" s="95" t="inlineStr">
-        <is>
-          <t>41 and above</t>
-        </is>
-      </c>
-      <c r="E70" s="95" t="n">
-        <v>28</v>
-      </c>
-      <c r="F70" s="95" t="inlineStr">
-        <is>
-          <t>41P-3</t>
-        </is>
-      </c>
-      <c r="G70" s="95" t="inlineStr">
-        <is>
-          <t>Board 2</t>
-        </is>
-      </c>
-      <c r="H70" s="95" t="inlineStr">
-        <is>
-          <t>Piyush Makharia</t>
-        </is>
-      </c>
-      <c r="I70" s="95" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J70" s="95" t="inlineStr">
-        <is>
-          <t>Prasad Akshintala</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="94" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B71" s="94" t="inlineStr">
-        <is>
-          <t>4:20PM</t>
-        </is>
-      </c>
-      <c r="C71" s="94" t="inlineStr">
-        <is>
-          <t>4:40PM</t>
-        </is>
-      </c>
-      <c r="D71" s="94" t="inlineStr">
-        <is>
-          <t>21 to 40</t>
-        </is>
-      </c>
-      <c r="E71" s="94" t="n">
-        <v>29</v>
-      </c>
-      <c r="F71" s="94" t="inlineStr">
-        <is>
-          <t>2140-13</t>
-        </is>
-      </c>
-      <c r="G71" s="94" t="inlineStr">
-        <is>
-          <t>Board 1</t>
-        </is>
-      </c>
-      <c r="H71" s="94" t="inlineStr">
-        <is>
-          <t>Rahul Garg</t>
-        </is>
-      </c>
-      <c r="I71" s="94" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J71" s="94" t="inlineStr">
-        <is>
-          <t>Swati Tripathi</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="95" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B72" s="95" t="inlineStr">
-        <is>
-          <t>4:20PM</t>
-        </is>
-      </c>
-      <c r="C72" s="95" t="inlineStr">
-        <is>
-          <t>4:40PM</t>
-        </is>
-      </c>
-      <c r="D72" s="95" t="inlineStr">
-        <is>
-          <t>41 and above</t>
-        </is>
-      </c>
-      <c r="E72" s="95" t="n">
-        <v>30</v>
-      </c>
-      <c r="F72" s="95" t="inlineStr">
-        <is>
-          <t>41P-2</t>
-        </is>
-      </c>
-      <c r="G72" s="95" t="inlineStr">
-        <is>
-          <t>Board 2</t>
-        </is>
-      </c>
-      <c r="H72" s="95" t="inlineStr">
-        <is>
-          <t>Ajit nair</t>
-        </is>
-      </c>
-      <c r="I72" s="95" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J72" s="95" t="inlineStr">
-        <is>
-          <t>Sanjay Kumar</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="94" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B73" s="94" t="inlineStr">
-        <is>
-          <t>4:40PM</t>
-        </is>
-      </c>
-      <c r="C73" s="94" t="inlineStr">
-        <is>
-          <t>5:00PM</t>
-        </is>
-      </c>
-      <c r="D73" s="94" t="inlineStr">
-        <is>
-          <t>21 to 40</t>
-        </is>
-      </c>
-      <c r="E73" s="94" t="n">
-        <v>31</v>
-      </c>
-      <c r="F73" s="94" t="inlineStr">
-        <is>
-          <t>2140-12</t>
-        </is>
-      </c>
-      <c r="G73" s="94" t="inlineStr">
-        <is>
-          <t>Board 1</t>
-        </is>
-      </c>
-      <c r="H73" s="94" t="inlineStr">
-        <is>
-          <t>Tej</t>
-        </is>
-      </c>
-      <c r="I73" s="94" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J73" s="94" t="inlineStr">
-        <is>
-          <t>Amit Nawandhar</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="95" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B74" s="95" t="inlineStr">
-        <is>
-          <t>4:40PM</t>
-        </is>
-      </c>
-      <c r="C74" s="95" t="inlineStr">
-        <is>
-          <t>5:00PM</t>
-        </is>
-      </c>
-      <c r="D74" s="95" t="inlineStr">
-        <is>
-          <t>41 and above</t>
-        </is>
-      </c>
-      <c r="E74" s="95" t="n">
-        <v>32</v>
-      </c>
-      <c r="F74" s="95" t="inlineStr">
-        <is>
-          <t>41P-6</t>
-        </is>
-      </c>
-      <c r="G74" s="95" t="inlineStr">
-        <is>
-          <t>Board 2</t>
-        </is>
-      </c>
-      <c r="H74" s="95" t="inlineStr">
-        <is>
-          <t>Piyush Makharia</t>
-        </is>
-      </c>
-      <c r="I74" s="95" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J74" s="95" t="inlineStr">
-        <is>
-          <t>Adil Khan</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="94" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B75" s="94" t="inlineStr">
-        <is>
-          <t>5:00PM</t>
-        </is>
-      </c>
-      <c r="C75" s="94" t="inlineStr">
-        <is>
-          <t>5:20PM</t>
-        </is>
-      </c>
-      <c r="D75" s="94" t="inlineStr">
-        <is>
-          <t>21 to 40</t>
-        </is>
-      </c>
-      <c r="E75" s="94" t="n">
-        <v>33</v>
-      </c>
-      <c r="F75" s="94" t="inlineStr">
-        <is>
-          <t>2140-15</t>
-        </is>
-      </c>
-      <c r="G75" s="94" t="inlineStr">
-        <is>
-          <t>Board 1</t>
-        </is>
-      </c>
-      <c r="H75" s="94" t="inlineStr">
-        <is>
-          <t>Rahul Garg</t>
-        </is>
-      </c>
-      <c r="I75" s="94" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J75" s="94" t="inlineStr">
-        <is>
-          <t>Tejas doshi</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="95" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B76" s="95" t="inlineStr">
-        <is>
-          <t>5:00PM</t>
-        </is>
-      </c>
-      <c r="C76" s="95" t="inlineStr">
-        <is>
-          <t>5:20PM</t>
-        </is>
-      </c>
-      <c r="D76" s="95" t="inlineStr">
-        <is>
-          <t>41 and above</t>
-        </is>
-      </c>
-      <c r="E76" s="95" t="n">
-        <v>34</v>
-      </c>
-      <c r="F76" s="95" t="inlineStr">
-        <is>
-          <t>41P-11</t>
-        </is>
-      </c>
-      <c r="G76" s="95" t="inlineStr">
-        <is>
-          <t>Board 2</t>
-        </is>
-      </c>
-      <c r="H76" s="95" t="inlineStr">
-        <is>
-          <t>Sachin Malgadnkar</t>
-        </is>
-      </c>
-      <c r="I76" s="95" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J76" s="95" t="inlineStr">
-        <is>
-          <t>Sanjay Kumar</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="94" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B77" s="94" t="inlineStr">
-        <is>
-          <t>5:20PM</t>
-        </is>
-      </c>
-      <c r="C77" s="94" t="inlineStr">
-        <is>
-          <t>5:40PM</t>
-        </is>
-      </c>
-      <c r="D77" s="94" t="inlineStr">
-        <is>
-          <t>21 to 40</t>
-        </is>
-      </c>
-      <c r="E77" s="94" t="n">
-        <v>35</v>
-      </c>
-      <c r="F77" s="94" t="inlineStr">
-        <is>
-          <t>2140-11</t>
-        </is>
-      </c>
-      <c r="G77" s="94" t="inlineStr">
-        <is>
-          <t>Board 1</t>
-        </is>
-      </c>
-      <c r="H77" s="94" t="inlineStr">
-        <is>
-          <t>Swati Tripathi</t>
-        </is>
-      </c>
-      <c r="I77" s="94" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J77" s="94" t="inlineStr">
-        <is>
-          <t>Nikunj Jhala</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="95" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B78" s="95" t="inlineStr">
-        <is>
-          <t>5:20PM</t>
-        </is>
-      </c>
-      <c r="C78" s="95" t="inlineStr">
-        <is>
-          <t>5:40PM</t>
-        </is>
-      </c>
-      <c r="D78" s="95" t="inlineStr">
-        <is>
-          <t>41 and above</t>
-        </is>
-      </c>
-      <c r="E78" s="95" t="n">
-        <v>36</v>
-      </c>
-      <c r="F78" s="95" t="inlineStr">
-        <is>
-          <t>41P-16</t>
-        </is>
-      </c>
-      <c r="G78" s="95" t="inlineStr">
-        <is>
-          <t>Board 2</t>
-        </is>
-      </c>
-      <c r="H78" s="95" t="inlineStr">
-        <is>
-          <t>Adil Khan</t>
-        </is>
-      </c>
-      <c r="I78" s="95" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J78" s="95" t="inlineStr">
-        <is>
-          <t>Harkishin malkan</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="94" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B79" s="94" t="inlineStr">
-        <is>
-          <t>5:40PM</t>
-        </is>
-      </c>
-      <c r="C79" s="94" t="inlineStr">
-        <is>
-          <t>6:00PM</t>
-        </is>
-      </c>
-      <c r="D79" s="94" t="inlineStr">
-        <is>
-          <t>12 to 20</t>
-        </is>
-      </c>
-      <c r="E79" s="94" t="n">
-        <v>37</v>
-      </c>
-      <c r="F79" s="94" t="inlineStr">
-        <is>
-          <t>1220-FINAL</t>
-        </is>
-      </c>
-      <c r="G79" s="94" t="inlineStr">
-        <is>
-          <t>Board 2</t>
-        </is>
-      </c>
-      <c r="H79" s="94" t="inlineStr">
-        <is>
-          <t>Pool 1st</t>
-        </is>
-      </c>
-      <c r="I79" s="94" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J79" s="94" t="inlineStr">
-        <is>
-          <t>Pool 2nd</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="95" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B80" s="95" t="inlineStr">
-        <is>
-          <t>5:40PM</t>
-        </is>
-      </c>
-      <c r="C80" s="95" t="inlineStr">
-        <is>
-          <t>6:00PM</t>
-        </is>
-      </c>
-      <c r="D80" s="95" t="inlineStr">
-        <is>
-          <t>41 and above</t>
-        </is>
-      </c>
-      <c r="E80" s="95" t="n">
-        <v>38</v>
-      </c>
-      <c r="F80" s="95" t="inlineStr">
-        <is>
-          <t>41P-17</t>
-        </is>
-      </c>
-      <c r="G80" s="95" t="inlineStr">
-        <is>
-          <t>Board 1</t>
-        </is>
-      </c>
-      <c r="H80" s="95" t="inlineStr">
-        <is>
-          <t>Sachin Malgadnkar</t>
-        </is>
-      </c>
-      <c r="I80" s="95" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J80" s="95" t="inlineStr">
-        <is>
-          <t>Ajit nair</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="94" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B81" s="94" t="inlineStr">
-        <is>
-          <t>6:00PM</t>
-        </is>
-      </c>
-      <c r="C81" s="94" t="inlineStr">
-        <is>
-          <t>6:20PM</t>
-        </is>
-      </c>
-      <c r="D81" s="94" t="inlineStr">
-        <is>
-          <t>21 to 40</t>
-        </is>
-      </c>
-      <c r="E81" s="94" t="n">
-        <v>39</v>
-      </c>
-      <c r="F81" s="94" t="inlineStr">
-        <is>
-          <t>2140-7</t>
-        </is>
-      </c>
-      <c r="G81" s="94" t="inlineStr">
-        <is>
-          <t>Board 1</t>
-        </is>
-      </c>
-      <c r="H81" s="94" t="inlineStr">
-        <is>
-          <t>Rahul Garg</t>
-        </is>
-      </c>
-      <c r="I81" s="94" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J81" s="94" t="inlineStr">
-        <is>
-          <t>Nikunj Jhala</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="95" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B82" s="95" t="inlineStr">
-        <is>
-          <t>6:00PM</t>
-        </is>
-      </c>
-      <c r="C82" s="95" t="inlineStr">
-        <is>
-          <t>6:20PM</t>
-        </is>
-      </c>
-      <c r="D82" s="95" t="inlineStr">
-        <is>
-          <t>41 and above</t>
-        </is>
-      </c>
-      <c r="E82" s="95" t="n">
-        <v>40</v>
-      </c>
-      <c r="F82" s="95" t="inlineStr">
-        <is>
-          <t>41P-18</t>
-        </is>
-      </c>
-      <c r="G82" s="95" t="inlineStr">
-        <is>
-          <t>Board 2</t>
-        </is>
-      </c>
-      <c r="H82" s="95" t="inlineStr">
-        <is>
-          <t>Piyush Makharia</t>
-        </is>
-      </c>
-      <c r="I82" s="95" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J82" s="95" t="inlineStr">
-        <is>
-          <t>Harkishin malkan</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="94" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B83" s="94" t="inlineStr">
-        <is>
-          <t>6:20PM</t>
-        </is>
-      </c>
-      <c r="C83" s="94" t="inlineStr">
-        <is>
-          <t>6:40PM</t>
-        </is>
-      </c>
-      <c r="D83" s="94" t="inlineStr">
-        <is>
-          <t>Under 11</t>
-        </is>
-      </c>
-      <c r="E83" s="94" t="n">
-        <v>41</v>
-      </c>
-      <c r="F83" s="94" t="inlineStr">
-        <is>
-          <t>U11-FINAL</t>
-        </is>
-      </c>
-      <c r="G83" s="94" t="inlineStr">
-        <is>
-          <t>Board 1</t>
-        </is>
-      </c>
-      <c r="H83" s="94" t="inlineStr">
-        <is>
-          <t>Pool 1st</t>
-        </is>
-      </c>
-      <c r="I83" s="94" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J83" s="94" t="inlineStr">
-        <is>
-          <t>Pool 2nd</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="95" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B84" s="95" t="inlineStr">
-        <is>
-          <t>6:30PM</t>
-        </is>
-      </c>
-      <c r="C84" s="95" t="inlineStr">
-        <is>
-          <t>6:50PM</t>
-        </is>
-      </c>
-      <c r="D84" s="95" t="inlineStr">
-        <is>
-          <t>21 to 40</t>
-        </is>
-      </c>
-      <c r="E84" s="95" t="n">
-        <v>42</v>
-      </c>
-      <c r="F84" s="95" t="inlineStr">
-        <is>
-          <t>2140-14</t>
-        </is>
-      </c>
-      <c r="G84" s="95" t="inlineStr">
-        <is>
-          <t>Board 2</t>
-        </is>
-      </c>
-      <c r="H84" s="95" t="inlineStr">
-        <is>
-          <t>Tej</t>
-        </is>
-      </c>
-      <c r="I84" s="95" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J84" s="95" t="inlineStr">
-        <is>
-          <t>Nikunj Jhala</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="94" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B85" s="94" t="inlineStr">
-        <is>
-          <t>6:40PM</t>
-        </is>
-      </c>
-      <c r="C85" s="94" t="inlineStr">
-        <is>
-          <t>7:00PM</t>
-        </is>
-      </c>
-      <c r="D85" s="94" t="inlineStr">
-        <is>
-          <t>41 and above</t>
-        </is>
-      </c>
-      <c r="E85" s="94" t="n">
-        <v>43</v>
-      </c>
-      <c r="F85" s="94" t="inlineStr">
-        <is>
-          <t>41P-7</t>
-        </is>
-      </c>
-      <c r="G85" s="94" t="inlineStr">
-        <is>
-          <t>Board 1</t>
-        </is>
-      </c>
-      <c r="H85" s="94" t="inlineStr">
-        <is>
-          <t>Piyush Makharia</t>
-        </is>
-      </c>
-      <c r="I85" s="94" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J85" s="94" t="inlineStr">
-        <is>
-          <t>Sachin Malgadnkar</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="95" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B86" s="95" t="inlineStr">
-        <is>
-          <t>6:50PM</t>
-        </is>
-      </c>
-      <c r="C86" s="95" t="inlineStr">
-        <is>
-          <t>7:10PM</t>
-        </is>
-      </c>
-      <c r="D86" s="95" t="inlineStr">
-        <is>
-          <t>41 and above</t>
-        </is>
-      </c>
-      <c r="E86" s="95" t="n">
-        <v>44</v>
-      </c>
-      <c r="F86" s="95" t="inlineStr">
-        <is>
-          <t>41P-20</t>
-        </is>
-      </c>
-      <c r="G86" s="95" t="inlineStr">
-        <is>
-          <t>Board 2</t>
-        </is>
-      </c>
-      <c r="H86" s="95" t="inlineStr">
-        <is>
-          <t>Ajit nair</t>
-        </is>
-      </c>
-      <c r="I86" s="95" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J86" s="95" t="inlineStr">
-        <is>
-          <t>Harkishin malkan</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="94" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B87" s="94" t="inlineStr">
-        <is>
-          <t>7:00PM</t>
-        </is>
-      </c>
-      <c r="C87" s="94" t="inlineStr">
-        <is>
-          <t>7:20PM</t>
-        </is>
-      </c>
-      <c r="D87" s="94" t="inlineStr">
-        <is>
-          <t>21 to 40</t>
-        </is>
-      </c>
-      <c r="E87" s="94" t="n">
-        <v>45</v>
-      </c>
-      <c r="F87" s="94" t="inlineStr">
-        <is>
-          <t>2140-8</t>
-        </is>
-      </c>
-      <c r="G87" s="94" t="inlineStr">
-        <is>
-          <t>Board 1</t>
-        </is>
-      </c>
-      <c r="H87" s="94" t="inlineStr">
-        <is>
-          <t>Tejas doshi</t>
-        </is>
-      </c>
-      <c r="I87" s="94" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J87" s="94" t="inlineStr">
-        <is>
-          <t>Nikunj Jhala</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="95" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B88" s="95" t="inlineStr">
-        <is>
-          <t>7:10PM</t>
-        </is>
-      </c>
-      <c r="C88" s="95" t="inlineStr">
-        <is>
-          <t>7:30PM</t>
-        </is>
-      </c>
-      <c r="D88" s="95" t="inlineStr">
-        <is>
-          <t>41 and above</t>
-        </is>
-      </c>
-      <c r="E88" s="95" t="n">
-        <v>46</v>
-      </c>
-      <c r="F88" s="95" t="inlineStr">
-        <is>
-          <t>41P-10</t>
-        </is>
-      </c>
-      <c r="G88" s="95" t="inlineStr">
-        <is>
-          <t>Board 2</t>
-        </is>
-      </c>
-      <c r="H88" s="95" t="inlineStr">
-        <is>
-          <t>Adil Khan</t>
-        </is>
-      </c>
-      <c r="I88" s="95" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J88" s="95" t="inlineStr">
-        <is>
-          <t>Prasad Akshintala</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="94" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B89" s="94" t="inlineStr">
-        <is>
-          <t>7:20PM</t>
-        </is>
-      </c>
-      <c r="C89" s="94" t="inlineStr">
-        <is>
-          <t>7:40PM</t>
-        </is>
-      </c>
-      <c r="D89" s="94" t="inlineStr">
-        <is>
-          <t>41 and above</t>
-        </is>
-      </c>
-      <c r="E89" s="94" t="n">
-        <v>47</v>
-      </c>
-      <c r="F89" s="94" t="inlineStr">
-        <is>
-          <t>41P-14</t>
-        </is>
-      </c>
-      <c r="G89" s="94" t="inlineStr">
-        <is>
-          <t>Board 1</t>
-        </is>
-      </c>
-      <c r="H89" s="94" t="inlineStr">
-        <is>
-          <t>Sanjay Kumar</t>
-        </is>
-      </c>
-      <c r="I89" s="94" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J89" s="94" t="inlineStr">
-        <is>
-          <t>Harkishin malkan</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="95" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B90" s="95" t="inlineStr">
-        <is>
-          <t>7:30PM</t>
-        </is>
-      </c>
-      <c r="C90" s="95" t="inlineStr">
-        <is>
-          <t>7:50PM</t>
-        </is>
-      </c>
-      <c r="D90" s="95" t="inlineStr">
-        <is>
-          <t>21 to 40</t>
-        </is>
-      </c>
-      <c r="E90" s="95" t="n">
-        <v>48</v>
-      </c>
-      <c r="F90" s="95" t="inlineStr">
-        <is>
-          <t>2140-FINAL</t>
-        </is>
-      </c>
-      <c r="G90" s="95" t="inlineStr">
-        <is>
-          <t>Board 2</t>
-        </is>
-      </c>
-      <c r="H90" s="95" t="inlineStr">
-        <is>
-          <t>Pool 1st</t>
-        </is>
-      </c>
-      <c r="I90" s="95" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J90" s="95" t="inlineStr">
-        <is>
-          <t>Pool 2nd</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="94" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B91" s="94" t="inlineStr">
-        <is>
-          <t>7:40PM</t>
-        </is>
-      </c>
-      <c r="C91" s="94" t="inlineStr">
-        <is>
-          <t>8:00PM</t>
-        </is>
-      </c>
-      <c r="D91" s="94" t="inlineStr">
-        <is>
-          <t>41 and above</t>
-        </is>
-      </c>
-      <c r="E91" s="94" t="n">
-        <v>49</v>
-      </c>
-      <c r="F91" s="94" t="inlineStr">
-        <is>
-          <t>41P-5</t>
-        </is>
-      </c>
-      <c r="G91" s="94" t="inlineStr">
-        <is>
-          <t>Board 1</t>
-        </is>
-      </c>
-      <c r="H91" s="94" t="inlineStr">
-        <is>
-          <t>Prasad Akshintala</t>
-        </is>
-      </c>
-      <c r="I91" s="94" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J91" s="94" t="inlineStr">
-        <is>
-          <t>Ajit nair</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="95" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B92" s="95" t="inlineStr">
-        <is>
-          <t>7:50PM</t>
-        </is>
-      </c>
-      <c r="C92" s="95" t="inlineStr">
-        <is>
-          <t>8:10PM</t>
-        </is>
-      </c>
-      <c r="D92" s="95" t="inlineStr">
-        <is>
-          <t>41 and above</t>
-        </is>
-      </c>
-      <c r="E92" s="95" t="n">
-        <v>50</v>
-      </c>
-      <c r="F92" s="95" t="inlineStr">
-        <is>
-          <t>41P-21</t>
-        </is>
-      </c>
-      <c r="G92" s="95" t="inlineStr">
-        <is>
-          <t>Board 2</t>
-        </is>
-      </c>
-      <c r="H92" s="95" t="inlineStr">
-        <is>
-          <t>Sachin Malgadnkar</t>
-        </is>
-      </c>
-      <c r="I92" s="95" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J92" s="95" t="inlineStr">
-        <is>
-          <t>Harkishin malkan</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="94" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B93" s="94" t="inlineStr">
-        <is>
-          <t>8:10PM</t>
-        </is>
-      </c>
-      <c r="C93" s="94" t="inlineStr">
-        <is>
-          <t>8:30PM</t>
-        </is>
-      </c>
-      <c r="D93" s="94" t="inlineStr">
-        <is>
-          <t>41 and above</t>
-        </is>
-      </c>
-      <c r="E93" s="94" t="n">
-        <v>51</v>
-      </c>
-      <c r="F93" s="94" t="inlineStr">
-        <is>
-          <t>41P-4</t>
-        </is>
-      </c>
-      <c r="G93" s="94" t="inlineStr">
-        <is>
-          <t>Board 1</t>
-        </is>
-      </c>
-      <c r="H93" s="94" t="inlineStr">
-        <is>
-          <t>Piyush Makharia</t>
-        </is>
-      </c>
-      <c r="I93" s="94" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J93" s="94" t="inlineStr">
-        <is>
-          <t>Sanjay Kumar</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="95" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B94" s="95" t="inlineStr">
-        <is>
-          <t>8:20PM</t>
-        </is>
-      </c>
-      <c r="C94" s="95" t="inlineStr">
-        <is>
-          <t>8:40PM</t>
-        </is>
-      </c>
-      <c r="D94" s="95" t="inlineStr">
-        <is>
-          <t>41 and above</t>
-        </is>
-      </c>
-      <c r="E94" s="95" t="n">
-        <v>52</v>
-      </c>
-      <c r="F94" s="95" t="inlineStr">
-        <is>
-          <t>41P-13</t>
-        </is>
-      </c>
-      <c r="G94" s="95" t="inlineStr">
-        <is>
-          <t>Board 2</t>
-        </is>
-      </c>
-      <c r="H94" s="95" t="inlineStr">
-        <is>
-          <t>Sachin Malgadnkar</t>
-        </is>
-      </c>
-      <c r="I94" s="95" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J94" s="95" t="inlineStr">
-        <is>
-          <t>Prasad Akshintala</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="94" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B95" s="94" t="inlineStr">
-        <is>
-          <t>8:55PM</t>
-        </is>
-      </c>
-      <c r="C95" s="94" t="inlineStr">
-        <is>
-          <t>9:15PM</t>
-        </is>
-      </c>
-      <c r="D95" s="94" t="inlineStr">
-        <is>
-          <t>41 and above</t>
-        </is>
-      </c>
-      <c r="E95" s="94" t="n">
-        <v>53</v>
-      </c>
-      <c r="F95" s="94" t="inlineStr">
-        <is>
-          <t>41P-15</t>
-        </is>
-      </c>
-      <c r="G95" s="94" t="inlineStr">
-        <is>
-          <t>Board 1</t>
-        </is>
-      </c>
-      <c r="H95" s="94" t="inlineStr">
-        <is>
-          <t>Adil Khan</t>
-        </is>
-      </c>
-      <c r="I95" s="94" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J95" s="94" t="inlineStr">
-        <is>
-          <t>Sachin Malgadnkar</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="95" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B96" s="95" t="inlineStr">
-        <is>
-          <t>9:35PM</t>
-        </is>
-      </c>
-      <c r="C96" s="95" t="inlineStr">
-        <is>
-          <t>9:55PM</t>
-        </is>
-      </c>
-      <c r="D96" s="95" t="inlineStr">
-        <is>
-          <t>41 and above</t>
-        </is>
-      </c>
-      <c r="E96" s="95" t="n">
-        <v>54</v>
-      </c>
-      <c r="F96" s="95" t="inlineStr">
-        <is>
-          <t>41P-19</t>
-        </is>
-      </c>
-      <c r="G96" s="95" t="inlineStr">
-        <is>
-          <t>Board 2</t>
-        </is>
-      </c>
-      <c r="H96" s="95" t="inlineStr">
-        <is>
-          <t>Prasad Akshintala</t>
-        </is>
-      </c>
-      <c r="I96" s="95" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J96" s="95" t="inlineStr">
-        <is>
-          <t>Harkishin malkan</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="94" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B97" s="94" t="inlineStr">
-        <is>
-          <t>9:35PM</t>
-        </is>
-      </c>
-      <c r="C97" s="94" t="inlineStr">
-        <is>
-          <t>9:55PM</t>
-        </is>
-      </c>
-      <c r="D97" s="94" t="inlineStr">
-        <is>
-          <t>41 and above</t>
-        </is>
-      </c>
-      <c r="E97" s="94" t="n">
-        <v>55</v>
-      </c>
-      <c r="F97" s="94" t="inlineStr">
-        <is>
-          <t>41P-9</t>
-        </is>
-      </c>
-      <c r="G97" s="94" t="inlineStr">
-        <is>
-          <t>Board 1</t>
-        </is>
-      </c>
-      <c r="H97" s="94" t="inlineStr">
-        <is>
-          <t>Adil Khan</t>
-        </is>
-      </c>
-      <c r="I97" s="94" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J97" s="94" t="inlineStr">
-        <is>
-          <t>Sanjay Kumar</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="95" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B98" s="95" t="inlineStr">
-        <is>
-          <t>9:55PM</t>
-        </is>
-      </c>
-      <c r="C98" s="95" t="inlineStr">
-        <is>
-          <t>10:15PM</t>
-        </is>
-      </c>
-      <c r="D98" s="95" t="inlineStr">
-        <is>
-          <t>41 and above</t>
-        </is>
-      </c>
-      <c r="E98" s="95" t="n">
-        <v>56</v>
-      </c>
-      <c r="F98" s="95" t="inlineStr">
-        <is>
-          <t>41P-SF1</t>
-        </is>
-      </c>
-      <c r="G98" s="95" t="inlineStr">
-        <is>
-          <t>Board 1</t>
-        </is>
-      </c>
-      <c r="H98" s="95" t="inlineStr">
-        <is>
-          <t>Round Robin 1st</t>
-        </is>
-      </c>
-      <c r="I98" s="95" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J98" s="95" t="inlineStr">
-        <is>
-          <t>Round Robin 4th</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="94" t="inlineStr">
-        <is>
-          <t>Aug 15</t>
-        </is>
-      </c>
-      <c r="B99" s="94" t="inlineStr">
-        <is>
-          <t>9:55PM</t>
-        </is>
-      </c>
-      <c r="C99" s="94" t="inlineStr">
-        <is>
-          <t>10:15PM</t>
-        </is>
-      </c>
-      <c r="D99" s="94" t="inlineStr">
-        <is>
-          <t>41 and above</t>
-        </is>
-      </c>
-      <c r="E99" s="94" t="n">
-        <v>57</v>
-      </c>
-      <c r="F99" s="94" t="inlineStr">
-        <is>
-          <t>41P-SF2</t>
-        </is>
-      </c>
-      <c r="G99" s="94" t="inlineStr">
-        <is>
-          <t>Board 2</t>
-        </is>
-      </c>
-      <c r="H99" s="94" t="inlineStr">
-        <is>
-          <t>Round Robin 2nd</t>
-        </is>
-      </c>
-      <c r="I99" s="94" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J99" s="94" t="inlineStr">
-        <is>
-          <t>Round Robin 3rd</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="95" t="inlineStr">
-        <is>
-          <t>Aug 16</t>
-        </is>
-      </c>
-      <c r="B100" s="95" t="inlineStr">
-        <is>
-          <t>8:00AM</t>
-        </is>
-      </c>
-      <c r="C100" s="95" t="inlineStr">
-        <is>
-          <t>8:20AM</t>
-        </is>
-      </c>
-      <c r="D100" s="95" t="inlineStr">
-        <is>
-          <t>41 and above</t>
-        </is>
-      </c>
-      <c r="E100" s="95" t="n">
-        <v>58</v>
-      </c>
-      <c r="F100" s="95" t="inlineStr">
-        <is>
-          <t>41P-FINAL</t>
-        </is>
-      </c>
-      <c r="G100" s="95" t="inlineStr">
-        <is>
-          <t>Board 1</t>
-        </is>
-      </c>
-      <c r="H100" s="95" t="inlineStr">
-        <is>
-          <t>Winner SF1</t>
-        </is>
-      </c>
-      <c r="I100" s="95" t="inlineStr">
-        <is>
-          <t>vs</t>
-        </is>
-      </c>
-      <c r="J100" s="95" t="inlineStr">
-        <is>
-          <t>Winner SF2</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A21:J21"/>
-    <mergeCell ref="A30:J30"/>
-    <mergeCell ref="A4:J4"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A41:J41"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>